--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2967.4</v>
+        <v>2941.2</v>
       </c>
       <c r="C2" t="n">
-        <v>2991.1</v>
+        <v>2979.8</v>
       </c>
       <c r="D2" t="n">
-        <v>2938.3</v>
+        <v>2910.3</v>
       </c>
       <c r="E2" t="n">
-        <v>2942.8</v>
+        <v>2919.6</v>
       </c>
       <c r="F2" t="n">
-        <v>-25.4</v>
+        <v>-23.2</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0086</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>52.8</v>
+        <v>69.5</v>
       </c>
       <c r="I2" t="n">
-        <v>2920.4</v>
+        <v>2885.5</v>
       </c>
       <c r="J2" t="n">
-        <v>2918.07</v>
+        <v>2879.05</v>
       </c>
       <c r="K2" t="n">
-        <v>2947.05</v>
+        <v>2916.4</v>
       </c>
       <c r="L2" t="n">
-        <v>2976.02</v>
+        <v>2953.75</v>
       </c>
       <c r="M2" t="n">
-        <v>2989.35</v>
+        <v>2969.2</v>
       </c>
       <c r="N2" t="n">
-        <v>3002.67</v>
+        <v>2984.65</v>
       </c>
       <c r="O2" t="n">
-        <v>3047.3</v>
+        <v>3043.9</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -727,50 +727,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2941.2</v>
+        <v>2925</v>
       </c>
       <c r="C3" t="n">
-        <v>2979.8</v>
+        <v>2972.3</v>
       </c>
       <c r="D3" t="n">
-        <v>2910.3</v>
+        <v>2925</v>
       </c>
       <c r="E3" t="n">
-        <v>2919.6</v>
+        <v>2960.73</v>
       </c>
       <c r="F3" t="n">
-        <v>-23.2</v>
+        <v>41.13</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0141</v>
       </c>
       <c r="H3" t="n">
-        <v>69.5</v>
+        <v>47.3</v>
       </c>
       <c r="I3" t="n">
-        <v>2885.5</v>
+        <v>2840.8</v>
       </c>
       <c r="J3" t="n">
-        <v>2879.05</v>
+        <v>2837.38</v>
       </c>
       <c r="K3" t="n">
-        <v>2916.4</v>
+        <v>2884.85</v>
       </c>
       <c r="L3" t="n">
-        <v>2953.75</v>
+        <v>2932.33</v>
       </c>
       <c r="M3" t="n">
-        <v>2969.2</v>
+        <v>2954.35</v>
       </c>
       <c r="N3" t="n">
-        <v>2984.65</v>
+        <v>2976.38</v>
       </c>
       <c r="O3" t="n">
-        <v>3043.9</v>
+        <v>3049.3</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -778,21 +778,19 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
@@ -806,57 +804,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2925</v>
+        <v>2989.9</v>
       </c>
       <c r="C4" t="n">
-        <v>2972.3</v>
+        <v>3039</v>
       </c>
       <c r="D4" t="n">
-        <v>2925</v>
+        <v>2970.8</v>
       </c>
       <c r="E4" t="n">
-        <v>2960.73</v>
+        <v>3024.1</v>
       </c>
       <c r="F4" t="n">
-        <v>41.13</v>
+        <v>63.37</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0141</v>
+        <v>0.0214</v>
       </c>
       <c r="H4" t="n">
-        <v>47.3</v>
+        <v>68.2</v>
       </c>
       <c r="I4" t="n">
-        <v>2840.8</v>
+        <v>2877.7</v>
       </c>
       <c r="J4" t="n">
-        <v>2837.38</v>
+        <v>2919.47</v>
       </c>
       <c r="K4" t="n">
-        <v>2884.85</v>
+        <v>2937.08</v>
       </c>
       <c r="L4" t="n">
-        <v>2932.33</v>
+        <v>2954.69</v>
       </c>
       <c r="M4" t="n">
-        <v>2954.35</v>
+        <v>2984.38</v>
       </c>
       <c r="N4" t="n">
-        <v>2976.38</v>
+        <v>3014.07</v>
       </c>
       <c r="O4" t="n">
-        <v>3049.3</v>
+        <v>3019.6</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -874,179 +872,179 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
-      </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2989.9</v>
+        <v>3022.4</v>
       </c>
       <c r="C5" t="n">
-        <v>3039</v>
+        <v>3028.4</v>
       </c>
       <c r="D5" t="n">
-        <v>2970.8</v>
+        <v>2965.2</v>
       </c>
       <c r="E5" t="n">
-        <v>3024.1</v>
+        <v>2998.2</v>
       </c>
       <c r="F5" t="n">
-        <v>63.37</v>
+        <v>-25.9</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0214</v>
+        <v>-0.0086</v>
       </c>
       <c r="H5" t="n">
-        <v>68.2</v>
+        <v>63.2</v>
       </c>
       <c r="I5" t="n">
-        <v>2877.7</v>
+        <v>2902.6</v>
       </c>
       <c r="J5" t="n">
-        <v>2919.47</v>
+        <v>2965.5</v>
       </c>
       <c r="K5" t="n">
-        <v>2937.08</v>
+        <v>2990</v>
       </c>
       <c r="L5" t="n">
-        <v>2954.69</v>
+        <v>3014.5</v>
       </c>
       <c r="M5" t="n">
-        <v>2984.38</v>
+        <v>3058.2</v>
       </c>
       <c r="N5" t="n">
-        <v>3014.07</v>
+        <v>3101.9</v>
       </c>
       <c r="O5" t="n">
-        <v>3019.6</v>
+        <v>3107.2</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
+      <c r="Q5" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
+      </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3022.4</v>
+        <v>2998.4</v>
       </c>
       <c r="C6" t="n">
-        <v>3028.4</v>
+        <v>3041.4</v>
       </c>
       <c r="D6" t="n">
-        <v>2965.2</v>
+        <v>2987.2</v>
       </c>
       <c r="E6" t="n">
-        <v>2998.2</v>
+        <v>3013.5</v>
       </c>
       <c r="F6" t="n">
-        <v>-25.9</v>
+        <v>15.3</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0051</v>
       </c>
       <c r="H6" t="n">
-        <v>63.2</v>
+        <v>54.2</v>
       </c>
       <c r="I6" t="n">
-        <v>2902.6</v>
+        <v>2902</v>
       </c>
       <c r="J6" t="n">
-        <v>2965.5</v>
+        <v>2935.7</v>
       </c>
       <c r="K6" t="n">
-        <v>2990</v>
+        <v>2966.6</v>
       </c>
       <c r="L6" t="n">
-        <v>3014.5</v>
+        <v>2997.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3058.2</v>
+        <v>3029.8</v>
       </c>
       <c r="N6" t="n">
-        <v>3101.9</v>
+        <v>3062.1</v>
       </c>
       <c r="O6" t="n">
-        <v>3107.2</v>
+        <v>3091.6</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1058,59 +1056,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2998.4</v>
+        <v>3023.7</v>
       </c>
       <c r="C7" t="n">
-        <v>3041.4</v>
+        <v>3062.4</v>
       </c>
       <c r="D7" t="n">
-        <v>2987.2</v>
+        <v>3010.5</v>
       </c>
       <c r="E7" t="n">
-        <v>3013.5</v>
+        <v>3030.7</v>
       </c>
       <c r="F7" t="n">
-        <v>15.3</v>
+        <v>17.2</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0057</v>
       </c>
       <c r="H7" t="n">
-        <v>54.2</v>
+        <v>51.9</v>
       </c>
       <c r="I7" t="n">
-        <v>2902</v>
+        <v>2933</v>
       </c>
       <c r="J7" t="n">
-        <v>2935.7</v>
+        <v>2958.9</v>
       </c>
       <c r="K7" t="n">
-        <v>2966.6</v>
+        <v>2986.4</v>
       </c>
       <c r="L7" t="n">
-        <v>2997.5</v>
+        <v>3013.9</v>
       </c>
       <c r="M7" t="n">
-        <v>3029.8</v>
+        <v>3040.6</v>
       </c>
       <c r="N7" t="n">
-        <v>3062.1</v>
+        <v>3067.3</v>
       </c>
       <c r="O7" t="n">
-        <v>3091.6</v>
+        <v>3095.6</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1123,12 +1117,12 @@
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U7" s="8" t="n">
@@ -1147,50 +1141,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3023.7</v>
+        <v>3034.7</v>
       </c>
       <c r="C8" t="n">
-        <v>3062.4</v>
+        <v>3045.7</v>
       </c>
       <c r="D8" t="n">
-        <v>3010.5</v>
+        <v>2999.6</v>
       </c>
       <c r="E8" t="n">
-        <v>3030.7</v>
+        <v>3022.6</v>
       </c>
       <c r="F8" t="n">
-        <v>17.2</v>
+        <v>-8.1</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.0027</v>
       </c>
       <c r="H8" t="n">
-        <v>51.9</v>
+        <v>46.1</v>
       </c>
       <c r="I8" t="n">
-        <v>2933</v>
+        <v>2958.6</v>
       </c>
       <c r="J8" t="n">
-        <v>2958.9</v>
+        <v>2975.93</v>
       </c>
       <c r="K8" t="n">
-        <v>2986.4</v>
+        <v>3004.75</v>
       </c>
       <c r="L8" t="n">
-        <v>3013.9</v>
+        <v>3033.57</v>
       </c>
       <c r="M8" t="n">
-        <v>3040.6</v>
+        <v>3056.65</v>
       </c>
       <c r="N8" t="n">
-        <v>3067.3</v>
+        <v>3079.72</v>
       </c>
       <c r="O8" t="n">
-        <v>3095.6</v>
+        <v>3114.3</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1198,18 +1192,18 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1222,55 +1216,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3034.7</v>
+        <v>3020.9</v>
       </c>
       <c r="C9" t="n">
-        <v>3045.7</v>
+        <v>3044.9</v>
       </c>
       <c r="D9" t="n">
-        <v>2999.6</v>
+        <v>2987.8</v>
       </c>
       <c r="E9" t="n">
-        <v>3022.6</v>
+        <v>3030.6</v>
       </c>
       <c r="F9" t="n">
-        <v>-8.1</v>
+        <v>8</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0026</v>
       </c>
       <c r="H9" t="n">
-        <v>46.1</v>
+        <v>57.1</v>
       </c>
       <c r="I9" t="n">
-        <v>2958.6</v>
+        <v>2953.5</v>
       </c>
       <c r="J9" t="n">
-        <v>2975.93</v>
+        <v>2976.48</v>
       </c>
       <c r="K9" t="n">
-        <v>3004.75</v>
+        <v>2999.55</v>
       </c>
       <c r="L9" t="n">
-        <v>3033.57</v>
+        <v>3022.63</v>
       </c>
       <c r="M9" t="n">
-        <v>3056.65</v>
+        <v>3045.65</v>
       </c>
       <c r="N9" t="n">
-        <v>3079.72</v>
+        <v>3068.67</v>
       </c>
       <c r="O9" t="n">
-        <v>3114.3</v>
+        <v>3091.8</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1283,9 +1281,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1304,57 +1302,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3020.9</v>
+        <v>3026.1</v>
       </c>
       <c r="C10" t="n">
-        <v>3044.9</v>
+        <v>3050.6</v>
       </c>
       <c r="D10" t="n">
-        <v>2987.8</v>
+        <v>3015.1</v>
       </c>
       <c r="E10" t="n">
-        <v>3030.6</v>
+        <v>3045.6</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0049</v>
       </c>
       <c r="H10" t="n">
-        <v>57.1</v>
+        <v>35.5</v>
       </c>
       <c r="I10" t="n">
-        <v>2953.5</v>
+        <v>2930.7</v>
       </c>
       <c r="J10" t="n">
-        <v>2976.48</v>
+        <v>2980.63</v>
       </c>
       <c r="K10" t="n">
-        <v>2999.55</v>
+        <v>3002.05</v>
       </c>
       <c r="L10" t="n">
-        <v>3022.63</v>
+        <v>3023.48</v>
       </c>
       <c r="M10" t="n">
-        <v>3045.65</v>
+        <v>3059.15</v>
       </c>
       <c r="N10" t="n">
-        <v>3068.67</v>
+        <v>3094.83</v>
       </c>
       <c r="O10" t="n">
-        <v>3091.8</v>
+        <v>3102</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1362,18 +1360,18 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1386,59 +1384,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3026.1</v>
+        <v>3040</v>
       </c>
       <c r="C11" t="n">
-        <v>3050.6</v>
+        <v>3068.4</v>
       </c>
       <c r="D11" t="n">
-        <v>3015.1</v>
+        <v>3023.7</v>
       </c>
       <c r="E11" t="n">
-        <v>3045.6</v>
+        <v>3035.1</v>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>-10.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.0034</v>
       </c>
       <c r="H11" t="n">
-        <v>35.5</v>
+        <v>44.7</v>
       </c>
       <c r="I11" t="n">
-        <v>2930.7</v>
+        <v>2979.6</v>
       </c>
       <c r="J11" t="n">
-        <v>2980.63</v>
+        <v>3016.48</v>
       </c>
       <c r="K11" t="n">
-        <v>3002.05</v>
+        <v>3027.85</v>
       </c>
       <c r="L11" t="n">
-        <v>3023.48</v>
+        <v>3039.23</v>
       </c>
       <c r="M11" t="n">
-        <v>3059.15</v>
+        <v>3063.35</v>
       </c>
       <c r="N11" t="n">
-        <v>3094.83</v>
+        <v>3087.48</v>
       </c>
       <c r="O11" t="n">
-        <v>3102</v>
+        <v>3086.1</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1446,17 +1440,19 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U11" s="8" t="n">
@@ -1470,55 +1466,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3040</v>
+        <v>3030.9</v>
       </c>
       <c r="C12" t="n">
-        <v>3068.4</v>
+        <v>3062.4</v>
       </c>
       <c r="D12" t="n">
-        <v>3023.7</v>
+        <v>2988.5</v>
       </c>
       <c r="E12" t="n">
-        <v>3035.1</v>
+        <v>3014.2</v>
       </c>
       <c r="F12" t="n">
-        <v>-10.5</v>
+        <v>-20.9</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0069</v>
       </c>
       <c r="H12" t="n">
-        <v>44.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>2979.6</v>
+        <v>2979</v>
       </c>
       <c r="J12" t="n">
-        <v>3016.48</v>
+        <v>2984.93</v>
       </c>
       <c r="K12" t="n">
-        <v>3027.85</v>
+        <v>3012.75</v>
       </c>
       <c r="L12" t="n">
-        <v>3039.23</v>
+        <v>3040.58</v>
       </c>
       <c r="M12" t="n">
-        <v>3063.35</v>
+        <v>3057.45</v>
       </c>
       <c r="N12" t="n">
-        <v>3087.48</v>
+        <v>3074.33</v>
       </c>
       <c r="O12" t="n">
-        <v>3086.1</v>
+        <v>3113.1</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1528,19 +1528,19 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1554,57 +1554,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3030.9</v>
+        <v>3019.7</v>
       </c>
       <c r="C13" t="n">
-        <v>3062.4</v>
+        <v>3042.1</v>
       </c>
       <c r="D13" t="n">
-        <v>2988.5</v>
+        <v>3006.7</v>
       </c>
       <c r="E13" t="n">
-        <v>3014.2</v>
+        <v>3027</v>
       </c>
       <c r="F13" t="n">
-        <v>-20.9</v>
+        <v>12.8</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0042</v>
       </c>
       <c r="H13" t="n">
-        <v>73.90000000000001</v>
+        <v>35.4</v>
       </c>
       <c r="I13" t="n">
-        <v>2979</v>
+        <v>2914.6</v>
       </c>
       <c r="J13" t="n">
-        <v>2984.93</v>
+        <v>2934.68</v>
       </c>
       <c r="K13" t="n">
-        <v>3012.75</v>
+        <v>2977.25</v>
       </c>
       <c r="L13" t="n">
-        <v>3040.58</v>
+        <v>3019.82</v>
       </c>
       <c r="M13" t="n">
-        <v>3057.45</v>
+        <v>3051.15</v>
       </c>
       <c r="N13" t="n">
-        <v>3074.33</v>
+        <v>3082.47</v>
       </c>
       <c r="O13" t="n">
-        <v>3113.1</v>
+        <v>3136.3</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1612,20 +1612,16 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1640,70 +1636,74 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3019.7</v>
+        <v>3033.4</v>
       </c>
       <c r="C14" t="n">
-        <v>3042.1</v>
+        <v>3042.6</v>
       </c>
       <c r="D14" t="n">
-        <v>3006.7</v>
+        <v>2988.8</v>
       </c>
       <c r="E14" t="n">
-        <v>3027</v>
+        <v>2998.8</v>
       </c>
       <c r="F14" t="n">
-        <v>12.8</v>
+        <v>-28.2</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>35.4</v>
+        <v>53.8</v>
       </c>
       <c r="I14" t="n">
-        <v>2914.6</v>
+        <v>2971.3</v>
       </c>
       <c r="J14" t="n">
-        <v>2934.68</v>
+        <v>2992.9</v>
       </c>
       <c r="K14" t="n">
-        <v>2977.25</v>
+        <v>3009.3</v>
       </c>
       <c r="L14" t="n">
-        <v>3019.82</v>
+        <v>3025.7</v>
       </c>
       <c r="M14" t="n">
-        <v>3051.15</v>
+        <v>3044.7</v>
       </c>
       <c r="N14" t="n">
-        <v>3082.47</v>
+        <v>3063.7</v>
       </c>
       <c r="O14" t="n">
-        <v>3136.3</v>
+        <v>3077.5</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1722,71 +1722,69 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3033.4</v>
+        <v>2994.3</v>
       </c>
       <c r="C15" t="n">
-        <v>3042.6</v>
+        <v>3004.3</v>
       </c>
       <c r="D15" t="n">
-        <v>2988.8</v>
+        <v>2943.4</v>
       </c>
       <c r="E15" t="n">
-        <v>2998.8</v>
+        <v>2971.5</v>
       </c>
       <c r="F15" t="n">
-        <v>-28.2</v>
+        <v>-27.3</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0091</v>
       </c>
       <c r="H15" t="n">
-        <v>53.8</v>
+        <v>60.9</v>
       </c>
       <c r="I15" t="n">
-        <v>2971.3</v>
+        <v>2935</v>
       </c>
       <c r="J15" t="n">
-        <v>2992.9</v>
+        <v>2936.55</v>
       </c>
       <c r="K15" t="n">
-        <v>3009.3</v>
+        <v>2971.9</v>
       </c>
       <c r="L15" t="n">
+        <v>3007.25</v>
+      </c>
+      <c r="M15" t="n">
         <v>3025.7</v>
       </c>
-      <c r="M15" t="n">
-        <v>3044.7</v>
-      </c>
       <c r="N15" t="n">
-        <v>3063.7</v>
+        <v>3044.15</v>
       </c>
       <c r="O15" t="n">
-        <v>3077.5</v>
+        <v>3096.4</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -1808,57 +1806,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2994.3</v>
+        <v>2965.8</v>
       </c>
       <c r="C16" t="n">
-        <v>3004.3</v>
+        <v>3014.9</v>
       </c>
       <c r="D16" t="n">
-        <v>2943.4</v>
+        <v>2964.3</v>
       </c>
       <c r="E16" t="n">
-        <v>2971.5</v>
+        <v>3008.4</v>
       </c>
       <c r="F16" t="n">
-        <v>-27.3</v>
+        <v>36.9</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0091</v>
+        <v>0.0124</v>
       </c>
       <c r="H16" t="n">
-        <v>60.9</v>
+        <v>50.6</v>
       </c>
       <c r="I16" t="n">
-        <v>2935</v>
+        <v>2882.5</v>
       </c>
       <c r="J16" t="n">
-        <v>2936.55</v>
+        <v>2909.42</v>
       </c>
       <c r="K16" t="n">
-        <v>2971.9</v>
+        <v>2941.05</v>
       </c>
       <c r="L16" t="n">
-        <v>3007.25</v>
+        <v>2972.67</v>
       </c>
       <c r="M16" t="n">
-        <v>3025.7</v>
+        <v>3001.95</v>
       </c>
       <c r="N16" t="n">
-        <v>3044.15</v>
+        <v>3031.23</v>
       </c>
       <c r="O16" t="n">
-        <v>3096.4</v>
+        <v>3065.2</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1866,19 +1864,19 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
@@ -1890,59 +1888,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2965.8</v>
+        <v>3008.1</v>
       </c>
       <c r="C17" t="n">
-        <v>3014.9</v>
+        <v>3019.5</v>
       </c>
       <c r="D17" t="n">
-        <v>2964.3</v>
+        <v>2970.8</v>
       </c>
       <c r="E17" t="n">
-        <v>3008.4</v>
+        <v>2994</v>
       </c>
       <c r="F17" t="n">
-        <v>36.9</v>
+        <v>-14.4</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0048</v>
       </c>
       <c r="H17" t="n">
-        <v>50.6</v>
+        <v>48.7</v>
       </c>
       <c r="I17" t="n">
-        <v>2882.5</v>
+        <v>2913.7</v>
       </c>
       <c r="J17" t="n">
-        <v>2909.42</v>
+        <v>2967.2</v>
       </c>
       <c r="K17" t="n">
-        <v>2941.05</v>
+        <v>2983.1</v>
       </c>
       <c r="L17" t="n">
-        <v>2972.67</v>
+        <v>2999</v>
       </c>
       <c r="M17" t="n">
-        <v>3001.95</v>
+        <v>3033.7</v>
       </c>
       <c r="N17" t="n">
-        <v>3031.23</v>
+        <v>3068.4</v>
       </c>
       <c r="O17" t="n">
-        <v>3065.2</v>
+        <v>3065.5</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1950,18 +1944,18 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1974,55 +1968,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3008.1</v>
+        <v>2984.7</v>
       </c>
       <c r="C18" t="n">
-        <v>3019.5</v>
+        <v>2995.8</v>
       </c>
       <c r="D18" t="n">
-        <v>2970.8</v>
+        <v>2961.8</v>
       </c>
       <c r="E18" t="n">
-        <v>2994</v>
+        <v>2970.4</v>
       </c>
       <c r="F18" t="n">
-        <v>-14.4</v>
+        <v>-23.6</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>48.7</v>
+        <v>34</v>
       </c>
       <c r="I18" t="n">
-        <v>2913.7</v>
+        <v>2922.1</v>
       </c>
       <c r="J18" t="n">
-        <v>2967.2</v>
+        <v>2944.73</v>
       </c>
       <c r="K18" t="n">
-        <v>2983.1</v>
+        <v>2969.65</v>
       </c>
       <c r="L18" t="n">
-        <v>2999</v>
+        <v>2994.58</v>
       </c>
       <c r="M18" t="n">
-        <v>3033.7</v>
+        <v>3018.35</v>
       </c>
       <c r="N18" t="n">
-        <v>3068.4</v>
+        <v>3042.12</v>
       </c>
       <c r="O18" t="n">
-        <v>3065.5</v>
+        <v>3068.2</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2032,12 +2030,12 @@
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2056,57 +2054,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2984.7</v>
+        <v>2967.2</v>
       </c>
       <c r="C19" t="n">
-        <v>2995.8</v>
+        <v>3029.8</v>
       </c>
       <c r="D19" t="n">
-        <v>2961.8</v>
+        <v>2956.2</v>
       </c>
       <c r="E19" t="n">
-        <v>2970.4</v>
+        <v>2979.9</v>
       </c>
       <c r="F19" t="n">
-        <v>-23.6</v>
+        <v>9.5</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H19" t="n">
-        <v>34</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>2922.1</v>
+        <v>2927.8</v>
       </c>
       <c r="J19" t="n">
-        <v>2944.73</v>
+        <v>2932.2</v>
       </c>
       <c r="K19" t="n">
-        <v>2969.65</v>
+        <v>2953.4</v>
       </c>
       <c r="L19" t="n">
-        <v>2994.58</v>
+        <v>2974.6</v>
       </c>
       <c r="M19" t="n">
-        <v>3018.35</v>
+        <v>2987.4</v>
       </c>
       <c r="N19" t="n">
-        <v>3042.12</v>
+        <v>3000.2</v>
       </c>
       <c r="O19" t="n">
-        <v>3068.2</v>
+        <v>3029.8</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2114,24 +2112,28 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
@@ -2140,57 +2142,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2967.2</v>
+        <v>2981.2</v>
       </c>
       <c r="C20" t="n">
-        <v>3029.8</v>
+        <v>3006.1</v>
       </c>
       <c r="D20" t="n">
-        <v>2956.2</v>
+        <v>2974.4</v>
       </c>
       <c r="E20" t="n">
-        <v>2979.9</v>
+        <v>2991.8</v>
       </c>
       <c r="F20" t="n">
-        <v>9.5</v>
+        <v>11.9</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.004</v>
       </c>
       <c r="H20" t="n">
-        <v>73.59999999999999</v>
+        <v>31.7</v>
       </c>
       <c r="I20" t="n">
-        <v>2927.8</v>
+        <v>2882.6</v>
       </c>
       <c r="J20" t="n">
-        <v>2932.2</v>
+        <v>2899.75</v>
       </c>
       <c r="K20" t="n">
-        <v>2953.4</v>
+        <v>2943.1</v>
       </c>
       <c r="L20" t="n">
-        <v>2974.6</v>
+        <v>2986.45</v>
       </c>
       <c r="M20" t="n">
-        <v>2987.4</v>
+        <v>3016.7</v>
       </c>
       <c r="N20" t="n">
-        <v>3000.2</v>
+        <v>3046.95</v>
       </c>
       <c r="O20" t="n">
-        <v>3029.8</v>
+        <v>3103.4</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2206,20 +2208,14 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
@@ -2235,50 +2231,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2981.2</v>
+        <v>2995.3</v>
       </c>
       <c r="C21" t="n">
-        <v>3006.1</v>
+        <v>3012.8</v>
       </c>
       <c r="D21" t="n">
-        <v>2974.4</v>
+        <v>2972.7</v>
       </c>
       <c r="E21" t="n">
-        <v>2991.8</v>
+        <v>2990.7</v>
       </c>
       <c r="F21" t="n">
-        <v>11.9</v>
+        <v>-1.1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0004</v>
       </c>
       <c r="H21" t="n">
-        <v>31.7</v>
+        <v>40.1</v>
       </c>
       <c r="I21" t="n">
-        <v>2882.6</v>
+        <v>2942.7</v>
       </c>
       <c r="J21" t="n">
-        <v>2899.75</v>
+        <v>2960.87</v>
       </c>
       <c r="K21" t="n">
-        <v>2943.1</v>
+        <v>2975.95</v>
       </c>
       <c r="L21" t="n">
-        <v>2986.45</v>
+        <v>2991.03</v>
       </c>
       <c r="M21" t="n">
-        <v>3016.7</v>
+        <v>3007.65</v>
       </c>
       <c r="N21" t="n">
-        <v>3046.95</v>
+        <v>3024.28</v>
       </c>
       <c r="O21" t="n">
-        <v>3103.4</v>
+        <v>3037.8</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2286,16 +2282,20 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2310,78 +2310,78 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2995.3</v>
+        <v>2991.7</v>
       </c>
       <c r="C22" t="n">
-        <v>3012.8</v>
+        <v>2994.8</v>
       </c>
       <c r="D22" t="n">
-        <v>2972.7</v>
+        <v>2949.3</v>
       </c>
       <c r="E22" t="n">
-        <v>2990.7</v>
+        <v>2973.5</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1</v>
+        <v>-17.2</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0058</v>
       </c>
       <c r="H22" t="n">
-        <v>40.1</v>
+        <v>45.5</v>
       </c>
       <c r="I22" t="n">
-        <v>2942.7</v>
+        <v>2932.6</v>
       </c>
       <c r="J22" t="n">
-        <v>2960.87</v>
+        <v>2949.57</v>
       </c>
       <c r="K22" t="n">
-        <v>2975.95</v>
+        <v>2970.65</v>
       </c>
       <c r="L22" t="n">
-        <v>2991.03</v>
+        <v>2991.72</v>
       </c>
       <c r="M22" t="n">
-        <v>3007.65</v>
+        <v>3010.75</v>
       </c>
       <c r="N22" t="n">
-        <v>3024.28</v>
+        <v>3029.78</v>
       </c>
       <c r="O22" t="n">
-        <v>3037.8</v>
+        <v>3052.9</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2396,79 +2396,79 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2991.7</v>
+        <v>2964.5</v>
       </c>
       <c r="C23" t="n">
-        <v>2994.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D23" t="n">
-        <v>2949.3</v>
+        <v>2952.7</v>
       </c>
       <c r="E23" t="n">
-        <v>2973.5</v>
+        <v>2955.2</v>
       </c>
       <c r="F23" t="n">
-        <v>-17.2</v>
+        <v>-18.3</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0062</v>
       </c>
       <c r="H23" t="n">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="I23" t="n">
-        <v>2932.6</v>
+        <v>2903.8</v>
       </c>
       <c r="J23" t="n">
-        <v>2949.57</v>
+        <v>2928.72</v>
       </c>
       <c r="K23" t="n">
-        <v>2970.65</v>
+        <v>2950.75</v>
       </c>
       <c r="L23" t="n">
-        <v>2991.72</v>
+        <v>2972.78</v>
       </c>
       <c r="M23" t="n">
-        <v>3010.75</v>
+        <v>2996.25</v>
       </c>
       <c r="N23" t="n">
-        <v>3029.78</v>
+        <v>3019.72</v>
       </c>
       <c r="O23" t="n">
-        <v>3052.9</v>
+        <v>3040.3</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
@@ -2482,57 +2482,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2964.5</v>
+        <v>2955.8</v>
       </c>
       <c r="C24" t="n">
-        <v>2998.7</v>
+        <v>2999.8</v>
       </c>
       <c r="D24" t="n">
-        <v>2952.7</v>
+        <v>2951.1</v>
       </c>
       <c r="E24" t="n">
-        <v>2955.2</v>
+        <v>2997</v>
       </c>
       <c r="F24" t="n">
-        <v>-18.3</v>
+        <v>41.8</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0141</v>
       </c>
       <c r="H24" t="n">
-        <v>46</v>
+        <v>48.7</v>
       </c>
       <c r="I24" t="n">
-        <v>2903.8</v>
+        <v>2906.7</v>
       </c>
       <c r="J24" t="n">
-        <v>2928.72</v>
+        <v>2898.95</v>
       </c>
       <c r="K24" t="n">
-        <v>2950.75</v>
+        <v>2932.2</v>
       </c>
       <c r="L24" t="n">
-        <v>2972.78</v>
+        <v>2965.45</v>
       </c>
       <c r="M24" t="n">
-        <v>2996.25</v>
+        <v>2978.2</v>
       </c>
       <c r="N24" t="n">
-        <v>3019.72</v>
+        <v>2990.95</v>
       </c>
       <c r="O24" t="n">
-        <v>3040.3</v>
+        <v>3044.7</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2540,23 +2540,23 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2575,50 +2575,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2955.8</v>
+        <v>2997</v>
       </c>
       <c r="C25" t="n">
-        <v>2999.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D25" t="n">
-        <v>2951.1</v>
+        <v>2965.5</v>
       </c>
       <c r="E25" t="n">
-        <v>2997</v>
+        <v>2969.8</v>
       </c>
       <c r="F25" t="n">
-        <v>41.8</v>
+        <v>-27.2</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0141</v>
+        <v>-0.0091</v>
       </c>
       <c r="H25" t="n">
-        <v>48.7</v>
+        <v>33.2</v>
       </c>
       <c r="I25" t="n">
-        <v>2906.7</v>
+        <v>2902.4</v>
       </c>
       <c r="J25" t="n">
-        <v>2898.95</v>
+        <v>2959.08</v>
       </c>
       <c r="K25" t="n">
-        <v>2932.2</v>
+        <v>2972.65</v>
       </c>
       <c r="L25" t="n">
-        <v>2965.45</v>
+        <v>2986.23</v>
       </c>
       <c r="M25" t="n">
-        <v>2978.2</v>
+        <v>3021.35</v>
       </c>
       <c r="N25" t="n">
-        <v>2990.95</v>
+        <v>3056.47</v>
       </c>
       <c r="O25" t="n">
-        <v>3044.7</v>
+        <v>3048.5</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2626,24 +2626,22 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
@@ -2654,60 +2652,62 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2997</v>
+        <v>2974.6</v>
       </c>
       <c r="C26" t="n">
-        <v>2998.7</v>
+        <v>2979</v>
       </c>
       <c r="D26" t="n">
-        <v>2965.5</v>
+        <v>2932.1</v>
       </c>
       <c r="E26" t="n">
-        <v>2969.8</v>
+        <v>2951.7</v>
       </c>
       <c r="F26" t="n">
-        <v>-27.2</v>
+        <v>-18.1</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0091</v>
+        <v>-0.0061</v>
       </c>
       <c r="H26" t="n">
-        <v>33.2</v>
+        <v>46.9</v>
       </c>
       <c r="I26" t="n">
-        <v>2902.4</v>
+        <v>2932.3</v>
       </c>
       <c r="J26" t="n">
-        <v>2959.08</v>
+        <v>2930.45</v>
       </c>
       <c r="K26" t="n">
-        <v>2972.65</v>
+        <v>2953.2</v>
       </c>
       <c r="L26" t="n">
-        <v>2986.23</v>
+        <v>2975.95</v>
       </c>
       <c r="M26" t="n">
-        <v>3021.35</v>
+        <v>2986.4</v>
       </c>
       <c r="N26" t="n">
-        <v>3056.47</v>
+        <v>2996.85</v>
       </c>
       <c r="O26" t="n">
-        <v>3048.5</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
+        <v>3031.9</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q26" s="6" t="n">
         <v/>
@@ -2738,74 +2738,70 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2974.6</v>
+        <v>2948.5</v>
       </c>
       <c r="C27" t="n">
-        <v>2979</v>
+        <v>2969.7</v>
       </c>
       <c r="D27" t="n">
-        <v>2932.1</v>
+        <v>2934.5</v>
       </c>
       <c r="E27" t="n">
-        <v>2951.7</v>
+        <v>2941.3</v>
       </c>
       <c r="F27" t="n">
-        <v>-18.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0035</v>
       </c>
       <c r="H27" t="n">
-        <v>46.9</v>
+        <v>35.2</v>
       </c>
       <c r="I27" t="n">
-        <v>2932.3</v>
+        <v>2885.2</v>
       </c>
       <c r="J27" t="n">
-        <v>2930.45</v>
+        <v>2902.88</v>
       </c>
       <c r="K27" t="n">
-        <v>2953.2</v>
+        <v>2928.25</v>
       </c>
       <c r="L27" t="n">
-        <v>2975.95</v>
+        <v>2953.62</v>
       </c>
       <c r="M27" t="n">
-        <v>2986.4</v>
+        <v>2975.15</v>
       </c>
       <c r="N27" t="n">
-        <v>2996.85</v>
+        <v>2996.67</v>
       </c>
       <c r="O27" t="n">
-        <v>3031.9</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3025.9</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
       </c>
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2824,57 +2820,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2948.5</v>
+        <v>2955.5</v>
       </c>
       <c r="C28" t="n">
-        <v>2969.7</v>
+        <v>2985.9</v>
       </c>
       <c r="D28" t="n">
-        <v>2934.5</v>
+        <v>2941.2</v>
       </c>
       <c r="E28" t="n">
-        <v>2941.3</v>
+        <v>2960</v>
       </c>
       <c r="F28" t="n">
-        <v>-10.4</v>
+        <v>18.7</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0064</v>
       </c>
       <c r="H28" t="n">
-        <v>35.2</v>
+        <v>44.7</v>
       </c>
       <c r="I28" t="n">
-        <v>2885.2</v>
+        <v>2899.3</v>
       </c>
       <c r="J28" t="n">
-        <v>2902.88</v>
+        <v>2900.7</v>
       </c>
       <c r="K28" t="n">
-        <v>2928.25</v>
+        <v>2923.7</v>
       </c>
       <c r="L28" t="n">
-        <v>2953.62</v>
+        <v>2946.7</v>
       </c>
       <c r="M28" t="n">
-        <v>2975.15</v>
+        <v>2958.9</v>
       </c>
       <c r="N28" t="n">
-        <v>2996.67</v>
+        <v>2971.1</v>
       </c>
       <c r="O28" t="n">
-        <v>3025.9</v>
+        <v>3004.9</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2885,16 +2881,20 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2904,59 +2904,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2955.5</v>
+        <v>2961.5</v>
       </c>
       <c r="C29" t="n">
-        <v>2985.9</v>
+        <v>2968.3</v>
       </c>
       <c r="D29" t="n">
-        <v>2941.2</v>
+        <v>2933.4</v>
       </c>
       <c r="E29" t="n">
-        <v>2960</v>
+        <v>2964.5</v>
       </c>
       <c r="F29" t="n">
-        <v>18.7</v>
+        <v>4.5</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0015</v>
       </c>
       <c r="H29" t="n">
-        <v>44.7</v>
+        <v>34.9</v>
       </c>
       <c r="I29" t="n">
-        <v>2899.3</v>
+        <v>2896.5</v>
       </c>
       <c r="J29" t="n">
-        <v>2900.7</v>
+        <v>2913.53</v>
       </c>
       <c r="K29" t="n">
-        <v>2923.7</v>
+        <v>2937.65</v>
       </c>
       <c r="L29" t="n">
-        <v>2946.7</v>
+        <v>2961.77</v>
       </c>
       <c r="M29" t="n">
-        <v>2958.9</v>
+        <v>2982.35</v>
       </c>
       <c r="N29" t="n">
-        <v>2971.1</v>
+        <v>3002.92</v>
       </c>
       <c r="O29" t="n">
-        <v>3004.9</v>
+        <v>3030.6</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2964,23 +2960,21 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2990,70 +2984,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2961.5</v>
+        <v>2966.9</v>
       </c>
       <c r="C30" t="n">
-        <v>2968.3</v>
+        <v>2978.3</v>
       </c>
       <c r="D30" t="n">
-        <v>2933.4</v>
+        <v>2902.3</v>
       </c>
       <c r="E30" t="n">
-        <v>2964.5</v>
+        <v>2915.4</v>
       </c>
       <c r="F30" t="n">
-        <v>4.5</v>
+        <v>-49.1</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0166</v>
       </c>
       <c r="H30" t="n">
-        <v>34.9</v>
+        <v>76</v>
       </c>
       <c r="I30" t="n">
-        <v>2896.5</v>
+        <v>2898.5</v>
       </c>
       <c r="J30" t="n">
-        <v>2913.53</v>
+        <v>2936.42</v>
       </c>
       <c r="K30" t="n">
-        <v>2937.65</v>
+        <v>2947.05</v>
       </c>
       <c r="L30" t="n">
-        <v>2961.77</v>
+        <v>2957.67</v>
       </c>
       <c r="M30" t="n">
-        <v>2982.35</v>
+        <v>2981.95</v>
       </c>
       <c r="N30" t="n">
-        <v>3002.92</v>
+        <v>3006.23</v>
       </c>
       <c r="O30" t="n">
-        <v>3030.6</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
+        <v>3003.2</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3065,88 +3067,84 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W30" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2966.9</v>
+        <v>2906.6</v>
       </c>
       <c r="C31" t="n">
-        <v>2978.3</v>
+        <v>2957.9</v>
       </c>
       <c r="D31" t="n">
-        <v>2902.3</v>
+        <v>2905.6</v>
       </c>
       <c r="E31" t="n">
-        <v>2915.4</v>
+        <v>2954.3</v>
       </c>
       <c r="F31" t="n">
-        <v>-49.1</v>
+        <v>38.9</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0166</v>
+        <v>0.0133</v>
       </c>
       <c r="H31" t="n">
-        <v>76</v>
+        <v>52.3</v>
       </c>
       <c r="I31" t="n">
-        <v>2898.5</v>
+        <v>2826.3</v>
       </c>
       <c r="J31" t="n">
-        <v>2936.42</v>
+        <v>2826.95</v>
       </c>
       <c r="K31" t="n">
-        <v>2947.05</v>
+        <v>2877.4</v>
       </c>
       <c r="L31" t="n">
-        <v>2957.67</v>
+        <v>2927.85</v>
       </c>
       <c r="M31" t="n">
-        <v>2981.95</v>
+        <v>2953.4</v>
       </c>
       <c r="N31" t="n">
-        <v>3006.23</v>
+        <v>2978.95</v>
       </c>
       <c r="O31" t="n">
-        <v>3003.2</v>
-      </c>
-      <c r="P31" s="6" t="inlineStr">
+        <v>3054.3</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
@@ -3160,76 +3158,78 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2906.6</v>
+        <v>2954</v>
       </c>
       <c r="C32" t="n">
-        <v>2957.9</v>
+        <v>2976.3</v>
       </c>
       <c r="D32" t="n">
-        <v>2905.6</v>
+        <v>2905.3</v>
       </c>
       <c r="E32" t="n">
-        <v>2954.3</v>
+        <v>2938</v>
       </c>
       <c r="F32" t="n">
-        <v>38.9</v>
+        <v>-16.3</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0055</v>
       </c>
       <c r="H32" t="n">
-        <v>52.3</v>
+        <v>71</v>
       </c>
       <c r="I32" t="n">
-        <v>2826.3</v>
+        <v>2853.3</v>
       </c>
       <c r="J32" t="n">
-        <v>2826.95</v>
+        <v>2913.28</v>
       </c>
       <c r="K32" t="n">
-        <v>2877.4</v>
+        <v>2928.15</v>
       </c>
       <c r="L32" t="n">
-        <v>2927.85</v>
+        <v>2943.03</v>
       </c>
       <c r="M32" t="n">
-        <v>2953.4</v>
+        <v>2980.45</v>
       </c>
       <c r="N32" t="n">
-        <v>2978.95</v>
+        <v>3017.87</v>
       </c>
       <c r="O32" t="n">
-        <v>3054.3</v>
+        <v>3010.2</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3244,78 +3244,76 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2954</v>
+        <v>2950</v>
       </c>
       <c r="C33" t="n">
-        <v>2976.3</v>
+        <v>2994.6</v>
       </c>
       <c r="D33" t="n">
-        <v>2905.3</v>
+        <v>2948.4</v>
       </c>
       <c r="E33" t="n">
-        <v>2938</v>
+        <v>2989.3</v>
       </c>
       <c r="F33" t="n">
-        <v>-16.3</v>
+        <v>51.3</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0175</v>
       </c>
       <c r="H33" t="n">
-        <v>71</v>
+        <v>46.2</v>
       </c>
       <c r="I33" t="n">
-        <v>2853.3</v>
+        <v>2834.3</v>
       </c>
       <c r="J33" t="n">
-        <v>2913.28</v>
+        <v>2865.6</v>
       </c>
       <c r="K33" t="n">
-        <v>2928.15</v>
+        <v>2902.5</v>
       </c>
       <c r="L33" t="n">
-        <v>2943.03</v>
+        <v>2939.4</v>
       </c>
       <c r="M33" t="n">
-        <v>2980.45</v>
+        <v>2973.5</v>
       </c>
       <c r="N33" t="n">
-        <v>3017.87</v>
+        <v>3007.6</v>
       </c>
       <c r="O33" t="n">
-        <v>3010.2</v>
+        <v>3047.3</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3330,57 +3328,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2950</v>
+        <v>2992.4</v>
       </c>
       <c r="C34" t="n">
-        <v>2994.6</v>
+        <v>3051.8</v>
       </c>
       <c r="D34" t="n">
-        <v>2948.4</v>
+        <v>2986.1</v>
       </c>
       <c r="E34" t="n">
-        <v>2989.3</v>
+        <v>3044.7</v>
       </c>
       <c r="F34" t="n">
-        <v>51.3</v>
+        <v>55.4</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0185</v>
       </c>
       <c r="H34" t="n">
-        <v>46.2</v>
+        <v>65.7</v>
       </c>
       <c r="I34" t="n">
-        <v>2834.3</v>
+        <v>2902.2</v>
       </c>
       <c r="J34" t="n">
-        <v>2865.6</v>
+        <v>2952</v>
       </c>
       <c r="K34" t="n">
-        <v>2902.5</v>
+        <v>2966.2</v>
       </c>
       <c r="L34" t="n">
-        <v>2939.4</v>
+        <v>2980.4</v>
       </c>
       <c r="M34" t="n">
-        <v>2973.5</v>
+        <v>3012.4</v>
       </c>
       <c r="N34" t="n">
-        <v>3007.6</v>
+        <v>3044.4</v>
       </c>
       <c r="O34" t="n">
-        <v>3047.3</v>
+        <v>3040.8</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3398,73 +3396,73 @@
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W34" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W34" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2992.4</v>
+        <v>3049.1</v>
       </c>
       <c r="C35" t="n">
-        <v>3051.8</v>
+        <v>3058.3</v>
       </c>
       <c r="D35" t="n">
-        <v>2986.1</v>
+        <v>3023.3</v>
       </c>
       <c r="E35" t="n">
-        <v>3044.7</v>
+        <v>3025.4</v>
       </c>
       <c r="F35" t="n">
-        <v>55.4</v>
+        <v>-19.3</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0063</v>
       </c>
       <c r="H35" t="n">
-        <v>65.7</v>
+        <v>35</v>
       </c>
       <c r="I35" t="n">
-        <v>2902.2</v>
+        <v>2920.4</v>
       </c>
       <c r="J35" t="n">
-        <v>2952</v>
+        <v>2991.87</v>
       </c>
       <c r="K35" t="n">
-        <v>2966.2</v>
+        <v>3011.85</v>
       </c>
       <c r="L35" t="n">
-        <v>2980.4</v>
+        <v>3031.83</v>
       </c>
       <c r="M35" t="n">
-        <v>3012.4</v>
+        <v>3077.55</v>
       </c>
       <c r="N35" t="n">
-        <v>3044.4</v>
+        <v>3123.27</v>
       </c>
       <c r="O35" t="n">
-        <v>3040.8</v>
+        <v>3117.5</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3475,80 +3473,78 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3049.1</v>
+        <v>3028.5</v>
       </c>
       <c r="C36" t="n">
-        <v>3058.3</v>
+        <v>3041</v>
       </c>
       <c r="D36" t="n">
-        <v>3023.3</v>
+        <v>3004.9</v>
       </c>
       <c r="E36" t="n">
-        <v>3025.4</v>
+        <v>3009.1</v>
       </c>
       <c r="F36" t="n">
-        <v>-19.3</v>
+        <v>-16.3</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0054</v>
       </c>
       <c r="H36" t="n">
-        <v>35</v>
+        <v>36.1</v>
       </c>
       <c r="I36" t="n">
-        <v>2920.4</v>
+        <v>2988.3</v>
       </c>
       <c r="J36" t="n">
-        <v>2991.87</v>
+        <v>2982.7</v>
       </c>
       <c r="K36" t="n">
-        <v>3011.85</v>
+        <v>3007.9</v>
       </c>
       <c r="L36" t="n">
-        <v>3031.83</v>
+        <v>3033.1</v>
       </c>
       <c r="M36" t="n">
-        <v>3077.55</v>
+        <v>3042.9</v>
       </c>
       <c r="N36" t="n">
-        <v>3123.27</v>
+        <v>3052.7</v>
       </c>
       <c r="O36" t="n">
-        <v>3117.5</v>
+        <v>3093.3</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3556,12 +3552,14 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3580,57 +3578,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3028.5</v>
+        <v>3008.5</v>
       </c>
       <c r="C37" t="n">
-        <v>3041</v>
+        <v>3046.8</v>
       </c>
       <c r="D37" t="n">
-        <v>3004.9</v>
+        <v>3002</v>
       </c>
       <c r="E37" t="n">
-        <v>3009.1</v>
+        <v>3041.6</v>
       </c>
       <c r="F37" t="n">
-        <v>-16.3</v>
+        <v>32.5</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0054</v>
+        <v>0.0108</v>
       </c>
       <c r="H37" t="n">
-        <v>36.1</v>
+        <v>44.8</v>
       </c>
       <c r="I37" t="n">
-        <v>2988.3</v>
+        <v>2968.8</v>
       </c>
       <c r="J37" t="n">
-        <v>2982.7</v>
+        <v>2966.08</v>
       </c>
       <c r="K37" t="n">
-        <v>3007.9</v>
+        <v>2991.05</v>
       </c>
       <c r="L37" t="n">
-        <v>3033.1</v>
+        <v>3016.03</v>
       </c>
       <c r="M37" t="n">
-        <v>3042.9</v>
+        <v>3027.15</v>
       </c>
       <c r="N37" t="n">
-        <v>3052.7</v>
+        <v>3038.28</v>
       </c>
       <c r="O37" t="n">
-        <v>3093.3</v>
+        <v>3077.1</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3638,22 +3636,24 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
@@ -3664,57 +3664,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3008.5</v>
+        <v>3038.9</v>
       </c>
       <c r="C38" t="n">
-        <v>3046.8</v>
+        <v>3044.6</v>
       </c>
       <c r="D38" t="n">
-        <v>3002</v>
+        <v>3016</v>
       </c>
       <c r="E38" t="n">
-        <v>3041.6</v>
+        <v>3025</v>
       </c>
       <c r="F38" t="n">
-        <v>32.5</v>
+        <v>-16.6</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0108</v>
+        <v>-0.0055</v>
       </c>
       <c r="H38" t="n">
-        <v>44.8</v>
+        <v>28.6</v>
       </c>
       <c r="I38" t="n">
-        <v>2968.8</v>
+        <v>2957.2</v>
       </c>
       <c r="J38" t="n">
-        <v>2966.08</v>
+        <v>3005.4</v>
       </c>
       <c r="K38" t="n">
-        <v>2991.05</v>
+        <v>3019.2</v>
       </c>
       <c r="L38" t="n">
-        <v>3016.03</v>
+        <v>3033</v>
       </c>
       <c r="M38" t="n">
-        <v>3027.15</v>
+        <v>3064</v>
       </c>
       <c r="N38" t="n">
-        <v>3038.28</v>
+        <v>3095</v>
       </c>
       <c r="O38" t="n">
-        <v>3077.1</v>
+        <v>3091.6</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3722,24 +3722,22 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
@@ -3750,57 +3748,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3038.9</v>
+        <v>3024.7</v>
       </c>
       <c r="C39" t="n">
-        <v>3044.6</v>
+        <v>3045.8</v>
       </c>
       <c r="D39" t="n">
-        <v>3016</v>
+        <v>3019.9</v>
       </c>
       <c r="E39" t="n">
-        <v>3025</v>
+        <v>3035.5</v>
       </c>
       <c r="F39" t="n">
-        <v>-16.6</v>
+        <v>10.5</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0035</v>
       </c>
       <c r="H39" t="n">
-        <v>28.6</v>
+        <v>25.9</v>
       </c>
       <c r="I39" t="n">
-        <v>2957.2</v>
+        <v>2987.4</v>
       </c>
       <c r="J39" t="n">
-        <v>3005.4</v>
+        <v>2993.75</v>
       </c>
       <c r="K39" t="n">
-        <v>3019.2</v>
+        <v>3010.7</v>
       </c>
       <c r="L39" t="n">
-        <v>3033</v>
+        <v>3027.65</v>
       </c>
       <c r="M39" t="n">
-        <v>3064</v>
+        <v>3039.3</v>
       </c>
       <c r="N39" t="n">
-        <v>3095</v>
+        <v>3050.95</v>
       </c>
       <c r="O39" t="n">
-        <v>3091.6</v>
+        <v>3073.2</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3808,19 +3806,19 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3832,59 +3830,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3024.7</v>
+        <v>3036.1</v>
       </c>
       <c r="C40" t="n">
-        <v>3045.8</v>
+        <v>3060</v>
       </c>
       <c r="D40" t="n">
-        <v>3019.9</v>
+        <v>3033.1</v>
       </c>
       <c r="E40" t="n">
-        <v>3035.5</v>
+        <v>3052.8</v>
       </c>
       <c r="F40" t="n">
-        <v>10.5</v>
+        <v>17.3</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0057</v>
       </c>
       <c r="H40" t="n">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
       <c r="I40" t="n">
-        <v>2987.4</v>
+        <v>2994</v>
       </c>
       <c r="J40" t="n">
-        <v>2993.75</v>
+        <v>3010.92</v>
       </c>
       <c r="K40" t="n">
-        <v>3010.7</v>
+        <v>3022.55</v>
       </c>
       <c r="L40" t="n">
-        <v>3027.65</v>
+        <v>3034.17</v>
       </c>
       <c r="M40" t="n">
-        <v>3039.3</v>
+        <v>3048.45</v>
       </c>
       <c r="N40" t="n">
-        <v>3050.95</v>
+        <v>3062.73</v>
       </c>
       <c r="O40" t="n">
-        <v>3073.2</v>
+        <v>3071.7</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3921,50 +3915,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3036.1</v>
+        <v>3056.2</v>
       </c>
       <c r="C41" t="n">
-        <v>3060</v>
+        <v>3076.3</v>
       </c>
       <c r="D41" t="n">
-        <v>3033.1</v>
+        <v>3052.5</v>
       </c>
       <c r="E41" t="n">
-        <v>3052.8</v>
+        <v>3060.2</v>
       </c>
       <c r="F41" t="n">
-        <v>17.3</v>
+        <v>7.4</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0024</v>
       </c>
       <c r="H41" t="n">
-        <v>26.9</v>
+        <v>23.8</v>
       </c>
       <c r="I41" t="n">
-        <v>2994</v>
+        <v>3006.2</v>
       </c>
       <c r="J41" t="n">
-        <v>3010.92</v>
+        <v>3029.03</v>
       </c>
       <c r="K41" t="n">
-        <v>3022.55</v>
+        <v>3039.35</v>
       </c>
       <c r="L41" t="n">
-        <v>3034.17</v>
+        <v>3049.68</v>
       </c>
       <c r="M41" t="n">
-        <v>3048.45</v>
+        <v>3066.25</v>
       </c>
       <c r="N41" t="n">
-        <v>3062.73</v>
+        <v>3082.82</v>
       </c>
       <c r="O41" t="n">
-        <v>3071.7</v>
+        <v>3086.9</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -4001,50 +3995,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3056.2</v>
+        <v>3062.2</v>
       </c>
       <c r="C42" t="n">
         <v>3076.3</v>
       </c>
       <c r="D42" t="n">
-        <v>3052.5</v>
+        <v>3051.7</v>
       </c>
       <c r="E42" t="n">
-        <v>3060.2</v>
+        <v>3074.9</v>
       </c>
       <c r="F42" t="n">
-        <v>7.4</v>
+        <v>14.7</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0048</v>
       </c>
       <c r="H42" t="n">
-        <v>23.8</v>
+        <v>24.6</v>
       </c>
       <c r="I42" t="n">
-        <v>3006.2</v>
+        <v>3028.7</v>
       </c>
       <c r="J42" t="n">
-        <v>3029.03</v>
+        <v>3034.3</v>
       </c>
       <c r="K42" t="n">
-        <v>3039.35</v>
+        <v>3048.3</v>
       </c>
       <c r="L42" t="n">
-        <v>3049.68</v>
+        <v>3062.3</v>
       </c>
       <c r="M42" t="n">
-        <v>3066.25</v>
+        <v>3072.1</v>
       </c>
       <c r="N42" t="n">
-        <v>3082.82</v>
+        <v>3081.9</v>
       </c>
       <c r="O42" t="n">
-        <v>3086.9</v>
+        <v>3100.1</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4076,55 +4070,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3062.2</v>
+        <v>3073.5</v>
       </c>
       <c r="C43" t="n">
-        <v>3076.3</v>
+        <v>3079.9</v>
       </c>
       <c r="D43" t="n">
-        <v>3051.7</v>
+        <v>3055.9</v>
       </c>
       <c r="E43" t="n">
-        <v>3074.9</v>
+        <v>3064.9</v>
       </c>
       <c r="F43" t="n">
-        <v>14.7</v>
+        <v>-10</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.0033</v>
       </c>
       <c r="H43" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="I43" t="n">
-        <v>3028.7</v>
+        <v>3027.1</v>
       </c>
       <c r="J43" t="n">
-        <v>3034.3</v>
+        <v>3055.75</v>
       </c>
       <c r="K43" t="n">
-        <v>3048.3</v>
+        <v>3062.6</v>
       </c>
       <c r="L43" t="n">
-        <v>3062.3</v>
+        <v>3069.45</v>
       </c>
       <c r="M43" t="n">
-        <v>3072.1</v>
+        <v>3087.2</v>
       </c>
       <c r="N43" t="n">
-        <v>3081.9</v>
+        <v>3104.95</v>
       </c>
       <c r="O43" t="n">
-        <v>3100.1</v>
+        <v>3100.9</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4132,18 +4130,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
+      <c r="R43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4165,60 +4163,64 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3073.5</v>
+        <v>3063.7</v>
       </c>
       <c r="C44" t="n">
-        <v>3079.9</v>
+        <v>3066.6</v>
       </c>
       <c r="D44" t="n">
-        <v>3055.9</v>
+        <v>3024.1</v>
       </c>
       <c r="E44" t="n">
-        <v>3064.9</v>
+        <v>3026.4</v>
       </c>
       <c r="F44" t="n">
-        <v>-10</v>
+        <v>-38.5</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0126</v>
       </c>
       <c r="H44" t="n">
-        <v>24</v>
+        <v>42.5</v>
       </c>
       <c r="I44" t="n">
-        <v>3027.1</v>
+        <v>3031.9</v>
       </c>
       <c r="J44" t="n">
-        <v>3055.75</v>
+        <v>3039.4</v>
       </c>
       <c r="K44" t="n">
-        <v>3062.6</v>
+        <v>3052.9</v>
       </c>
       <c r="L44" t="n">
-        <v>3069.45</v>
+        <v>3066.4</v>
       </c>
       <c r="M44" t="n">
-        <v>3087.2</v>
+        <v>3076.9</v>
       </c>
       <c r="N44" t="n">
-        <v>3104.95</v>
+        <v>3087.4</v>
       </c>
       <c r="O44" t="n">
-        <v>3100.9</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
+        <v>3103.9</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S44" s="7" t="inlineStr">
@@ -4235,88 +4237,80 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W44" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3063.7</v>
+        <v>3025.9</v>
       </c>
       <c r="C45" t="n">
-        <v>3066.6</v>
+        <v>3059.1</v>
       </c>
       <c r="D45" t="n">
-        <v>3024.1</v>
+        <v>3019.8</v>
       </c>
       <c r="E45" t="n">
-        <v>3026.4</v>
+        <v>3039.9</v>
       </c>
       <c r="F45" t="n">
-        <v>-38.5</v>
+        <v>13.5</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0045</v>
       </c>
       <c r="H45" t="n">
-        <v>42.5</v>
+        <v>39.3</v>
       </c>
       <c r="I45" t="n">
-        <v>3031.9</v>
+        <v>2981.6</v>
       </c>
       <c r="J45" t="n">
-        <v>3039.4</v>
+        <v>2974.42</v>
       </c>
       <c r="K45" t="n">
-        <v>3052.9</v>
+        <v>3005.15</v>
       </c>
       <c r="L45" t="n">
-        <v>3066.4</v>
+        <v>3035.88</v>
       </c>
       <c r="M45" t="n">
-        <v>3076.9</v>
+        <v>3047.65</v>
       </c>
       <c r="N45" t="n">
-        <v>3087.4</v>
+        <v>3059.42</v>
       </c>
       <c r="O45" t="n">
-        <v>3103.9</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
+        <v>3109.1</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
@@ -4328,75 +4322,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3025.9</v>
+        <v>3041.4</v>
       </c>
       <c r="C46" t="n">
-        <v>3059.1</v>
+        <v>3048.5</v>
       </c>
       <c r="D46" t="n">
-        <v>3019.8</v>
+        <v>2993.2</v>
       </c>
       <c r="E46" t="n">
-        <v>3039.9</v>
+        <v>2999.2</v>
       </c>
       <c r="F46" t="n">
-        <v>13.5</v>
+        <v>-40.7</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0134</v>
       </c>
       <c r="H46" t="n">
-        <v>39.3</v>
+        <v>55.3</v>
       </c>
       <c r="I46" t="n">
-        <v>2981.6</v>
+        <v>2980.5</v>
       </c>
       <c r="J46" t="n">
-        <v>2974.42</v>
+        <v>3000.82</v>
       </c>
       <c r="K46" t="n">
-        <v>3005.15</v>
+        <v>3020.25</v>
       </c>
       <c r="L46" t="n">
-        <v>3035.88</v>
+        <v>3039.67</v>
       </c>
       <c r="M46" t="n">
-        <v>3047.65</v>
+        <v>3059.55</v>
       </c>
       <c r="N46" t="n">
-        <v>3059.42</v>
+        <v>3079.42</v>
       </c>
       <c r="O46" t="n">
-        <v>3109.1</v>
+        <v>3098.4</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4408,81 +4408,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3041.4</v>
+        <v>2999.6</v>
       </c>
       <c r="C47" t="n">
-        <v>3048.5</v>
+        <v>3026.7</v>
       </c>
       <c r="D47" t="n">
-        <v>2993.2</v>
+        <v>2997.9</v>
       </c>
       <c r="E47" t="n">
-        <v>2999.2</v>
+        <v>3022.1</v>
       </c>
       <c r="F47" t="n">
-        <v>-40.7</v>
+        <v>22.9</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0134</v>
+        <v>0.0076</v>
       </c>
       <c r="H47" t="n">
-        <v>55.3</v>
+        <v>28.8</v>
       </c>
       <c r="I47" t="n">
-        <v>2980.5</v>
+        <v>2937.9</v>
       </c>
       <c r="J47" t="n">
-        <v>3000.82</v>
+        <v>2933.07</v>
       </c>
       <c r="K47" t="n">
-        <v>3020.25</v>
+        <v>2971.55</v>
       </c>
       <c r="L47" t="n">
-        <v>3039.67</v>
+        <v>3010.02</v>
       </c>
       <c r="M47" t="n">
-        <v>3059.55</v>
+        <v>3026.85</v>
       </c>
       <c r="N47" t="n">
-        <v>3079.42</v>
+        <v>3043.67</v>
       </c>
       <c r="O47" t="n">
-        <v>3098.4</v>
+        <v>3103.8</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
       <c r="U47" s="8" t="n">
         <v/>
       </c>
@@ -4494,75 +4488,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2999.6</v>
+        <v>3023</v>
       </c>
       <c r="C48" t="n">
-        <v>3026.7</v>
+        <v>3028.9</v>
       </c>
       <c r="D48" t="n">
-        <v>2997.9</v>
+        <v>2996</v>
       </c>
       <c r="E48" t="n">
-        <v>3022.1</v>
+        <v>3001.6</v>
       </c>
       <c r="F48" t="n">
-        <v>22.9</v>
+        <v>-20.5</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0076</v>
+        <v>-0.0068</v>
       </c>
       <c r="H48" t="n">
-        <v>28.8</v>
+        <v>32.9</v>
       </c>
       <c r="I48" t="n">
-        <v>2937.9</v>
+        <v>2969.1</v>
       </c>
       <c r="J48" t="n">
-        <v>2933.07</v>
+        <v>2998.2</v>
       </c>
       <c r="K48" t="n">
-        <v>2971.55</v>
+        <v>3007.7</v>
       </c>
       <c r="L48" t="n">
-        <v>3010.02</v>
+        <v>3017.2</v>
       </c>
       <c r="M48" t="n">
-        <v>3026.85</v>
+        <v>3036.5</v>
       </c>
       <c r="N48" t="n">
-        <v>3043.67</v>
+        <v>3055.8</v>
       </c>
       <c r="O48" t="n">
-        <v>3103.8</v>
+        <v>3055.5</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
+      <c r="Q48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
       <c r="U48" s="8" t="n">
         <v/>
       </c>
@@ -4576,79 +4576,77 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3023</v>
+        <v>3004.6</v>
       </c>
       <c r="C49" t="n">
-        <v>3028.9</v>
+        <v>3025.4</v>
       </c>
       <c r="D49" t="n">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="E49" t="n">
-        <v>3001.6</v>
+        <v>3014.4</v>
       </c>
       <c r="F49" t="n">
-        <v>-20.5</v>
+        <v>12.8</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0043</v>
       </c>
       <c r="H49" t="n">
-        <v>32.9</v>
+        <v>28.4</v>
       </c>
       <c r="I49" t="n">
-        <v>2969.1</v>
+        <v>2963.1</v>
       </c>
       <c r="J49" t="n">
-        <v>2998.2</v>
+        <v>2963.28</v>
       </c>
       <c r="K49" t="n">
-        <v>3007.7</v>
+        <v>2985.15</v>
       </c>
       <c r="L49" t="n">
-        <v>3017.2</v>
+        <v>3007.03</v>
       </c>
       <c r="M49" t="n">
-        <v>3036.5</v>
+        <v>3018.05</v>
       </c>
       <c r="N49" t="n">
-        <v>3055.8</v>
+        <v>3029.08</v>
       </c>
       <c r="O49" t="n">
-        <v>3055.5</v>
+        <v>3061.8</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
       <c r="U49" s="8" t="n">
         <v/>
       </c>
@@ -4662,57 +4660,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3004.6</v>
+        <v>3014.6</v>
       </c>
       <c r="C50" t="n">
-        <v>3025.4</v>
+        <v>3020.5</v>
       </c>
       <c r="D50" t="n">
-        <v>2997</v>
+        <v>3002.6</v>
       </c>
       <c r="E50" t="n">
-        <v>3014.4</v>
+        <v>3010.1</v>
       </c>
       <c r="F50" t="n">
-        <v>12.8</v>
+        <v>-4.3</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0014</v>
       </c>
       <c r="H50" t="n">
-        <v>28.4</v>
+        <v>17.9</v>
       </c>
       <c r="I50" t="n">
-        <v>2963.1</v>
+        <v>2968.6</v>
       </c>
       <c r="J50" t="n">
-        <v>2963.28</v>
+        <v>2987.6</v>
       </c>
       <c r="K50" t="n">
-        <v>2985.15</v>
+        <v>3000.2</v>
       </c>
       <c r="L50" t="n">
-        <v>3007.03</v>
+        <v>3012.8</v>
       </c>
       <c r="M50" t="n">
-        <v>3018.05</v>
+        <v>3028.6</v>
       </c>
       <c r="N50" t="n">
-        <v>3029.08</v>
+        <v>3044.4</v>
       </c>
       <c r="O50" t="n">
-        <v>3061.8</v>
+        <v>3053.8</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4723,15 +4721,13 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4746,57 +4742,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3014.6</v>
+        <v>3016.9</v>
       </c>
       <c r="C51" t="n">
-        <v>3020.5</v>
+        <v>3024.2</v>
       </c>
       <c r="D51" t="n">
-        <v>3002.6</v>
+        <v>3002.1</v>
       </c>
       <c r="E51" t="n">
-        <v>3010.1</v>
+        <v>3019</v>
       </c>
       <c r="F51" t="n">
-        <v>-4.3</v>
+        <v>8.9</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0014</v>
+        <v>0.003</v>
       </c>
       <c r="H51" t="n">
-        <v>17.9</v>
+        <v>22.1</v>
       </c>
       <c r="I51" t="n">
-        <v>2968.6</v>
+        <v>2984.7</v>
       </c>
       <c r="J51" t="n">
-        <v>2987.6</v>
+        <v>2991.48</v>
       </c>
       <c r="K51" t="n">
-        <v>3000.2</v>
+        <v>3001.15</v>
       </c>
       <c r="L51" t="n">
-        <v>3012.8</v>
+        <v>3010.83</v>
       </c>
       <c r="M51" t="n">
-        <v>3028.6</v>
+        <v>3019.05</v>
       </c>
       <c r="N51" t="n">
-        <v>3044.4</v>
+        <v>3027.28</v>
       </c>
       <c r="O51" t="n">
-        <v>3053.8</v>
+        <v>3038.4</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4807,13 +4803,15 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4828,77 +4826,81 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3016.9</v>
+        <v>3019.6</v>
       </c>
       <c r="C52" t="n">
-        <v>3024.2</v>
+        <v>3025.5</v>
       </c>
       <c r="D52" t="n">
-        <v>3002.1</v>
+        <v>2976.6</v>
       </c>
       <c r="E52" t="n">
-        <v>3019</v>
+        <v>2977.5</v>
       </c>
       <c r="F52" t="n">
-        <v>8.9</v>
+        <v>-41.5</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0137</v>
       </c>
       <c r="H52" t="n">
-        <v>22.1</v>
+        <v>48.9</v>
       </c>
       <c r="I52" t="n">
-        <v>2984.7</v>
+        <v>2980</v>
       </c>
       <c r="J52" t="n">
-        <v>2991.48</v>
+        <v>2999.83</v>
       </c>
       <c r="K52" t="n">
-        <v>3001.15</v>
+        <v>3007.95</v>
       </c>
       <c r="L52" t="n">
-        <v>3010.83</v>
+        <v>3016.08</v>
       </c>
       <c r="M52" t="n">
-        <v>3019.05</v>
+        <v>3030.05</v>
       </c>
       <c r="N52" t="n">
-        <v>3027.28</v>
+        <v>3044.02</v>
       </c>
       <c r="O52" t="n">
-        <v>3038.4</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
+        <v>3046.3</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
@@ -4912,73 +4914,69 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3019.6</v>
+        <v>2971</v>
       </c>
       <c r="C53" t="n">
-        <v>3025.5</v>
+        <v>2982.5</v>
       </c>
       <c r="D53" t="n">
-        <v>2976.6</v>
+        <v>2946.1</v>
       </c>
       <c r="E53" t="n">
-        <v>2977.5</v>
+        <v>2958.7</v>
       </c>
       <c r="F53" t="n">
-        <v>-41.5</v>
+        <v>-18.8</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0063</v>
       </c>
       <c r="H53" t="n">
-        <v>48.9</v>
+        <v>36.4</v>
       </c>
       <c r="I53" t="n">
-        <v>2980</v>
+        <v>2927.7</v>
       </c>
       <c r="J53" t="n">
-        <v>2999.83</v>
+        <v>2916.83</v>
       </c>
       <c r="K53" t="n">
-        <v>3007.95</v>
+        <v>2953.05</v>
       </c>
       <c r="L53" t="n">
-        <v>3016.08</v>
+        <v>2989.28</v>
       </c>
       <c r="M53" t="n">
-        <v>3030.05</v>
+        <v>3001.95</v>
       </c>
       <c r="N53" t="n">
-        <v>3044.02</v>
+        <v>3014.62</v>
       </c>
       <c r="O53" t="n">
-        <v>3046.3</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
+        <v>3074.4</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4998,69 +4996,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2971</v>
+        <v>2958</v>
       </c>
       <c r="C54" t="n">
-        <v>2982.5</v>
+        <v>2964.6</v>
       </c>
       <c r="D54" t="n">
-        <v>2946.1</v>
+        <v>2918.9</v>
       </c>
       <c r="E54" t="n">
-        <v>2958.7</v>
+        <v>2924.7</v>
       </c>
       <c r="F54" t="n">
-        <v>-18.8</v>
+        <v>-34</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0115</v>
       </c>
       <c r="H54" t="n">
-        <v>36.4</v>
+        <v>45.7</v>
       </c>
       <c r="I54" t="n">
-        <v>2927.7</v>
+        <v>2909.7</v>
       </c>
       <c r="J54" t="n">
-        <v>2916.83</v>
+        <v>2919.5</v>
       </c>
       <c r="K54" t="n">
-        <v>2953.05</v>
+        <v>2940.5</v>
       </c>
       <c r="L54" t="n">
-        <v>2989.28</v>
+        <v>2961.5</v>
       </c>
       <c r="M54" t="n">
-        <v>3001.95</v>
+        <v>2976.9</v>
       </c>
       <c r="N54" t="n">
-        <v>3014.62</v>
+        <v>2992.3</v>
       </c>
       <c r="O54" t="n">
-        <v>3074.4</v>
+        <v>3018.9</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
@@ -5087,75 +5083,75 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2958</v>
+        <v>2926.4</v>
       </c>
       <c r="C55" t="n">
-        <v>2964.6</v>
+        <v>2962.5</v>
       </c>
       <c r="D55" t="n">
-        <v>2918.9</v>
+        <v>2914.5</v>
       </c>
       <c r="E55" t="n">
-        <v>2924.7</v>
+        <v>2958.8</v>
       </c>
       <c r="F55" t="n">
-        <v>-34</v>
+        <v>34.1</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0.0117</v>
       </c>
       <c r="H55" t="n">
-        <v>45.7</v>
+        <v>48</v>
       </c>
       <c r="I55" t="n">
-        <v>2909.7</v>
+        <v>2873.2</v>
       </c>
       <c r="J55" t="n">
-        <v>2919.5</v>
+        <v>2870.47</v>
       </c>
       <c r="K55" t="n">
-        <v>2940.5</v>
+        <v>2901.85</v>
       </c>
       <c r="L55" t="n">
-        <v>2961.5</v>
+        <v>2933.22</v>
       </c>
       <c r="M55" t="n">
-        <v>2976.9</v>
+        <v>2947.55</v>
       </c>
       <c r="N55" t="n">
-        <v>2992.3</v>
+        <v>2961.88</v>
       </c>
       <c r="O55" t="n">
-        <v>3018.9</v>
+        <v>3010.3</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
@@ -5164,55 +5160,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2926.4</v>
+        <v>2957.6</v>
       </c>
       <c r="C56" t="n">
-        <v>2962.5</v>
+        <v>2983.3</v>
       </c>
       <c r="D56" t="n">
-        <v>2914.5</v>
+        <v>2949.9</v>
       </c>
       <c r="E56" t="n">
-        <v>2958.8</v>
+        <v>2969.7</v>
       </c>
       <c r="F56" t="n">
-        <v>34.1</v>
+        <v>10.9</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0117</v>
+        <v>0.0037</v>
       </c>
       <c r="H56" t="n">
-        <v>48</v>
+        <v>33.4</v>
       </c>
       <c r="I56" t="n">
-        <v>2873.2</v>
+        <v>2866.5</v>
       </c>
       <c r="J56" t="n">
-        <v>2870.47</v>
+        <v>2920.95</v>
       </c>
       <c r="K56" t="n">
-        <v>2901.85</v>
+        <v>2934.8</v>
       </c>
       <c r="L56" t="n">
-        <v>2933.22</v>
+        <v>2948.65</v>
       </c>
       <c r="M56" t="n">
-        <v>2947.55</v>
+        <v>2982.8</v>
       </c>
       <c r="N56" t="n">
-        <v>2961.88</v>
+        <v>3016.95</v>
       </c>
       <c r="O56" t="n">
-        <v>3010.3</v>
+        <v>3010.5</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5230,14 +5230,12 @@
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
@@ -5248,57 +5246,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2957.6</v>
+        <v>2967.9</v>
       </c>
       <c r="C57" t="n">
-        <v>2983.3</v>
+        <v>2979.3</v>
       </c>
       <c r="D57" t="n">
-        <v>2949.9</v>
+        <v>2949.5</v>
       </c>
       <c r="E57" t="n">
-        <v>2969.7</v>
+        <v>2976.6</v>
       </c>
       <c r="F57" t="n">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0023</v>
       </c>
       <c r="H57" t="n">
-        <v>33.4</v>
+        <v>29.8</v>
       </c>
       <c r="I57" t="n">
-        <v>2866.5</v>
+        <v>2916.5</v>
       </c>
       <c r="J57" t="n">
-        <v>2920.95</v>
+        <v>2937.85</v>
       </c>
       <c r="K57" t="n">
-        <v>2934.8</v>
+        <v>2953</v>
       </c>
       <c r="L57" t="n">
-        <v>2948.65</v>
+        <v>2968.15</v>
       </c>
       <c r="M57" t="n">
-        <v>2982.8</v>
+        <v>2986.4</v>
       </c>
       <c r="N57" t="n">
-        <v>3016.95</v>
+        <v>3004.65</v>
       </c>
       <c r="O57" t="n">
-        <v>3010.5</v>
+        <v>3016.7</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5306,18 +5304,18 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5332,57 +5330,57 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2967.9</v>
+        <v>2974.7</v>
       </c>
       <c r="C58" t="n">
-        <v>2979.3</v>
+        <v>2977.9</v>
       </c>
       <c r="D58" t="n">
-        <v>2949.5</v>
+        <v>2954.7</v>
       </c>
       <c r="E58" t="n">
-        <v>2976.6</v>
+        <v>2963.6</v>
       </c>
       <c r="F58" t="n">
-        <v>6.9</v>
+        <v>-13</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0044</v>
       </c>
       <c r="H58" t="n">
-        <v>29.8</v>
+        <v>23.2</v>
       </c>
       <c r="I58" t="n">
-        <v>2916.5</v>
+        <v>2919.7</v>
       </c>
       <c r="J58" t="n">
-        <v>2937.85</v>
+        <v>2952.9</v>
       </c>
       <c r="K58" t="n">
-        <v>2953</v>
+        <v>2961.7</v>
       </c>
       <c r="L58" t="n">
-        <v>2968.15</v>
+        <v>2970.5</v>
       </c>
       <c r="M58" t="n">
-        <v>2986.4</v>
+        <v>2991.5</v>
       </c>
       <c r="N58" t="n">
-        <v>3004.65</v>
+        <v>3012.5</v>
       </c>
       <c r="O58" t="n">
-        <v>3016.7</v>
+        <v>3009.1</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5392,12 +5390,12 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5423,60 +5421,64 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2974.7</v>
+        <v>2963.1</v>
       </c>
       <c r="C59" t="n">
-        <v>2977.9</v>
+        <v>2966.2</v>
       </c>
       <c r="D59" t="n">
-        <v>2954.7</v>
+        <v>2919.4</v>
       </c>
       <c r="E59" t="n">
-        <v>2963.6</v>
+        <v>2923</v>
       </c>
       <c r="F59" t="n">
-        <v>-13</v>
+        <v>-40.6</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0137</v>
       </c>
       <c r="H59" t="n">
-        <v>23.2</v>
+        <v>46.8</v>
       </c>
       <c r="I59" t="n">
-        <v>2919.7</v>
+        <v>2931.5</v>
       </c>
       <c r="J59" t="n">
-        <v>2952.9</v>
+        <v>2939.05</v>
       </c>
       <c r="K59" t="n">
-        <v>2961.7</v>
+        <v>2952</v>
       </c>
       <c r="L59" t="n">
-        <v>2970.5</v>
+        <v>2964.95</v>
       </c>
       <c r="M59" t="n">
-        <v>2991.5</v>
+        <v>2975.2</v>
       </c>
       <c r="N59" t="n">
-        <v>3012.5</v>
+        <v>2985.45</v>
       </c>
       <c r="O59" t="n">
-        <v>3009.1</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
+        <v>3001.1</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S59" s="7" t="inlineStr">
@@ -5498,73 +5500,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2963.1</v>
+        <v>2923.1</v>
       </c>
       <c r="C60" t="n">
-        <v>2966.2</v>
+        <v>2933.8</v>
       </c>
       <c r="D60" t="n">
-        <v>2919.4</v>
+        <v>2887.8</v>
       </c>
       <c r="E60" t="n">
-        <v>2923</v>
+        <v>2893.4</v>
       </c>
       <c r="F60" t="n">
-        <v>-40.6</v>
+        <v>-29.6</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0101</v>
       </c>
       <c r="H60" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="I60" t="n">
-        <v>2931.5</v>
+        <v>2872.6</v>
       </c>
       <c r="J60" t="n">
-        <v>2939.05</v>
+        <v>2866.3</v>
       </c>
       <c r="K60" t="n">
-        <v>2952</v>
+        <v>2899.6</v>
       </c>
       <c r="L60" t="n">
-        <v>2964.95</v>
+        <v>2932.9</v>
       </c>
       <c r="M60" t="n">
-        <v>2975.2</v>
+        <v>2946.4</v>
       </c>
       <c r="N60" t="n">
-        <v>2985.45</v>
+        <v>2959.9</v>
       </c>
       <c r="O60" t="n">
-        <v>3001.1</v>
-      </c>
-      <c r="P60" s="6" t="inlineStr">
+        <v>3013</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S60" s="7" t="inlineStr">
@@ -5591,50 +5585,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2923.1</v>
+        <v>2890.9</v>
       </c>
       <c r="C61" t="n">
-        <v>2933.8</v>
+        <v>2929.8</v>
       </c>
       <c r="D61" t="n">
-        <v>2887.8</v>
+        <v>2887.6</v>
       </c>
       <c r="E61" t="n">
-        <v>2893.4</v>
+        <v>2904.5</v>
       </c>
       <c r="F61" t="n">
-        <v>-29.6</v>
+        <v>11.1</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0101</v>
+        <v>0.0038</v>
       </c>
       <c r="H61" t="n">
-        <v>46</v>
+        <v>42.2</v>
       </c>
       <c r="I61" t="n">
-        <v>2872.6</v>
+        <v>2841.8</v>
       </c>
       <c r="J61" t="n">
-        <v>2866.3</v>
+        <v>2838.7</v>
       </c>
       <c r="K61" t="n">
-        <v>2899.6</v>
+        <v>2870.4</v>
       </c>
       <c r="L61" t="n">
-        <v>2932.9</v>
+        <v>2902.1</v>
       </c>
       <c r="M61" t="n">
-        <v>2946.4</v>
+        <v>2916.4</v>
       </c>
       <c r="N61" t="n">
-        <v>2959.9</v>
+        <v>2930.7</v>
       </c>
       <c r="O61" t="n">
-        <v>3013</v>
+        <v>2979.8</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5642,18 +5636,18 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5666,117 +5660,37 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>2890.9</v>
-      </c>
-      <c r="C62" t="n">
-        <v>2929.8</v>
-      </c>
-      <c r="D62" t="n">
-        <v>2887.6</v>
-      </c>
-      <c r="E62" t="n">
-        <v>2904.5</v>
-      </c>
-      <c r="F62" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.0038</v>
-      </c>
-      <c r="H62" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="I62" t="n">
-        <v>2841.8</v>
-      </c>
-      <c r="J62" t="n">
-        <v>2838.7</v>
-      </c>
-      <c r="K62" t="n">
-        <v>2870.4</v>
-      </c>
-      <c r="L62" t="n">
-        <v>2902.1</v>
-      </c>
-      <c r="M62" t="n">
-        <v>2916.4</v>
-      </c>
-      <c r="N62" t="n">
-        <v>2930.7</v>
-      </c>
-      <c r="O62" t="n">
-        <v>2979.8</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I63" s="13" t="n">
+      <c r="I62" s="13" t="n">
         <v>2845.4</v>
       </c>
-      <c r="J63" s="13" t="n">
+      <c r="J62" s="13" t="n">
         <v>2860.2</v>
       </c>
-      <c r="K63" s="13" t="n">
+      <c r="K62" s="13" t="n">
         <v>2883.4</v>
       </c>
-      <c r="L63" s="13" t="n">
+      <c r="L62" s="13" t="n">
         <v>2906.6</v>
       </c>
-      <c r="M63" s="13" t="n">
+      <c r="M62" s="13" t="n">
         <v>2925.6</v>
       </c>
-      <c r="N63" s="13" t="n">
+      <c r="N62" s="13" t="n">
         <v>2944.6</v>
       </c>
-      <c r="O63" s="13" t="n">
+      <c r="O62" s="13" t="n">
         <v>2972</v>
       </c>
     </row>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -109,14 +109,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2941.2</v>
+        <v>2925</v>
       </c>
       <c r="C2" t="n">
-        <v>2979.8</v>
+        <v>2972.3</v>
       </c>
       <c r="D2" t="n">
-        <v>2910.3</v>
+        <v>2925</v>
       </c>
       <c r="E2" t="n">
-        <v>2919.6</v>
+        <v>2960.73</v>
       </c>
       <c r="F2" t="n">
-        <v>-23.2</v>
+        <v>41.13</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0141</v>
       </c>
       <c r="H2" t="n">
-        <v>69.5</v>
+        <v>47.3</v>
       </c>
       <c r="I2" t="n">
-        <v>2885.5</v>
+        <v>2840.8</v>
       </c>
       <c r="J2" t="n">
-        <v>2879.05</v>
+        <v>2837.38</v>
       </c>
       <c r="K2" t="n">
-        <v>2916.4</v>
+        <v>2884.85</v>
       </c>
       <c r="L2" t="n">
-        <v>2953.75</v>
+        <v>2932.33</v>
       </c>
       <c r="M2" t="n">
-        <v>2969.2</v>
+        <v>2954.35</v>
       </c>
       <c r="N2" t="n">
-        <v>2984.65</v>
+        <v>2976.38</v>
       </c>
       <c r="O2" t="n">
-        <v>3043.9</v>
+        <v>3049.3</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,21 +692,19 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -720,57 +718,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2925</v>
+        <v>2989.9</v>
       </c>
       <c r="C3" t="n">
-        <v>2972.3</v>
+        <v>3039</v>
       </c>
       <c r="D3" t="n">
-        <v>2925</v>
+        <v>2970.8</v>
       </c>
       <c r="E3" t="n">
-        <v>2960.73</v>
+        <v>3024.1</v>
       </c>
       <c r="F3" t="n">
-        <v>41.13</v>
+        <v>63.37</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0141</v>
+        <v>0.0214</v>
       </c>
       <c r="H3" t="n">
-        <v>47.3</v>
+        <v>68.2</v>
       </c>
       <c r="I3" t="n">
-        <v>2840.8</v>
+        <v>2877.7</v>
       </c>
       <c r="J3" t="n">
-        <v>2837.38</v>
+        <v>2919.47</v>
       </c>
       <c r="K3" t="n">
-        <v>2884.85</v>
+        <v>2937.08</v>
       </c>
       <c r="L3" t="n">
-        <v>2932.33</v>
+        <v>2954.69</v>
       </c>
       <c r="M3" t="n">
-        <v>2954.35</v>
+        <v>2984.38</v>
       </c>
       <c r="N3" t="n">
-        <v>2976.38</v>
+        <v>3014.07</v>
       </c>
       <c r="O3" t="n">
-        <v>3049.3</v>
+        <v>3019.6</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -781,186 +779,186 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
-      </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2989.9</v>
+        <v>3022.4</v>
       </c>
       <c r="C4" t="n">
-        <v>3039</v>
+        <v>3028.4</v>
       </c>
       <c r="D4" t="n">
-        <v>2970.8</v>
+        <v>2965.2</v>
       </c>
       <c r="E4" t="n">
-        <v>3024.1</v>
+        <v>2998.2</v>
       </c>
       <c r="F4" t="n">
-        <v>63.37</v>
+        <v>-25.9</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0214</v>
+        <v>-0.0086</v>
       </c>
       <c r="H4" t="n">
-        <v>68.2</v>
+        <v>63.2</v>
       </c>
       <c r="I4" t="n">
-        <v>2877.7</v>
+        <v>2902.6</v>
       </c>
       <c r="J4" t="n">
-        <v>2919.47</v>
+        <v>2965.5</v>
       </c>
       <c r="K4" t="n">
-        <v>2937.08</v>
+        <v>2990</v>
       </c>
       <c r="L4" t="n">
-        <v>2954.69</v>
+        <v>3014.5</v>
       </c>
       <c r="M4" t="n">
-        <v>2984.38</v>
+        <v>3058.2</v>
       </c>
       <c r="N4" t="n">
-        <v>3014.07</v>
+        <v>3101.9</v>
       </c>
       <c r="O4" t="n">
-        <v>3019.6</v>
+        <v>3107.2</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3022.4</v>
+        <v>2998.4</v>
       </c>
       <c r="C5" t="n">
-        <v>3028.4</v>
+        <v>3041.4</v>
       </c>
       <c r="D5" t="n">
-        <v>2965.2</v>
+        <v>2987.2</v>
       </c>
       <c r="E5" t="n">
-        <v>2998.2</v>
+        <v>3013.5</v>
       </c>
       <c r="F5" t="n">
-        <v>-25.9</v>
+        <v>15.3</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0051</v>
       </c>
       <c r="H5" t="n">
-        <v>63.2</v>
+        <v>54.2</v>
       </c>
       <c r="I5" t="n">
-        <v>2902.6</v>
+        <v>2902</v>
       </c>
       <c r="J5" t="n">
-        <v>2965.5</v>
+        <v>2935.7</v>
       </c>
       <c r="K5" t="n">
-        <v>2990</v>
+        <v>2966.6</v>
       </c>
       <c r="L5" t="n">
-        <v>3014.5</v>
+        <v>2997.5</v>
       </c>
       <c r="M5" t="n">
-        <v>3058.2</v>
+        <v>3029.8</v>
       </c>
       <c r="N5" t="n">
-        <v>3101.9</v>
+        <v>3062.1</v>
       </c>
       <c r="O5" t="n">
-        <v>3107.2</v>
+        <v>3091.6</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -972,59 +970,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2998.4</v>
+        <v>3023.7</v>
       </c>
       <c r="C6" t="n">
-        <v>3041.4</v>
+        <v>3062.4</v>
       </c>
       <c r="D6" t="n">
-        <v>2987.2</v>
+        <v>3010.5</v>
       </c>
       <c r="E6" t="n">
-        <v>3013.5</v>
+        <v>3030.7</v>
       </c>
       <c r="F6" t="n">
-        <v>15.3</v>
+        <v>17.2</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0057</v>
       </c>
       <c r="H6" t="n">
-        <v>54.2</v>
+        <v>51.9</v>
       </c>
       <c r="I6" t="n">
-        <v>2902</v>
+        <v>2933</v>
       </c>
       <c r="J6" t="n">
-        <v>2935.7</v>
+        <v>2958.9</v>
       </c>
       <c r="K6" t="n">
-        <v>2966.6</v>
+        <v>2986.4</v>
       </c>
       <c r="L6" t="n">
-        <v>2997.5</v>
+        <v>3013.9</v>
       </c>
       <c r="M6" t="n">
-        <v>3029.8</v>
+        <v>3040.6</v>
       </c>
       <c r="N6" t="n">
-        <v>3062.1</v>
+        <v>3067.3</v>
       </c>
       <c r="O6" t="n">
-        <v>3091.6</v>
+        <v>3095.6</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1035,14 +1029,14 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U6" s="8" t="n">
@@ -1061,50 +1055,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3023.7</v>
+        <v>3034.7</v>
       </c>
       <c r="C7" t="n">
-        <v>3062.4</v>
+        <v>3045.7</v>
       </c>
       <c r="D7" t="n">
-        <v>3010.5</v>
+        <v>2999.6</v>
       </c>
       <c r="E7" t="n">
-        <v>3030.7</v>
+        <v>3022.6</v>
       </c>
       <c r="F7" t="n">
-        <v>17.2</v>
+        <v>-8.1</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.0027</v>
       </c>
       <c r="H7" t="n">
-        <v>51.9</v>
+        <v>46.1</v>
       </c>
       <c r="I7" t="n">
-        <v>2933</v>
+        <v>2958.6</v>
       </c>
       <c r="J7" t="n">
-        <v>2958.9</v>
+        <v>2975.93</v>
       </c>
       <c r="K7" t="n">
-        <v>2986.4</v>
+        <v>3004.75</v>
       </c>
       <c r="L7" t="n">
-        <v>3013.9</v>
+        <v>3033.57</v>
       </c>
       <c r="M7" t="n">
-        <v>3040.6</v>
+        <v>3056.65</v>
       </c>
       <c r="N7" t="n">
-        <v>3067.3</v>
+        <v>3079.72</v>
       </c>
       <c r="O7" t="n">
-        <v>3095.6</v>
+        <v>3114.3</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1112,18 +1106,18 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1136,55 +1130,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3034.7</v>
+        <v>3020.9</v>
       </c>
       <c r="C8" t="n">
-        <v>3045.7</v>
+        <v>3044.9</v>
       </c>
       <c r="D8" t="n">
-        <v>2999.6</v>
+        <v>2987.8</v>
       </c>
       <c r="E8" t="n">
-        <v>3022.6</v>
+        <v>3030.6</v>
       </c>
       <c r="F8" t="n">
-        <v>-8.1</v>
+        <v>8</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0026</v>
       </c>
       <c r="H8" t="n">
-        <v>46.1</v>
+        <v>57.1</v>
       </c>
       <c r="I8" t="n">
-        <v>2958.6</v>
+        <v>2953.5</v>
       </c>
       <c r="J8" t="n">
-        <v>2975.93</v>
+        <v>2976.48</v>
       </c>
       <c r="K8" t="n">
-        <v>3004.75</v>
+        <v>2999.55</v>
       </c>
       <c r="L8" t="n">
-        <v>3033.57</v>
+        <v>3022.63</v>
       </c>
       <c r="M8" t="n">
-        <v>3056.65</v>
+        <v>3045.65</v>
       </c>
       <c r="N8" t="n">
-        <v>3079.72</v>
+        <v>3068.67</v>
       </c>
       <c r="O8" t="n">
-        <v>3114.3</v>
+        <v>3091.8</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1199,7 +1197,7 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1218,57 +1216,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3020.9</v>
+        <v>3026.1</v>
       </c>
       <c r="C9" t="n">
-        <v>3044.9</v>
+        <v>3050.6</v>
       </c>
       <c r="D9" t="n">
-        <v>2987.8</v>
+        <v>3015.1</v>
       </c>
       <c r="E9" t="n">
-        <v>3030.6</v>
+        <v>3045.6</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0049</v>
       </c>
       <c r="H9" t="n">
-        <v>57.1</v>
+        <v>35.5</v>
       </c>
       <c r="I9" t="n">
-        <v>2953.5</v>
+        <v>2930.7</v>
       </c>
       <c r="J9" t="n">
-        <v>2976.48</v>
+        <v>2980.63</v>
       </c>
       <c r="K9" t="n">
-        <v>2999.55</v>
+        <v>3002.05</v>
       </c>
       <c r="L9" t="n">
-        <v>3022.63</v>
+        <v>3023.48</v>
       </c>
       <c r="M9" t="n">
-        <v>3045.65</v>
+        <v>3059.15</v>
       </c>
       <c r="N9" t="n">
-        <v>3068.67</v>
+        <v>3094.83</v>
       </c>
       <c r="O9" t="n">
-        <v>3091.8</v>
+        <v>3102</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1276,18 +1274,18 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1300,59 +1298,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3026.1</v>
+        <v>3040</v>
       </c>
       <c r="C10" t="n">
-        <v>3050.6</v>
+        <v>3068.4</v>
       </c>
       <c r="D10" t="n">
-        <v>3015.1</v>
+        <v>3023.7</v>
       </c>
       <c r="E10" t="n">
-        <v>3045.6</v>
+        <v>3035.1</v>
       </c>
       <c r="F10" t="n">
-        <v>15</v>
+        <v>-10.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.0034</v>
       </c>
       <c r="H10" t="n">
-        <v>35.5</v>
+        <v>44.7</v>
       </c>
       <c r="I10" t="n">
-        <v>2930.7</v>
+        <v>2979.6</v>
       </c>
       <c r="J10" t="n">
-        <v>2980.63</v>
+        <v>3016.48</v>
       </c>
       <c r="K10" t="n">
-        <v>3002.05</v>
+        <v>3027.85</v>
       </c>
       <c r="L10" t="n">
-        <v>3023.48</v>
+        <v>3039.23</v>
       </c>
       <c r="M10" t="n">
-        <v>3059.15</v>
+        <v>3063.35</v>
       </c>
       <c r="N10" t="n">
-        <v>3094.83</v>
+        <v>3087.48</v>
       </c>
       <c r="O10" t="n">
-        <v>3102</v>
+        <v>3086.1</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1360,17 +1354,19 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U10" s="8" t="n">
@@ -1384,55 +1380,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3040</v>
+        <v>3030.9</v>
       </c>
       <c r="C11" t="n">
-        <v>3068.4</v>
+        <v>3062.4</v>
       </c>
       <c r="D11" t="n">
-        <v>3023.7</v>
+        <v>2988.5</v>
       </c>
       <c r="E11" t="n">
-        <v>3035.1</v>
+        <v>3014.2</v>
       </c>
       <c r="F11" t="n">
-        <v>-10.5</v>
+        <v>-20.9</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0069</v>
       </c>
       <c r="H11" t="n">
-        <v>44.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>2979.6</v>
+        <v>2979</v>
       </c>
       <c r="J11" t="n">
-        <v>3016.48</v>
+        <v>2984.93</v>
       </c>
       <c r="K11" t="n">
-        <v>3027.85</v>
+        <v>3012.75</v>
       </c>
       <c r="L11" t="n">
-        <v>3039.23</v>
+        <v>3040.58</v>
       </c>
       <c r="M11" t="n">
-        <v>3063.35</v>
+        <v>3057.45</v>
       </c>
       <c r="N11" t="n">
-        <v>3087.48</v>
+        <v>3074.33</v>
       </c>
       <c r="O11" t="n">
-        <v>3086.1</v>
+        <v>3113.1</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1442,19 +1442,19 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
@@ -1468,57 +1468,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3030.9</v>
+        <v>3019.7</v>
       </c>
       <c r="C12" t="n">
-        <v>3062.4</v>
+        <v>3042.1</v>
       </c>
       <c r="D12" t="n">
-        <v>2988.5</v>
+        <v>3006.7</v>
       </c>
       <c r="E12" t="n">
-        <v>3014.2</v>
+        <v>3027</v>
       </c>
       <c r="F12" t="n">
-        <v>-20.9</v>
+        <v>12.8</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0042</v>
       </c>
       <c r="H12" t="n">
-        <v>73.90000000000001</v>
+        <v>35.4</v>
       </c>
       <c r="I12" t="n">
-        <v>2979</v>
+        <v>2914.6</v>
       </c>
       <c r="J12" t="n">
-        <v>2984.93</v>
+        <v>2934.68</v>
       </c>
       <c r="K12" t="n">
-        <v>3012.75</v>
+        <v>2977.25</v>
       </c>
       <c r="L12" t="n">
-        <v>3040.58</v>
+        <v>3019.82</v>
       </c>
       <c r="M12" t="n">
-        <v>3057.45</v>
+        <v>3051.15</v>
       </c>
       <c r="N12" t="n">
-        <v>3074.33</v>
+        <v>3082.47</v>
       </c>
       <c r="O12" t="n">
-        <v>3113.1</v>
+        <v>3136.3</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1526,20 +1526,16 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R12" s="6" t="n">
+        <v/>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1554,70 +1550,74 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3019.7</v>
+        <v>3033.4</v>
       </c>
       <c r="C13" t="n">
-        <v>3042.1</v>
+        <v>3042.6</v>
       </c>
       <c r="D13" t="n">
-        <v>3006.7</v>
+        <v>2988.8</v>
       </c>
       <c r="E13" t="n">
-        <v>3027</v>
+        <v>2998.8</v>
       </c>
       <c r="F13" t="n">
-        <v>12.8</v>
+        <v>-28.2</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>35.4</v>
+        <v>53.8</v>
       </c>
       <c r="I13" t="n">
-        <v>2914.6</v>
+        <v>2971.3</v>
       </c>
       <c r="J13" t="n">
-        <v>2934.68</v>
+        <v>2992.9</v>
       </c>
       <c r="K13" t="n">
-        <v>2977.25</v>
+        <v>3009.3</v>
       </c>
       <c r="L13" t="n">
-        <v>3019.82</v>
+        <v>3025.7</v>
       </c>
       <c r="M13" t="n">
-        <v>3051.15</v>
+        <v>3044.7</v>
       </c>
       <c r="N13" t="n">
-        <v>3082.47</v>
+        <v>3063.7</v>
       </c>
       <c r="O13" t="n">
-        <v>3136.3</v>
+        <v>3077.5</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1636,72 +1636,70 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3033.4</v>
+        <v>2994.3</v>
       </c>
       <c r="C14" t="n">
-        <v>3042.6</v>
+        <v>3004.3</v>
       </c>
       <c r="D14" t="n">
-        <v>2988.8</v>
+        <v>2943.4</v>
       </c>
       <c r="E14" t="n">
-        <v>2998.8</v>
+        <v>2971.5</v>
       </c>
       <c r="F14" t="n">
-        <v>-28.2</v>
+        <v>-27.3</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0091</v>
       </c>
       <c r="H14" t="n">
-        <v>53.8</v>
+        <v>60.9</v>
       </c>
       <c r="I14" t="n">
-        <v>2971.3</v>
+        <v>2935</v>
       </c>
       <c r="J14" t="n">
-        <v>2992.9</v>
+        <v>2936.55</v>
       </c>
       <c r="K14" t="n">
-        <v>3009.3</v>
+        <v>2971.9</v>
       </c>
       <c r="L14" t="n">
+        <v>3007.25</v>
+      </c>
+      <c r="M14" t="n">
         <v>3025.7</v>
       </c>
-      <c r="M14" t="n">
-        <v>3044.7</v>
-      </c>
       <c r="N14" t="n">
-        <v>3063.7</v>
+        <v>3044.15</v>
       </c>
       <c r="O14" t="n">
-        <v>3077.5</v>
+        <v>3096.4</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1722,57 +1720,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2994.3</v>
+        <v>2965.8</v>
       </c>
       <c r="C15" t="n">
-        <v>3004.3</v>
+        <v>3014.9</v>
       </c>
       <c r="D15" t="n">
-        <v>2943.4</v>
+        <v>2964.3</v>
       </c>
       <c r="E15" t="n">
-        <v>2971.5</v>
+        <v>3008.4</v>
       </c>
       <c r="F15" t="n">
-        <v>-27.3</v>
+        <v>36.9</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0091</v>
+        <v>0.0124</v>
       </c>
       <c r="H15" t="n">
-        <v>60.9</v>
+        <v>50.6</v>
       </c>
       <c r="I15" t="n">
-        <v>2935</v>
+        <v>2882.5</v>
       </c>
       <c r="J15" t="n">
-        <v>2936.55</v>
+        <v>2909.42</v>
       </c>
       <c r="K15" t="n">
-        <v>2971.9</v>
+        <v>2941.05</v>
       </c>
       <c r="L15" t="n">
-        <v>3007.25</v>
+        <v>2972.67</v>
       </c>
       <c r="M15" t="n">
-        <v>3025.7</v>
+        <v>3001.95</v>
       </c>
       <c r="N15" t="n">
-        <v>3044.15</v>
+        <v>3031.23</v>
       </c>
       <c r="O15" t="n">
-        <v>3096.4</v>
+        <v>3065.2</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1780,19 +1778,19 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
@@ -1804,59 +1802,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2965.8</v>
+        <v>3008.1</v>
       </c>
       <c r="C16" t="n">
-        <v>3014.9</v>
+        <v>3019.5</v>
       </c>
       <c r="D16" t="n">
-        <v>2964.3</v>
+        <v>2970.8</v>
       </c>
       <c r="E16" t="n">
-        <v>3008.4</v>
+        <v>2994</v>
       </c>
       <c r="F16" t="n">
-        <v>36.9</v>
+        <v>-14.4</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0048</v>
       </c>
       <c r="H16" t="n">
-        <v>50.6</v>
+        <v>48.7</v>
       </c>
       <c r="I16" t="n">
-        <v>2882.5</v>
+        <v>2913.7</v>
       </c>
       <c r="J16" t="n">
-        <v>2909.42</v>
+        <v>2967.2</v>
       </c>
       <c r="K16" t="n">
-        <v>2941.05</v>
+        <v>2983.1</v>
       </c>
       <c r="L16" t="n">
-        <v>2972.67</v>
+        <v>2999</v>
       </c>
       <c r="M16" t="n">
-        <v>3001.95</v>
+        <v>3033.7</v>
       </c>
       <c r="N16" t="n">
-        <v>3031.23</v>
+        <v>3068.4</v>
       </c>
       <c r="O16" t="n">
-        <v>3065.2</v>
+        <v>3065.5</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1864,18 +1858,18 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1888,55 +1882,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3008.1</v>
+        <v>2984.7</v>
       </c>
       <c r="C17" t="n">
-        <v>3019.5</v>
+        <v>2995.8</v>
       </c>
       <c r="D17" t="n">
-        <v>2970.8</v>
+        <v>2961.8</v>
       </c>
       <c r="E17" t="n">
-        <v>2994</v>
+        <v>2970.4</v>
       </c>
       <c r="F17" t="n">
-        <v>-14.4</v>
+        <v>-23.6</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>48.7</v>
+        <v>34</v>
       </c>
       <c r="I17" t="n">
-        <v>2913.7</v>
+        <v>2922.1</v>
       </c>
       <c r="J17" t="n">
-        <v>2967.2</v>
+        <v>2944.73</v>
       </c>
       <c r="K17" t="n">
-        <v>2983.1</v>
+        <v>2969.65</v>
       </c>
       <c r="L17" t="n">
-        <v>2999</v>
+        <v>2994.58</v>
       </c>
       <c r="M17" t="n">
-        <v>3033.7</v>
+        <v>3018.35</v>
       </c>
       <c r="N17" t="n">
-        <v>3068.4</v>
+        <v>3042.12</v>
       </c>
       <c r="O17" t="n">
-        <v>3065.5</v>
+        <v>3068.2</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1946,12 +1944,12 @@
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1970,57 +1968,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2984.7</v>
+        <v>2967.2</v>
       </c>
       <c r="C18" t="n">
-        <v>2995.8</v>
+        <v>3029.8</v>
       </c>
       <c r="D18" t="n">
-        <v>2961.8</v>
+        <v>2956.2</v>
       </c>
       <c r="E18" t="n">
-        <v>2970.4</v>
+        <v>2979.9</v>
       </c>
       <c r="F18" t="n">
-        <v>-23.6</v>
+        <v>9.5</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H18" t="n">
-        <v>34</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>2922.1</v>
+        <v>2927.8</v>
       </c>
       <c r="J18" t="n">
-        <v>2944.73</v>
+        <v>2932.2</v>
       </c>
       <c r="K18" t="n">
-        <v>2969.65</v>
+        <v>2953.4</v>
       </c>
       <c r="L18" t="n">
-        <v>2994.58</v>
+        <v>2974.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3018.35</v>
+        <v>2987.4</v>
       </c>
       <c r="N18" t="n">
-        <v>3042.12</v>
+        <v>3000.2</v>
       </c>
       <c r="O18" t="n">
-        <v>3068.2</v>
+        <v>3029.8</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2028,24 +2026,28 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R18" s="6" t="n">
+        <v/>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
@@ -2054,57 +2056,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2967.2</v>
+        <v>2981.2</v>
       </c>
       <c r="C19" t="n">
-        <v>3029.8</v>
+        <v>3006.1</v>
       </c>
       <c r="D19" t="n">
-        <v>2956.2</v>
+        <v>2974.4</v>
       </c>
       <c r="E19" t="n">
-        <v>2979.9</v>
+        <v>2991.8</v>
       </c>
       <c r="F19" t="n">
-        <v>9.5</v>
+        <v>11.9</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.004</v>
       </c>
       <c r="H19" t="n">
-        <v>73.59999999999999</v>
+        <v>31.7</v>
       </c>
       <c r="I19" t="n">
-        <v>2927.8</v>
+        <v>2882.6</v>
       </c>
       <c r="J19" t="n">
-        <v>2932.2</v>
+        <v>2899.75</v>
       </c>
       <c r="K19" t="n">
-        <v>2953.4</v>
+        <v>2943.1</v>
       </c>
       <c r="L19" t="n">
-        <v>2974.6</v>
+        <v>2986.45</v>
       </c>
       <c r="M19" t="n">
-        <v>2987.4</v>
+        <v>3016.7</v>
       </c>
       <c r="N19" t="n">
-        <v>3000.2</v>
+        <v>3046.95</v>
       </c>
       <c r="O19" t="n">
-        <v>3029.8</v>
+        <v>3103.4</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2115,25 +2117,19 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
@@ -2149,50 +2145,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2981.2</v>
+        <v>2995.3</v>
       </c>
       <c r="C20" t="n">
-        <v>3006.1</v>
+        <v>3012.8</v>
       </c>
       <c r="D20" t="n">
-        <v>2974.4</v>
+        <v>2972.7</v>
       </c>
       <c r="E20" t="n">
-        <v>2991.8</v>
+        <v>2990.7</v>
       </c>
       <c r="F20" t="n">
-        <v>11.9</v>
+        <v>-1.1</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0004</v>
       </c>
       <c r="H20" t="n">
-        <v>31.7</v>
+        <v>40.1</v>
       </c>
       <c r="I20" t="n">
-        <v>2882.6</v>
+        <v>2942.7</v>
       </c>
       <c r="J20" t="n">
-        <v>2899.75</v>
+        <v>2960.87</v>
       </c>
       <c r="K20" t="n">
-        <v>2943.1</v>
+        <v>2975.95</v>
       </c>
       <c r="L20" t="n">
-        <v>2986.45</v>
+        <v>2991.03</v>
       </c>
       <c r="M20" t="n">
-        <v>3016.7</v>
+        <v>3007.65</v>
       </c>
       <c r="N20" t="n">
-        <v>3046.95</v>
+        <v>3024.28</v>
       </c>
       <c r="O20" t="n">
-        <v>3103.4</v>
+        <v>3037.8</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2200,16 +2196,20 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2224,78 +2224,78 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2995.3</v>
+        <v>2991.7</v>
       </c>
       <c r="C21" t="n">
-        <v>3012.8</v>
+        <v>2994.8</v>
       </c>
       <c r="D21" t="n">
-        <v>2972.7</v>
+        <v>2949.3</v>
       </c>
       <c r="E21" t="n">
-        <v>2990.7</v>
+        <v>2973.5</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1</v>
+        <v>-17.2</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0058</v>
       </c>
       <c r="H21" t="n">
-        <v>40.1</v>
+        <v>45.5</v>
       </c>
       <c r="I21" t="n">
-        <v>2942.7</v>
+        <v>2932.6</v>
       </c>
       <c r="J21" t="n">
-        <v>2960.87</v>
+        <v>2949.57</v>
       </c>
       <c r="K21" t="n">
-        <v>2975.95</v>
+        <v>2970.65</v>
       </c>
       <c r="L21" t="n">
-        <v>2991.03</v>
+        <v>2991.72</v>
       </c>
       <c r="M21" t="n">
-        <v>3007.65</v>
+        <v>3010.75</v>
       </c>
       <c r="N21" t="n">
-        <v>3024.28</v>
+        <v>3029.78</v>
       </c>
       <c r="O21" t="n">
-        <v>3037.8</v>
+        <v>3052.9</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2310,79 +2310,79 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2991.7</v>
+        <v>2964.5</v>
       </c>
       <c r="C22" t="n">
-        <v>2994.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D22" t="n">
-        <v>2949.3</v>
+        <v>2952.7</v>
       </c>
       <c r="E22" t="n">
-        <v>2973.5</v>
+        <v>2955.2</v>
       </c>
       <c r="F22" t="n">
-        <v>-17.2</v>
+        <v>-18.3</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0062</v>
       </c>
       <c r="H22" t="n">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="I22" t="n">
-        <v>2932.6</v>
+        <v>2903.8</v>
       </c>
       <c r="J22" t="n">
-        <v>2949.57</v>
+        <v>2928.72</v>
       </c>
       <c r="K22" t="n">
-        <v>2970.65</v>
+        <v>2950.75</v>
       </c>
       <c r="L22" t="n">
-        <v>2991.72</v>
+        <v>2972.78</v>
       </c>
       <c r="M22" t="n">
-        <v>3010.75</v>
+        <v>2996.25</v>
       </c>
       <c r="N22" t="n">
-        <v>3029.78</v>
+        <v>3019.72</v>
       </c>
       <c r="O22" t="n">
-        <v>3052.9</v>
+        <v>3040.3</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
@@ -2396,57 +2396,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2964.5</v>
+        <v>2955.8</v>
       </c>
       <c r="C23" t="n">
-        <v>2998.7</v>
+        <v>2999.8</v>
       </c>
       <c r="D23" t="n">
-        <v>2952.7</v>
+        <v>2951.1</v>
       </c>
       <c r="E23" t="n">
-        <v>2955.2</v>
+        <v>2997</v>
       </c>
       <c r="F23" t="n">
-        <v>-18.3</v>
+        <v>41.8</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0141</v>
       </c>
       <c r="H23" t="n">
-        <v>46</v>
+        <v>48.7</v>
       </c>
       <c r="I23" t="n">
-        <v>2903.8</v>
+        <v>2906.7</v>
       </c>
       <c r="J23" t="n">
-        <v>2928.72</v>
+        <v>2898.95</v>
       </c>
       <c r="K23" t="n">
-        <v>2950.75</v>
+        <v>2932.2</v>
       </c>
       <c r="L23" t="n">
-        <v>2972.78</v>
+        <v>2965.45</v>
       </c>
       <c r="M23" t="n">
-        <v>2996.25</v>
+        <v>2978.2</v>
       </c>
       <c r="N23" t="n">
-        <v>3019.72</v>
+        <v>2990.95</v>
       </c>
       <c r="O23" t="n">
-        <v>3040.3</v>
+        <v>3044.7</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2454,23 +2454,23 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2489,50 +2489,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2955.8</v>
+        <v>2997</v>
       </c>
       <c r="C24" t="n">
-        <v>2999.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D24" t="n">
-        <v>2951.1</v>
+        <v>2965.5</v>
       </c>
       <c r="E24" t="n">
-        <v>2997</v>
+        <v>2969.8</v>
       </c>
       <c r="F24" t="n">
-        <v>41.8</v>
+        <v>-27.2</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0141</v>
+        <v>-0.0091</v>
       </c>
       <c r="H24" t="n">
-        <v>48.7</v>
+        <v>33.2</v>
       </c>
       <c r="I24" t="n">
-        <v>2906.7</v>
+        <v>2902.4</v>
       </c>
       <c r="J24" t="n">
-        <v>2898.95</v>
+        <v>2959.08</v>
       </c>
       <c r="K24" t="n">
-        <v>2932.2</v>
+        <v>2972.65</v>
       </c>
       <c r="L24" t="n">
-        <v>2965.45</v>
+        <v>2986.23</v>
       </c>
       <c r="M24" t="n">
-        <v>2978.2</v>
+        <v>3021.35</v>
       </c>
       <c r="N24" t="n">
-        <v>2990.95</v>
+        <v>3056.47</v>
       </c>
       <c r="O24" t="n">
-        <v>3044.7</v>
+        <v>3048.5</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2540,23 +2540,21 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2568,60 +2566,62 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2997</v>
+        <v>2974.6</v>
       </c>
       <c r="C25" t="n">
-        <v>2998.7</v>
+        <v>2979</v>
       </c>
       <c r="D25" t="n">
-        <v>2965.5</v>
+        <v>2932.1</v>
       </c>
       <c r="E25" t="n">
-        <v>2969.8</v>
+        <v>2951.7</v>
       </c>
       <c r="F25" t="n">
-        <v>-27.2</v>
+        <v>-18.1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0091</v>
+        <v>-0.0061</v>
       </c>
       <c r="H25" t="n">
-        <v>33.2</v>
+        <v>46.9</v>
       </c>
       <c r="I25" t="n">
-        <v>2902.4</v>
+        <v>2932.3</v>
       </c>
       <c r="J25" t="n">
-        <v>2959.08</v>
+        <v>2930.45</v>
       </c>
       <c r="K25" t="n">
-        <v>2972.65</v>
+        <v>2953.2</v>
       </c>
       <c r="L25" t="n">
-        <v>2986.23</v>
+        <v>2975.95</v>
       </c>
       <c r="M25" t="n">
-        <v>3021.35</v>
+        <v>2986.4</v>
       </c>
       <c r="N25" t="n">
-        <v>3056.47</v>
+        <v>2996.85</v>
       </c>
       <c r="O25" t="n">
-        <v>3048.5</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
+        <v>3031.9</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q25" s="6" t="n">
         <v/>
@@ -2631,7 +2631,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S25" s="7" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2652,74 +2652,70 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2974.6</v>
+        <v>2948.5</v>
       </c>
       <c r="C26" t="n">
-        <v>2979</v>
+        <v>2969.7</v>
       </c>
       <c r="D26" t="n">
-        <v>2932.1</v>
+        <v>2934.5</v>
       </c>
       <c r="E26" t="n">
-        <v>2951.7</v>
+        <v>2941.3</v>
       </c>
       <c r="F26" t="n">
-        <v>-18.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0035</v>
       </c>
       <c r="H26" t="n">
-        <v>46.9</v>
+        <v>35.2</v>
       </c>
       <c r="I26" t="n">
-        <v>2932.3</v>
+        <v>2885.2</v>
       </c>
       <c r="J26" t="n">
-        <v>2930.45</v>
+        <v>2902.88</v>
       </c>
       <c r="K26" t="n">
-        <v>2953.2</v>
+        <v>2928.25</v>
       </c>
       <c r="L26" t="n">
-        <v>2975.95</v>
+        <v>2953.62</v>
       </c>
       <c r="M26" t="n">
-        <v>2986.4</v>
+        <v>2975.15</v>
       </c>
       <c r="N26" t="n">
-        <v>2996.85</v>
+        <v>2996.67</v>
       </c>
       <c r="O26" t="n">
-        <v>3031.9</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3025.9</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
       </c>
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2738,57 +2734,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2948.5</v>
+        <v>2955.5</v>
       </c>
       <c r="C27" t="n">
-        <v>2969.7</v>
+        <v>2985.9</v>
       </c>
       <c r="D27" t="n">
-        <v>2934.5</v>
+        <v>2941.2</v>
       </c>
       <c r="E27" t="n">
-        <v>2941.3</v>
+        <v>2960</v>
       </c>
       <c r="F27" t="n">
-        <v>-10.4</v>
+        <v>18.7</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0064</v>
       </c>
       <c r="H27" t="n">
-        <v>35.2</v>
+        <v>44.7</v>
       </c>
       <c r="I27" t="n">
-        <v>2885.2</v>
+        <v>2899.3</v>
       </c>
       <c r="J27" t="n">
-        <v>2902.88</v>
+        <v>2900.7</v>
       </c>
       <c r="K27" t="n">
-        <v>2928.25</v>
+        <v>2923.7</v>
       </c>
       <c r="L27" t="n">
-        <v>2953.62</v>
+        <v>2946.7</v>
       </c>
       <c r="M27" t="n">
-        <v>2975.15</v>
+        <v>2958.9</v>
       </c>
       <c r="N27" t="n">
-        <v>2996.67</v>
+        <v>2971.1</v>
       </c>
       <c r="O27" t="n">
-        <v>3025.9</v>
+        <v>3004.9</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2801,14 +2797,18 @@
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2818,59 +2818,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2955.5</v>
+        <v>2961.5</v>
       </c>
       <c r="C28" t="n">
-        <v>2985.9</v>
+        <v>2968.3</v>
       </c>
       <c r="D28" t="n">
-        <v>2941.2</v>
+        <v>2933.4</v>
       </c>
       <c r="E28" t="n">
-        <v>2960</v>
+        <v>2964.5</v>
       </c>
       <c r="F28" t="n">
-        <v>18.7</v>
+        <v>4.5</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0015</v>
       </c>
       <c r="H28" t="n">
-        <v>44.7</v>
+        <v>34.9</v>
       </c>
       <c r="I28" t="n">
-        <v>2899.3</v>
+        <v>2896.5</v>
       </c>
       <c r="J28" t="n">
-        <v>2900.7</v>
+        <v>2913.53</v>
       </c>
       <c r="K28" t="n">
-        <v>2923.7</v>
+        <v>2937.65</v>
       </c>
       <c r="L28" t="n">
-        <v>2946.7</v>
+        <v>2961.77</v>
       </c>
       <c r="M28" t="n">
-        <v>2958.9</v>
+        <v>2982.35</v>
       </c>
       <c r="N28" t="n">
-        <v>2971.1</v>
+        <v>3002.92</v>
       </c>
       <c r="O28" t="n">
-        <v>3004.9</v>
+        <v>3030.6</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2878,24 +2874,22 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
@@ -2904,61 +2898,69 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2961.5</v>
+        <v>2966.9</v>
       </c>
       <c r="C29" t="n">
-        <v>2968.3</v>
+        <v>2978.3</v>
       </c>
       <c r="D29" t="n">
-        <v>2933.4</v>
+        <v>2902.3</v>
       </c>
       <c r="E29" t="n">
-        <v>2964.5</v>
+        <v>2915.4</v>
       </c>
       <c r="F29" t="n">
-        <v>4.5</v>
+        <v>-49.1</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0166</v>
       </c>
       <c r="H29" t="n">
-        <v>34.9</v>
+        <v>76</v>
       </c>
       <c r="I29" t="n">
-        <v>2896.5</v>
+        <v>2898.5</v>
       </c>
       <c r="J29" t="n">
-        <v>2913.53</v>
+        <v>2936.42</v>
       </c>
       <c r="K29" t="n">
-        <v>2937.65</v>
+        <v>2947.05</v>
       </c>
       <c r="L29" t="n">
-        <v>2961.77</v>
+        <v>2957.67</v>
       </c>
       <c r="M29" t="n">
-        <v>2982.35</v>
+        <v>2981.95</v>
       </c>
       <c r="N29" t="n">
-        <v>3002.92</v>
+        <v>3006.23</v>
       </c>
       <c r="O29" t="n">
-        <v>3030.6</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
+        <v>3003.2</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
@@ -2967,7 +2969,7 @@
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2979,88 +2981,84 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W29" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2966.9</v>
+        <v>2906.6</v>
       </c>
       <c r="C30" t="n">
-        <v>2978.3</v>
+        <v>2957.9</v>
       </c>
       <c r="D30" t="n">
-        <v>2902.3</v>
+        <v>2905.6</v>
       </c>
       <c r="E30" t="n">
-        <v>2915.4</v>
+        <v>2954.3</v>
       </c>
       <c r="F30" t="n">
-        <v>-49.1</v>
+        <v>38.9</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0166</v>
+        <v>0.0133</v>
       </c>
       <c r="H30" t="n">
-        <v>76</v>
+        <v>52.3</v>
       </c>
       <c r="I30" t="n">
-        <v>2898.5</v>
+        <v>2826.3</v>
       </c>
       <c r="J30" t="n">
-        <v>2936.42</v>
+        <v>2826.95</v>
       </c>
       <c r="K30" t="n">
-        <v>2947.05</v>
+        <v>2877.4</v>
       </c>
       <c r="L30" t="n">
-        <v>2957.67</v>
+        <v>2927.85</v>
       </c>
       <c r="M30" t="n">
-        <v>2981.95</v>
+        <v>2953.4</v>
       </c>
       <c r="N30" t="n">
-        <v>3006.23</v>
+        <v>2978.95</v>
       </c>
       <c r="O30" t="n">
-        <v>3003.2</v>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
+        <v>3054.3</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
@@ -3074,76 +3072,78 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2906.6</v>
+        <v>2954</v>
       </c>
       <c r="C31" t="n">
-        <v>2957.9</v>
+        <v>2976.3</v>
       </c>
       <c r="D31" t="n">
-        <v>2905.6</v>
+        <v>2905.3</v>
       </c>
       <c r="E31" t="n">
-        <v>2954.3</v>
+        <v>2938</v>
       </c>
       <c r="F31" t="n">
-        <v>38.9</v>
+        <v>-16.3</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0055</v>
       </c>
       <c r="H31" t="n">
-        <v>52.3</v>
+        <v>71</v>
       </c>
       <c r="I31" t="n">
-        <v>2826.3</v>
+        <v>2853.3</v>
       </c>
       <c r="J31" t="n">
-        <v>2826.95</v>
+        <v>2913.28</v>
       </c>
       <c r="K31" t="n">
-        <v>2877.4</v>
+        <v>2928.15</v>
       </c>
       <c r="L31" t="n">
-        <v>2927.85</v>
+        <v>2943.03</v>
       </c>
       <c r="M31" t="n">
-        <v>2953.4</v>
+        <v>2980.45</v>
       </c>
       <c r="N31" t="n">
-        <v>2978.95</v>
+        <v>3017.87</v>
       </c>
       <c r="O31" t="n">
-        <v>3054.3</v>
+        <v>3010.2</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3158,78 +3158,76 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2954</v>
+        <v>2950</v>
       </c>
       <c r="C32" t="n">
-        <v>2976.3</v>
+        <v>2994.6</v>
       </c>
       <c r="D32" t="n">
-        <v>2905.3</v>
+        <v>2948.4</v>
       </c>
       <c r="E32" t="n">
-        <v>2938</v>
+        <v>2989.3</v>
       </c>
       <c r="F32" t="n">
-        <v>-16.3</v>
+        <v>51.3</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0175</v>
       </c>
       <c r="H32" t="n">
-        <v>71</v>
+        <v>46.2</v>
       </c>
       <c r="I32" t="n">
-        <v>2853.3</v>
+        <v>2834.3</v>
       </c>
       <c r="J32" t="n">
-        <v>2913.28</v>
+        <v>2865.6</v>
       </c>
       <c r="K32" t="n">
-        <v>2928.15</v>
+        <v>2902.5</v>
       </c>
       <c r="L32" t="n">
-        <v>2943.03</v>
+        <v>2939.4</v>
       </c>
       <c r="M32" t="n">
-        <v>2980.45</v>
+        <v>2973.5</v>
       </c>
       <c r="N32" t="n">
-        <v>3017.87</v>
+        <v>3007.6</v>
       </c>
       <c r="O32" t="n">
-        <v>3010.2</v>
+        <v>3047.3</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3244,57 +3242,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2950</v>
+        <v>2992.4</v>
       </c>
       <c r="C33" t="n">
-        <v>2994.6</v>
+        <v>3051.8</v>
       </c>
       <c r="D33" t="n">
-        <v>2948.4</v>
+        <v>2986.1</v>
       </c>
       <c r="E33" t="n">
-        <v>2989.3</v>
+        <v>3044.7</v>
       </c>
       <c r="F33" t="n">
-        <v>51.3</v>
+        <v>55.4</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0185</v>
       </c>
       <c r="H33" t="n">
-        <v>46.2</v>
+        <v>65.7</v>
       </c>
       <c r="I33" t="n">
-        <v>2834.3</v>
+        <v>2902.2</v>
       </c>
       <c r="J33" t="n">
-        <v>2865.6</v>
+        <v>2952</v>
       </c>
       <c r="K33" t="n">
-        <v>2902.5</v>
+        <v>2966.2</v>
       </c>
       <c r="L33" t="n">
-        <v>2939.4</v>
+        <v>2980.4</v>
       </c>
       <c r="M33" t="n">
-        <v>2973.5</v>
+        <v>3012.4</v>
       </c>
       <c r="N33" t="n">
-        <v>3007.6</v>
+        <v>3044.4</v>
       </c>
       <c r="O33" t="n">
-        <v>3047.3</v>
+        <v>3040.8</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3305,80 +3303,80 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W33" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W33" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2992.4</v>
+        <v>3049.1</v>
       </c>
       <c r="C34" t="n">
-        <v>3051.8</v>
+        <v>3058.3</v>
       </c>
       <c r="D34" t="n">
-        <v>2986.1</v>
+        <v>3023.3</v>
       </c>
       <c r="E34" t="n">
-        <v>3044.7</v>
+        <v>3025.4</v>
       </c>
       <c r="F34" t="n">
-        <v>55.4</v>
+        <v>-19.3</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0063</v>
       </c>
       <c r="H34" t="n">
-        <v>65.7</v>
+        <v>35</v>
       </c>
       <c r="I34" t="n">
-        <v>2902.2</v>
+        <v>2920.4</v>
       </c>
       <c r="J34" t="n">
-        <v>2952</v>
+        <v>2991.87</v>
       </c>
       <c r="K34" t="n">
-        <v>2966.2</v>
+        <v>3011.85</v>
       </c>
       <c r="L34" t="n">
-        <v>2980.4</v>
+        <v>3031.83</v>
       </c>
       <c r="M34" t="n">
-        <v>3012.4</v>
+        <v>3077.55</v>
       </c>
       <c r="N34" t="n">
-        <v>3044.4</v>
+        <v>3123.27</v>
       </c>
       <c r="O34" t="n">
-        <v>3040.8</v>
+        <v>3117.5</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3391,78 +3389,76 @@
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3049.1</v>
+        <v>3028.5</v>
       </c>
       <c r="C35" t="n">
-        <v>3058.3</v>
+        <v>3041</v>
       </c>
       <c r="D35" t="n">
-        <v>3023.3</v>
+        <v>3004.9</v>
       </c>
       <c r="E35" t="n">
-        <v>3025.4</v>
+        <v>3009.1</v>
       </c>
       <c r="F35" t="n">
-        <v>-19.3</v>
+        <v>-16.3</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0054</v>
       </c>
       <c r="H35" t="n">
-        <v>35</v>
+        <v>36.1</v>
       </c>
       <c r="I35" t="n">
-        <v>2920.4</v>
+        <v>2988.3</v>
       </c>
       <c r="J35" t="n">
-        <v>2991.87</v>
+        <v>2982.7</v>
       </c>
       <c r="K35" t="n">
-        <v>3011.85</v>
+        <v>3007.9</v>
       </c>
       <c r="L35" t="n">
-        <v>3031.83</v>
+        <v>3033.1</v>
       </c>
       <c r="M35" t="n">
-        <v>3077.55</v>
+        <v>3042.9</v>
       </c>
       <c r="N35" t="n">
-        <v>3123.27</v>
+        <v>3052.7</v>
       </c>
       <c r="O35" t="n">
-        <v>3117.5</v>
+        <v>3093.3</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3470,12 +3466,14 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3494,57 +3492,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3028.5</v>
+        <v>3008.5</v>
       </c>
       <c r="C36" t="n">
-        <v>3041</v>
+        <v>3046.8</v>
       </c>
       <c r="D36" t="n">
-        <v>3004.9</v>
+        <v>3002</v>
       </c>
       <c r="E36" t="n">
-        <v>3009.1</v>
+        <v>3041.6</v>
       </c>
       <c r="F36" t="n">
-        <v>-16.3</v>
+        <v>32.5</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0054</v>
+        <v>0.0108</v>
       </c>
       <c r="H36" t="n">
-        <v>36.1</v>
+        <v>44.8</v>
       </c>
       <c r="I36" t="n">
-        <v>2988.3</v>
+        <v>2968.8</v>
       </c>
       <c r="J36" t="n">
-        <v>2982.7</v>
+        <v>2966.08</v>
       </c>
       <c r="K36" t="n">
-        <v>3007.9</v>
+        <v>2991.05</v>
       </c>
       <c r="L36" t="n">
-        <v>3033.1</v>
+        <v>3016.03</v>
       </c>
       <c r="M36" t="n">
-        <v>3042.9</v>
+        <v>3027.15</v>
       </c>
       <c r="N36" t="n">
-        <v>3052.7</v>
+        <v>3038.28</v>
       </c>
       <c r="O36" t="n">
-        <v>3093.3</v>
+        <v>3077.1</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3552,22 +3550,24 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
@@ -3578,57 +3578,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3008.5</v>
+        <v>3038.9</v>
       </c>
       <c r="C37" t="n">
-        <v>3046.8</v>
+        <v>3044.6</v>
       </c>
       <c r="D37" t="n">
-        <v>3002</v>
+        <v>3016</v>
       </c>
       <c r="E37" t="n">
-        <v>3041.6</v>
+        <v>3025</v>
       </c>
       <c r="F37" t="n">
-        <v>32.5</v>
+        <v>-16.6</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0108</v>
+        <v>-0.0055</v>
       </c>
       <c r="H37" t="n">
-        <v>44.8</v>
+        <v>28.6</v>
       </c>
       <c r="I37" t="n">
-        <v>2968.8</v>
+        <v>2957.2</v>
       </c>
       <c r="J37" t="n">
-        <v>2966.08</v>
+        <v>3005.4</v>
       </c>
       <c r="K37" t="n">
-        <v>2991.05</v>
+        <v>3019.2</v>
       </c>
       <c r="L37" t="n">
-        <v>3016.03</v>
+        <v>3033</v>
       </c>
       <c r="M37" t="n">
-        <v>3027.15</v>
+        <v>3064</v>
       </c>
       <c r="N37" t="n">
-        <v>3038.28</v>
+        <v>3095</v>
       </c>
       <c r="O37" t="n">
-        <v>3077.1</v>
+        <v>3091.6</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3636,23 +3636,21 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3664,57 +3662,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3038.9</v>
+        <v>3024.7</v>
       </c>
       <c r="C38" t="n">
-        <v>3044.6</v>
+        <v>3045.8</v>
       </c>
       <c r="D38" t="n">
-        <v>3016</v>
+        <v>3019.9</v>
       </c>
       <c r="E38" t="n">
-        <v>3025</v>
+        <v>3035.5</v>
       </c>
       <c r="F38" t="n">
-        <v>-16.6</v>
+        <v>10.5</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0035</v>
       </c>
       <c r="H38" t="n">
-        <v>28.6</v>
+        <v>25.9</v>
       </c>
       <c r="I38" t="n">
-        <v>2957.2</v>
+        <v>2987.4</v>
       </c>
       <c r="J38" t="n">
-        <v>3005.4</v>
+        <v>2993.75</v>
       </c>
       <c r="K38" t="n">
-        <v>3019.2</v>
+        <v>3010.7</v>
       </c>
       <c r="L38" t="n">
-        <v>3033</v>
+        <v>3027.65</v>
       </c>
       <c r="M38" t="n">
-        <v>3064</v>
+        <v>3039.3</v>
       </c>
       <c r="N38" t="n">
-        <v>3095</v>
+        <v>3050.95</v>
       </c>
       <c r="O38" t="n">
-        <v>3091.6</v>
+        <v>3073.2</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3722,19 +3720,19 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3746,59 +3744,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3024.7</v>
+        <v>3036.1</v>
       </c>
       <c r="C39" t="n">
-        <v>3045.8</v>
+        <v>3060</v>
       </c>
       <c r="D39" t="n">
-        <v>3019.9</v>
+        <v>3033.1</v>
       </c>
       <c r="E39" t="n">
-        <v>3035.5</v>
+        <v>3052.8</v>
       </c>
       <c r="F39" t="n">
-        <v>10.5</v>
+        <v>17.3</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0057</v>
       </c>
       <c r="H39" t="n">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
       <c r="I39" t="n">
-        <v>2987.4</v>
+        <v>2994</v>
       </c>
       <c r="J39" t="n">
-        <v>2993.75</v>
+        <v>3010.92</v>
       </c>
       <c r="K39" t="n">
-        <v>3010.7</v>
+        <v>3022.55</v>
       </c>
       <c r="L39" t="n">
-        <v>3027.65</v>
+        <v>3034.17</v>
       </c>
       <c r="M39" t="n">
-        <v>3039.3</v>
+        <v>3048.45</v>
       </c>
       <c r="N39" t="n">
-        <v>3050.95</v>
+        <v>3062.73</v>
       </c>
       <c r="O39" t="n">
-        <v>3073.2</v>
+        <v>3071.7</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3809,7 +3803,7 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
+      <c r="S39" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3835,50 +3829,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3036.1</v>
+        <v>3056.2</v>
       </c>
       <c r="C40" t="n">
-        <v>3060</v>
+        <v>3076.3</v>
       </c>
       <c r="D40" t="n">
-        <v>3033.1</v>
+        <v>3052.5</v>
       </c>
       <c r="E40" t="n">
-        <v>3052.8</v>
+        <v>3060.2</v>
       </c>
       <c r="F40" t="n">
-        <v>17.3</v>
+        <v>7.4</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0024</v>
       </c>
       <c r="H40" t="n">
-        <v>26.9</v>
+        <v>23.8</v>
       </c>
       <c r="I40" t="n">
-        <v>2994</v>
+        <v>3006.2</v>
       </c>
       <c r="J40" t="n">
-        <v>3010.92</v>
+        <v>3029.03</v>
       </c>
       <c r="K40" t="n">
-        <v>3022.55</v>
+        <v>3039.35</v>
       </c>
       <c r="L40" t="n">
-        <v>3034.17</v>
+        <v>3049.68</v>
       </c>
       <c r="M40" t="n">
-        <v>3048.45</v>
+        <v>3066.25</v>
       </c>
       <c r="N40" t="n">
-        <v>3062.73</v>
+        <v>3082.82</v>
       </c>
       <c r="O40" t="n">
-        <v>3071.7</v>
+        <v>3086.9</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3889,7 +3883,7 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="10" t="inlineStr">
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3915,50 +3909,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3056.2</v>
+        <v>3062.2</v>
       </c>
       <c r="C41" t="n">
         <v>3076.3</v>
       </c>
       <c r="D41" t="n">
-        <v>3052.5</v>
+        <v>3051.7</v>
       </c>
       <c r="E41" t="n">
-        <v>3060.2</v>
+        <v>3074.9</v>
       </c>
       <c r="F41" t="n">
-        <v>7.4</v>
+        <v>14.7</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0048</v>
       </c>
       <c r="H41" t="n">
-        <v>23.8</v>
+        <v>24.6</v>
       </c>
       <c r="I41" t="n">
-        <v>3006.2</v>
+        <v>3028.7</v>
       </c>
       <c r="J41" t="n">
-        <v>3029.03</v>
+        <v>3034.3</v>
       </c>
       <c r="K41" t="n">
-        <v>3039.35</v>
+        <v>3048.3</v>
       </c>
       <c r="L41" t="n">
-        <v>3049.68</v>
+        <v>3062.3</v>
       </c>
       <c r="M41" t="n">
-        <v>3066.25</v>
+        <v>3072.1</v>
       </c>
       <c r="N41" t="n">
-        <v>3082.82</v>
+        <v>3081.9</v>
       </c>
       <c r="O41" t="n">
-        <v>3086.9</v>
+        <v>3100.1</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3969,7 +3963,7 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3990,55 +3984,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3062.2</v>
+        <v>3073.5</v>
       </c>
       <c r="C42" t="n">
-        <v>3076.3</v>
+        <v>3079.9</v>
       </c>
       <c r="D42" t="n">
-        <v>3051.7</v>
+        <v>3055.9</v>
       </c>
       <c r="E42" t="n">
-        <v>3074.9</v>
+        <v>3064.9</v>
       </c>
       <c r="F42" t="n">
-        <v>14.7</v>
+        <v>-10</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.0033</v>
       </c>
       <c r="H42" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="I42" t="n">
-        <v>3028.7</v>
+        <v>3027.1</v>
       </c>
       <c r="J42" t="n">
-        <v>3034.3</v>
+        <v>3055.75</v>
       </c>
       <c r="K42" t="n">
-        <v>3048.3</v>
+        <v>3062.6</v>
       </c>
       <c r="L42" t="n">
-        <v>3062.3</v>
+        <v>3069.45</v>
       </c>
       <c r="M42" t="n">
-        <v>3072.1</v>
+        <v>3087.2</v>
       </c>
       <c r="N42" t="n">
-        <v>3081.9</v>
+        <v>3104.95</v>
       </c>
       <c r="O42" t="n">
-        <v>3100.1</v>
+        <v>3100.9</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4046,18 +4044,18 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4079,63 +4077,67 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3073.5</v>
+        <v>3063.7</v>
       </c>
       <c r="C43" t="n">
-        <v>3079.9</v>
+        <v>3066.6</v>
       </c>
       <c r="D43" t="n">
-        <v>3055.9</v>
+        <v>3024.1</v>
       </c>
       <c r="E43" t="n">
-        <v>3064.9</v>
+        <v>3026.4</v>
       </c>
       <c r="F43" t="n">
-        <v>-10</v>
+        <v>-38.5</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0126</v>
       </c>
       <c r="H43" t="n">
-        <v>24</v>
+        <v>42.5</v>
       </c>
       <c r="I43" t="n">
-        <v>3027.1</v>
+        <v>3031.9</v>
       </c>
       <c r="J43" t="n">
-        <v>3055.75</v>
+        <v>3039.4</v>
       </c>
       <c r="K43" t="n">
-        <v>3062.6</v>
+        <v>3052.9</v>
       </c>
       <c r="L43" t="n">
-        <v>3069.45</v>
+        <v>3066.4</v>
       </c>
       <c r="M43" t="n">
-        <v>3087.2</v>
+        <v>3076.9</v>
       </c>
       <c r="N43" t="n">
-        <v>3104.95</v>
+        <v>3087.4</v>
       </c>
       <c r="O43" t="n">
-        <v>3100.9</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
+        <v>3103.9</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4149,88 +4151,80 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W43" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3063.7</v>
+        <v>3025.9</v>
       </c>
       <c r="C44" t="n">
-        <v>3066.6</v>
+        <v>3059.1</v>
       </c>
       <c r="D44" t="n">
-        <v>3024.1</v>
+        <v>3019.8</v>
       </c>
       <c r="E44" t="n">
-        <v>3026.4</v>
+        <v>3039.9</v>
       </c>
       <c r="F44" t="n">
-        <v>-38.5</v>
+        <v>13.5</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0045</v>
       </c>
       <c r="H44" t="n">
-        <v>42.5</v>
+        <v>39.3</v>
       </c>
       <c r="I44" t="n">
-        <v>3031.9</v>
+        <v>2981.6</v>
       </c>
       <c r="J44" t="n">
-        <v>3039.4</v>
+        <v>2974.42</v>
       </c>
       <c r="K44" t="n">
-        <v>3052.9</v>
+        <v>3005.15</v>
       </c>
       <c r="L44" t="n">
-        <v>3066.4</v>
+        <v>3035.88</v>
       </c>
       <c r="M44" t="n">
-        <v>3076.9</v>
+        <v>3047.65</v>
       </c>
       <c r="N44" t="n">
-        <v>3087.4</v>
+        <v>3059.42</v>
       </c>
       <c r="O44" t="n">
-        <v>3103.9</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
+        <v>3109.1</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
@@ -4242,74 +4236,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3025.9</v>
+        <v>3041.4</v>
       </c>
       <c r="C45" t="n">
-        <v>3059.1</v>
+        <v>3048.5</v>
       </c>
       <c r="D45" t="n">
-        <v>3019.8</v>
+        <v>2993.2</v>
       </c>
       <c r="E45" t="n">
-        <v>3039.9</v>
+        <v>2999.2</v>
       </c>
       <c r="F45" t="n">
-        <v>13.5</v>
+        <v>-40.7</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0134</v>
       </c>
       <c r="H45" t="n">
-        <v>39.3</v>
+        <v>55.3</v>
       </c>
       <c r="I45" t="n">
-        <v>2981.6</v>
+        <v>2980.5</v>
       </c>
       <c r="J45" t="n">
-        <v>2974.42</v>
+        <v>3000.82</v>
       </c>
       <c r="K45" t="n">
-        <v>3005.15</v>
+        <v>3020.25</v>
       </c>
       <c r="L45" t="n">
-        <v>3035.88</v>
+        <v>3039.67</v>
       </c>
       <c r="M45" t="n">
-        <v>3047.65</v>
+        <v>3059.55</v>
       </c>
       <c r="N45" t="n">
-        <v>3059.42</v>
+        <v>3079.42</v>
       </c>
       <c r="O45" t="n">
-        <v>3109.1</v>
+        <v>3098.4</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4322,81 +4322,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3041.4</v>
+        <v>2999.6</v>
       </c>
       <c r="C46" t="n">
-        <v>3048.5</v>
+        <v>3026.7</v>
       </c>
       <c r="D46" t="n">
-        <v>2993.2</v>
+        <v>2997.9</v>
       </c>
       <c r="E46" t="n">
-        <v>2999.2</v>
+        <v>3022.1</v>
       </c>
       <c r="F46" t="n">
-        <v>-40.7</v>
+        <v>22.9</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0134</v>
+        <v>0.0076</v>
       </c>
       <c r="H46" t="n">
-        <v>55.3</v>
+        <v>28.8</v>
       </c>
       <c r="I46" t="n">
-        <v>2980.5</v>
+        <v>2937.9</v>
       </c>
       <c r="J46" t="n">
-        <v>3000.82</v>
+        <v>2933.07</v>
       </c>
       <c r="K46" t="n">
-        <v>3020.25</v>
+        <v>2971.55</v>
       </c>
       <c r="L46" t="n">
-        <v>3039.67</v>
+        <v>3010.02</v>
       </c>
       <c r="M46" t="n">
-        <v>3059.55</v>
+        <v>3026.85</v>
       </c>
       <c r="N46" t="n">
-        <v>3079.42</v>
+        <v>3043.67</v>
       </c>
       <c r="O46" t="n">
-        <v>3098.4</v>
+        <v>3103.8</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4408,74 +4402,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2999.6</v>
+        <v>3023</v>
       </c>
       <c r="C47" t="n">
-        <v>3026.7</v>
+        <v>3028.9</v>
       </c>
       <c r="D47" t="n">
-        <v>2997.9</v>
+        <v>2996</v>
       </c>
       <c r="E47" t="n">
-        <v>3022.1</v>
+        <v>3001.6</v>
       </c>
       <c r="F47" t="n">
-        <v>22.9</v>
+        <v>-20.5</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0076</v>
+        <v>-0.0068</v>
       </c>
       <c r="H47" t="n">
-        <v>28.8</v>
+        <v>32.9</v>
       </c>
       <c r="I47" t="n">
-        <v>2937.9</v>
+        <v>2969.1</v>
       </c>
       <c r="J47" t="n">
-        <v>2933.07</v>
+        <v>2998.2</v>
       </c>
       <c r="K47" t="n">
-        <v>2971.55</v>
+        <v>3007.7</v>
       </c>
       <c r="L47" t="n">
-        <v>3010.02</v>
+        <v>3017.2</v>
       </c>
       <c r="M47" t="n">
-        <v>3026.85</v>
+        <v>3036.5</v>
       </c>
       <c r="N47" t="n">
-        <v>3043.67</v>
+        <v>3055.8</v>
       </c>
       <c r="O47" t="n">
-        <v>3103.8</v>
+        <v>3055.5</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4490,79 +4490,77 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3023</v>
+        <v>3004.6</v>
       </c>
       <c r="C48" t="n">
-        <v>3028.9</v>
+        <v>3025.4</v>
       </c>
       <c r="D48" t="n">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="E48" t="n">
-        <v>3001.6</v>
+        <v>3014.4</v>
       </c>
       <c r="F48" t="n">
-        <v>-20.5</v>
+        <v>12.8</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0043</v>
       </c>
       <c r="H48" t="n">
-        <v>32.9</v>
+        <v>28.4</v>
       </c>
       <c r="I48" t="n">
-        <v>2969.1</v>
+        <v>2963.1</v>
       </c>
       <c r="J48" t="n">
-        <v>2998.2</v>
+        <v>2963.28</v>
       </c>
       <c r="K48" t="n">
-        <v>3007.7</v>
+        <v>2985.15</v>
       </c>
       <c r="L48" t="n">
-        <v>3017.2</v>
+        <v>3007.03</v>
       </c>
       <c r="M48" t="n">
-        <v>3036.5</v>
+        <v>3018.05</v>
       </c>
       <c r="N48" t="n">
-        <v>3055.8</v>
+        <v>3029.08</v>
       </c>
       <c r="O48" t="n">
-        <v>3055.5</v>
+        <v>3061.8</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
       <c r="U48" s="8" t="n">
         <v/>
       </c>
@@ -4576,57 +4574,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3004.6</v>
+        <v>3014.6</v>
       </c>
       <c r="C49" t="n">
-        <v>3025.4</v>
+        <v>3020.5</v>
       </c>
       <c r="D49" t="n">
-        <v>2997</v>
+        <v>3002.6</v>
       </c>
       <c r="E49" t="n">
-        <v>3014.4</v>
+        <v>3010.1</v>
       </c>
       <c r="F49" t="n">
-        <v>12.8</v>
+        <v>-4.3</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0014</v>
       </c>
       <c r="H49" t="n">
-        <v>28.4</v>
+        <v>17.9</v>
       </c>
       <c r="I49" t="n">
-        <v>2963.1</v>
+        <v>2968.6</v>
       </c>
       <c r="J49" t="n">
-        <v>2963.28</v>
+        <v>2987.6</v>
       </c>
       <c r="K49" t="n">
-        <v>2985.15</v>
+        <v>3000.2</v>
       </c>
       <c r="L49" t="n">
-        <v>3007.03</v>
+        <v>3012.8</v>
       </c>
       <c r="M49" t="n">
-        <v>3018.05</v>
+        <v>3028.6</v>
       </c>
       <c r="N49" t="n">
-        <v>3029.08</v>
+        <v>3044.4</v>
       </c>
       <c r="O49" t="n">
-        <v>3061.8</v>
+        <v>3053.8</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4639,13 +4637,11 @@
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4660,57 +4656,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3014.6</v>
+        <v>3016.9</v>
       </c>
       <c r="C50" t="n">
-        <v>3020.5</v>
+        <v>3024.2</v>
       </c>
       <c r="D50" t="n">
-        <v>3002.6</v>
+        <v>3002.1</v>
       </c>
       <c r="E50" t="n">
-        <v>3010.1</v>
+        <v>3019</v>
       </c>
       <c r="F50" t="n">
-        <v>-4.3</v>
+        <v>8.9</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0014</v>
+        <v>0.003</v>
       </c>
       <c r="H50" t="n">
-        <v>17.9</v>
+        <v>22.1</v>
       </c>
       <c r="I50" t="n">
-        <v>2968.6</v>
+        <v>2984.7</v>
       </c>
       <c r="J50" t="n">
-        <v>2987.6</v>
+        <v>2991.48</v>
       </c>
       <c r="K50" t="n">
-        <v>3000.2</v>
+        <v>3001.15</v>
       </c>
       <c r="L50" t="n">
-        <v>3012.8</v>
+        <v>3010.83</v>
       </c>
       <c r="M50" t="n">
-        <v>3028.6</v>
+        <v>3019.05</v>
       </c>
       <c r="N50" t="n">
-        <v>3044.4</v>
+        <v>3027.28</v>
       </c>
       <c r="O50" t="n">
-        <v>3053.8</v>
+        <v>3038.4</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4723,11 +4719,13 @@
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4742,76 +4740,80 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3016.9</v>
+        <v>3019.6</v>
       </c>
       <c r="C51" t="n">
-        <v>3024.2</v>
+        <v>3025.5</v>
       </c>
       <c r="D51" t="n">
-        <v>3002.1</v>
+        <v>2976.6</v>
       </c>
       <c r="E51" t="n">
-        <v>3019</v>
+        <v>2977.5</v>
       </c>
       <c r="F51" t="n">
-        <v>8.9</v>
+        <v>-41.5</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0137</v>
       </c>
       <c r="H51" t="n">
-        <v>22.1</v>
+        <v>48.9</v>
       </c>
       <c r="I51" t="n">
-        <v>2984.7</v>
+        <v>2980</v>
       </c>
       <c r="J51" t="n">
-        <v>2991.48</v>
+        <v>2999.83</v>
       </c>
       <c r="K51" t="n">
-        <v>3001.15</v>
+        <v>3007.95</v>
       </c>
       <c r="L51" t="n">
-        <v>3010.83</v>
+        <v>3016.08</v>
       </c>
       <c r="M51" t="n">
-        <v>3019.05</v>
+        <v>3030.05</v>
       </c>
       <c r="N51" t="n">
-        <v>3027.28</v>
+        <v>3044.02</v>
       </c>
       <c r="O51" t="n">
-        <v>3038.4</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+        <v>3046.3</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4826,74 +4828,70 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3019.6</v>
+        <v>2971</v>
       </c>
       <c r="C52" t="n">
-        <v>3025.5</v>
+        <v>2982.5</v>
       </c>
       <c r="D52" t="n">
-        <v>2976.6</v>
+        <v>2946.1</v>
       </c>
       <c r="E52" t="n">
-        <v>2977.5</v>
+        <v>2958.7</v>
       </c>
       <c r="F52" t="n">
-        <v>-41.5</v>
+        <v>-18.8</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0063</v>
       </c>
       <c r="H52" t="n">
-        <v>48.9</v>
+        <v>36.4</v>
       </c>
       <c r="I52" t="n">
-        <v>2980</v>
+        <v>2927.7</v>
       </c>
       <c r="J52" t="n">
-        <v>2999.83</v>
+        <v>2916.83</v>
       </c>
       <c r="K52" t="n">
-        <v>3007.95</v>
+        <v>2953.05</v>
       </c>
       <c r="L52" t="n">
-        <v>3016.08</v>
+        <v>2989.28</v>
       </c>
       <c r="M52" t="n">
-        <v>3030.05</v>
+        <v>3001.95</v>
       </c>
       <c r="N52" t="n">
-        <v>3044.02</v>
+        <v>3014.62</v>
       </c>
       <c r="O52" t="n">
-        <v>3046.3</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
+        <v>3074.4</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4912,72 +4910,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2971</v>
+        <v>2958</v>
       </c>
       <c r="C53" t="n">
-        <v>2982.5</v>
+        <v>2964.6</v>
       </c>
       <c r="D53" t="n">
-        <v>2946.1</v>
+        <v>2918.9</v>
       </c>
       <c r="E53" t="n">
-        <v>2958.7</v>
+        <v>2924.7</v>
       </c>
       <c r="F53" t="n">
-        <v>-18.8</v>
+        <v>-34</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0115</v>
       </c>
       <c r="H53" t="n">
-        <v>36.4</v>
+        <v>45.7</v>
       </c>
       <c r="I53" t="n">
-        <v>2927.7</v>
+        <v>2909.7</v>
       </c>
       <c r="J53" t="n">
-        <v>2916.83</v>
+        <v>2919.5</v>
       </c>
       <c r="K53" t="n">
-        <v>2953.05</v>
+        <v>2940.5</v>
       </c>
       <c r="L53" t="n">
-        <v>2989.28</v>
+        <v>2961.5</v>
       </c>
       <c r="M53" t="n">
-        <v>3001.95</v>
+        <v>2976.9</v>
       </c>
       <c r="N53" t="n">
-        <v>3014.62</v>
+        <v>2992.3</v>
       </c>
       <c r="O53" t="n">
-        <v>3074.4</v>
+        <v>3018.9</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5001,75 +4997,75 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2958</v>
+        <v>2926.4</v>
       </c>
       <c r="C54" t="n">
-        <v>2964.6</v>
+        <v>2962.5</v>
       </c>
       <c r="D54" t="n">
-        <v>2918.9</v>
+        <v>2914.5</v>
       </c>
       <c r="E54" t="n">
-        <v>2924.7</v>
+        <v>2958.8</v>
       </c>
       <c r="F54" t="n">
-        <v>-34</v>
+        <v>34.1</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0.0117</v>
       </c>
       <c r="H54" t="n">
-        <v>45.7</v>
+        <v>48</v>
       </c>
       <c r="I54" t="n">
-        <v>2909.7</v>
+        <v>2873.2</v>
       </c>
       <c r="J54" t="n">
-        <v>2919.5</v>
+        <v>2870.47</v>
       </c>
       <c r="K54" t="n">
-        <v>2940.5</v>
+        <v>2901.85</v>
       </c>
       <c r="L54" t="n">
-        <v>2961.5</v>
+        <v>2933.22</v>
       </c>
       <c r="M54" t="n">
-        <v>2976.9</v>
+        <v>2947.55</v>
       </c>
       <c r="N54" t="n">
-        <v>2992.3</v>
+        <v>2961.88</v>
       </c>
       <c r="O54" t="n">
-        <v>3018.9</v>
+        <v>3010.3</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
@@ -5078,55 +5074,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2926.4</v>
+        <v>2957.6</v>
       </c>
       <c r="C55" t="n">
-        <v>2962.5</v>
+        <v>2983.3</v>
       </c>
       <c r="D55" t="n">
-        <v>2914.5</v>
+        <v>2949.9</v>
       </c>
       <c r="E55" t="n">
-        <v>2958.8</v>
+        <v>2969.7</v>
       </c>
       <c r="F55" t="n">
-        <v>34.1</v>
+        <v>10.9</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0117</v>
+        <v>0.0037</v>
       </c>
       <c r="H55" t="n">
-        <v>48</v>
+        <v>33.4</v>
       </c>
       <c r="I55" t="n">
-        <v>2873.2</v>
+        <v>2866.5</v>
       </c>
       <c r="J55" t="n">
-        <v>2870.47</v>
+        <v>2920.95</v>
       </c>
       <c r="K55" t="n">
-        <v>2901.85</v>
+        <v>2934.8</v>
       </c>
       <c r="L55" t="n">
-        <v>2933.22</v>
+        <v>2948.65</v>
       </c>
       <c r="M55" t="n">
-        <v>2947.55</v>
+        <v>2982.8</v>
       </c>
       <c r="N55" t="n">
-        <v>2961.88</v>
+        <v>3016.95</v>
       </c>
       <c r="O55" t="n">
-        <v>3010.3</v>
+        <v>3010.5</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5137,21 +5137,19 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="10" t="inlineStr">
+      <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
@@ -5162,57 +5160,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2957.6</v>
+        <v>2967.9</v>
       </c>
       <c r="C56" t="n">
-        <v>2983.3</v>
+        <v>2979.3</v>
       </c>
       <c r="D56" t="n">
-        <v>2949.9</v>
+        <v>2949.5</v>
       </c>
       <c r="E56" t="n">
-        <v>2969.7</v>
+        <v>2976.6</v>
       </c>
       <c r="F56" t="n">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0023</v>
       </c>
       <c r="H56" t="n">
-        <v>33.4</v>
+        <v>29.8</v>
       </c>
       <c r="I56" t="n">
-        <v>2866.5</v>
+        <v>2916.5</v>
       </c>
       <c r="J56" t="n">
-        <v>2920.95</v>
+        <v>2937.85</v>
       </c>
       <c r="K56" t="n">
-        <v>2934.8</v>
+        <v>2953</v>
       </c>
       <c r="L56" t="n">
-        <v>2948.65</v>
+        <v>2968.15</v>
       </c>
       <c r="M56" t="n">
-        <v>2982.8</v>
+        <v>2986.4</v>
       </c>
       <c r="N56" t="n">
-        <v>3016.95</v>
+        <v>3004.65</v>
       </c>
       <c r="O56" t="n">
-        <v>3010.5</v>
+        <v>3016.7</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5220,18 +5218,18 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5246,57 +5244,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2967.9</v>
+        <v>2974.7</v>
       </c>
       <c r="C57" t="n">
-        <v>2979.3</v>
+        <v>2977.9</v>
       </c>
       <c r="D57" t="n">
-        <v>2949.5</v>
+        <v>2954.7</v>
       </c>
       <c r="E57" t="n">
-        <v>2976.6</v>
+        <v>2963.6</v>
       </c>
       <c r="F57" t="n">
-        <v>6.9</v>
+        <v>-13</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0044</v>
       </c>
       <c r="H57" t="n">
-        <v>29.8</v>
+        <v>23.2</v>
       </c>
       <c r="I57" t="n">
-        <v>2916.5</v>
+        <v>2919.7</v>
       </c>
       <c r="J57" t="n">
-        <v>2937.85</v>
+        <v>2952.9</v>
       </c>
       <c r="K57" t="n">
-        <v>2953</v>
+        <v>2961.7</v>
       </c>
       <c r="L57" t="n">
-        <v>2968.15</v>
+        <v>2970.5</v>
       </c>
       <c r="M57" t="n">
-        <v>2986.4</v>
+        <v>2991.5</v>
       </c>
       <c r="N57" t="n">
-        <v>3004.65</v>
+        <v>3012.5</v>
       </c>
       <c r="O57" t="n">
-        <v>3016.7</v>
+        <v>3009.1</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5306,12 +5304,12 @@
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5337,63 +5335,67 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2974.7</v>
+        <v>2963.1</v>
       </c>
       <c r="C58" t="n">
-        <v>2977.9</v>
+        <v>2966.2</v>
       </c>
       <c r="D58" t="n">
-        <v>2954.7</v>
+        <v>2919.4</v>
       </c>
       <c r="E58" t="n">
-        <v>2963.6</v>
+        <v>2923</v>
       </c>
       <c r="F58" t="n">
-        <v>-13</v>
+        <v>-40.6</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0137</v>
       </c>
       <c r="H58" t="n">
-        <v>23.2</v>
+        <v>46.8</v>
       </c>
       <c r="I58" t="n">
-        <v>2919.7</v>
+        <v>2931.5</v>
       </c>
       <c r="J58" t="n">
-        <v>2952.9</v>
+        <v>2939.05</v>
       </c>
       <c r="K58" t="n">
-        <v>2961.7</v>
+        <v>2952</v>
       </c>
       <c r="L58" t="n">
-        <v>2970.5</v>
+        <v>2964.95</v>
       </c>
       <c r="M58" t="n">
-        <v>2991.5</v>
+        <v>2975.2</v>
       </c>
       <c r="N58" t="n">
-        <v>3012.5</v>
+        <v>2985.45</v>
       </c>
       <c r="O58" t="n">
-        <v>3009.1</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+        <v>3001.1</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5412,76 +5414,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2963.1</v>
+        <v>2923.1</v>
       </c>
       <c r="C59" t="n">
-        <v>2966.2</v>
+        <v>2933.8</v>
       </c>
       <c r="D59" t="n">
-        <v>2919.4</v>
+        <v>2887.8</v>
       </c>
       <c r="E59" t="n">
-        <v>2923</v>
+        <v>2893.4</v>
       </c>
       <c r="F59" t="n">
-        <v>-40.6</v>
+        <v>-29.6</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0101</v>
       </c>
       <c r="H59" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="I59" t="n">
-        <v>2931.5</v>
+        <v>2872.6</v>
       </c>
       <c r="J59" t="n">
-        <v>2939.05</v>
+        <v>2866.3</v>
       </c>
       <c r="K59" t="n">
-        <v>2952</v>
+        <v>2899.6</v>
       </c>
       <c r="L59" t="n">
-        <v>2964.95</v>
+        <v>2932.9</v>
       </c>
       <c r="M59" t="n">
-        <v>2975.2</v>
+        <v>2946.4</v>
       </c>
       <c r="N59" t="n">
-        <v>2985.45</v>
+        <v>2959.9</v>
       </c>
       <c r="O59" t="n">
-        <v>3001.1</v>
-      </c>
-      <c r="P59" s="6" t="inlineStr">
+        <v>3013</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
+      <c r="S59" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5505,50 +5499,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2923.1</v>
+        <v>2890.9</v>
       </c>
       <c r="C60" t="n">
-        <v>2933.8</v>
+        <v>2929.8</v>
       </c>
       <c r="D60" t="n">
-        <v>2887.8</v>
+        <v>2887.6</v>
       </c>
       <c r="E60" t="n">
-        <v>2893.4</v>
+        <v>2904.5</v>
       </c>
       <c r="F60" t="n">
-        <v>-29.6</v>
+        <v>11.1</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0101</v>
+        <v>0.0038</v>
       </c>
       <c r="H60" t="n">
-        <v>46</v>
+        <v>42.2</v>
       </c>
       <c r="I60" t="n">
-        <v>2872.6</v>
+        <v>2841.8</v>
       </c>
       <c r="J60" t="n">
-        <v>2866.3</v>
+        <v>2838.7</v>
       </c>
       <c r="K60" t="n">
-        <v>2899.6</v>
+        <v>2870.4</v>
       </c>
       <c r="L60" t="n">
-        <v>2932.9</v>
+        <v>2902.1</v>
       </c>
       <c r="M60" t="n">
-        <v>2946.4</v>
+        <v>2916.4</v>
       </c>
       <c r="N60" t="n">
-        <v>2959.9</v>
+        <v>2930.7</v>
       </c>
       <c r="O60" t="n">
-        <v>3013</v>
+        <v>2979.8</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5556,18 +5550,18 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R60" s="6" t="n">
+        <v/>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5580,55 +5574,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2890.9</v>
+        <v>2892.7</v>
       </c>
       <c r="C61" t="n">
-        <v>2929.8</v>
+        <v>2935.7</v>
       </c>
       <c r="D61" t="n">
-        <v>2887.6</v>
+        <v>2906.1</v>
       </c>
       <c r="E61" t="n">
-        <v>2904.5</v>
+        <v>2917.7</v>
       </c>
       <c r="F61" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0045</v>
       </c>
       <c r="H61" t="n">
-        <v>42.2</v>
+        <v>29.6</v>
       </c>
       <c r="I61" t="n">
-        <v>2841.8</v>
+        <v>2845.4</v>
       </c>
       <c r="J61" t="n">
-        <v>2838.7</v>
+        <v>2860.2</v>
       </c>
       <c r="K61" t="n">
-        <v>2870.4</v>
+        <v>2883.4</v>
       </c>
       <c r="L61" t="n">
-        <v>2902.1</v>
+        <v>2906.6</v>
       </c>
       <c r="M61" t="n">
-        <v>2916.4</v>
+        <v>2925.6</v>
       </c>
       <c r="N61" t="n">
-        <v>2930.7</v>
+        <v>2944.6</v>
       </c>
       <c r="O61" t="n">
-        <v>2979.8</v>
+        <v>2972</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5639,14 +5637,14 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U61" s="8" t="n">
@@ -5662,7 +5660,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
@@ -5673,25 +5671,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>2845.4</v>
+        <v>2876.5</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>2860.2</v>
+        <v>2886.5</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>2883.4</v>
+        <v>2902.9</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>2906.6</v>
+        <v>2919.3</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>2925.6</v>
+        <v>2932.5</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>2944.6</v>
+        <v>2945.7</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>2972</v>
+        <v>2965.3</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -5587,25 +5587,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2892.7</v>
+        <v>2917.2</v>
       </c>
       <c r="C61" t="n">
-        <v>2935.7</v>
+        <v>2918.3</v>
       </c>
       <c r="D61" t="n">
-        <v>2906.1</v>
+        <v>2913.4</v>
       </c>
       <c r="E61" t="n">
-        <v>2917.7</v>
+        <v>2913.5</v>
       </c>
       <c r="F61" t="n">
-        <v>13.2</v>
+        <v>9</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0045</v>
+        <v>0.0031</v>
       </c>
       <c r="H61" t="n">
-        <v>29.6</v>
+        <v>4.9</v>
       </c>
       <c r="I61" t="n">
         <v>2845.4</v>
@@ -5639,13 +5639,11 @@
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5660,7 +5658,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -5671,25 +5669,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>2876.5</v>
+        <v>2908.5</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>2886.5</v>
+        <v>2907.42</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>2902.9</v>
+        <v>2911.05</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>2919.3</v>
+        <v>2914.67</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>2932.5</v>
+        <v>2915.95</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>2945.7</v>
+        <v>2917.23</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>2965.3</v>
+        <v>2923.2</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -5593,19 +5593,19 @@
         <v>2918.3</v>
       </c>
       <c r="D61" t="n">
-        <v>2913.4</v>
+        <v>2911.6</v>
       </c>
       <c r="E61" t="n">
-        <v>2913.5</v>
+        <v>2913.3</v>
       </c>
       <c r="F61" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.003</v>
       </c>
       <c r="H61" t="n">
-        <v>4.9</v>
+        <v>6.7</v>
       </c>
       <c r="I61" t="n">
         <v>2845.4</v>
@@ -5669,25 +5669,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>2908.5</v>
+        <v>2904.9</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>2907.42</v>
+        <v>2905.78</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>2911.05</v>
+        <v>2909.95</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>2914.67</v>
+        <v>2914.13</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>2915.95</v>
+        <v>2916.65</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>2917.23</v>
+        <v>2919.17</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>2923.2</v>
+        <v>2925</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -5593,19 +5593,19 @@
         <v>2918.3</v>
       </c>
       <c r="D61" t="n">
-        <v>2911.6</v>
+        <v>2911.1</v>
       </c>
       <c r="E61" t="n">
-        <v>2913.3</v>
+        <v>2912.1</v>
       </c>
       <c r="F61" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.003</v>
+        <v>0.0026</v>
       </c>
       <c r="H61" t="n">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="I61" t="n">
         <v>2845.4</v>
@@ -5669,25 +5669,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>2904.9</v>
+        <v>2903.9</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>2905.78</v>
+        <v>2903.6</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>2909.95</v>
+        <v>2908.5</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>2914.13</v>
+        <v>2913.4</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>2916.65</v>
+        <v>2915.7</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>2919.17</v>
+        <v>2918</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>2925</v>
+        <v>2925.5</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -5587,25 +5587,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2917.2</v>
+        <v>2892.7</v>
       </c>
       <c r="C61" t="n">
-        <v>2918.3</v>
+        <v>2913.5</v>
       </c>
       <c r="D61" t="n">
-        <v>2911.1</v>
+        <v>2884.3</v>
       </c>
       <c r="E61" t="n">
-        <v>2912.1</v>
+        <v>2894.1</v>
       </c>
       <c r="F61" t="n">
-        <v>7.6</v>
+        <v>-10.4</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0036</v>
       </c>
       <c r="H61" t="n">
-        <v>7.2</v>
+        <v>29.2</v>
       </c>
       <c r="I61" t="n">
         <v>2845.4</v>
@@ -5634,12 +5634,14 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5656,11 +5658,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -5669,25 +5667,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>2903.9</v>
+        <v>2855.1</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>2903.6</v>
+        <v>2862.5</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>2908.5</v>
+        <v>2879.5</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>2913.4</v>
+        <v>2896.5</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>2915.7</v>
+        <v>2908.7</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>2918</v>
+        <v>2920.9</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>2925.5</v>
+        <v>2942.7</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2925</v>
+        <v>2989.9</v>
       </c>
       <c r="C2" t="n">
-        <v>2972.3</v>
+        <v>3039</v>
       </c>
       <c r="D2" t="n">
-        <v>2925</v>
+        <v>2970.8</v>
       </c>
       <c r="E2" t="n">
-        <v>2960.73</v>
+        <v>3024.1</v>
       </c>
       <c r="F2" t="n">
-        <v>41.13</v>
+        <v>63.37</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0141</v>
+        <v>0.0214</v>
       </c>
       <c r="H2" t="n">
-        <v>47.3</v>
+        <v>68.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2840.8</v>
+        <v>2877.7</v>
       </c>
       <c r="J2" t="n">
-        <v>2837.38</v>
+        <v>2919.47</v>
       </c>
       <c r="K2" t="n">
-        <v>2884.85</v>
+        <v>2937.08</v>
       </c>
       <c r="L2" t="n">
-        <v>2932.33</v>
+        <v>2954.69</v>
       </c>
       <c r="M2" t="n">
-        <v>2954.35</v>
+        <v>2984.38</v>
       </c>
       <c r="N2" t="n">
-        <v>2976.38</v>
+        <v>3014.07</v>
       </c>
       <c r="O2" t="n">
-        <v>3049.3</v>
+        <v>3019.6</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -702,179 +702,179 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
-      </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2989.9</v>
+        <v>3022.4</v>
       </c>
       <c r="C3" t="n">
-        <v>3039</v>
+        <v>3028.4</v>
       </c>
       <c r="D3" t="n">
-        <v>2970.8</v>
+        <v>2965.2</v>
       </c>
       <c r="E3" t="n">
-        <v>3024.1</v>
+        <v>2998.2</v>
       </c>
       <c r="F3" t="n">
-        <v>63.37</v>
+        <v>-25.9</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0214</v>
+        <v>-0.0086</v>
       </c>
       <c r="H3" t="n">
-        <v>68.2</v>
+        <v>63.2</v>
       </c>
       <c r="I3" t="n">
-        <v>2877.7</v>
+        <v>2902.6</v>
       </c>
       <c r="J3" t="n">
-        <v>2919.47</v>
+        <v>2965.5</v>
       </c>
       <c r="K3" t="n">
-        <v>2937.08</v>
+        <v>2990</v>
       </c>
       <c r="L3" t="n">
-        <v>2954.69</v>
+        <v>3014.5</v>
       </c>
       <c r="M3" t="n">
-        <v>2984.38</v>
+        <v>3058.2</v>
       </c>
       <c r="N3" t="n">
-        <v>3014.07</v>
+        <v>3101.9</v>
       </c>
       <c r="O3" t="n">
-        <v>3019.6</v>
+        <v>3107.2</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
+      <c r="Q3" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
+      </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3022.4</v>
+        <v>2998.4</v>
       </c>
       <c r="C4" t="n">
-        <v>3028.4</v>
+        <v>3041.4</v>
       </c>
       <c r="D4" t="n">
-        <v>2965.2</v>
+        <v>2987.2</v>
       </c>
       <c r="E4" t="n">
-        <v>2998.2</v>
+        <v>3013.5</v>
       </c>
       <c r="F4" t="n">
-        <v>-25.9</v>
+        <v>15.3</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0051</v>
       </c>
       <c r="H4" t="n">
-        <v>63.2</v>
+        <v>54.2</v>
       </c>
       <c r="I4" t="n">
-        <v>2902.6</v>
+        <v>2902</v>
       </c>
       <c r="J4" t="n">
-        <v>2965.5</v>
+        <v>2935.7</v>
       </c>
       <c r="K4" t="n">
-        <v>2990</v>
+        <v>2966.6</v>
       </c>
       <c r="L4" t="n">
-        <v>3014.5</v>
+        <v>2997.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3058.2</v>
+        <v>3029.8</v>
       </c>
       <c r="N4" t="n">
-        <v>3101.9</v>
+        <v>3062.1</v>
       </c>
       <c r="O4" t="n">
-        <v>3107.2</v>
+        <v>3091.6</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -886,59 +886,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2998.4</v>
+        <v>3023.7</v>
       </c>
       <c r="C5" t="n">
-        <v>3041.4</v>
+        <v>3062.4</v>
       </c>
       <c r="D5" t="n">
-        <v>2987.2</v>
+        <v>3010.5</v>
       </c>
       <c r="E5" t="n">
-        <v>3013.5</v>
+        <v>3030.7</v>
       </c>
       <c r="F5" t="n">
-        <v>15.3</v>
+        <v>17.2</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0057</v>
       </c>
       <c r="H5" t="n">
-        <v>54.2</v>
+        <v>51.9</v>
       </c>
       <c r="I5" t="n">
-        <v>2902</v>
+        <v>2933</v>
       </c>
       <c r="J5" t="n">
-        <v>2935.7</v>
+        <v>2958.9</v>
       </c>
       <c r="K5" t="n">
-        <v>2966.6</v>
+        <v>2986.4</v>
       </c>
       <c r="L5" t="n">
-        <v>2997.5</v>
+        <v>3013.9</v>
       </c>
       <c r="M5" t="n">
-        <v>3029.8</v>
+        <v>3040.6</v>
       </c>
       <c r="N5" t="n">
-        <v>3062.1</v>
+        <v>3067.3</v>
       </c>
       <c r="O5" t="n">
-        <v>3091.6</v>
+        <v>3095.6</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -951,12 +947,12 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U5" s="8" t="n">
@@ -975,50 +971,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3023.7</v>
+        <v>3034.7</v>
       </c>
       <c r="C6" t="n">
-        <v>3062.4</v>
+        <v>3045.7</v>
       </c>
       <c r="D6" t="n">
-        <v>3010.5</v>
+        <v>2999.6</v>
       </c>
       <c r="E6" t="n">
-        <v>3030.7</v>
+        <v>3022.6</v>
       </c>
       <c r="F6" t="n">
-        <v>17.2</v>
+        <v>-8.1</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.0027</v>
       </c>
       <c r="H6" t="n">
-        <v>51.9</v>
+        <v>46.1</v>
       </c>
       <c r="I6" t="n">
-        <v>2933</v>
+        <v>2958.6</v>
       </c>
       <c r="J6" t="n">
-        <v>2958.9</v>
+        <v>2975.93</v>
       </c>
       <c r="K6" t="n">
-        <v>2986.4</v>
+        <v>3004.75</v>
       </c>
       <c r="L6" t="n">
-        <v>3013.9</v>
+        <v>3033.57</v>
       </c>
       <c r="M6" t="n">
-        <v>3040.6</v>
+        <v>3056.65</v>
       </c>
       <c r="N6" t="n">
-        <v>3067.3</v>
+        <v>3079.72</v>
       </c>
       <c r="O6" t="n">
-        <v>3095.6</v>
+        <v>3114.3</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1026,18 +1022,18 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1050,55 +1046,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3034.7</v>
+        <v>3020.9</v>
       </c>
       <c r="C7" t="n">
-        <v>3045.7</v>
+        <v>3044.9</v>
       </c>
       <c r="D7" t="n">
-        <v>2999.6</v>
+        <v>2987.8</v>
       </c>
       <c r="E7" t="n">
-        <v>3022.6</v>
+        <v>3030.6</v>
       </c>
       <c r="F7" t="n">
-        <v>-8.1</v>
+        <v>8</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0026</v>
       </c>
       <c r="H7" t="n">
-        <v>46.1</v>
+        <v>57.1</v>
       </c>
       <c r="I7" t="n">
-        <v>2958.6</v>
+        <v>2953.5</v>
       </c>
       <c r="J7" t="n">
-        <v>2975.93</v>
+        <v>2976.48</v>
       </c>
       <c r="K7" t="n">
-        <v>3004.75</v>
+        <v>2999.55</v>
       </c>
       <c r="L7" t="n">
-        <v>3033.57</v>
+        <v>3022.63</v>
       </c>
       <c r="M7" t="n">
-        <v>3056.65</v>
+        <v>3045.65</v>
       </c>
       <c r="N7" t="n">
-        <v>3079.72</v>
+        <v>3068.67</v>
       </c>
       <c r="O7" t="n">
-        <v>3114.3</v>
+        <v>3091.8</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1111,9 +1111,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1132,57 +1132,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3020.9</v>
+        <v>3026.1</v>
       </c>
       <c r="C8" t="n">
-        <v>3044.9</v>
+        <v>3050.6</v>
       </c>
       <c r="D8" t="n">
-        <v>2987.8</v>
+        <v>3015.1</v>
       </c>
       <c r="E8" t="n">
-        <v>3030.6</v>
+        <v>3045.6</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0049</v>
       </c>
       <c r="H8" t="n">
-        <v>57.1</v>
+        <v>35.5</v>
       </c>
       <c r="I8" t="n">
-        <v>2953.5</v>
+        <v>2930.7</v>
       </c>
       <c r="J8" t="n">
-        <v>2976.48</v>
+        <v>2980.63</v>
       </c>
       <c r="K8" t="n">
-        <v>2999.55</v>
+        <v>3002.05</v>
       </c>
       <c r="L8" t="n">
-        <v>3022.63</v>
+        <v>3023.48</v>
       </c>
       <c r="M8" t="n">
-        <v>3045.65</v>
+        <v>3059.15</v>
       </c>
       <c r="N8" t="n">
-        <v>3068.67</v>
+        <v>3094.83</v>
       </c>
       <c r="O8" t="n">
-        <v>3091.8</v>
+        <v>3102</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1190,18 +1190,18 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R8" s="6" t="n">
+        <v/>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1214,59 +1214,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3026.1</v>
+        <v>3040</v>
       </c>
       <c r="C9" t="n">
-        <v>3050.6</v>
+        <v>3068.4</v>
       </c>
       <c r="D9" t="n">
-        <v>3015.1</v>
+        <v>3023.7</v>
       </c>
       <c r="E9" t="n">
-        <v>3045.6</v>
+        <v>3035.1</v>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>-10.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.0034</v>
       </c>
       <c r="H9" t="n">
-        <v>35.5</v>
+        <v>44.7</v>
       </c>
       <c r="I9" t="n">
-        <v>2930.7</v>
+        <v>2979.6</v>
       </c>
       <c r="J9" t="n">
-        <v>2980.63</v>
+        <v>3016.48</v>
       </c>
       <c r="K9" t="n">
-        <v>3002.05</v>
+        <v>3027.85</v>
       </c>
       <c r="L9" t="n">
-        <v>3023.48</v>
+        <v>3039.23</v>
       </c>
       <c r="M9" t="n">
-        <v>3059.15</v>
+        <v>3063.35</v>
       </c>
       <c r="N9" t="n">
-        <v>3094.83</v>
+        <v>3087.48</v>
       </c>
       <c r="O9" t="n">
-        <v>3102</v>
+        <v>3086.1</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1274,17 +1270,19 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U9" s="8" t="n">
@@ -1298,55 +1296,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3040</v>
+        <v>3030.9</v>
       </c>
       <c r="C10" t="n">
-        <v>3068.4</v>
+        <v>3062.4</v>
       </c>
       <c r="D10" t="n">
-        <v>3023.7</v>
+        <v>2988.5</v>
       </c>
       <c r="E10" t="n">
-        <v>3035.1</v>
+        <v>3014.2</v>
       </c>
       <c r="F10" t="n">
-        <v>-10.5</v>
+        <v>-20.9</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0069</v>
       </c>
       <c r="H10" t="n">
-        <v>44.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>2979.6</v>
+        <v>2979</v>
       </c>
       <c r="J10" t="n">
-        <v>3016.48</v>
+        <v>2984.93</v>
       </c>
       <c r="K10" t="n">
-        <v>3027.85</v>
+        <v>3012.75</v>
       </c>
       <c r="L10" t="n">
-        <v>3039.23</v>
+        <v>3040.58</v>
       </c>
       <c r="M10" t="n">
-        <v>3063.35</v>
+        <v>3057.45</v>
       </c>
       <c r="N10" t="n">
-        <v>3087.48</v>
+        <v>3074.33</v>
       </c>
       <c r="O10" t="n">
-        <v>3086.1</v>
+        <v>3113.1</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1356,19 +1358,19 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
@@ -1382,57 +1384,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3030.9</v>
+        <v>3019.7</v>
       </c>
       <c r="C11" t="n">
-        <v>3062.4</v>
+        <v>3042.1</v>
       </c>
       <c r="D11" t="n">
-        <v>2988.5</v>
+        <v>3006.7</v>
       </c>
       <c r="E11" t="n">
-        <v>3014.2</v>
+        <v>3027</v>
       </c>
       <c r="F11" t="n">
-        <v>-20.9</v>
+        <v>12.8</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0042</v>
       </c>
       <c r="H11" t="n">
-        <v>73.90000000000001</v>
+        <v>35.4</v>
       </c>
       <c r="I11" t="n">
-        <v>2979</v>
+        <v>2914.6</v>
       </c>
       <c r="J11" t="n">
-        <v>2984.93</v>
+        <v>2934.68</v>
       </c>
       <c r="K11" t="n">
-        <v>3012.75</v>
+        <v>2977.25</v>
       </c>
       <c r="L11" t="n">
-        <v>3040.58</v>
+        <v>3019.82</v>
       </c>
       <c r="M11" t="n">
-        <v>3057.45</v>
+        <v>3051.15</v>
       </c>
       <c r="N11" t="n">
-        <v>3074.33</v>
+        <v>3082.47</v>
       </c>
       <c r="O11" t="n">
-        <v>3113.1</v>
+        <v>3136.3</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1440,20 +1442,16 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1468,70 +1466,74 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3019.7</v>
+        <v>3033.4</v>
       </c>
       <c r="C12" t="n">
-        <v>3042.1</v>
+        <v>3042.6</v>
       </c>
       <c r="D12" t="n">
-        <v>3006.7</v>
+        <v>2988.8</v>
       </c>
       <c r="E12" t="n">
-        <v>3027</v>
+        <v>2998.8</v>
       </c>
       <c r="F12" t="n">
-        <v>12.8</v>
+        <v>-28.2</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>35.4</v>
+        <v>53.8</v>
       </c>
       <c r="I12" t="n">
-        <v>2914.6</v>
+        <v>2971.3</v>
       </c>
       <c r="J12" t="n">
-        <v>2934.68</v>
+        <v>2992.9</v>
       </c>
       <c r="K12" t="n">
-        <v>2977.25</v>
+        <v>3009.3</v>
       </c>
       <c r="L12" t="n">
-        <v>3019.82</v>
+        <v>3025.7</v>
       </c>
       <c r="M12" t="n">
-        <v>3051.15</v>
+        <v>3044.7</v>
       </c>
       <c r="N12" t="n">
-        <v>3082.47</v>
+        <v>3063.7</v>
       </c>
       <c r="O12" t="n">
-        <v>3136.3</v>
+        <v>3077.5</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1550,71 +1552,69 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3033.4</v>
+        <v>2994.3</v>
       </c>
       <c r="C13" t="n">
-        <v>3042.6</v>
+        <v>3004.3</v>
       </c>
       <c r="D13" t="n">
-        <v>2988.8</v>
+        <v>2943.4</v>
       </c>
       <c r="E13" t="n">
-        <v>2998.8</v>
+        <v>2971.5</v>
       </c>
       <c r="F13" t="n">
-        <v>-28.2</v>
+        <v>-27.3</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0091</v>
       </c>
       <c r="H13" t="n">
-        <v>53.8</v>
+        <v>60.9</v>
       </c>
       <c r="I13" t="n">
-        <v>2971.3</v>
+        <v>2935</v>
       </c>
       <c r="J13" t="n">
-        <v>2992.9</v>
+        <v>2936.55</v>
       </c>
       <c r="K13" t="n">
-        <v>3009.3</v>
+        <v>2971.9</v>
       </c>
       <c r="L13" t="n">
+        <v>3007.25</v>
+      </c>
+      <c r="M13" t="n">
         <v>3025.7</v>
       </c>
-      <c r="M13" t="n">
-        <v>3044.7</v>
-      </c>
       <c r="N13" t="n">
-        <v>3063.7</v>
+        <v>3044.15</v>
       </c>
       <c r="O13" t="n">
-        <v>3077.5</v>
+        <v>3096.4</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -1636,57 +1636,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2994.3</v>
+        <v>2965.8</v>
       </c>
       <c r="C14" t="n">
-        <v>3004.3</v>
+        <v>3014.9</v>
       </c>
       <c r="D14" t="n">
-        <v>2943.4</v>
+        <v>2964.3</v>
       </c>
       <c r="E14" t="n">
-        <v>2971.5</v>
+        <v>3008.4</v>
       </c>
       <c r="F14" t="n">
-        <v>-27.3</v>
+        <v>36.9</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0091</v>
+        <v>0.0124</v>
       </c>
       <c r="H14" t="n">
-        <v>60.9</v>
+        <v>50.6</v>
       </c>
       <c r="I14" t="n">
-        <v>2935</v>
+        <v>2882.5</v>
       </c>
       <c r="J14" t="n">
-        <v>2936.55</v>
+        <v>2909.42</v>
       </c>
       <c r="K14" t="n">
-        <v>2971.9</v>
+        <v>2941.05</v>
       </c>
       <c r="L14" t="n">
-        <v>3007.25</v>
+        <v>2972.67</v>
       </c>
       <c r="M14" t="n">
-        <v>3025.7</v>
+        <v>3001.95</v>
       </c>
       <c r="N14" t="n">
-        <v>3044.15</v>
+        <v>3031.23</v>
       </c>
       <c r="O14" t="n">
-        <v>3096.4</v>
+        <v>3065.2</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1694,19 +1694,19 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
@@ -1718,59 +1718,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2965.8</v>
+        <v>3008.1</v>
       </c>
       <c r="C15" t="n">
-        <v>3014.9</v>
+        <v>3019.5</v>
       </c>
       <c r="D15" t="n">
-        <v>2964.3</v>
+        <v>2970.8</v>
       </c>
       <c r="E15" t="n">
-        <v>3008.4</v>
+        <v>2994</v>
       </c>
       <c r="F15" t="n">
-        <v>36.9</v>
+        <v>-14.4</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0048</v>
       </c>
       <c r="H15" t="n">
-        <v>50.6</v>
+        <v>48.7</v>
       </c>
       <c r="I15" t="n">
-        <v>2882.5</v>
+        <v>2913.7</v>
       </c>
       <c r="J15" t="n">
-        <v>2909.42</v>
+        <v>2967.2</v>
       </c>
       <c r="K15" t="n">
-        <v>2941.05</v>
+        <v>2983.1</v>
       </c>
       <c r="L15" t="n">
-        <v>2972.67</v>
+        <v>2999</v>
       </c>
       <c r="M15" t="n">
-        <v>3001.95</v>
+        <v>3033.7</v>
       </c>
       <c r="N15" t="n">
-        <v>3031.23</v>
+        <v>3068.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3065.2</v>
+        <v>3065.5</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1778,18 +1774,18 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1802,55 +1798,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3008.1</v>
+        <v>2984.7</v>
       </c>
       <c r="C16" t="n">
-        <v>3019.5</v>
+        <v>2995.8</v>
       </c>
       <c r="D16" t="n">
-        <v>2970.8</v>
+        <v>2961.8</v>
       </c>
       <c r="E16" t="n">
-        <v>2994</v>
+        <v>2970.4</v>
       </c>
       <c r="F16" t="n">
-        <v>-14.4</v>
+        <v>-23.6</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>48.7</v>
+        <v>34</v>
       </c>
       <c r="I16" t="n">
-        <v>2913.7</v>
+        <v>2922.1</v>
       </c>
       <c r="J16" t="n">
-        <v>2967.2</v>
+        <v>2944.73</v>
       </c>
       <c r="K16" t="n">
-        <v>2983.1</v>
+        <v>2969.65</v>
       </c>
       <c r="L16" t="n">
-        <v>2999</v>
+        <v>2994.58</v>
       </c>
       <c r="M16" t="n">
-        <v>3033.7</v>
+        <v>3018.35</v>
       </c>
       <c r="N16" t="n">
-        <v>3068.4</v>
+        <v>3042.12</v>
       </c>
       <c r="O16" t="n">
-        <v>3065.5</v>
+        <v>3068.2</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1884,57 +1884,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2984.7</v>
+        <v>2967.2</v>
       </c>
       <c r="C17" t="n">
-        <v>2995.8</v>
+        <v>3029.8</v>
       </c>
       <c r="D17" t="n">
-        <v>2961.8</v>
+        <v>2956.2</v>
       </c>
       <c r="E17" t="n">
-        <v>2970.4</v>
+        <v>2979.9</v>
       </c>
       <c r="F17" t="n">
-        <v>-23.6</v>
+        <v>9.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H17" t="n">
-        <v>34</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>2922.1</v>
+        <v>2927.8</v>
       </c>
       <c r="J17" t="n">
-        <v>2944.73</v>
+        <v>2932.2</v>
       </c>
       <c r="K17" t="n">
-        <v>2969.65</v>
+        <v>2953.4</v>
       </c>
       <c r="L17" t="n">
-        <v>2994.58</v>
+        <v>2974.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3018.35</v>
+        <v>2987.4</v>
       </c>
       <c r="N17" t="n">
-        <v>3042.12</v>
+        <v>3000.2</v>
       </c>
       <c r="O17" t="n">
-        <v>3068.2</v>
+        <v>3029.8</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1942,24 +1942,28 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
@@ -1968,57 +1972,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2967.2</v>
+        <v>2981.2</v>
       </c>
       <c r="C18" t="n">
-        <v>3029.8</v>
+        <v>3006.1</v>
       </c>
       <c r="D18" t="n">
-        <v>2956.2</v>
+        <v>2974.4</v>
       </c>
       <c r="E18" t="n">
-        <v>2979.9</v>
+        <v>2991.8</v>
       </c>
       <c r="F18" t="n">
-        <v>9.5</v>
+        <v>11.9</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.004</v>
       </c>
       <c r="H18" t="n">
-        <v>73.59999999999999</v>
+        <v>31.7</v>
       </c>
       <c r="I18" t="n">
-        <v>2927.8</v>
+        <v>2882.6</v>
       </c>
       <c r="J18" t="n">
-        <v>2932.2</v>
+        <v>2899.75</v>
       </c>
       <c r="K18" t="n">
-        <v>2953.4</v>
+        <v>2943.1</v>
       </c>
       <c r="L18" t="n">
-        <v>2974.6</v>
+        <v>2986.45</v>
       </c>
       <c r="M18" t="n">
-        <v>2987.4</v>
+        <v>3016.7</v>
       </c>
       <c r="N18" t="n">
-        <v>3000.2</v>
+        <v>3046.95</v>
       </c>
       <c r="O18" t="n">
-        <v>3029.8</v>
+        <v>3103.4</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2034,20 +2038,14 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
@@ -2063,50 +2061,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2981.2</v>
+        <v>2995.3</v>
       </c>
       <c r="C19" t="n">
-        <v>3006.1</v>
+        <v>3012.8</v>
       </c>
       <c r="D19" t="n">
-        <v>2974.4</v>
+        <v>2972.7</v>
       </c>
       <c r="E19" t="n">
-        <v>2991.8</v>
+        <v>2990.7</v>
       </c>
       <c r="F19" t="n">
-        <v>11.9</v>
+        <v>-1.1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0004</v>
       </c>
       <c r="H19" t="n">
-        <v>31.7</v>
+        <v>40.1</v>
       </c>
       <c r="I19" t="n">
-        <v>2882.6</v>
+        <v>2942.7</v>
       </c>
       <c r="J19" t="n">
-        <v>2899.75</v>
+        <v>2960.87</v>
       </c>
       <c r="K19" t="n">
-        <v>2943.1</v>
+        <v>2975.95</v>
       </c>
       <c r="L19" t="n">
-        <v>2986.45</v>
+        <v>2991.03</v>
       </c>
       <c r="M19" t="n">
-        <v>3016.7</v>
+        <v>3007.65</v>
       </c>
       <c r="N19" t="n">
-        <v>3046.95</v>
+        <v>3024.28</v>
       </c>
       <c r="O19" t="n">
-        <v>3103.4</v>
+        <v>3037.8</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2114,16 +2112,20 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2138,78 +2140,78 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2995.3</v>
+        <v>2991.7</v>
       </c>
       <c r="C20" t="n">
-        <v>3012.8</v>
+        <v>2994.8</v>
       </c>
       <c r="D20" t="n">
-        <v>2972.7</v>
+        <v>2949.3</v>
       </c>
       <c r="E20" t="n">
-        <v>2990.7</v>
+        <v>2973.5</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1</v>
+        <v>-17.2</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0058</v>
       </c>
       <c r="H20" t="n">
-        <v>40.1</v>
+        <v>45.5</v>
       </c>
       <c r="I20" t="n">
-        <v>2942.7</v>
+        <v>2932.6</v>
       </c>
       <c r="J20" t="n">
-        <v>2960.87</v>
+        <v>2949.57</v>
       </c>
       <c r="K20" t="n">
-        <v>2975.95</v>
+        <v>2970.65</v>
       </c>
       <c r="L20" t="n">
-        <v>2991.03</v>
+        <v>2991.72</v>
       </c>
       <c r="M20" t="n">
-        <v>3007.65</v>
+        <v>3010.75</v>
       </c>
       <c r="N20" t="n">
-        <v>3024.28</v>
+        <v>3029.78</v>
       </c>
       <c r="O20" t="n">
-        <v>3037.8</v>
+        <v>3052.9</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2224,79 +2226,79 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2991.7</v>
+        <v>2964.5</v>
       </c>
       <c r="C21" t="n">
-        <v>2994.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D21" t="n">
-        <v>2949.3</v>
+        <v>2952.7</v>
       </c>
       <c r="E21" t="n">
-        <v>2973.5</v>
+        <v>2955.2</v>
       </c>
       <c r="F21" t="n">
-        <v>-17.2</v>
+        <v>-18.3</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0062</v>
       </c>
       <c r="H21" t="n">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="I21" t="n">
-        <v>2932.6</v>
+        <v>2903.8</v>
       </c>
       <c r="J21" t="n">
-        <v>2949.57</v>
+        <v>2928.72</v>
       </c>
       <c r="K21" t="n">
-        <v>2970.65</v>
+        <v>2950.75</v>
       </c>
       <c r="L21" t="n">
-        <v>2991.72</v>
+        <v>2972.78</v>
       </c>
       <c r="M21" t="n">
-        <v>3010.75</v>
+        <v>2996.25</v>
       </c>
       <c r="N21" t="n">
-        <v>3029.78</v>
+        <v>3019.72</v>
       </c>
       <c r="O21" t="n">
-        <v>3052.9</v>
+        <v>3040.3</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
@@ -2310,57 +2312,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2964.5</v>
+        <v>2955.8</v>
       </c>
       <c r="C22" t="n">
-        <v>2998.7</v>
+        <v>2999.8</v>
       </c>
       <c r="D22" t="n">
-        <v>2952.7</v>
+        <v>2951.1</v>
       </c>
       <c r="E22" t="n">
-        <v>2955.2</v>
+        <v>2997</v>
       </c>
       <c r="F22" t="n">
-        <v>-18.3</v>
+        <v>41.8</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0141</v>
       </c>
       <c r="H22" t="n">
-        <v>46</v>
+        <v>48.7</v>
       </c>
       <c r="I22" t="n">
-        <v>2903.8</v>
+        <v>2906.7</v>
       </c>
       <c r="J22" t="n">
-        <v>2928.72</v>
+        <v>2898.95</v>
       </c>
       <c r="K22" t="n">
-        <v>2950.75</v>
+        <v>2932.2</v>
       </c>
       <c r="L22" t="n">
-        <v>2972.78</v>
+        <v>2965.45</v>
       </c>
       <c r="M22" t="n">
-        <v>2996.25</v>
+        <v>2978.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3019.72</v>
+        <v>2990.95</v>
       </c>
       <c r="O22" t="n">
-        <v>3040.3</v>
+        <v>3044.7</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2368,23 +2370,23 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2403,50 +2405,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2955.8</v>
+        <v>2997</v>
       </c>
       <c r="C23" t="n">
-        <v>2999.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D23" t="n">
-        <v>2951.1</v>
+        <v>2965.5</v>
       </c>
       <c r="E23" t="n">
-        <v>2997</v>
+        <v>2969.8</v>
       </c>
       <c r="F23" t="n">
-        <v>41.8</v>
+        <v>-27.2</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0141</v>
+        <v>-0.0091</v>
       </c>
       <c r="H23" t="n">
-        <v>48.7</v>
+        <v>33.2</v>
       </c>
       <c r="I23" t="n">
-        <v>2906.7</v>
+        <v>2902.4</v>
       </c>
       <c r="J23" t="n">
-        <v>2898.95</v>
+        <v>2959.08</v>
       </c>
       <c r="K23" t="n">
-        <v>2932.2</v>
+        <v>2972.65</v>
       </c>
       <c r="L23" t="n">
-        <v>2965.45</v>
+        <v>2986.23</v>
       </c>
       <c r="M23" t="n">
-        <v>2978.2</v>
+        <v>3021.35</v>
       </c>
       <c r="N23" t="n">
-        <v>2990.95</v>
+        <v>3056.47</v>
       </c>
       <c r="O23" t="n">
-        <v>3044.7</v>
+        <v>3048.5</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2454,24 +2456,22 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
@@ -2482,60 +2482,62 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2997</v>
+        <v>2974.6</v>
       </c>
       <c r="C24" t="n">
-        <v>2998.7</v>
+        <v>2979</v>
       </c>
       <c r="D24" t="n">
-        <v>2965.5</v>
+        <v>2932.1</v>
       </c>
       <c r="E24" t="n">
-        <v>2969.8</v>
+        <v>2951.7</v>
       </c>
       <c r="F24" t="n">
-        <v>-27.2</v>
+        <v>-18.1</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0091</v>
+        <v>-0.0061</v>
       </c>
       <c r="H24" t="n">
-        <v>33.2</v>
+        <v>46.9</v>
       </c>
       <c r="I24" t="n">
-        <v>2902.4</v>
+        <v>2932.3</v>
       </c>
       <c r="J24" t="n">
-        <v>2959.08</v>
+        <v>2930.45</v>
       </c>
       <c r="K24" t="n">
-        <v>2972.65</v>
+        <v>2953.2</v>
       </c>
       <c r="L24" t="n">
-        <v>2986.23</v>
+        <v>2975.95</v>
       </c>
       <c r="M24" t="n">
-        <v>3021.35</v>
+        <v>2986.4</v>
       </c>
       <c r="N24" t="n">
-        <v>3056.47</v>
+        <v>2996.85</v>
       </c>
       <c r="O24" t="n">
-        <v>3048.5</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
+        <v>3031.9</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q24" s="6" t="n">
         <v/>
@@ -2566,74 +2568,70 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2974.6</v>
+        <v>2948.5</v>
       </c>
       <c r="C25" t="n">
-        <v>2979</v>
+        <v>2969.7</v>
       </c>
       <c r="D25" t="n">
-        <v>2932.1</v>
+        <v>2934.5</v>
       </c>
       <c r="E25" t="n">
-        <v>2951.7</v>
+        <v>2941.3</v>
       </c>
       <c r="F25" t="n">
-        <v>-18.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0035</v>
       </c>
       <c r="H25" t="n">
-        <v>46.9</v>
+        <v>35.2</v>
       </c>
       <c r="I25" t="n">
-        <v>2932.3</v>
+        <v>2885.2</v>
       </c>
       <c r="J25" t="n">
-        <v>2930.45</v>
+        <v>2902.88</v>
       </c>
       <c r="K25" t="n">
-        <v>2953.2</v>
+        <v>2928.25</v>
       </c>
       <c r="L25" t="n">
-        <v>2975.95</v>
+        <v>2953.62</v>
       </c>
       <c r="M25" t="n">
-        <v>2986.4</v>
+        <v>2975.15</v>
       </c>
       <c r="N25" t="n">
-        <v>2996.85</v>
+        <v>2996.67</v>
       </c>
       <c r="O25" t="n">
-        <v>3031.9</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3025.9</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
       </c>
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2652,57 +2650,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2948.5</v>
+        <v>2955.5</v>
       </c>
       <c r="C26" t="n">
-        <v>2969.7</v>
+        <v>2985.9</v>
       </c>
       <c r="D26" t="n">
-        <v>2934.5</v>
+        <v>2941.2</v>
       </c>
       <c r="E26" t="n">
-        <v>2941.3</v>
+        <v>2960</v>
       </c>
       <c r="F26" t="n">
-        <v>-10.4</v>
+        <v>18.7</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0064</v>
       </c>
       <c r="H26" t="n">
-        <v>35.2</v>
+        <v>44.7</v>
       </c>
       <c r="I26" t="n">
-        <v>2885.2</v>
+        <v>2899.3</v>
       </c>
       <c r="J26" t="n">
-        <v>2902.88</v>
+        <v>2900.7</v>
       </c>
       <c r="K26" t="n">
-        <v>2928.25</v>
+        <v>2923.7</v>
       </c>
       <c r="L26" t="n">
-        <v>2953.62</v>
+        <v>2946.7</v>
       </c>
       <c r="M26" t="n">
-        <v>2975.15</v>
+        <v>2958.9</v>
       </c>
       <c r="N26" t="n">
-        <v>2996.67</v>
+        <v>2971.1</v>
       </c>
       <c r="O26" t="n">
-        <v>3025.9</v>
+        <v>3004.9</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2713,16 +2711,20 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2732,59 +2734,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2955.5</v>
+        <v>2961.5</v>
       </c>
       <c r="C27" t="n">
-        <v>2985.9</v>
+        <v>2968.3</v>
       </c>
       <c r="D27" t="n">
-        <v>2941.2</v>
+        <v>2933.4</v>
       </c>
       <c r="E27" t="n">
-        <v>2960</v>
+        <v>2964.5</v>
       </c>
       <c r="F27" t="n">
-        <v>18.7</v>
+        <v>4.5</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0015</v>
       </c>
       <c r="H27" t="n">
-        <v>44.7</v>
+        <v>34.9</v>
       </c>
       <c r="I27" t="n">
-        <v>2899.3</v>
+        <v>2896.5</v>
       </c>
       <c r="J27" t="n">
-        <v>2900.7</v>
+        <v>2913.53</v>
       </c>
       <c r="K27" t="n">
-        <v>2923.7</v>
+        <v>2937.65</v>
       </c>
       <c r="L27" t="n">
-        <v>2946.7</v>
+        <v>2961.77</v>
       </c>
       <c r="M27" t="n">
-        <v>2958.9</v>
+        <v>2982.35</v>
       </c>
       <c r="N27" t="n">
-        <v>2971.1</v>
+        <v>3002.92</v>
       </c>
       <c r="O27" t="n">
-        <v>3004.9</v>
+        <v>3030.6</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2792,23 +2790,21 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2818,70 +2814,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2961.5</v>
+        <v>2966.9</v>
       </c>
       <c r="C28" t="n">
-        <v>2968.3</v>
+        <v>2978.3</v>
       </c>
       <c r="D28" t="n">
-        <v>2933.4</v>
+        <v>2902.3</v>
       </c>
       <c r="E28" t="n">
-        <v>2964.5</v>
+        <v>2915.4</v>
       </c>
       <c r="F28" t="n">
-        <v>4.5</v>
+        <v>-49.1</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0166</v>
       </c>
       <c r="H28" t="n">
-        <v>34.9</v>
+        <v>76</v>
       </c>
       <c r="I28" t="n">
-        <v>2896.5</v>
+        <v>2898.5</v>
       </c>
       <c r="J28" t="n">
-        <v>2913.53</v>
+        <v>2936.42</v>
       </c>
       <c r="K28" t="n">
-        <v>2937.65</v>
+        <v>2947.05</v>
       </c>
       <c r="L28" t="n">
-        <v>2961.77</v>
+        <v>2957.67</v>
       </c>
       <c r="M28" t="n">
-        <v>2982.35</v>
+        <v>2981.95</v>
       </c>
       <c r="N28" t="n">
-        <v>3002.92</v>
+        <v>3006.23</v>
       </c>
       <c r="O28" t="n">
-        <v>3030.6</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
+        <v>3003.2</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2893,88 +2897,84 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W28" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2966.9</v>
+        <v>2906.6</v>
       </c>
       <c r="C29" t="n">
-        <v>2978.3</v>
+        <v>2957.9</v>
       </c>
       <c r="D29" t="n">
-        <v>2902.3</v>
+        <v>2905.6</v>
       </c>
       <c r="E29" t="n">
-        <v>2915.4</v>
+        <v>2954.3</v>
       </c>
       <c r="F29" t="n">
-        <v>-49.1</v>
+        <v>38.9</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0166</v>
+        <v>0.0133</v>
       </c>
       <c r="H29" t="n">
-        <v>76</v>
+        <v>52.3</v>
       </c>
       <c r="I29" t="n">
-        <v>2898.5</v>
+        <v>2826.3</v>
       </c>
       <c r="J29" t="n">
-        <v>2936.42</v>
+        <v>2826.95</v>
       </c>
       <c r="K29" t="n">
-        <v>2947.05</v>
+        <v>2877.4</v>
       </c>
       <c r="L29" t="n">
-        <v>2957.67</v>
+        <v>2927.85</v>
       </c>
       <c r="M29" t="n">
-        <v>2981.95</v>
+        <v>2953.4</v>
       </c>
       <c r="N29" t="n">
-        <v>3006.23</v>
+        <v>2978.95</v>
       </c>
       <c r="O29" t="n">
-        <v>3003.2</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
+        <v>3054.3</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
       <c r="U29" s="8" t="n">
         <v/>
       </c>
@@ -2988,76 +2988,78 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2906.6</v>
+        <v>2954</v>
       </c>
       <c r="C30" t="n">
-        <v>2957.9</v>
+        <v>2976.3</v>
       </c>
       <c r="D30" t="n">
-        <v>2905.6</v>
+        <v>2905.3</v>
       </c>
       <c r="E30" t="n">
-        <v>2954.3</v>
+        <v>2938</v>
       </c>
       <c r="F30" t="n">
-        <v>38.9</v>
+        <v>-16.3</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0055</v>
       </c>
       <c r="H30" t="n">
-        <v>52.3</v>
+        <v>71</v>
       </c>
       <c r="I30" t="n">
-        <v>2826.3</v>
+        <v>2853.3</v>
       </c>
       <c r="J30" t="n">
-        <v>2826.95</v>
+        <v>2913.28</v>
       </c>
       <c r="K30" t="n">
-        <v>2877.4</v>
+        <v>2928.15</v>
       </c>
       <c r="L30" t="n">
-        <v>2927.85</v>
+        <v>2943.03</v>
       </c>
       <c r="M30" t="n">
-        <v>2953.4</v>
+        <v>2980.45</v>
       </c>
       <c r="N30" t="n">
-        <v>2978.95</v>
+        <v>3017.87</v>
       </c>
       <c r="O30" t="n">
-        <v>3054.3</v>
+        <v>3010.2</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3072,78 +3074,76 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2954</v>
+        <v>2950</v>
       </c>
       <c r="C31" t="n">
-        <v>2976.3</v>
+        <v>2994.6</v>
       </c>
       <c r="D31" t="n">
-        <v>2905.3</v>
+        <v>2948.4</v>
       </c>
       <c r="E31" t="n">
-        <v>2938</v>
+        <v>2989.3</v>
       </c>
       <c r="F31" t="n">
-        <v>-16.3</v>
+        <v>51.3</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0175</v>
       </c>
       <c r="H31" t="n">
-        <v>71</v>
+        <v>46.2</v>
       </c>
       <c r="I31" t="n">
-        <v>2853.3</v>
+        <v>2834.3</v>
       </c>
       <c r="J31" t="n">
-        <v>2913.28</v>
+        <v>2865.6</v>
       </c>
       <c r="K31" t="n">
-        <v>2928.15</v>
+        <v>2902.5</v>
       </c>
       <c r="L31" t="n">
-        <v>2943.03</v>
+        <v>2939.4</v>
       </c>
       <c r="M31" t="n">
-        <v>2980.45</v>
+        <v>2973.5</v>
       </c>
       <c r="N31" t="n">
-        <v>3017.87</v>
+        <v>3007.6</v>
       </c>
       <c r="O31" t="n">
-        <v>3010.2</v>
+        <v>3047.3</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3158,57 +3158,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2950</v>
+        <v>2992.4</v>
       </c>
       <c r="C32" t="n">
-        <v>2994.6</v>
+        <v>3051.8</v>
       </c>
       <c r="D32" t="n">
-        <v>2948.4</v>
+        <v>2986.1</v>
       </c>
       <c r="E32" t="n">
-        <v>2989.3</v>
+        <v>3044.7</v>
       </c>
       <c r="F32" t="n">
-        <v>51.3</v>
+        <v>55.4</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0185</v>
       </c>
       <c r="H32" t="n">
-        <v>46.2</v>
+        <v>65.7</v>
       </c>
       <c r="I32" t="n">
-        <v>2834.3</v>
+        <v>2902.2</v>
       </c>
       <c r="J32" t="n">
-        <v>2865.6</v>
+        <v>2952</v>
       </c>
       <c r="K32" t="n">
-        <v>2902.5</v>
+        <v>2966.2</v>
       </c>
       <c r="L32" t="n">
-        <v>2939.4</v>
+        <v>2980.4</v>
       </c>
       <c r="M32" t="n">
-        <v>2973.5</v>
+        <v>3012.4</v>
       </c>
       <c r="N32" t="n">
-        <v>3007.6</v>
+        <v>3044.4</v>
       </c>
       <c r="O32" t="n">
-        <v>3047.3</v>
+        <v>3040.8</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3226,73 +3226,73 @@
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W32" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W32" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2992.4</v>
+        <v>3049.1</v>
       </c>
       <c r="C33" t="n">
-        <v>3051.8</v>
+        <v>3058.3</v>
       </c>
       <c r="D33" t="n">
-        <v>2986.1</v>
+        <v>3023.3</v>
       </c>
       <c r="E33" t="n">
-        <v>3044.7</v>
+        <v>3025.4</v>
       </c>
       <c r="F33" t="n">
-        <v>55.4</v>
+        <v>-19.3</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0063</v>
       </c>
       <c r="H33" t="n">
-        <v>65.7</v>
+        <v>35</v>
       </c>
       <c r="I33" t="n">
-        <v>2902.2</v>
+        <v>2920.4</v>
       </c>
       <c r="J33" t="n">
-        <v>2952</v>
+        <v>2991.87</v>
       </c>
       <c r="K33" t="n">
-        <v>2966.2</v>
+        <v>3011.85</v>
       </c>
       <c r="L33" t="n">
-        <v>2980.4</v>
+        <v>3031.83</v>
       </c>
       <c r="M33" t="n">
-        <v>3012.4</v>
+        <v>3077.55</v>
       </c>
       <c r="N33" t="n">
-        <v>3044.4</v>
+        <v>3123.27</v>
       </c>
       <c r="O33" t="n">
-        <v>3040.8</v>
+        <v>3117.5</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3303,80 +3303,78 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3049.1</v>
+        <v>3028.5</v>
       </c>
       <c r="C34" t="n">
-        <v>3058.3</v>
+        <v>3041</v>
       </c>
       <c r="D34" t="n">
-        <v>3023.3</v>
+        <v>3004.9</v>
       </c>
       <c r="E34" t="n">
-        <v>3025.4</v>
+        <v>3009.1</v>
       </c>
       <c r="F34" t="n">
-        <v>-19.3</v>
+        <v>-16.3</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0054</v>
       </c>
       <c r="H34" t="n">
-        <v>35</v>
+        <v>36.1</v>
       </c>
       <c r="I34" t="n">
-        <v>2920.4</v>
+        <v>2988.3</v>
       </c>
       <c r="J34" t="n">
-        <v>2991.87</v>
+        <v>2982.7</v>
       </c>
       <c r="K34" t="n">
-        <v>3011.85</v>
+        <v>3007.9</v>
       </c>
       <c r="L34" t="n">
-        <v>3031.83</v>
+        <v>3033.1</v>
       </c>
       <c r="M34" t="n">
-        <v>3077.55</v>
+        <v>3042.9</v>
       </c>
       <c r="N34" t="n">
-        <v>3123.27</v>
+        <v>3052.7</v>
       </c>
       <c r="O34" t="n">
-        <v>3117.5</v>
+        <v>3093.3</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3384,12 +3382,14 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3408,57 +3408,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3028.5</v>
+        <v>3008.5</v>
       </c>
       <c r="C35" t="n">
-        <v>3041</v>
+        <v>3046.8</v>
       </c>
       <c r="D35" t="n">
-        <v>3004.9</v>
+        <v>3002</v>
       </c>
       <c r="E35" t="n">
-        <v>3009.1</v>
+        <v>3041.6</v>
       </c>
       <c r="F35" t="n">
-        <v>-16.3</v>
+        <v>32.5</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0054</v>
+        <v>0.0108</v>
       </c>
       <c r="H35" t="n">
-        <v>36.1</v>
+        <v>44.8</v>
       </c>
       <c r="I35" t="n">
-        <v>2988.3</v>
+        <v>2968.8</v>
       </c>
       <c r="J35" t="n">
-        <v>2982.7</v>
+        <v>2966.08</v>
       </c>
       <c r="K35" t="n">
-        <v>3007.9</v>
+        <v>2991.05</v>
       </c>
       <c r="L35" t="n">
-        <v>3033.1</v>
+        <v>3016.03</v>
       </c>
       <c r="M35" t="n">
-        <v>3042.9</v>
+        <v>3027.15</v>
       </c>
       <c r="N35" t="n">
-        <v>3052.7</v>
+        <v>3038.28</v>
       </c>
       <c r="O35" t="n">
-        <v>3093.3</v>
+        <v>3077.1</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3466,22 +3466,24 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
@@ -3492,57 +3494,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3008.5</v>
+        <v>3038.9</v>
       </c>
       <c r="C36" t="n">
-        <v>3046.8</v>
+        <v>3044.6</v>
       </c>
       <c r="D36" t="n">
-        <v>3002</v>
+        <v>3016</v>
       </c>
       <c r="E36" t="n">
-        <v>3041.6</v>
+        <v>3025</v>
       </c>
       <c r="F36" t="n">
-        <v>32.5</v>
+        <v>-16.6</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0108</v>
+        <v>-0.0055</v>
       </c>
       <c r="H36" t="n">
-        <v>44.8</v>
+        <v>28.6</v>
       </c>
       <c r="I36" t="n">
-        <v>2968.8</v>
+        <v>2957.2</v>
       </c>
       <c r="J36" t="n">
-        <v>2966.08</v>
+        <v>3005.4</v>
       </c>
       <c r="K36" t="n">
-        <v>2991.05</v>
+        <v>3019.2</v>
       </c>
       <c r="L36" t="n">
-        <v>3016.03</v>
+        <v>3033</v>
       </c>
       <c r="M36" t="n">
-        <v>3027.15</v>
+        <v>3064</v>
       </c>
       <c r="N36" t="n">
-        <v>3038.28</v>
+        <v>3095</v>
       </c>
       <c r="O36" t="n">
-        <v>3077.1</v>
+        <v>3091.6</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3550,24 +3552,22 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
@@ -3578,57 +3578,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3038.9</v>
+        <v>3024.7</v>
       </c>
       <c r="C37" t="n">
-        <v>3044.6</v>
+        <v>3045.8</v>
       </c>
       <c r="D37" t="n">
-        <v>3016</v>
+        <v>3019.9</v>
       </c>
       <c r="E37" t="n">
-        <v>3025</v>
+        <v>3035.5</v>
       </c>
       <c r="F37" t="n">
-        <v>-16.6</v>
+        <v>10.5</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0035</v>
       </c>
       <c r="H37" t="n">
-        <v>28.6</v>
+        <v>25.9</v>
       </c>
       <c r="I37" t="n">
-        <v>2957.2</v>
+        <v>2987.4</v>
       </c>
       <c r="J37" t="n">
-        <v>3005.4</v>
+        <v>2993.75</v>
       </c>
       <c r="K37" t="n">
-        <v>3019.2</v>
+        <v>3010.7</v>
       </c>
       <c r="L37" t="n">
-        <v>3033</v>
+        <v>3027.65</v>
       </c>
       <c r="M37" t="n">
-        <v>3064</v>
+        <v>3039.3</v>
       </c>
       <c r="N37" t="n">
-        <v>3095</v>
+        <v>3050.95</v>
       </c>
       <c r="O37" t="n">
-        <v>3091.6</v>
+        <v>3073.2</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3636,19 +3636,19 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
@@ -3660,59 +3660,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3024.7</v>
+        <v>3036.1</v>
       </c>
       <c r="C38" t="n">
-        <v>3045.8</v>
+        <v>3060</v>
       </c>
       <c r="D38" t="n">
-        <v>3019.9</v>
+        <v>3033.1</v>
       </c>
       <c r="E38" t="n">
-        <v>3035.5</v>
+        <v>3052.8</v>
       </c>
       <c r="F38" t="n">
-        <v>10.5</v>
+        <v>17.3</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0057</v>
       </c>
       <c r="H38" t="n">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
       <c r="I38" t="n">
-        <v>2987.4</v>
+        <v>2994</v>
       </c>
       <c r="J38" t="n">
-        <v>2993.75</v>
+        <v>3010.92</v>
       </c>
       <c r="K38" t="n">
-        <v>3010.7</v>
+        <v>3022.55</v>
       </c>
       <c r="L38" t="n">
-        <v>3027.65</v>
+        <v>3034.17</v>
       </c>
       <c r="M38" t="n">
-        <v>3039.3</v>
+        <v>3048.45</v>
       </c>
       <c r="N38" t="n">
-        <v>3050.95</v>
+        <v>3062.73</v>
       </c>
       <c r="O38" t="n">
-        <v>3073.2</v>
+        <v>3071.7</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3749,50 +3745,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3036.1</v>
+        <v>3056.2</v>
       </c>
       <c r="C39" t="n">
-        <v>3060</v>
+        <v>3076.3</v>
       </c>
       <c r="D39" t="n">
-        <v>3033.1</v>
+        <v>3052.5</v>
       </c>
       <c r="E39" t="n">
-        <v>3052.8</v>
+        <v>3060.2</v>
       </c>
       <c r="F39" t="n">
-        <v>17.3</v>
+        <v>7.4</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0024</v>
       </c>
       <c r="H39" t="n">
-        <v>26.9</v>
+        <v>23.8</v>
       </c>
       <c r="I39" t="n">
-        <v>2994</v>
+        <v>3006.2</v>
       </c>
       <c r="J39" t="n">
-        <v>3010.92</v>
+        <v>3029.03</v>
       </c>
       <c r="K39" t="n">
-        <v>3022.55</v>
+        <v>3039.35</v>
       </c>
       <c r="L39" t="n">
-        <v>3034.17</v>
+        <v>3049.68</v>
       </c>
       <c r="M39" t="n">
-        <v>3048.45</v>
+        <v>3066.25</v>
       </c>
       <c r="N39" t="n">
-        <v>3062.73</v>
+        <v>3082.82</v>
       </c>
       <c r="O39" t="n">
-        <v>3071.7</v>
+        <v>3086.9</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3829,50 +3825,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3056.2</v>
+        <v>3062.2</v>
       </c>
       <c r="C40" t="n">
         <v>3076.3</v>
       </c>
       <c r="D40" t="n">
-        <v>3052.5</v>
+        <v>3051.7</v>
       </c>
       <c r="E40" t="n">
-        <v>3060.2</v>
+        <v>3074.9</v>
       </c>
       <c r="F40" t="n">
-        <v>7.4</v>
+        <v>14.7</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0048</v>
       </c>
       <c r="H40" t="n">
-        <v>23.8</v>
+        <v>24.6</v>
       </c>
       <c r="I40" t="n">
-        <v>3006.2</v>
+        <v>3028.7</v>
       </c>
       <c r="J40" t="n">
-        <v>3029.03</v>
+        <v>3034.3</v>
       </c>
       <c r="K40" t="n">
-        <v>3039.35</v>
+        <v>3048.3</v>
       </c>
       <c r="L40" t="n">
-        <v>3049.68</v>
+        <v>3062.3</v>
       </c>
       <c r="M40" t="n">
-        <v>3066.25</v>
+        <v>3072.1</v>
       </c>
       <c r="N40" t="n">
-        <v>3082.82</v>
+        <v>3081.9</v>
       </c>
       <c r="O40" t="n">
-        <v>3086.9</v>
+        <v>3100.1</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3904,55 +3900,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3062.2</v>
+        <v>3073.5</v>
       </c>
       <c r="C41" t="n">
-        <v>3076.3</v>
+        <v>3079.9</v>
       </c>
       <c r="D41" t="n">
-        <v>3051.7</v>
+        <v>3055.9</v>
       </c>
       <c r="E41" t="n">
-        <v>3074.9</v>
+        <v>3064.9</v>
       </c>
       <c r="F41" t="n">
-        <v>14.7</v>
+        <v>-10</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.0033</v>
       </c>
       <c r="H41" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="I41" t="n">
-        <v>3028.7</v>
+        <v>3027.1</v>
       </c>
       <c r="J41" t="n">
-        <v>3034.3</v>
+        <v>3055.75</v>
       </c>
       <c r="K41" t="n">
-        <v>3048.3</v>
+        <v>3062.6</v>
       </c>
       <c r="L41" t="n">
-        <v>3062.3</v>
+        <v>3069.45</v>
       </c>
       <c r="M41" t="n">
-        <v>3072.1</v>
+        <v>3087.2</v>
       </c>
       <c r="N41" t="n">
-        <v>3081.9</v>
+        <v>3104.95</v>
       </c>
       <c r="O41" t="n">
-        <v>3100.1</v>
+        <v>3100.9</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3960,18 +3960,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
+      <c r="R41" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3993,60 +3993,64 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3073.5</v>
+        <v>3063.7</v>
       </c>
       <c r="C42" t="n">
-        <v>3079.9</v>
+        <v>3066.6</v>
       </c>
       <c r="D42" t="n">
-        <v>3055.9</v>
+        <v>3024.1</v>
       </c>
       <c r="E42" t="n">
-        <v>3064.9</v>
+        <v>3026.4</v>
       </c>
       <c r="F42" t="n">
-        <v>-10</v>
+        <v>-38.5</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0126</v>
       </c>
       <c r="H42" t="n">
-        <v>24</v>
+        <v>42.5</v>
       </c>
       <c r="I42" t="n">
-        <v>3027.1</v>
+        <v>3031.9</v>
       </c>
       <c r="J42" t="n">
-        <v>3055.75</v>
+        <v>3039.4</v>
       </c>
       <c r="K42" t="n">
-        <v>3062.6</v>
+        <v>3052.9</v>
       </c>
       <c r="L42" t="n">
-        <v>3069.45</v>
+        <v>3066.4</v>
       </c>
       <c r="M42" t="n">
-        <v>3087.2</v>
+        <v>3076.9</v>
       </c>
       <c r="N42" t="n">
-        <v>3104.95</v>
+        <v>3087.4</v>
       </c>
       <c r="O42" t="n">
-        <v>3100.9</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
+        <v>3103.9</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
@@ -4063,88 +4067,80 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W42" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3063.7</v>
+        <v>3025.9</v>
       </c>
       <c r="C43" t="n">
-        <v>3066.6</v>
+        <v>3059.1</v>
       </c>
       <c r="D43" t="n">
-        <v>3024.1</v>
+        <v>3019.8</v>
       </c>
       <c r="E43" t="n">
-        <v>3026.4</v>
+        <v>3039.9</v>
       </c>
       <c r="F43" t="n">
-        <v>-38.5</v>
+        <v>13.5</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0045</v>
       </c>
       <c r="H43" t="n">
-        <v>42.5</v>
+        <v>39.3</v>
       </c>
       <c r="I43" t="n">
-        <v>3031.9</v>
+        <v>2981.6</v>
       </c>
       <c r="J43" t="n">
-        <v>3039.4</v>
+        <v>2974.42</v>
       </c>
       <c r="K43" t="n">
-        <v>3052.9</v>
+        <v>3005.15</v>
       </c>
       <c r="L43" t="n">
-        <v>3066.4</v>
+        <v>3035.88</v>
       </c>
       <c r="M43" t="n">
-        <v>3076.9</v>
+        <v>3047.65</v>
       </c>
       <c r="N43" t="n">
-        <v>3087.4</v>
+        <v>3059.42</v>
       </c>
       <c r="O43" t="n">
-        <v>3103.9</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
+        <v>3109.1</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4156,75 +4152,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3025.9</v>
+        <v>3041.4</v>
       </c>
       <c r="C44" t="n">
-        <v>3059.1</v>
+        <v>3048.5</v>
       </c>
       <c r="D44" t="n">
-        <v>3019.8</v>
+        <v>2993.2</v>
       </c>
       <c r="E44" t="n">
-        <v>3039.9</v>
+        <v>2999.2</v>
       </c>
       <c r="F44" t="n">
-        <v>13.5</v>
+        <v>-40.7</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0134</v>
       </c>
       <c r="H44" t="n">
-        <v>39.3</v>
+        <v>55.3</v>
       </c>
       <c r="I44" t="n">
-        <v>2981.6</v>
+        <v>2980.5</v>
       </c>
       <c r="J44" t="n">
-        <v>2974.42</v>
+        <v>3000.82</v>
       </c>
       <c r="K44" t="n">
-        <v>3005.15</v>
+        <v>3020.25</v>
       </c>
       <c r="L44" t="n">
-        <v>3035.88</v>
+        <v>3039.67</v>
       </c>
       <c r="M44" t="n">
-        <v>3047.65</v>
+        <v>3059.55</v>
       </c>
       <c r="N44" t="n">
-        <v>3059.42</v>
+        <v>3079.42</v>
       </c>
       <c r="O44" t="n">
-        <v>3109.1</v>
+        <v>3098.4</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
@@ -4236,81 +4238,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3041.4</v>
+        <v>2999.6</v>
       </c>
       <c r="C45" t="n">
-        <v>3048.5</v>
+        <v>3026.7</v>
       </c>
       <c r="D45" t="n">
-        <v>2993.2</v>
+        <v>2997.9</v>
       </c>
       <c r="E45" t="n">
-        <v>2999.2</v>
+        <v>3022.1</v>
       </c>
       <c r="F45" t="n">
-        <v>-40.7</v>
+        <v>22.9</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0134</v>
+        <v>0.0076</v>
       </c>
       <c r="H45" t="n">
-        <v>55.3</v>
+        <v>28.8</v>
       </c>
       <c r="I45" t="n">
-        <v>2980.5</v>
+        <v>2937.9</v>
       </c>
       <c r="J45" t="n">
-        <v>3000.82</v>
+        <v>2933.07</v>
       </c>
       <c r="K45" t="n">
-        <v>3020.25</v>
+        <v>2971.55</v>
       </c>
       <c r="L45" t="n">
-        <v>3039.67</v>
+        <v>3010.02</v>
       </c>
       <c r="M45" t="n">
-        <v>3059.55</v>
+        <v>3026.85</v>
       </c>
       <c r="N45" t="n">
-        <v>3079.42</v>
+        <v>3043.67</v>
       </c>
       <c r="O45" t="n">
-        <v>3098.4</v>
+        <v>3103.8</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
@@ -4322,75 +4318,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2999.6</v>
+        <v>3023</v>
       </c>
       <c r="C46" t="n">
-        <v>3026.7</v>
+        <v>3028.9</v>
       </c>
       <c r="D46" t="n">
-        <v>2997.9</v>
+        <v>2996</v>
       </c>
       <c r="E46" t="n">
-        <v>3022.1</v>
+        <v>3001.6</v>
       </c>
       <c r="F46" t="n">
-        <v>22.9</v>
+        <v>-20.5</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0076</v>
+        <v>-0.0068</v>
       </c>
       <c r="H46" t="n">
-        <v>28.8</v>
+        <v>32.9</v>
       </c>
       <c r="I46" t="n">
-        <v>2937.9</v>
+        <v>2969.1</v>
       </c>
       <c r="J46" t="n">
-        <v>2933.07</v>
+        <v>2998.2</v>
       </c>
       <c r="K46" t="n">
-        <v>2971.55</v>
+        <v>3007.7</v>
       </c>
       <c r="L46" t="n">
-        <v>3010.02</v>
+        <v>3017.2</v>
       </c>
       <c r="M46" t="n">
-        <v>3026.85</v>
+        <v>3036.5</v>
       </c>
       <c r="N46" t="n">
-        <v>3043.67</v>
+        <v>3055.8</v>
       </c>
       <c r="O46" t="n">
-        <v>3103.8</v>
+        <v>3055.5</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
+      <c r="Q46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4404,79 +4406,77 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3023</v>
+        <v>3004.6</v>
       </c>
       <c r="C47" t="n">
-        <v>3028.9</v>
+        <v>3025.4</v>
       </c>
       <c r="D47" t="n">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="E47" t="n">
-        <v>3001.6</v>
+        <v>3014.4</v>
       </c>
       <c r="F47" t="n">
-        <v>-20.5</v>
+        <v>12.8</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0043</v>
       </c>
       <c r="H47" t="n">
-        <v>32.9</v>
+        <v>28.4</v>
       </c>
       <c r="I47" t="n">
-        <v>2969.1</v>
+        <v>2963.1</v>
       </c>
       <c r="J47" t="n">
-        <v>2998.2</v>
+        <v>2963.28</v>
       </c>
       <c r="K47" t="n">
-        <v>3007.7</v>
+        <v>2985.15</v>
       </c>
       <c r="L47" t="n">
-        <v>3017.2</v>
+        <v>3007.03</v>
       </c>
       <c r="M47" t="n">
-        <v>3036.5</v>
+        <v>3018.05</v>
       </c>
       <c r="N47" t="n">
-        <v>3055.8</v>
+        <v>3029.08</v>
       </c>
       <c r="O47" t="n">
-        <v>3055.5</v>
+        <v>3061.8</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
       <c r="U47" s="8" t="n">
         <v/>
       </c>
@@ -4490,57 +4490,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3004.6</v>
+        <v>3014.6</v>
       </c>
       <c r="C48" t="n">
-        <v>3025.4</v>
+        <v>3020.5</v>
       </c>
       <c r="D48" t="n">
-        <v>2997</v>
+        <v>3002.6</v>
       </c>
       <c r="E48" t="n">
-        <v>3014.4</v>
+        <v>3010.1</v>
       </c>
       <c r="F48" t="n">
-        <v>12.8</v>
+        <v>-4.3</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0014</v>
       </c>
       <c r="H48" t="n">
-        <v>28.4</v>
+        <v>17.9</v>
       </c>
       <c r="I48" t="n">
-        <v>2963.1</v>
+        <v>2968.6</v>
       </c>
       <c r="J48" t="n">
-        <v>2963.28</v>
+        <v>2987.6</v>
       </c>
       <c r="K48" t="n">
-        <v>2985.15</v>
+        <v>3000.2</v>
       </c>
       <c r="L48" t="n">
-        <v>3007.03</v>
+        <v>3012.8</v>
       </c>
       <c r="M48" t="n">
-        <v>3018.05</v>
+        <v>3028.6</v>
       </c>
       <c r="N48" t="n">
-        <v>3029.08</v>
+        <v>3044.4</v>
       </c>
       <c r="O48" t="n">
-        <v>3061.8</v>
+        <v>3053.8</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4551,15 +4551,13 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4574,57 +4572,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3014.6</v>
+        <v>3016.9</v>
       </c>
       <c r="C49" t="n">
-        <v>3020.5</v>
+        <v>3024.2</v>
       </c>
       <c r="D49" t="n">
-        <v>3002.6</v>
+        <v>3002.1</v>
       </c>
       <c r="E49" t="n">
-        <v>3010.1</v>
+        <v>3019</v>
       </c>
       <c r="F49" t="n">
-        <v>-4.3</v>
+        <v>8.9</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0014</v>
+        <v>0.003</v>
       </c>
       <c r="H49" t="n">
-        <v>17.9</v>
+        <v>22.1</v>
       </c>
       <c r="I49" t="n">
-        <v>2968.6</v>
+        <v>2984.7</v>
       </c>
       <c r="J49" t="n">
-        <v>2987.6</v>
+        <v>2991.48</v>
       </c>
       <c r="K49" t="n">
-        <v>3000.2</v>
+        <v>3001.15</v>
       </c>
       <c r="L49" t="n">
-        <v>3012.8</v>
+        <v>3010.83</v>
       </c>
       <c r="M49" t="n">
-        <v>3028.6</v>
+        <v>3019.05</v>
       </c>
       <c r="N49" t="n">
-        <v>3044.4</v>
+        <v>3027.28</v>
       </c>
       <c r="O49" t="n">
-        <v>3053.8</v>
+        <v>3038.4</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4635,13 +4633,15 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4656,77 +4656,81 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3016.9</v>
+        <v>3019.6</v>
       </c>
       <c r="C50" t="n">
-        <v>3024.2</v>
+        <v>3025.5</v>
       </c>
       <c r="D50" t="n">
-        <v>3002.1</v>
+        <v>2976.6</v>
       </c>
       <c r="E50" t="n">
-        <v>3019</v>
+        <v>2977.5</v>
       </c>
       <c r="F50" t="n">
-        <v>8.9</v>
+        <v>-41.5</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0137</v>
       </c>
       <c r="H50" t="n">
-        <v>22.1</v>
+        <v>48.9</v>
       </c>
       <c r="I50" t="n">
-        <v>2984.7</v>
+        <v>2980</v>
       </c>
       <c r="J50" t="n">
-        <v>2991.48</v>
+        <v>2999.83</v>
       </c>
       <c r="K50" t="n">
-        <v>3001.15</v>
+        <v>3007.95</v>
       </c>
       <c r="L50" t="n">
-        <v>3010.83</v>
+        <v>3016.08</v>
       </c>
       <c r="M50" t="n">
-        <v>3019.05</v>
+        <v>3030.05</v>
       </c>
       <c r="N50" t="n">
-        <v>3027.28</v>
+        <v>3044.02</v>
       </c>
       <c r="O50" t="n">
-        <v>3038.4</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
+        <v>3046.3</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
       <c r="U50" s="8" t="n">
         <v/>
       </c>
@@ -4740,73 +4744,69 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3019.6</v>
+        <v>2971</v>
       </c>
       <c r="C51" t="n">
-        <v>3025.5</v>
+        <v>2982.5</v>
       </c>
       <c r="D51" t="n">
-        <v>2976.6</v>
+        <v>2946.1</v>
       </c>
       <c r="E51" t="n">
-        <v>2977.5</v>
+        <v>2958.7</v>
       </c>
       <c r="F51" t="n">
-        <v>-41.5</v>
+        <v>-18.8</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0063</v>
       </c>
       <c r="H51" t="n">
-        <v>48.9</v>
+        <v>36.4</v>
       </c>
       <c r="I51" t="n">
-        <v>2980</v>
+        <v>2927.7</v>
       </c>
       <c r="J51" t="n">
-        <v>2999.83</v>
+        <v>2916.83</v>
       </c>
       <c r="K51" t="n">
-        <v>3007.95</v>
+        <v>2953.05</v>
       </c>
       <c r="L51" t="n">
-        <v>3016.08</v>
+        <v>2989.28</v>
       </c>
       <c r="M51" t="n">
-        <v>3030.05</v>
+        <v>3001.95</v>
       </c>
       <c r="N51" t="n">
-        <v>3044.02</v>
+        <v>3014.62</v>
       </c>
       <c r="O51" t="n">
-        <v>3046.3</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
+        <v>3074.4</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4826,69 +4826,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2971</v>
+        <v>2958</v>
       </c>
       <c r="C52" t="n">
-        <v>2982.5</v>
+        <v>2964.6</v>
       </c>
       <c r="D52" t="n">
-        <v>2946.1</v>
+        <v>2918.9</v>
       </c>
       <c r="E52" t="n">
-        <v>2958.7</v>
+        <v>2924.7</v>
       </c>
       <c r="F52" t="n">
-        <v>-18.8</v>
+        <v>-34</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0115</v>
       </c>
       <c r="H52" t="n">
-        <v>36.4</v>
+        <v>45.7</v>
       </c>
       <c r="I52" t="n">
-        <v>2927.7</v>
+        <v>2909.7</v>
       </c>
       <c r="J52" t="n">
-        <v>2916.83</v>
+        <v>2919.5</v>
       </c>
       <c r="K52" t="n">
-        <v>2953.05</v>
+        <v>2940.5</v>
       </c>
       <c r="L52" t="n">
-        <v>2989.28</v>
+        <v>2961.5</v>
       </c>
       <c r="M52" t="n">
-        <v>3001.95</v>
+        <v>2976.9</v>
       </c>
       <c r="N52" t="n">
-        <v>3014.62</v>
+        <v>2992.3</v>
       </c>
       <c r="O52" t="n">
-        <v>3074.4</v>
+        <v>3018.9</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
@@ -4915,75 +4913,75 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2958</v>
+        <v>2926.4</v>
       </c>
       <c r="C53" t="n">
-        <v>2964.6</v>
+        <v>2962.5</v>
       </c>
       <c r="D53" t="n">
-        <v>2918.9</v>
+        <v>2914.5</v>
       </c>
       <c r="E53" t="n">
-        <v>2924.7</v>
+        <v>2958.8</v>
       </c>
       <c r="F53" t="n">
-        <v>-34</v>
+        <v>34.1</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0.0117</v>
       </c>
       <c r="H53" t="n">
-        <v>45.7</v>
+        <v>48</v>
       </c>
       <c r="I53" t="n">
-        <v>2909.7</v>
+        <v>2873.2</v>
       </c>
       <c r="J53" t="n">
-        <v>2919.5</v>
+        <v>2870.47</v>
       </c>
       <c r="K53" t="n">
-        <v>2940.5</v>
+        <v>2901.85</v>
       </c>
       <c r="L53" t="n">
-        <v>2961.5</v>
+        <v>2933.22</v>
       </c>
       <c r="M53" t="n">
-        <v>2976.9</v>
+        <v>2947.55</v>
       </c>
       <c r="N53" t="n">
-        <v>2992.3</v>
+        <v>2961.88</v>
       </c>
       <c r="O53" t="n">
-        <v>3018.9</v>
+        <v>3010.3</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
@@ -4992,55 +4990,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2926.4</v>
+        <v>2957.6</v>
       </c>
       <c r="C54" t="n">
-        <v>2962.5</v>
+        <v>2983.3</v>
       </c>
       <c r="D54" t="n">
-        <v>2914.5</v>
+        <v>2949.9</v>
       </c>
       <c r="E54" t="n">
-        <v>2958.8</v>
+        <v>2969.7</v>
       </c>
       <c r="F54" t="n">
-        <v>34.1</v>
+        <v>10.9</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0117</v>
+        <v>0.0037</v>
       </c>
       <c r="H54" t="n">
-        <v>48</v>
+        <v>33.4</v>
       </c>
       <c r="I54" t="n">
-        <v>2873.2</v>
+        <v>2866.5</v>
       </c>
       <c r="J54" t="n">
-        <v>2870.47</v>
+        <v>2920.95</v>
       </c>
       <c r="K54" t="n">
-        <v>2901.85</v>
+        <v>2934.8</v>
       </c>
       <c r="L54" t="n">
-        <v>2933.22</v>
+        <v>2948.65</v>
       </c>
       <c r="M54" t="n">
-        <v>2947.55</v>
+        <v>2982.8</v>
       </c>
       <c r="N54" t="n">
-        <v>2961.88</v>
+        <v>3016.95</v>
       </c>
       <c r="O54" t="n">
-        <v>3010.3</v>
+        <v>3010.5</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5058,14 +5060,12 @@
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
@@ -5076,57 +5076,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2957.6</v>
+        <v>2967.9</v>
       </c>
       <c r="C55" t="n">
-        <v>2983.3</v>
+        <v>2979.3</v>
       </c>
       <c r="D55" t="n">
-        <v>2949.9</v>
+        <v>2949.5</v>
       </c>
       <c r="E55" t="n">
-        <v>2969.7</v>
+        <v>2976.6</v>
       </c>
       <c r="F55" t="n">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0023</v>
       </c>
       <c r="H55" t="n">
-        <v>33.4</v>
+        <v>29.8</v>
       </c>
       <c r="I55" t="n">
-        <v>2866.5</v>
+        <v>2916.5</v>
       </c>
       <c r="J55" t="n">
-        <v>2920.95</v>
+        <v>2937.85</v>
       </c>
       <c r="K55" t="n">
-        <v>2934.8</v>
+        <v>2953</v>
       </c>
       <c r="L55" t="n">
-        <v>2948.65</v>
+        <v>2968.15</v>
       </c>
       <c r="M55" t="n">
-        <v>2982.8</v>
+        <v>2986.4</v>
       </c>
       <c r="N55" t="n">
-        <v>3016.95</v>
+        <v>3004.65</v>
       </c>
       <c r="O55" t="n">
-        <v>3010.5</v>
+        <v>3016.7</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5134,18 +5134,18 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5160,57 +5160,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2967.9</v>
+        <v>2974.7</v>
       </c>
       <c r="C56" t="n">
-        <v>2979.3</v>
+        <v>2977.9</v>
       </c>
       <c r="D56" t="n">
-        <v>2949.5</v>
+        <v>2954.7</v>
       </c>
       <c r="E56" t="n">
-        <v>2976.6</v>
+        <v>2963.6</v>
       </c>
       <c r="F56" t="n">
-        <v>6.9</v>
+        <v>-13</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0044</v>
       </c>
       <c r="H56" t="n">
-        <v>29.8</v>
+        <v>23.2</v>
       </c>
       <c r="I56" t="n">
-        <v>2916.5</v>
+        <v>2919.7</v>
       </c>
       <c r="J56" t="n">
-        <v>2937.85</v>
+        <v>2952.9</v>
       </c>
       <c r="K56" t="n">
-        <v>2953</v>
+        <v>2961.7</v>
       </c>
       <c r="L56" t="n">
-        <v>2968.15</v>
+        <v>2970.5</v>
       </c>
       <c r="M56" t="n">
-        <v>2986.4</v>
+        <v>2991.5</v>
       </c>
       <c r="N56" t="n">
-        <v>3004.65</v>
+        <v>3012.5</v>
       </c>
       <c r="O56" t="n">
-        <v>3016.7</v>
+        <v>3009.1</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5220,12 +5220,12 @@
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5251,60 +5251,64 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2974.7</v>
+        <v>2963.1</v>
       </c>
       <c r="C57" t="n">
-        <v>2977.9</v>
+        <v>2966.2</v>
       </c>
       <c r="D57" t="n">
-        <v>2954.7</v>
+        <v>2919.4</v>
       </c>
       <c r="E57" t="n">
-        <v>2963.6</v>
+        <v>2923</v>
       </c>
       <c r="F57" t="n">
-        <v>-13</v>
+        <v>-40.6</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0137</v>
       </c>
       <c r="H57" t="n">
-        <v>23.2</v>
+        <v>46.8</v>
       </c>
       <c r="I57" t="n">
-        <v>2919.7</v>
+        <v>2931.5</v>
       </c>
       <c r="J57" t="n">
-        <v>2952.9</v>
+        <v>2939.05</v>
       </c>
       <c r="K57" t="n">
-        <v>2961.7</v>
+        <v>2952</v>
       </c>
       <c r="L57" t="n">
-        <v>2970.5</v>
+        <v>2964.95</v>
       </c>
       <c r="M57" t="n">
-        <v>2991.5</v>
+        <v>2975.2</v>
       </c>
       <c r="N57" t="n">
-        <v>3012.5</v>
+        <v>2985.45</v>
       </c>
       <c r="O57" t="n">
-        <v>3009.1</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
+        <v>3001.1</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
@@ -5326,73 +5330,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2963.1</v>
+        <v>2923.1</v>
       </c>
       <c r="C58" t="n">
-        <v>2966.2</v>
+        <v>2933.8</v>
       </c>
       <c r="D58" t="n">
-        <v>2919.4</v>
+        <v>2887.8</v>
       </c>
       <c r="E58" t="n">
-        <v>2923</v>
+        <v>2893.4</v>
       </c>
       <c r="F58" t="n">
-        <v>-40.6</v>
+        <v>-29.6</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0101</v>
       </c>
       <c r="H58" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="I58" t="n">
-        <v>2931.5</v>
+        <v>2872.6</v>
       </c>
       <c r="J58" t="n">
-        <v>2939.05</v>
+        <v>2866.3</v>
       </c>
       <c r="K58" t="n">
-        <v>2952</v>
+        <v>2899.6</v>
       </c>
       <c r="L58" t="n">
-        <v>2964.95</v>
+        <v>2932.9</v>
       </c>
       <c r="M58" t="n">
-        <v>2975.2</v>
+        <v>2946.4</v>
       </c>
       <c r="N58" t="n">
-        <v>2985.45</v>
+        <v>2959.9</v>
       </c>
       <c r="O58" t="n">
-        <v>3001.1</v>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
+        <v>3013</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
@@ -5419,50 +5415,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2923.1</v>
+        <v>2890.9</v>
       </c>
       <c r="C59" t="n">
-        <v>2933.8</v>
+        <v>2929.8</v>
       </c>
       <c r="D59" t="n">
-        <v>2887.8</v>
+        <v>2887.6</v>
       </c>
       <c r="E59" t="n">
-        <v>2893.4</v>
+        <v>2904.5</v>
       </c>
       <c r="F59" t="n">
-        <v>-29.6</v>
+        <v>11.1</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0101</v>
+        <v>0.0038</v>
       </c>
       <c r="H59" t="n">
-        <v>46</v>
+        <v>42.2</v>
       </c>
       <c r="I59" t="n">
-        <v>2872.6</v>
+        <v>2841.8</v>
       </c>
       <c r="J59" t="n">
-        <v>2866.3</v>
+        <v>2838.7</v>
       </c>
       <c r="K59" t="n">
-        <v>2899.6</v>
+        <v>2870.4</v>
       </c>
       <c r="L59" t="n">
-        <v>2932.9</v>
+        <v>2902.1</v>
       </c>
       <c r="M59" t="n">
-        <v>2946.4</v>
+        <v>2916.4</v>
       </c>
       <c r="N59" t="n">
-        <v>2959.9</v>
+        <v>2930.7</v>
       </c>
       <c r="O59" t="n">
-        <v>3013</v>
+        <v>2979.8</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5470,18 +5466,18 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5494,55 +5490,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2890.9</v>
+        <v>2892.7</v>
       </c>
       <c r="C60" t="n">
-        <v>2929.8</v>
+        <v>2913.5</v>
       </c>
       <c r="D60" t="n">
-        <v>2887.6</v>
+        <v>2884.3</v>
       </c>
       <c r="E60" t="n">
-        <v>2904.5</v>
+        <v>2894.1</v>
       </c>
       <c r="F60" t="n">
-        <v>11.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0036</v>
       </c>
       <c r="H60" t="n">
-        <v>42.2</v>
+        <v>29.2</v>
       </c>
       <c r="I60" t="n">
-        <v>2841.8</v>
+        <v>2845.4</v>
       </c>
       <c r="J60" t="n">
-        <v>2838.7</v>
+        <v>2860.2</v>
       </c>
       <c r="K60" t="n">
-        <v>2870.4</v>
+        <v>2883.4</v>
       </c>
       <c r="L60" t="n">
-        <v>2902.1</v>
+        <v>2906.6</v>
       </c>
       <c r="M60" t="n">
-        <v>2916.4</v>
+        <v>2925.6</v>
       </c>
       <c r="N60" t="n">
-        <v>2930.7</v>
+        <v>2944.6</v>
       </c>
       <c r="O60" t="n">
-        <v>2979.8</v>
+        <v>2972</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5550,18 +5550,18 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5574,59 +5574,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2892.7</v>
+        <v>2917.2</v>
       </c>
       <c r="C61" t="n">
-        <v>2913.5</v>
+        <v>2918.3</v>
       </c>
       <c r="D61" t="n">
-        <v>2884.3</v>
+        <v>2883.6</v>
       </c>
       <c r="E61" t="n">
-        <v>2894.1</v>
+        <v>2896.6</v>
       </c>
       <c r="F61" t="n">
-        <v>-10.4</v>
+        <v>2.5</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0036</v>
+        <v>0.0009</v>
       </c>
       <c r="H61" t="n">
-        <v>29.2</v>
+        <v>34.7</v>
       </c>
       <c r="I61" t="n">
-        <v>2845.4</v>
+        <v>2855.1</v>
       </c>
       <c r="J61" t="n">
-        <v>2860.2</v>
+        <v>2862.5</v>
       </c>
       <c r="K61" t="n">
-        <v>2883.4</v>
+        <v>2879.5</v>
       </c>
       <c r="L61" t="n">
-        <v>2906.6</v>
+        <v>2896.5</v>
       </c>
       <c r="M61" t="n">
-        <v>2925.6</v>
+        <v>2908.7</v>
       </c>
       <c r="N61" t="n">
-        <v>2944.6</v>
+        <v>2920.9</v>
       </c>
       <c r="O61" t="n">
-        <v>2972</v>
+        <v>2942.7</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5634,18 +5630,18 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5658,7 +5654,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -5667,25 +5667,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>2855.1</v>
+        <v>2848.9</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>2862.5</v>
+        <v>2859.73</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>2879.5</v>
+        <v>2879.25</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>2896.5</v>
+        <v>2898.78</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>2908.7</v>
+        <v>2913.95</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>2920.9</v>
+        <v>2929.13</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>2942.7</v>
+        <v>2953</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -5583,25 +5583,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2917.2</v>
+        <v>2898.5</v>
       </c>
       <c r="C61" t="n">
-        <v>2918.3</v>
+        <v>2898.9</v>
       </c>
       <c r="D61" t="n">
-        <v>2883.6</v>
+        <v>2895.7</v>
       </c>
       <c r="E61" t="n">
-        <v>2896.6</v>
+        <v>2896.2</v>
       </c>
       <c r="F61" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.0007</v>
       </c>
       <c r="H61" t="n">
-        <v>34.7</v>
+        <v>3.2</v>
       </c>
       <c r="I61" t="n">
         <v>2855.1</v>
@@ -5633,15 +5633,13 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5667,25 +5665,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>2848.9</v>
+        <v>2892.5</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>2859.73</v>
+        <v>2892.45</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>2879.25</v>
+        <v>2894.6</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>2898.78</v>
+        <v>2896.75</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>2913.95</v>
+        <v>2897.8</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>2929.13</v>
+        <v>2898.85</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>2953</v>
+        <v>2902.1</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5583,25 +5583,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2898.5</v>
+        <v>2896.4</v>
       </c>
       <c r="C61" t="n">
-        <v>2898.9</v>
+        <v>2896.5</v>
       </c>
       <c r="D61" t="n">
-        <v>2895.7</v>
+        <v>2862.7</v>
       </c>
       <c r="E61" t="n">
-        <v>2896.2</v>
+        <v>2873.1</v>
       </c>
       <c r="F61" t="n">
-        <v>2.1</v>
+        <v>-21</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0073</v>
       </c>
       <c r="H61" t="n">
-        <v>3.2</v>
+        <v>33.8</v>
       </c>
       <c r="I61" t="n">
         <v>2855.1</v>
@@ -5630,12 +5630,14 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5652,38 +5654,120 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2898.5</v>
+      </c>
+      <c r="C62" t="n">
+        <v>2903.3</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2894.8</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2898.9</v>
+      </c>
+      <c r="F62" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="H62" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I62" t="n">
+        <v>2828.9</v>
+      </c>
+      <c r="J62" t="n">
+        <v>2836.05</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2856.2</v>
+      </c>
+      <c r="L62" t="n">
+        <v>2876.35</v>
+      </c>
+      <c r="M62" t="n">
+        <v>2890</v>
+      </c>
+      <c r="N62" t="n">
+        <v>2903.65</v>
+      </c>
+      <c r="O62" t="n">
+        <v>2930.3</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I62" s="13" t="n">
-        <v>2892.5</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>2892.45</v>
-      </c>
-      <c r="K62" s="13" t="n">
-        <v>2894.6</v>
-      </c>
-      <c r="L62" s="13" t="n">
-        <v>2896.75</v>
-      </c>
-      <c r="M62" s="13" t="n">
-        <v>2897.8</v>
-      </c>
-      <c r="N62" s="13" t="n">
-        <v>2898.85</v>
-      </c>
-      <c r="O62" s="13" t="n">
-        <v>2902.1</v>
+      <c r="I63" s="13" t="n">
+        <v>2886.3</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>2890.32</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>2894.65</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>2898.97</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>2903.15</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>2907.32</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>2911.8</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -5666,22 +5666,22 @@
         <v>2898.5</v>
       </c>
       <c r="C62" t="n">
-        <v>2903.3</v>
+        <v>2903.6</v>
       </c>
       <c r="D62" t="n">
-        <v>2894.8</v>
+        <v>2892.5</v>
       </c>
       <c r="E62" t="n">
-        <v>2898.9</v>
+        <v>2900.4</v>
       </c>
       <c r="F62" t="n">
-        <v>25.8</v>
+        <v>27.3</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0095</v>
       </c>
       <c r="H62" t="n">
-        <v>8.5</v>
+        <v>11.1</v>
       </c>
       <c r="I62" t="n">
         <v>2828.9</v>
@@ -5749,25 +5749,25 @@
         </is>
       </c>
       <c r="I63" s="13" t="n">
-        <v>2886.3</v>
+        <v>2881.4</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>2890.32</v>
+        <v>2890.47</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>2894.65</v>
+        <v>2894.85</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>2898.97</v>
+        <v>2899.22</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>2903.15</v>
+        <v>2905.95</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>2907.32</v>
+        <v>2912.67</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>2911.8</v>
+        <v>2914.7</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -5666,22 +5666,22 @@
         <v>2898.5</v>
       </c>
       <c r="C62" t="n">
-        <v>2903.6</v>
+        <v>2904.7</v>
       </c>
       <c r="D62" t="n">
         <v>2892.5</v>
       </c>
       <c r="E62" t="n">
-        <v>2900.4</v>
+        <v>2903.8</v>
       </c>
       <c r="F62" t="n">
-        <v>27.3</v>
+        <v>30.7</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.0107</v>
       </c>
       <c r="H62" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="I62" t="n">
         <v>2828.9</v>
@@ -5731,16 +5731,12 @@
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W62" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
@@ -5749,25 +5745,25 @@
         </is>
       </c>
       <c r="I63" s="13" t="n">
-        <v>2881.4</v>
+        <v>2880.3</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>2890.47</v>
+        <v>2894.2</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>2894.85</v>
+        <v>2897.7</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>2899.22</v>
+        <v>2901.2</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>2905.95</v>
+        <v>2909.9</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>2912.67</v>
+        <v>2918.6</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>2914.7</v>
+        <v>2916.9</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -5672,13 +5672,13 @@
         <v>2892.5</v>
       </c>
       <c r="E62" t="n">
-        <v>2903.8</v>
+        <v>2903.6</v>
       </c>
       <c r="F62" t="n">
-        <v>30.7</v>
+        <v>30.5</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0107</v>
+        <v>0.0106</v>
       </c>
       <c r="H62" t="n">
         <v>12.2</v>
@@ -5731,12 +5731,16 @@
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="W62" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
@@ -5748,19 +5752,19 @@
         <v>2880.3</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>2894.2</v>
+        <v>2893.9</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>2897.7</v>
+        <v>2897.5</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>2901.2</v>
+        <v>2901.1</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>2909.9</v>
+        <v>2909.7</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>2918.6</v>
+        <v>2918.3</v>
       </c>
       <c r="O63" s="13" t="n">
         <v>2916.9</v>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -109,14 +109,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,156 +641,156 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2989.9</v>
+        <v>3022.4</v>
       </c>
       <c r="C2" t="n">
-        <v>3039</v>
+        <v>3028.4</v>
       </c>
       <c r="D2" t="n">
-        <v>2970.8</v>
+        <v>2965.2</v>
       </c>
       <c r="E2" t="n">
-        <v>3024.1</v>
+        <v>2998.2</v>
       </c>
       <c r="F2" t="n">
-        <v>63.37</v>
+        <v>-25.9</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0214</v>
+        <v>-0.0086</v>
       </c>
       <c r="H2" t="n">
-        <v>68.2</v>
+        <v>63.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2877.7</v>
+        <v>2902.6</v>
       </c>
       <c r="J2" t="n">
-        <v>2919.47</v>
+        <v>2965.5</v>
       </c>
       <c r="K2" t="n">
-        <v>2937.08</v>
+        <v>2990</v>
       </c>
       <c r="L2" t="n">
-        <v>2954.69</v>
+        <v>3014.5</v>
       </c>
       <c r="M2" t="n">
-        <v>2984.38</v>
+        <v>3058.2</v>
       </c>
       <c r="N2" t="n">
-        <v>3014.07</v>
+        <v>3101.9</v>
       </c>
       <c r="O2" t="n">
-        <v>3019.6</v>
+        <v>3107.2</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3022.4</v>
+        <v>2998.4</v>
       </c>
       <c r="C3" t="n">
-        <v>3028.4</v>
+        <v>3041.4</v>
       </c>
       <c r="D3" t="n">
-        <v>2965.2</v>
+        <v>2987.2</v>
       </c>
       <c r="E3" t="n">
-        <v>2998.2</v>
+        <v>3013.5</v>
       </c>
       <c r="F3" t="n">
-        <v>-25.9</v>
+        <v>15.3</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0051</v>
       </c>
       <c r="H3" t="n">
-        <v>63.2</v>
+        <v>54.2</v>
       </c>
       <c r="I3" t="n">
-        <v>2902.6</v>
+        <v>2902</v>
       </c>
       <c r="J3" t="n">
-        <v>2965.5</v>
+        <v>2935.7</v>
       </c>
       <c r="K3" t="n">
-        <v>2990</v>
+        <v>2966.6</v>
       </c>
       <c r="L3" t="n">
-        <v>3014.5</v>
+        <v>2997.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3058.2</v>
+        <v>3029.8</v>
       </c>
       <c r="N3" t="n">
-        <v>3101.9</v>
+        <v>3062.1</v>
       </c>
       <c r="O3" t="n">
-        <v>3107.2</v>
+        <v>3091.6</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
@@ -802,59 +802,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2998.4</v>
+        <v>3023.7</v>
       </c>
       <c r="C4" t="n">
-        <v>3041.4</v>
+        <v>3062.4</v>
       </c>
       <c r="D4" t="n">
-        <v>2987.2</v>
+        <v>3010.5</v>
       </c>
       <c r="E4" t="n">
-        <v>3013.5</v>
+        <v>3030.7</v>
       </c>
       <c r="F4" t="n">
-        <v>15.3</v>
+        <v>17.2</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0057</v>
       </c>
       <c r="H4" t="n">
-        <v>54.2</v>
+        <v>51.9</v>
       </c>
       <c r="I4" t="n">
-        <v>2902</v>
+        <v>2933</v>
       </c>
       <c r="J4" t="n">
-        <v>2935.7</v>
+        <v>2958.9</v>
       </c>
       <c r="K4" t="n">
-        <v>2966.6</v>
+        <v>2986.4</v>
       </c>
       <c r="L4" t="n">
-        <v>2997.5</v>
+        <v>3013.9</v>
       </c>
       <c r="M4" t="n">
-        <v>3029.8</v>
+        <v>3040.6</v>
       </c>
       <c r="N4" t="n">
-        <v>3062.1</v>
+        <v>3067.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3091.6</v>
+        <v>3095.6</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -865,14 +861,14 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U4" s="8" t="n">
@@ -891,50 +887,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3023.7</v>
+        <v>3034.7</v>
       </c>
       <c r="C5" t="n">
-        <v>3062.4</v>
+        <v>3045.7</v>
       </c>
       <c r="D5" t="n">
-        <v>3010.5</v>
+        <v>2999.6</v>
       </c>
       <c r="E5" t="n">
-        <v>3030.7</v>
+        <v>3022.6</v>
       </c>
       <c r="F5" t="n">
-        <v>17.2</v>
+        <v>-8.1</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.0027</v>
       </c>
       <c r="H5" t="n">
-        <v>51.9</v>
+        <v>46.1</v>
       </c>
       <c r="I5" t="n">
-        <v>2933</v>
+        <v>2958.6</v>
       </c>
       <c r="J5" t="n">
-        <v>2958.9</v>
+        <v>2975.93</v>
       </c>
       <c r="K5" t="n">
-        <v>2986.4</v>
+        <v>3004.75</v>
       </c>
       <c r="L5" t="n">
-        <v>3013.9</v>
+        <v>3033.57</v>
       </c>
       <c r="M5" t="n">
-        <v>3040.6</v>
+        <v>3056.65</v>
       </c>
       <c r="N5" t="n">
-        <v>3067.3</v>
+        <v>3079.72</v>
       </c>
       <c r="O5" t="n">
-        <v>3095.6</v>
+        <v>3114.3</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -942,18 +938,18 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -966,55 +962,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3034.7</v>
+        <v>3020.9</v>
       </c>
       <c r="C6" t="n">
-        <v>3045.7</v>
+        <v>3044.9</v>
       </c>
       <c r="D6" t="n">
-        <v>2999.6</v>
+        <v>2987.8</v>
       </c>
       <c r="E6" t="n">
-        <v>3022.6</v>
+        <v>3030.6</v>
       </c>
       <c r="F6" t="n">
-        <v>-8.1</v>
+        <v>8</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0026</v>
       </c>
       <c r="H6" t="n">
-        <v>46.1</v>
+        <v>57.1</v>
       </c>
       <c r="I6" t="n">
-        <v>2958.6</v>
+        <v>2953.5</v>
       </c>
       <c r="J6" t="n">
-        <v>2975.93</v>
+        <v>2976.48</v>
       </c>
       <c r="K6" t="n">
-        <v>3004.75</v>
+        <v>2999.55</v>
       </c>
       <c r="L6" t="n">
-        <v>3033.57</v>
+        <v>3022.63</v>
       </c>
       <c r="M6" t="n">
-        <v>3056.65</v>
+        <v>3045.65</v>
       </c>
       <c r="N6" t="n">
-        <v>3079.72</v>
+        <v>3068.67</v>
       </c>
       <c r="O6" t="n">
-        <v>3114.3</v>
+        <v>3091.8</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1048,57 +1048,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3020.9</v>
+        <v>3026.1</v>
       </c>
       <c r="C7" t="n">
-        <v>3044.9</v>
+        <v>3050.6</v>
       </c>
       <c r="D7" t="n">
-        <v>2987.8</v>
+        <v>3015.1</v>
       </c>
       <c r="E7" t="n">
-        <v>3030.6</v>
+        <v>3045.6</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0049</v>
       </c>
       <c r="H7" t="n">
-        <v>57.1</v>
+        <v>35.5</v>
       </c>
       <c r="I7" t="n">
-        <v>2953.5</v>
+        <v>2930.7</v>
       </c>
       <c r="J7" t="n">
-        <v>2976.48</v>
+        <v>2980.63</v>
       </c>
       <c r="K7" t="n">
-        <v>2999.55</v>
+        <v>3002.05</v>
       </c>
       <c r="L7" t="n">
-        <v>3022.63</v>
+        <v>3023.48</v>
       </c>
       <c r="M7" t="n">
-        <v>3045.65</v>
+        <v>3059.15</v>
       </c>
       <c r="N7" t="n">
-        <v>3068.67</v>
+        <v>3094.83</v>
       </c>
       <c r="O7" t="n">
-        <v>3091.8</v>
+        <v>3102</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1106,18 +1106,18 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1130,59 +1130,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3026.1</v>
+        <v>3040</v>
       </c>
       <c r="C8" t="n">
-        <v>3050.6</v>
+        <v>3068.4</v>
       </c>
       <c r="D8" t="n">
-        <v>3015.1</v>
+        <v>3023.7</v>
       </c>
       <c r="E8" t="n">
-        <v>3045.6</v>
+        <v>3035.1</v>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>-10.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.0034</v>
       </c>
       <c r="H8" t="n">
-        <v>35.5</v>
+        <v>44.7</v>
       </c>
       <c r="I8" t="n">
-        <v>2930.7</v>
+        <v>2979.6</v>
       </c>
       <c r="J8" t="n">
-        <v>2980.63</v>
+        <v>3016.48</v>
       </c>
       <c r="K8" t="n">
-        <v>3002.05</v>
+        <v>3027.85</v>
       </c>
       <c r="L8" t="n">
-        <v>3023.48</v>
+        <v>3039.23</v>
       </c>
       <c r="M8" t="n">
-        <v>3059.15</v>
+        <v>3063.35</v>
       </c>
       <c r="N8" t="n">
-        <v>3094.83</v>
+        <v>3087.48</v>
       </c>
       <c r="O8" t="n">
-        <v>3102</v>
+        <v>3086.1</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1190,17 +1186,19 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U8" s="8" t="n">
@@ -1214,55 +1212,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3040</v>
+        <v>3030.9</v>
       </c>
       <c r="C9" t="n">
-        <v>3068.4</v>
+        <v>3062.4</v>
       </c>
       <c r="D9" t="n">
-        <v>3023.7</v>
+        <v>2988.5</v>
       </c>
       <c r="E9" t="n">
-        <v>3035.1</v>
+        <v>3014.2</v>
       </c>
       <c r="F9" t="n">
-        <v>-10.5</v>
+        <v>-20.9</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0069</v>
       </c>
       <c r="H9" t="n">
-        <v>44.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>2979.6</v>
+        <v>2979</v>
       </c>
       <c r="J9" t="n">
-        <v>3016.48</v>
+        <v>2984.93</v>
       </c>
       <c r="K9" t="n">
-        <v>3027.85</v>
+        <v>3012.75</v>
       </c>
       <c r="L9" t="n">
-        <v>3039.23</v>
+        <v>3040.58</v>
       </c>
       <c r="M9" t="n">
-        <v>3063.35</v>
+        <v>3057.45</v>
       </c>
       <c r="N9" t="n">
-        <v>3087.48</v>
+        <v>3074.33</v>
       </c>
       <c r="O9" t="n">
-        <v>3086.1</v>
+        <v>3113.1</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1272,19 +1274,19 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1298,57 +1300,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3030.9</v>
+        <v>3019.7</v>
       </c>
       <c r="C10" t="n">
-        <v>3062.4</v>
+        <v>3042.1</v>
       </c>
       <c r="D10" t="n">
-        <v>2988.5</v>
+        <v>3006.7</v>
       </c>
       <c r="E10" t="n">
-        <v>3014.2</v>
+        <v>3027</v>
       </c>
       <c r="F10" t="n">
-        <v>-20.9</v>
+        <v>12.8</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0042</v>
       </c>
       <c r="H10" t="n">
-        <v>73.90000000000001</v>
+        <v>35.4</v>
       </c>
       <c r="I10" t="n">
-        <v>2979</v>
+        <v>2914.6</v>
       </c>
       <c r="J10" t="n">
-        <v>2984.93</v>
+        <v>2934.68</v>
       </c>
       <c r="K10" t="n">
-        <v>3012.75</v>
+        <v>2977.25</v>
       </c>
       <c r="L10" t="n">
-        <v>3040.58</v>
+        <v>3019.82</v>
       </c>
       <c r="M10" t="n">
-        <v>3057.45</v>
+        <v>3051.15</v>
       </c>
       <c r="N10" t="n">
-        <v>3074.33</v>
+        <v>3082.47</v>
       </c>
       <c r="O10" t="n">
-        <v>3113.1</v>
+        <v>3136.3</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1356,20 +1358,16 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1384,70 +1382,74 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3019.7</v>
+        <v>3033.4</v>
       </c>
       <c r="C11" t="n">
-        <v>3042.1</v>
+        <v>3042.6</v>
       </c>
       <c r="D11" t="n">
-        <v>3006.7</v>
+        <v>2988.8</v>
       </c>
       <c r="E11" t="n">
-        <v>3027</v>
+        <v>2998.8</v>
       </c>
       <c r="F11" t="n">
-        <v>12.8</v>
+        <v>-28.2</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>35.4</v>
+        <v>53.8</v>
       </c>
       <c r="I11" t="n">
-        <v>2914.6</v>
+        <v>2971.3</v>
       </c>
       <c r="J11" t="n">
-        <v>2934.68</v>
+        <v>2992.9</v>
       </c>
       <c r="K11" t="n">
-        <v>2977.25</v>
+        <v>3009.3</v>
       </c>
       <c r="L11" t="n">
-        <v>3019.82</v>
+        <v>3025.7</v>
       </c>
       <c r="M11" t="n">
-        <v>3051.15</v>
+        <v>3044.7</v>
       </c>
       <c r="N11" t="n">
-        <v>3082.47</v>
+        <v>3063.7</v>
       </c>
       <c r="O11" t="n">
-        <v>3136.3</v>
+        <v>3077.5</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1466,72 +1468,70 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3033.4</v>
+        <v>2994.3</v>
       </c>
       <c r="C12" t="n">
-        <v>3042.6</v>
+        <v>3004.3</v>
       </c>
       <c r="D12" t="n">
-        <v>2988.8</v>
+        <v>2943.4</v>
       </c>
       <c r="E12" t="n">
-        <v>2998.8</v>
+        <v>2971.5</v>
       </c>
       <c r="F12" t="n">
-        <v>-28.2</v>
+        <v>-27.3</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0091</v>
       </c>
       <c r="H12" t="n">
-        <v>53.8</v>
+        <v>60.9</v>
       </c>
       <c r="I12" t="n">
-        <v>2971.3</v>
+        <v>2935</v>
       </c>
       <c r="J12" t="n">
-        <v>2992.9</v>
+        <v>2936.55</v>
       </c>
       <c r="K12" t="n">
-        <v>3009.3</v>
+        <v>2971.9</v>
       </c>
       <c r="L12" t="n">
+        <v>3007.25</v>
+      </c>
+      <c r="M12" t="n">
         <v>3025.7</v>
       </c>
-      <c r="M12" t="n">
-        <v>3044.7</v>
-      </c>
       <c r="N12" t="n">
-        <v>3063.7</v>
+        <v>3044.15</v>
       </c>
       <c r="O12" t="n">
-        <v>3077.5</v>
+        <v>3096.4</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1552,57 +1552,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2994.3</v>
+        <v>2965.8</v>
       </c>
       <c r="C13" t="n">
-        <v>3004.3</v>
+        <v>3014.9</v>
       </c>
       <c r="D13" t="n">
-        <v>2943.4</v>
+        <v>2964.3</v>
       </c>
       <c r="E13" t="n">
-        <v>2971.5</v>
+        <v>3008.4</v>
       </c>
       <c r="F13" t="n">
-        <v>-27.3</v>
+        <v>36.9</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0091</v>
+        <v>0.0124</v>
       </c>
       <c r="H13" t="n">
-        <v>60.9</v>
+        <v>50.6</v>
       </c>
       <c r="I13" t="n">
-        <v>2935</v>
+        <v>2882.5</v>
       </c>
       <c r="J13" t="n">
-        <v>2936.55</v>
+        <v>2909.42</v>
       </c>
       <c r="K13" t="n">
-        <v>2971.9</v>
+        <v>2941.05</v>
       </c>
       <c r="L13" t="n">
-        <v>3007.25</v>
+        <v>2972.67</v>
       </c>
       <c r="M13" t="n">
-        <v>3025.7</v>
+        <v>3001.95</v>
       </c>
       <c r="N13" t="n">
-        <v>3044.15</v>
+        <v>3031.23</v>
       </c>
       <c r="O13" t="n">
-        <v>3096.4</v>
+        <v>3065.2</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1610,19 +1610,19 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1634,59 +1634,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2965.8</v>
+        <v>3008.1</v>
       </c>
       <c r="C14" t="n">
-        <v>3014.9</v>
+        <v>3019.5</v>
       </c>
       <c r="D14" t="n">
-        <v>2964.3</v>
+        <v>2970.8</v>
       </c>
       <c r="E14" t="n">
-        <v>3008.4</v>
+        <v>2994</v>
       </c>
       <c r="F14" t="n">
-        <v>36.9</v>
+        <v>-14.4</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0048</v>
       </c>
       <c r="H14" t="n">
-        <v>50.6</v>
+        <v>48.7</v>
       </c>
       <c r="I14" t="n">
-        <v>2882.5</v>
+        <v>2913.7</v>
       </c>
       <c r="J14" t="n">
-        <v>2909.42</v>
+        <v>2967.2</v>
       </c>
       <c r="K14" t="n">
-        <v>2941.05</v>
+        <v>2983.1</v>
       </c>
       <c r="L14" t="n">
-        <v>2972.67</v>
+        <v>2999</v>
       </c>
       <c r="M14" t="n">
-        <v>3001.95</v>
+        <v>3033.7</v>
       </c>
       <c r="N14" t="n">
-        <v>3031.23</v>
+        <v>3068.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3065.2</v>
+        <v>3065.5</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1694,18 +1690,18 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1718,55 +1714,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3008.1</v>
+        <v>2984.7</v>
       </c>
       <c r="C15" t="n">
-        <v>3019.5</v>
+        <v>2995.8</v>
       </c>
       <c r="D15" t="n">
-        <v>2970.8</v>
+        <v>2961.8</v>
       </c>
       <c r="E15" t="n">
-        <v>2994</v>
+        <v>2970.4</v>
       </c>
       <c r="F15" t="n">
-        <v>-14.4</v>
+        <v>-23.6</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>48.7</v>
+        <v>34</v>
       </c>
       <c r="I15" t="n">
-        <v>2913.7</v>
+        <v>2922.1</v>
       </c>
       <c r="J15" t="n">
-        <v>2967.2</v>
+        <v>2944.73</v>
       </c>
       <c r="K15" t="n">
-        <v>2983.1</v>
+        <v>2969.65</v>
       </c>
       <c r="L15" t="n">
-        <v>2999</v>
+        <v>2994.58</v>
       </c>
       <c r="M15" t="n">
-        <v>3033.7</v>
+        <v>3018.35</v>
       </c>
       <c r="N15" t="n">
-        <v>3068.4</v>
+        <v>3042.12</v>
       </c>
       <c r="O15" t="n">
-        <v>3065.5</v>
+        <v>3068.2</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1776,12 +1776,12 @@
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1800,57 +1800,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2984.7</v>
+        <v>2967.2</v>
       </c>
       <c r="C16" t="n">
-        <v>2995.8</v>
+        <v>3029.8</v>
       </c>
       <c r="D16" t="n">
-        <v>2961.8</v>
+        <v>2956.2</v>
       </c>
       <c r="E16" t="n">
-        <v>2970.4</v>
+        <v>2979.9</v>
       </c>
       <c r="F16" t="n">
-        <v>-23.6</v>
+        <v>9.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H16" t="n">
-        <v>34</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>2922.1</v>
+        <v>2927.8</v>
       </c>
       <c r="J16" t="n">
-        <v>2944.73</v>
+        <v>2932.2</v>
       </c>
       <c r="K16" t="n">
-        <v>2969.65</v>
+        <v>2953.4</v>
       </c>
       <c r="L16" t="n">
-        <v>2994.58</v>
+        <v>2974.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3018.35</v>
+        <v>2987.4</v>
       </c>
       <c r="N16" t="n">
-        <v>3042.12</v>
+        <v>3000.2</v>
       </c>
       <c r="O16" t="n">
-        <v>3068.2</v>
+        <v>3029.8</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1858,24 +1858,28 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R16" s="6" t="n">
+        <v/>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
@@ -1884,57 +1888,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2967.2</v>
+        <v>2981.2</v>
       </c>
       <c r="C17" t="n">
-        <v>3029.8</v>
+        <v>3006.1</v>
       </c>
       <c r="D17" t="n">
-        <v>2956.2</v>
+        <v>2974.4</v>
       </c>
       <c r="E17" t="n">
-        <v>2979.9</v>
+        <v>2991.8</v>
       </c>
       <c r="F17" t="n">
-        <v>9.5</v>
+        <v>11.9</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.004</v>
       </c>
       <c r="H17" t="n">
-        <v>73.59999999999999</v>
+        <v>31.7</v>
       </c>
       <c r="I17" t="n">
-        <v>2927.8</v>
+        <v>2882.6</v>
       </c>
       <c r="J17" t="n">
-        <v>2932.2</v>
+        <v>2899.75</v>
       </c>
       <c r="K17" t="n">
-        <v>2953.4</v>
+        <v>2943.1</v>
       </c>
       <c r="L17" t="n">
-        <v>2974.6</v>
+        <v>2986.45</v>
       </c>
       <c r="M17" t="n">
-        <v>2987.4</v>
+        <v>3016.7</v>
       </c>
       <c r="N17" t="n">
-        <v>3000.2</v>
+        <v>3046.95</v>
       </c>
       <c r="O17" t="n">
-        <v>3029.8</v>
+        <v>3103.4</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1945,25 +1949,19 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
@@ -1979,50 +1977,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2981.2</v>
+        <v>2995.3</v>
       </c>
       <c r="C18" t="n">
-        <v>3006.1</v>
+        <v>3012.8</v>
       </c>
       <c r="D18" t="n">
-        <v>2974.4</v>
+        <v>2972.7</v>
       </c>
       <c r="E18" t="n">
-        <v>2991.8</v>
+        <v>2990.7</v>
       </c>
       <c r="F18" t="n">
-        <v>11.9</v>
+        <v>-1.1</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0004</v>
       </c>
       <c r="H18" t="n">
-        <v>31.7</v>
+        <v>40.1</v>
       </c>
       <c r="I18" t="n">
-        <v>2882.6</v>
+        <v>2942.7</v>
       </c>
       <c r="J18" t="n">
-        <v>2899.75</v>
+        <v>2960.87</v>
       </c>
       <c r="K18" t="n">
-        <v>2943.1</v>
+        <v>2975.95</v>
       </c>
       <c r="L18" t="n">
-        <v>2986.45</v>
+        <v>2991.03</v>
       </c>
       <c r="M18" t="n">
-        <v>3016.7</v>
+        <v>3007.65</v>
       </c>
       <c r="N18" t="n">
-        <v>3046.95</v>
+        <v>3024.28</v>
       </c>
       <c r="O18" t="n">
-        <v>3103.4</v>
+        <v>3037.8</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2030,16 +2028,20 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2054,78 +2056,78 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2995.3</v>
+        <v>2991.7</v>
       </c>
       <c r="C19" t="n">
-        <v>3012.8</v>
+        <v>2994.8</v>
       </c>
       <c r="D19" t="n">
-        <v>2972.7</v>
+        <v>2949.3</v>
       </c>
       <c r="E19" t="n">
-        <v>2990.7</v>
+        <v>2973.5</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1</v>
+        <v>-17.2</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0058</v>
       </c>
       <c r="H19" t="n">
-        <v>40.1</v>
+        <v>45.5</v>
       </c>
       <c r="I19" t="n">
-        <v>2942.7</v>
+        <v>2932.6</v>
       </c>
       <c r="J19" t="n">
-        <v>2960.87</v>
+        <v>2949.57</v>
       </c>
       <c r="K19" t="n">
-        <v>2975.95</v>
+        <v>2970.65</v>
       </c>
       <c r="L19" t="n">
-        <v>2991.03</v>
+        <v>2991.72</v>
       </c>
       <c r="M19" t="n">
-        <v>3007.65</v>
+        <v>3010.75</v>
       </c>
       <c r="N19" t="n">
-        <v>3024.28</v>
+        <v>3029.78</v>
       </c>
       <c r="O19" t="n">
-        <v>3037.8</v>
+        <v>3052.9</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2140,79 +2142,79 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2991.7</v>
+        <v>2964.5</v>
       </c>
       <c r="C20" t="n">
-        <v>2994.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D20" t="n">
-        <v>2949.3</v>
+        <v>2952.7</v>
       </c>
       <c r="E20" t="n">
-        <v>2973.5</v>
+        <v>2955.2</v>
       </c>
       <c r="F20" t="n">
-        <v>-17.2</v>
+        <v>-18.3</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0062</v>
       </c>
       <c r="H20" t="n">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="I20" t="n">
-        <v>2932.6</v>
+        <v>2903.8</v>
       </c>
       <c r="J20" t="n">
-        <v>2949.57</v>
+        <v>2928.72</v>
       </c>
       <c r="K20" t="n">
-        <v>2970.65</v>
+        <v>2950.75</v>
       </c>
       <c r="L20" t="n">
-        <v>2991.72</v>
+        <v>2972.78</v>
       </c>
       <c r="M20" t="n">
-        <v>3010.75</v>
+        <v>2996.25</v>
       </c>
       <c r="N20" t="n">
-        <v>3029.78</v>
+        <v>3019.72</v>
       </c>
       <c r="O20" t="n">
-        <v>3052.9</v>
+        <v>3040.3</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
@@ -2226,57 +2228,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2964.5</v>
+        <v>2955.8</v>
       </c>
       <c r="C21" t="n">
-        <v>2998.7</v>
+        <v>2999.8</v>
       </c>
       <c r="D21" t="n">
-        <v>2952.7</v>
+        <v>2951.1</v>
       </c>
       <c r="E21" t="n">
-        <v>2955.2</v>
+        <v>2997</v>
       </c>
       <c r="F21" t="n">
-        <v>-18.3</v>
+        <v>41.8</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0141</v>
       </c>
       <c r="H21" t="n">
-        <v>46</v>
+        <v>48.7</v>
       </c>
       <c r="I21" t="n">
-        <v>2903.8</v>
+        <v>2906.7</v>
       </c>
       <c r="J21" t="n">
-        <v>2928.72</v>
+        <v>2898.95</v>
       </c>
       <c r="K21" t="n">
-        <v>2950.75</v>
+        <v>2932.2</v>
       </c>
       <c r="L21" t="n">
-        <v>2972.78</v>
+        <v>2965.45</v>
       </c>
       <c r="M21" t="n">
-        <v>2996.25</v>
+        <v>2978.2</v>
       </c>
       <c r="N21" t="n">
-        <v>3019.72</v>
+        <v>2990.95</v>
       </c>
       <c r="O21" t="n">
-        <v>3040.3</v>
+        <v>3044.7</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2284,23 +2286,23 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2319,50 +2321,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2955.8</v>
+        <v>2997</v>
       </c>
       <c r="C22" t="n">
-        <v>2999.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D22" t="n">
-        <v>2951.1</v>
+        <v>2965.5</v>
       </c>
       <c r="E22" t="n">
-        <v>2997</v>
+        <v>2969.8</v>
       </c>
       <c r="F22" t="n">
-        <v>41.8</v>
+        <v>-27.2</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0141</v>
+        <v>-0.0091</v>
       </c>
       <c r="H22" t="n">
-        <v>48.7</v>
+        <v>33.2</v>
       </c>
       <c r="I22" t="n">
-        <v>2906.7</v>
+        <v>2902.4</v>
       </c>
       <c r="J22" t="n">
-        <v>2898.95</v>
+        <v>2959.08</v>
       </c>
       <c r="K22" t="n">
-        <v>2932.2</v>
+        <v>2972.65</v>
       </c>
       <c r="L22" t="n">
-        <v>2965.45</v>
+        <v>2986.23</v>
       </c>
       <c r="M22" t="n">
-        <v>2978.2</v>
+        <v>3021.35</v>
       </c>
       <c r="N22" t="n">
-        <v>2990.95</v>
+        <v>3056.47</v>
       </c>
       <c r="O22" t="n">
-        <v>3044.7</v>
+        <v>3048.5</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2370,23 +2372,21 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2398,60 +2398,62 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2997</v>
+        <v>2974.6</v>
       </c>
       <c r="C23" t="n">
-        <v>2998.7</v>
+        <v>2979</v>
       </c>
       <c r="D23" t="n">
-        <v>2965.5</v>
+        <v>2932.1</v>
       </c>
       <c r="E23" t="n">
-        <v>2969.8</v>
+        <v>2951.7</v>
       </c>
       <c r="F23" t="n">
-        <v>-27.2</v>
+        <v>-18.1</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0091</v>
+        <v>-0.0061</v>
       </c>
       <c r="H23" t="n">
-        <v>33.2</v>
+        <v>46.9</v>
       </c>
       <c r="I23" t="n">
-        <v>2902.4</v>
+        <v>2932.3</v>
       </c>
       <c r="J23" t="n">
-        <v>2959.08</v>
+        <v>2930.45</v>
       </c>
       <c r="K23" t="n">
-        <v>2972.65</v>
+        <v>2953.2</v>
       </c>
       <c r="L23" t="n">
-        <v>2986.23</v>
+        <v>2975.95</v>
       </c>
       <c r="M23" t="n">
-        <v>3021.35</v>
+        <v>2986.4</v>
       </c>
       <c r="N23" t="n">
-        <v>3056.47</v>
+        <v>2996.85</v>
       </c>
       <c r="O23" t="n">
-        <v>3048.5</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
+        <v>3031.9</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q23" s="6" t="n">
         <v/>
@@ -2461,7 +2463,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2482,74 +2484,70 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2974.6</v>
+        <v>2948.5</v>
       </c>
       <c r="C24" t="n">
-        <v>2979</v>
+        <v>2969.7</v>
       </c>
       <c r="D24" t="n">
-        <v>2932.1</v>
+        <v>2934.5</v>
       </c>
       <c r="E24" t="n">
-        <v>2951.7</v>
+        <v>2941.3</v>
       </c>
       <c r="F24" t="n">
-        <v>-18.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0035</v>
       </c>
       <c r="H24" t="n">
-        <v>46.9</v>
+        <v>35.2</v>
       </c>
       <c r="I24" t="n">
-        <v>2932.3</v>
+        <v>2885.2</v>
       </c>
       <c r="J24" t="n">
-        <v>2930.45</v>
+        <v>2902.88</v>
       </c>
       <c r="K24" t="n">
-        <v>2953.2</v>
+        <v>2928.25</v>
       </c>
       <c r="L24" t="n">
-        <v>2975.95</v>
+        <v>2953.62</v>
       </c>
       <c r="M24" t="n">
-        <v>2986.4</v>
+        <v>2975.15</v>
       </c>
       <c r="N24" t="n">
-        <v>2996.85</v>
+        <v>2996.67</v>
       </c>
       <c r="O24" t="n">
-        <v>3031.9</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3025.9</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
       </c>
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2568,57 +2566,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2948.5</v>
+        <v>2955.5</v>
       </c>
       <c r="C25" t="n">
-        <v>2969.7</v>
+        <v>2985.9</v>
       </c>
       <c r="D25" t="n">
-        <v>2934.5</v>
+        <v>2941.2</v>
       </c>
       <c r="E25" t="n">
-        <v>2941.3</v>
+        <v>2960</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.4</v>
+        <v>18.7</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0064</v>
       </c>
       <c r="H25" t="n">
-        <v>35.2</v>
+        <v>44.7</v>
       </c>
       <c r="I25" t="n">
-        <v>2885.2</v>
+        <v>2899.3</v>
       </c>
       <c r="J25" t="n">
-        <v>2902.88</v>
+        <v>2900.7</v>
       </c>
       <c r="K25" t="n">
-        <v>2928.25</v>
+        <v>2923.7</v>
       </c>
       <c r="L25" t="n">
-        <v>2953.62</v>
+        <v>2946.7</v>
       </c>
       <c r="M25" t="n">
-        <v>2975.15</v>
+        <v>2958.9</v>
       </c>
       <c r="N25" t="n">
-        <v>2996.67</v>
+        <v>2971.1</v>
       </c>
       <c r="O25" t="n">
-        <v>3025.9</v>
+        <v>3004.9</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2631,14 +2629,18 @@
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2648,59 +2650,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2955.5</v>
+        <v>2961.5</v>
       </c>
       <c r="C26" t="n">
-        <v>2985.9</v>
+        <v>2968.3</v>
       </c>
       <c r="D26" t="n">
-        <v>2941.2</v>
+        <v>2933.4</v>
       </c>
       <c r="E26" t="n">
-        <v>2960</v>
+        <v>2964.5</v>
       </c>
       <c r="F26" t="n">
-        <v>18.7</v>
+        <v>4.5</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0015</v>
       </c>
       <c r="H26" t="n">
-        <v>44.7</v>
+        <v>34.9</v>
       </c>
       <c r="I26" t="n">
-        <v>2899.3</v>
+        <v>2896.5</v>
       </c>
       <c r="J26" t="n">
-        <v>2900.7</v>
+        <v>2913.53</v>
       </c>
       <c r="K26" t="n">
-        <v>2923.7</v>
+        <v>2937.65</v>
       </c>
       <c r="L26" t="n">
-        <v>2946.7</v>
+        <v>2961.77</v>
       </c>
       <c r="M26" t="n">
-        <v>2958.9</v>
+        <v>2982.35</v>
       </c>
       <c r="N26" t="n">
-        <v>2971.1</v>
+        <v>3002.92</v>
       </c>
       <c r="O26" t="n">
-        <v>3004.9</v>
+        <v>3030.6</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2708,24 +2706,22 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
@@ -2734,61 +2730,69 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2961.5</v>
+        <v>2966.9</v>
       </c>
       <c r="C27" t="n">
-        <v>2968.3</v>
+        <v>2978.3</v>
       </c>
       <c r="D27" t="n">
-        <v>2933.4</v>
+        <v>2902.3</v>
       </c>
       <c r="E27" t="n">
-        <v>2964.5</v>
+        <v>2915.4</v>
       </c>
       <c r="F27" t="n">
-        <v>4.5</v>
+        <v>-49.1</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0166</v>
       </c>
       <c r="H27" t="n">
-        <v>34.9</v>
+        <v>76</v>
       </c>
       <c r="I27" t="n">
-        <v>2896.5</v>
+        <v>2898.5</v>
       </c>
       <c r="J27" t="n">
-        <v>2913.53</v>
+        <v>2936.42</v>
       </c>
       <c r="K27" t="n">
-        <v>2937.65</v>
+        <v>2947.05</v>
       </c>
       <c r="L27" t="n">
-        <v>2961.77</v>
+        <v>2957.67</v>
       </c>
       <c r="M27" t="n">
-        <v>2982.35</v>
+        <v>2981.95</v>
       </c>
       <c r="N27" t="n">
-        <v>3002.92</v>
+        <v>3006.23</v>
       </c>
       <c r="O27" t="n">
-        <v>3030.6</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
+        <v>3003.2</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
@@ -2797,7 +2801,7 @@
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2809,88 +2813,84 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W27" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2966.9</v>
+        <v>2906.6</v>
       </c>
       <c r="C28" t="n">
-        <v>2978.3</v>
+        <v>2957.9</v>
       </c>
       <c r="D28" t="n">
-        <v>2902.3</v>
+        <v>2905.6</v>
       </c>
       <c r="E28" t="n">
-        <v>2915.4</v>
+        <v>2954.3</v>
       </c>
       <c r="F28" t="n">
-        <v>-49.1</v>
+        <v>38.9</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0166</v>
+        <v>0.0133</v>
       </c>
       <c r="H28" t="n">
-        <v>76</v>
+        <v>52.3</v>
       </c>
       <c r="I28" t="n">
-        <v>2898.5</v>
+        <v>2826.3</v>
       </c>
       <c r="J28" t="n">
-        <v>2936.42</v>
+        <v>2826.95</v>
       </c>
       <c r="K28" t="n">
-        <v>2947.05</v>
+        <v>2877.4</v>
       </c>
       <c r="L28" t="n">
-        <v>2957.67</v>
+        <v>2927.85</v>
       </c>
       <c r="M28" t="n">
-        <v>2981.95</v>
+        <v>2953.4</v>
       </c>
       <c r="N28" t="n">
-        <v>3006.23</v>
+        <v>2978.95</v>
       </c>
       <c r="O28" t="n">
-        <v>3003.2</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
+        <v>3054.3</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
       <c r="U28" s="8" t="n">
         <v/>
       </c>
@@ -2904,76 +2904,78 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2906.6</v>
+        <v>2954</v>
       </c>
       <c r="C29" t="n">
-        <v>2957.9</v>
+        <v>2976.3</v>
       </c>
       <c r="D29" t="n">
-        <v>2905.6</v>
+        <v>2905.3</v>
       </c>
       <c r="E29" t="n">
-        <v>2954.3</v>
+        <v>2938</v>
       </c>
       <c r="F29" t="n">
-        <v>38.9</v>
+        <v>-16.3</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0055</v>
       </c>
       <c r="H29" t="n">
-        <v>52.3</v>
+        <v>71</v>
       </c>
       <c r="I29" t="n">
-        <v>2826.3</v>
+        <v>2853.3</v>
       </c>
       <c r="J29" t="n">
-        <v>2826.95</v>
+        <v>2913.28</v>
       </c>
       <c r="K29" t="n">
-        <v>2877.4</v>
+        <v>2928.15</v>
       </c>
       <c r="L29" t="n">
-        <v>2927.85</v>
+        <v>2943.03</v>
       </c>
       <c r="M29" t="n">
-        <v>2953.4</v>
+        <v>2980.45</v>
       </c>
       <c r="N29" t="n">
-        <v>2978.95</v>
+        <v>3017.87</v>
       </c>
       <c r="O29" t="n">
-        <v>3054.3</v>
+        <v>3010.2</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2988,78 +2990,76 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2954</v>
+        <v>2950</v>
       </c>
       <c r="C30" t="n">
-        <v>2976.3</v>
+        <v>2994.6</v>
       </c>
       <c r="D30" t="n">
-        <v>2905.3</v>
+        <v>2948.4</v>
       </c>
       <c r="E30" t="n">
-        <v>2938</v>
+        <v>2989.3</v>
       </c>
       <c r="F30" t="n">
-        <v>-16.3</v>
+        <v>51.3</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0175</v>
       </c>
       <c r="H30" t="n">
-        <v>71</v>
+        <v>46.2</v>
       </c>
       <c r="I30" t="n">
-        <v>2853.3</v>
+        <v>2834.3</v>
       </c>
       <c r="J30" t="n">
-        <v>2913.28</v>
+        <v>2865.6</v>
       </c>
       <c r="K30" t="n">
-        <v>2928.15</v>
+        <v>2902.5</v>
       </c>
       <c r="L30" t="n">
-        <v>2943.03</v>
+        <v>2939.4</v>
       </c>
       <c r="M30" t="n">
-        <v>2980.45</v>
+        <v>2973.5</v>
       </c>
       <c r="N30" t="n">
-        <v>3017.87</v>
+        <v>3007.6</v>
       </c>
       <c r="O30" t="n">
-        <v>3010.2</v>
+        <v>3047.3</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3074,57 +3074,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2950</v>
+        <v>2992.4</v>
       </c>
       <c r="C31" t="n">
-        <v>2994.6</v>
+        <v>3051.8</v>
       </c>
       <c r="D31" t="n">
-        <v>2948.4</v>
+        <v>2986.1</v>
       </c>
       <c r="E31" t="n">
-        <v>2989.3</v>
+        <v>3044.7</v>
       </c>
       <c r="F31" t="n">
-        <v>51.3</v>
+        <v>55.4</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0185</v>
       </c>
       <c r="H31" t="n">
-        <v>46.2</v>
+        <v>65.7</v>
       </c>
       <c r="I31" t="n">
-        <v>2834.3</v>
+        <v>2902.2</v>
       </c>
       <c r="J31" t="n">
-        <v>2865.6</v>
+        <v>2952</v>
       </c>
       <c r="K31" t="n">
-        <v>2902.5</v>
+        <v>2966.2</v>
       </c>
       <c r="L31" t="n">
-        <v>2939.4</v>
+        <v>2980.4</v>
       </c>
       <c r="M31" t="n">
-        <v>2973.5</v>
+        <v>3012.4</v>
       </c>
       <c r="N31" t="n">
-        <v>3007.6</v>
+        <v>3044.4</v>
       </c>
       <c r="O31" t="n">
-        <v>3047.3</v>
+        <v>3040.8</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3135,80 +3135,80 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W31" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W31" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2992.4</v>
+        <v>3049.1</v>
       </c>
       <c r="C32" t="n">
-        <v>3051.8</v>
+        <v>3058.3</v>
       </c>
       <c r="D32" t="n">
-        <v>2986.1</v>
+        <v>3023.3</v>
       </c>
       <c r="E32" t="n">
-        <v>3044.7</v>
+        <v>3025.4</v>
       </c>
       <c r="F32" t="n">
-        <v>55.4</v>
+        <v>-19.3</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0063</v>
       </c>
       <c r="H32" t="n">
-        <v>65.7</v>
+        <v>35</v>
       </c>
       <c r="I32" t="n">
-        <v>2902.2</v>
+        <v>2920.4</v>
       </c>
       <c r="J32" t="n">
-        <v>2952</v>
+        <v>2991.87</v>
       </c>
       <c r="K32" t="n">
-        <v>2966.2</v>
+        <v>3011.85</v>
       </c>
       <c r="L32" t="n">
-        <v>2980.4</v>
+        <v>3031.83</v>
       </c>
       <c r="M32" t="n">
-        <v>3012.4</v>
+        <v>3077.55</v>
       </c>
       <c r="N32" t="n">
-        <v>3044.4</v>
+        <v>3123.27</v>
       </c>
       <c r="O32" t="n">
-        <v>3040.8</v>
+        <v>3117.5</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3221,78 +3221,76 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
       </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3049.1</v>
+        <v>3028.5</v>
       </c>
       <c r="C33" t="n">
-        <v>3058.3</v>
+        <v>3041</v>
       </c>
       <c r="D33" t="n">
-        <v>3023.3</v>
+        <v>3004.9</v>
       </c>
       <c r="E33" t="n">
-        <v>3025.4</v>
+        <v>3009.1</v>
       </c>
       <c r="F33" t="n">
-        <v>-19.3</v>
+        <v>-16.3</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0054</v>
       </c>
       <c r="H33" t="n">
-        <v>35</v>
+        <v>36.1</v>
       </c>
       <c r="I33" t="n">
-        <v>2920.4</v>
+        <v>2988.3</v>
       </c>
       <c r="J33" t="n">
-        <v>2991.87</v>
+        <v>2982.7</v>
       </c>
       <c r="K33" t="n">
-        <v>3011.85</v>
+        <v>3007.9</v>
       </c>
       <c r="L33" t="n">
-        <v>3031.83</v>
+        <v>3033.1</v>
       </c>
       <c r="M33" t="n">
-        <v>3077.55</v>
+        <v>3042.9</v>
       </c>
       <c r="N33" t="n">
-        <v>3123.27</v>
+        <v>3052.7</v>
       </c>
       <c r="O33" t="n">
-        <v>3117.5</v>
+        <v>3093.3</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3300,12 +3298,14 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3324,57 +3324,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3028.5</v>
+        <v>3008.5</v>
       </c>
       <c r="C34" t="n">
-        <v>3041</v>
+        <v>3046.8</v>
       </c>
       <c r="D34" t="n">
-        <v>3004.9</v>
+        <v>3002</v>
       </c>
       <c r="E34" t="n">
-        <v>3009.1</v>
+        <v>3041.6</v>
       </c>
       <c r="F34" t="n">
-        <v>-16.3</v>
+        <v>32.5</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0054</v>
+        <v>0.0108</v>
       </c>
       <c r="H34" t="n">
-        <v>36.1</v>
+        <v>44.8</v>
       </c>
       <c r="I34" t="n">
-        <v>2988.3</v>
+        <v>2968.8</v>
       </c>
       <c r="J34" t="n">
-        <v>2982.7</v>
+        <v>2966.08</v>
       </c>
       <c r="K34" t="n">
-        <v>3007.9</v>
+        <v>2991.05</v>
       </c>
       <c r="L34" t="n">
-        <v>3033.1</v>
+        <v>3016.03</v>
       </c>
       <c r="M34" t="n">
-        <v>3042.9</v>
+        <v>3027.15</v>
       </c>
       <c r="N34" t="n">
-        <v>3052.7</v>
+        <v>3038.28</v>
       </c>
       <c r="O34" t="n">
-        <v>3093.3</v>
+        <v>3077.1</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3382,22 +3382,24 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
@@ -3408,57 +3410,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3008.5</v>
+        <v>3038.9</v>
       </c>
       <c r="C35" t="n">
-        <v>3046.8</v>
+        <v>3044.6</v>
       </c>
       <c r="D35" t="n">
-        <v>3002</v>
+        <v>3016</v>
       </c>
       <c r="E35" t="n">
-        <v>3041.6</v>
+        <v>3025</v>
       </c>
       <c r="F35" t="n">
-        <v>32.5</v>
+        <v>-16.6</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0108</v>
+        <v>-0.0055</v>
       </c>
       <c r="H35" t="n">
-        <v>44.8</v>
+        <v>28.6</v>
       </c>
       <c r="I35" t="n">
-        <v>2968.8</v>
+        <v>2957.2</v>
       </c>
       <c r="J35" t="n">
-        <v>2966.08</v>
+        <v>3005.4</v>
       </c>
       <c r="K35" t="n">
-        <v>2991.05</v>
+        <v>3019.2</v>
       </c>
       <c r="L35" t="n">
-        <v>3016.03</v>
+        <v>3033</v>
       </c>
       <c r="M35" t="n">
-        <v>3027.15</v>
+        <v>3064</v>
       </c>
       <c r="N35" t="n">
-        <v>3038.28</v>
+        <v>3095</v>
       </c>
       <c r="O35" t="n">
-        <v>3077.1</v>
+        <v>3091.6</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3466,23 +3468,21 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3494,57 +3494,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3038.9</v>
+        <v>3024.7</v>
       </c>
       <c r="C36" t="n">
-        <v>3044.6</v>
+        <v>3045.8</v>
       </c>
       <c r="D36" t="n">
-        <v>3016</v>
+        <v>3019.9</v>
       </c>
       <c r="E36" t="n">
-        <v>3025</v>
+        <v>3035.5</v>
       </c>
       <c r="F36" t="n">
-        <v>-16.6</v>
+        <v>10.5</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0035</v>
       </c>
       <c r="H36" t="n">
-        <v>28.6</v>
+        <v>25.9</v>
       </c>
       <c r="I36" t="n">
-        <v>2957.2</v>
+        <v>2987.4</v>
       </c>
       <c r="J36" t="n">
-        <v>3005.4</v>
+        <v>2993.75</v>
       </c>
       <c r="K36" t="n">
-        <v>3019.2</v>
+        <v>3010.7</v>
       </c>
       <c r="L36" t="n">
-        <v>3033</v>
+        <v>3027.65</v>
       </c>
       <c r="M36" t="n">
-        <v>3064</v>
+        <v>3039.3</v>
       </c>
       <c r="N36" t="n">
-        <v>3095</v>
+        <v>3050.95</v>
       </c>
       <c r="O36" t="n">
-        <v>3091.6</v>
+        <v>3073.2</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3552,19 +3552,19 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3576,59 +3576,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3024.7</v>
+        <v>3036.1</v>
       </c>
       <c r="C37" t="n">
-        <v>3045.8</v>
+        <v>3060</v>
       </c>
       <c r="D37" t="n">
-        <v>3019.9</v>
+        <v>3033.1</v>
       </c>
       <c r="E37" t="n">
-        <v>3035.5</v>
+        <v>3052.8</v>
       </c>
       <c r="F37" t="n">
-        <v>10.5</v>
+        <v>17.3</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0057</v>
       </c>
       <c r="H37" t="n">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
       <c r="I37" t="n">
-        <v>2987.4</v>
+        <v>2994</v>
       </c>
       <c r="J37" t="n">
-        <v>2993.75</v>
+        <v>3010.92</v>
       </c>
       <c r="K37" t="n">
-        <v>3010.7</v>
+        <v>3022.55</v>
       </c>
       <c r="L37" t="n">
-        <v>3027.65</v>
+        <v>3034.17</v>
       </c>
       <c r="M37" t="n">
-        <v>3039.3</v>
+        <v>3048.45</v>
       </c>
       <c r="N37" t="n">
-        <v>3050.95</v>
+        <v>3062.73</v>
       </c>
       <c r="O37" t="n">
-        <v>3073.2</v>
+        <v>3071.7</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3639,7 +3635,7 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3665,50 +3661,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3036.1</v>
+        <v>3056.2</v>
       </c>
       <c r="C38" t="n">
-        <v>3060</v>
+        <v>3076.3</v>
       </c>
       <c r="D38" t="n">
-        <v>3033.1</v>
+        <v>3052.5</v>
       </c>
       <c r="E38" t="n">
-        <v>3052.8</v>
+        <v>3060.2</v>
       </c>
       <c r="F38" t="n">
-        <v>17.3</v>
+        <v>7.4</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0024</v>
       </c>
       <c r="H38" t="n">
-        <v>26.9</v>
+        <v>23.8</v>
       </c>
       <c r="I38" t="n">
-        <v>2994</v>
+        <v>3006.2</v>
       </c>
       <c r="J38" t="n">
-        <v>3010.92</v>
+        <v>3029.03</v>
       </c>
       <c r="K38" t="n">
-        <v>3022.55</v>
+        <v>3039.35</v>
       </c>
       <c r="L38" t="n">
-        <v>3034.17</v>
+        <v>3049.68</v>
       </c>
       <c r="M38" t="n">
-        <v>3048.45</v>
+        <v>3066.25</v>
       </c>
       <c r="N38" t="n">
-        <v>3062.73</v>
+        <v>3082.82</v>
       </c>
       <c r="O38" t="n">
-        <v>3071.7</v>
+        <v>3086.9</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3719,7 +3715,7 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
+      <c r="S38" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3745,50 +3741,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3056.2</v>
+        <v>3062.2</v>
       </c>
       <c r="C39" t="n">
         <v>3076.3</v>
       </c>
       <c r="D39" t="n">
-        <v>3052.5</v>
+        <v>3051.7</v>
       </c>
       <c r="E39" t="n">
-        <v>3060.2</v>
+        <v>3074.9</v>
       </c>
       <c r="F39" t="n">
-        <v>7.4</v>
+        <v>14.7</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0048</v>
       </c>
       <c r="H39" t="n">
-        <v>23.8</v>
+        <v>24.6</v>
       </c>
       <c r="I39" t="n">
-        <v>3006.2</v>
+        <v>3028.7</v>
       </c>
       <c r="J39" t="n">
-        <v>3029.03</v>
+        <v>3034.3</v>
       </c>
       <c r="K39" t="n">
-        <v>3039.35</v>
+        <v>3048.3</v>
       </c>
       <c r="L39" t="n">
-        <v>3049.68</v>
+        <v>3062.3</v>
       </c>
       <c r="M39" t="n">
-        <v>3066.25</v>
+        <v>3072.1</v>
       </c>
       <c r="N39" t="n">
-        <v>3082.82</v>
+        <v>3081.9</v>
       </c>
       <c r="O39" t="n">
-        <v>3086.9</v>
+        <v>3100.1</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3799,7 +3795,7 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3820,55 +3816,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3062.2</v>
+        <v>3073.5</v>
       </c>
       <c r="C40" t="n">
-        <v>3076.3</v>
+        <v>3079.9</v>
       </c>
       <c r="D40" t="n">
-        <v>3051.7</v>
+        <v>3055.9</v>
       </c>
       <c r="E40" t="n">
-        <v>3074.9</v>
+        <v>3064.9</v>
       </c>
       <c r="F40" t="n">
-        <v>14.7</v>
+        <v>-10</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.0033</v>
       </c>
       <c r="H40" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="I40" t="n">
-        <v>3028.7</v>
+        <v>3027.1</v>
       </c>
       <c r="J40" t="n">
-        <v>3034.3</v>
+        <v>3055.75</v>
       </c>
       <c r="K40" t="n">
-        <v>3048.3</v>
+        <v>3062.6</v>
       </c>
       <c r="L40" t="n">
-        <v>3062.3</v>
+        <v>3069.45</v>
       </c>
       <c r="M40" t="n">
-        <v>3072.1</v>
+        <v>3087.2</v>
       </c>
       <c r="N40" t="n">
-        <v>3081.9</v>
+        <v>3104.95</v>
       </c>
       <c r="O40" t="n">
-        <v>3100.1</v>
+        <v>3100.9</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3876,18 +3876,18 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3909,63 +3909,67 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3073.5</v>
+        <v>3063.7</v>
       </c>
       <c r="C41" t="n">
-        <v>3079.9</v>
+        <v>3066.6</v>
       </c>
       <c r="D41" t="n">
-        <v>3055.9</v>
+        <v>3024.1</v>
       </c>
       <c r="E41" t="n">
-        <v>3064.9</v>
+        <v>3026.4</v>
       </c>
       <c r="F41" t="n">
-        <v>-10</v>
+        <v>-38.5</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0126</v>
       </c>
       <c r="H41" t="n">
-        <v>24</v>
+        <v>42.5</v>
       </c>
       <c r="I41" t="n">
-        <v>3027.1</v>
+        <v>3031.9</v>
       </c>
       <c r="J41" t="n">
-        <v>3055.75</v>
+        <v>3039.4</v>
       </c>
       <c r="K41" t="n">
-        <v>3062.6</v>
+        <v>3052.9</v>
       </c>
       <c r="L41" t="n">
-        <v>3069.45</v>
+        <v>3066.4</v>
       </c>
       <c r="M41" t="n">
-        <v>3087.2</v>
+        <v>3076.9</v>
       </c>
       <c r="N41" t="n">
-        <v>3104.95</v>
+        <v>3087.4</v>
       </c>
       <c r="O41" t="n">
-        <v>3100.9</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
+        <v>3103.9</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3979,88 +3983,80 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W41" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3063.7</v>
+        <v>3025.9</v>
       </c>
       <c r="C42" t="n">
-        <v>3066.6</v>
+        <v>3059.1</v>
       </c>
       <c r="D42" t="n">
-        <v>3024.1</v>
+        <v>3019.8</v>
       </c>
       <c r="E42" t="n">
-        <v>3026.4</v>
+        <v>3039.9</v>
       </c>
       <c r="F42" t="n">
-        <v>-38.5</v>
+        <v>13.5</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0045</v>
       </c>
       <c r="H42" t="n">
-        <v>42.5</v>
+        <v>39.3</v>
       </c>
       <c r="I42" t="n">
-        <v>3031.9</v>
+        <v>2981.6</v>
       </c>
       <c r="J42" t="n">
-        <v>3039.4</v>
+        <v>2974.42</v>
       </c>
       <c r="K42" t="n">
-        <v>3052.9</v>
+        <v>3005.15</v>
       </c>
       <c r="L42" t="n">
-        <v>3066.4</v>
+        <v>3035.88</v>
       </c>
       <c r="M42" t="n">
-        <v>3076.9</v>
+        <v>3047.65</v>
       </c>
       <c r="N42" t="n">
-        <v>3087.4</v>
+        <v>3059.42</v>
       </c>
       <c r="O42" t="n">
-        <v>3103.9</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
+        <v>3109.1</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4072,74 +4068,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3025.9</v>
+        <v>3041.4</v>
       </c>
       <c r="C43" t="n">
-        <v>3059.1</v>
+        <v>3048.5</v>
       </c>
       <c r="D43" t="n">
-        <v>3019.8</v>
+        <v>2993.2</v>
       </c>
       <c r="E43" t="n">
-        <v>3039.9</v>
+        <v>2999.2</v>
       </c>
       <c r="F43" t="n">
-        <v>13.5</v>
+        <v>-40.7</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0134</v>
       </c>
       <c r="H43" t="n">
-        <v>39.3</v>
+        <v>55.3</v>
       </c>
       <c r="I43" t="n">
-        <v>2981.6</v>
+        <v>2980.5</v>
       </c>
       <c r="J43" t="n">
-        <v>2974.42</v>
+        <v>3000.82</v>
       </c>
       <c r="K43" t="n">
-        <v>3005.15</v>
+        <v>3020.25</v>
       </c>
       <c r="L43" t="n">
-        <v>3035.88</v>
+        <v>3039.67</v>
       </c>
       <c r="M43" t="n">
-        <v>3047.65</v>
+        <v>3059.55</v>
       </c>
       <c r="N43" t="n">
-        <v>3059.42</v>
+        <v>3079.42</v>
       </c>
       <c r="O43" t="n">
-        <v>3109.1</v>
+        <v>3098.4</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4152,81 +4154,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3041.4</v>
+        <v>2999.6</v>
       </c>
       <c r="C44" t="n">
-        <v>3048.5</v>
+        <v>3026.7</v>
       </c>
       <c r="D44" t="n">
-        <v>2993.2</v>
+        <v>2997.9</v>
       </c>
       <c r="E44" t="n">
-        <v>2999.2</v>
+        <v>3022.1</v>
       </c>
       <c r="F44" t="n">
-        <v>-40.7</v>
+        <v>22.9</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0134</v>
+        <v>0.0076</v>
       </c>
       <c r="H44" t="n">
-        <v>55.3</v>
+        <v>28.8</v>
       </c>
       <c r="I44" t="n">
-        <v>2980.5</v>
+        <v>2937.9</v>
       </c>
       <c r="J44" t="n">
-        <v>3000.82</v>
+        <v>2933.07</v>
       </c>
       <c r="K44" t="n">
-        <v>3020.25</v>
+        <v>2971.55</v>
       </c>
       <c r="L44" t="n">
-        <v>3039.67</v>
+        <v>3010.02</v>
       </c>
       <c r="M44" t="n">
-        <v>3059.55</v>
+        <v>3026.85</v>
       </c>
       <c r="N44" t="n">
-        <v>3079.42</v>
+        <v>3043.67</v>
       </c>
       <c r="O44" t="n">
-        <v>3098.4</v>
+        <v>3103.8</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
@@ -4238,74 +4234,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2999.6</v>
+        <v>3023</v>
       </c>
       <c r="C45" t="n">
-        <v>3026.7</v>
+        <v>3028.9</v>
       </c>
       <c r="D45" t="n">
-        <v>2997.9</v>
+        <v>2996</v>
       </c>
       <c r="E45" t="n">
-        <v>3022.1</v>
+        <v>3001.6</v>
       </c>
       <c r="F45" t="n">
-        <v>22.9</v>
+        <v>-20.5</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0076</v>
+        <v>-0.0068</v>
       </c>
       <c r="H45" t="n">
-        <v>28.8</v>
+        <v>32.9</v>
       </c>
       <c r="I45" t="n">
-        <v>2937.9</v>
+        <v>2969.1</v>
       </c>
       <c r="J45" t="n">
-        <v>2933.07</v>
+        <v>2998.2</v>
       </c>
       <c r="K45" t="n">
-        <v>2971.55</v>
+        <v>3007.7</v>
       </c>
       <c r="L45" t="n">
-        <v>3010.02</v>
+        <v>3017.2</v>
       </c>
       <c r="M45" t="n">
-        <v>3026.85</v>
+        <v>3036.5</v>
       </c>
       <c r="N45" t="n">
-        <v>3043.67</v>
+        <v>3055.8</v>
       </c>
       <c r="O45" t="n">
-        <v>3103.8</v>
+        <v>3055.5</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4320,79 +4322,77 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3023</v>
+        <v>3004.6</v>
       </c>
       <c r="C46" t="n">
-        <v>3028.9</v>
+        <v>3025.4</v>
       </c>
       <c r="D46" t="n">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="E46" t="n">
-        <v>3001.6</v>
+        <v>3014.4</v>
       </c>
       <c r="F46" t="n">
-        <v>-20.5</v>
+        <v>12.8</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0043</v>
       </c>
       <c r="H46" t="n">
-        <v>32.9</v>
+        <v>28.4</v>
       </c>
       <c r="I46" t="n">
-        <v>2969.1</v>
+        <v>2963.1</v>
       </c>
       <c r="J46" t="n">
-        <v>2998.2</v>
+        <v>2963.28</v>
       </c>
       <c r="K46" t="n">
-        <v>3007.7</v>
+        <v>2985.15</v>
       </c>
       <c r="L46" t="n">
-        <v>3017.2</v>
+        <v>3007.03</v>
       </c>
       <c r="M46" t="n">
-        <v>3036.5</v>
+        <v>3018.05</v>
       </c>
       <c r="N46" t="n">
-        <v>3055.8</v>
+        <v>3029.08</v>
       </c>
       <c r="O46" t="n">
-        <v>3055.5</v>
+        <v>3061.8</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4406,57 +4406,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3004.6</v>
+        <v>3014.6</v>
       </c>
       <c r="C47" t="n">
-        <v>3025.4</v>
+        <v>3020.5</v>
       </c>
       <c r="D47" t="n">
-        <v>2997</v>
+        <v>3002.6</v>
       </c>
       <c r="E47" t="n">
-        <v>3014.4</v>
+        <v>3010.1</v>
       </c>
       <c r="F47" t="n">
-        <v>12.8</v>
+        <v>-4.3</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0014</v>
       </c>
       <c r="H47" t="n">
-        <v>28.4</v>
+        <v>17.9</v>
       </c>
       <c r="I47" t="n">
-        <v>2963.1</v>
+        <v>2968.6</v>
       </c>
       <c r="J47" t="n">
-        <v>2963.28</v>
+        <v>2987.6</v>
       </c>
       <c r="K47" t="n">
-        <v>2985.15</v>
+        <v>3000.2</v>
       </c>
       <c r="L47" t="n">
-        <v>3007.03</v>
+        <v>3012.8</v>
       </c>
       <c r="M47" t="n">
-        <v>3018.05</v>
+        <v>3028.6</v>
       </c>
       <c r="N47" t="n">
-        <v>3029.08</v>
+        <v>3044.4</v>
       </c>
       <c r="O47" t="n">
-        <v>3061.8</v>
+        <v>3053.8</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4469,13 +4469,11 @@
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4490,57 +4488,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3014.6</v>
+        <v>3016.9</v>
       </c>
       <c r="C48" t="n">
-        <v>3020.5</v>
+        <v>3024.2</v>
       </c>
       <c r="D48" t="n">
-        <v>3002.6</v>
+        <v>3002.1</v>
       </c>
       <c r="E48" t="n">
-        <v>3010.1</v>
+        <v>3019</v>
       </c>
       <c r="F48" t="n">
-        <v>-4.3</v>
+        <v>8.9</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0014</v>
+        <v>0.003</v>
       </c>
       <c r="H48" t="n">
-        <v>17.9</v>
+        <v>22.1</v>
       </c>
       <c r="I48" t="n">
-        <v>2968.6</v>
+        <v>2984.7</v>
       </c>
       <c r="J48" t="n">
-        <v>2987.6</v>
+        <v>2991.48</v>
       </c>
       <c r="K48" t="n">
-        <v>3000.2</v>
+        <v>3001.15</v>
       </c>
       <c r="L48" t="n">
-        <v>3012.8</v>
+        <v>3010.83</v>
       </c>
       <c r="M48" t="n">
-        <v>3028.6</v>
+        <v>3019.05</v>
       </c>
       <c r="N48" t="n">
-        <v>3044.4</v>
+        <v>3027.28</v>
       </c>
       <c r="O48" t="n">
-        <v>3053.8</v>
+        <v>3038.4</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4553,11 +4551,13 @@
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4572,76 +4572,80 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3016.9</v>
+        <v>3019.6</v>
       </c>
       <c r="C49" t="n">
-        <v>3024.2</v>
+        <v>3025.5</v>
       </c>
       <c r="D49" t="n">
-        <v>3002.1</v>
+        <v>2976.6</v>
       </c>
       <c r="E49" t="n">
-        <v>3019</v>
+        <v>2977.5</v>
       </c>
       <c r="F49" t="n">
-        <v>8.9</v>
+        <v>-41.5</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0137</v>
       </c>
       <c r="H49" t="n">
-        <v>22.1</v>
+        <v>48.9</v>
       </c>
       <c r="I49" t="n">
-        <v>2984.7</v>
+        <v>2980</v>
       </c>
       <c r="J49" t="n">
-        <v>2991.48</v>
+        <v>2999.83</v>
       </c>
       <c r="K49" t="n">
-        <v>3001.15</v>
+        <v>3007.95</v>
       </c>
       <c r="L49" t="n">
-        <v>3010.83</v>
+        <v>3016.08</v>
       </c>
       <c r="M49" t="n">
-        <v>3019.05</v>
+        <v>3030.05</v>
       </c>
       <c r="N49" t="n">
-        <v>3027.28</v>
+        <v>3044.02</v>
       </c>
       <c r="O49" t="n">
-        <v>3038.4</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+        <v>3046.3</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4656,74 +4660,70 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3019.6</v>
+        <v>2971</v>
       </c>
       <c r="C50" t="n">
-        <v>3025.5</v>
+        <v>2982.5</v>
       </c>
       <c r="D50" t="n">
-        <v>2976.6</v>
+        <v>2946.1</v>
       </c>
       <c r="E50" t="n">
-        <v>2977.5</v>
+        <v>2958.7</v>
       </c>
       <c r="F50" t="n">
-        <v>-41.5</v>
+        <v>-18.8</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0063</v>
       </c>
       <c r="H50" t="n">
-        <v>48.9</v>
+        <v>36.4</v>
       </c>
       <c r="I50" t="n">
-        <v>2980</v>
+        <v>2927.7</v>
       </c>
       <c r="J50" t="n">
-        <v>2999.83</v>
+        <v>2916.83</v>
       </c>
       <c r="K50" t="n">
-        <v>3007.95</v>
+        <v>2953.05</v>
       </c>
       <c r="L50" t="n">
-        <v>3016.08</v>
+        <v>2989.28</v>
       </c>
       <c r="M50" t="n">
-        <v>3030.05</v>
+        <v>3001.95</v>
       </c>
       <c r="N50" t="n">
-        <v>3044.02</v>
+        <v>3014.62</v>
       </c>
       <c r="O50" t="n">
-        <v>3046.3</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
+        <v>3074.4</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
+      <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4742,72 +4742,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2971</v>
+        <v>2958</v>
       </c>
       <c r="C51" t="n">
-        <v>2982.5</v>
+        <v>2964.6</v>
       </c>
       <c r="D51" t="n">
-        <v>2946.1</v>
+        <v>2918.9</v>
       </c>
       <c r="E51" t="n">
-        <v>2958.7</v>
+        <v>2924.7</v>
       </c>
       <c r="F51" t="n">
-        <v>-18.8</v>
+        <v>-34</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0115</v>
       </c>
       <c r="H51" t="n">
-        <v>36.4</v>
+        <v>45.7</v>
       </c>
       <c r="I51" t="n">
-        <v>2927.7</v>
+        <v>2909.7</v>
       </c>
       <c r="J51" t="n">
-        <v>2916.83</v>
+        <v>2919.5</v>
       </c>
       <c r="K51" t="n">
-        <v>2953.05</v>
+        <v>2940.5</v>
       </c>
       <c r="L51" t="n">
-        <v>2989.28</v>
+        <v>2961.5</v>
       </c>
       <c r="M51" t="n">
-        <v>3001.95</v>
+        <v>2976.9</v>
       </c>
       <c r="N51" t="n">
-        <v>3014.62</v>
+        <v>2992.3</v>
       </c>
       <c r="O51" t="n">
-        <v>3074.4</v>
+        <v>3018.9</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4831,75 +4829,75 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2958</v>
+        <v>2926.4</v>
       </c>
       <c r="C52" t="n">
-        <v>2964.6</v>
+        <v>2962.5</v>
       </c>
       <c r="D52" t="n">
-        <v>2918.9</v>
+        <v>2914.5</v>
       </c>
       <c r="E52" t="n">
-        <v>2924.7</v>
+        <v>2958.8</v>
       </c>
       <c r="F52" t="n">
-        <v>-34</v>
+        <v>34.1</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0.0117</v>
       </c>
       <c r="H52" t="n">
-        <v>45.7</v>
+        <v>48</v>
       </c>
       <c r="I52" t="n">
-        <v>2909.7</v>
+        <v>2873.2</v>
       </c>
       <c r="J52" t="n">
-        <v>2919.5</v>
+        <v>2870.47</v>
       </c>
       <c r="K52" t="n">
-        <v>2940.5</v>
+        <v>2901.85</v>
       </c>
       <c r="L52" t="n">
-        <v>2961.5</v>
+        <v>2933.22</v>
       </c>
       <c r="M52" t="n">
-        <v>2976.9</v>
+        <v>2947.55</v>
       </c>
       <c r="N52" t="n">
-        <v>2992.3</v>
+        <v>2961.88</v>
       </c>
       <c r="O52" t="n">
-        <v>3018.9</v>
+        <v>3010.3</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
@@ -4908,55 +4906,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2926.4</v>
+        <v>2957.6</v>
       </c>
       <c r="C53" t="n">
-        <v>2962.5</v>
+        <v>2983.3</v>
       </c>
       <c r="D53" t="n">
-        <v>2914.5</v>
+        <v>2949.9</v>
       </c>
       <c r="E53" t="n">
-        <v>2958.8</v>
+        <v>2969.7</v>
       </c>
       <c r="F53" t="n">
-        <v>34.1</v>
+        <v>10.9</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0117</v>
+        <v>0.0037</v>
       </c>
       <c r="H53" t="n">
-        <v>48</v>
+        <v>33.4</v>
       </c>
       <c r="I53" t="n">
-        <v>2873.2</v>
+        <v>2866.5</v>
       </c>
       <c r="J53" t="n">
-        <v>2870.47</v>
+        <v>2920.95</v>
       </c>
       <c r="K53" t="n">
-        <v>2901.85</v>
+        <v>2934.8</v>
       </c>
       <c r="L53" t="n">
-        <v>2933.22</v>
+        <v>2948.65</v>
       </c>
       <c r="M53" t="n">
-        <v>2947.55</v>
+        <v>2982.8</v>
       </c>
       <c r="N53" t="n">
-        <v>2961.88</v>
+        <v>3016.95</v>
       </c>
       <c r="O53" t="n">
-        <v>3010.3</v>
+        <v>3010.5</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4967,21 +4969,19 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="7" t="inlineStr">
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
@@ -4992,57 +4992,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2957.6</v>
+        <v>2967.9</v>
       </c>
       <c r="C54" t="n">
-        <v>2983.3</v>
+        <v>2979.3</v>
       </c>
       <c r="D54" t="n">
-        <v>2949.9</v>
+        <v>2949.5</v>
       </c>
       <c r="E54" t="n">
-        <v>2969.7</v>
+        <v>2976.6</v>
       </c>
       <c r="F54" t="n">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0023</v>
       </c>
       <c r="H54" t="n">
-        <v>33.4</v>
+        <v>29.8</v>
       </c>
       <c r="I54" t="n">
-        <v>2866.5</v>
+        <v>2916.5</v>
       </c>
       <c r="J54" t="n">
-        <v>2920.95</v>
+        <v>2937.85</v>
       </c>
       <c r="K54" t="n">
-        <v>2934.8</v>
+        <v>2953</v>
       </c>
       <c r="L54" t="n">
-        <v>2948.65</v>
+        <v>2968.15</v>
       </c>
       <c r="M54" t="n">
-        <v>2982.8</v>
+        <v>2986.4</v>
       </c>
       <c r="N54" t="n">
-        <v>3016.95</v>
+        <v>3004.65</v>
       </c>
       <c r="O54" t="n">
-        <v>3010.5</v>
+        <v>3016.7</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5050,18 +5050,18 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5076,57 +5076,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2967.9</v>
+        <v>2974.7</v>
       </c>
       <c r="C55" t="n">
-        <v>2979.3</v>
+        <v>2977.9</v>
       </c>
       <c r="D55" t="n">
-        <v>2949.5</v>
+        <v>2954.7</v>
       </c>
       <c r="E55" t="n">
-        <v>2976.6</v>
+        <v>2963.6</v>
       </c>
       <c r="F55" t="n">
-        <v>6.9</v>
+        <v>-13</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0044</v>
       </c>
       <c r="H55" t="n">
-        <v>29.8</v>
+        <v>23.2</v>
       </c>
       <c r="I55" t="n">
-        <v>2916.5</v>
+        <v>2919.7</v>
       </c>
       <c r="J55" t="n">
-        <v>2937.85</v>
+        <v>2952.9</v>
       </c>
       <c r="K55" t="n">
-        <v>2953</v>
+        <v>2961.7</v>
       </c>
       <c r="L55" t="n">
-        <v>2968.15</v>
+        <v>2970.5</v>
       </c>
       <c r="M55" t="n">
-        <v>2986.4</v>
+        <v>2991.5</v>
       </c>
       <c r="N55" t="n">
-        <v>3004.65</v>
+        <v>3012.5</v>
       </c>
       <c r="O55" t="n">
-        <v>3016.7</v>
+        <v>3009.1</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5136,12 +5136,12 @@
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5167,63 +5167,67 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2974.7</v>
+        <v>2963.1</v>
       </c>
       <c r="C56" t="n">
-        <v>2977.9</v>
+        <v>2966.2</v>
       </c>
       <c r="D56" t="n">
-        <v>2954.7</v>
+        <v>2919.4</v>
       </c>
       <c r="E56" t="n">
-        <v>2963.6</v>
+        <v>2923</v>
       </c>
       <c r="F56" t="n">
-        <v>-13</v>
+        <v>-40.6</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0137</v>
       </c>
       <c r="H56" t="n">
-        <v>23.2</v>
+        <v>46.8</v>
       </c>
       <c r="I56" t="n">
-        <v>2919.7</v>
+        <v>2931.5</v>
       </c>
       <c r="J56" t="n">
-        <v>2952.9</v>
+        <v>2939.05</v>
       </c>
       <c r="K56" t="n">
-        <v>2961.7</v>
+        <v>2952</v>
       </c>
       <c r="L56" t="n">
-        <v>2970.5</v>
+        <v>2964.95</v>
       </c>
       <c r="M56" t="n">
-        <v>2991.5</v>
+        <v>2975.2</v>
       </c>
       <c r="N56" t="n">
-        <v>3012.5</v>
+        <v>2985.45</v>
       </c>
       <c r="O56" t="n">
-        <v>3009.1</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
+        <v>3001.1</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5242,76 +5246,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2963.1</v>
+        <v>2923.1</v>
       </c>
       <c r="C57" t="n">
-        <v>2966.2</v>
+        <v>2933.8</v>
       </c>
       <c r="D57" t="n">
-        <v>2919.4</v>
+        <v>2887.8</v>
       </c>
       <c r="E57" t="n">
-        <v>2923</v>
+        <v>2893.4</v>
       </c>
       <c r="F57" t="n">
-        <v>-40.6</v>
+        <v>-29.6</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0101</v>
       </c>
       <c r="H57" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="I57" t="n">
-        <v>2931.5</v>
+        <v>2872.6</v>
       </c>
       <c r="J57" t="n">
-        <v>2939.05</v>
+        <v>2866.3</v>
       </c>
       <c r="K57" t="n">
-        <v>2952</v>
+        <v>2899.6</v>
       </c>
       <c r="L57" t="n">
-        <v>2964.95</v>
+        <v>2932.9</v>
       </c>
       <c r="M57" t="n">
-        <v>2975.2</v>
+        <v>2946.4</v>
       </c>
       <c r="N57" t="n">
-        <v>2985.45</v>
+        <v>2959.9</v>
       </c>
       <c r="O57" t="n">
-        <v>3001.1</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
+        <v>3013</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5335,50 +5331,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2923.1</v>
+        <v>2890.9</v>
       </c>
       <c r="C58" t="n">
-        <v>2933.8</v>
+        <v>2929.8</v>
       </c>
       <c r="D58" t="n">
-        <v>2887.8</v>
+        <v>2887.6</v>
       </c>
       <c r="E58" t="n">
-        <v>2893.4</v>
+        <v>2904.5</v>
       </c>
       <c r="F58" t="n">
-        <v>-29.6</v>
+        <v>11.1</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0101</v>
+        <v>0.0038</v>
       </c>
       <c r="H58" t="n">
-        <v>46</v>
+        <v>42.2</v>
       </c>
       <c r="I58" t="n">
-        <v>2872.6</v>
+        <v>2841.8</v>
       </c>
       <c r="J58" t="n">
-        <v>2866.3</v>
+        <v>2838.7</v>
       </c>
       <c r="K58" t="n">
-        <v>2899.6</v>
+        <v>2870.4</v>
       </c>
       <c r="L58" t="n">
-        <v>2932.9</v>
+        <v>2902.1</v>
       </c>
       <c r="M58" t="n">
-        <v>2946.4</v>
+        <v>2916.4</v>
       </c>
       <c r="N58" t="n">
-        <v>2959.9</v>
+        <v>2930.7</v>
       </c>
       <c r="O58" t="n">
-        <v>3013</v>
+        <v>2979.8</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5386,18 +5382,18 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R58" s="6" t="n">
+        <v/>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5410,55 +5406,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2890.9</v>
+        <v>2892.7</v>
       </c>
       <c r="C59" t="n">
-        <v>2929.8</v>
+        <v>2913.5</v>
       </c>
       <c r="D59" t="n">
-        <v>2887.6</v>
+        <v>2884.3</v>
       </c>
       <c r="E59" t="n">
-        <v>2904.5</v>
+        <v>2894.1</v>
       </c>
       <c r="F59" t="n">
-        <v>11.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0036</v>
       </c>
       <c r="H59" t="n">
-        <v>42.2</v>
+        <v>29.2</v>
       </c>
       <c r="I59" t="n">
-        <v>2841.8</v>
+        <v>2845.4</v>
       </c>
       <c r="J59" t="n">
-        <v>2838.7</v>
+        <v>2860.2</v>
       </c>
       <c r="K59" t="n">
-        <v>2870.4</v>
+        <v>2883.4</v>
       </c>
       <c r="L59" t="n">
-        <v>2902.1</v>
+        <v>2906.6</v>
       </c>
       <c r="M59" t="n">
-        <v>2916.4</v>
+        <v>2925.6</v>
       </c>
       <c r="N59" t="n">
-        <v>2930.7</v>
+        <v>2944.6</v>
       </c>
       <c r="O59" t="n">
-        <v>2979.8</v>
+        <v>2972</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5466,18 +5466,18 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="n">
-        <v/>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5490,59 +5490,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2892.7</v>
+        <v>2896.4</v>
       </c>
       <c r="C60" t="n">
-        <v>2913.5</v>
+        <v>2896.5</v>
       </c>
       <c r="D60" t="n">
-        <v>2884.3</v>
+        <v>2862.7</v>
       </c>
       <c r="E60" t="n">
-        <v>2894.1</v>
+        <v>2873.1</v>
       </c>
       <c r="F60" t="n">
-        <v>-10.4</v>
+        <v>-21</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0073</v>
       </c>
       <c r="H60" t="n">
-        <v>29.2</v>
+        <v>33.8</v>
       </c>
       <c r="I60" t="n">
-        <v>2845.4</v>
+        <v>2855.1</v>
       </c>
       <c r="J60" t="n">
-        <v>2860.2</v>
+        <v>2862.5</v>
       </c>
       <c r="K60" t="n">
-        <v>2883.4</v>
+        <v>2879.5</v>
       </c>
       <c r="L60" t="n">
-        <v>2906.6</v>
+        <v>2896.5</v>
       </c>
       <c r="M60" t="n">
-        <v>2925.6</v>
+        <v>2908.7</v>
       </c>
       <c r="N60" t="n">
-        <v>2944.6</v>
+        <v>2920.9</v>
       </c>
       <c r="O60" t="n">
-        <v>2972</v>
+        <v>2942.7</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5555,7 +5551,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S60" s="10" t="inlineStr">
+      <c r="S60" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5579,50 +5575,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2896.4</v>
+        <v>2882.3</v>
       </c>
       <c r="C61" t="n">
-        <v>2896.5</v>
+        <v>2884</v>
       </c>
       <c r="D61" t="n">
-        <v>2862.7</v>
+        <v>2879.3</v>
       </c>
       <c r="E61" t="n">
-        <v>2873.1</v>
+        <v>2880.9</v>
       </c>
       <c r="F61" t="n">
-        <v>-21</v>
+        <v>7.8</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0027</v>
       </c>
       <c r="H61" t="n">
-        <v>33.8</v>
+        <v>4.7</v>
       </c>
       <c r="I61" t="n">
-        <v>2855.1</v>
+        <v>2828.9</v>
       </c>
       <c r="J61" t="n">
-        <v>2862.5</v>
+        <v>2836.05</v>
       </c>
       <c r="K61" t="n">
-        <v>2879.5</v>
+        <v>2856.2</v>
       </c>
       <c r="L61" t="n">
-        <v>2896.5</v>
+        <v>2876.35</v>
       </c>
       <c r="M61" t="n">
-        <v>2908.7</v>
+        <v>2890</v>
       </c>
       <c r="N61" t="n">
-        <v>2920.9</v>
+        <v>2903.65</v>
       </c>
       <c r="O61" t="n">
-        <v>2942.7</v>
+        <v>2930.3</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5630,14 +5626,12 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R61" s="6" t="n">
+        <v/>
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5654,120 +5648,38 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>2898.5</v>
-      </c>
-      <c r="C62" t="n">
-        <v>2904.7</v>
-      </c>
-      <c r="D62" t="n">
-        <v>2892.5</v>
-      </c>
-      <c r="E62" t="n">
-        <v>2903.6</v>
-      </c>
-      <c r="F62" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.0106</v>
-      </c>
-      <c r="H62" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="I62" t="n">
-        <v>2828.9</v>
-      </c>
-      <c r="J62" t="n">
-        <v>2836.05</v>
-      </c>
-      <c r="K62" t="n">
-        <v>2856.2</v>
-      </c>
-      <c r="L62" t="n">
-        <v>2876.35</v>
-      </c>
-      <c r="M62" t="n">
-        <v>2890</v>
-      </c>
-      <c r="N62" t="n">
-        <v>2903.65</v>
-      </c>
-      <c r="O62" t="n">
-        <v>2930.3</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I63" s="13" t="n">
-        <v>2880.3</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>2893.9</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>2897.5</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>2901.1</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>2909.7</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>2918.3</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>2916.9</v>
+      <c r="I62" s="13" t="n">
+        <v>2874.6</v>
+      </c>
+      <c r="J62" s="13" t="n">
+        <v>2875.82</v>
+      </c>
+      <c r="K62" s="13" t="n">
+        <v>2878.55</v>
+      </c>
+      <c r="L62" s="13" t="n">
+        <v>2881.27</v>
+      </c>
+      <c r="M62" s="13" t="n">
+        <v>2883.25</v>
+      </c>
+      <c r="N62" s="13" t="n">
+        <v>2885.22</v>
+      </c>
+      <c r="O62" s="13" t="n">
+        <v>2888.7</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -5582,22 +5582,22 @@
         <v>2882.3</v>
       </c>
       <c r="C61" t="n">
-        <v>2884</v>
+        <v>2902.8</v>
       </c>
       <c r="D61" t="n">
         <v>2879.3</v>
       </c>
       <c r="E61" t="n">
-        <v>2880.9</v>
+        <v>2900.4</v>
       </c>
       <c r="F61" t="n">
-        <v>7.8</v>
+        <v>27.3</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0027</v>
+        <v>0.0095</v>
       </c>
       <c r="H61" t="n">
-        <v>4.7</v>
+        <v>23.5</v>
       </c>
       <c r="I61" t="n">
         <v>2828.9</v>
@@ -5631,14 +5631,18 @@
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
@@ -5650,7 +5654,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
@@ -5661,25 +5665,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>2874.6</v>
+        <v>2855.8</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>2875.82</v>
+        <v>2881.57</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>2878.55</v>
+        <v>2888.65</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>2881.27</v>
+        <v>2895.72</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>2883.25</v>
+        <v>2912.15</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>2885.22</v>
+        <v>2928.57</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>2888.7</v>
+        <v>2926.3</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5579,25 +5579,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2882.3</v>
+        <v>2875.1</v>
       </c>
       <c r="C61" t="n">
-        <v>2902.8</v>
+        <v>2892.5</v>
       </c>
       <c r="D61" t="n">
-        <v>2879.3</v>
+        <v>2831.9</v>
       </c>
       <c r="E61" t="n">
-        <v>2900.4</v>
+        <v>2861.7</v>
       </c>
       <c r="F61" t="n">
-        <v>27.3</v>
+        <v>-11.4</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0095</v>
+        <v>-0.004</v>
       </c>
       <c r="H61" t="n">
-        <v>23.5</v>
+        <v>60.6</v>
       </c>
       <c r="I61" t="n">
         <v>2828.9</v>
@@ -5623,67 +5623,149 @@
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W61" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2893.9</v>
+      </c>
+      <c r="C62" t="n">
+        <v>2894.7</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2893.3</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2893.5</v>
+      </c>
+      <c r="F62" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I62" t="n">
+        <v>2771.3</v>
+      </c>
+      <c r="J62" t="n">
+        <v>2800.85</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2831.4</v>
+      </c>
+      <c r="L62" t="n">
+        <v>2861.95</v>
+      </c>
+      <c r="M62" t="n">
+        <v>2892</v>
+      </c>
+      <c r="N62" t="n">
+        <v>2922.05</v>
+      </c>
+      <c r="O62" t="n">
+        <v>2953.1</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
+      <c r="T62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W61" s="11" t="inlineStr">
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>強警訊</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I62" s="13" t="n">
-        <v>2855.8</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>2881.57</v>
-      </c>
-      <c r="K62" s="13" t="n">
-        <v>2888.65</v>
-      </c>
-      <c r="L62" s="13" t="n">
-        <v>2895.72</v>
-      </c>
-      <c r="M62" s="13" t="n">
-        <v>2912.15</v>
-      </c>
-      <c r="N62" s="13" t="n">
-        <v>2928.57</v>
-      </c>
-      <c r="O62" s="13" t="n">
-        <v>2926.3</v>
+      <c r="I63" s="13" t="n">
+        <v>2891.9</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>2891.85</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>2892.8</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>2893.75</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>2894.2</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>2894.65</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>2896.1</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -5669,19 +5669,19 @@
         <v>2894.7</v>
       </c>
       <c r="D62" t="n">
-        <v>2893.3</v>
+        <v>2890.9</v>
       </c>
       <c r="E62" t="n">
-        <v>2893.5</v>
+        <v>2892.2</v>
       </c>
       <c r="F62" t="n">
-        <v>31.8</v>
+        <v>30.5</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0111</v>
+        <v>0.0107</v>
       </c>
       <c r="H62" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="I62" t="n">
         <v>2771.3</v>
@@ -5747,25 +5747,25 @@
         </is>
       </c>
       <c r="I63" s="13" t="n">
-        <v>2891.9</v>
+        <v>2887.1</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>2891.85</v>
+        <v>2888.1</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>2892.8</v>
+        <v>2890.3</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>2893.75</v>
+        <v>2892.5</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>2894.2</v>
+        <v>2894.1</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>2894.65</v>
+        <v>2895.7</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>2896.1</v>
+        <v>2898.5</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,8 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5669,19 +5662,19 @@
         <v>2894.7</v>
       </c>
       <c r="D62" t="n">
+        <v>2890.6</v>
+      </c>
+      <c r="E62" t="n">
         <v>2890.9</v>
       </c>
-      <c r="E62" t="n">
-        <v>2892.2</v>
-      </c>
       <c r="F62" t="n">
-        <v>30.5</v>
+        <v>29.2</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0107</v>
+        <v>0.0102</v>
       </c>
       <c r="H62" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="I62" t="n">
         <v>2771.3</v>
@@ -5738,34 +5731,6 @@
         <is>
           <t>強警訊</t>
         </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>明日預測</t>
-        </is>
-      </c>
-      <c r="I63" s="13" t="n">
-        <v>2887.1</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>2888.1</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>2890.3</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>2892.5</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>2894.1</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>2895.7</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>2898.5</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -5662,7 +5662,7 @@
         <v>2894.7</v>
       </c>
       <c r="D62" t="n">
-        <v>2890.6</v>
+        <v>2890.5</v>
       </c>
       <c r="E62" t="n">
         <v>2890.9</v>
@@ -5674,7 +5674,7 @@
         <v>0.0102</v>
       </c>
       <c r="H62" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I62" t="n">
         <v>2771.3</v>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,72 +634,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3022.4</v>
+        <v>2998.4</v>
       </c>
       <c r="C2" t="n">
-        <v>3028.4</v>
+        <v>3041.4</v>
       </c>
       <c r="D2" t="n">
-        <v>2965.2</v>
+        <v>2987.2</v>
       </c>
       <c r="E2" t="n">
-        <v>2998.2</v>
+        <v>3013.5</v>
       </c>
       <c r="F2" t="n">
-        <v>-25.9</v>
+        <v>15.3</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0051</v>
       </c>
       <c r="H2" t="n">
-        <v>63.2</v>
+        <v>54.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2902.6</v>
+        <v>2902</v>
       </c>
       <c r="J2" t="n">
-        <v>2965.5</v>
+        <v>2935.7</v>
       </c>
       <c r="K2" t="n">
-        <v>2990</v>
+        <v>2966.6</v>
       </c>
       <c r="L2" t="n">
-        <v>3014.5</v>
+        <v>2997.5</v>
       </c>
       <c r="M2" t="n">
-        <v>3058.2</v>
+        <v>3029.8</v>
       </c>
       <c r="N2" t="n">
-        <v>3101.9</v>
+        <v>3062.1</v>
       </c>
       <c r="O2" t="n">
-        <v>3107.2</v>
+        <v>3091.6</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -711,59 +709,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2998.4</v>
+        <v>3023.7</v>
       </c>
       <c r="C3" t="n">
-        <v>3041.4</v>
+        <v>3062.4</v>
       </c>
       <c r="D3" t="n">
-        <v>2987.2</v>
+        <v>3010.5</v>
       </c>
       <c r="E3" t="n">
-        <v>3013.5</v>
+        <v>3030.7</v>
       </c>
       <c r="F3" t="n">
-        <v>15.3</v>
+        <v>17.2</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0057</v>
       </c>
       <c r="H3" t="n">
-        <v>54.2</v>
+        <v>51.9</v>
       </c>
       <c r="I3" t="n">
-        <v>2902</v>
+        <v>2933</v>
       </c>
       <c r="J3" t="n">
-        <v>2935.7</v>
+        <v>2958.9</v>
       </c>
       <c r="K3" t="n">
-        <v>2966.6</v>
+        <v>2986.4</v>
       </c>
       <c r="L3" t="n">
-        <v>2997.5</v>
+        <v>3013.9</v>
       </c>
       <c r="M3" t="n">
-        <v>3029.8</v>
+        <v>3040.6</v>
       </c>
       <c r="N3" t="n">
-        <v>3062.1</v>
+        <v>3067.3</v>
       </c>
       <c r="O3" t="n">
-        <v>3091.6</v>
+        <v>3095.6</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -774,14 +768,14 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U3" s="8" t="n">
@@ -800,50 +794,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3023.7</v>
+        <v>3034.7</v>
       </c>
       <c r="C4" t="n">
-        <v>3062.4</v>
+        <v>3045.7</v>
       </c>
       <c r="D4" t="n">
-        <v>3010.5</v>
+        <v>2999.6</v>
       </c>
       <c r="E4" t="n">
-        <v>3030.7</v>
+        <v>3022.6</v>
       </c>
       <c r="F4" t="n">
-        <v>17.2</v>
+        <v>-8.1</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.0027</v>
       </c>
       <c r="H4" t="n">
-        <v>51.9</v>
+        <v>46.1</v>
       </c>
       <c r="I4" t="n">
-        <v>2933</v>
+        <v>2958.6</v>
       </c>
       <c r="J4" t="n">
-        <v>2958.9</v>
+        <v>2975.93</v>
       </c>
       <c r="K4" t="n">
-        <v>2986.4</v>
+        <v>3004.75</v>
       </c>
       <c r="L4" t="n">
-        <v>3013.9</v>
+        <v>3033.57</v>
       </c>
       <c r="M4" t="n">
-        <v>3040.6</v>
+        <v>3056.65</v>
       </c>
       <c r="N4" t="n">
-        <v>3067.3</v>
+        <v>3079.72</v>
       </c>
       <c r="O4" t="n">
-        <v>3095.6</v>
+        <v>3114.3</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -851,18 +845,18 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -875,55 +869,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3034.7</v>
+        <v>3020.9</v>
       </c>
       <c r="C5" t="n">
-        <v>3045.7</v>
+        <v>3044.9</v>
       </c>
       <c r="D5" t="n">
-        <v>2999.6</v>
+        <v>2987.8</v>
       </c>
       <c r="E5" t="n">
-        <v>3022.6</v>
+        <v>3030.6</v>
       </c>
       <c r="F5" t="n">
-        <v>-8.1</v>
+        <v>8</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0026</v>
       </c>
       <c r="H5" t="n">
-        <v>46.1</v>
+        <v>57.1</v>
       </c>
       <c r="I5" t="n">
-        <v>2958.6</v>
+        <v>2953.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2975.93</v>
+        <v>2976.48</v>
       </c>
       <c r="K5" t="n">
-        <v>3004.75</v>
+        <v>2999.55</v>
       </c>
       <c r="L5" t="n">
-        <v>3033.57</v>
+        <v>3022.63</v>
       </c>
       <c r="M5" t="n">
-        <v>3056.65</v>
+        <v>3045.65</v>
       </c>
       <c r="N5" t="n">
-        <v>3079.72</v>
+        <v>3068.67</v>
       </c>
       <c r="O5" t="n">
-        <v>3114.3</v>
+        <v>3091.8</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -938,7 +936,7 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -957,57 +955,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3020.9</v>
+        <v>3026.1</v>
       </c>
       <c r="C6" t="n">
-        <v>3044.9</v>
+        <v>3050.6</v>
       </c>
       <c r="D6" t="n">
-        <v>2987.8</v>
+        <v>3015.1</v>
       </c>
       <c r="E6" t="n">
-        <v>3030.6</v>
+        <v>3045.6</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0049</v>
       </c>
       <c r="H6" t="n">
-        <v>57.1</v>
+        <v>35.5</v>
       </c>
       <c r="I6" t="n">
-        <v>2953.5</v>
+        <v>2930.7</v>
       </c>
       <c r="J6" t="n">
-        <v>2976.48</v>
+        <v>2980.63</v>
       </c>
       <c r="K6" t="n">
-        <v>2999.55</v>
+        <v>3002.05</v>
       </c>
       <c r="L6" t="n">
-        <v>3022.63</v>
+        <v>3023.48</v>
       </c>
       <c r="M6" t="n">
-        <v>3045.65</v>
+        <v>3059.15</v>
       </c>
       <c r="N6" t="n">
-        <v>3068.67</v>
+        <v>3094.83</v>
       </c>
       <c r="O6" t="n">
-        <v>3091.8</v>
+        <v>3102</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1015,18 +1013,18 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1039,59 +1037,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3026.1</v>
+        <v>3040</v>
       </c>
       <c r="C7" t="n">
-        <v>3050.6</v>
+        <v>3068.4</v>
       </c>
       <c r="D7" t="n">
-        <v>3015.1</v>
+        <v>3023.7</v>
       </c>
       <c r="E7" t="n">
-        <v>3045.6</v>
+        <v>3035.1</v>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>-10.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.0034</v>
       </c>
       <c r="H7" t="n">
-        <v>35.5</v>
+        <v>44.7</v>
       </c>
       <c r="I7" t="n">
-        <v>2930.7</v>
+        <v>2979.6</v>
       </c>
       <c r="J7" t="n">
-        <v>2980.63</v>
+        <v>3016.48</v>
       </c>
       <c r="K7" t="n">
-        <v>3002.05</v>
+        <v>3027.85</v>
       </c>
       <c r="L7" t="n">
-        <v>3023.48</v>
+        <v>3039.23</v>
       </c>
       <c r="M7" t="n">
-        <v>3059.15</v>
+        <v>3063.35</v>
       </c>
       <c r="N7" t="n">
-        <v>3094.83</v>
+        <v>3087.48</v>
       </c>
       <c r="O7" t="n">
-        <v>3102</v>
+        <v>3086.1</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1099,17 +1093,19 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U7" s="8" t="n">
@@ -1123,55 +1119,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3040</v>
+        <v>3030.9</v>
       </c>
       <c r="C8" t="n">
-        <v>3068.4</v>
+        <v>3062.4</v>
       </c>
       <c r="D8" t="n">
-        <v>3023.7</v>
+        <v>2988.5</v>
       </c>
       <c r="E8" t="n">
-        <v>3035.1</v>
+        <v>3014.2</v>
       </c>
       <c r="F8" t="n">
-        <v>-10.5</v>
+        <v>-20.9</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0069</v>
       </c>
       <c r="H8" t="n">
-        <v>44.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>2979.6</v>
+        <v>2979</v>
       </c>
       <c r="J8" t="n">
-        <v>3016.48</v>
+        <v>2984.93</v>
       </c>
       <c r="K8" t="n">
-        <v>3027.85</v>
+        <v>3012.75</v>
       </c>
       <c r="L8" t="n">
-        <v>3039.23</v>
+        <v>3040.58</v>
       </c>
       <c r="M8" t="n">
-        <v>3063.35</v>
+        <v>3057.45</v>
       </c>
       <c r="N8" t="n">
-        <v>3087.48</v>
+        <v>3074.33</v>
       </c>
       <c r="O8" t="n">
-        <v>3086.1</v>
+        <v>3113.1</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1181,19 +1181,19 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1207,57 +1207,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3030.9</v>
+        <v>3019.7</v>
       </c>
       <c r="C9" t="n">
-        <v>3062.4</v>
+        <v>3042.1</v>
       </c>
       <c r="D9" t="n">
-        <v>2988.5</v>
+        <v>3006.7</v>
       </c>
       <c r="E9" t="n">
-        <v>3014.2</v>
+        <v>3027</v>
       </c>
       <c r="F9" t="n">
-        <v>-20.9</v>
+        <v>12.8</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0042</v>
       </c>
       <c r="H9" t="n">
-        <v>73.90000000000001</v>
+        <v>35.4</v>
       </c>
       <c r="I9" t="n">
-        <v>2979</v>
+        <v>2914.6</v>
       </c>
       <c r="J9" t="n">
-        <v>2984.93</v>
+        <v>2934.68</v>
       </c>
       <c r="K9" t="n">
-        <v>3012.75</v>
+        <v>2977.25</v>
       </c>
       <c r="L9" t="n">
-        <v>3040.58</v>
+        <v>3019.82</v>
       </c>
       <c r="M9" t="n">
-        <v>3057.45</v>
+        <v>3051.15</v>
       </c>
       <c r="N9" t="n">
-        <v>3074.33</v>
+        <v>3082.47</v>
       </c>
       <c r="O9" t="n">
-        <v>3113.1</v>
+        <v>3136.3</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1265,20 +1265,16 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R9" s="6" t="n">
+        <v/>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1293,70 +1289,74 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3019.7</v>
+        <v>3033.4</v>
       </c>
       <c r="C10" t="n">
-        <v>3042.1</v>
+        <v>3042.6</v>
       </c>
       <c r="D10" t="n">
-        <v>3006.7</v>
+        <v>2988.8</v>
       </c>
       <c r="E10" t="n">
-        <v>3027</v>
+        <v>2998.8</v>
       </c>
       <c r="F10" t="n">
-        <v>12.8</v>
+        <v>-28.2</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>35.4</v>
+        <v>53.8</v>
       </c>
       <c r="I10" t="n">
-        <v>2914.6</v>
+        <v>2971.3</v>
       </c>
       <c r="J10" t="n">
-        <v>2934.68</v>
+        <v>2992.9</v>
       </c>
       <c r="K10" t="n">
-        <v>2977.25</v>
+        <v>3009.3</v>
       </c>
       <c r="L10" t="n">
-        <v>3019.82</v>
+        <v>3025.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3051.15</v>
+        <v>3044.7</v>
       </c>
       <c r="N10" t="n">
-        <v>3082.47</v>
+        <v>3063.7</v>
       </c>
       <c r="O10" t="n">
-        <v>3136.3</v>
+        <v>3077.5</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1375,72 +1375,70 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3033.4</v>
+        <v>2994.3</v>
       </c>
       <c r="C11" t="n">
-        <v>3042.6</v>
+        <v>3004.3</v>
       </c>
       <c r="D11" t="n">
-        <v>2988.8</v>
+        <v>2943.4</v>
       </c>
       <c r="E11" t="n">
-        <v>2998.8</v>
+        <v>2971.5</v>
       </c>
       <c r="F11" t="n">
-        <v>-28.2</v>
+        <v>-27.3</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0091</v>
       </c>
       <c r="H11" t="n">
-        <v>53.8</v>
+        <v>60.9</v>
       </c>
       <c r="I11" t="n">
-        <v>2971.3</v>
+        <v>2935</v>
       </c>
       <c r="J11" t="n">
-        <v>2992.9</v>
+        <v>2936.55</v>
       </c>
       <c r="K11" t="n">
-        <v>3009.3</v>
+        <v>2971.9</v>
       </c>
       <c r="L11" t="n">
+        <v>3007.25</v>
+      </c>
+      <c r="M11" t="n">
         <v>3025.7</v>
       </c>
-      <c r="M11" t="n">
-        <v>3044.7</v>
-      </c>
       <c r="N11" t="n">
-        <v>3063.7</v>
+        <v>3044.15</v>
       </c>
       <c r="O11" t="n">
-        <v>3077.5</v>
+        <v>3096.4</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1461,57 +1459,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2994.3</v>
+        <v>2965.8</v>
       </c>
       <c r="C12" t="n">
-        <v>3004.3</v>
+        <v>3014.9</v>
       </c>
       <c r="D12" t="n">
-        <v>2943.4</v>
+        <v>2964.3</v>
       </c>
       <c r="E12" t="n">
-        <v>2971.5</v>
+        <v>3008.4</v>
       </c>
       <c r="F12" t="n">
-        <v>-27.3</v>
+        <v>36.9</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0091</v>
+        <v>0.0124</v>
       </c>
       <c r="H12" t="n">
-        <v>60.9</v>
+        <v>50.6</v>
       </c>
       <c r="I12" t="n">
-        <v>2935</v>
+        <v>2882.5</v>
       </c>
       <c r="J12" t="n">
-        <v>2936.55</v>
+        <v>2909.42</v>
       </c>
       <c r="K12" t="n">
-        <v>2971.9</v>
+        <v>2941.05</v>
       </c>
       <c r="L12" t="n">
-        <v>3007.25</v>
+        <v>2972.67</v>
       </c>
       <c r="M12" t="n">
-        <v>3025.7</v>
+        <v>3001.95</v>
       </c>
       <c r="N12" t="n">
-        <v>3044.15</v>
+        <v>3031.23</v>
       </c>
       <c r="O12" t="n">
-        <v>3096.4</v>
+        <v>3065.2</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1519,19 +1517,19 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1543,59 +1541,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2965.8</v>
+        <v>3008.1</v>
       </c>
       <c r="C13" t="n">
-        <v>3014.9</v>
+        <v>3019.5</v>
       </c>
       <c r="D13" t="n">
-        <v>2964.3</v>
+        <v>2970.8</v>
       </c>
       <c r="E13" t="n">
-        <v>3008.4</v>
+        <v>2994</v>
       </c>
       <c r="F13" t="n">
-        <v>36.9</v>
+        <v>-14.4</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0048</v>
       </c>
       <c r="H13" t="n">
-        <v>50.6</v>
+        <v>48.7</v>
       </c>
       <c r="I13" t="n">
-        <v>2882.5</v>
+        <v>2913.7</v>
       </c>
       <c r="J13" t="n">
-        <v>2909.42</v>
+        <v>2967.2</v>
       </c>
       <c r="K13" t="n">
-        <v>2941.05</v>
+        <v>2983.1</v>
       </c>
       <c r="L13" t="n">
-        <v>2972.67</v>
+        <v>2999</v>
       </c>
       <c r="M13" t="n">
-        <v>3001.95</v>
+        <v>3033.7</v>
       </c>
       <c r="N13" t="n">
-        <v>3031.23</v>
+        <v>3068.4</v>
       </c>
       <c r="O13" t="n">
-        <v>3065.2</v>
+        <v>3065.5</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1603,18 +1597,18 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1627,55 +1621,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3008.1</v>
+        <v>2984.7</v>
       </c>
       <c r="C14" t="n">
-        <v>3019.5</v>
+        <v>2995.8</v>
       </c>
       <c r="D14" t="n">
-        <v>2970.8</v>
+        <v>2961.8</v>
       </c>
       <c r="E14" t="n">
-        <v>2994</v>
+        <v>2970.4</v>
       </c>
       <c r="F14" t="n">
-        <v>-14.4</v>
+        <v>-23.6</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>48.7</v>
+        <v>34</v>
       </c>
       <c r="I14" t="n">
-        <v>2913.7</v>
+        <v>2922.1</v>
       </c>
       <c r="J14" t="n">
-        <v>2967.2</v>
+        <v>2944.73</v>
       </c>
       <c r="K14" t="n">
-        <v>2983.1</v>
+        <v>2969.65</v>
       </c>
       <c r="L14" t="n">
-        <v>2999</v>
+        <v>2994.58</v>
       </c>
       <c r="M14" t="n">
-        <v>3033.7</v>
+        <v>3018.35</v>
       </c>
       <c r="N14" t="n">
-        <v>3068.4</v>
+        <v>3042.12</v>
       </c>
       <c r="O14" t="n">
-        <v>3065.5</v>
+        <v>3068.2</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1685,12 +1683,12 @@
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1709,57 +1707,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2984.7</v>
+        <v>2967.2</v>
       </c>
       <c r="C15" t="n">
-        <v>2995.8</v>
+        <v>3029.8</v>
       </c>
       <c r="D15" t="n">
-        <v>2961.8</v>
+        <v>2956.2</v>
       </c>
       <c r="E15" t="n">
-        <v>2970.4</v>
+        <v>2979.9</v>
       </c>
       <c r="F15" t="n">
-        <v>-23.6</v>
+        <v>9.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H15" t="n">
-        <v>34</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>2922.1</v>
+        <v>2927.8</v>
       </c>
       <c r="J15" t="n">
-        <v>2944.73</v>
+        <v>2932.2</v>
       </c>
       <c r="K15" t="n">
-        <v>2969.65</v>
+        <v>2953.4</v>
       </c>
       <c r="L15" t="n">
-        <v>2994.58</v>
+        <v>2974.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3018.35</v>
+        <v>2987.4</v>
       </c>
       <c r="N15" t="n">
-        <v>3042.12</v>
+        <v>3000.2</v>
       </c>
       <c r="O15" t="n">
-        <v>3068.2</v>
+        <v>3029.8</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1767,24 +1765,28 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R15" s="6" t="n">
+        <v/>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
@@ -1793,57 +1795,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2967.2</v>
+        <v>2981.2</v>
       </c>
       <c r="C16" t="n">
-        <v>3029.8</v>
+        <v>3006.1</v>
       </c>
       <c r="D16" t="n">
-        <v>2956.2</v>
+        <v>2974.4</v>
       </c>
       <c r="E16" t="n">
-        <v>2979.9</v>
+        <v>2991.8</v>
       </c>
       <c r="F16" t="n">
-        <v>9.5</v>
+        <v>11.9</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.004</v>
       </c>
       <c r="H16" t="n">
-        <v>73.59999999999999</v>
+        <v>31.7</v>
       </c>
       <c r="I16" t="n">
-        <v>2927.8</v>
+        <v>2882.6</v>
       </c>
       <c r="J16" t="n">
-        <v>2932.2</v>
+        <v>2899.75</v>
       </c>
       <c r="K16" t="n">
-        <v>2953.4</v>
+        <v>2943.1</v>
       </c>
       <c r="L16" t="n">
-        <v>2974.6</v>
+        <v>2986.45</v>
       </c>
       <c r="M16" t="n">
-        <v>2987.4</v>
+        <v>3016.7</v>
       </c>
       <c r="N16" t="n">
-        <v>3000.2</v>
+        <v>3046.95</v>
       </c>
       <c r="O16" t="n">
-        <v>3029.8</v>
+        <v>3103.4</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1854,25 +1856,19 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
@@ -1888,50 +1884,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2981.2</v>
+        <v>2995.3</v>
       </c>
       <c r="C17" t="n">
-        <v>3006.1</v>
+        <v>3012.8</v>
       </c>
       <c r="D17" t="n">
-        <v>2974.4</v>
+        <v>2972.7</v>
       </c>
       <c r="E17" t="n">
-        <v>2991.8</v>
+        <v>2990.7</v>
       </c>
       <c r="F17" t="n">
-        <v>11.9</v>
+        <v>-1.1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0004</v>
       </c>
       <c r="H17" t="n">
-        <v>31.7</v>
+        <v>40.1</v>
       </c>
       <c r="I17" t="n">
-        <v>2882.6</v>
+        <v>2942.7</v>
       </c>
       <c r="J17" t="n">
-        <v>2899.75</v>
+        <v>2960.87</v>
       </c>
       <c r="K17" t="n">
-        <v>2943.1</v>
+        <v>2975.95</v>
       </c>
       <c r="L17" t="n">
-        <v>2986.45</v>
+        <v>2991.03</v>
       </c>
       <c r="M17" t="n">
-        <v>3016.7</v>
+        <v>3007.65</v>
       </c>
       <c r="N17" t="n">
-        <v>3046.95</v>
+        <v>3024.28</v>
       </c>
       <c r="O17" t="n">
-        <v>3103.4</v>
+        <v>3037.8</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1939,16 +1935,20 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1963,78 +1963,78 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2995.3</v>
+        <v>2991.7</v>
       </c>
       <c r="C18" t="n">
-        <v>3012.8</v>
+        <v>2994.8</v>
       </c>
       <c r="D18" t="n">
-        <v>2972.7</v>
+        <v>2949.3</v>
       </c>
       <c r="E18" t="n">
-        <v>2990.7</v>
+        <v>2973.5</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1</v>
+        <v>-17.2</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0058</v>
       </c>
       <c r="H18" t="n">
-        <v>40.1</v>
+        <v>45.5</v>
       </c>
       <c r="I18" t="n">
-        <v>2942.7</v>
+        <v>2932.6</v>
       </c>
       <c r="J18" t="n">
-        <v>2960.87</v>
+        <v>2949.57</v>
       </c>
       <c r="K18" t="n">
-        <v>2975.95</v>
+        <v>2970.65</v>
       </c>
       <c r="L18" t="n">
-        <v>2991.03</v>
+        <v>2991.72</v>
       </c>
       <c r="M18" t="n">
-        <v>3007.65</v>
+        <v>3010.75</v>
       </c>
       <c r="N18" t="n">
-        <v>3024.28</v>
+        <v>3029.78</v>
       </c>
       <c r="O18" t="n">
-        <v>3037.8</v>
+        <v>3052.9</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2049,79 +2049,79 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2991.7</v>
+        <v>2964.5</v>
       </c>
       <c r="C19" t="n">
-        <v>2994.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D19" t="n">
-        <v>2949.3</v>
+        <v>2952.7</v>
       </c>
       <c r="E19" t="n">
-        <v>2973.5</v>
+        <v>2955.2</v>
       </c>
       <c r="F19" t="n">
-        <v>-17.2</v>
+        <v>-18.3</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0062</v>
       </c>
       <c r="H19" t="n">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="I19" t="n">
-        <v>2932.6</v>
+        <v>2903.8</v>
       </c>
       <c r="J19" t="n">
-        <v>2949.57</v>
+        <v>2928.72</v>
       </c>
       <c r="K19" t="n">
-        <v>2970.65</v>
+        <v>2950.75</v>
       </c>
       <c r="L19" t="n">
-        <v>2991.72</v>
+        <v>2972.78</v>
       </c>
       <c r="M19" t="n">
-        <v>3010.75</v>
+        <v>2996.25</v>
       </c>
       <c r="N19" t="n">
-        <v>3029.78</v>
+        <v>3019.72</v>
       </c>
       <c r="O19" t="n">
-        <v>3052.9</v>
+        <v>3040.3</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
@@ -2135,57 +2135,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2964.5</v>
+        <v>2955.8</v>
       </c>
       <c r="C20" t="n">
-        <v>2998.7</v>
+        <v>2999.8</v>
       </c>
       <c r="D20" t="n">
-        <v>2952.7</v>
+        <v>2951.1</v>
       </c>
       <c r="E20" t="n">
-        <v>2955.2</v>
+        <v>2997</v>
       </c>
       <c r="F20" t="n">
-        <v>-18.3</v>
+        <v>41.8</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0141</v>
       </c>
       <c r="H20" t="n">
-        <v>46</v>
+        <v>48.7</v>
       </c>
       <c r="I20" t="n">
-        <v>2903.8</v>
+        <v>2906.7</v>
       </c>
       <c r="J20" t="n">
-        <v>2928.72</v>
+        <v>2898.95</v>
       </c>
       <c r="K20" t="n">
-        <v>2950.75</v>
+        <v>2932.2</v>
       </c>
       <c r="L20" t="n">
-        <v>2972.78</v>
+        <v>2965.45</v>
       </c>
       <c r="M20" t="n">
-        <v>2996.25</v>
+        <v>2978.2</v>
       </c>
       <c r="N20" t="n">
-        <v>3019.72</v>
+        <v>2990.95</v>
       </c>
       <c r="O20" t="n">
-        <v>3040.3</v>
+        <v>3044.7</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2193,23 +2193,23 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2228,50 +2228,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2955.8</v>
+        <v>2997</v>
       </c>
       <c r="C21" t="n">
-        <v>2999.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D21" t="n">
-        <v>2951.1</v>
+        <v>2965.5</v>
       </c>
       <c r="E21" t="n">
-        <v>2997</v>
+        <v>2969.8</v>
       </c>
       <c r="F21" t="n">
-        <v>41.8</v>
+        <v>-27.2</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0141</v>
+        <v>-0.0091</v>
       </c>
       <c r="H21" t="n">
-        <v>48.7</v>
+        <v>33.2</v>
       </c>
       <c r="I21" t="n">
-        <v>2906.7</v>
+        <v>2902.4</v>
       </c>
       <c r="J21" t="n">
-        <v>2898.95</v>
+        <v>2959.08</v>
       </c>
       <c r="K21" t="n">
-        <v>2932.2</v>
+        <v>2972.65</v>
       </c>
       <c r="L21" t="n">
-        <v>2965.45</v>
+        <v>2986.23</v>
       </c>
       <c r="M21" t="n">
-        <v>2978.2</v>
+        <v>3021.35</v>
       </c>
       <c r="N21" t="n">
-        <v>2990.95</v>
+        <v>3056.47</v>
       </c>
       <c r="O21" t="n">
-        <v>3044.7</v>
+        <v>3048.5</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2279,23 +2279,21 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2307,60 +2305,62 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2997</v>
+        <v>2974.6</v>
       </c>
       <c r="C22" t="n">
-        <v>2998.7</v>
+        <v>2979</v>
       </c>
       <c r="D22" t="n">
-        <v>2965.5</v>
+        <v>2932.1</v>
       </c>
       <c r="E22" t="n">
-        <v>2969.8</v>
+        <v>2951.7</v>
       </c>
       <c r="F22" t="n">
-        <v>-27.2</v>
+        <v>-18.1</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0091</v>
+        <v>-0.0061</v>
       </c>
       <c r="H22" t="n">
-        <v>33.2</v>
+        <v>46.9</v>
       </c>
       <c r="I22" t="n">
-        <v>2902.4</v>
+        <v>2932.3</v>
       </c>
       <c r="J22" t="n">
-        <v>2959.08</v>
+        <v>2930.45</v>
       </c>
       <c r="K22" t="n">
-        <v>2972.65</v>
+        <v>2953.2</v>
       </c>
       <c r="L22" t="n">
-        <v>2986.23</v>
+        <v>2975.95</v>
       </c>
       <c r="M22" t="n">
-        <v>3021.35</v>
+        <v>2986.4</v>
       </c>
       <c r="N22" t="n">
-        <v>3056.47</v>
+        <v>2996.85</v>
       </c>
       <c r="O22" t="n">
-        <v>3048.5</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
+        <v>3031.9</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q22" s="6" t="n">
         <v/>
@@ -2370,7 +2370,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2391,74 +2391,70 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2974.6</v>
+        <v>2948.5</v>
       </c>
       <c r="C23" t="n">
-        <v>2979</v>
+        <v>2969.7</v>
       </c>
       <c r="D23" t="n">
-        <v>2932.1</v>
+        <v>2934.5</v>
       </c>
       <c r="E23" t="n">
-        <v>2951.7</v>
+        <v>2941.3</v>
       </c>
       <c r="F23" t="n">
-        <v>-18.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0035</v>
       </c>
       <c r="H23" t="n">
-        <v>46.9</v>
+        <v>35.2</v>
       </c>
       <c r="I23" t="n">
-        <v>2932.3</v>
+        <v>2885.2</v>
       </c>
       <c r="J23" t="n">
-        <v>2930.45</v>
+        <v>2902.88</v>
       </c>
       <c r="K23" t="n">
-        <v>2953.2</v>
+        <v>2928.25</v>
       </c>
       <c r="L23" t="n">
-        <v>2975.95</v>
+        <v>2953.62</v>
       </c>
       <c r="M23" t="n">
-        <v>2986.4</v>
+        <v>2975.15</v>
       </c>
       <c r="N23" t="n">
-        <v>2996.85</v>
+        <v>2996.67</v>
       </c>
       <c r="O23" t="n">
-        <v>3031.9</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3025.9</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
       </c>
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2477,57 +2473,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2948.5</v>
+        <v>2955.5</v>
       </c>
       <c r="C24" t="n">
-        <v>2969.7</v>
+        <v>2985.9</v>
       </c>
       <c r="D24" t="n">
-        <v>2934.5</v>
+        <v>2941.2</v>
       </c>
       <c r="E24" t="n">
-        <v>2941.3</v>
+        <v>2960</v>
       </c>
       <c r="F24" t="n">
-        <v>-10.4</v>
+        <v>18.7</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0064</v>
       </c>
       <c r="H24" t="n">
-        <v>35.2</v>
+        <v>44.7</v>
       </c>
       <c r="I24" t="n">
-        <v>2885.2</v>
+        <v>2899.3</v>
       </c>
       <c r="J24" t="n">
-        <v>2902.88</v>
+        <v>2900.7</v>
       </c>
       <c r="K24" t="n">
-        <v>2928.25</v>
+        <v>2923.7</v>
       </c>
       <c r="L24" t="n">
-        <v>2953.62</v>
+        <v>2946.7</v>
       </c>
       <c r="M24" t="n">
-        <v>2975.15</v>
+        <v>2958.9</v>
       </c>
       <c r="N24" t="n">
-        <v>2996.67</v>
+        <v>2971.1</v>
       </c>
       <c r="O24" t="n">
-        <v>3025.9</v>
+        <v>3004.9</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2540,14 +2536,18 @@
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2557,59 +2557,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2955.5</v>
+        <v>2961.5</v>
       </c>
       <c r="C25" t="n">
-        <v>2985.9</v>
+        <v>2968.3</v>
       </c>
       <c r="D25" t="n">
-        <v>2941.2</v>
+        <v>2933.4</v>
       </c>
       <c r="E25" t="n">
-        <v>2960</v>
+        <v>2964.5</v>
       </c>
       <c r="F25" t="n">
-        <v>18.7</v>
+        <v>4.5</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0015</v>
       </c>
       <c r="H25" t="n">
-        <v>44.7</v>
+        <v>34.9</v>
       </c>
       <c r="I25" t="n">
-        <v>2899.3</v>
+        <v>2896.5</v>
       </c>
       <c r="J25" t="n">
-        <v>2900.7</v>
+        <v>2913.53</v>
       </c>
       <c r="K25" t="n">
-        <v>2923.7</v>
+        <v>2937.65</v>
       </c>
       <c r="L25" t="n">
-        <v>2946.7</v>
+        <v>2961.77</v>
       </c>
       <c r="M25" t="n">
-        <v>2958.9</v>
+        <v>2982.35</v>
       </c>
       <c r="N25" t="n">
-        <v>2971.1</v>
+        <v>3002.92</v>
       </c>
       <c r="O25" t="n">
-        <v>3004.9</v>
+        <v>3030.6</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2617,24 +2613,22 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
@@ -2643,61 +2637,69 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2961.5</v>
+        <v>2966.9</v>
       </c>
       <c r="C26" t="n">
-        <v>2968.3</v>
+        <v>2978.3</v>
       </c>
       <c r="D26" t="n">
-        <v>2933.4</v>
+        <v>2902.3</v>
       </c>
       <c r="E26" t="n">
-        <v>2964.5</v>
+        <v>2915.4</v>
       </c>
       <c r="F26" t="n">
-        <v>4.5</v>
+        <v>-49.1</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0166</v>
       </c>
       <c r="H26" t="n">
-        <v>34.9</v>
+        <v>76</v>
       </c>
       <c r="I26" t="n">
-        <v>2896.5</v>
+        <v>2898.5</v>
       </c>
       <c r="J26" t="n">
-        <v>2913.53</v>
+        <v>2936.42</v>
       </c>
       <c r="K26" t="n">
-        <v>2937.65</v>
+        <v>2947.05</v>
       </c>
       <c r="L26" t="n">
-        <v>2961.77</v>
+        <v>2957.67</v>
       </c>
       <c r="M26" t="n">
-        <v>2982.35</v>
+        <v>2981.95</v>
       </c>
       <c r="N26" t="n">
-        <v>3002.92</v>
+        <v>3006.23</v>
       </c>
       <c r="O26" t="n">
-        <v>3030.6</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
+        <v>3003.2</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
@@ -2706,7 +2708,7 @@
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2718,88 +2720,84 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W26" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2966.9</v>
+        <v>2906.6</v>
       </c>
       <c r="C27" t="n">
-        <v>2978.3</v>
+        <v>2957.9</v>
       </c>
       <c r="D27" t="n">
-        <v>2902.3</v>
+        <v>2905.6</v>
       </c>
       <c r="E27" t="n">
-        <v>2915.4</v>
+        <v>2954.3</v>
       </c>
       <c r="F27" t="n">
-        <v>-49.1</v>
+        <v>38.9</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0166</v>
+        <v>0.0133</v>
       </c>
       <c r="H27" t="n">
-        <v>76</v>
+        <v>52.3</v>
       </c>
       <c r="I27" t="n">
-        <v>2898.5</v>
+        <v>2826.3</v>
       </c>
       <c r="J27" t="n">
-        <v>2936.42</v>
+        <v>2826.95</v>
       </c>
       <c r="K27" t="n">
-        <v>2947.05</v>
+        <v>2877.4</v>
       </c>
       <c r="L27" t="n">
-        <v>2957.67</v>
+        <v>2927.85</v>
       </c>
       <c r="M27" t="n">
-        <v>2981.95</v>
+        <v>2953.4</v>
       </c>
       <c r="N27" t="n">
-        <v>3006.23</v>
+        <v>2978.95</v>
       </c>
       <c r="O27" t="n">
-        <v>3003.2</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
+        <v>3054.3</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
       <c r="U27" s="8" t="n">
         <v/>
       </c>
@@ -2813,76 +2811,78 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2906.6</v>
+        <v>2954</v>
       </c>
       <c r="C28" t="n">
-        <v>2957.9</v>
+        <v>2976.3</v>
       </c>
       <c r="D28" t="n">
-        <v>2905.6</v>
+        <v>2905.3</v>
       </c>
       <c r="E28" t="n">
-        <v>2954.3</v>
+        <v>2938</v>
       </c>
       <c r="F28" t="n">
-        <v>38.9</v>
+        <v>-16.3</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0055</v>
       </c>
       <c r="H28" t="n">
-        <v>52.3</v>
+        <v>71</v>
       </c>
       <c r="I28" t="n">
-        <v>2826.3</v>
+        <v>2853.3</v>
       </c>
       <c r="J28" t="n">
-        <v>2826.95</v>
+        <v>2913.28</v>
       </c>
       <c r="K28" t="n">
-        <v>2877.4</v>
+        <v>2928.15</v>
       </c>
       <c r="L28" t="n">
-        <v>2927.85</v>
+        <v>2943.03</v>
       </c>
       <c r="M28" t="n">
-        <v>2953.4</v>
+        <v>2980.45</v>
       </c>
       <c r="N28" t="n">
-        <v>2978.95</v>
+        <v>3017.87</v>
       </c>
       <c r="O28" t="n">
-        <v>3054.3</v>
+        <v>3010.2</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2897,78 +2897,76 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2954</v>
+        <v>2950</v>
       </c>
       <c r="C29" t="n">
-        <v>2976.3</v>
+        <v>2994.6</v>
       </c>
       <c r="D29" t="n">
-        <v>2905.3</v>
+        <v>2948.4</v>
       </c>
       <c r="E29" t="n">
-        <v>2938</v>
+        <v>2989.3</v>
       </c>
       <c r="F29" t="n">
-        <v>-16.3</v>
+        <v>51.3</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0175</v>
       </c>
       <c r="H29" t="n">
-        <v>71</v>
+        <v>46.2</v>
       </c>
       <c r="I29" t="n">
-        <v>2853.3</v>
+        <v>2834.3</v>
       </c>
       <c r="J29" t="n">
-        <v>2913.28</v>
+        <v>2865.6</v>
       </c>
       <c r="K29" t="n">
-        <v>2928.15</v>
+        <v>2902.5</v>
       </c>
       <c r="L29" t="n">
-        <v>2943.03</v>
+        <v>2939.4</v>
       </c>
       <c r="M29" t="n">
-        <v>2980.45</v>
+        <v>2973.5</v>
       </c>
       <c r="N29" t="n">
-        <v>3017.87</v>
+        <v>3007.6</v>
       </c>
       <c r="O29" t="n">
-        <v>3010.2</v>
+        <v>3047.3</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2983,57 +2981,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2950</v>
+        <v>2992.4</v>
       </c>
       <c r="C30" t="n">
-        <v>2994.6</v>
+        <v>3051.8</v>
       </c>
       <c r="D30" t="n">
-        <v>2948.4</v>
+        <v>2986.1</v>
       </c>
       <c r="E30" t="n">
-        <v>2989.3</v>
+        <v>3044.7</v>
       </c>
       <c r="F30" t="n">
-        <v>51.3</v>
+        <v>55.4</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0185</v>
       </c>
       <c r="H30" t="n">
-        <v>46.2</v>
+        <v>65.7</v>
       </c>
       <c r="I30" t="n">
-        <v>2834.3</v>
+        <v>2902.2</v>
       </c>
       <c r="J30" t="n">
-        <v>2865.6</v>
+        <v>2952</v>
       </c>
       <c r="K30" t="n">
-        <v>2902.5</v>
+        <v>2966.2</v>
       </c>
       <c r="L30" t="n">
-        <v>2939.4</v>
+        <v>2980.4</v>
       </c>
       <c r="M30" t="n">
-        <v>2973.5</v>
+        <v>3012.4</v>
       </c>
       <c r="N30" t="n">
-        <v>3007.6</v>
+        <v>3044.4</v>
       </c>
       <c r="O30" t="n">
-        <v>3047.3</v>
+        <v>3040.8</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3044,80 +3042,80 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W30" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W30" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2992.4</v>
+        <v>3049.1</v>
       </c>
       <c r="C31" t="n">
-        <v>3051.8</v>
+        <v>3058.3</v>
       </c>
       <c r="D31" t="n">
-        <v>2986.1</v>
+        <v>3023.3</v>
       </c>
       <c r="E31" t="n">
-        <v>3044.7</v>
+        <v>3025.4</v>
       </c>
       <c r="F31" t="n">
-        <v>55.4</v>
+        <v>-19.3</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0063</v>
       </c>
       <c r="H31" t="n">
-        <v>65.7</v>
+        <v>35</v>
       </c>
       <c r="I31" t="n">
-        <v>2902.2</v>
+        <v>2920.4</v>
       </c>
       <c r="J31" t="n">
-        <v>2952</v>
+        <v>2991.87</v>
       </c>
       <c r="K31" t="n">
-        <v>2966.2</v>
+        <v>3011.85</v>
       </c>
       <c r="L31" t="n">
-        <v>2980.4</v>
+        <v>3031.83</v>
       </c>
       <c r="M31" t="n">
-        <v>3012.4</v>
+        <v>3077.55</v>
       </c>
       <c r="N31" t="n">
-        <v>3044.4</v>
+        <v>3123.27</v>
       </c>
       <c r="O31" t="n">
-        <v>3040.8</v>
+        <v>3117.5</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3130,78 +3128,76 @@
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v/>
       </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3049.1</v>
+        <v>3028.5</v>
       </c>
       <c r="C32" t="n">
-        <v>3058.3</v>
+        <v>3041</v>
       </c>
       <c r="D32" t="n">
-        <v>3023.3</v>
+        <v>3004.9</v>
       </c>
       <c r="E32" t="n">
-        <v>3025.4</v>
+        <v>3009.1</v>
       </c>
       <c r="F32" t="n">
-        <v>-19.3</v>
+        <v>-16.3</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0054</v>
       </c>
       <c r="H32" t="n">
-        <v>35</v>
+        <v>36.1</v>
       </c>
       <c r="I32" t="n">
-        <v>2920.4</v>
+        <v>2988.3</v>
       </c>
       <c r="J32" t="n">
-        <v>2991.87</v>
+        <v>2982.7</v>
       </c>
       <c r="K32" t="n">
-        <v>3011.85</v>
+        <v>3007.9</v>
       </c>
       <c r="L32" t="n">
-        <v>3031.83</v>
+        <v>3033.1</v>
       </c>
       <c r="M32" t="n">
-        <v>3077.55</v>
+        <v>3042.9</v>
       </c>
       <c r="N32" t="n">
-        <v>3123.27</v>
+        <v>3052.7</v>
       </c>
       <c r="O32" t="n">
-        <v>3117.5</v>
+        <v>3093.3</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3209,12 +3205,14 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3233,57 +3231,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3028.5</v>
+        <v>3008.5</v>
       </c>
       <c r="C33" t="n">
-        <v>3041</v>
+        <v>3046.8</v>
       </c>
       <c r="D33" t="n">
-        <v>3004.9</v>
+        <v>3002</v>
       </c>
       <c r="E33" t="n">
-        <v>3009.1</v>
+        <v>3041.6</v>
       </c>
       <c r="F33" t="n">
-        <v>-16.3</v>
+        <v>32.5</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0054</v>
+        <v>0.0108</v>
       </c>
       <c r="H33" t="n">
-        <v>36.1</v>
+        <v>44.8</v>
       </c>
       <c r="I33" t="n">
-        <v>2988.3</v>
+        <v>2968.8</v>
       </c>
       <c r="J33" t="n">
-        <v>2982.7</v>
+        <v>2966.08</v>
       </c>
       <c r="K33" t="n">
-        <v>3007.9</v>
+        <v>2991.05</v>
       </c>
       <c r="L33" t="n">
-        <v>3033.1</v>
+        <v>3016.03</v>
       </c>
       <c r="M33" t="n">
-        <v>3042.9</v>
+        <v>3027.15</v>
       </c>
       <c r="N33" t="n">
-        <v>3052.7</v>
+        <v>3038.28</v>
       </c>
       <c r="O33" t="n">
-        <v>3093.3</v>
+        <v>3077.1</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3291,22 +3289,24 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
@@ -3317,57 +3317,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3008.5</v>
+        <v>3038.9</v>
       </c>
       <c r="C34" t="n">
-        <v>3046.8</v>
+        <v>3044.6</v>
       </c>
       <c r="D34" t="n">
-        <v>3002</v>
+        <v>3016</v>
       </c>
       <c r="E34" t="n">
-        <v>3041.6</v>
+        <v>3025</v>
       </c>
       <c r="F34" t="n">
-        <v>32.5</v>
+        <v>-16.6</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0108</v>
+        <v>-0.0055</v>
       </c>
       <c r="H34" t="n">
-        <v>44.8</v>
+        <v>28.6</v>
       </c>
       <c r="I34" t="n">
-        <v>2968.8</v>
+        <v>2957.2</v>
       </c>
       <c r="J34" t="n">
-        <v>2966.08</v>
+        <v>3005.4</v>
       </c>
       <c r="K34" t="n">
-        <v>2991.05</v>
+        <v>3019.2</v>
       </c>
       <c r="L34" t="n">
-        <v>3016.03</v>
+        <v>3033</v>
       </c>
       <c r="M34" t="n">
-        <v>3027.15</v>
+        <v>3064</v>
       </c>
       <c r="N34" t="n">
-        <v>3038.28</v>
+        <v>3095</v>
       </c>
       <c r="O34" t="n">
-        <v>3077.1</v>
+        <v>3091.6</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3375,23 +3375,21 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3403,57 +3401,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3038.9</v>
+        <v>3024.7</v>
       </c>
       <c r="C35" t="n">
-        <v>3044.6</v>
+        <v>3045.8</v>
       </c>
       <c r="D35" t="n">
-        <v>3016</v>
+        <v>3019.9</v>
       </c>
       <c r="E35" t="n">
-        <v>3025</v>
+        <v>3035.5</v>
       </c>
       <c r="F35" t="n">
-        <v>-16.6</v>
+        <v>10.5</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0035</v>
       </c>
       <c r="H35" t="n">
-        <v>28.6</v>
+        <v>25.9</v>
       </c>
       <c r="I35" t="n">
-        <v>2957.2</v>
+        <v>2987.4</v>
       </c>
       <c r="J35" t="n">
-        <v>3005.4</v>
+        <v>2993.75</v>
       </c>
       <c r="K35" t="n">
-        <v>3019.2</v>
+        <v>3010.7</v>
       </c>
       <c r="L35" t="n">
-        <v>3033</v>
+        <v>3027.65</v>
       </c>
       <c r="M35" t="n">
-        <v>3064</v>
+        <v>3039.3</v>
       </c>
       <c r="N35" t="n">
-        <v>3095</v>
+        <v>3050.95</v>
       </c>
       <c r="O35" t="n">
-        <v>3091.6</v>
+        <v>3073.2</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3461,19 +3459,19 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
@@ -3485,59 +3483,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3024.7</v>
+        <v>3036.1</v>
       </c>
       <c r="C36" t="n">
-        <v>3045.8</v>
+        <v>3060</v>
       </c>
       <c r="D36" t="n">
-        <v>3019.9</v>
+        <v>3033.1</v>
       </c>
       <c r="E36" t="n">
-        <v>3035.5</v>
+        <v>3052.8</v>
       </c>
       <c r="F36" t="n">
-        <v>10.5</v>
+        <v>17.3</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0057</v>
       </c>
       <c r="H36" t="n">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
       <c r="I36" t="n">
-        <v>2987.4</v>
+        <v>2994</v>
       </c>
       <c r="J36" t="n">
-        <v>2993.75</v>
+        <v>3010.92</v>
       </c>
       <c r="K36" t="n">
-        <v>3010.7</v>
+        <v>3022.55</v>
       </c>
       <c r="L36" t="n">
-        <v>3027.65</v>
+        <v>3034.17</v>
       </c>
       <c r="M36" t="n">
-        <v>3039.3</v>
+        <v>3048.45</v>
       </c>
       <c r="N36" t="n">
-        <v>3050.95</v>
+        <v>3062.73</v>
       </c>
       <c r="O36" t="n">
-        <v>3073.2</v>
+        <v>3071.7</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3548,7 +3542,7 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="10" t="inlineStr">
+      <c r="S36" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3574,50 +3568,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3036.1</v>
+        <v>3056.2</v>
       </c>
       <c r="C37" t="n">
-        <v>3060</v>
+        <v>3076.3</v>
       </c>
       <c r="D37" t="n">
-        <v>3033.1</v>
+        <v>3052.5</v>
       </c>
       <c r="E37" t="n">
-        <v>3052.8</v>
+        <v>3060.2</v>
       </c>
       <c r="F37" t="n">
-        <v>17.3</v>
+        <v>7.4</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0024</v>
       </c>
       <c r="H37" t="n">
-        <v>26.9</v>
+        <v>23.8</v>
       </c>
       <c r="I37" t="n">
-        <v>2994</v>
+        <v>3006.2</v>
       </c>
       <c r="J37" t="n">
-        <v>3010.92</v>
+        <v>3029.03</v>
       </c>
       <c r="K37" t="n">
-        <v>3022.55</v>
+        <v>3039.35</v>
       </c>
       <c r="L37" t="n">
-        <v>3034.17</v>
+        <v>3049.68</v>
       </c>
       <c r="M37" t="n">
-        <v>3048.45</v>
+        <v>3066.25</v>
       </c>
       <c r="N37" t="n">
-        <v>3062.73</v>
+        <v>3082.82</v>
       </c>
       <c r="O37" t="n">
-        <v>3071.7</v>
+        <v>3086.9</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3628,7 +3622,7 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
+      <c r="S37" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3654,50 +3648,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3056.2</v>
+        <v>3062.2</v>
       </c>
       <c r="C38" t="n">
         <v>3076.3</v>
       </c>
       <c r="D38" t="n">
-        <v>3052.5</v>
+        <v>3051.7</v>
       </c>
       <c r="E38" t="n">
-        <v>3060.2</v>
+        <v>3074.9</v>
       </c>
       <c r="F38" t="n">
-        <v>7.4</v>
+        <v>14.7</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0048</v>
       </c>
       <c r="H38" t="n">
-        <v>23.8</v>
+        <v>24.6</v>
       </c>
       <c r="I38" t="n">
-        <v>3006.2</v>
+        <v>3028.7</v>
       </c>
       <c r="J38" t="n">
-        <v>3029.03</v>
+        <v>3034.3</v>
       </c>
       <c r="K38" t="n">
-        <v>3039.35</v>
+        <v>3048.3</v>
       </c>
       <c r="L38" t="n">
-        <v>3049.68</v>
+        <v>3062.3</v>
       </c>
       <c r="M38" t="n">
-        <v>3066.25</v>
+        <v>3072.1</v>
       </c>
       <c r="N38" t="n">
-        <v>3082.82</v>
+        <v>3081.9</v>
       </c>
       <c r="O38" t="n">
-        <v>3086.9</v>
+        <v>3100.1</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3708,7 +3702,7 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="S38" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3729,55 +3723,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3062.2</v>
+        <v>3073.5</v>
       </c>
       <c r="C39" t="n">
-        <v>3076.3</v>
+        <v>3079.9</v>
       </c>
       <c r="D39" t="n">
-        <v>3051.7</v>
+        <v>3055.9</v>
       </c>
       <c r="E39" t="n">
-        <v>3074.9</v>
+        <v>3064.9</v>
       </c>
       <c r="F39" t="n">
-        <v>14.7</v>
+        <v>-10</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.0033</v>
       </c>
       <c r="H39" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="I39" t="n">
-        <v>3028.7</v>
+        <v>3027.1</v>
       </c>
       <c r="J39" t="n">
-        <v>3034.3</v>
+        <v>3055.75</v>
       </c>
       <c r="K39" t="n">
-        <v>3048.3</v>
+        <v>3062.6</v>
       </c>
       <c r="L39" t="n">
-        <v>3062.3</v>
+        <v>3069.45</v>
       </c>
       <c r="M39" t="n">
-        <v>3072.1</v>
+        <v>3087.2</v>
       </c>
       <c r="N39" t="n">
-        <v>3081.9</v>
+        <v>3104.95</v>
       </c>
       <c r="O39" t="n">
-        <v>3100.1</v>
+        <v>3100.9</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3785,18 +3783,18 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3818,63 +3816,67 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3073.5</v>
+        <v>3063.7</v>
       </c>
       <c r="C40" t="n">
-        <v>3079.9</v>
+        <v>3066.6</v>
       </c>
       <c r="D40" t="n">
-        <v>3055.9</v>
+        <v>3024.1</v>
       </c>
       <c r="E40" t="n">
-        <v>3064.9</v>
+        <v>3026.4</v>
       </c>
       <c r="F40" t="n">
-        <v>-10</v>
+        <v>-38.5</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0126</v>
       </c>
       <c r="H40" t="n">
-        <v>24</v>
+        <v>42.5</v>
       </c>
       <c r="I40" t="n">
-        <v>3027.1</v>
+        <v>3031.9</v>
       </c>
       <c r="J40" t="n">
-        <v>3055.75</v>
+        <v>3039.4</v>
       </c>
       <c r="K40" t="n">
-        <v>3062.6</v>
+        <v>3052.9</v>
       </c>
       <c r="L40" t="n">
-        <v>3069.45</v>
+        <v>3066.4</v>
       </c>
       <c r="M40" t="n">
-        <v>3087.2</v>
+        <v>3076.9</v>
       </c>
       <c r="N40" t="n">
-        <v>3104.95</v>
+        <v>3087.4</v>
       </c>
       <c r="O40" t="n">
-        <v>3100.9</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
+        <v>3103.9</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3888,88 +3890,80 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W40" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3063.7</v>
+        <v>3025.9</v>
       </c>
       <c r="C41" t="n">
-        <v>3066.6</v>
+        <v>3059.1</v>
       </c>
       <c r="D41" t="n">
-        <v>3024.1</v>
+        <v>3019.8</v>
       </c>
       <c r="E41" t="n">
-        <v>3026.4</v>
+        <v>3039.9</v>
       </c>
       <c r="F41" t="n">
-        <v>-38.5</v>
+        <v>13.5</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0045</v>
       </c>
       <c r="H41" t="n">
-        <v>42.5</v>
+        <v>39.3</v>
       </c>
       <c r="I41" t="n">
-        <v>3031.9</v>
+        <v>2981.6</v>
       </c>
       <c r="J41" t="n">
-        <v>3039.4</v>
+        <v>2974.42</v>
       </c>
       <c r="K41" t="n">
-        <v>3052.9</v>
+        <v>3005.15</v>
       </c>
       <c r="L41" t="n">
-        <v>3066.4</v>
+        <v>3035.88</v>
       </c>
       <c r="M41" t="n">
-        <v>3076.9</v>
+        <v>3047.65</v>
       </c>
       <c r="N41" t="n">
-        <v>3087.4</v>
+        <v>3059.42</v>
       </c>
       <c r="O41" t="n">
-        <v>3103.9</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
+        <v>3109.1</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3981,74 +3975,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3025.9</v>
+        <v>3041.4</v>
       </c>
       <c r="C42" t="n">
-        <v>3059.1</v>
+        <v>3048.5</v>
       </c>
       <c r="D42" t="n">
-        <v>3019.8</v>
+        <v>2993.2</v>
       </c>
       <c r="E42" t="n">
-        <v>3039.9</v>
+        <v>2999.2</v>
       </c>
       <c r="F42" t="n">
-        <v>13.5</v>
+        <v>-40.7</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0134</v>
       </c>
       <c r="H42" t="n">
-        <v>39.3</v>
+        <v>55.3</v>
       </c>
       <c r="I42" t="n">
-        <v>2981.6</v>
+        <v>2980.5</v>
       </c>
       <c r="J42" t="n">
-        <v>2974.42</v>
+        <v>3000.82</v>
       </c>
       <c r="K42" t="n">
-        <v>3005.15</v>
+        <v>3020.25</v>
       </c>
       <c r="L42" t="n">
-        <v>3035.88</v>
+        <v>3039.67</v>
       </c>
       <c r="M42" t="n">
-        <v>3047.65</v>
+        <v>3059.55</v>
       </c>
       <c r="N42" t="n">
-        <v>3059.42</v>
+        <v>3079.42</v>
       </c>
       <c r="O42" t="n">
-        <v>3109.1</v>
+        <v>3098.4</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4061,81 +4061,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3041.4</v>
+        <v>2999.6</v>
       </c>
       <c r="C43" t="n">
-        <v>3048.5</v>
+        <v>3026.7</v>
       </c>
       <c r="D43" t="n">
-        <v>2993.2</v>
+        <v>2997.9</v>
       </c>
       <c r="E43" t="n">
-        <v>2999.2</v>
+        <v>3022.1</v>
       </c>
       <c r="F43" t="n">
-        <v>-40.7</v>
+        <v>22.9</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0134</v>
+        <v>0.0076</v>
       </c>
       <c r="H43" t="n">
-        <v>55.3</v>
+        <v>28.8</v>
       </c>
       <c r="I43" t="n">
-        <v>2980.5</v>
+        <v>2937.9</v>
       </c>
       <c r="J43" t="n">
-        <v>3000.82</v>
+        <v>2933.07</v>
       </c>
       <c r="K43" t="n">
-        <v>3020.25</v>
+        <v>2971.55</v>
       </c>
       <c r="L43" t="n">
-        <v>3039.67</v>
+        <v>3010.02</v>
       </c>
       <c r="M43" t="n">
-        <v>3059.55</v>
+        <v>3026.85</v>
       </c>
       <c r="N43" t="n">
-        <v>3079.42</v>
+        <v>3043.67</v>
       </c>
       <c r="O43" t="n">
-        <v>3098.4</v>
+        <v>3103.8</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4147,74 +4141,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2999.6</v>
+        <v>3023</v>
       </c>
       <c r="C44" t="n">
-        <v>3026.7</v>
+        <v>3028.9</v>
       </c>
       <c r="D44" t="n">
-        <v>2997.9</v>
+        <v>2996</v>
       </c>
       <c r="E44" t="n">
-        <v>3022.1</v>
+        <v>3001.6</v>
       </c>
       <c r="F44" t="n">
-        <v>22.9</v>
+        <v>-20.5</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0076</v>
+        <v>-0.0068</v>
       </c>
       <c r="H44" t="n">
-        <v>28.8</v>
+        <v>32.9</v>
       </c>
       <c r="I44" t="n">
-        <v>2937.9</v>
+        <v>2969.1</v>
       </c>
       <c r="J44" t="n">
-        <v>2933.07</v>
+        <v>2998.2</v>
       </c>
       <c r="K44" t="n">
-        <v>2971.55</v>
+        <v>3007.7</v>
       </c>
       <c r="L44" t="n">
-        <v>3010.02</v>
+        <v>3017.2</v>
       </c>
       <c r="M44" t="n">
-        <v>3026.85</v>
+        <v>3036.5</v>
       </c>
       <c r="N44" t="n">
-        <v>3043.67</v>
+        <v>3055.8</v>
       </c>
       <c r="O44" t="n">
-        <v>3103.8</v>
+        <v>3055.5</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4229,79 +4229,77 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3023</v>
+        <v>3004.6</v>
       </c>
       <c r="C45" t="n">
-        <v>3028.9</v>
+        <v>3025.4</v>
       </c>
       <c r="D45" t="n">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="E45" t="n">
-        <v>3001.6</v>
+        <v>3014.4</v>
       </c>
       <c r="F45" t="n">
-        <v>-20.5</v>
+        <v>12.8</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0043</v>
       </c>
       <c r="H45" t="n">
-        <v>32.9</v>
+        <v>28.4</v>
       </c>
       <c r="I45" t="n">
-        <v>2969.1</v>
+        <v>2963.1</v>
       </c>
       <c r="J45" t="n">
-        <v>2998.2</v>
+        <v>2963.28</v>
       </c>
       <c r="K45" t="n">
-        <v>3007.7</v>
+        <v>2985.15</v>
       </c>
       <c r="L45" t="n">
-        <v>3017.2</v>
+        <v>3007.03</v>
       </c>
       <c r="M45" t="n">
-        <v>3036.5</v>
+        <v>3018.05</v>
       </c>
       <c r="N45" t="n">
-        <v>3055.8</v>
+        <v>3029.08</v>
       </c>
       <c r="O45" t="n">
-        <v>3055.5</v>
+        <v>3061.8</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
@@ -4315,57 +4313,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3004.6</v>
+        <v>3014.6</v>
       </c>
       <c r="C46" t="n">
-        <v>3025.4</v>
+        <v>3020.5</v>
       </c>
       <c r="D46" t="n">
-        <v>2997</v>
+        <v>3002.6</v>
       </c>
       <c r="E46" t="n">
-        <v>3014.4</v>
+        <v>3010.1</v>
       </c>
       <c r="F46" t="n">
-        <v>12.8</v>
+        <v>-4.3</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0014</v>
       </c>
       <c r="H46" t="n">
-        <v>28.4</v>
+        <v>17.9</v>
       </c>
       <c r="I46" t="n">
-        <v>2963.1</v>
+        <v>2968.6</v>
       </c>
       <c r="J46" t="n">
-        <v>2963.28</v>
+        <v>2987.6</v>
       </c>
       <c r="K46" t="n">
-        <v>2985.15</v>
+        <v>3000.2</v>
       </c>
       <c r="L46" t="n">
-        <v>3007.03</v>
+        <v>3012.8</v>
       </c>
       <c r="M46" t="n">
-        <v>3018.05</v>
+        <v>3028.6</v>
       </c>
       <c r="N46" t="n">
-        <v>3029.08</v>
+        <v>3044.4</v>
       </c>
       <c r="O46" t="n">
-        <v>3061.8</v>
+        <v>3053.8</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4378,13 +4376,11 @@
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4399,57 +4395,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3014.6</v>
+        <v>3016.9</v>
       </c>
       <c r="C47" t="n">
-        <v>3020.5</v>
+        <v>3024.2</v>
       </c>
       <c r="D47" t="n">
-        <v>3002.6</v>
+        <v>3002.1</v>
       </c>
       <c r="E47" t="n">
-        <v>3010.1</v>
+        <v>3019</v>
       </c>
       <c r="F47" t="n">
-        <v>-4.3</v>
+        <v>8.9</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0014</v>
+        <v>0.003</v>
       </c>
       <c r="H47" t="n">
-        <v>17.9</v>
+        <v>22.1</v>
       </c>
       <c r="I47" t="n">
-        <v>2968.6</v>
+        <v>2984.7</v>
       </c>
       <c r="J47" t="n">
-        <v>2987.6</v>
+        <v>2991.48</v>
       </c>
       <c r="K47" t="n">
-        <v>3000.2</v>
+        <v>3001.15</v>
       </c>
       <c r="L47" t="n">
-        <v>3012.8</v>
+        <v>3010.83</v>
       </c>
       <c r="M47" t="n">
-        <v>3028.6</v>
+        <v>3019.05</v>
       </c>
       <c r="N47" t="n">
-        <v>3044.4</v>
+        <v>3027.28</v>
       </c>
       <c r="O47" t="n">
-        <v>3053.8</v>
+        <v>3038.4</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4462,11 +4458,13 @@
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4481,76 +4479,80 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3016.9</v>
+        <v>3019.6</v>
       </c>
       <c r="C48" t="n">
-        <v>3024.2</v>
+        <v>3025.5</v>
       </c>
       <c r="D48" t="n">
-        <v>3002.1</v>
+        <v>2976.6</v>
       </c>
       <c r="E48" t="n">
-        <v>3019</v>
+        <v>2977.5</v>
       </c>
       <c r="F48" t="n">
-        <v>8.9</v>
+        <v>-41.5</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0137</v>
       </c>
       <c r="H48" t="n">
-        <v>22.1</v>
+        <v>48.9</v>
       </c>
       <c r="I48" t="n">
-        <v>2984.7</v>
+        <v>2980</v>
       </c>
       <c r="J48" t="n">
-        <v>2991.48</v>
+        <v>2999.83</v>
       </c>
       <c r="K48" t="n">
-        <v>3001.15</v>
+        <v>3007.95</v>
       </c>
       <c r="L48" t="n">
-        <v>3010.83</v>
+        <v>3016.08</v>
       </c>
       <c r="M48" t="n">
-        <v>3019.05</v>
+        <v>3030.05</v>
       </c>
       <c r="N48" t="n">
-        <v>3027.28</v>
+        <v>3044.02</v>
       </c>
       <c r="O48" t="n">
-        <v>3038.4</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+        <v>3046.3</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4565,74 +4567,70 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3019.6</v>
+        <v>2971</v>
       </c>
       <c r="C49" t="n">
-        <v>3025.5</v>
+        <v>2982.5</v>
       </c>
       <c r="D49" t="n">
-        <v>2976.6</v>
+        <v>2946.1</v>
       </c>
       <c r="E49" t="n">
-        <v>2977.5</v>
+        <v>2958.7</v>
       </c>
       <c r="F49" t="n">
-        <v>-41.5</v>
+        <v>-18.8</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0063</v>
       </c>
       <c r="H49" t="n">
-        <v>48.9</v>
+        <v>36.4</v>
       </c>
       <c r="I49" t="n">
-        <v>2980</v>
+        <v>2927.7</v>
       </c>
       <c r="J49" t="n">
-        <v>2999.83</v>
+        <v>2916.83</v>
       </c>
       <c r="K49" t="n">
-        <v>3007.95</v>
+        <v>2953.05</v>
       </c>
       <c r="L49" t="n">
-        <v>3016.08</v>
+        <v>2989.28</v>
       </c>
       <c r="M49" t="n">
-        <v>3030.05</v>
+        <v>3001.95</v>
       </c>
       <c r="N49" t="n">
-        <v>3044.02</v>
+        <v>3014.62</v>
       </c>
       <c r="O49" t="n">
-        <v>3046.3</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
+        <v>3074.4</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4651,72 +4649,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2971</v>
+        <v>2958</v>
       </c>
       <c r="C50" t="n">
-        <v>2982.5</v>
+        <v>2964.6</v>
       </c>
       <c r="D50" t="n">
-        <v>2946.1</v>
+        <v>2918.9</v>
       </c>
       <c r="E50" t="n">
-        <v>2958.7</v>
+        <v>2924.7</v>
       </c>
       <c r="F50" t="n">
-        <v>-18.8</v>
+        <v>-34</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0115</v>
       </c>
       <c r="H50" t="n">
-        <v>36.4</v>
+        <v>45.7</v>
       </c>
       <c r="I50" t="n">
-        <v>2927.7</v>
+        <v>2909.7</v>
       </c>
       <c r="J50" t="n">
-        <v>2916.83</v>
+        <v>2919.5</v>
       </c>
       <c r="K50" t="n">
-        <v>2953.05</v>
+        <v>2940.5</v>
       </c>
       <c r="L50" t="n">
-        <v>2989.28</v>
+        <v>2961.5</v>
       </c>
       <c r="M50" t="n">
-        <v>3001.95</v>
+        <v>2976.9</v>
       </c>
       <c r="N50" t="n">
-        <v>3014.62</v>
+        <v>2992.3</v>
       </c>
       <c r="O50" t="n">
-        <v>3074.4</v>
+        <v>3018.9</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4740,75 +4736,75 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2958</v>
+        <v>2926.4</v>
       </c>
       <c r="C51" t="n">
-        <v>2964.6</v>
+        <v>2962.5</v>
       </c>
       <c r="D51" t="n">
-        <v>2918.9</v>
+        <v>2914.5</v>
       </c>
       <c r="E51" t="n">
-        <v>2924.7</v>
+        <v>2958.8</v>
       </c>
       <c r="F51" t="n">
-        <v>-34</v>
+        <v>34.1</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0.0117</v>
       </c>
       <c r="H51" t="n">
-        <v>45.7</v>
+        <v>48</v>
       </c>
       <c r="I51" t="n">
-        <v>2909.7</v>
+        <v>2873.2</v>
       </c>
       <c r="J51" t="n">
-        <v>2919.5</v>
+        <v>2870.47</v>
       </c>
       <c r="K51" t="n">
-        <v>2940.5</v>
+        <v>2901.85</v>
       </c>
       <c r="L51" t="n">
-        <v>2961.5</v>
+        <v>2933.22</v>
       </c>
       <c r="M51" t="n">
-        <v>2976.9</v>
+        <v>2947.55</v>
       </c>
       <c r="N51" t="n">
-        <v>2992.3</v>
+        <v>2961.88</v>
       </c>
       <c r="O51" t="n">
-        <v>3018.9</v>
+        <v>3010.3</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
@@ -4817,55 +4813,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2926.4</v>
+        <v>2957.6</v>
       </c>
       <c r="C52" t="n">
-        <v>2962.5</v>
+        <v>2983.3</v>
       </c>
       <c r="D52" t="n">
-        <v>2914.5</v>
+        <v>2949.9</v>
       </c>
       <c r="E52" t="n">
-        <v>2958.8</v>
+        <v>2969.7</v>
       </c>
       <c r="F52" t="n">
-        <v>34.1</v>
+        <v>10.9</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0117</v>
+        <v>0.0037</v>
       </c>
       <c r="H52" t="n">
-        <v>48</v>
+        <v>33.4</v>
       </c>
       <c r="I52" t="n">
-        <v>2873.2</v>
+        <v>2866.5</v>
       </c>
       <c r="J52" t="n">
-        <v>2870.47</v>
+        <v>2920.95</v>
       </c>
       <c r="K52" t="n">
-        <v>2901.85</v>
+        <v>2934.8</v>
       </c>
       <c r="L52" t="n">
-        <v>2933.22</v>
+        <v>2948.65</v>
       </c>
       <c r="M52" t="n">
-        <v>2947.55</v>
+        <v>2982.8</v>
       </c>
       <c r="N52" t="n">
-        <v>2961.88</v>
+        <v>3016.95</v>
       </c>
       <c r="O52" t="n">
-        <v>3010.3</v>
+        <v>3010.5</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4876,21 +4876,19 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="10" t="inlineStr">
+      <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
@@ -4901,57 +4899,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2957.6</v>
+        <v>2967.9</v>
       </c>
       <c r="C53" t="n">
-        <v>2983.3</v>
+        <v>2979.3</v>
       </c>
       <c r="D53" t="n">
-        <v>2949.9</v>
+        <v>2949.5</v>
       </c>
       <c r="E53" t="n">
-        <v>2969.7</v>
+        <v>2976.6</v>
       </c>
       <c r="F53" t="n">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0023</v>
       </c>
       <c r="H53" t="n">
-        <v>33.4</v>
+        <v>29.8</v>
       </c>
       <c r="I53" t="n">
-        <v>2866.5</v>
+        <v>2916.5</v>
       </c>
       <c r="J53" t="n">
-        <v>2920.95</v>
+        <v>2937.85</v>
       </c>
       <c r="K53" t="n">
-        <v>2934.8</v>
+        <v>2953</v>
       </c>
       <c r="L53" t="n">
-        <v>2948.65</v>
+        <v>2968.15</v>
       </c>
       <c r="M53" t="n">
-        <v>2982.8</v>
+        <v>2986.4</v>
       </c>
       <c r="N53" t="n">
-        <v>3016.95</v>
+        <v>3004.65</v>
       </c>
       <c r="O53" t="n">
-        <v>3010.5</v>
+        <v>3016.7</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4959,18 +4957,18 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4985,57 +4983,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2967.9</v>
+        <v>2974.7</v>
       </c>
       <c r="C54" t="n">
-        <v>2979.3</v>
+        <v>2977.9</v>
       </c>
       <c r="D54" t="n">
-        <v>2949.5</v>
+        <v>2954.7</v>
       </c>
       <c r="E54" t="n">
-        <v>2976.6</v>
+        <v>2963.6</v>
       </c>
       <c r="F54" t="n">
-        <v>6.9</v>
+        <v>-13</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0044</v>
       </c>
       <c r="H54" t="n">
-        <v>29.8</v>
+        <v>23.2</v>
       </c>
       <c r="I54" t="n">
-        <v>2916.5</v>
+        <v>2919.7</v>
       </c>
       <c r="J54" t="n">
-        <v>2937.85</v>
+        <v>2952.9</v>
       </c>
       <c r="K54" t="n">
-        <v>2953</v>
+        <v>2961.7</v>
       </c>
       <c r="L54" t="n">
-        <v>2968.15</v>
+        <v>2970.5</v>
       </c>
       <c r="M54" t="n">
-        <v>2986.4</v>
+        <v>2991.5</v>
       </c>
       <c r="N54" t="n">
-        <v>3004.65</v>
+        <v>3012.5</v>
       </c>
       <c r="O54" t="n">
-        <v>3016.7</v>
+        <v>3009.1</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5045,12 +5043,12 @@
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5076,63 +5074,67 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2974.7</v>
+        <v>2963.1</v>
       </c>
       <c r="C55" t="n">
-        <v>2977.9</v>
+        <v>2966.2</v>
       </c>
       <c r="D55" t="n">
-        <v>2954.7</v>
+        <v>2919.4</v>
       </c>
       <c r="E55" t="n">
-        <v>2963.6</v>
+        <v>2923</v>
       </c>
       <c r="F55" t="n">
-        <v>-13</v>
+        <v>-40.6</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0137</v>
       </c>
       <c r="H55" t="n">
-        <v>23.2</v>
+        <v>46.8</v>
       </c>
       <c r="I55" t="n">
-        <v>2919.7</v>
+        <v>2931.5</v>
       </c>
       <c r="J55" t="n">
-        <v>2952.9</v>
+        <v>2939.05</v>
       </c>
       <c r="K55" t="n">
-        <v>2961.7</v>
+        <v>2952</v>
       </c>
       <c r="L55" t="n">
-        <v>2970.5</v>
+        <v>2964.95</v>
       </c>
       <c r="M55" t="n">
-        <v>2991.5</v>
+        <v>2975.2</v>
       </c>
       <c r="N55" t="n">
-        <v>3012.5</v>
+        <v>2985.45</v>
       </c>
       <c r="O55" t="n">
-        <v>3009.1</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
+        <v>3001.1</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5151,76 +5153,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2963.1</v>
+        <v>2923.1</v>
       </c>
       <c r="C56" t="n">
-        <v>2966.2</v>
+        <v>2933.8</v>
       </c>
       <c r="D56" t="n">
-        <v>2919.4</v>
+        <v>2887.8</v>
       </c>
       <c r="E56" t="n">
-        <v>2923</v>
+        <v>2893.4</v>
       </c>
       <c r="F56" t="n">
-        <v>-40.6</v>
+        <v>-29.6</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0101</v>
       </c>
       <c r="H56" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="I56" t="n">
-        <v>2931.5</v>
+        <v>2872.6</v>
       </c>
       <c r="J56" t="n">
-        <v>2939.05</v>
+        <v>2866.3</v>
       </c>
       <c r="K56" t="n">
-        <v>2952</v>
+        <v>2899.6</v>
       </c>
       <c r="L56" t="n">
-        <v>2964.95</v>
+        <v>2932.9</v>
       </c>
       <c r="M56" t="n">
-        <v>2975.2</v>
+        <v>2946.4</v>
       </c>
       <c r="N56" t="n">
-        <v>2985.45</v>
+        <v>2959.9</v>
       </c>
       <c r="O56" t="n">
-        <v>3001.1</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
+        <v>3013</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5244,50 +5238,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2923.1</v>
+        <v>2890.9</v>
       </c>
       <c r="C57" t="n">
-        <v>2933.8</v>
+        <v>2929.8</v>
       </c>
       <c r="D57" t="n">
-        <v>2887.8</v>
+        <v>2887.6</v>
       </c>
       <c r="E57" t="n">
-        <v>2893.4</v>
+        <v>2904.5</v>
       </c>
       <c r="F57" t="n">
-        <v>-29.6</v>
+        <v>11.1</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0101</v>
+        <v>0.0038</v>
       </c>
       <c r="H57" t="n">
-        <v>46</v>
+        <v>42.2</v>
       </c>
       <c r="I57" t="n">
-        <v>2872.6</v>
+        <v>2841.8</v>
       </c>
       <c r="J57" t="n">
-        <v>2866.3</v>
+        <v>2838.7</v>
       </c>
       <c r="K57" t="n">
-        <v>2899.6</v>
+        <v>2870.4</v>
       </c>
       <c r="L57" t="n">
-        <v>2932.9</v>
+        <v>2902.1</v>
       </c>
       <c r="M57" t="n">
-        <v>2946.4</v>
+        <v>2916.4</v>
       </c>
       <c r="N57" t="n">
-        <v>2959.9</v>
+        <v>2930.7</v>
       </c>
       <c r="O57" t="n">
-        <v>3013</v>
+        <v>2979.8</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5295,18 +5289,18 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R57" s="6" t="n">
+        <v/>
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5319,55 +5313,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2890.9</v>
+        <v>2892.7</v>
       </c>
       <c r="C58" t="n">
-        <v>2929.8</v>
+        <v>2913.5</v>
       </c>
       <c r="D58" t="n">
-        <v>2887.6</v>
+        <v>2884.3</v>
       </c>
       <c r="E58" t="n">
-        <v>2904.5</v>
+        <v>2894.1</v>
       </c>
       <c r="F58" t="n">
-        <v>11.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0036</v>
       </c>
       <c r="H58" t="n">
-        <v>42.2</v>
+        <v>29.2</v>
       </c>
       <c r="I58" t="n">
-        <v>2841.8</v>
+        <v>2845.4</v>
       </c>
       <c r="J58" t="n">
-        <v>2838.7</v>
+        <v>2860.2</v>
       </c>
       <c r="K58" t="n">
-        <v>2870.4</v>
+        <v>2883.4</v>
       </c>
       <c r="L58" t="n">
-        <v>2902.1</v>
+        <v>2906.6</v>
       </c>
       <c r="M58" t="n">
-        <v>2916.4</v>
+        <v>2925.6</v>
       </c>
       <c r="N58" t="n">
-        <v>2930.7</v>
+        <v>2944.6</v>
       </c>
       <c r="O58" t="n">
-        <v>2979.8</v>
+        <v>2972</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5375,18 +5373,18 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5399,59 +5397,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2892.7</v>
+        <v>2896.4</v>
       </c>
       <c r="C59" t="n">
-        <v>2913.5</v>
+        <v>2896.5</v>
       </c>
       <c r="D59" t="n">
-        <v>2884.3</v>
+        <v>2862.7</v>
       </c>
       <c r="E59" t="n">
-        <v>2894.1</v>
+        <v>2873.1</v>
       </c>
       <c r="F59" t="n">
-        <v>-10.4</v>
+        <v>-21</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0073</v>
       </c>
       <c r="H59" t="n">
-        <v>29.2</v>
+        <v>33.8</v>
       </c>
       <c r="I59" t="n">
-        <v>2845.4</v>
+        <v>2855.1</v>
       </c>
       <c r="J59" t="n">
-        <v>2860.2</v>
+        <v>2862.5</v>
       </c>
       <c r="K59" t="n">
-        <v>2883.4</v>
+        <v>2879.5</v>
       </c>
       <c r="L59" t="n">
-        <v>2906.6</v>
+        <v>2896.5</v>
       </c>
       <c r="M59" t="n">
-        <v>2925.6</v>
+        <v>2908.7</v>
       </c>
       <c r="N59" t="n">
-        <v>2944.6</v>
+        <v>2920.9</v>
       </c>
       <c r="O59" t="n">
-        <v>2972</v>
+        <v>2942.7</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5464,7 +5458,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S59" s="7" t="inlineStr">
+      <c r="S59" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5488,69 +5482,73 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2896.4</v>
+        <v>2875.1</v>
       </c>
       <c r="C60" t="n">
-        <v>2896.5</v>
+        <v>2892.5</v>
       </c>
       <c r="D60" t="n">
-        <v>2862.7</v>
+        <v>2831.9</v>
       </c>
       <c r="E60" t="n">
-        <v>2873.1</v>
+        <v>2861.7</v>
       </c>
       <c r="F60" t="n">
-        <v>-21</v>
+        <v>-11.4</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.004</v>
       </c>
       <c r="H60" t="n">
-        <v>33.8</v>
+        <v>60.6</v>
       </c>
       <c r="I60" t="n">
-        <v>2855.1</v>
+        <v>2828.9</v>
       </c>
       <c r="J60" t="n">
-        <v>2862.5</v>
+        <v>2836.05</v>
       </c>
       <c r="K60" t="n">
-        <v>2879.5</v>
+        <v>2856.2</v>
       </c>
       <c r="L60" t="n">
-        <v>2896.5</v>
+        <v>2876.35</v>
       </c>
       <c r="M60" t="n">
-        <v>2908.7</v>
+        <v>2890</v>
       </c>
       <c r="N60" t="n">
-        <v>2920.9</v>
+        <v>2903.65</v>
       </c>
       <c r="O60" t="n">
-        <v>2942.7</v>
+        <v>2930.3</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S60" s="7" t="inlineStr">
+      <c r="S60" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T60" s="8" t="n">
-        <v/>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5568,74 +5566,70 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2875.1</v>
+        <v>2861.2</v>
       </c>
       <c r="C61" t="n">
-        <v>2892.5</v>
+        <v>2904.6</v>
       </c>
       <c r="D61" t="n">
-        <v>2831.9</v>
+        <v>2859.3</v>
       </c>
       <c r="E61" t="n">
-        <v>2861.7</v>
+        <v>2875.9</v>
       </c>
       <c r="F61" t="n">
-        <v>-11.4</v>
+        <v>14.2</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.005</v>
       </c>
       <c r="H61" t="n">
-        <v>60.6</v>
+        <v>45.3</v>
       </c>
       <c r="I61" t="n">
-        <v>2828.9</v>
+        <v>2771.3</v>
       </c>
       <c r="J61" t="n">
-        <v>2836.05</v>
+        <v>2800.85</v>
       </c>
       <c r="K61" t="n">
-        <v>2856.2</v>
+        <v>2831.4</v>
       </c>
       <c r="L61" t="n">
-        <v>2876.35</v>
+        <v>2861.95</v>
       </c>
       <c r="M61" t="n">
-        <v>2890</v>
+        <v>2892</v>
       </c>
       <c r="N61" t="n">
-        <v>2903.65</v>
+        <v>2922.05</v>
       </c>
       <c r="O61" t="n">
-        <v>2930.3</v>
+        <v>2953.1</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U61" s="8" t="n">
         <v/>
       </c>
@@ -5647,55 +5641,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2893.9</v>
+        <v>2870.5</v>
       </c>
       <c r="C62" t="n">
-        <v>2894.7</v>
+        <v>2883</v>
       </c>
       <c r="D62" t="n">
-        <v>2890.5</v>
+        <v>2856.9</v>
       </c>
       <c r="E62" t="n">
-        <v>2890.9</v>
+        <v>2873.23</v>
       </c>
       <c r="F62" t="n">
-        <v>29.2</v>
+        <v>-2.67</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0009</v>
       </c>
       <c r="H62" t="n">
-        <v>4.2</v>
+        <v>26.1</v>
       </c>
       <c r="I62" t="n">
-        <v>2771.3</v>
+        <v>2814</v>
       </c>
       <c r="J62" t="n">
-        <v>2800.85</v>
+        <v>2827.57</v>
       </c>
       <c r="K62" t="n">
-        <v>2831.4</v>
+        <v>2853.25</v>
       </c>
       <c r="L62" t="n">
-        <v>2861.95</v>
+        <v>2878.92</v>
       </c>
       <c r="M62" t="n">
-        <v>2892</v>
+        <v>2898.55</v>
       </c>
       <c r="N62" t="n">
-        <v>2922.05</v>
+        <v>2918.17</v>
       </c>
       <c r="O62" t="n">
-        <v>2953.1</v>
+        <v>2949.9</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5708,28 +5706,106 @@
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2879.5</v>
+      </c>
+      <c r="C63" t="n">
+        <v>2879.5</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2876.6</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2881.5</v>
+      </c>
+      <c r="F63" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2830.8</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2848.77</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2860.18</v>
+      </c>
+      <c r="L63" t="n">
+        <v>2871.59</v>
+      </c>
+      <c r="M63" t="n">
+        <v>2886.28</v>
+      </c>
+      <c r="N63" t="n">
+        <v>2900.97</v>
+      </c>
+      <c r="O63" t="n">
+        <v>2909.1</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T62" s="8" t="inlineStr">
+      <c r="T63" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2998.4</v>
+        <v>3023.7</v>
       </c>
       <c r="C2" t="n">
-        <v>3041.4</v>
+        <v>3062.4</v>
       </c>
       <c r="D2" t="n">
-        <v>2987.2</v>
+        <v>3010.5</v>
       </c>
       <c r="E2" t="n">
-        <v>3013.5</v>
+        <v>3030.7</v>
       </c>
       <c r="F2" t="n">
-        <v>15.3</v>
+        <v>17.2</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0057</v>
       </c>
       <c r="H2" t="n">
-        <v>54.2</v>
+        <v>51.9</v>
       </c>
       <c r="I2" t="n">
-        <v>2902</v>
+        <v>2933</v>
       </c>
       <c r="J2" t="n">
-        <v>2935.7</v>
+        <v>2958.9</v>
       </c>
       <c r="K2" t="n">
-        <v>2966.6</v>
+        <v>2986.4</v>
       </c>
       <c r="L2" t="n">
-        <v>2997.5</v>
+        <v>3013.9</v>
       </c>
       <c r="M2" t="n">
-        <v>3029.8</v>
+        <v>3040.6</v>
       </c>
       <c r="N2" t="n">
-        <v>3062.1</v>
+        <v>3067.3</v>
       </c>
       <c r="O2" t="n">
-        <v>3091.6</v>
+        <v>3095.6</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,12 +690,12 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U2" s="8" t="n">
@@ -714,50 +714,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3023.7</v>
+        <v>3034.7</v>
       </c>
       <c r="C3" t="n">
-        <v>3062.4</v>
+        <v>3045.7</v>
       </c>
       <c r="D3" t="n">
-        <v>3010.5</v>
+        <v>2999.6</v>
       </c>
       <c r="E3" t="n">
-        <v>3030.7</v>
+        <v>3022.6</v>
       </c>
       <c r="F3" t="n">
-        <v>17.2</v>
+        <v>-8.1</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.0027</v>
       </c>
       <c r="H3" t="n">
-        <v>51.9</v>
+        <v>46.1</v>
       </c>
       <c r="I3" t="n">
-        <v>2933</v>
+        <v>2958.6</v>
       </c>
       <c r="J3" t="n">
-        <v>2958.9</v>
+        <v>2975.93</v>
       </c>
       <c r="K3" t="n">
-        <v>2986.4</v>
+        <v>3004.75</v>
       </c>
       <c r="L3" t="n">
-        <v>3013.9</v>
+        <v>3033.57</v>
       </c>
       <c r="M3" t="n">
-        <v>3040.6</v>
+        <v>3056.65</v>
       </c>
       <c r="N3" t="n">
-        <v>3067.3</v>
+        <v>3079.72</v>
       </c>
       <c r="O3" t="n">
-        <v>3095.6</v>
+        <v>3114.3</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -765,18 +765,18 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -789,55 +789,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3034.7</v>
+        <v>3020.9</v>
       </c>
       <c r="C4" t="n">
-        <v>3045.7</v>
+        <v>3044.9</v>
       </c>
       <c r="D4" t="n">
-        <v>2999.6</v>
+        <v>2987.8</v>
       </c>
       <c r="E4" t="n">
-        <v>3022.6</v>
+        <v>3030.6</v>
       </c>
       <c r="F4" t="n">
-        <v>-8.1</v>
+        <v>8</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0026</v>
       </c>
       <c r="H4" t="n">
-        <v>46.1</v>
+        <v>57.1</v>
       </c>
       <c r="I4" t="n">
-        <v>2958.6</v>
+        <v>2953.5</v>
       </c>
       <c r="J4" t="n">
-        <v>2975.93</v>
+        <v>2976.48</v>
       </c>
       <c r="K4" t="n">
-        <v>3004.75</v>
+        <v>2999.55</v>
       </c>
       <c r="L4" t="n">
-        <v>3033.57</v>
+        <v>3022.63</v>
       </c>
       <c r="M4" t="n">
-        <v>3056.65</v>
+        <v>3045.65</v>
       </c>
       <c r="N4" t="n">
-        <v>3079.72</v>
+        <v>3068.67</v>
       </c>
       <c r="O4" t="n">
-        <v>3114.3</v>
+        <v>3091.8</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -850,9 +854,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -871,57 +875,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3020.9</v>
+        <v>3026.1</v>
       </c>
       <c r="C5" t="n">
-        <v>3044.9</v>
+        <v>3050.6</v>
       </c>
       <c r="D5" t="n">
-        <v>2987.8</v>
+        <v>3015.1</v>
       </c>
       <c r="E5" t="n">
-        <v>3030.6</v>
+        <v>3045.6</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0049</v>
       </c>
       <c r="H5" t="n">
-        <v>57.1</v>
+        <v>35.5</v>
       </c>
       <c r="I5" t="n">
-        <v>2953.5</v>
+        <v>2930.7</v>
       </c>
       <c r="J5" t="n">
-        <v>2976.48</v>
+        <v>2980.63</v>
       </c>
       <c r="K5" t="n">
-        <v>2999.55</v>
+        <v>3002.05</v>
       </c>
       <c r="L5" t="n">
-        <v>3022.63</v>
+        <v>3023.48</v>
       </c>
       <c r="M5" t="n">
-        <v>3045.65</v>
+        <v>3059.15</v>
       </c>
       <c r="N5" t="n">
-        <v>3068.67</v>
+        <v>3094.83</v>
       </c>
       <c r="O5" t="n">
-        <v>3091.8</v>
+        <v>3102</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -929,18 +933,18 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R5" s="6" t="n">
+        <v/>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -953,59 +957,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3026.1</v>
+        <v>3040</v>
       </c>
       <c r="C6" t="n">
-        <v>3050.6</v>
+        <v>3068.4</v>
       </c>
       <c r="D6" t="n">
-        <v>3015.1</v>
+        <v>3023.7</v>
       </c>
       <c r="E6" t="n">
-        <v>3045.6</v>
+        <v>3035.1</v>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>-10.5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.0034</v>
       </c>
       <c r="H6" t="n">
-        <v>35.5</v>
+        <v>44.7</v>
       </c>
       <c r="I6" t="n">
-        <v>2930.7</v>
+        <v>2979.6</v>
       </c>
       <c r="J6" t="n">
-        <v>2980.63</v>
+        <v>3016.48</v>
       </c>
       <c r="K6" t="n">
-        <v>3002.05</v>
+        <v>3027.85</v>
       </c>
       <c r="L6" t="n">
-        <v>3023.48</v>
+        <v>3039.23</v>
       </c>
       <c r="M6" t="n">
-        <v>3059.15</v>
+        <v>3063.35</v>
       </c>
       <c r="N6" t="n">
-        <v>3094.83</v>
+        <v>3087.48</v>
       </c>
       <c r="O6" t="n">
-        <v>3102</v>
+        <v>3086.1</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1013,17 +1013,19 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U6" s="8" t="n">
@@ -1037,55 +1039,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3040</v>
+        <v>3030.9</v>
       </c>
       <c r="C7" t="n">
-        <v>3068.4</v>
+        <v>3062.4</v>
       </c>
       <c r="D7" t="n">
-        <v>3023.7</v>
+        <v>2988.5</v>
       </c>
       <c r="E7" t="n">
-        <v>3035.1</v>
+        <v>3014.2</v>
       </c>
       <c r="F7" t="n">
-        <v>-10.5</v>
+        <v>-20.9</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0069</v>
       </c>
       <c r="H7" t="n">
-        <v>44.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>2979.6</v>
+        <v>2979</v>
       </c>
       <c r="J7" t="n">
-        <v>3016.48</v>
+        <v>2984.93</v>
       </c>
       <c r="K7" t="n">
-        <v>3027.85</v>
+        <v>3012.75</v>
       </c>
       <c r="L7" t="n">
-        <v>3039.23</v>
+        <v>3040.58</v>
       </c>
       <c r="M7" t="n">
-        <v>3063.35</v>
+        <v>3057.45</v>
       </c>
       <c r="N7" t="n">
-        <v>3087.48</v>
+        <v>3074.33</v>
       </c>
       <c r="O7" t="n">
-        <v>3086.1</v>
+        <v>3113.1</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1095,19 +1101,19 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1121,57 +1127,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3030.9</v>
+        <v>3019.7</v>
       </c>
       <c r="C8" t="n">
-        <v>3062.4</v>
+        <v>3042.1</v>
       </c>
       <c r="D8" t="n">
-        <v>2988.5</v>
+        <v>3006.7</v>
       </c>
       <c r="E8" t="n">
-        <v>3014.2</v>
+        <v>3027</v>
       </c>
       <c r="F8" t="n">
-        <v>-20.9</v>
+        <v>12.8</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0042</v>
       </c>
       <c r="H8" t="n">
-        <v>73.90000000000001</v>
+        <v>35.4</v>
       </c>
       <c r="I8" t="n">
-        <v>2979</v>
+        <v>2914.6</v>
       </c>
       <c r="J8" t="n">
-        <v>2984.93</v>
+        <v>2934.68</v>
       </c>
       <c r="K8" t="n">
-        <v>3012.75</v>
+        <v>2977.25</v>
       </c>
       <c r="L8" t="n">
-        <v>3040.58</v>
+        <v>3019.82</v>
       </c>
       <c r="M8" t="n">
-        <v>3057.45</v>
+        <v>3051.15</v>
       </c>
       <c r="N8" t="n">
-        <v>3074.33</v>
+        <v>3082.47</v>
       </c>
       <c r="O8" t="n">
-        <v>3113.1</v>
+        <v>3136.3</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1179,20 +1185,16 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1207,70 +1209,74 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3019.7</v>
+        <v>3033.4</v>
       </c>
       <c r="C9" t="n">
-        <v>3042.1</v>
+        <v>3042.6</v>
       </c>
       <c r="D9" t="n">
-        <v>3006.7</v>
+        <v>2988.8</v>
       </c>
       <c r="E9" t="n">
-        <v>3027</v>
+        <v>2998.8</v>
       </c>
       <c r="F9" t="n">
-        <v>12.8</v>
+        <v>-28.2</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>35.4</v>
+        <v>53.8</v>
       </c>
       <c r="I9" t="n">
-        <v>2914.6</v>
+        <v>2971.3</v>
       </c>
       <c r="J9" t="n">
-        <v>2934.68</v>
+        <v>2992.9</v>
       </c>
       <c r="K9" t="n">
-        <v>2977.25</v>
+        <v>3009.3</v>
       </c>
       <c r="L9" t="n">
-        <v>3019.82</v>
+        <v>3025.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3051.15</v>
+        <v>3044.7</v>
       </c>
       <c r="N9" t="n">
-        <v>3082.47</v>
+        <v>3063.7</v>
       </c>
       <c r="O9" t="n">
-        <v>3136.3</v>
+        <v>3077.5</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1289,71 +1295,69 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3033.4</v>
+        <v>2994.3</v>
       </c>
       <c r="C10" t="n">
-        <v>3042.6</v>
+        <v>3004.3</v>
       </c>
       <c r="D10" t="n">
-        <v>2988.8</v>
+        <v>2943.4</v>
       </c>
       <c r="E10" t="n">
-        <v>2998.8</v>
+        <v>2971.5</v>
       </c>
       <c r="F10" t="n">
-        <v>-28.2</v>
+        <v>-27.3</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0091</v>
       </c>
       <c r="H10" t="n">
-        <v>53.8</v>
+        <v>60.9</v>
       </c>
       <c r="I10" t="n">
-        <v>2971.3</v>
+        <v>2935</v>
       </c>
       <c r="J10" t="n">
-        <v>2992.9</v>
+        <v>2936.55</v>
       </c>
       <c r="K10" t="n">
-        <v>3009.3</v>
+        <v>2971.9</v>
       </c>
       <c r="L10" t="n">
+        <v>3007.25</v>
+      </c>
+      <c r="M10" t="n">
         <v>3025.7</v>
       </c>
-      <c r="M10" t="n">
-        <v>3044.7</v>
-      </c>
       <c r="N10" t="n">
-        <v>3063.7</v>
+        <v>3044.15</v>
       </c>
       <c r="O10" t="n">
-        <v>3077.5</v>
+        <v>3096.4</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -1375,57 +1379,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2994.3</v>
+        <v>2965.8</v>
       </c>
       <c r="C11" t="n">
-        <v>3004.3</v>
+        <v>3014.9</v>
       </c>
       <c r="D11" t="n">
-        <v>2943.4</v>
+        <v>2964.3</v>
       </c>
       <c r="E11" t="n">
-        <v>2971.5</v>
+        <v>3008.4</v>
       </c>
       <c r="F11" t="n">
-        <v>-27.3</v>
+        <v>36.9</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0091</v>
+        <v>0.0124</v>
       </c>
       <c r="H11" t="n">
-        <v>60.9</v>
+        <v>50.6</v>
       </c>
       <c r="I11" t="n">
-        <v>2935</v>
+        <v>2882.5</v>
       </c>
       <c r="J11" t="n">
-        <v>2936.55</v>
+        <v>2909.42</v>
       </c>
       <c r="K11" t="n">
-        <v>2971.9</v>
+        <v>2941.05</v>
       </c>
       <c r="L11" t="n">
-        <v>3007.25</v>
+        <v>2972.67</v>
       </c>
       <c r="M11" t="n">
-        <v>3025.7</v>
+        <v>3001.95</v>
       </c>
       <c r="N11" t="n">
-        <v>3044.15</v>
+        <v>3031.23</v>
       </c>
       <c r="O11" t="n">
-        <v>3096.4</v>
+        <v>3065.2</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1433,19 +1437,19 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
@@ -1457,59 +1461,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2965.8</v>
+        <v>3008.1</v>
       </c>
       <c r="C12" t="n">
-        <v>3014.9</v>
+        <v>3019.5</v>
       </c>
       <c r="D12" t="n">
-        <v>2964.3</v>
+        <v>2970.8</v>
       </c>
       <c r="E12" t="n">
-        <v>3008.4</v>
+        <v>2994</v>
       </c>
       <c r="F12" t="n">
-        <v>36.9</v>
+        <v>-14.4</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0048</v>
       </c>
       <c r="H12" t="n">
-        <v>50.6</v>
+        <v>48.7</v>
       </c>
       <c r="I12" t="n">
-        <v>2882.5</v>
+        <v>2913.7</v>
       </c>
       <c r="J12" t="n">
-        <v>2909.42</v>
+        <v>2967.2</v>
       </c>
       <c r="K12" t="n">
-        <v>2941.05</v>
+        <v>2983.1</v>
       </c>
       <c r="L12" t="n">
-        <v>2972.67</v>
+        <v>2999</v>
       </c>
       <c r="M12" t="n">
-        <v>3001.95</v>
+        <v>3033.7</v>
       </c>
       <c r="N12" t="n">
-        <v>3031.23</v>
+        <v>3068.4</v>
       </c>
       <c r="O12" t="n">
-        <v>3065.2</v>
+        <v>3065.5</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1517,18 +1517,18 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1541,55 +1541,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3008.1</v>
+        <v>2984.7</v>
       </c>
       <c r="C13" t="n">
-        <v>3019.5</v>
+        <v>2995.8</v>
       </c>
       <c r="D13" t="n">
-        <v>2970.8</v>
+        <v>2961.8</v>
       </c>
       <c r="E13" t="n">
-        <v>2994</v>
+        <v>2970.4</v>
       </c>
       <c r="F13" t="n">
-        <v>-14.4</v>
+        <v>-23.6</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>48.7</v>
+        <v>34</v>
       </c>
       <c r="I13" t="n">
-        <v>2913.7</v>
+        <v>2922.1</v>
       </c>
       <c r="J13" t="n">
-        <v>2967.2</v>
+        <v>2944.73</v>
       </c>
       <c r="K13" t="n">
-        <v>2983.1</v>
+        <v>2969.65</v>
       </c>
       <c r="L13" t="n">
-        <v>2999</v>
+        <v>2994.58</v>
       </c>
       <c r="M13" t="n">
-        <v>3033.7</v>
+        <v>3018.35</v>
       </c>
       <c r="N13" t="n">
-        <v>3068.4</v>
+        <v>3042.12</v>
       </c>
       <c r="O13" t="n">
-        <v>3065.5</v>
+        <v>3068.2</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1599,12 +1603,12 @@
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1623,57 +1627,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2984.7</v>
+        <v>2967.2</v>
       </c>
       <c r="C14" t="n">
-        <v>2995.8</v>
+        <v>3029.8</v>
       </c>
       <c r="D14" t="n">
-        <v>2961.8</v>
+        <v>2956.2</v>
       </c>
       <c r="E14" t="n">
-        <v>2970.4</v>
+        <v>2979.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-23.6</v>
+        <v>9.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H14" t="n">
-        <v>34</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>2922.1</v>
+        <v>2927.8</v>
       </c>
       <c r="J14" t="n">
-        <v>2944.73</v>
+        <v>2932.2</v>
       </c>
       <c r="K14" t="n">
-        <v>2969.65</v>
+        <v>2953.4</v>
       </c>
       <c r="L14" t="n">
-        <v>2994.58</v>
+        <v>2974.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3018.35</v>
+        <v>2987.4</v>
       </c>
       <c r="N14" t="n">
-        <v>3042.12</v>
+        <v>3000.2</v>
       </c>
       <c r="O14" t="n">
-        <v>3068.2</v>
+        <v>3029.8</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1681,24 +1685,28 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v/>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
@@ -1707,57 +1715,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2967.2</v>
+        <v>2981.2</v>
       </c>
       <c r="C15" t="n">
-        <v>3029.8</v>
+        <v>3006.1</v>
       </c>
       <c r="D15" t="n">
-        <v>2956.2</v>
+        <v>2974.4</v>
       </c>
       <c r="E15" t="n">
-        <v>2979.9</v>
+        <v>2991.8</v>
       </c>
       <c r="F15" t="n">
-        <v>9.5</v>
+        <v>11.9</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.004</v>
       </c>
       <c r="H15" t="n">
-        <v>73.59999999999999</v>
+        <v>31.7</v>
       </c>
       <c r="I15" t="n">
-        <v>2927.8</v>
+        <v>2882.6</v>
       </c>
       <c r="J15" t="n">
-        <v>2932.2</v>
+        <v>2899.75</v>
       </c>
       <c r="K15" t="n">
-        <v>2953.4</v>
+        <v>2943.1</v>
       </c>
       <c r="L15" t="n">
-        <v>2974.6</v>
+        <v>2986.45</v>
       </c>
       <c r="M15" t="n">
-        <v>2987.4</v>
+        <v>3016.7</v>
       </c>
       <c r="N15" t="n">
-        <v>3000.2</v>
+        <v>3046.95</v>
       </c>
       <c r="O15" t="n">
-        <v>3029.8</v>
+        <v>3103.4</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1773,20 +1781,14 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v/>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
@@ -1802,50 +1804,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2981.2</v>
+        <v>2995.3</v>
       </c>
       <c r="C16" t="n">
-        <v>3006.1</v>
+        <v>3012.8</v>
       </c>
       <c r="D16" t="n">
-        <v>2974.4</v>
+        <v>2972.7</v>
       </c>
       <c r="E16" t="n">
-        <v>2991.8</v>
+        <v>2990.7</v>
       </c>
       <c r="F16" t="n">
-        <v>11.9</v>
+        <v>-1.1</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0004</v>
       </c>
       <c r="H16" t="n">
-        <v>31.7</v>
+        <v>40.1</v>
       </c>
       <c r="I16" t="n">
-        <v>2882.6</v>
+        <v>2942.7</v>
       </c>
       <c r="J16" t="n">
-        <v>2899.75</v>
+        <v>2960.87</v>
       </c>
       <c r="K16" t="n">
-        <v>2943.1</v>
+        <v>2975.95</v>
       </c>
       <c r="L16" t="n">
-        <v>2986.45</v>
+        <v>2991.03</v>
       </c>
       <c r="M16" t="n">
-        <v>3016.7</v>
+        <v>3007.65</v>
       </c>
       <c r="N16" t="n">
-        <v>3046.95</v>
+        <v>3024.28</v>
       </c>
       <c r="O16" t="n">
-        <v>3103.4</v>
+        <v>3037.8</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1853,16 +1855,20 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1877,78 +1883,78 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2995.3</v>
+        <v>2991.7</v>
       </c>
       <c r="C17" t="n">
-        <v>3012.8</v>
+        <v>2994.8</v>
       </c>
       <c r="D17" t="n">
-        <v>2972.7</v>
+        <v>2949.3</v>
       </c>
       <c r="E17" t="n">
-        <v>2990.7</v>
+        <v>2973.5</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1</v>
+        <v>-17.2</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0058</v>
       </c>
       <c r="H17" t="n">
-        <v>40.1</v>
+        <v>45.5</v>
       </c>
       <c r="I17" t="n">
-        <v>2942.7</v>
+        <v>2932.6</v>
       </c>
       <c r="J17" t="n">
-        <v>2960.87</v>
+        <v>2949.57</v>
       </c>
       <c r="K17" t="n">
-        <v>2975.95</v>
+        <v>2970.65</v>
       </c>
       <c r="L17" t="n">
-        <v>2991.03</v>
+        <v>2991.72</v>
       </c>
       <c r="M17" t="n">
-        <v>3007.65</v>
+        <v>3010.75</v>
       </c>
       <c r="N17" t="n">
-        <v>3024.28</v>
+        <v>3029.78</v>
       </c>
       <c r="O17" t="n">
-        <v>3037.8</v>
+        <v>3052.9</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1963,79 +1969,79 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2991.7</v>
+        <v>2964.5</v>
       </c>
       <c r="C18" t="n">
-        <v>2994.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D18" t="n">
-        <v>2949.3</v>
+        <v>2952.7</v>
       </c>
       <c r="E18" t="n">
-        <v>2973.5</v>
+        <v>2955.2</v>
       </c>
       <c r="F18" t="n">
-        <v>-17.2</v>
+        <v>-18.3</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0062</v>
       </c>
       <c r="H18" t="n">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="I18" t="n">
-        <v>2932.6</v>
+        <v>2903.8</v>
       </c>
       <c r="J18" t="n">
-        <v>2949.57</v>
+        <v>2928.72</v>
       </c>
       <c r="K18" t="n">
-        <v>2970.65</v>
+        <v>2950.75</v>
       </c>
       <c r="L18" t="n">
-        <v>2991.72</v>
+        <v>2972.78</v>
       </c>
       <c r="M18" t="n">
-        <v>3010.75</v>
+        <v>2996.25</v>
       </c>
       <c r="N18" t="n">
-        <v>3029.78</v>
+        <v>3019.72</v>
       </c>
       <c r="O18" t="n">
-        <v>3052.9</v>
+        <v>3040.3</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
@@ -2049,57 +2055,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2964.5</v>
+        <v>2955.8</v>
       </c>
       <c r="C19" t="n">
-        <v>2998.7</v>
+        <v>2999.8</v>
       </c>
       <c r="D19" t="n">
-        <v>2952.7</v>
+        <v>2951.1</v>
       </c>
       <c r="E19" t="n">
-        <v>2955.2</v>
+        <v>2997</v>
       </c>
       <c r="F19" t="n">
-        <v>-18.3</v>
+        <v>41.8</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0141</v>
       </c>
       <c r="H19" t="n">
-        <v>46</v>
+        <v>48.7</v>
       </c>
       <c r="I19" t="n">
-        <v>2903.8</v>
+        <v>2906.7</v>
       </c>
       <c r="J19" t="n">
-        <v>2928.72</v>
+        <v>2898.95</v>
       </c>
       <c r="K19" t="n">
-        <v>2950.75</v>
+        <v>2932.2</v>
       </c>
       <c r="L19" t="n">
-        <v>2972.78</v>
+        <v>2965.45</v>
       </c>
       <c r="M19" t="n">
-        <v>2996.25</v>
+        <v>2978.2</v>
       </c>
       <c r="N19" t="n">
-        <v>3019.72</v>
+        <v>2990.95</v>
       </c>
       <c r="O19" t="n">
-        <v>3040.3</v>
+        <v>3044.7</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2107,23 +2113,23 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2142,50 +2148,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2955.8</v>
+        <v>2997</v>
       </c>
       <c r="C20" t="n">
-        <v>2999.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D20" t="n">
-        <v>2951.1</v>
+        <v>2965.5</v>
       </c>
       <c r="E20" t="n">
-        <v>2997</v>
+        <v>2969.8</v>
       </c>
       <c r="F20" t="n">
-        <v>41.8</v>
+        <v>-27.2</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0141</v>
+        <v>-0.0091</v>
       </c>
       <c r="H20" t="n">
-        <v>48.7</v>
+        <v>33.2</v>
       </c>
       <c r="I20" t="n">
-        <v>2906.7</v>
+        <v>2902.4</v>
       </c>
       <c r="J20" t="n">
-        <v>2898.95</v>
+        <v>2959.08</v>
       </c>
       <c r="K20" t="n">
-        <v>2932.2</v>
+        <v>2972.65</v>
       </c>
       <c r="L20" t="n">
-        <v>2965.45</v>
+        <v>2986.23</v>
       </c>
       <c r="M20" t="n">
-        <v>2978.2</v>
+        <v>3021.35</v>
       </c>
       <c r="N20" t="n">
-        <v>2990.95</v>
+        <v>3056.47</v>
       </c>
       <c r="O20" t="n">
-        <v>3044.7</v>
+        <v>3048.5</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2193,24 +2199,22 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
@@ -2221,60 +2225,62 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2997</v>
+        <v>2974.6</v>
       </c>
       <c r="C21" t="n">
-        <v>2998.7</v>
+        <v>2979</v>
       </c>
       <c r="D21" t="n">
-        <v>2965.5</v>
+        <v>2932.1</v>
       </c>
       <c r="E21" t="n">
-        <v>2969.8</v>
+        <v>2951.7</v>
       </c>
       <c r="F21" t="n">
-        <v>-27.2</v>
+        <v>-18.1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0091</v>
+        <v>-0.0061</v>
       </c>
       <c r="H21" t="n">
-        <v>33.2</v>
+        <v>46.9</v>
       </c>
       <c r="I21" t="n">
-        <v>2902.4</v>
+        <v>2932.3</v>
       </c>
       <c r="J21" t="n">
-        <v>2959.08</v>
+        <v>2930.45</v>
       </c>
       <c r="K21" t="n">
-        <v>2972.65</v>
+        <v>2953.2</v>
       </c>
       <c r="L21" t="n">
-        <v>2986.23</v>
+        <v>2975.95</v>
       </c>
       <c r="M21" t="n">
-        <v>3021.35</v>
+        <v>2986.4</v>
       </c>
       <c r="N21" t="n">
-        <v>3056.47</v>
+        <v>2996.85</v>
       </c>
       <c r="O21" t="n">
-        <v>3048.5</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
+        <v>3031.9</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q21" s="6" t="n">
         <v/>
@@ -2305,74 +2311,70 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2974.6</v>
+        <v>2948.5</v>
       </c>
       <c r="C22" t="n">
-        <v>2979</v>
+        <v>2969.7</v>
       </c>
       <c r="D22" t="n">
-        <v>2932.1</v>
+        <v>2934.5</v>
       </c>
       <c r="E22" t="n">
-        <v>2951.7</v>
+        <v>2941.3</v>
       </c>
       <c r="F22" t="n">
-        <v>-18.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0035</v>
       </c>
       <c r="H22" t="n">
-        <v>46.9</v>
+        <v>35.2</v>
       </c>
       <c r="I22" t="n">
-        <v>2932.3</v>
+        <v>2885.2</v>
       </c>
       <c r="J22" t="n">
-        <v>2930.45</v>
+        <v>2902.88</v>
       </c>
       <c r="K22" t="n">
-        <v>2953.2</v>
+        <v>2928.25</v>
       </c>
       <c r="L22" t="n">
-        <v>2975.95</v>
+        <v>2953.62</v>
       </c>
       <c r="M22" t="n">
-        <v>2986.4</v>
+        <v>2975.15</v>
       </c>
       <c r="N22" t="n">
-        <v>2996.85</v>
+        <v>2996.67</v>
       </c>
       <c r="O22" t="n">
-        <v>3031.9</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3025.9</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
       </c>
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2391,57 +2393,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2948.5</v>
+        <v>2955.5</v>
       </c>
       <c r="C23" t="n">
-        <v>2969.7</v>
+        <v>2985.9</v>
       </c>
       <c r="D23" t="n">
-        <v>2934.5</v>
+        <v>2941.2</v>
       </c>
       <c r="E23" t="n">
-        <v>2941.3</v>
+        <v>2960</v>
       </c>
       <c r="F23" t="n">
-        <v>-10.4</v>
+        <v>18.7</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0064</v>
       </c>
       <c r="H23" t="n">
-        <v>35.2</v>
+        <v>44.7</v>
       </c>
       <c r="I23" t="n">
-        <v>2885.2</v>
+        <v>2899.3</v>
       </c>
       <c r="J23" t="n">
-        <v>2902.88</v>
+        <v>2900.7</v>
       </c>
       <c r="K23" t="n">
-        <v>2928.25</v>
+        <v>2923.7</v>
       </c>
       <c r="L23" t="n">
-        <v>2953.62</v>
+        <v>2946.7</v>
       </c>
       <c r="M23" t="n">
-        <v>2975.15</v>
+        <v>2958.9</v>
       </c>
       <c r="N23" t="n">
-        <v>2996.67</v>
+        <v>2971.1</v>
       </c>
       <c r="O23" t="n">
-        <v>3025.9</v>
+        <v>3004.9</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2452,16 +2454,20 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2471,59 +2477,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2955.5</v>
+        <v>2961.5</v>
       </c>
       <c r="C24" t="n">
-        <v>2985.9</v>
+        <v>2968.3</v>
       </c>
       <c r="D24" t="n">
-        <v>2941.2</v>
+        <v>2933.4</v>
       </c>
       <c r="E24" t="n">
-        <v>2960</v>
+        <v>2964.5</v>
       </c>
       <c r="F24" t="n">
-        <v>18.7</v>
+        <v>4.5</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0015</v>
       </c>
       <c r="H24" t="n">
-        <v>44.7</v>
+        <v>34.9</v>
       </c>
       <c r="I24" t="n">
-        <v>2899.3</v>
+        <v>2896.5</v>
       </c>
       <c r="J24" t="n">
-        <v>2900.7</v>
+        <v>2913.53</v>
       </c>
       <c r="K24" t="n">
-        <v>2923.7</v>
+        <v>2937.65</v>
       </c>
       <c r="L24" t="n">
-        <v>2946.7</v>
+        <v>2961.77</v>
       </c>
       <c r="M24" t="n">
-        <v>2958.9</v>
+        <v>2982.35</v>
       </c>
       <c r="N24" t="n">
-        <v>2971.1</v>
+        <v>3002.92</v>
       </c>
       <c r="O24" t="n">
-        <v>3004.9</v>
+        <v>3030.6</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2531,23 +2533,21 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2557,70 +2557,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2961.5</v>
+        <v>2966.9</v>
       </c>
       <c r="C25" t="n">
-        <v>2968.3</v>
+        <v>2978.3</v>
       </c>
       <c r="D25" t="n">
-        <v>2933.4</v>
+        <v>2902.3</v>
       </c>
       <c r="E25" t="n">
-        <v>2964.5</v>
+        <v>2915.4</v>
       </c>
       <c r="F25" t="n">
-        <v>4.5</v>
+        <v>-49.1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0166</v>
       </c>
       <c r="H25" t="n">
-        <v>34.9</v>
+        <v>76</v>
       </c>
       <c r="I25" t="n">
-        <v>2896.5</v>
+        <v>2898.5</v>
       </c>
       <c r="J25" t="n">
-        <v>2913.53</v>
+        <v>2936.42</v>
       </c>
       <c r="K25" t="n">
-        <v>2937.65</v>
+        <v>2947.05</v>
       </c>
       <c r="L25" t="n">
-        <v>2961.77</v>
+        <v>2957.67</v>
       </c>
       <c r="M25" t="n">
-        <v>2982.35</v>
+        <v>2981.95</v>
       </c>
       <c r="N25" t="n">
-        <v>3002.92</v>
+        <v>3006.23</v>
       </c>
       <c r="O25" t="n">
-        <v>3030.6</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
+        <v>3003.2</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2632,88 +2640,84 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W25" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2966.9</v>
+        <v>2906.6</v>
       </c>
       <c r="C26" t="n">
-        <v>2978.3</v>
+        <v>2957.9</v>
       </c>
       <c r="D26" t="n">
-        <v>2902.3</v>
+        <v>2905.6</v>
       </c>
       <c r="E26" t="n">
-        <v>2915.4</v>
+        <v>2954.3</v>
       </c>
       <c r="F26" t="n">
-        <v>-49.1</v>
+        <v>38.9</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0166</v>
+        <v>0.0133</v>
       </c>
       <c r="H26" t="n">
-        <v>76</v>
+        <v>52.3</v>
       </c>
       <c r="I26" t="n">
-        <v>2898.5</v>
+        <v>2826.3</v>
       </c>
       <c r="J26" t="n">
-        <v>2936.42</v>
+        <v>2826.95</v>
       </c>
       <c r="K26" t="n">
-        <v>2947.05</v>
+        <v>2877.4</v>
       </c>
       <c r="L26" t="n">
-        <v>2957.67</v>
+        <v>2927.85</v>
       </c>
       <c r="M26" t="n">
-        <v>2981.95</v>
+        <v>2953.4</v>
       </c>
       <c r="N26" t="n">
-        <v>3006.23</v>
+        <v>2978.95</v>
       </c>
       <c r="O26" t="n">
-        <v>3003.2</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
+        <v>3054.3</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
       <c r="U26" s="8" t="n">
         <v/>
       </c>
@@ -2727,76 +2731,78 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2906.6</v>
+        <v>2954</v>
       </c>
       <c r="C27" t="n">
-        <v>2957.9</v>
+        <v>2976.3</v>
       </c>
       <c r="D27" t="n">
-        <v>2905.6</v>
+        <v>2905.3</v>
       </c>
       <c r="E27" t="n">
-        <v>2954.3</v>
+        <v>2938</v>
       </c>
       <c r="F27" t="n">
-        <v>38.9</v>
+        <v>-16.3</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0055</v>
       </c>
       <c r="H27" t="n">
-        <v>52.3</v>
+        <v>71</v>
       </c>
       <c r="I27" t="n">
-        <v>2826.3</v>
+        <v>2853.3</v>
       </c>
       <c r="J27" t="n">
-        <v>2826.95</v>
+        <v>2913.28</v>
       </c>
       <c r="K27" t="n">
-        <v>2877.4</v>
+        <v>2928.15</v>
       </c>
       <c r="L27" t="n">
-        <v>2927.85</v>
+        <v>2943.03</v>
       </c>
       <c r="M27" t="n">
-        <v>2953.4</v>
+        <v>2980.45</v>
       </c>
       <c r="N27" t="n">
-        <v>2978.95</v>
+        <v>3017.87</v>
       </c>
       <c r="O27" t="n">
-        <v>3054.3</v>
+        <v>3010.2</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2811,78 +2817,76 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2954</v>
+        <v>2950</v>
       </c>
       <c r="C28" t="n">
-        <v>2976.3</v>
+        <v>2994.6</v>
       </c>
       <c r="D28" t="n">
-        <v>2905.3</v>
+        <v>2948.4</v>
       </c>
       <c r="E28" t="n">
-        <v>2938</v>
+        <v>2989.3</v>
       </c>
       <c r="F28" t="n">
-        <v>-16.3</v>
+        <v>51.3</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0175</v>
       </c>
       <c r="H28" t="n">
-        <v>71</v>
+        <v>46.2</v>
       </c>
       <c r="I28" t="n">
-        <v>2853.3</v>
+        <v>2834.3</v>
       </c>
       <c r="J28" t="n">
-        <v>2913.28</v>
+        <v>2865.6</v>
       </c>
       <c r="K28" t="n">
-        <v>2928.15</v>
+        <v>2902.5</v>
       </c>
       <c r="L28" t="n">
-        <v>2943.03</v>
+        <v>2939.4</v>
       </c>
       <c r="M28" t="n">
-        <v>2980.45</v>
+        <v>2973.5</v>
       </c>
       <c r="N28" t="n">
-        <v>3017.87</v>
+        <v>3007.6</v>
       </c>
       <c r="O28" t="n">
-        <v>3010.2</v>
+        <v>3047.3</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2897,57 +2901,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2950</v>
+        <v>2992.4</v>
       </c>
       <c r="C29" t="n">
-        <v>2994.6</v>
+        <v>3051.8</v>
       </c>
       <c r="D29" t="n">
-        <v>2948.4</v>
+        <v>2986.1</v>
       </c>
       <c r="E29" t="n">
-        <v>2989.3</v>
+        <v>3044.7</v>
       </c>
       <c r="F29" t="n">
-        <v>51.3</v>
+        <v>55.4</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0185</v>
       </c>
       <c r="H29" t="n">
-        <v>46.2</v>
+        <v>65.7</v>
       </c>
       <c r="I29" t="n">
-        <v>2834.3</v>
+        <v>2902.2</v>
       </c>
       <c r="J29" t="n">
-        <v>2865.6</v>
+        <v>2952</v>
       </c>
       <c r="K29" t="n">
-        <v>2902.5</v>
+        <v>2966.2</v>
       </c>
       <c r="L29" t="n">
-        <v>2939.4</v>
+        <v>2980.4</v>
       </c>
       <c r="M29" t="n">
-        <v>2973.5</v>
+        <v>3012.4</v>
       </c>
       <c r="N29" t="n">
-        <v>3007.6</v>
+        <v>3044.4</v>
       </c>
       <c r="O29" t="n">
-        <v>3047.3</v>
+        <v>3040.8</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2965,73 +2969,73 @@
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W29" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W29" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2992.4</v>
+        <v>3049.1</v>
       </c>
       <c r="C30" t="n">
-        <v>3051.8</v>
+        <v>3058.3</v>
       </c>
       <c r="D30" t="n">
-        <v>2986.1</v>
+        <v>3023.3</v>
       </c>
       <c r="E30" t="n">
-        <v>3044.7</v>
+        <v>3025.4</v>
       </c>
       <c r="F30" t="n">
-        <v>55.4</v>
+        <v>-19.3</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0063</v>
       </c>
       <c r="H30" t="n">
-        <v>65.7</v>
+        <v>35</v>
       </c>
       <c r="I30" t="n">
-        <v>2902.2</v>
+        <v>2920.4</v>
       </c>
       <c r="J30" t="n">
-        <v>2952</v>
+        <v>2991.87</v>
       </c>
       <c r="K30" t="n">
-        <v>2966.2</v>
+        <v>3011.85</v>
       </c>
       <c r="L30" t="n">
-        <v>2980.4</v>
+        <v>3031.83</v>
       </c>
       <c r="M30" t="n">
-        <v>3012.4</v>
+        <v>3077.55</v>
       </c>
       <c r="N30" t="n">
-        <v>3044.4</v>
+        <v>3123.27</v>
       </c>
       <c r="O30" t="n">
-        <v>3040.8</v>
+        <v>3117.5</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3042,80 +3046,78 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V30" s="8" t="n">
+        <v/>
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3049.1</v>
+        <v>3028.5</v>
       </c>
       <c r="C31" t="n">
-        <v>3058.3</v>
+        <v>3041</v>
       </c>
       <c r="D31" t="n">
-        <v>3023.3</v>
+        <v>3004.9</v>
       </c>
       <c r="E31" t="n">
-        <v>3025.4</v>
+        <v>3009.1</v>
       </c>
       <c r="F31" t="n">
-        <v>-19.3</v>
+        <v>-16.3</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0054</v>
       </c>
       <c r="H31" t="n">
-        <v>35</v>
+        <v>36.1</v>
       </c>
       <c r="I31" t="n">
-        <v>2920.4</v>
+        <v>2988.3</v>
       </c>
       <c r="J31" t="n">
-        <v>2991.87</v>
+        <v>2982.7</v>
       </c>
       <c r="K31" t="n">
-        <v>3011.85</v>
+        <v>3007.9</v>
       </c>
       <c r="L31" t="n">
-        <v>3031.83</v>
+        <v>3033.1</v>
       </c>
       <c r="M31" t="n">
-        <v>3077.55</v>
+        <v>3042.9</v>
       </c>
       <c r="N31" t="n">
-        <v>3123.27</v>
+        <v>3052.7</v>
       </c>
       <c r="O31" t="n">
-        <v>3117.5</v>
+        <v>3093.3</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3123,12 +3125,14 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3147,57 +3151,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3028.5</v>
+        <v>3008.5</v>
       </c>
       <c r="C32" t="n">
-        <v>3041</v>
+        <v>3046.8</v>
       </c>
       <c r="D32" t="n">
-        <v>3004.9</v>
+        <v>3002</v>
       </c>
       <c r="E32" t="n">
-        <v>3009.1</v>
+        <v>3041.6</v>
       </c>
       <c r="F32" t="n">
-        <v>-16.3</v>
+        <v>32.5</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0054</v>
+        <v>0.0108</v>
       </c>
       <c r="H32" t="n">
-        <v>36.1</v>
+        <v>44.8</v>
       </c>
       <c r="I32" t="n">
-        <v>2988.3</v>
+        <v>2968.8</v>
       </c>
       <c r="J32" t="n">
-        <v>2982.7</v>
+        <v>2966.08</v>
       </c>
       <c r="K32" t="n">
-        <v>3007.9</v>
+        <v>2991.05</v>
       </c>
       <c r="L32" t="n">
-        <v>3033.1</v>
+        <v>3016.03</v>
       </c>
       <c r="M32" t="n">
-        <v>3042.9</v>
+        <v>3027.15</v>
       </c>
       <c r="N32" t="n">
-        <v>3052.7</v>
+        <v>3038.28</v>
       </c>
       <c r="O32" t="n">
-        <v>3093.3</v>
+        <v>3077.1</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3205,22 +3209,24 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
@@ -3231,57 +3237,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3008.5</v>
+        <v>3038.9</v>
       </c>
       <c r="C33" t="n">
-        <v>3046.8</v>
+        <v>3044.6</v>
       </c>
       <c r="D33" t="n">
-        <v>3002</v>
+        <v>3016</v>
       </c>
       <c r="E33" t="n">
-        <v>3041.6</v>
+        <v>3025</v>
       </c>
       <c r="F33" t="n">
-        <v>32.5</v>
+        <v>-16.6</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0108</v>
+        <v>-0.0055</v>
       </c>
       <c r="H33" t="n">
-        <v>44.8</v>
+        <v>28.6</v>
       </c>
       <c r="I33" t="n">
-        <v>2968.8</v>
+        <v>2957.2</v>
       </c>
       <c r="J33" t="n">
-        <v>2966.08</v>
+        <v>3005.4</v>
       </c>
       <c r="K33" t="n">
-        <v>2991.05</v>
+        <v>3019.2</v>
       </c>
       <c r="L33" t="n">
-        <v>3016.03</v>
+        <v>3033</v>
       </c>
       <c r="M33" t="n">
-        <v>3027.15</v>
+        <v>3064</v>
       </c>
       <c r="N33" t="n">
-        <v>3038.28</v>
+        <v>3095</v>
       </c>
       <c r="O33" t="n">
-        <v>3077.1</v>
+        <v>3091.6</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3289,24 +3295,22 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
+      <c r="R33" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
@@ -3317,57 +3321,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3038.9</v>
+        <v>3024.7</v>
       </c>
       <c r="C34" t="n">
-        <v>3044.6</v>
+        <v>3045.8</v>
       </c>
       <c r="D34" t="n">
-        <v>3016</v>
+        <v>3019.9</v>
       </c>
       <c r="E34" t="n">
-        <v>3025</v>
+        <v>3035.5</v>
       </c>
       <c r="F34" t="n">
-        <v>-16.6</v>
+        <v>10.5</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0035</v>
       </c>
       <c r="H34" t="n">
-        <v>28.6</v>
+        <v>25.9</v>
       </c>
       <c r="I34" t="n">
-        <v>2957.2</v>
+        <v>2987.4</v>
       </c>
       <c r="J34" t="n">
-        <v>3005.4</v>
+        <v>2993.75</v>
       </c>
       <c r="K34" t="n">
-        <v>3019.2</v>
+        <v>3010.7</v>
       </c>
       <c r="L34" t="n">
-        <v>3033</v>
+        <v>3027.65</v>
       </c>
       <c r="M34" t="n">
-        <v>3064</v>
+        <v>3039.3</v>
       </c>
       <c r="N34" t="n">
-        <v>3095</v>
+        <v>3050.95</v>
       </c>
       <c r="O34" t="n">
-        <v>3091.6</v>
+        <v>3073.2</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3375,19 +3379,19 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
@@ -3399,59 +3403,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3024.7</v>
+        <v>3036.1</v>
       </c>
       <c r="C35" t="n">
-        <v>3045.8</v>
+        <v>3060</v>
       </c>
       <c r="D35" t="n">
-        <v>3019.9</v>
+        <v>3033.1</v>
       </c>
       <c r="E35" t="n">
-        <v>3035.5</v>
+        <v>3052.8</v>
       </c>
       <c r="F35" t="n">
-        <v>10.5</v>
+        <v>17.3</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0057</v>
       </c>
       <c r="H35" t="n">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
       <c r="I35" t="n">
-        <v>2987.4</v>
+        <v>2994</v>
       </c>
       <c r="J35" t="n">
-        <v>2993.75</v>
+        <v>3010.92</v>
       </c>
       <c r="K35" t="n">
-        <v>3010.7</v>
+        <v>3022.55</v>
       </c>
       <c r="L35" t="n">
-        <v>3027.65</v>
+        <v>3034.17</v>
       </c>
       <c r="M35" t="n">
-        <v>3039.3</v>
+        <v>3048.45</v>
       </c>
       <c r="N35" t="n">
-        <v>3050.95</v>
+        <v>3062.73</v>
       </c>
       <c r="O35" t="n">
-        <v>3073.2</v>
+        <v>3071.7</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3488,50 +3488,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3036.1</v>
+        <v>3056.2</v>
       </c>
       <c r="C36" t="n">
-        <v>3060</v>
+        <v>3076.3</v>
       </c>
       <c r="D36" t="n">
-        <v>3033.1</v>
+        <v>3052.5</v>
       </c>
       <c r="E36" t="n">
-        <v>3052.8</v>
+        <v>3060.2</v>
       </c>
       <c r="F36" t="n">
-        <v>17.3</v>
+        <v>7.4</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0024</v>
       </c>
       <c r="H36" t="n">
-        <v>26.9</v>
+        <v>23.8</v>
       </c>
       <c r="I36" t="n">
-        <v>2994</v>
+        <v>3006.2</v>
       </c>
       <c r="J36" t="n">
-        <v>3010.92</v>
+        <v>3029.03</v>
       </c>
       <c r="K36" t="n">
-        <v>3022.55</v>
+        <v>3039.35</v>
       </c>
       <c r="L36" t="n">
-        <v>3034.17</v>
+        <v>3049.68</v>
       </c>
       <c r="M36" t="n">
-        <v>3048.45</v>
+        <v>3066.25</v>
       </c>
       <c r="N36" t="n">
-        <v>3062.73</v>
+        <v>3082.82</v>
       </c>
       <c r="O36" t="n">
-        <v>3071.7</v>
+        <v>3086.9</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3568,50 +3568,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3056.2</v>
+        <v>3062.2</v>
       </c>
       <c r="C37" t="n">
         <v>3076.3</v>
       </c>
       <c r="D37" t="n">
-        <v>3052.5</v>
+        <v>3051.7</v>
       </c>
       <c r="E37" t="n">
-        <v>3060.2</v>
+        <v>3074.9</v>
       </c>
       <c r="F37" t="n">
-        <v>7.4</v>
+        <v>14.7</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0048</v>
       </c>
       <c r="H37" t="n">
-        <v>23.8</v>
+        <v>24.6</v>
       </c>
       <c r="I37" t="n">
-        <v>3006.2</v>
+        <v>3028.7</v>
       </c>
       <c r="J37" t="n">
-        <v>3029.03</v>
+        <v>3034.3</v>
       </c>
       <c r="K37" t="n">
-        <v>3039.35</v>
+        <v>3048.3</v>
       </c>
       <c r="L37" t="n">
-        <v>3049.68</v>
+        <v>3062.3</v>
       </c>
       <c r="M37" t="n">
-        <v>3066.25</v>
+        <v>3072.1</v>
       </c>
       <c r="N37" t="n">
-        <v>3082.82</v>
+        <v>3081.9</v>
       </c>
       <c r="O37" t="n">
-        <v>3086.9</v>
+        <v>3100.1</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3643,55 +3643,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3062.2</v>
+        <v>3073.5</v>
       </c>
       <c r="C38" t="n">
-        <v>3076.3</v>
+        <v>3079.9</v>
       </c>
       <c r="D38" t="n">
-        <v>3051.7</v>
+        <v>3055.9</v>
       </c>
       <c r="E38" t="n">
-        <v>3074.9</v>
+        <v>3064.9</v>
       </c>
       <c r="F38" t="n">
-        <v>14.7</v>
+        <v>-10</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.0033</v>
       </c>
       <c r="H38" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="I38" t="n">
-        <v>3028.7</v>
+        <v>3027.1</v>
       </c>
       <c r="J38" t="n">
-        <v>3034.3</v>
+        <v>3055.75</v>
       </c>
       <c r="K38" t="n">
-        <v>3048.3</v>
+        <v>3062.6</v>
       </c>
       <c r="L38" t="n">
-        <v>3062.3</v>
+        <v>3069.45</v>
       </c>
       <c r="M38" t="n">
-        <v>3072.1</v>
+        <v>3087.2</v>
       </c>
       <c r="N38" t="n">
-        <v>3081.9</v>
+        <v>3104.95</v>
       </c>
       <c r="O38" t="n">
-        <v>3100.1</v>
+        <v>3100.9</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3699,18 +3703,18 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3732,60 +3736,64 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3073.5</v>
+        <v>3063.7</v>
       </c>
       <c r="C39" t="n">
-        <v>3079.9</v>
+        <v>3066.6</v>
       </c>
       <c r="D39" t="n">
-        <v>3055.9</v>
+        <v>3024.1</v>
       </c>
       <c r="E39" t="n">
-        <v>3064.9</v>
+        <v>3026.4</v>
       </c>
       <c r="F39" t="n">
-        <v>-10</v>
+        <v>-38.5</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0126</v>
       </c>
       <c r="H39" t="n">
-        <v>24</v>
+        <v>42.5</v>
       </c>
       <c r="I39" t="n">
-        <v>3027.1</v>
+        <v>3031.9</v>
       </c>
       <c r="J39" t="n">
-        <v>3055.75</v>
+        <v>3039.4</v>
       </c>
       <c r="K39" t="n">
-        <v>3062.6</v>
+        <v>3052.9</v>
       </c>
       <c r="L39" t="n">
-        <v>3069.45</v>
+        <v>3066.4</v>
       </c>
       <c r="M39" t="n">
-        <v>3087.2</v>
+        <v>3076.9</v>
       </c>
       <c r="N39" t="n">
-        <v>3104.95</v>
+        <v>3087.4</v>
       </c>
       <c r="O39" t="n">
-        <v>3100.9</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
+        <v>3103.9</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
@@ -3802,88 +3810,80 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W39" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3063.7</v>
+        <v>3025.9</v>
       </c>
       <c r="C40" t="n">
-        <v>3066.6</v>
+        <v>3059.1</v>
       </c>
       <c r="D40" t="n">
-        <v>3024.1</v>
+        <v>3019.8</v>
       </c>
       <c r="E40" t="n">
-        <v>3026.4</v>
+        <v>3039.9</v>
       </c>
       <c r="F40" t="n">
-        <v>-38.5</v>
+        <v>13.5</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0045</v>
       </c>
       <c r="H40" t="n">
-        <v>42.5</v>
+        <v>39.3</v>
       </c>
       <c r="I40" t="n">
-        <v>3031.9</v>
+        <v>2981.6</v>
       </c>
       <c r="J40" t="n">
-        <v>3039.4</v>
+        <v>2974.42</v>
       </c>
       <c r="K40" t="n">
-        <v>3052.9</v>
+        <v>3005.15</v>
       </c>
       <c r="L40" t="n">
-        <v>3066.4</v>
+        <v>3035.88</v>
       </c>
       <c r="M40" t="n">
-        <v>3076.9</v>
+        <v>3047.65</v>
       </c>
       <c r="N40" t="n">
-        <v>3087.4</v>
+        <v>3059.42</v>
       </c>
       <c r="O40" t="n">
-        <v>3103.9</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
+        <v>3109.1</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3895,75 +3895,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3025.9</v>
+        <v>3041.4</v>
       </c>
       <c r="C41" t="n">
-        <v>3059.1</v>
+        <v>3048.5</v>
       </c>
       <c r="D41" t="n">
-        <v>3019.8</v>
+        <v>2993.2</v>
       </c>
       <c r="E41" t="n">
-        <v>3039.9</v>
+        <v>2999.2</v>
       </c>
       <c r="F41" t="n">
-        <v>13.5</v>
+        <v>-40.7</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0134</v>
       </c>
       <c r="H41" t="n">
-        <v>39.3</v>
+        <v>55.3</v>
       </c>
       <c r="I41" t="n">
-        <v>2981.6</v>
+        <v>2980.5</v>
       </c>
       <c r="J41" t="n">
-        <v>2974.42</v>
+        <v>3000.82</v>
       </c>
       <c r="K41" t="n">
-        <v>3005.15</v>
+        <v>3020.25</v>
       </c>
       <c r="L41" t="n">
-        <v>3035.88</v>
+        <v>3039.67</v>
       </c>
       <c r="M41" t="n">
-        <v>3047.65</v>
+        <v>3059.55</v>
       </c>
       <c r="N41" t="n">
-        <v>3059.42</v>
+        <v>3079.42</v>
       </c>
       <c r="O41" t="n">
-        <v>3109.1</v>
+        <v>3098.4</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3975,81 +3981,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3041.4</v>
+        <v>2999.6</v>
       </c>
       <c r="C42" t="n">
-        <v>3048.5</v>
+        <v>3026.7</v>
       </c>
       <c r="D42" t="n">
-        <v>2993.2</v>
+        <v>2997.9</v>
       </c>
       <c r="E42" t="n">
-        <v>2999.2</v>
+        <v>3022.1</v>
       </c>
       <c r="F42" t="n">
-        <v>-40.7</v>
+        <v>22.9</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0134</v>
+        <v>0.0076</v>
       </c>
       <c r="H42" t="n">
-        <v>55.3</v>
+        <v>28.8</v>
       </c>
       <c r="I42" t="n">
-        <v>2980.5</v>
+        <v>2937.9</v>
       </c>
       <c r="J42" t="n">
-        <v>3000.82</v>
+        <v>2933.07</v>
       </c>
       <c r="K42" t="n">
-        <v>3020.25</v>
+        <v>2971.55</v>
       </c>
       <c r="L42" t="n">
-        <v>3039.67</v>
+        <v>3010.02</v>
       </c>
       <c r="M42" t="n">
-        <v>3059.55</v>
+        <v>3026.85</v>
       </c>
       <c r="N42" t="n">
-        <v>3079.42</v>
+        <v>3043.67</v>
       </c>
       <c r="O42" t="n">
-        <v>3098.4</v>
+        <v>3103.8</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4061,75 +4061,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2999.6</v>
+        <v>3023</v>
       </c>
       <c r="C43" t="n">
-        <v>3026.7</v>
+        <v>3028.9</v>
       </c>
       <c r="D43" t="n">
-        <v>2997.9</v>
+        <v>2996</v>
       </c>
       <c r="E43" t="n">
-        <v>3022.1</v>
+        <v>3001.6</v>
       </c>
       <c r="F43" t="n">
-        <v>22.9</v>
+        <v>-20.5</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0076</v>
+        <v>-0.0068</v>
       </c>
       <c r="H43" t="n">
-        <v>28.8</v>
+        <v>32.9</v>
       </c>
       <c r="I43" t="n">
-        <v>2937.9</v>
+        <v>2969.1</v>
       </c>
       <c r="J43" t="n">
-        <v>2933.07</v>
+        <v>2998.2</v>
       </c>
       <c r="K43" t="n">
-        <v>2971.55</v>
+        <v>3007.7</v>
       </c>
       <c r="L43" t="n">
-        <v>3010.02</v>
+        <v>3017.2</v>
       </c>
       <c r="M43" t="n">
-        <v>3026.85</v>
+        <v>3036.5</v>
       </c>
       <c r="N43" t="n">
-        <v>3043.67</v>
+        <v>3055.8</v>
       </c>
       <c r="O43" t="n">
-        <v>3103.8</v>
+        <v>3055.5</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
+      <c r="Q43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4143,79 +4149,77 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3023</v>
+        <v>3004.6</v>
       </c>
       <c r="C44" t="n">
-        <v>3028.9</v>
+        <v>3025.4</v>
       </c>
       <c r="D44" t="n">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="E44" t="n">
-        <v>3001.6</v>
+        <v>3014.4</v>
       </c>
       <c r="F44" t="n">
-        <v>-20.5</v>
+        <v>12.8</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0043</v>
       </c>
       <c r="H44" t="n">
-        <v>32.9</v>
+        <v>28.4</v>
       </c>
       <c r="I44" t="n">
-        <v>2969.1</v>
+        <v>2963.1</v>
       </c>
       <c r="J44" t="n">
-        <v>2998.2</v>
+        <v>2963.28</v>
       </c>
       <c r="K44" t="n">
-        <v>3007.7</v>
+        <v>2985.15</v>
       </c>
       <c r="L44" t="n">
-        <v>3017.2</v>
+        <v>3007.03</v>
       </c>
       <c r="M44" t="n">
-        <v>3036.5</v>
+        <v>3018.05</v>
       </c>
       <c r="N44" t="n">
-        <v>3055.8</v>
+        <v>3029.08</v>
       </c>
       <c r="O44" t="n">
-        <v>3055.5</v>
+        <v>3061.8</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
@@ -4229,57 +4233,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3004.6</v>
+        <v>3014.6</v>
       </c>
       <c r="C45" t="n">
-        <v>3025.4</v>
+        <v>3020.5</v>
       </c>
       <c r="D45" t="n">
-        <v>2997</v>
+        <v>3002.6</v>
       </c>
       <c r="E45" t="n">
-        <v>3014.4</v>
+        <v>3010.1</v>
       </c>
       <c r="F45" t="n">
-        <v>12.8</v>
+        <v>-4.3</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0014</v>
       </c>
       <c r="H45" t="n">
-        <v>28.4</v>
+        <v>17.9</v>
       </c>
       <c r="I45" t="n">
-        <v>2963.1</v>
+        <v>2968.6</v>
       </c>
       <c r="J45" t="n">
-        <v>2963.28</v>
+        <v>2987.6</v>
       </c>
       <c r="K45" t="n">
-        <v>2985.15</v>
+        <v>3000.2</v>
       </c>
       <c r="L45" t="n">
-        <v>3007.03</v>
+        <v>3012.8</v>
       </c>
       <c r="M45" t="n">
-        <v>3018.05</v>
+        <v>3028.6</v>
       </c>
       <c r="N45" t="n">
-        <v>3029.08</v>
+        <v>3044.4</v>
       </c>
       <c r="O45" t="n">
-        <v>3061.8</v>
+        <v>3053.8</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4290,15 +4294,13 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4313,57 +4315,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3014.6</v>
+        <v>3016.9</v>
       </c>
       <c r="C46" t="n">
-        <v>3020.5</v>
+        <v>3024.2</v>
       </c>
       <c r="D46" t="n">
-        <v>3002.6</v>
+        <v>3002.1</v>
       </c>
       <c r="E46" t="n">
-        <v>3010.1</v>
+        <v>3019</v>
       </c>
       <c r="F46" t="n">
-        <v>-4.3</v>
+        <v>8.9</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0014</v>
+        <v>0.003</v>
       </c>
       <c r="H46" t="n">
-        <v>17.9</v>
+        <v>22.1</v>
       </c>
       <c r="I46" t="n">
-        <v>2968.6</v>
+        <v>2984.7</v>
       </c>
       <c r="J46" t="n">
-        <v>2987.6</v>
+        <v>2991.48</v>
       </c>
       <c r="K46" t="n">
-        <v>3000.2</v>
+        <v>3001.15</v>
       </c>
       <c r="L46" t="n">
-        <v>3012.8</v>
+        <v>3010.83</v>
       </c>
       <c r="M46" t="n">
-        <v>3028.6</v>
+        <v>3019.05</v>
       </c>
       <c r="N46" t="n">
-        <v>3044.4</v>
+        <v>3027.28</v>
       </c>
       <c r="O46" t="n">
-        <v>3053.8</v>
+        <v>3038.4</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4374,13 +4376,15 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4395,77 +4399,81 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3016.9</v>
+        <v>3019.6</v>
       </c>
       <c r="C47" t="n">
-        <v>3024.2</v>
+        <v>3025.5</v>
       </c>
       <c r="D47" t="n">
-        <v>3002.1</v>
+        <v>2976.6</v>
       </c>
       <c r="E47" t="n">
-        <v>3019</v>
+        <v>2977.5</v>
       </c>
       <c r="F47" t="n">
-        <v>8.9</v>
+        <v>-41.5</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0137</v>
       </c>
       <c r="H47" t="n">
-        <v>22.1</v>
+        <v>48.9</v>
       </c>
       <c r="I47" t="n">
-        <v>2984.7</v>
+        <v>2980</v>
       </c>
       <c r="J47" t="n">
-        <v>2991.48</v>
+        <v>2999.83</v>
       </c>
       <c r="K47" t="n">
-        <v>3001.15</v>
+        <v>3007.95</v>
       </c>
       <c r="L47" t="n">
-        <v>3010.83</v>
+        <v>3016.08</v>
       </c>
       <c r="M47" t="n">
-        <v>3019.05</v>
+        <v>3030.05</v>
       </c>
       <c r="N47" t="n">
-        <v>3027.28</v>
+        <v>3044.02</v>
       </c>
       <c r="O47" t="n">
-        <v>3038.4</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
+        <v>3046.3</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
       <c r="U47" s="8" t="n">
         <v/>
       </c>
@@ -4479,73 +4487,69 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3019.6</v>
+        <v>2971</v>
       </c>
       <c r="C48" t="n">
-        <v>3025.5</v>
+        <v>2982.5</v>
       </c>
       <c r="D48" t="n">
-        <v>2976.6</v>
+        <v>2946.1</v>
       </c>
       <c r="E48" t="n">
-        <v>2977.5</v>
+        <v>2958.7</v>
       </c>
       <c r="F48" t="n">
-        <v>-41.5</v>
+        <v>-18.8</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0063</v>
       </c>
       <c r="H48" t="n">
-        <v>48.9</v>
+        <v>36.4</v>
       </c>
       <c r="I48" t="n">
-        <v>2980</v>
+        <v>2927.7</v>
       </c>
       <c r="J48" t="n">
-        <v>2999.83</v>
+        <v>2916.83</v>
       </c>
       <c r="K48" t="n">
-        <v>3007.95</v>
+        <v>2953.05</v>
       </c>
       <c r="L48" t="n">
-        <v>3016.08</v>
+        <v>2989.28</v>
       </c>
       <c r="M48" t="n">
-        <v>3030.05</v>
+        <v>3001.95</v>
       </c>
       <c r="N48" t="n">
-        <v>3044.02</v>
+        <v>3014.62</v>
       </c>
       <c r="O48" t="n">
-        <v>3046.3</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
+        <v>3074.4</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4565,69 +4569,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2971</v>
+        <v>2958</v>
       </c>
       <c r="C49" t="n">
-        <v>2982.5</v>
+        <v>2964.6</v>
       </c>
       <c r="D49" t="n">
-        <v>2946.1</v>
+        <v>2918.9</v>
       </c>
       <c r="E49" t="n">
-        <v>2958.7</v>
+        <v>2924.7</v>
       </c>
       <c r="F49" t="n">
-        <v>-18.8</v>
+        <v>-34</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0115</v>
       </c>
       <c r="H49" t="n">
-        <v>36.4</v>
+        <v>45.7</v>
       </c>
       <c r="I49" t="n">
-        <v>2927.7</v>
+        <v>2909.7</v>
       </c>
       <c r="J49" t="n">
-        <v>2916.83</v>
+        <v>2919.5</v>
       </c>
       <c r="K49" t="n">
-        <v>2953.05</v>
+        <v>2940.5</v>
       </c>
       <c r="L49" t="n">
-        <v>2989.28</v>
+        <v>2961.5</v>
       </c>
       <c r="M49" t="n">
-        <v>3001.95</v>
+        <v>2976.9</v>
       </c>
       <c r="N49" t="n">
-        <v>3014.62</v>
+        <v>2992.3</v>
       </c>
       <c r="O49" t="n">
-        <v>3074.4</v>
+        <v>3018.9</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
@@ -4654,75 +4656,75 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2958</v>
+        <v>2926.4</v>
       </c>
       <c r="C50" t="n">
-        <v>2964.6</v>
+        <v>2962.5</v>
       </c>
       <c r="D50" t="n">
-        <v>2918.9</v>
+        <v>2914.5</v>
       </c>
       <c r="E50" t="n">
-        <v>2924.7</v>
+        <v>2958.8</v>
       </c>
       <c r="F50" t="n">
-        <v>-34</v>
+        <v>34.1</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0.0117</v>
       </c>
       <c r="H50" t="n">
-        <v>45.7</v>
+        <v>48</v>
       </c>
       <c r="I50" t="n">
-        <v>2909.7</v>
+        <v>2873.2</v>
       </c>
       <c r="J50" t="n">
-        <v>2919.5</v>
+        <v>2870.47</v>
       </c>
       <c r="K50" t="n">
-        <v>2940.5</v>
+        <v>2901.85</v>
       </c>
       <c r="L50" t="n">
-        <v>2961.5</v>
+        <v>2933.22</v>
       </c>
       <c r="M50" t="n">
-        <v>2976.9</v>
+        <v>2947.55</v>
       </c>
       <c r="N50" t="n">
-        <v>2992.3</v>
+        <v>2961.88</v>
       </c>
       <c r="O50" t="n">
-        <v>3018.9</v>
+        <v>3010.3</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
@@ -4731,55 +4733,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2926.4</v>
+        <v>2957.6</v>
       </c>
       <c r="C51" t="n">
-        <v>2962.5</v>
+        <v>2983.3</v>
       </c>
       <c r="D51" t="n">
-        <v>2914.5</v>
+        <v>2949.9</v>
       </c>
       <c r="E51" t="n">
-        <v>2958.8</v>
+        <v>2969.7</v>
       </c>
       <c r="F51" t="n">
-        <v>34.1</v>
+        <v>10.9</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0117</v>
+        <v>0.0037</v>
       </c>
       <c r="H51" t="n">
-        <v>48</v>
+        <v>33.4</v>
       </c>
       <c r="I51" t="n">
-        <v>2873.2</v>
+        <v>2866.5</v>
       </c>
       <c r="J51" t="n">
-        <v>2870.47</v>
+        <v>2920.95</v>
       </c>
       <c r="K51" t="n">
-        <v>2901.85</v>
+        <v>2934.8</v>
       </c>
       <c r="L51" t="n">
-        <v>2933.22</v>
+        <v>2948.65</v>
       </c>
       <c r="M51" t="n">
-        <v>2947.55</v>
+        <v>2982.8</v>
       </c>
       <c r="N51" t="n">
-        <v>2961.88</v>
+        <v>3016.95</v>
       </c>
       <c r="O51" t="n">
-        <v>3010.3</v>
+        <v>3010.5</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4797,14 +4803,12 @@
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
@@ -4815,57 +4819,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2957.6</v>
+        <v>2967.9</v>
       </c>
       <c r="C52" t="n">
-        <v>2983.3</v>
+        <v>2979.3</v>
       </c>
       <c r="D52" t="n">
-        <v>2949.9</v>
+        <v>2949.5</v>
       </c>
       <c r="E52" t="n">
-        <v>2969.7</v>
+        <v>2976.6</v>
       </c>
       <c r="F52" t="n">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0023</v>
       </c>
       <c r="H52" t="n">
-        <v>33.4</v>
+        <v>29.8</v>
       </c>
       <c r="I52" t="n">
-        <v>2866.5</v>
+        <v>2916.5</v>
       </c>
       <c r="J52" t="n">
-        <v>2920.95</v>
+        <v>2937.85</v>
       </c>
       <c r="K52" t="n">
-        <v>2934.8</v>
+        <v>2953</v>
       </c>
       <c r="L52" t="n">
-        <v>2948.65</v>
+        <v>2968.15</v>
       </c>
       <c r="M52" t="n">
-        <v>2982.8</v>
+        <v>2986.4</v>
       </c>
       <c r="N52" t="n">
-        <v>3016.95</v>
+        <v>3004.65</v>
       </c>
       <c r="O52" t="n">
-        <v>3010.5</v>
+        <v>3016.7</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4873,18 +4877,18 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4899,57 +4903,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2967.9</v>
+        <v>2974.7</v>
       </c>
       <c r="C53" t="n">
-        <v>2979.3</v>
+        <v>2977.9</v>
       </c>
       <c r="D53" t="n">
-        <v>2949.5</v>
+        <v>2954.7</v>
       </c>
       <c r="E53" t="n">
-        <v>2976.6</v>
+        <v>2963.6</v>
       </c>
       <c r="F53" t="n">
-        <v>6.9</v>
+        <v>-13</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0044</v>
       </c>
       <c r="H53" t="n">
-        <v>29.8</v>
+        <v>23.2</v>
       </c>
       <c r="I53" t="n">
-        <v>2916.5</v>
+        <v>2919.7</v>
       </c>
       <c r="J53" t="n">
-        <v>2937.85</v>
+        <v>2952.9</v>
       </c>
       <c r="K53" t="n">
-        <v>2953</v>
+        <v>2961.7</v>
       </c>
       <c r="L53" t="n">
-        <v>2968.15</v>
+        <v>2970.5</v>
       </c>
       <c r="M53" t="n">
-        <v>2986.4</v>
+        <v>2991.5</v>
       </c>
       <c r="N53" t="n">
-        <v>3004.65</v>
+        <v>3012.5</v>
       </c>
       <c r="O53" t="n">
-        <v>3016.7</v>
+        <v>3009.1</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4959,12 +4963,12 @@
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4990,60 +4994,64 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2974.7</v>
+        <v>2963.1</v>
       </c>
       <c r="C54" t="n">
-        <v>2977.9</v>
+        <v>2966.2</v>
       </c>
       <c r="D54" t="n">
-        <v>2954.7</v>
+        <v>2919.4</v>
       </c>
       <c r="E54" t="n">
-        <v>2963.6</v>
+        <v>2923</v>
       </c>
       <c r="F54" t="n">
-        <v>-13</v>
+        <v>-40.6</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0137</v>
       </c>
       <c r="H54" t="n">
-        <v>23.2</v>
+        <v>46.8</v>
       </c>
       <c r="I54" t="n">
-        <v>2919.7</v>
+        <v>2931.5</v>
       </c>
       <c r="J54" t="n">
-        <v>2952.9</v>
+        <v>2939.05</v>
       </c>
       <c r="K54" t="n">
-        <v>2961.7</v>
+        <v>2952</v>
       </c>
       <c r="L54" t="n">
-        <v>2970.5</v>
+        <v>2964.95</v>
       </c>
       <c r="M54" t="n">
-        <v>2991.5</v>
+        <v>2975.2</v>
       </c>
       <c r="N54" t="n">
-        <v>3012.5</v>
+        <v>2985.45</v>
       </c>
       <c r="O54" t="n">
-        <v>3009.1</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
+        <v>3001.1</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
@@ -5065,73 +5073,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2963.1</v>
+        <v>2923.1</v>
       </c>
       <c r="C55" t="n">
-        <v>2966.2</v>
+        <v>2933.8</v>
       </c>
       <c r="D55" t="n">
-        <v>2919.4</v>
+        <v>2887.8</v>
       </c>
       <c r="E55" t="n">
-        <v>2923</v>
+        <v>2893.4</v>
       </c>
       <c r="F55" t="n">
-        <v>-40.6</v>
+        <v>-29.6</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0101</v>
       </c>
       <c r="H55" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="I55" t="n">
-        <v>2931.5</v>
+        <v>2872.6</v>
       </c>
       <c r="J55" t="n">
-        <v>2939.05</v>
+        <v>2866.3</v>
       </c>
       <c r="K55" t="n">
-        <v>2952</v>
+        <v>2899.6</v>
       </c>
       <c r="L55" t="n">
-        <v>2964.95</v>
+        <v>2932.9</v>
       </c>
       <c r="M55" t="n">
-        <v>2975.2</v>
+        <v>2946.4</v>
       </c>
       <c r="N55" t="n">
-        <v>2985.45</v>
+        <v>2959.9</v>
       </c>
       <c r="O55" t="n">
-        <v>3001.1</v>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
+        <v>3013</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
@@ -5158,50 +5158,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2923.1</v>
+        <v>2890.9</v>
       </c>
       <c r="C56" t="n">
-        <v>2933.8</v>
+        <v>2929.8</v>
       </c>
       <c r="D56" t="n">
-        <v>2887.8</v>
+        <v>2887.6</v>
       </c>
       <c r="E56" t="n">
-        <v>2893.4</v>
+        <v>2904.5</v>
       </c>
       <c r="F56" t="n">
-        <v>-29.6</v>
+        <v>11.1</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0101</v>
+        <v>0.0038</v>
       </c>
       <c r="H56" t="n">
-        <v>46</v>
+        <v>42.2</v>
       </c>
       <c r="I56" t="n">
-        <v>2872.6</v>
+        <v>2841.8</v>
       </c>
       <c r="J56" t="n">
-        <v>2866.3</v>
+        <v>2838.7</v>
       </c>
       <c r="K56" t="n">
-        <v>2899.6</v>
+        <v>2870.4</v>
       </c>
       <c r="L56" t="n">
-        <v>2932.9</v>
+        <v>2902.1</v>
       </c>
       <c r="M56" t="n">
-        <v>2946.4</v>
+        <v>2916.4</v>
       </c>
       <c r="N56" t="n">
-        <v>2959.9</v>
+        <v>2930.7</v>
       </c>
       <c r="O56" t="n">
-        <v>3013</v>
+        <v>2979.8</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5209,18 +5209,18 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5233,55 +5233,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2890.9</v>
+        <v>2892.7</v>
       </c>
       <c r="C57" t="n">
-        <v>2929.8</v>
+        <v>2913.5</v>
       </c>
       <c r="D57" t="n">
-        <v>2887.6</v>
+        <v>2884.3</v>
       </c>
       <c r="E57" t="n">
-        <v>2904.5</v>
+        <v>2894.1</v>
       </c>
       <c r="F57" t="n">
-        <v>11.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0036</v>
       </c>
       <c r="H57" t="n">
-        <v>42.2</v>
+        <v>29.2</v>
       </c>
       <c r="I57" t="n">
-        <v>2841.8</v>
+        <v>2845.4</v>
       </c>
       <c r="J57" t="n">
-        <v>2838.7</v>
+        <v>2860.2</v>
       </c>
       <c r="K57" t="n">
-        <v>2870.4</v>
+        <v>2883.4</v>
       </c>
       <c r="L57" t="n">
-        <v>2902.1</v>
+        <v>2906.6</v>
       </c>
       <c r="M57" t="n">
-        <v>2916.4</v>
+        <v>2925.6</v>
       </c>
       <c r="N57" t="n">
-        <v>2930.7</v>
+        <v>2944.6</v>
       </c>
       <c r="O57" t="n">
-        <v>2979.8</v>
+        <v>2972</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5289,18 +5293,18 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5313,59 +5317,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2892.7</v>
+        <v>2896.4</v>
       </c>
       <c r="C58" t="n">
-        <v>2913.5</v>
+        <v>2896.5</v>
       </c>
       <c r="D58" t="n">
-        <v>2884.3</v>
+        <v>2862.7</v>
       </c>
       <c r="E58" t="n">
-        <v>2894.1</v>
+        <v>2873.1</v>
       </c>
       <c r="F58" t="n">
-        <v>-10.4</v>
+        <v>-21</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0073</v>
       </c>
       <c r="H58" t="n">
-        <v>29.2</v>
+        <v>33.8</v>
       </c>
       <c r="I58" t="n">
-        <v>2845.4</v>
+        <v>2855.1</v>
       </c>
       <c r="J58" t="n">
-        <v>2860.2</v>
+        <v>2862.5</v>
       </c>
       <c r="K58" t="n">
-        <v>2883.4</v>
+        <v>2879.5</v>
       </c>
       <c r="L58" t="n">
-        <v>2906.6</v>
+        <v>2896.5</v>
       </c>
       <c r="M58" t="n">
-        <v>2925.6</v>
+        <v>2908.7</v>
       </c>
       <c r="N58" t="n">
-        <v>2944.6</v>
+        <v>2920.9</v>
       </c>
       <c r="O58" t="n">
-        <v>2972</v>
+        <v>2942.7</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5402,56 +5402,58 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2896.4</v>
+        <v>2875.1</v>
       </c>
       <c r="C59" t="n">
-        <v>2896.5</v>
+        <v>2892.5</v>
       </c>
       <c r="D59" t="n">
-        <v>2862.7</v>
+        <v>2831.9</v>
       </c>
       <c r="E59" t="n">
-        <v>2873.1</v>
+        <v>2861.7</v>
       </c>
       <c r="F59" t="n">
-        <v>-21</v>
+        <v>-11.4</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.004</v>
       </c>
       <c r="H59" t="n">
-        <v>33.8</v>
+        <v>60.6</v>
       </c>
       <c r="I59" t="n">
-        <v>2855.1</v>
+        <v>2828.9</v>
       </c>
       <c r="J59" t="n">
-        <v>2862.5</v>
+        <v>2836.05</v>
       </c>
       <c r="K59" t="n">
-        <v>2879.5</v>
+        <v>2856.2</v>
       </c>
       <c r="L59" t="n">
-        <v>2896.5</v>
+        <v>2876.35</v>
       </c>
       <c r="M59" t="n">
-        <v>2908.7</v>
+        <v>2890</v>
       </c>
       <c r="N59" t="n">
-        <v>2920.9</v>
+        <v>2903.65</v>
       </c>
       <c r="O59" t="n">
-        <v>2942.7</v>
+        <v>2930.3</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
@@ -5463,8 +5465,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T59" s="8" t="n">
-        <v/>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5482,74 +5486,70 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2875.1</v>
+        <v>2861.2</v>
       </c>
       <c r="C60" t="n">
-        <v>2892.5</v>
+        <v>2904.6</v>
       </c>
       <c r="D60" t="n">
-        <v>2831.9</v>
+        <v>2859.3</v>
       </c>
       <c r="E60" t="n">
-        <v>2861.7</v>
+        <v>2875.9</v>
       </c>
       <c r="F60" t="n">
-        <v>-11.4</v>
+        <v>14.2</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.005</v>
       </c>
       <c r="H60" t="n">
-        <v>60.6</v>
+        <v>45.3</v>
       </c>
       <c r="I60" t="n">
-        <v>2828.9</v>
+        <v>2771.3</v>
       </c>
       <c r="J60" t="n">
-        <v>2836.05</v>
+        <v>2800.85</v>
       </c>
       <c r="K60" t="n">
-        <v>2856.2</v>
+        <v>2831.4</v>
       </c>
       <c r="L60" t="n">
-        <v>2876.35</v>
+        <v>2861.95</v>
       </c>
       <c r="M60" t="n">
-        <v>2890</v>
+        <v>2892</v>
       </c>
       <c r="N60" t="n">
-        <v>2903.65</v>
+        <v>2922.05</v>
       </c>
       <c r="O60" t="n">
-        <v>2930.3</v>
+        <v>2953.1</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U60" s="8" t="n">
         <v/>
       </c>
@@ -5561,55 +5561,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2861.2</v>
+        <v>2870.5</v>
       </c>
       <c r="C61" t="n">
-        <v>2904.6</v>
+        <v>2883</v>
       </c>
       <c r="D61" t="n">
-        <v>2859.3</v>
+        <v>2856.9</v>
       </c>
       <c r="E61" t="n">
-        <v>2875.9</v>
+        <v>2873.23</v>
       </c>
       <c r="F61" t="n">
-        <v>14.2</v>
+        <v>-2.67</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0009</v>
       </c>
       <c r="H61" t="n">
-        <v>45.3</v>
+        <v>26.1</v>
       </c>
       <c r="I61" t="n">
-        <v>2771.3</v>
+        <v>2814</v>
       </c>
       <c r="J61" t="n">
-        <v>2800.85</v>
+        <v>2827.57</v>
       </c>
       <c r="K61" t="n">
-        <v>2831.4</v>
+        <v>2853.25</v>
       </c>
       <c r="L61" t="n">
-        <v>2861.95</v>
+        <v>2878.92</v>
       </c>
       <c r="M61" t="n">
-        <v>2892</v>
+        <v>2898.55</v>
       </c>
       <c r="N61" t="n">
-        <v>2922.05</v>
+        <v>2918.17</v>
       </c>
       <c r="O61" t="n">
-        <v>2953.1</v>
+        <v>2949.9</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5620,15 +5624,13 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5641,59 +5643,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2870.5</v>
+        <v>2897.8</v>
       </c>
       <c r="C62" t="n">
-        <v>2883</v>
+        <v>2899.1</v>
       </c>
       <c r="D62" t="n">
-        <v>2856.9</v>
+        <v>2897.8</v>
       </c>
       <c r="E62" t="n">
-        <v>2873.23</v>
+        <v>2898.8</v>
       </c>
       <c r="F62" t="n">
-        <v>-2.67</v>
+        <v>25.57</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0089</v>
       </c>
       <c r="H62" t="n">
-        <v>26.1</v>
+        <v>1.3</v>
       </c>
       <c r="I62" t="n">
-        <v>2814</v>
+        <v>2830.8</v>
       </c>
       <c r="J62" t="n">
-        <v>2827.57</v>
+        <v>2848.77</v>
       </c>
       <c r="K62" t="n">
-        <v>2853.25</v>
+        <v>2860.18</v>
       </c>
       <c r="L62" t="n">
-        <v>2878.92</v>
+        <v>2871.59</v>
       </c>
       <c r="M62" t="n">
-        <v>2898.55</v>
+        <v>2886.28</v>
       </c>
       <c r="N62" t="n">
-        <v>2918.17</v>
+        <v>2900.97</v>
       </c>
       <c r="O62" t="n">
-        <v>2949.9</v>
+        <v>2909.1</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5704,16 +5702,20 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V62" s="8" t="n">
         <v/>
@@ -5723,89 +5725,9 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>2879.5</v>
-      </c>
-      <c r="C63" t="n">
-        <v>2879.5</v>
-      </c>
-      <c r="D63" t="n">
-        <v>2876.6</v>
-      </c>
-      <c r="E63" t="n">
-        <v>2881.5</v>
-      </c>
-      <c r="F63" t="n">
-        <v>8.27</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="H63" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="I63" t="n">
-        <v>2830.8</v>
-      </c>
-      <c r="J63" t="n">
-        <v>2848.77</v>
-      </c>
-      <c r="K63" t="n">
-        <v>2860.18</v>
-      </c>
-      <c r="L63" t="n">
-        <v>2871.59</v>
-      </c>
-      <c r="M63" t="n">
-        <v>2886.28</v>
-      </c>
-      <c r="N63" t="n">
-        <v>2900.97</v>
-      </c>
-      <c r="O63" t="n">
-        <v>2909.1</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>中警訊</t>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5652,25 +5652,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2897.8</v>
+        <v>2879.5</v>
       </c>
       <c r="C62" t="n">
-        <v>2899.1</v>
+        <v>2907.3</v>
       </c>
       <c r="D62" t="n">
-        <v>2897.8</v>
+        <v>2876.6</v>
       </c>
       <c r="E62" t="n">
-        <v>2898.8</v>
+        <v>2897.4</v>
       </c>
       <c r="F62" t="n">
-        <v>25.57</v>
+        <v>24.17</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0089</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H62" t="n">
-        <v>1.3</v>
+        <v>30.7</v>
       </c>
       <c r="I62" t="n">
         <v>2830.8</v>
@@ -5726,6 +5726,92 @@
         </is>
       </c>
       <c r="X62" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2897.8</v>
+      </c>
+      <c r="C63" t="n">
+        <v>2925.6</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2884.2</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2924</v>
+      </c>
+      <c r="F63" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="H63" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2845.9</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2869.42</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2882.05</v>
+      </c>
+      <c r="L63" t="n">
+        <v>2894.67</v>
+      </c>
+      <c r="M63" t="n">
+        <v>2912.75</v>
+      </c>
+      <c r="N63" t="n">
+        <v>2930.82</v>
+      </c>
+      <c r="O63" t="n">
+        <v>2938</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
         <is>
           <t>強警訊</t>
         </is>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -5741,22 +5741,22 @@
         <v>2897.8</v>
       </c>
       <c r="C63" t="n">
-        <v>2925.6</v>
+        <v>2931.2</v>
       </c>
       <c r="D63" t="n">
         <v>2884.2</v>
       </c>
       <c r="E63" t="n">
-        <v>2924</v>
+        <v>2904.8</v>
       </c>
       <c r="F63" t="n">
-        <v>26.6</v>
+        <v>7.4</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0092</v>
+        <v>0.0026</v>
       </c>
       <c r="H63" t="n">
-        <v>41.4</v>
+        <v>47</v>
       </c>
       <c r="I63" t="n">
         <v>2845.9</v>
@@ -5795,12 +5795,12 @@
       </c>
       <c r="T63" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="V63" s="8" t="n">

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3023.7</v>
+        <v>3034.7</v>
       </c>
       <c r="C2" t="n">
-        <v>3062.4</v>
+        <v>3045.7</v>
       </c>
       <c r="D2" t="n">
-        <v>3010.5</v>
+        <v>2999.6</v>
       </c>
       <c r="E2" t="n">
-        <v>3030.7</v>
+        <v>3022.6</v>
       </c>
       <c r="F2" t="n">
-        <v>17.2</v>
+        <v>-8.1</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.0027</v>
       </c>
       <c r="H2" t="n">
-        <v>51.9</v>
+        <v>46.1</v>
       </c>
       <c r="I2" t="n">
-        <v>2933</v>
+        <v>2958.6</v>
       </c>
       <c r="J2" t="n">
-        <v>2958.9</v>
+        <v>2975.93</v>
       </c>
       <c r="K2" t="n">
-        <v>2986.4</v>
+        <v>3004.75</v>
       </c>
       <c r="L2" t="n">
-        <v>3013.9</v>
+        <v>3033.57</v>
       </c>
       <c r="M2" t="n">
-        <v>3040.6</v>
+        <v>3056.65</v>
       </c>
       <c r="N2" t="n">
-        <v>3067.3</v>
+        <v>3079.72</v>
       </c>
       <c r="O2" t="n">
-        <v>3095.6</v>
+        <v>3114.3</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,18 +685,18 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -709,55 +709,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3034.7</v>
+        <v>3020.9</v>
       </c>
       <c r="C3" t="n">
-        <v>3045.7</v>
+        <v>3044.9</v>
       </c>
       <c r="D3" t="n">
-        <v>2999.6</v>
+        <v>2987.8</v>
       </c>
       <c r="E3" t="n">
-        <v>3022.6</v>
+        <v>3030.6</v>
       </c>
       <c r="F3" t="n">
-        <v>-8.1</v>
+        <v>8</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0026</v>
       </c>
       <c r="H3" t="n">
-        <v>46.1</v>
+        <v>57.1</v>
       </c>
       <c r="I3" t="n">
-        <v>2958.6</v>
+        <v>2953.5</v>
       </c>
       <c r="J3" t="n">
-        <v>2975.93</v>
+        <v>2976.48</v>
       </c>
       <c r="K3" t="n">
-        <v>3004.75</v>
+        <v>2999.55</v>
       </c>
       <c r="L3" t="n">
-        <v>3033.57</v>
+        <v>3022.63</v>
       </c>
       <c r="M3" t="n">
-        <v>3056.65</v>
+        <v>3045.65</v>
       </c>
       <c r="N3" t="n">
-        <v>3079.72</v>
+        <v>3068.67</v>
       </c>
       <c r="O3" t="n">
-        <v>3114.3</v>
+        <v>3091.8</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,7 +776,7 @@
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -791,57 +795,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3020.9</v>
+        <v>3026.1</v>
       </c>
       <c r="C4" t="n">
-        <v>3044.9</v>
+        <v>3050.6</v>
       </c>
       <c r="D4" t="n">
-        <v>2987.8</v>
+        <v>3015.1</v>
       </c>
       <c r="E4" t="n">
-        <v>3030.6</v>
+        <v>3045.6</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0049</v>
       </c>
       <c r="H4" t="n">
-        <v>57.1</v>
+        <v>35.5</v>
       </c>
       <c r="I4" t="n">
-        <v>2953.5</v>
+        <v>2930.7</v>
       </c>
       <c r="J4" t="n">
-        <v>2976.48</v>
+        <v>2980.63</v>
       </c>
       <c r="K4" t="n">
-        <v>2999.55</v>
+        <v>3002.05</v>
       </c>
       <c r="L4" t="n">
-        <v>3022.63</v>
+        <v>3023.48</v>
       </c>
       <c r="M4" t="n">
-        <v>3045.65</v>
+        <v>3059.15</v>
       </c>
       <c r="N4" t="n">
-        <v>3068.67</v>
+        <v>3094.83</v>
       </c>
       <c r="O4" t="n">
-        <v>3091.8</v>
+        <v>3102</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -849,18 +853,18 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -873,59 +877,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3026.1</v>
+        <v>3040</v>
       </c>
       <c r="C5" t="n">
-        <v>3050.6</v>
+        <v>3068.4</v>
       </c>
       <c r="D5" t="n">
-        <v>3015.1</v>
+        <v>3023.7</v>
       </c>
       <c r="E5" t="n">
-        <v>3045.6</v>
+        <v>3035.1</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>-10.5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.0034</v>
       </c>
       <c r="H5" t="n">
-        <v>35.5</v>
+        <v>44.7</v>
       </c>
       <c r="I5" t="n">
-        <v>2930.7</v>
+        <v>2979.6</v>
       </c>
       <c r="J5" t="n">
-        <v>2980.63</v>
+        <v>3016.48</v>
       </c>
       <c r="K5" t="n">
-        <v>3002.05</v>
+        <v>3027.85</v>
       </c>
       <c r="L5" t="n">
-        <v>3023.48</v>
+        <v>3039.23</v>
       </c>
       <c r="M5" t="n">
-        <v>3059.15</v>
+        <v>3063.35</v>
       </c>
       <c r="N5" t="n">
-        <v>3094.83</v>
+        <v>3087.48</v>
       </c>
       <c r="O5" t="n">
-        <v>3102</v>
+        <v>3086.1</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -933,17 +933,19 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U5" s="8" t="n">
@@ -957,55 +959,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3040</v>
+        <v>3030.9</v>
       </c>
       <c r="C6" t="n">
-        <v>3068.4</v>
+        <v>3062.4</v>
       </c>
       <c r="D6" t="n">
-        <v>3023.7</v>
+        <v>2988.5</v>
       </c>
       <c r="E6" t="n">
-        <v>3035.1</v>
+        <v>3014.2</v>
       </c>
       <c r="F6" t="n">
-        <v>-10.5</v>
+        <v>-20.9</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0069</v>
       </c>
       <c r="H6" t="n">
-        <v>44.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>2979.6</v>
+        <v>2979</v>
       </c>
       <c r="J6" t="n">
-        <v>3016.48</v>
+        <v>2984.93</v>
       </c>
       <c r="K6" t="n">
-        <v>3027.85</v>
+        <v>3012.75</v>
       </c>
       <c r="L6" t="n">
-        <v>3039.23</v>
+        <v>3040.58</v>
       </c>
       <c r="M6" t="n">
-        <v>3063.35</v>
+        <v>3057.45</v>
       </c>
       <c r="N6" t="n">
-        <v>3087.48</v>
+        <v>3074.33</v>
       </c>
       <c r="O6" t="n">
-        <v>3086.1</v>
+        <v>3113.1</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1015,19 +1021,19 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1041,57 +1047,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3030.9</v>
+        <v>3019.7</v>
       </c>
       <c r="C7" t="n">
-        <v>3062.4</v>
+        <v>3042.1</v>
       </c>
       <c r="D7" t="n">
-        <v>2988.5</v>
+        <v>3006.7</v>
       </c>
       <c r="E7" t="n">
-        <v>3014.2</v>
+        <v>3027</v>
       </c>
       <c r="F7" t="n">
-        <v>-20.9</v>
+        <v>12.8</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0042</v>
       </c>
       <c r="H7" t="n">
-        <v>73.90000000000001</v>
+        <v>35.4</v>
       </c>
       <c r="I7" t="n">
-        <v>2979</v>
+        <v>2914.6</v>
       </c>
       <c r="J7" t="n">
-        <v>2984.93</v>
+        <v>2934.68</v>
       </c>
       <c r="K7" t="n">
-        <v>3012.75</v>
+        <v>2977.25</v>
       </c>
       <c r="L7" t="n">
-        <v>3040.58</v>
+        <v>3019.82</v>
       </c>
       <c r="M7" t="n">
-        <v>3057.45</v>
+        <v>3051.15</v>
       </c>
       <c r="N7" t="n">
-        <v>3074.33</v>
+        <v>3082.47</v>
       </c>
       <c r="O7" t="n">
-        <v>3113.1</v>
+        <v>3136.3</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1099,20 +1105,16 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R7" s="6" t="n">
+        <v/>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1127,70 +1129,74 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3019.7</v>
+        <v>3033.4</v>
       </c>
       <c r="C8" t="n">
-        <v>3042.1</v>
+        <v>3042.6</v>
       </c>
       <c r="D8" t="n">
-        <v>3006.7</v>
+        <v>2988.8</v>
       </c>
       <c r="E8" t="n">
-        <v>3027</v>
+        <v>2998.8</v>
       </c>
       <c r="F8" t="n">
-        <v>12.8</v>
+        <v>-28.2</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>35.4</v>
+        <v>53.8</v>
       </c>
       <c r="I8" t="n">
-        <v>2914.6</v>
+        <v>2971.3</v>
       </c>
       <c r="J8" t="n">
-        <v>2934.68</v>
+        <v>2992.9</v>
       </c>
       <c r="K8" t="n">
-        <v>2977.25</v>
+        <v>3009.3</v>
       </c>
       <c r="L8" t="n">
-        <v>3019.82</v>
+        <v>3025.7</v>
       </c>
       <c r="M8" t="n">
-        <v>3051.15</v>
+        <v>3044.7</v>
       </c>
       <c r="N8" t="n">
-        <v>3082.47</v>
+        <v>3063.7</v>
       </c>
       <c r="O8" t="n">
-        <v>3136.3</v>
+        <v>3077.5</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1209,72 +1215,70 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3033.4</v>
+        <v>2994.3</v>
       </c>
       <c r="C9" t="n">
-        <v>3042.6</v>
+        <v>3004.3</v>
       </c>
       <c r="D9" t="n">
-        <v>2988.8</v>
+        <v>2943.4</v>
       </c>
       <c r="E9" t="n">
-        <v>2998.8</v>
+        <v>2971.5</v>
       </c>
       <c r="F9" t="n">
-        <v>-28.2</v>
+        <v>-27.3</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0091</v>
       </c>
       <c r="H9" t="n">
-        <v>53.8</v>
+        <v>60.9</v>
       </c>
       <c r="I9" t="n">
-        <v>2971.3</v>
+        <v>2935</v>
       </c>
       <c r="J9" t="n">
-        <v>2992.9</v>
+        <v>2936.55</v>
       </c>
       <c r="K9" t="n">
-        <v>3009.3</v>
+        <v>2971.9</v>
       </c>
       <c r="L9" t="n">
+        <v>3007.25</v>
+      </c>
+      <c r="M9" t="n">
         <v>3025.7</v>
       </c>
-      <c r="M9" t="n">
-        <v>3044.7</v>
-      </c>
       <c r="N9" t="n">
-        <v>3063.7</v>
+        <v>3044.15</v>
       </c>
       <c r="O9" t="n">
-        <v>3077.5</v>
+        <v>3096.4</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1295,57 +1299,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2994.3</v>
+        <v>2965.8</v>
       </c>
       <c r="C10" t="n">
-        <v>3004.3</v>
+        <v>3014.9</v>
       </c>
       <c r="D10" t="n">
-        <v>2943.4</v>
+        <v>2964.3</v>
       </c>
       <c r="E10" t="n">
-        <v>2971.5</v>
+        <v>3008.4</v>
       </c>
       <c r="F10" t="n">
-        <v>-27.3</v>
+        <v>36.9</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0091</v>
+        <v>0.0124</v>
       </c>
       <c r="H10" t="n">
-        <v>60.9</v>
+        <v>50.6</v>
       </c>
       <c r="I10" t="n">
-        <v>2935</v>
+        <v>2882.5</v>
       </c>
       <c r="J10" t="n">
-        <v>2936.55</v>
+        <v>2909.42</v>
       </c>
       <c r="K10" t="n">
-        <v>2971.9</v>
+        <v>2941.05</v>
       </c>
       <c r="L10" t="n">
-        <v>3007.25</v>
+        <v>2972.67</v>
       </c>
       <c r="M10" t="n">
-        <v>3025.7</v>
+        <v>3001.95</v>
       </c>
       <c r="N10" t="n">
-        <v>3044.15</v>
+        <v>3031.23</v>
       </c>
       <c r="O10" t="n">
-        <v>3096.4</v>
+        <v>3065.2</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1353,19 +1357,19 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
@@ -1377,59 +1381,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2965.8</v>
+        <v>3008.1</v>
       </c>
       <c r="C11" t="n">
-        <v>3014.9</v>
+        <v>3019.5</v>
       </c>
       <c r="D11" t="n">
-        <v>2964.3</v>
+        <v>2970.8</v>
       </c>
       <c r="E11" t="n">
-        <v>3008.4</v>
+        <v>2994</v>
       </c>
       <c r="F11" t="n">
-        <v>36.9</v>
+        <v>-14.4</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0048</v>
       </c>
       <c r="H11" t="n">
-        <v>50.6</v>
+        <v>48.7</v>
       </c>
       <c r="I11" t="n">
-        <v>2882.5</v>
+        <v>2913.7</v>
       </c>
       <c r="J11" t="n">
-        <v>2909.42</v>
+        <v>2967.2</v>
       </c>
       <c r="K11" t="n">
-        <v>2941.05</v>
+        <v>2983.1</v>
       </c>
       <c r="L11" t="n">
-        <v>2972.67</v>
+        <v>2999</v>
       </c>
       <c r="M11" t="n">
-        <v>3001.95</v>
+        <v>3033.7</v>
       </c>
       <c r="N11" t="n">
-        <v>3031.23</v>
+        <v>3068.4</v>
       </c>
       <c r="O11" t="n">
-        <v>3065.2</v>
+        <v>3065.5</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1437,18 +1437,18 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1461,55 +1461,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3008.1</v>
+        <v>2984.7</v>
       </c>
       <c r="C12" t="n">
-        <v>3019.5</v>
+        <v>2995.8</v>
       </c>
       <c r="D12" t="n">
-        <v>2970.8</v>
+        <v>2961.8</v>
       </c>
       <c r="E12" t="n">
-        <v>2994</v>
+        <v>2970.4</v>
       </c>
       <c r="F12" t="n">
-        <v>-14.4</v>
+        <v>-23.6</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>48.7</v>
+        <v>34</v>
       </c>
       <c r="I12" t="n">
-        <v>2913.7</v>
+        <v>2922.1</v>
       </c>
       <c r="J12" t="n">
-        <v>2967.2</v>
+        <v>2944.73</v>
       </c>
       <c r="K12" t="n">
-        <v>2983.1</v>
+        <v>2969.65</v>
       </c>
       <c r="L12" t="n">
-        <v>2999</v>
+        <v>2994.58</v>
       </c>
       <c r="M12" t="n">
-        <v>3033.7</v>
+        <v>3018.35</v>
       </c>
       <c r="N12" t="n">
-        <v>3068.4</v>
+        <v>3042.12</v>
       </c>
       <c r="O12" t="n">
-        <v>3065.5</v>
+        <v>3068.2</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1519,12 +1523,12 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1543,57 +1547,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2984.7</v>
+        <v>2967.2</v>
       </c>
       <c r="C13" t="n">
-        <v>2995.8</v>
+        <v>3029.8</v>
       </c>
       <c r="D13" t="n">
-        <v>2961.8</v>
+        <v>2956.2</v>
       </c>
       <c r="E13" t="n">
-        <v>2970.4</v>
+        <v>2979.9</v>
       </c>
       <c r="F13" t="n">
-        <v>-23.6</v>
+        <v>9.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H13" t="n">
-        <v>34</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>2922.1</v>
+        <v>2927.8</v>
       </c>
       <c r="J13" t="n">
-        <v>2944.73</v>
+        <v>2932.2</v>
       </c>
       <c r="K13" t="n">
-        <v>2969.65</v>
+        <v>2953.4</v>
       </c>
       <c r="L13" t="n">
-        <v>2994.58</v>
+        <v>2974.6</v>
       </c>
       <c r="M13" t="n">
-        <v>3018.35</v>
+        <v>2987.4</v>
       </c>
       <c r="N13" t="n">
-        <v>3042.12</v>
+        <v>3000.2</v>
       </c>
       <c r="O13" t="n">
-        <v>3068.2</v>
+        <v>3029.8</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1601,24 +1605,28 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R13" s="6" t="n">
+        <v/>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
@@ -1627,57 +1635,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2967.2</v>
+        <v>2981.2</v>
       </c>
       <c r="C14" t="n">
-        <v>3029.8</v>
+        <v>3006.1</v>
       </c>
       <c r="D14" t="n">
-        <v>2956.2</v>
+        <v>2974.4</v>
       </c>
       <c r="E14" t="n">
-        <v>2979.9</v>
+        <v>2991.8</v>
       </c>
       <c r="F14" t="n">
-        <v>9.5</v>
+        <v>11.9</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.004</v>
       </c>
       <c r="H14" t="n">
-        <v>73.59999999999999</v>
+        <v>31.7</v>
       </c>
       <c r="I14" t="n">
-        <v>2927.8</v>
+        <v>2882.6</v>
       </c>
       <c r="J14" t="n">
-        <v>2932.2</v>
+        <v>2899.75</v>
       </c>
       <c r="K14" t="n">
-        <v>2953.4</v>
+        <v>2943.1</v>
       </c>
       <c r="L14" t="n">
-        <v>2974.6</v>
+        <v>2986.45</v>
       </c>
       <c r="M14" t="n">
-        <v>2987.4</v>
+        <v>3016.7</v>
       </c>
       <c r="N14" t="n">
-        <v>3000.2</v>
+        <v>3046.95</v>
       </c>
       <c r="O14" t="n">
-        <v>3029.8</v>
+        <v>3103.4</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1688,25 +1696,19 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
@@ -1722,50 +1724,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2981.2</v>
+        <v>2995.3</v>
       </c>
       <c r="C15" t="n">
-        <v>3006.1</v>
+        <v>3012.8</v>
       </c>
       <c r="D15" t="n">
-        <v>2974.4</v>
+        <v>2972.7</v>
       </c>
       <c r="E15" t="n">
-        <v>2991.8</v>
+        <v>2990.7</v>
       </c>
       <c r="F15" t="n">
-        <v>11.9</v>
+        <v>-1.1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0004</v>
       </c>
       <c r="H15" t="n">
-        <v>31.7</v>
+        <v>40.1</v>
       </c>
       <c r="I15" t="n">
-        <v>2882.6</v>
+        <v>2942.7</v>
       </c>
       <c r="J15" t="n">
-        <v>2899.75</v>
+        <v>2960.87</v>
       </c>
       <c r="K15" t="n">
-        <v>2943.1</v>
+        <v>2975.95</v>
       </c>
       <c r="L15" t="n">
-        <v>2986.45</v>
+        <v>2991.03</v>
       </c>
       <c r="M15" t="n">
-        <v>3016.7</v>
+        <v>3007.65</v>
       </c>
       <c r="N15" t="n">
-        <v>3046.95</v>
+        <v>3024.28</v>
       </c>
       <c r="O15" t="n">
-        <v>3103.4</v>
+        <v>3037.8</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1773,16 +1775,20 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1797,78 +1803,78 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2995.3</v>
+        <v>2991.7</v>
       </c>
       <c r="C16" t="n">
-        <v>3012.8</v>
+        <v>2994.8</v>
       </c>
       <c r="D16" t="n">
-        <v>2972.7</v>
+        <v>2949.3</v>
       </c>
       <c r="E16" t="n">
-        <v>2990.7</v>
+        <v>2973.5</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1</v>
+        <v>-17.2</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0058</v>
       </c>
       <c r="H16" t="n">
-        <v>40.1</v>
+        <v>45.5</v>
       </c>
       <c r="I16" t="n">
-        <v>2942.7</v>
+        <v>2932.6</v>
       </c>
       <c r="J16" t="n">
-        <v>2960.87</v>
+        <v>2949.57</v>
       </c>
       <c r="K16" t="n">
-        <v>2975.95</v>
+        <v>2970.65</v>
       </c>
       <c r="L16" t="n">
-        <v>2991.03</v>
+        <v>2991.72</v>
       </c>
       <c r="M16" t="n">
-        <v>3007.65</v>
+        <v>3010.75</v>
       </c>
       <c r="N16" t="n">
-        <v>3024.28</v>
+        <v>3029.78</v>
       </c>
       <c r="O16" t="n">
-        <v>3037.8</v>
+        <v>3052.9</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1883,79 +1889,79 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2991.7</v>
+        <v>2964.5</v>
       </c>
       <c r="C17" t="n">
-        <v>2994.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D17" t="n">
-        <v>2949.3</v>
+        <v>2952.7</v>
       </c>
       <c r="E17" t="n">
-        <v>2973.5</v>
+        <v>2955.2</v>
       </c>
       <c r="F17" t="n">
-        <v>-17.2</v>
+        <v>-18.3</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0062</v>
       </c>
       <c r="H17" t="n">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="I17" t="n">
-        <v>2932.6</v>
+        <v>2903.8</v>
       </c>
       <c r="J17" t="n">
-        <v>2949.57</v>
+        <v>2928.72</v>
       </c>
       <c r="K17" t="n">
-        <v>2970.65</v>
+        <v>2950.75</v>
       </c>
       <c r="L17" t="n">
-        <v>2991.72</v>
+        <v>2972.78</v>
       </c>
       <c r="M17" t="n">
-        <v>3010.75</v>
+        <v>2996.25</v>
       </c>
       <c r="N17" t="n">
-        <v>3029.78</v>
+        <v>3019.72</v>
       </c>
       <c r="O17" t="n">
-        <v>3052.9</v>
+        <v>3040.3</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
@@ -1969,57 +1975,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2964.5</v>
+        <v>2955.8</v>
       </c>
       <c r="C18" t="n">
-        <v>2998.7</v>
+        <v>2999.8</v>
       </c>
       <c r="D18" t="n">
-        <v>2952.7</v>
+        <v>2951.1</v>
       </c>
       <c r="E18" t="n">
-        <v>2955.2</v>
+        <v>2997</v>
       </c>
       <c r="F18" t="n">
-        <v>-18.3</v>
+        <v>41.8</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0141</v>
       </c>
       <c r="H18" t="n">
-        <v>46</v>
+        <v>48.7</v>
       </c>
       <c r="I18" t="n">
-        <v>2903.8</v>
+        <v>2906.7</v>
       </c>
       <c r="J18" t="n">
-        <v>2928.72</v>
+        <v>2898.95</v>
       </c>
       <c r="K18" t="n">
-        <v>2950.75</v>
+        <v>2932.2</v>
       </c>
       <c r="L18" t="n">
-        <v>2972.78</v>
+        <v>2965.45</v>
       </c>
       <c r="M18" t="n">
-        <v>2996.25</v>
+        <v>2978.2</v>
       </c>
       <c r="N18" t="n">
-        <v>3019.72</v>
+        <v>2990.95</v>
       </c>
       <c r="O18" t="n">
-        <v>3040.3</v>
+        <v>3044.7</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2027,23 +2033,23 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2062,50 +2068,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2955.8</v>
+        <v>2997</v>
       </c>
       <c r="C19" t="n">
-        <v>2999.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D19" t="n">
-        <v>2951.1</v>
+        <v>2965.5</v>
       </c>
       <c r="E19" t="n">
-        <v>2997</v>
+        <v>2969.8</v>
       </c>
       <c r="F19" t="n">
-        <v>41.8</v>
+        <v>-27.2</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0141</v>
+        <v>-0.0091</v>
       </c>
       <c r="H19" t="n">
-        <v>48.7</v>
+        <v>33.2</v>
       </c>
       <c r="I19" t="n">
-        <v>2906.7</v>
+        <v>2902.4</v>
       </c>
       <c r="J19" t="n">
-        <v>2898.95</v>
+        <v>2959.08</v>
       </c>
       <c r="K19" t="n">
-        <v>2932.2</v>
+        <v>2972.65</v>
       </c>
       <c r="L19" t="n">
-        <v>2965.45</v>
+        <v>2986.23</v>
       </c>
       <c r="M19" t="n">
-        <v>2978.2</v>
+        <v>3021.35</v>
       </c>
       <c r="N19" t="n">
-        <v>2990.95</v>
+        <v>3056.47</v>
       </c>
       <c r="O19" t="n">
-        <v>3044.7</v>
+        <v>3048.5</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2113,23 +2119,21 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2141,60 +2145,62 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2997</v>
+        <v>2974.6</v>
       </c>
       <c r="C20" t="n">
-        <v>2998.7</v>
+        <v>2979</v>
       </c>
       <c r="D20" t="n">
-        <v>2965.5</v>
+        <v>2932.1</v>
       </c>
       <c r="E20" t="n">
-        <v>2969.8</v>
+        <v>2951.7</v>
       </c>
       <c r="F20" t="n">
-        <v>-27.2</v>
+        <v>-18.1</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0091</v>
+        <v>-0.0061</v>
       </c>
       <c r="H20" t="n">
-        <v>33.2</v>
+        <v>46.9</v>
       </c>
       <c r="I20" t="n">
-        <v>2902.4</v>
+        <v>2932.3</v>
       </c>
       <c r="J20" t="n">
-        <v>2959.08</v>
+        <v>2930.45</v>
       </c>
       <c r="K20" t="n">
-        <v>2972.65</v>
+        <v>2953.2</v>
       </c>
       <c r="L20" t="n">
-        <v>2986.23</v>
+        <v>2975.95</v>
       </c>
       <c r="M20" t="n">
-        <v>3021.35</v>
+        <v>2986.4</v>
       </c>
       <c r="N20" t="n">
-        <v>3056.47</v>
+        <v>2996.85</v>
       </c>
       <c r="O20" t="n">
-        <v>3048.5</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
+        <v>3031.9</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q20" s="6" t="n">
         <v/>
@@ -2204,7 +2210,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2225,74 +2231,70 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2974.6</v>
+        <v>2948.5</v>
       </c>
       <c r="C21" t="n">
-        <v>2979</v>
+        <v>2969.7</v>
       </c>
       <c r="D21" t="n">
-        <v>2932.1</v>
+        <v>2934.5</v>
       </c>
       <c r="E21" t="n">
-        <v>2951.7</v>
+        <v>2941.3</v>
       </c>
       <c r="F21" t="n">
-        <v>-18.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0035</v>
       </c>
       <c r="H21" t="n">
-        <v>46.9</v>
+        <v>35.2</v>
       </c>
       <c r="I21" t="n">
-        <v>2932.3</v>
+        <v>2885.2</v>
       </c>
       <c r="J21" t="n">
-        <v>2930.45</v>
+        <v>2902.88</v>
       </c>
       <c r="K21" t="n">
-        <v>2953.2</v>
+        <v>2928.25</v>
       </c>
       <c r="L21" t="n">
-        <v>2975.95</v>
+        <v>2953.62</v>
       </c>
       <c r="M21" t="n">
-        <v>2986.4</v>
+        <v>2975.15</v>
       </c>
       <c r="N21" t="n">
-        <v>2996.85</v>
+        <v>2996.67</v>
       </c>
       <c r="O21" t="n">
-        <v>3031.9</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3025.9</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
       </c>
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2311,57 +2313,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2948.5</v>
+        <v>2955.5</v>
       </c>
       <c r="C22" t="n">
-        <v>2969.7</v>
+        <v>2985.9</v>
       </c>
       <c r="D22" t="n">
-        <v>2934.5</v>
+        <v>2941.2</v>
       </c>
       <c r="E22" t="n">
-        <v>2941.3</v>
+        <v>2960</v>
       </c>
       <c r="F22" t="n">
-        <v>-10.4</v>
+        <v>18.7</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0064</v>
       </c>
       <c r="H22" t="n">
-        <v>35.2</v>
+        <v>44.7</v>
       </c>
       <c r="I22" t="n">
-        <v>2885.2</v>
+        <v>2899.3</v>
       </c>
       <c r="J22" t="n">
-        <v>2902.88</v>
+        <v>2900.7</v>
       </c>
       <c r="K22" t="n">
-        <v>2928.25</v>
+        <v>2923.7</v>
       </c>
       <c r="L22" t="n">
-        <v>2953.62</v>
+        <v>2946.7</v>
       </c>
       <c r="M22" t="n">
-        <v>2975.15</v>
+        <v>2958.9</v>
       </c>
       <c r="N22" t="n">
-        <v>2996.67</v>
+        <v>2971.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3025.9</v>
+        <v>3004.9</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2374,14 +2376,18 @@
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2391,59 +2397,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2955.5</v>
+        <v>2961.5</v>
       </c>
       <c r="C23" t="n">
-        <v>2985.9</v>
+        <v>2968.3</v>
       </c>
       <c r="D23" t="n">
-        <v>2941.2</v>
+        <v>2933.4</v>
       </c>
       <c r="E23" t="n">
-        <v>2960</v>
+        <v>2964.5</v>
       </c>
       <c r="F23" t="n">
-        <v>18.7</v>
+        <v>4.5</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0015</v>
       </c>
       <c r="H23" t="n">
-        <v>44.7</v>
+        <v>34.9</v>
       </c>
       <c r="I23" t="n">
-        <v>2899.3</v>
+        <v>2896.5</v>
       </c>
       <c r="J23" t="n">
-        <v>2900.7</v>
+        <v>2913.53</v>
       </c>
       <c r="K23" t="n">
-        <v>2923.7</v>
+        <v>2937.65</v>
       </c>
       <c r="L23" t="n">
-        <v>2946.7</v>
+        <v>2961.77</v>
       </c>
       <c r="M23" t="n">
-        <v>2958.9</v>
+        <v>2982.35</v>
       </c>
       <c r="N23" t="n">
-        <v>2971.1</v>
+        <v>3002.92</v>
       </c>
       <c r="O23" t="n">
-        <v>3004.9</v>
+        <v>3030.6</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2451,24 +2453,22 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
@@ -2477,61 +2477,69 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2961.5</v>
+        <v>2966.9</v>
       </c>
       <c r="C24" t="n">
-        <v>2968.3</v>
+        <v>2978.3</v>
       </c>
       <c r="D24" t="n">
-        <v>2933.4</v>
+        <v>2902.3</v>
       </c>
       <c r="E24" t="n">
-        <v>2964.5</v>
+        <v>2915.4</v>
       </c>
       <c r="F24" t="n">
-        <v>4.5</v>
+        <v>-49.1</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0166</v>
       </c>
       <c r="H24" t="n">
-        <v>34.9</v>
+        <v>76</v>
       </c>
       <c r="I24" t="n">
-        <v>2896.5</v>
+        <v>2898.5</v>
       </c>
       <c r="J24" t="n">
-        <v>2913.53</v>
+        <v>2936.42</v>
       </c>
       <c r="K24" t="n">
-        <v>2937.65</v>
+        <v>2947.05</v>
       </c>
       <c r="L24" t="n">
-        <v>2961.77</v>
+        <v>2957.67</v>
       </c>
       <c r="M24" t="n">
-        <v>2982.35</v>
+        <v>2981.95</v>
       </c>
       <c r="N24" t="n">
-        <v>3002.92</v>
+        <v>3006.23</v>
       </c>
       <c r="O24" t="n">
-        <v>3030.6</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
+        <v>3003.2</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
@@ -2540,7 +2548,7 @@
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2552,88 +2560,84 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W24" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2966.9</v>
+        <v>2906.6</v>
       </c>
       <c r="C25" t="n">
-        <v>2978.3</v>
+        <v>2957.9</v>
       </c>
       <c r="D25" t="n">
-        <v>2902.3</v>
+        <v>2905.6</v>
       </c>
       <c r="E25" t="n">
-        <v>2915.4</v>
+        <v>2954.3</v>
       </c>
       <c r="F25" t="n">
-        <v>-49.1</v>
+        <v>38.9</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0166</v>
+        <v>0.0133</v>
       </c>
       <c r="H25" t="n">
-        <v>76</v>
+        <v>52.3</v>
       </c>
       <c r="I25" t="n">
-        <v>2898.5</v>
+        <v>2826.3</v>
       </c>
       <c r="J25" t="n">
-        <v>2936.42</v>
+        <v>2826.95</v>
       </c>
       <c r="K25" t="n">
-        <v>2947.05</v>
+        <v>2877.4</v>
       </c>
       <c r="L25" t="n">
-        <v>2957.67</v>
+        <v>2927.85</v>
       </c>
       <c r="M25" t="n">
-        <v>2981.95</v>
+        <v>2953.4</v>
       </c>
       <c r="N25" t="n">
-        <v>3006.23</v>
+        <v>2978.95</v>
       </c>
       <c r="O25" t="n">
-        <v>3003.2</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
+        <v>3054.3</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
       <c r="U25" s="8" t="n">
         <v/>
       </c>
@@ -2647,76 +2651,78 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2906.6</v>
+        <v>2954</v>
       </c>
       <c r="C26" t="n">
-        <v>2957.9</v>
+        <v>2976.3</v>
       </c>
       <c r="D26" t="n">
-        <v>2905.6</v>
+        <v>2905.3</v>
       </c>
       <c r="E26" t="n">
-        <v>2954.3</v>
+        <v>2938</v>
       </c>
       <c r="F26" t="n">
-        <v>38.9</v>
+        <v>-16.3</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0055</v>
       </c>
       <c r="H26" t="n">
-        <v>52.3</v>
+        <v>71</v>
       </c>
       <c r="I26" t="n">
-        <v>2826.3</v>
+        <v>2853.3</v>
       </c>
       <c r="J26" t="n">
-        <v>2826.95</v>
+        <v>2913.28</v>
       </c>
       <c r="K26" t="n">
-        <v>2877.4</v>
+        <v>2928.15</v>
       </c>
       <c r="L26" t="n">
-        <v>2927.85</v>
+        <v>2943.03</v>
       </c>
       <c r="M26" t="n">
-        <v>2953.4</v>
+        <v>2980.45</v>
       </c>
       <c r="N26" t="n">
-        <v>2978.95</v>
+        <v>3017.87</v>
       </c>
       <c r="O26" t="n">
-        <v>3054.3</v>
+        <v>3010.2</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2731,78 +2737,76 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2954</v>
+        <v>2950</v>
       </c>
       <c r="C27" t="n">
-        <v>2976.3</v>
+        <v>2994.6</v>
       </c>
       <c r="D27" t="n">
-        <v>2905.3</v>
+        <v>2948.4</v>
       </c>
       <c r="E27" t="n">
-        <v>2938</v>
+        <v>2989.3</v>
       </c>
       <c r="F27" t="n">
-        <v>-16.3</v>
+        <v>51.3</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0175</v>
       </c>
       <c r="H27" t="n">
-        <v>71</v>
+        <v>46.2</v>
       </c>
       <c r="I27" t="n">
-        <v>2853.3</v>
+        <v>2834.3</v>
       </c>
       <c r="J27" t="n">
-        <v>2913.28</v>
+        <v>2865.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2928.15</v>
+        <v>2902.5</v>
       </c>
       <c r="L27" t="n">
-        <v>2943.03</v>
+        <v>2939.4</v>
       </c>
       <c r="M27" t="n">
-        <v>2980.45</v>
+        <v>2973.5</v>
       </c>
       <c r="N27" t="n">
-        <v>3017.87</v>
+        <v>3007.6</v>
       </c>
       <c r="O27" t="n">
-        <v>3010.2</v>
+        <v>3047.3</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2817,57 +2821,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2950</v>
+        <v>2992.4</v>
       </c>
       <c r="C28" t="n">
-        <v>2994.6</v>
+        <v>3051.8</v>
       </c>
       <c r="D28" t="n">
-        <v>2948.4</v>
+        <v>2986.1</v>
       </c>
       <c r="E28" t="n">
-        <v>2989.3</v>
+        <v>3044.7</v>
       </c>
       <c r="F28" t="n">
-        <v>51.3</v>
+        <v>55.4</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0185</v>
       </c>
       <c r="H28" t="n">
-        <v>46.2</v>
+        <v>65.7</v>
       </c>
       <c r="I28" t="n">
-        <v>2834.3</v>
+        <v>2902.2</v>
       </c>
       <c r="J28" t="n">
-        <v>2865.6</v>
+        <v>2952</v>
       </c>
       <c r="K28" t="n">
-        <v>2902.5</v>
+        <v>2966.2</v>
       </c>
       <c r="L28" t="n">
-        <v>2939.4</v>
+        <v>2980.4</v>
       </c>
       <c r="M28" t="n">
-        <v>2973.5</v>
+        <v>3012.4</v>
       </c>
       <c r="N28" t="n">
-        <v>3007.6</v>
+        <v>3044.4</v>
       </c>
       <c r="O28" t="n">
-        <v>3047.3</v>
+        <v>3040.8</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2878,80 +2882,80 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W28" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W28" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2992.4</v>
+        <v>3049.1</v>
       </c>
       <c r="C29" t="n">
-        <v>3051.8</v>
+        <v>3058.3</v>
       </c>
       <c r="D29" t="n">
-        <v>2986.1</v>
+        <v>3023.3</v>
       </c>
       <c r="E29" t="n">
-        <v>3044.7</v>
+        <v>3025.4</v>
       </c>
       <c r="F29" t="n">
-        <v>55.4</v>
+        <v>-19.3</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0063</v>
       </c>
       <c r="H29" t="n">
-        <v>65.7</v>
+        <v>35</v>
       </c>
       <c r="I29" t="n">
-        <v>2902.2</v>
+        <v>2920.4</v>
       </c>
       <c r="J29" t="n">
-        <v>2952</v>
+        <v>2991.87</v>
       </c>
       <c r="K29" t="n">
-        <v>2966.2</v>
+        <v>3011.85</v>
       </c>
       <c r="L29" t="n">
-        <v>2980.4</v>
+        <v>3031.83</v>
       </c>
       <c r="M29" t="n">
-        <v>3012.4</v>
+        <v>3077.55</v>
       </c>
       <c r="N29" t="n">
-        <v>3044.4</v>
+        <v>3123.27</v>
       </c>
       <c r="O29" t="n">
-        <v>3040.8</v>
+        <v>3117.5</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2964,78 +2968,76 @@
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3049.1</v>
+        <v>3028.5</v>
       </c>
       <c r="C30" t="n">
-        <v>3058.3</v>
+        <v>3041</v>
       </c>
       <c r="D30" t="n">
-        <v>3023.3</v>
+        <v>3004.9</v>
       </c>
       <c r="E30" t="n">
-        <v>3025.4</v>
+        <v>3009.1</v>
       </c>
       <c r="F30" t="n">
-        <v>-19.3</v>
+        <v>-16.3</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0054</v>
       </c>
       <c r="H30" t="n">
-        <v>35</v>
+        <v>36.1</v>
       </c>
       <c r="I30" t="n">
-        <v>2920.4</v>
+        <v>2988.3</v>
       </c>
       <c r="J30" t="n">
-        <v>2991.87</v>
+        <v>2982.7</v>
       </c>
       <c r="K30" t="n">
-        <v>3011.85</v>
+        <v>3007.9</v>
       </c>
       <c r="L30" t="n">
-        <v>3031.83</v>
+        <v>3033.1</v>
       </c>
       <c r="M30" t="n">
-        <v>3077.55</v>
+        <v>3042.9</v>
       </c>
       <c r="N30" t="n">
-        <v>3123.27</v>
+        <v>3052.7</v>
       </c>
       <c r="O30" t="n">
-        <v>3117.5</v>
+        <v>3093.3</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3043,12 +3045,14 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3067,57 +3071,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3028.5</v>
+        <v>3008.5</v>
       </c>
       <c r="C31" t="n">
-        <v>3041</v>
+        <v>3046.8</v>
       </c>
       <c r="D31" t="n">
-        <v>3004.9</v>
+        <v>3002</v>
       </c>
       <c r="E31" t="n">
-        <v>3009.1</v>
+        <v>3041.6</v>
       </c>
       <c r="F31" t="n">
-        <v>-16.3</v>
+        <v>32.5</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0054</v>
+        <v>0.0108</v>
       </c>
       <c r="H31" t="n">
-        <v>36.1</v>
+        <v>44.8</v>
       </c>
       <c r="I31" t="n">
-        <v>2988.3</v>
+        <v>2968.8</v>
       </c>
       <c r="J31" t="n">
-        <v>2982.7</v>
+        <v>2966.08</v>
       </c>
       <c r="K31" t="n">
-        <v>3007.9</v>
+        <v>2991.05</v>
       </c>
       <c r="L31" t="n">
-        <v>3033.1</v>
+        <v>3016.03</v>
       </c>
       <c r="M31" t="n">
-        <v>3042.9</v>
+        <v>3027.15</v>
       </c>
       <c r="N31" t="n">
-        <v>3052.7</v>
+        <v>3038.28</v>
       </c>
       <c r="O31" t="n">
-        <v>3093.3</v>
+        <v>3077.1</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3125,22 +3129,24 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
@@ -3151,57 +3157,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3008.5</v>
+        <v>3038.9</v>
       </c>
       <c r="C32" t="n">
-        <v>3046.8</v>
+        <v>3044.6</v>
       </c>
       <c r="D32" t="n">
-        <v>3002</v>
+        <v>3016</v>
       </c>
       <c r="E32" t="n">
-        <v>3041.6</v>
+        <v>3025</v>
       </c>
       <c r="F32" t="n">
-        <v>32.5</v>
+        <v>-16.6</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0108</v>
+        <v>-0.0055</v>
       </c>
       <c r="H32" t="n">
-        <v>44.8</v>
+        <v>28.6</v>
       </c>
       <c r="I32" t="n">
-        <v>2968.8</v>
+        <v>2957.2</v>
       </c>
       <c r="J32" t="n">
-        <v>2966.08</v>
+        <v>3005.4</v>
       </c>
       <c r="K32" t="n">
-        <v>2991.05</v>
+        <v>3019.2</v>
       </c>
       <c r="L32" t="n">
-        <v>3016.03</v>
+        <v>3033</v>
       </c>
       <c r="M32" t="n">
-        <v>3027.15</v>
+        <v>3064</v>
       </c>
       <c r="N32" t="n">
-        <v>3038.28</v>
+        <v>3095</v>
       </c>
       <c r="O32" t="n">
-        <v>3077.1</v>
+        <v>3091.6</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3209,23 +3215,21 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3237,57 +3241,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3038.9</v>
+        <v>3024.7</v>
       </c>
       <c r="C33" t="n">
-        <v>3044.6</v>
+        <v>3045.8</v>
       </c>
       <c r="D33" t="n">
-        <v>3016</v>
+        <v>3019.9</v>
       </c>
       <c r="E33" t="n">
-        <v>3025</v>
+        <v>3035.5</v>
       </c>
       <c r="F33" t="n">
-        <v>-16.6</v>
+        <v>10.5</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0035</v>
       </c>
       <c r="H33" t="n">
-        <v>28.6</v>
+        <v>25.9</v>
       </c>
       <c r="I33" t="n">
-        <v>2957.2</v>
+        <v>2987.4</v>
       </c>
       <c r="J33" t="n">
-        <v>3005.4</v>
+        <v>2993.75</v>
       </c>
       <c r="K33" t="n">
-        <v>3019.2</v>
+        <v>3010.7</v>
       </c>
       <c r="L33" t="n">
-        <v>3033</v>
+        <v>3027.65</v>
       </c>
       <c r="M33" t="n">
-        <v>3064</v>
+        <v>3039.3</v>
       </c>
       <c r="N33" t="n">
-        <v>3095</v>
+        <v>3050.95</v>
       </c>
       <c r="O33" t="n">
-        <v>3091.6</v>
+        <v>3073.2</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3295,19 +3299,19 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3319,59 +3323,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3024.7</v>
+        <v>3036.1</v>
       </c>
       <c r="C34" t="n">
-        <v>3045.8</v>
+        <v>3060</v>
       </c>
       <c r="D34" t="n">
-        <v>3019.9</v>
+        <v>3033.1</v>
       </c>
       <c r="E34" t="n">
-        <v>3035.5</v>
+        <v>3052.8</v>
       </c>
       <c r="F34" t="n">
-        <v>10.5</v>
+        <v>17.3</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0057</v>
       </c>
       <c r="H34" t="n">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
       <c r="I34" t="n">
-        <v>2987.4</v>
+        <v>2994</v>
       </c>
       <c r="J34" t="n">
-        <v>2993.75</v>
+        <v>3010.92</v>
       </c>
       <c r="K34" t="n">
-        <v>3010.7</v>
+        <v>3022.55</v>
       </c>
       <c r="L34" t="n">
-        <v>3027.65</v>
+        <v>3034.17</v>
       </c>
       <c r="M34" t="n">
-        <v>3039.3</v>
+        <v>3048.45</v>
       </c>
       <c r="N34" t="n">
-        <v>3050.95</v>
+        <v>3062.73</v>
       </c>
       <c r="O34" t="n">
-        <v>3073.2</v>
+        <v>3071.7</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3382,7 +3382,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3408,50 +3408,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3036.1</v>
+        <v>3056.2</v>
       </c>
       <c r="C35" t="n">
-        <v>3060</v>
+        <v>3076.3</v>
       </c>
       <c r="D35" t="n">
-        <v>3033.1</v>
+        <v>3052.5</v>
       </c>
       <c r="E35" t="n">
-        <v>3052.8</v>
+        <v>3060.2</v>
       </c>
       <c r="F35" t="n">
-        <v>17.3</v>
+        <v>7.4</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0024</v>
       </c>
       <c r="H35" t="n">
-        <v>26.9</v>
+        <v>23.8</v>
       </c>
       <c r="I35" t="n">
-        <v>2994</v>
+        <v>3006.2</v>
       </c>
       <c r="J35" t="n">
-        <v>3010.92</v>
+        <v>3029.03</v>
       </c>
       <c r="K35" t="n">
-        <v>3022.55</v>
+        <v>3039.35</v>
       </c>
       <c r="L35" t="n">
-        <v>3034.17</v>
+        <v>3049.68</v>
       </c>
       <c r="M35" t="n">
-        <v>3048.45</v>
+        <v>3066.25</v>
       </c>
       <c r="N35" t="n">
-        <v>3062.73</v>
+        <v>3082.82</v>
       </c>
       <c r="O35" t="n">
-        <v>3071.7</v>
+        <v>3086.9</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3462,7 +3462,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3488,50 +3488,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3056.2</v>
+        <v>3062.2</v>
       </c>
       <c r="C36" t="n">
         <v>3076.3</v>
       </c>
       <c r="D36" t="n">
-        <v>3052.5</v>
+        <v>3051.7</v>
       </c>
       <c r="E36" t="n">
-        <v>3060.2</v>
+        <v>3074.9</v>
       </c>
       <c r="F36" t="n">
-        <v>7.4</v>
+        <v>14.7</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0048</v>
       </c>
       <c r="H36" t="n">
-        <v>23.8</v>
+        <v>24.6</v>
       </c>
       <c r="I36" t="n">
-        <v>3006.2</v>
+        <v>3028.7</v>
       </c>
       <c r="J36" t="n">
-        <v>3029.03</v>
+        <v>3034.3</v>
       </c>
       <c r="K36" t="n">
-        <v>3039.35</v>
+        <v>3048.3</v>
       </c>
       <c r="L36" t="n">
-        <v>3049.68</v>
+        <v>3062.3</v>
       </c>
       <c r="M36" t="n">
-        <v>3066.25</v>
+        <v>3072.1</v>
       </c>
       <c r="N36" t="n">
-        <v>3082.82</v>
+        <v>3081.9</v>
       </c>
       <c r="O36" t="n">
-        <v>3086.9</v>
+        <v>3100.1</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3542,7 +3542,7 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="7" t="inlineStr">
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3563,55 +3563,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3062.2</v>
+        <v>3073.5</v>
       </c>
       <c r="C37" t="n">
-        <v>3076.3</v>
+        <v>3079.9</v>
       </c>
       <c r="D37" t="n">
-        <v>3051.7</v>
+        <v>3055.9</v>
       </c>
       <c r="E37" t="n">
-        <v>3074.9</v>
+        <v>3064.9</v>
       </c>
       <c r="F37" t="n">
-        <v>14.7</v>
+        <v>-10</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.0033</v>
       </c>
       <c r="H37" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="I37" t="n">
-        <v>3028.7</v>
+        <v>3027.1</v>
       </c>
       <c r="J37" t="n">
-        <v>3034.3</v>
+        <v>3055.75</v>
       </c>
       <c r="K37" t="n">
-        <v>3048.3</v>
+        <v>3062.6</v>
       </c>
       <c r="L37" t="n">
-        <v>3062.3</v>
+        <v>3069.45</v>
       </c>
       <c r="M37" t="n">
-        <v>3072.1</v>
+        <v>3087.2</v>
       </c>
       <c r="N37" t="n">
-        <v>3081.9</v>
+        <v>3104.95</v>
       </c>
       <c r="O37" t="n">
-        <v>3100.1</v>
+        <v>3100.9</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3619,18 +3623,18 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3652,63 +3656,67 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3073.5</v>
+        <v>3063.7</v>
       </c>
       <c r="C38" t="n">
-        <v>3079.9</v>
+        <v>3066.6</v>
       </c>
       <c r="D38" t="n">
-        <v>3055.9</v>
+        <v>3024.1</v>
       </c>
       <c r="E38" t="n">
-        <v>3064.9</v>
+        <v>3026.4</v>
       </c>
       <c r="F38" t="n">
-        <v>-10</v>
+        <v>-38.5</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0126</v>
       </c>
       <c r="H38" t="n">
-        <v>24</v>
+        <v>42.5</v>
       </c>
       <c r="I38" t="n">
-        <v>3027.1</v>
+        <v>3031.9</v>
       </c>
       <c r="J38" t="n">
-        <v>3055.75</v>
+        <v>3039.4</v>
       </c>
       <c r="K38" t="n">
-        <v>3062.6</v>
+        <v>3052.9</v>
       </c>
       <c r="L38" t="n">
-        <v>3069.45</v>
+        <v>3066.4</v>
       </c>
       <c r="M38" t="n">
-        <v>3087.2</v>
+        <v>3076.9</v>
       </c>
       <c r="N38" t="n">
-        <v>3104.95</v>
+        <v>3087.4</v>
       </c>
       <c r="O38" t="n">
-        <v>3100.9</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
+        <v>3103.9</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3722,88 +3730,80 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W38" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3063.7</v>
+        <v>3025.9</v>
       </c>
       <c r="C39" t="n">
-        <v>3066.6</v>
+        <v>3059.1</v>
       </c>
       <c r="D39" t="n">
-        <v>3024.1</v>
+        <v>3019.8</v>
       </c>
       <c r="E39" t="n">
-        <v>3026.4</v>
+        <v>3039.9</v>
       </c>
       <c r="F39" t="n">
-        <v>-38.5</v>
+        <v>13.5</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0045</v>
       </c>
       <c r="H39" t="n">
-        <v>42.5</v>
+        <v>39.3</v>
       </c>
       <c r="I39" t="n">
-        <v>3031.9</v>
+        <v>2981.6</v>
       </c>
       <c r="J39" t="n">
-        <v>3039.4</v>
+        <v>2974.42</v>
       </c>
       <c r="K39" t="n">
-        <v>3052.9</v>
+        <v>3005.15</v>
       </c>
       <c r="L39" t="n">
-        <v>3066.4</v>
+        <v>3035.88</v>
       </c>
       <c r="M39" t="n">
-        <v>3076.9</v>
+        <v>3047.65</v>
       </c>
       <c r="N39" t="n">
-        <v>3087.4</v>
+        <v>3059.42</v>
       </c>
       <c r="O39" t="n">
-        <v>3103.9</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q39" s="6" t="inlineStr">
+        <v>3109.1</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3815,74 +3815,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3025.9</v>
+        <v>3041.4</v>
       </c>
       <c r="C40" t="n">
-        <v>3059.1</v>
+        <v>3048.5</v>
       </c>
       <c r="D40" t="n">
-        <v>3019.8</v>
+        <v>2993.2</v>
       </c>
       <c r="E40" t="n">
-        <v>3039.9</v>
+        <v>2999.2</v>
       </c>
       <c r="F40" t="n">
-        <v>13.5</v>
+        <v>-40.7</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0134</v>
       </c>
       <c r="H40" t="n">
-        <v>39.3</v>
+        <v>55.3</v>
       </c>
       <c r="I40" t="n">
-        <v>2981.6</v>
+        <v>2980.5</v>
       </c>
       <c r="J40" t="n">
-        <v>2974.42</v>
+        <v>3000.82</v>
       </c>
       <c r="K40" t="n">
-        <v>3005.15</v>
+        <v>3020.25</v>
       </c>
       <c r="L40" t="n">
-        <v>3035.88</v>
+        <v>3039.67</v>
       </c>
       <c r="M40" t="n">
-        <v>3047.65</v>
+        <v>3059.55</v>
       </c>
       <c r="N40" t="n">
-        <v>3059.42</v>
+        <v>3079.42</v>
       </c>
       <c r="O40" t="n">
-        <v>3109.1</v>
+        <v>3098.4</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3895,81 +3901,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3041.4</v>
+        <v>2999.6</v>
       </c>
       <c r="C41" t="n">
-        <v>3048.5</v>
+        <v>3026.7</v>
       </c>
       <c r="D41" t="n">
-        <v>2993.2</v>
+        <v>2997.9</v>
       </c>
       <c r="E41" t="n">
-        <v>2999.2</v>
+        <v>3022.1</v>
       </c>
       <c r="F41" t="n">
-        <v>-40.7</v>
+        <v>22.9</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0134</v>
+        <v>0.0076</v>
       </c>
       <c r="H41" t="n">
-        <v>55.3</v>
+        <v>28.8</v>
       </c>
       <c r="I41" t="n">
-        <v>2980.5</v>
+        <v>2937.9</v>
       </c>
       <c r="J41" t="n">
-        <v>3000.82</v>
+        <v>2933.07</v>
       </c>
       <c r="K41" t="n">
-        <v>3020.25</v>
+        <v>2971.55</v>
       </c>
       <c r="L41" t="n">
-        <v>3039.67</v>
+        <v>3010.02</v>
       </c>
       <c r="M41" t="n">
-        <v>3059.55</v>
+        <v>3026.85</v>
       </c>
       <c r="N41" t="n">
-        <v>3079.42</v>
+        <v>3043.67</v>
       </c>
       <c r="O41" t="n">
-        <v>3098.4</v>
+        <v>3103.8</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3981,74 +3981,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2999.6</v>
+        <v>3023</v>
       </c>
       <c r="C42" t="n">
-        <v>3026.7</v>
+        <v>3028.9</v>
       </c>
       <c r="D42" t="n">
-        <v>2997.9</v>
+        <v>2996</v>
       </c>
       <c r="E42" t="n">
-        <v>3022.1</v>
+        <v>3001.6</v>
       </c>
       <c r="F42" t="n">
-        <v>22.9</v>
+        <v>-20.5</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0076</v>
+        <v>-0.0068</v>
       </c>
       <c r="H42" t="n">
-        <v>28.8</v>
+        <v>32.9</v>
       </c>
       <c r="I42" t="n">
-        <v>2937.9</v>
+        <v>2969.1</v>
       </c>
       <c r="J42" t="n">
-        <v>2933.07</v>
+        <v>2998.2</v>
       </c>
       <c r="K42" t="n">
-        <v>2971.55</v>
+        <v>3007.7</v>
       </c>
       <c r="L42" t="n">
-        <v>3010.02</v>
+        <v>3017.2</v>
       </c>
       <c r="M42" t="n">
-        <v>3026.85</v>
+        <v>3036.5</v>
       </c>
       <c r="N42" t="n">
-        <v>3043.67</v>
+        <v>3055.8</v>
       </c>
       <c r="O42" t="n">
-        <v>3103.8</v>
+        <v>3055.5</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4063,79 +4069,77 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3023</v>
+        <v>3004.6</v>
       </c>
       <c r="C43" t="n">
-        <v>3028.9</v>
+        <v>3025.4</v>
       </c>
       <c r="D43" t="n">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="E43" t="n">
-        <v>3001.6</v>
+        <v>3014.4</v>
       </c>
       <c r="F43" t="n">
-        <v>-20.5</v>
+        <v>12.8</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0043</v>
       </c>
       <c r="H43" t="n">
-        <v>32.9</v>
+        <v>28.4</v>
       </c>
       <c r="I43" t="n">
-        <v>2969.1</v>
+        <v>2963.1</v>
       </c>
       <c r="J43" t="n">
-        <v>2998.2</v>
+        <v>2963.28</v>
       </c>
       <c r="K43" t="n">
-        <v>3007.7</v>
+        <v>2985.15</v>
       </c>
       <c r="L43" t="n">
-        <v>3017.2</v>
+        <v>3007.03</v>
       </c>
       <c r="M43" t="n">
-        <v>3036.5</v>
+        <v>3018.05</v>
       </c>
       <c r="N43" t="n">
-        <v>3055.8</v>
+        <v>3029.08</v>
       </c>
       <c r="O43" t="n">
-        <v>3055.5</v>
+        <v>3061.8</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4149,57 +4153,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3004.6</v>
+        <v>3014.6</v>
       </c>
       <c r="C44" t="n">
-        <v>3025.4</v>
+        <v>3020.5</v>
       </c>
       <c r="D44" t="n">
-        <v>2997</v>
+        <v>3002.6</v>
       </c>
       <c r="E44" t="n">
-        <v>3014.4</v>
+        <v>3010.1</v>
       </c>
       <c r="F44" t="n">
-        <v>12.8</v>
+        <v>-4.3</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0014</v>
       </c>
       <c r="H44" t="n">
-        <v>28.4</v>
+        <v>17.9</v>
       </c>
       <c r="I44" t="n">
-        <v>2963.1</v>
+        <v>2968.6</v>
       </c>
       <c r="J44" t="n">
-        <v>2963.28</v>
+        <v>2987.6</v>
       </c>
       <c r="K44" t="n">
-        <v>2985.15</v>
+        <v>3000.2</v>
       </c>
       <c r="L44" t="n">
-        <v>3007.03</v>
+        <v>3012.8</v>
       </c>
       <c r="M44" t="n">
-        <v>3018.05</v>
+        <v>3028.6</v>
       </c>
       <c r="N44" t="n">
-        <v>3029.08</v>
+        <v>3044.4</v>
       </c>
       <c r="O44" t="n">
-        <v>3061.8</v>
+        <v>3053.8</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4212,13 +4216,11 @@
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4233,57 +4235,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3014.6</v>
+        <v>3016.9</v>
       </c>
       <c r="C45" t="n">
-        <v>3020.5</v>
+        <v>3024.2</v>
       </c>
       <c r="D45" t="n">
-        <v>3002.6</v>
+        <v>3002.1</v>
       </c>
       <c r="E45" t="n">
-        <v>3010.1</v>
+        <v>3019</v>
       </c>
       <c r="F45" t="n">
-        <v>-4.3</v>
+        <v>8.9</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0014</v>
+        <v>0.003</v>
       </c>
       <c r="H45" t="n">
-        <v>17.9</v>
+        <v>22.1</v>
       </c>
       <c r="I45" t="n">
-        <v>2968.6</v>
+        <v>2984.7</v>
       </c>
       <c r="J45" t="n">
-        <v>2987.6</v>
+        <v>2991.48</v>
       </c>
       <c r="K45" t="n">
-        <v>3000.2</v>
+        <v>3001.15</v>
       </c>
       <c r="L45" t="n">
-        <v>3012.8</v>
+        <v>3010.83</v>
       </c>
       <c r="M45" t="n">
-        <v>3028.6</v>
+        <v>3019.05</v>
       </c>
       <c r="N45" t="n">
-        <v>3044.4</v>
+        <v>3027.28</v>
       </c>
       <c r="O45" t="n">
-        <v>3053.8</v>
+        <v>3038.4</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4296,11 +4298,13 @@
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4315,76 +4319,80 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3016.9</v>
+        <v>3019.6</v>
       </c>
       <c r="C46" t="n">
-        <v>3024.2</v>
+        <v>3025.5</v>
       </c>
       <c r="D46" t="n">
-        <v>3002.1</v>
+        <v>2976.6</v>
       </c>
       <c r="E46" t="n">
-        <v>3019</v>
+        <v>2977.5</v>
       </c>
       <c r="F46" t="n">
-        <v>8.9</v>
+        <v>-41.5</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0137</v>
       </c>
       <c r="H46" t="n">
-        <v>22.1</v>
+        <v>48.9</v>
       </c>
       <c r="I46" t="n">
-        <v>2984.7</v>
+        <v>2980</v>
       </c>
       <c r="J46" t="n">
-        <v>2991.48</v>
+        <v>2999.83</v>
       </c>
       <c r="K46" t="n">
-        <v>3001.15</v>
+        <v>3007.95</v>
       </c>
       <c r="L46" t="n">
-        <v>3010.83</v>
+        <v>3016.08</v>
       </c>
       <c r="M46" t="n">
-        <v>3019.05</v>
+        <v>3030.05</v>
       </c>
       <c r="N46" t="n">
-        <v>3027.28</v>
+        <v>3044.02</v>
       </c>
       <c r="O46" t="n">
-        <v>3038.4</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+        <v>3046.3</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4399,74 +4407,70 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3019.6</v>
+        <v>2971</v>
       </c>
       <c r="C47" t="n">
-        <v>3025.5</v>
+        <v>2982.5</v>
       </c>
       <c r="D47" t="n">
-        <v>2976.6</v>
+        <v>2946.1</v>
       </c>
       <c r="E47" t="n">
-        <v>2977.5</v>
+        <v>2958.7</v>
       </c>
       <c r="F47" t="n">
-        <v>-41.5</v>
+        <v>-18.8</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0063</v>
       </c>
       <c r="H47" t="n">
-        <v>48.9</v>
+        <v>36.4</v>
       </c>
       <c r="I47" t="n">
-        <v>2980</v>
+        <v>2927.7</v>
       </c>
       <c r="J47" t="n">
-        <v>2999.83</v>
+        <v>2916.83</v>
       </c>
       <c r="K47" t="n">
-        <v>3007.95</v>
+        <v>2953.05</v>
       </c>
       <c r="L47" t="n">
-        <v>3016.08</v>
+        <v>2989.28</v>
       </c>
       <c r="M47" t="n">
-        <v>3030.05</v>
+        <v>3001.95</v>
       </c>
       <c r="N47" t="n">
-        <v>3044.02</v>
+        <v>3014.62</v>
       </c>
       <c r="O47" t="n">
-        <v>3046.3</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
+        <v>3074.4</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4485,72 +4489,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2971</v>
+        <v>2958</v>
       </c>
       <c r="C48" t="n">
-        <v>2982.5</v>
+        <v>2964.6</v>
       </c>
       <c r="D48" t="n">
-        <v>2946.1</v>
+        <v>2918.9</v>
       </c>
       <c r="E48" t="n">
-        <v>2958.7</v>
+        <v>2924.7</v>
       </c>
       <c r="F48" t="n">
-        <v>-18.8</v>
+        <v>-34</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0115</v>
       </c>
       <c r="H48" t="n">
-        <v>36.4</v>
+        <v>45.7</v>
       </c>
       <c r="I48" t="n">
-        <v>2927.7</v>
+        <v>2909.7</v>
       </c>
       <c r="J48" t="n">
-        <v>2916.83</v>
+        <v>2919.5</v>
       </c>
       <c r="K48" t="n">
-        <v>2953.05</v>
+        <v>2940.5</v>
       </c>
       <c r="L48" t="n">
-        <v>2989.28</v>
+        <v>2961.5</v>
       </c>
       <c r="M48" t="n">
-        <v>3001.95</v>
+        <v>2976.9</v>
       </c>
       <c r="N48" t="n">
-        <v>3014.62</v>
+        <v>2992.3</v>
       </c>
       <c r="O48" t="n">
-        <v>3074.4</v>
+        <v>3018.9</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4574,75 +4576,75 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2958</v>
+        <v>2926.4</v>
       </c>
       <c r="C49" t="n">
-        <v>2964.6</v>
+        <v>2962.5</v>
       </c>
       <c r="D49" t="n">
-        <v>2918.9</v>
+        <v>2914.5</v>
       </c>
       <c r="E49" t="n">
-        <v>2924.7</v>
+        <v>2958.8</v>
       </c>
       <c r="F49" t="n">
-        <v>-34</v>
+        <v>34.1</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0.0117</v>
       </c>
       <c r="H49" t="n">
-        <v>45.7</v>
+        <v>48</v>
       </c>
       <c r="I49" t="n">
-        <v>2909.7</v>
+        <v>2873.2</v>
       </c>
       <c r="J49" t="n">
-        <v>2919.5</v>
+        <v>2870.47</v>
       </c>
       <c r="K49" t="n">
-        <v>2940.5</v>
+        <v>2901.85</v>
       </c>
       <c r="L49" t="n">
-        <v>2961.5</v>
+        <v>2933.22</v>
       </c>
       <c r="M49" t="n">
-        <v>2976.9</v>
+        <v>2947.55</v>
       </c>
       <c r="N49" t="n">
-        <v>2992.3</v>
+        <v>2961.88</v>
       </c>
       <c r="O49" t="n">
-        <v>3018.9</v>
+        <v>3010.3</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
@@ -4651,55 +4653,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2926.4</v>
+        <v>2957.6</v>
       </c>
       <c r="C50" t="n">
-        <v>2962.5</v>
+        <v>2983.3</v>
       </c>
       <c r="D50" t="n">
-        <v>2914.5</v>
+        <v>2949.9</v>
       </c>
       <c r="E50" t="n">
-        <v>2958.8</v>
+        <v>2969.7</v>
       </c>
       <c r="F50" t="n">
-        <v>34.1</v>
+        <v>10.9</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0117</v>
+        <v>0.0037</v>
       </c>
       <c r="H50" t="n">
-        <v>48</v>
+        <v>33.4</v>
       </c>
       <c r="I50" t="n">
-        <v>2873.2</v>
+        <v>2866.5</v>
       </c>
       <c r="J50" t="n">
-        <v>2870.47</v>
+        <v>2920.95</v>
       </c>
       <c r="K50" t="n">
-        <v>2901.85</v>
+        <v>2934.8</v>
       </c>
       <c r="L50" t="n">
-        <v>2933.22</v>
+        <v>2948.65</v>
       </c>
       <c r="M50" t="n">
-        <v>2947.55</v>
+        <v>2982.8</v>
       </c>
       <c r="N50" t="n">
-        <v>2961.88</v>
+        <v>3016.95</v>
       </c>
       <c r="O50" t="n">
-        <v>3010.3</v>
+        <v>3010.5</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4710,21 +4716,19 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="7" t="inlineStr">
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
@@ -4735,57 +4739,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2957.6</v>
+        <v>2967.9</v>
       </c>
       <c r="C51" t="n">
-        <v>2983.3</v>
+        <v>2979.3</v>
       </c>
       <c r="D51" t="n">
-        <v>2949.9</v>
+        <v>2949.5</v>
       </c>
       <c r="E51" t="n">
-        <v>2969.7</v>
+        <v>2976.6</v>
       </c>
       <c r="F51" t="n">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0023</v>
       </c>
       <c r="H51" t="n">
-        <v>33.4</v>
+        <v>29.8</v>
       </c>
       <c r="I51" t="n">
-        <v>2866.5</v>
+        <v>2916.5</v>
       </c>
       <c r="J51" t="n">
-        <v>2920.95</v>
+        <v>2937.85</v>
       </c>
       <c r="K51" t="n">
-        <v>2934.8</v>
+        <v>2953</v>
       </c>
       <c r="L51" t="n">
-        <v>2948.65</v>
+        <v>2968.15</v>
       </c>
       <c r="M51" t="n">
-        <v>2982.8</v>
+        <v>2986.4</v>
       </c>
       <c r="N51" t="n">
-        <v>3016.95</v>
+        <v>3004.65</v>
       </c>
       <c r="O51" t="n">
-        <v>3010.5</v>
+        <v>3016.7</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4793,18 +4797,18 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4819,57 +4823,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2967.9</v>
+        <v>2974.7</v>
       </c>
       <c r="C52" t="n">
-        <v>2979.3</v>
+        <v>2977.9</v>
       </c>
       <c r="D52" t="n">
-        <v>2949.5</v>
+        <v>2954.7</v>
       </c>
       <c r="E52" t="n">
-        <v>2976.6</v>
+        <v>2963.6</v>
       </c>
       <c r="F52" t="n">
-        <v>6.9</v>
+        <v>-13</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0044</v>
       </c>
       <c r="H52" t="n">
-        <v>29.8</v>
+        <v>23.2</v>
       </c>
       <c r="I52" t="n">
-        <v>2916.5</v>
+        <v>2919.7</v>
       </c>
       <c r="J52" t="n">
-        <v>2937.85</v>
+        <v>2952.9</v>
       </c>
       <c r="K52" t="n">
-        <v>2953</v>
+        <v>2961.7</v>
       </c>
       <c r="L52" t="n">
-        <v>2968.15</v>
+        <v>2970.5</v>
       </c>
       <c r="M52" t="n">
-        <v>2986.4</v>
+        <v>2991.5</v>
       </c>
       <c r="N52" t="n">
-        <v>3004.65</v>
+        <v>3012.5</v>
       </c>
       <c r="O52" t="n">
-        <v>3016.7</v>
+        <v>3009.1</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4879,12 +4883,12 @@
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4910,63 +4914,67 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2974.7</v>
+        <v>2963.1</v>
       </c>
       <c r="C53" t="n">
-        <v>2977.9</v>
+        <v>2966.2</v>
       </c>
       <c r="D53" t="n">
-        <v>2954.7</v>
+        <v>2919.4</v>
       </c>
       <c r="E53" t="n">
-        <v>2963.6</v>
+        <v>2923</v>
       </c>
       <c r="F53" t="n">
-        <v>-13</v>
+        <v>-40.6</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0137</v>
       </c>
       <c r="H53" t="n">
-        <v>23.2</v>
+        <v>46.8</v>
       </c>
       <c r="I53" t="n">
-        <v>2919.7</v>
+        <v>2931.5</v>
       </c>
       <c r="J53" t="n">
-        <v>2952.9</v>
+        <v>2939.05</v>
       </c>
       <c r="K53" t="n">
-        <v>2961.7</v>
+        <v>2952</v>
       </c>
       <c r="L53" t="n">
-        <v>2970.5</v>
+        <v>2964.95</v>
       </c>
       <c r="M53" t="n">
-        <v>2991.5</v>
+        <v>2975.2</v>
       </c>
       <c r="N53" t="n">
-        <v>3012.5</v>
+        <v>2985.45</v>
       </c>
       <c r="O53" t="n">
-        <v>3009.1</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
+        <v>3001.1</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4985,76 +4993,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2963.1</v>
+        <v>2923.1</v>
       </c>
       <c r="C54" t="n">
-        <v>2966.2</v>
+        <v>2933.8</v>
       </c>
       <c r="D54" t="n">
-        <v>2919.4</v>
+        <v>2887.8</v>
       </c>
       <c r="E54" t="n">
-        <v>2923</v>
+        <v>2893.4</v>
       </c>
       <c r="F54" t="n">
-        <v>-40.6</v>
+        <v>-29.6</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0101</v>
       </c>
       <c r="H54" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="I54" t="n">
-        <v>2931.5</v>
+        <v>2872.6</v>
       </c>
       <c r="J54" t="n">
-        <v>2939.05</v>
+        <v>2866.3</v>
       </c>
       <c r="K54" t="n">
-        <v>2952</v>
+        <v>2899.6</v>
       </c>
       <c r="L54" t="n">
-        <v>2964.95</v>
+        <v>2932.9</v>
       </c>
       <c r="M54" t="n">
-        <v>2975.2</v>
+        <v>2946.4</v>
       </c>
       <c r="N54" t="n">
-        <v>2985.45</v>
+        <v>2959.9</v>
       </c>
       <c r="O54" t="n">
-        <v>3001.1</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
+        <v>3013</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
+      <c r="S54" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5078,50 +5078,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2923.1</v>
+        <v>2890.9</v>
       </c>
       <c r="C55" t="n">
-        <v>2933.8</v>
+        <v>2929.8</v>
       </c>
       <c r="D55" t="n">
-        <v>2887.8</v>
+        <v>2887.6</v>
       </c>
       <c r="E55" t="n">
-        <v>2893.4</v>
+        <v>2904.5</v>
       </c>
       <c r="F55" t="n">
-        <v>-29.6</v>
+        <v>11.1</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0101</v>
+        <v>0.0038</v>
       </c>
       <c r="H55" t="n">
-        <v>46</v>
+        <v>42.2</v>
       </c>
       <c r="I55" t="n">
-        <v>2872.6</v>
+        <v>2841.8</v>
       </c>
       <c r="J55" t="n">
-        <v>2866.3</v>
+        <v>2838.7</v>
       </c>
       <c r="K55" t="n">
-        <v>2899.6</v>
+        <v>2870.4</v>
       </c>
       <c r="L55" t="n">
-        <v>2932.9</v>
+        <v>2902.1</v>
       </c>
       <c r="M55" t="n">
-        <v>2946.4</v>
+        <v>2916.4</v>
       </c>
       <c r="N55" t="n">
-        <v>2959.9</v>
+        <v>2930.7</v>
       </c>
       <c r="O55" t="n">
-        <v>3013</v>
+        <v>2979.8</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5129,18 +5129,18 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R55" s="6" t="n">
+        <v/>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5153,55 +5153,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2890.9</v>
+        <v>2892.7</v>
       </c>
       <c r="C56" t="n">
-        <v>2929.8</v>
+        <v>2913.5</v>
       </c>
       <c r="D56" t="n">
-        <v>2887.6</v>
+        <v>2884.3</v>
       </c>
       <c r="E56" t="n">
-        <v>2904.5</v>
+        <v>2894.1</v>
       </c>
       <c r="F56" t="n">
-        <v>11.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0036</v>
       </c>
       <c r="H56" t="n">
-        <v>42.2</v>
+        <v>29.2</v>
       </c>
       <c r="I56" t="n">
-        <v>2841.8</v>
+        <v>2845.4</v>
       </c>
       <c r="J56" t="n">
-        <v>2838.7</v>
+        <v>2860.2</v>
       </c>
       <c r="K56" t="n">
-        <v>2870.4</v>
+        <v>2883.4</v>
       </c>
       <c r="L56" t="n">
-        <v>2902.1</v>
+        <v>2906.6</v>
       </c>
       <c r="M56" t="n">
-        <v>2916.4</v>
+        <v>2925.6</v>
       </c>
       <c r="N56" t="n">
-        <v>2930.7</v>
+        <v>2944.6</v>
       </c>
       <c r="O56" t="n">
-        <v>2979.8</v>
+        <v>2972</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5209,18 +5213,18 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5233,59 +5237,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2892.7</v>
+        <v>2896.4</v>
       </c>
       <c r="C57" t="n">
-        <v>2913.5</v>
+        <v>2896.5</v>
       </c>
       <c r="D57" t="n">
-        <v>2884.3</v>
+        <v>2862.7</v>
       </c>
       <c r="E57" t="n">
-        <v>2894.1</v>
+        <v>2873.1</v>
       </c>
       <c r="F57" t="n">
-        <v>-10.4</v>
+        <v>-21</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0073</v>
       </c>
       <c r="H57" t="n">
-        <v>29.2</v>
+        <v>33.8</v>
       </c>
       <c r="I57" t="n">
-        <v>2845.4</v>
+        <v>2855.1</v>
       </c>
       <c r="J57" t="n">
-        <v>2860.2</v>
+        <v>2862.5</v>
       </c>
       <c r="K57" t="n">
-        <v>2883.4</v>
+        <v>2879.5</v>
       </c>
       <c r="L57" t="n">
-        <v>2906.6</v>
+        <v>2896.5</v>
       </c>
       <c r="M57" t="n">
-        <v>2925.6</v>
+        <v>2908.7</v>
       </c>
       <c r="N57" t="n">
-        <v>2944.6</v>
+        <v>2920.9</v>
       </c>
       <c r="O57" t="n">
-        <v>2972</v>
+        <v>2942.7</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5298,7 +5298,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5322,69 +5322,73 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2896.4</v>
+        <v>2875.1</v>
       </c>
       <c r="C58" t="n">
-        <v>2896.5</v>
+        <v>2892.5</v>
       </c>
       <c r="D58" t="n">
-        <v>2862.7</v>
+        <v>2831.9</v>
       </c>
       <c r="E58" t="n">
-        <v>2873.1</v>
+        <v>2861.7</v>
       </c>
       <c r="F58" t="n">
-        <v>-21</v>
+        <v>-11.4</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.004</v>
       </c>
       <c r="H58" t="n">
-        <v>33.8</v>
+        <v>60.6</v>
       </c>
       <c r="I58" t="n">
-        <v>2855.1</v>
+        <v>2828.9</v>
       </c>
       <c r="J58" t="n">
-        <v>2862.5</v>
+        <v>2836.05</v>
       </c>
       <c r="K58" t="n">
-        <v>2879.5</v>
+        <v>2856.2</v>
       </c>
       <c r="L58" t="n">
-        <v>2896.5</v>
+        <v>2876.35</v>
       </c>
       <c r="M58" t="n">
-        <v>2908.7</v>
+        <v>2890</v>
       </c>
       <c r="N58" t="n">
-        <v>2920.9</v>
+        <v>2903.65</v>
       </c>
       <c r="O58" t="n">
-        <v>2942.7</v>
+        <v>2930.3</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S58" s="10" t="inlineStr">
+      <c r="S58" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5402,74 +5406,70 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2875.1</v>
+        <v>2861.2</v>
       </c>
       <c r="C59" t="n">
-        <v>2892.5</v>
+        <v>2904.6</v>
       </c>
       <c r="D59" t="n">
-        <v>2831.9</v>
+        <v>2859.3</v>
       </c>
       <c r="E59" t="n">
-        <v>2861.7</v>
+        <v>2875.9</v>
       </c>
       <c r="F59" t="n">
-        <v>-11.4</v>
+        <v>14.2</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.005</v>
       </c>
       <c r="H59" t="n">
-        <v>60.6</v>
+        <v>45.3</v>
       </c>
       <c r="I59" t="n">
-        <v>2828.9</v>
+        <v>2771.3</v>
       </c>
       <c r="J59" t="n">
-        <v>2836.05</v>
+        <v>2800.85</v>
       </c>
       <c r="K59" t="n">
-        <v>2856.2</v>
+        <v>2831.4</v>
       </c>
       <c r="L59" t="n">
-        <v>2876.35</v>
+        <v>2861.95</v>
       </c>
       <c r="M59" t="n">
-        <v>2890</v>
+        <v>2892</v>
       </c>
       <c r="N59" t="n">
-        <v>2903.65</v>
+        <v>2922.05</v>
       </c>
       <c r="O59" t="n">
-        <v>2930.3</v>
+        <v>2953.1</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U59" s="8" t="n">
         <v/>
       </c>
@@ -5481,55 +5481,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2861.2</v>
+        <v>2870.5</v>
       </c>
       <c r="C60" t="n">
-        <v>2904.6</v>
+        <v>2883</v>
       </c>
       <c r="D60" t="n">
-        <v>2859.3</v>
+        <v>2856.9</v>
       </c>
       <c r="E60" t="n">
-        <v>2875.9</v>
+        <v>2873.23</v>
       </c>
       <c r="F60" t="n">
-        <v>14.2</v>
+        <v>-2.67</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0009</v>
       </c>
       <c r="H60" t="n">
-        <v>45.3</v>
+        <v>26.1</v>
       </c>
       <c r="I60" t="n">
-        <v>2771.3</v>
+        <v>2814</v>
       </c>
       <c r="J60" t="n">
-        <v>2800.85</v>
+        <v>2827.57</v>
       </c>
       <c r="K60" t="n">
-        <v>2831.4</v>
+        <v>2853.25</v>
       </c>
       <c r="L60" t="n">
-        <v>2861.95</v>
+        <v>2878.92</v>
       </c>
       <c r="M60" t="n">
-        <v>2892</v>
+        <v>2898.55</v>
       </c>
       <c r="N60" t="n">
-        <v>2922.05</v>
+        <v>2918.17</v>
       </c>
       <c r="O60" t="n">
-        <v>2953.1</v>
+        <v>2949.9</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5542,13 +5546,11 @@
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5561,59 +5563,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2870.5</v>
+        <v>2879.5</v>
       </c>
       <c r="C61" t="n">
-        <v>2883</v>
+        <v>2907.3</v>
       </c>
       <c r="D61" t="n">
-        <v>2856.9</v>
+        <v>2876.6</v>
       </c>
       <c r="E61" t="n">
-        <v>2873.23</v>
+        <v>2897.4</v>
       </c>
       <c r="F61" t="n">
-        <v>-2.67</v>
+        <v>24.17</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>26.1</v>
+        <v>30.7</v>
       </c>
       <c r="I61" t="n">
-        <v>2814</v>
+        <v>2830.8</v>
       </c>
       <c r="J61" t="n">
-        <v>2827.57</v>
+        <v>2848.77</v>
       </c>
       <c r="K61" t="n">
-        <v>2853.25</v>
+        <v>2860.18</v>
       </c>
       <c r="L61" t="n">
-        <v>2878.92</v>
+        <v>2871.59</v>
       </c>
       <c r="M61" t="n">
-        <v>2898.55</v>
+        <v>2886.28</v>
       </c>
       <c r="N61" t="n">
-        <v>2918.17</v>
+        <v>2900.97</v>
       </c>
       <c r="O61" t="n">
-        <v>2949.9</v>
+        <v>2909.1</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5626,14 +5624,18 @@
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
@@ -5643,55 +5645,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2879.5</v>
+        <v>2912</v>
       </c>
       <c r="C62" t="n">
-        <v>2907.3</v>
+        <v>2914.3</v>
       </c>
       <c r="D62" t="n">
-        <v>2876.6</v>
+        <v>2911.9</v>
       </c>
       <c r="E62" t="n">
-        <v>2897.4</v>
+        <v>2913</v>
       </c>
       <c r="F62" t="n">
-        <v>24.17</v>
+        <v>15.6</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0054</v>
       </c>
       <c r="H62" t="n">
-        <v>30.7</v>
+        <v>2.4</v>
       </c>
       <c r="I62" t="n">
-        <v>2830.8</v>
+        <v>2845.9</v>
       </c>
       <c r="J62" t="n">
-        <v>2848.77</v>
+        <v>2869.42</v>
       </c>
       <c r="K62" t="n">
-        <v>2860.18</v>
+        <v>2882.05</v>
       </c>
       <c r="L62" t="n">
-        <v>2871.59</v>
+        <v>2894.67</v>
       </c>
       <c r="M62" t="n">
-        <v>2886.28</v>
+        <v>2912.75</v>
       </c>
       <c r="N62" t="n">
-        <v>2900.97</v>
+        <v>2930.82</v>
       </c>
       <c r="O62" t="n">
-        <v>2909.1</v>
+        <v>2938</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5702,21 +5708,19 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="7" t="inlineStr">
+      <c r="S62" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T62" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
       <c r="V62" s="8" t="n">
         <v/>
       </c>
@@ -5726,92 +5730,6 @@
         </is>
       </c>
       <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>2897.8</v>
-      </c>
-      <c r="C63" t="n">
-        <v>2931.2</v>
-      </c>
-      <c r="D63" t="n">
-        <v>2884.2</v>
-      </c>
-      <c r="E63" t="n">
-        <v>2904.8</v>
-      </c>
-      <c r="F63" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0.0026</v>
-      </c>
-      <c r="H63" t="n">
-        <v>47</v>
-      </c>
-      <c r="I63" t="n">
-        <v>2845.9</v>
-      </c>
-      <c r="J63" t="n">
-        <v>2869.42</v>
-      </c>
-      <c r="K63" t="n">
-        <v>2882.05</v>
-      </c>
-      <c r="L63" t="n">
-        <v>2894.67</v>
-      </c>
-      <c r="M63" t="n">
-        <v>2912.75</v>
-      </c>
-      <c r="N63" t="n">
-        <v>2930.82</v>
-      </c>
-      <c r="O63" t="n">
-        <v>2938</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
         <is>
           <t>強警訊</t>
         </is>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -5661,22 +5661,22 @@
         <v>2912</v>
       </c>
       <c r="C62" t="n">
-        <v>2914.3</v>
+        <v>2915.2</v>
       </c>
       <c r="D62" t="n">
-        <v>2911.9</v>
+        <v>2909.7</v>
       </c>
       <c r="E62" t="n">
-        <v>2913</v>
+        <v>2910.5</v>
       </c>
       <c r="F62" t="n">
-        <v>15.6</v>
+        <v>13.1</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0045</v>
       </c>
       <c r="H62" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="I62" t="n">
         <v>2845.9</v>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -5667,13 +5667,13 @@
         <v>2909.7</v>
       </c>
       <c r="E62" t="n">
-        <v>2910.5</v>
+        <v>2910.1</v>
       </c>
       <c r="F62" t="n">
-        <v>13.1</v>
+        <v>12.7</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0045</v>
+        <v>0.0044</v>
       </c>
       <c r="H62" t="n">
         <v>5.5</v>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -5664,19 +5664,19 @@
         <v>2915.2</v>
       </c>
       <c r="D62" t="n">
-        <v>2909.7</v>
+        <v>2909.4</v>
       </c>
       <c r="E62" t="n">
-        <v>2910.1</v>
+        <v>2911.4</v>
       </c>
       <c r="F62" t="n">
-        <v>12.7</v>
+        <v>14</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0048</v>
       </c>
       <c r="H62" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="I62" t="n">
         <v>2845.9</v>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -5667,13 +5667,13 @@
         <v>2909.4</v>
       </c>
       <c r="E62" t="n">
-        <v>2911.4</v>
+        <v>2912.2</v>
       </c>
       <c r="F62" t="n">
-        <v>14</v>
+        <v>14.8</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0048</v>
+        <v>0.0051</v>
       </c>
       <c r="H62" t="n">
         <v>5.8</v>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5658,25 +5658,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2912</v>
+        <v>2897.8</v>
       </c>
       <c r="C62" t="n">
-        <v>2915.2</v>
+        <v>2931.2</v>
       </c>
       <c r="D62" t="n">
-        <v>2909.4</v>
+        <v>2884.2</v>
       </c>
       <c r="E62" t="n">
-        <v>2912.2</v>
+        <v>2914.1</v>
       </c>
       <c r="F62" t="n">
-        <v>14.8</v>
+        <v>16.7</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0058</v>
       </c>
       <c r="H62" t="n">
-        <v>5.8</v>
+        <v>47</v>
       </c>
       <c r="I62" t="n">
         <v>2845.9</v>
@@ -5718,8 +5718,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U62" s="8" t="n">
-        <v/>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V62" s="8" t="n">
         <v/>
@@ -5732,6 +5734,90 @@
       <c r="X62" t="inlineStr">
         <is>
           <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2912</v>
+      </c>
+      <c r="C63" t="n">
+        <v>2915.3</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2895.5</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2897.2</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-16.9</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="H63" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2837.2</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2870.3</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2890.6</v>
+      </c>
+      <c r="L63" t="n">
+        <v>2910.9</v>
+      </c>
+      <c r="M63" t="n">
+        <v>2937.6</v>
+      </c>
+      <c r="N63" t="n">
+        <v>2964.3</v>
+      </c>
+      <c r="O63" t="n">
+        <v>2978.2</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3034.7</v>
+        <v>3020.9</v>
       </c>
       <c r="C2" t="n">
-        <v>3045.7</v>
+        <v>3044.9</v>
       </c>
       <c r="D2" t="n">
-        <v>2999.6</v>
+        <v>2987.8</v>
       </c>
       <c r="E2" t="n">
-        <v>3022.6</v>
+        <v>3030.6</v>
       </c>
       <c r="F2" t="n">
-        <v>-8.1</v>
+        <v>8</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0026</v>
       </c>
       <c r="H2" t="n">
-        <v>46.1</v>
+        <v>57.1</v>
       </c>
       <c r="I2" t="n">
-        <v>2958.6</v>
+        <v>2953.5</v>
       </c>
       <c r="J2" t="n">
-        <v>2975.93</v>
+        <v>2976.48</v>
       </c>
       <c r="K2" t="n">
-        <v>3004.75</v>
+        <v>2999.55</v>
       </c>
       <c r="L2" t="n">
-        <v>3033.57</v>
+        <v>3022.63</v>
       </c>
       <c r="M2" t="n">
-        <v>3056.65</v>
+        <v>3045.65</v>
       </c>
       <c r="N2" t="n">
-        <v>3079.72</v>
+        <v>3068.67</v>
       </c>
       <c r="O2" t="n">
-        <v>3114.3</v>
+        <v>3091.8</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,7 +692,7 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -711,57 +711,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3020.9</v>
+        <v>3026.1</v>
       </c>
       <c r="C3" t="n">
-        <v>3044.9</v>
+        <v>3050.6</v>
       </c>
       <c r="D3" t="n">
-        <v>2987.8</v>
+        <v>3015.1</v>
       </c>
       <c r="E3" t="n">
-        <v>3030.6</v>
+        <v>3045.6</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0049</v>
       </c>
       <c r="H3" t="n">
-        <v>57.1</v>
+        <v>35.5</v>
       </c>
       <c r="I3" t="n">
-        <v>2953.5</v>
+        <v>2930.7</v>
       </c>
       <c r="J3" t="n">
-        <v>2976.48</v>
+        <v>2980.63</v>
       </c>
       <c r="K3" t="n">
-        <v>2999.55</v>
+        <v>3002.05</v>
       </c>
       <c r="L3" t="n">
-        <v>3022.63</v>
+        <v>3023.48</v>
       </c>
       <c r="M3" t="n">
-        <v>3045.65</v>
+        <v>3059.15</v>
       </c>
       <c r="N3" t="n">
-        <v>3068.67</v>
+        <v>3094.83</v>
       </c>
       <c r="O3" t="n">
-        <v>3091.8</v>
+        <v>3102</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -769,18 +769,18 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -793,59 +793,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3026.1</v>
+        <v>3040</v>
       </c>
       <c r="C4" t="n">
-        <v>3050.6</v>
+        <v>3068.4</v>
       </c>
       <c r="D4" t="n">
-        <v>3015.1</v>
+        <v>3023.7</v>
       </c>
       <c r="E4" t="n">
-        <v>3045.6</v>
+        <v>3035.1</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>-10.5</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.0034</v>
       </c>
       <c r="H4" t="n">
-        <v>35.5</v>
+        <v>44.7</v>
       </c>
       <c r="I4" t="n">
-        <v>2930.7</v>
+        <v>2979.6</v>
       </c>
       <c r="J4" t="n">
-        <v>2980.63</v>
+        <v>3016.48</v>
       </c>
       <c r="K4" t="n">
-        <v>3002.05</v>
+        <v>3027.85</v>
       </c>
       <c r="L4" t="n">
-        <v>3023.48</v>
+        <v>3039.23</v>
       </c>
       <c r="M4" t="n">
-        <v>3059.15</v>
+        <v>3063.35</v>
       </c>
       <c r="N4" t="n">
-        <v>3094.83</v>
+        <v>3087.48</v>
       </c>
       <c r="O4" t="n">
-        <v>3102</v>
+        <v>3086.1</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -853,17 +849,19 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U4" s="8" t="n">
@@ -877,55 +875,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3040</v>
+        <v>3030.9</v>
       </c>
       <c r="C5" t="n">
-        <v>3068.4</v>
+        <v>3062.4</v>
       </c>
       <c r="D5" t="n">
-        <v>3023.7</v>
+        <v>2988.5</v>
       </c>
       <c r="E5" t="n">
-        <v>3035.1</v>
+        <v>3014.2</v>
       </c>
       <c r="F5" t="n">
-        <v>-10.5</v>
+        <v>-20.9</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0069</v>
       </c>
       <c r="H5" t="n">
-        <v>44.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>2979.6</v>
+        <v>2979</v>
       </c>
       <c r="J5" t="n">
-        <v>3016.48</v>
+        <v>2984.93</v>
       </c>
       <c r="K5" t="n">
-        <v>3027.85</v>
+        <v>3012.75</v>
       </c>
       <c r="L5" t="n">
-        <v>3039.23</v>
+        <v>3040.58</v>
       </c>
       <c r="M5" t="n">
-        <v>3063.35</v>
+        <v>3057.45</v>
       </c>
       <c r="N5" t="n">
-        <v>3087.48</v>
+        <v>3074.33</v>
       </c>
       <c r="O5" t="n">
-        <v>3086.1</v>
+        <v>3113.1</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -935,19 +937,19 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -961,57 +963,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3030.9</v>
+        <v>3019.7</v>
       </c>
       <c r="C6" t="n">
-        <v>3062.4</v>
+        <v>3042.1</v>
       </c>
       <c r="D6" t="n">
-        <v>2988.5</v>
+        <v>3006.7</v>
       </c>
       <c r="E6" t="n">
-        <v>3014.2</v>
+        <v>3027</v>
       </c>
       <c r="F6" t="n">
-        <v>-20.9</v>
+        <v>12.8</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0042</v>
       </c>
       <c r="H6" t="n">
-        <v>73.90000000000001</v>
+        <v>35.4</v>
       </c>
       <c r="I6" t="n">
-        <v>2979</v>
+        <v>2914.6</v>
       </c>
       <c r="J6" t="n">
-        <v>2984.93</v>
+        <v>2934.68</v>
       </c>
       <c r="K6" t="n">
-        <v>3012.75</v>
+        <v>2977.25</v>
       </c>
       <c r="L6" t="n">
-        <v>3040.58</v>
+        <v>3019.82</v>
       </c>
       <c r="M6" t="n">
-        <v>3057.45</v>
+        <v>3051.15</v>
       </c>
       <c r="N6" t="n">
-        <v>3074.33</v>
+        <v>3082.47</v>
       </c>
       <c r="O6" t="n">
-        <v>3113.1</v>
+        <v>3136.3</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1019,20 +1021,16 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R6" s="6" t="n">
+        <v/>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1047,70 +1045,74 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3019.7</v>
+        <v>3033.4</v>
       </c>
       <c r="C7" t="n">
-        <v>3042.1</v>
+        <v>3042.6</v>
       </c>
       <c r="D7" t="n">
-        <v>3006.7</v>
+        <v>2988.8</v>
       </c>
       <c r="E7" t="n">
-        <v>3027</v>
+        <v>2998.8</v>
       </c>
       <c r="F7" t="n">
-        <v>12.8</v>
+        <v>-28.2</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>35.4</v>
+        <v>53.8</v>
       </c>
       <c r="I7" t="n">
-        <v>2914.6</v>
+        <v>2971.3</v>
       </c>
       <c r="J7" t="n">
-        <v>2934.68</v>
+        <v>2992.9</v>
       </c>
       <c r="K7" t="n">
-        <v>2977.25</v>
+        <v>3009.3</v>
       </c>
       <c r="L7" t="n">
-        <v>3019.82</v>
+        <v>3025.7</v>
       </c>
       <c r="M7" t="n">
-        <v>3051.15</v>
+        <v>3044.7</v>
       </c>
       <c r="N7" t="n">
-        <v>3082.47</v>
+        <v>3063.7</v>
       </c>
       <c r="O7" t="n">
-        <v>3136.3</v>
+        <v>3077.5</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1129,72 +1131,70 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3033.4</v>
+        <v>2994.3</v>
       </c>
       <c r="C8" t="n">
-        <v>3042.6</v>
+        <v>3004.3</v>
       </c>
       <c r="D8" t="n">
-        <v>2988.8</v>
+        <v>2943.4</v>
       </c>
       <c r="E8" t="n">
-        <v>2998.8</v>
+        <v>2971.5</v>
       </c>
       <c r="F8" t="n">
-        <v>-28.2</v>
+        <v>-27.3</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0091</v>
       </c>
       <c r="H8" t="n">
-        <v>53.8</v>
+        <v>60.9</v>
       </c>
       <c r="I8" t="n">
-        <v>2971.3</v>
+        <v>2935</v>
       </c>
       <c r="J8" t="n">
-        <v>2992.9</v>
+        <v>2936.55</v>
       </c>
       <c r="K8" t="n">
-        <v>3009.3</v>
+        <v>2971.9</v>
       </c>
       <c r="L8" t="n">
+        <v>3007.25</v>
+      </c>
+      <c r="M8" t="n">
         <v>3025.7</v>
       </c>
-      <c r="M8" t="n">
-        <v>3044.7</v>
-      </c>
       <c r="N8" t="n">
-        <v>3063.7</v>
+        <v>3044.15</v>
       </c>
       <c r="O8" t="n">
-        <v>3077.5</v>
+        <v>3096.4</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1215,57 +1215,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2994.3</v>
+        <v>2965.8</v>
       </c>
       <c r="C9" t="n">
-        <v>3004.3</v>
+        <v>3014.9</v>
       </c>
       <c r="D9" t="n">
-        <v>2943.4</v>
+        <v>2964.3</v>
       </c>
       <c r="E9" t="n">
-        <v>2971.5</v>
+        <v>3008.4</v>
       </c>
       <c r="F9" t="n">
-        <v>-27.3</v>
+        <v>36.9</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0091</v>
+        <v>0.0124</v>
       </c>
       <c r="H9" t="n">
-        <v>60.9</v>
+        <v>50.6</v>
       </c>
       <c r="I9" t="n">
-        <v>2935</v>
+        <v>2882.5</v>
       </c>
       <c r="J9" t="n">
-        <v>2936.55</v>
+        <v>2909.42</v>
       </c>
       <c r="K9" t="n">
-        <v>2971.9</v>
+        <v>2941.05</v>
       </c>
       <c r="L9" t="n">
-        <v>3007.25</v>
+        <v>2972.67</v>
       </c>
       <c r="M9" t="n">
-        <v>3025.7</v>
+        <v>3001.95</v>
       </c>
       <c r="N9" t="n">
-        <v>3044.15</v>
+        <v>3031.23</v>
       </c>
       <c r="O9" t="n">
-        <v>3096.4</v>
+        <v>3065.2</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1273,19 +1273,19 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1297,59 +1297,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2965.8</v>
+        <v>3008.1</v>
       </c>
       <c r="C10" t="n">
-        <v>3014.9</v>
+        <v>3019.5</v>
       </c>
       <c r="D10" t="n">
-        <v>2964.3</v>
+        <v>2970.8</v>
       </c>
       <c r="E10" t="n">
-        <v>3008.4</v>
+        <v>2994</v>
       </c>
       <c r="F10" t="n">
-        <v>36.9</v>
+        <v>-14.4</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0048</v>
       </c>
       <c r="H10" t="n">
-        <v>50.6</v>
+        <v>48.7</v>
       </c>
       <c r="I10" t="n">
-        <v>2882.5</v>
+        <v>2913.7</v>
       </c>
       <c r="J10" t="n">
-        <v>2909.42</v>
+        <v>2967.2</v>
       </c>
       <c r="K10" t="n">
-        <v>2941.05</v>
+        <v>2983.1</v>
       </c>
       <c r="L10" t="n">
-        <v>2972.67</v>
+        <v>2999</v>
       </c>
       <c r="M10" t="n">
-        <v>3001.95</v>
+        <v>3033.7</v>
       </c>
       <c r="N10" t="n">
-        <v>3031.23</v>
+        <v>3068.4</v>
       </c>
       <c r="O10" t="n">
-        <v>3065.2</v>
+        <v>3065.5</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1357,18 +1353,18 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1381,55 +1377,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3008.1</v>
+        <v>2984.7</v>
       </c>
       <c r="C11" t="n">
-        <v>3019.5</v>
+        <v>2995.8</v>
       </c>
       <c r="D11" t="n">
-        <v>2970.8</v>
+        <v>2961.8</v>
       </c>
       <c r="E11" t="n">
-        <v>2994</v>
+        <v>2970.4</v>
       </c>
       <c r="F11" t="n">
-        <v>-14.4</v>
+        <v>-23.6</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>48.7</v>
+        <v>34</v>
       </c>
       <c r="I11" t="n">
-        <v>2913.7</v>
+        <v>2922.1</v>
       </c>
       <c r="J11" t="n">
-        <v>2967.2</v>
+        <v>2944.73</v>
       </c>
       <c r="K11" t="n">
-        <v>2983.1</v>
+        <v>2969.65</v>
       </c>
       <c r="L11" t="n">
-        <v>2999</v>
+        <v>2994.58</v>
       </c>
       <c r="M11" t="n">
-        <v>3033.7</v>
+        <v>3018.35</v>
       </c>
       <c r="N11" t="n">
-        <v>3068.4</v>
+        <v>3042.12</v>
       </c>
       <c r="O11" t="n">
-        <v>3065.5</v>
+        <v>3068.2</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1463,57 +1463,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2984.7</v>
+        <v>2967.2</v>
       </c>
       <c r="C12" t="n">
-        <v>2995.8</v>
+        <v>3029.8</v>
       </c>
       <c r="D12" t="n">
-        <v>2961.8</v>
+        <v>2956.2</v>
       </c>
       <c r="E12" t="n">
-        <v>2970.4</v>
+        <v>2979.9</v>
       </c>
       <c r="F12" t="n">
-        <v>-23.6</v>
+        <v>9.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H12" t="n">
-        <v>34</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>2922.1</v>
+        <v>2927.8</v>
       </c>
       <c r="J12" t="n">
-        <v>2944.73</v>
+        <v>2932.2</v>
       </c>
       <c r="K12" t="n">
-        <v>2969.65</v>
+        <v>2953.4</v>
       </c>
       <c r="L12" t="n">
-        <v>2994.58</v>
+        <v>2974.6</v>
       </c>
       <c r="M12" t="n">
-        <v>3018.35</v>
+        <v>2987.4</v>
       </c>
       <c r="N12" t="n">
-        <v>3042.12</v>
+        <v>3000.2</v>
       </c>
       <c r="O12" t="n">
-        <v>3068.2</v>
+        <v>3029.8</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1521,24 +1521,28 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R12" s="6" t="n">
+        <v/>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
@@ -1547,57 +1551,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2967.2</v>
+        <v>2981.2</v>
       </c>
       <c r="C13" t="n">
-        <v>3029.8</v>
+        <v>3006.1</v>
       </c>
       <c r="D13" t="n">
-        <v>2956.2</v>
+        <v>2974.4</v>
       </c>
       <c r="E13" t="n">
-        <v>2979.9</v>
+        <v>2991.8</v>
       </c>
       <c r="F13" t="n">
-        <v>9.5</v>
+        <v>11.9</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.004</v>
       </c>
       <c r="H13" t="n">
-        <v>73.59999999999999</v>
+        <v>31.7</v>
       </c>
       <c r="I13" t="n">
-        <v>2927.8</v>
+        <v>2882.6</v>
       </c>
       <c r="J13" t="n">
-        <v>2932.2</v>
+        <v>2899.75</v>
       </c>
       <c r="K13" t="n">
-        <v>2953.4</v>
+        <v>2943.1</v>
       </c>
       <c r="L13" t="n">
-        <v>2974.6</v>
+        <v>2986.45</v>
       </c>
       <c r="M13" t="n">
-        <v>2987.4</v>
+        <v>3016.7</v>
       </c>
       <c r="N13" t="n">
-        <v>3000.2</v>
+        <v>3046.95</v>
       </c>
       <c r="O13" t="n">
-        <v>3029.8</v>
+        <v>3103.4</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1608,25 +1612,19 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v/>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
@@ -1642,50 +1640,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2981.2</v>
+        <v>2995.3</v>
       </c>
       <c r="C14" t="n">
-        <v>3006.1</v>
+        <v>3012.8</v>
       </c>
       <c r="D14" t="n">
-        <v>2974.4</v>
+        <v>2972.7</v>
       </c>
       <c r="E14" t="n">
-        <v>2991.8</v>
+        <v>2990.7</v>
       </c>
       <c r="F14" t="n">
-        <v>11.9</v>
+        <v>-1.1</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0004</v>
       </c>
       <c r="H14" t="n">
-        <v>31.7</v>
+        <v>40.1</v>
       </c>
       <c r="I14" t="n">
-        <v>2882.6</v>
+        <v>2942.7</v>
       </c>
       <c r="J14" t="n">
-        <v>2899.75</v>
+        <v>2960.87</v>
       </c>
       <c r="K14" t="n">
-        <v>2943.1</v>
+        <v>2975.95</v>
       </c>
       <c r="L14" t="n">
-        <v>2986.45</v>
+        <v>2991.03</v>
       </c>
       <c r="M14" t="n">
-        <v>3016.7</v>
+        <v>3007.65</v>
       </c>
       <c r="N14" t="n">
-        <v>3046.95</v>
+        <v>3024.28</v>
       </c>
       <c r="O14" t="n">
-        <v>3103.4</v>
+        <v>3037.8</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1693,16 +1691,20 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1717,78 +1719,78 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2995.3</v>
+        <v>2991.7</v>
       </c>
       <c r="C15" t="n">
-        <v>3012.8</v>
+        <v>2994.8</v>
       </c>
       <c r="D15" t="n">
-        <v>2972.7</v>
+        <v>2949.3</v>
       </c>
       <c r="E15" t="n">
-        <v>2990.7</v>
+        <v>2973.5</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1</v>
+        <v>-17.2</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0058</v>
       </c>
       <c r="H15" t="n">
-        <v>40.1</v>
+        <v>45.5</v>
       </c>
       <c r="I15" t="n">
-        <v>2942.7</v>
+        <v>2932.6</v>
       </c>
       <c r="J15" t="n">
-        <v>2960.87</v>
+        <v>2949.57</v>
       </c>
       <c r="K15" t="n">
-        <v>2975.95</v>
+        <v>2970.65</v>
       </c>
       <c r="L15" t="n">
-        <v>2991.03</v>
+        <v>2991.72</v>
       </c>
       <c r="M15" t="n">
-        <v>3007.65</v>
+        <v>3010.75</v>
       </c>
       <c r="N15" t="n">
-        <v>3024.28</v>
+        <v>3029.78</v>
       </c>
       <c r="O15" t="n">
-        <v>3037.8</v>
+        <v>3052.9</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1803,79 +1805,79 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2991.7</v>
+        <v>2964.5</v>
       </c>
       <c r="C16" t="n">
-        <v>2994.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D16" t="n">
-        <v>2949.3</v>
+        <v>2952.7</v>
       </c>
       <c r="E16" t="n">
-        <v>2973.5</v>
+        <v>2955.2</v>
       </c>
       <c r="F16" t="n">
-        <v>-17.2</v>
+        <v>-18.3</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0062</v>
       </c>
       <c r="H16" t="n">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="I16" t="n">
-        <v>2932.6</v>
+        <v>2903.8</v>
       </c>
       <c r="J16" t="n">
-        <v>2949.57</v>
+        <v>2928.72</v>
       </c>
       <c r="K16" t="n">
-        <v>2970.65</v>
+        <v>2950.75</v>
       </c>
       <c r="L16" t="n">
-        <v>2991.72</v>
+        <v>2972.78</v>
       </c>
       <c r="M16" t="n">
-        <v>3010.75</v>
+        <v>2996.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3029.78</v>
+        <v>3019.72</v>
       </c>
       <c r="O16" t="n">
-        <v>3052.9</v>
+        <v>3040.3</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
@@ -1889,57 +1891,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2964.5</v>
+        <v>2955.8</v>
       </c>
       <c r="C17" t="n">
-        <v>2998.7</v>
+        <v>2999.8</v>
       </c>
       <c r="D17" t="n">
-        <v>2952.7</v>
+        <v>2951.1</v>
       </c>
       <c r="E17" t="n">
-        <v>2955.2</v>
+        <v>2997</v>
       </c>
       <c r="F17" t="n">
-        <v>-18.3</v>
+        <v>41.8</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0141</v>
       </c>
       <c r="H17" t="n">
-        <v>46</v>
+        <v>48.7</v>
       </c>
       <c r="I17" t="n">
-        <v>2903.8</v>
+        <v>2906.7</v>
       </c>
       <c r="J17" t="n">
-        <v>2928.72</v>
+        <v>2898.95</v>
       </c>
       <c r="K17" t="n">
-        <v>2950.75</v>
+        <v>2932.2</v>
       </c>
       <c r="L17" t="n">
-        <v>2972.78</v>
+        <v>2965.45</v>
       </c>
       <c r="M17" t="n">
-        <v>2996.25</v>
+        <v>2978.2</v>
       </c>
       <c r="N17" t="n">
-        <v>3019.72</v>
+        <v>2990.95</v>
       </c>
       <c r="O17" t="n">
-        <v>3040.3</v>
+        <v>3044.7</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1947,23 +1949,23 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1982,50 +1984,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2955.8</v>
+        <v>2997</v>
       </c>
       <c r="C18" t="n">
-        <v>2999.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D18" t="n">
-        <v>2951.1</v>
+        <v>2965.5</v>
       </c>
       <c r="E18" t="n">
-        <v>2997</v>
+        <v>2969.8</v>
       </c>
       <c r="F18" t="n">
-        <v>41.8</v>
+        <v>-27.2</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0141</v>
+        <v>-0.0091</v>
       </c>
       <c r="H18" t="n">
-        <v>48.7</v>
+        <v>33.2</v>
       </c>
       <c r="I18" t="n">
-        <v>2906.7</v>
+        <v>2902.4</v>
       </c>
       <c r="J18" t="n">
-        <v>2898.95</v>
+        <v>2959.08</v>
       </c>
       <c r="K18" t="n">
-        <v>2932.2</v>
+        <v>2972.65</v>
       </c>
       <c r="L18" t="n">
-        <v>2965.45</v>
+        <v>2986.23</v>
       </c>
       <c r="M18" t="n">
-        <v>2978.2</v>
+        <v>3021.35</v>
       </c>
       <c r="N18" t="n">
-        <v>2990.95</v>
+        <v>3056.47</v>
       </c>
       <c r="O18" t="n">
-        <v>3044.7</v>
+        <v>3048.5</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2033,23 +2035,21 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2061,60 +2061,62 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2997</v>
+        <v>2974.6</v>
       </c>
       <c r="C19" t="n">
-        <v>2998.7</v>
+        <v>2979</v>
       </c>
       <c r="D19" t="n">
-        <v>2965.5</v>
+        <v>2932.1</v>
       </c>
       <c r="E19" t="n">
-        <v>2969.8</v>
+        <v>2951.7</v>
       </c>
       <c r="F19" t="n">
-        <v>-27.2</v>
+        <v>-18.1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0091</v>
+        <v>-0.0061</v>
       </c>
       <c r="H19" t="n">
-        <v>33.2</v>
+        <v>46.9</v>
       </c>
       <c r="I19" t="n">
-        <v>2902.4</v>
+        <v>2932.3</v>
       </c>
       <c r="J19" t="n">
-        <v>2959.08</v>
+        <v>2930.45</v>
       </c>
       <c r="K19" t="n">
-        <v>2972.65</v>
+        <v>2953.2</v>
       </c>
       <c r="L19" t="n">
-        <v>2986.23</v>
+        <v>2975.95</v>
       </c>
       <c r="M19" t="n">
-        <v>3021.35</v>
+        <v>2986.4</v>
       </c>
       <c r="N19" t="n">
-        <v>3056.47</v>
+        <v>2996.85</v>
       </c>
       <c r="O19" t="n">
-        <v>3048.5</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
+        <v>3031.9</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q19" s="6" t="n">
         <v/>
@@ -2124,7 +2126,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S19" s="7" t="inlineStr">
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2145,74 +2147,70 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2974.6</v>
+        <v>2948.5</v>
       </c>
       <c r="C20" t="n">
-        <v>2979</v>
+        <v>2969.7</v>
       </c>
       <c r="D20" t="n">
-        <v>2932.1</v>
+        <v>2934.5</v>
       </c>
       <c r="E20" t="n">
-        <v>2951.7</v>
+        <v>2941.3</v>
       </c>
       <c r="F20" t="n">
-        <v>-18.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0035</v>
       </c>
       <c r="H20" t="n">
-        <v>46.9</v>
+        <v>35.2</v>
       </c>
       <c r="I20" t="n">
-        <v>2932.3</v>
+        <v>2885.2</v>
       </c>
       <c r="J20" t="n">
-        <v>2930.45</v>
+        <v>2902.88</v>
       </c>
       <c r="K20" t="n">
-        <v>2953.2</v>
+        <v>2928.25</v>
       </c>
       <c r="L20" t="n">
-        <v>2975.95</v>
+        <v>2953.62</v>
       </c>
       <c r="M20" t="n">
-        <v>2986.4</v>
+        <v>2975.15</v>
       </c>
       <c r="N20" t="n">
-        <v>2996.85</v>
+        <v>2996.67</v>
       </c>
       <c r="O20" t="n">
-        <v>3031.9</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3025.9</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
       </c>
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2231,57 +2229,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2948.5</v>
+        <v>2955.5</v>
       </c>
       <c r="C21" t="n">
-        <v>2969.7</v>
+        <v>2985.9</v>
       </c>
       <c r="D21" t="n">
-        <v>2934.5</v>
+        <v>2941.2</v>
       </c>
       <c r="E21" t="n">
-        <v>2941.3</v>
+        <v>2960</v>
       </c>
       <c r="F21" t="n">
-        <v>-10.4</v>
+        <v>18.7</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0064</v>
       </c>
       <c r="H21" t="n">
-        <v>35.2</v>
+        <v>44.7</v>
       </c>
       <c r="I21" t="n">
-        <v>2885.2</v>
+        <v>2899.3</v>
       </c>
       <c r="J21" t="n">
-        <v>2902.88</v>
+        <v>2900.7</v>
       </c>
       <c r="K21" t="n">
-        <v>2928.25</v>
+        <v>2923.7</v>
       </c>
       <c r="L21" t="n">
-        <v>2953.62</v>
+        <v>2946.7</v>
       </c>
       <c r="M21" t="n">
-        <v>2975.15</v>
+        <v>2958.9</v>
       </c>
       <c r="N21" t="n">
-        <v>2996.67</v>
+        <v>2971.1</v>
       </c>
       <c r="O21" t="n">
-        <v>3025.9</v>
+        <v>3004.9</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2294,14 +2292,18 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2311,59 +2313,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2955.5</v>
+        <v>2961.5</v>
       </c>
       <c r="C22" t="n">
-        <v>2985.9</v>
+        <v>2968.3</v>
       </c>
       <c r="D22" t="n">
-        <v>2941.2</v>
+        <v>2933.4</v>
       </c>
       <c r="E22" t="n">
-        <v>2960</v>
+        <v>2964.5</v>
       </c>
       <c r="F22" t="n">
-        <v>18.7</v>
+        <v>4.5</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0015</v>
       </c>
       <c r="H22" t="n">
-        <v>44.7</v>
+        <v>34.9</v>
       </c>
       <c r="I22" t="n">
-        <v>2899.3</v>
+        <v>2896.5</v>
       </c>
       <c r="J22" t="n">
-        <v>2900.7</v>
+        <v>2913.53</v>
       </c>
       <c r="K22" t="n">
-        <v>2923.7</v>
+        <v>2937.65</v>
       </c>
       <c r="L22" t="n">
-        <v>2946.7</v>
+        <v>2961.77</v>
       </c>
       <c r="M22" t="n">
-        <v>2958.9</v>
+        <v>2982.35</v>
       </c>
       <c r="N22" t="n">
-        <v>2971.1</v>
+        <v>3002.92</v>
       </c>
       <c r="O22" t="n">
-        <v>3004.9</v>
+        <v>3030.6</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2371,24 +2369,22 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
@@ -2397,61 +2393,69 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2961.5</v>
+        <v>2966.9</v>
       </c>
       <c r="C23" t="n">
-        <v>2968.3</v>
+        <v>2978.3</v>
       </c>
       <c r="D23" t="n">
-        <v>2933.4</v>
+        <v>2902.3</v>
       </c>
       <c r="E23" t="n">
-        <v>2964.5</v>
+        <v>2915.4</v>
       </c>
       <c r="F23" t="n">
-        <v>4.5</v>
+        <v>-49.1</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0166</v>
       </c>
       <c r="H23" t="n">
-        <v>34.9</v>
+        <v>76</v>
       </c>
       <c r="I23" t="n">
-        <v>2896.5</v>
+        <v>2898.5</v>
       </c>
       <c r="J23" t="n">
-        <v>2913.53</v>
+        <v>2936.42</v>
       </c>
       <c r="K23" t="n">
-        <v>2937.65</v>
+        <v>2947.05</v>
       </c>
       <c r="L23" t="n">
-        <v>2961.77</v>
+        <v>2957.67</v>
       </c>
       <c r="M23" t="n">
-        <v>2982.35</v>
+        <v>2981.95</v>
       </c>
       <c r="N23" t="n">
-        <v>3002.92</v>
+        <v>3006.23</v>
       </c>
       <c r="O23" t="n">
-        <v>3030.6</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
+        <v>3003.2</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
@@ -2460,7 +2464,7 @@
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2472,88 +2476,84 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W23" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2966.9</v>
+        <v>2906.6</v>
       </c>
       <c r="C24" t="n">
-        <v>2978.3</v>
+        <v>2957.9</v>
       </c>
       <c r="D24" t="n">
-        <v>2902.3</v>
+        <v>2905.6</v>
       </c>
       <c r="E24" t="n">
-        <v>2915.4</v>
+        <v>2954.3</v>
       </c>
       <c r="F24" t="n">
-        <v>-49.1</v>
+        <v>38.9</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0166</v>
+        <v>0.0133</v>
       </c>
       <c r="H24" t="n">
-        <v>76</v>
+        <v>52.3</v>
       </c>
       <c r="I24" t="n">
-        <v>2898.5</v>
+        <v>2826.3</v>
       </c>
       <c r="J24" t="n">
-        <v>2936.42</v>
+        <v>2826.95</v>
       </c>
       <c r="K24" t="n">
-        <v>2947.05</v>
+        <v>2877.4</v>
       </c>
       <c r="L24" t="n">
-        <v>2957.67</v>
+        <v>2927.85</v>
       </c>
       <c r="M24" t="n">
-        <v>2981.95</v>
+        <v>2953.4</v>
       </c>
       <c r="N24" t="n">
-        <v>3006.23</v>
+        <v>2978.95</v>
       </c>
       <c r="O24" t="n">
-        <v>3003.2</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
+        <v>3054.3</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
@@ -2567,76 +2567,78 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2906.6</v>
+        <v>2954</v>
       </c>
       <c r="C25" t="n">
-        <v>2957.9</v>
+        <v>2976.3</v>
       </c>
       <c r="D25" t="n">
-        <v>2905.6</v>
+        <v>2905.3</v>
       </c>
       <c r="E25" t="n">
-        <v>2954.3</v>
+        <v>2938</v>
       </c>
       <c r="F25" t="n">
-        <v>38.9</v>
+        <v>-16.3</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0055</v>
       </c>
       <c r="H25" t="n">
-        <v>52.3</v>
+        <v>71</v>
       </c>
       <c r="I25" t="n">
-        <v>2826.3</v>
+        <v>2853.3</v>
       </c>
       <c r="J25" t="n">
-        <v>2826.95</v>
+        <v>2913.28</v>
       </c>
       <c r="K25" t="n">
-        <v>2877.4</v>
+        <v>2928.15</v>
       </c>
       <c r="L25" t="n">
-        <v>2927.85</v>
+        <v>2943.03</v>
       </c>
       <c r="M25" t="n">
-        <v>2953.4</v>
+        <v>2980.45</v>
       </c>
       <c r="N25" t="n">
-        <v>2978.95</v>
+        <v>3017.87</v>
       </c>
       <c r="O25" t="n">
-        <v>3054.3</v>
+        <v>3010.2</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2651,78 +2653,76 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2954</v>
+        <v>2950</v>
       </c>
       <c r="C26" t="n">
-        <v>2976.3</v>
+        <v>2994.6</v>
       </c>
       <c r="D26" t="n">
-        <v>2905.3</v>
+        <v>2948.4</v>
       </c>
       <c r="E26" t="n">
-        <v>2938</v>
+        <v>2989.3</v>
       </c>
       <c r="F26" t="n">
-        <v>-16.3</v>
+        <v>51.3</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0175</v>
       </c>
       <c r="H26" t="n">
-        <v>71</v>
+        <v>46.2</v>
       </c>
       <c r="I26" t="n">
-        <v>2853.3</v>
+        <v>2834.3</v>
       </c>
       <c r="J26" t="n">
-        <v>2913.28</v>
+        <v>2865.6</v>
       </c>
       <c r="K26" t="n">
-        <v>2928.15</v>
+        <v>2902.5</v>
       </c>
       <c r="L26" t="n">
-        <v>2943.03</v>
+        <v>2939.4</v>
       </c>
       <c r="M26" t="n">
-        <v>2980.45</v>
+        <v>2973.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3017.87</v>
+        <v>3007.6</v>
       </c>
       <c r="O26" t="n">
-        <v>3010.2</v>
+        <v>3047.3</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2737,57 +2737,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2950</v>
+        <v>2992.4</v>
       </c>
       <c r="C27" t="n">
-        <v>2994.6</v>
+        <v>3051.8</v>
       </c>
       <c r="D27" t="n">
-        <v>2948.4</v>
+        <v>2986.1</v>
       </c>
       <c r="E27" t="n">
-        <v>2989.3</v>
+        <v>3044.7</v>
       </c>
       <c r="F27" t="n">
-        <v>51.3</v>
+        <v>55.4</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0185</v>
       </c>
       <c r="H27" t="n">
-        <v>46.2</v>
+        <v>65.7</v>
       </c>
       <c r="I27" t="n">
-        <v>2834.3</v>
+        <v>2902.2</v>
       </c>
       <c r="J27" t="n">
-        <v>2865.6</v>
+        <v>2952</v>
       </c>
       <c r="K27" t="n">
-        <v>2902.5</v>
+        <v>2966.2</v>
       </c>
       <c r="L27" t="n">
-        <v>2939.4</v>
+        <v>2980.4</v>
       </c>
       <c r="M27" t="n">
-        <v>2973.5</v>
+        <v>3012.4</v>
       </c>
       <c r="N27" t="n">
-        <v>3007.6</v>
+        <v>3044.4</v>
       </c>
       <c r="O27" t="n">
-        <v>3047.3</v>
+        <v>3040.8</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2798,80 +2798,80 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W27" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W27" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2992.4</v>
+        <v>3049.1</v>
       </c>
       <c r="C28" t="n">
-        <v>3051.8</v>
+        <v>3058.3</v>
       </c>
       <c r="D28" t="n">
-        <v>2986.1</v>
+        <v>3023.3</v>
       </c>
       <c r="E28" t="n">
-        <v>3044.7</v>
+        <v>3025.4</v>
       </c>
       <c r="F28" t="n">
-        <v>55.4</v>
+        <v>-19.3</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0063</v>
       </c>
       <c r="H28" t="n">
-        <v>65.7</v>
+        <v>35</v>
       </c>
       <c r="I28" t="n">
-        <v>2902.2</v>
+        <v>2920.4</v>
       </c>
       <c r="J28" t="n">
-        <v>2952</v>
+        <v>2991.87</v>
       </c>
       <c r="K28" t="n">
-        <v>2966.2</v>
+        <v>3011.85</v>
       </c>
       <c r="L28" t="n">
-        <v>2980.4</v>
+        <v>3031.83</v>
       </c>
       <c r="M28" t="n">
-        <v>3012.4</v>
+        <v>3077.55</v>
       </c>
       <c r="N28" t="n">
-        <v>3044.4</v>
+        <v>3123.27</v>
       </c>
       <c r="O28" t="n">
-        <v>3040.8</v>
+        <v>3117.5</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2884,78 +2884,76 @@
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3049.1</v>
+        <v>3028.5</v>
       </c>
       <c r="C29" t="n">
-        <v>3058.3</v>
+        <v>3041</v>
       </c>
       <c r="D29" t="n">
-        <v>3023.3</v>
+        <v>3004.9</v>
       </c>
       <c r="E29" t="n">
-        <v>3025.4</v>
+        <v>3009.1</v>
       </c>
       <c r="F29" t="n">
-        <v>-19.3</v>
+        <v>-16.3</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0054</v>
       </c>
       <c r="H29" t="n">
-        <v>35</v>
+        <v>36.1</v>
       </c>
       <c r="I29" t="n">
-        <v>2920.4</v>
+        <v>2988.3</v>
       </c>
       <c r="J29" t="n">
-        <v>2991.87</v>
+        <v>2982.7</v>
       </c>
       <c r="K29" t="n">
-        <v>3011.85</v>
+        <v>3007.9</v>
       </c>
       <c r="L29" t="n">
-        <v>3031.83</v>
+        <v>3033.1</v>
       </c>
       <c r="M29" t="n">
-        <v>3077.55</v>
+        <v>3042.9</v>
       </c>
       <c r="N29" t="n">
-        <v>3123.27</v>
+        <v>3052.7</v>
       </c>
       <c r="O29" t="n">
-        <v>3117.5</v>
+        <v>3093.3</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2963,12 +2961,14 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2987,57 +2987,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3028.5</v>
+        <v>3008.5</v>
       </c>
       <c r="C30" t="n">
-        <v>3041</v>
+        <v>3046.8</v>
       </c>
       <c r="D30" t="n">
-        <v>3004.9</v>
+        <v>3002</v>
       </c>
       <c r="E30" t="n">
-        <v>3009.1</v>
+        <v>3041.6</v>
       </c>
       <c r="F30" t="n">
-        <v>-16.3</v>
+        <v>32.5</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0054</v>
+        <v>0.0108</v>
       </c>
       <c r="H30" t="n">
-        <v>36.1</v>
+        <v>44.8</v>
       </c>
       <c r="I30" t="n">
-        <v>2988.3</v>
+        <v>2968.8</v>
       </c>
       <c r="J30" t="n">
-        <v>2982.7</v>
+        <v>2966.08</v>
       </c>
       <c r="K30" t="n">
-        <v>3007.9</v>
+        <v>2991.05</v>
       </c>
       <c r="L30" t="n">
-        <v>3033.1</v>
+        <v>3016.03</v>
       </c>
       <c r="M30" t="n">
-        <v>3042.9</v>
+        <v>3027.15</v>
       </c>
       <c r="N30" t="n">
-        <v>3052.7</v>
+        <v>3038.28</v>
       </c>
       <c r="O30" t="n">
-        <v>3093.3</v>
+        <v>3077.1</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3045,22 +3045,24 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
@@ -3071,57 +3073,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3008.5</v>
+        <v>3038.9</v>
       </c>
       <c r="C31" t="n">
-        <v>3046.8</v>
+        <v>3044.6</v>
       </c>
       <c r="D31" t="n">
-        <v>3002</v>
+        <v>3016</v>
       </c>
       <c r="E31" t="n">
-        <v>3041.6</v>
+        <v>3025</v>
       </c>
       <c r="F31" t="n">
-        <v>32.5</v>
+        <v>-16.6</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0108</v>
+        <v>-0.0055</v>
       </c>
       <c r="H31" t="n">
-        <v>44.8</v>
+        <v>28.6</v>
       </c>
       <c r="I31" t="n">
-        <v>2968.8</v>
+        <v>2957.2</v>
       </c>
       <c r="J31" t="n">
-        <v>2966.08</v>
+        <v>3005.4</v>
       </c>
       <c r="K31" t="n">
-        <v>2991.05</v>
+        <v>3019.2</v>
       </c>
       <c r="L31" t="n">
-        <v>3016.03</v>
+        <v>3033</v>
       </c>
       <c r="M31" t="n">
-        <v>3027.15</v>
+        <v>3064</v>
       </c>
       <c r="N31" t="n">
-        <v>3038.28</v>
+        <v>3095</v>
       </c>
       <c r="O31" t="n">
-        <v>3077.1</v>
+        <v>3091.6</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3129,23 +3131,21 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3157,57 +3157,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3038.9</v>
+        <v>3024.7</v>
       </c>
       <c r="C32" t="n">
-        <v>3044.6</v>
+        <v>3045.8</v>
       </c>
       <c r="D32" t="n">
-        <v>3016</v>
+        <v>3019.9</v>
       </c>
       <c r="E32" t="n">
-        <v>3025</v>
+        <v>3035.5</v>
       </c>
       <c r="F32" t="n">
-        <v>-16.6</v>
+        <v>10.5</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0035</v>
       </c>
       <c r="H32" t="n">
-        <v>28.6</v>
+        <v>25.9</v>
       </c>
       <c r="I32" t="n">
-        <v>2957.2</v>
+        <v>2987.4</v>
       </c>
       <c r="J32" t="n">
-        <v>3005.4</v>
+        <v>2993.75</v>
       </c>
       <c r="K32" t="n">
-        <v>3019.2</v>
+        <v>3010.7</v>
       </c>
       <c r="L32" t="n">
-        <v>3033</v>
+        <v>3027.65</v>
       </c>
       <c r="M32" t="n">
-        <v>3064</v>
+        <v>3039.3</v>
       </c>
       <c r="N32" t="n">
-        <v>3095</v>
+        <v>3050.95</v>
       </c>
       <c r="O32" t="n">
-        <v>3091.6</v>
+        <v>3073.2</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3215,19 +3215,19 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
@@ -3239,59 +3239,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3024.7</v>
+        <v>3036.1</v>
       </c>
       <c r="C33" t="n">
-        <v>3045.8</v>
+        <v>3060</v>
       </c>
       <c r="D33" t="n">
-        <v>3019.9</v>
+        <v>3033.1</v>
       </c>
       <c r="E33" t="n">
-        <v>3035.5</v>
+        <v>3052.8</v>
       </c>
       <c r="F33" t="n">
-        <v>10.5</v>
+        <v>17.3</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0057</v>
       </c>
       <c r="H33" t="n">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
       <c r="I33" t="n">
-        <v>2987.4</v>
+        <v>2994</v>
       </c>
       <c r="J33" t="n">
-        <v>2993.75</v>
+        <v>3010.92</v>
       </c>
       <c r="K33" t="n">
-        <v>3010.7</v>
+        <v>3022.55</v>
       </c>
       <c r="L33" t="n">
-        <v>3027.65</v>
+        <v>3034.17</v>
       </c>
       <c r="M33" t="n">
-        <v>3039.3</v>
+        <v>3048.45</v>
       </c>
       <c r="N33" t="n">
-        <v>3050.95</v>
+        <v>3062.73</v>
       </c>
       <c r="O33" t="n">
-        <v>3073.2</v>
+        <v>3071.7</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3302,7 +3298,7 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3328,50 +3324,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3036.1</v>
+        <v>3056.2</v>
       </c>
       <c r="C34" t="n">
-        <v>3060</v>
+        <v>3076.3</v>
       </c>
       <c r="D34" t="n">
-        <v>3033.1</v>
+        <v>3052.5</v>
       </c>
       <c r="E34" t="n">
-        <v>3052.8</v>
+        <v>3060.2</v>
       </c>
       <c r="F34" t="n">
-        <v>17.3</v>
+        <v>7.4</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0024</v>
       </c>
       <c r="H34" t="n">
-        <v>26.9</v>
+        <v>23.8</v>
       </c>
       <c r="I34" t="n">
-        <v>2994</v>
+        <v>3006.2</v>
       </c>
       <c r="J34" t="n">
-        <v>3010.92</v>
+        <v>3029.03</v>
       </c>
       <c r="K34" t="n">
-        <v>3022.55</v>
+        <v>3039.35</v>
       </c>
       <c r="L34" t="n">
-        <v>3034.17</v>
+        <v>3049.68</v>
       </c>
       <c r="M34" t="n">
-        <v>3048.45</v>
+        <v>3066.25</v>
       </c>
       <c r="N34" t="n">
-        <v>3062.73</v>
+        <v>3082.82</v>
       </c>
       <c r="O34" t="n">
-        <v>3071.7</v>
+        <v>3086.9</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3382,7 +3378,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3408,50 +3404,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3056.2</v>
+        <v>3062.2</v>
       </c>
       <c r="C35" t="n">
         <v>3076.3</v>
       </c>
       <c r="D35" t="n">
-        <v>3052.5</v>
+        <v>3051.7</v>
       </c>
       <c r="E35" t="n">
-        <v>3060.2</v>
+        <v>3074.9</v>
       </c>
       <c r="F35" t="n">
-        <v>7.4</v>
+        <v>14.7</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0048</v>
       </c>
       <c r="H35" t="n">
-        <v>23.8</v>
+        <v>24.6</v>
       </c>
       <c r="I35" t="n">
-        <v>3006.2</v>
+        <v>3028.7</v>
       </c>
       <c r="J35" t="n">
-        <v>3029.03</v>
+        <v>3034.3</v>
       </c>
       <c r="K35" t="n">
-        <v>3039.35</v>
+        <v>3048.3</v>
       </c>
       <c r="L35" t="n">
-        <v>3049.68</v>
+        <v>3062.3</v>
       </c>
       <c r="M35" t="n">
-        <v>3066.25</v>
+        <v>3072.1</v>
       </c>
       <c r="N35" t="n">
-        <v>3082.82</v>
+        <v>3081.9</v>
       </c>
       <c r="O35" t="n">
-        <v>3086.9</v>
+        <v>3100.1</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3462,7 +3458,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3483,55 +3479,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3062.2</v>
+        <v>3073.5</v>
       </c>
       <c r="C36" t="n">
-        <v>3076.3</v>
+        <v>3079.9</v>
       </c>
       <c r="D36" t="n">
-        <v>3051.7</v>
+        <v>3055.9</v>
       </c>
       <c r="E36" t="n">
-        <v>3074.9</v>
+        <v>3064.9</v>
       </c>
       <c r="F36" t="n">
-        <v>14.7</v>
+        <v>-10</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.0033</v>
       </c>
       <c r="H36" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="I36" t="n">
-        <v>3028.7</v>
+        <v>3027.1</v>
       </c>
       <c r="J36" t="n">
-        <v>3034.3</v>
+        <v>3055.75</v>
       </c>
       <c r="K36" t="n">
-        <v>3048.3</v>
+        <v>3062.6</v>
       </c>
       <c r="L36" t="n">
-        <v>3062.3</v>
+        <v>3069.45</v>
       </c>
       <c r="M36" t="n">
-        <v>3072.1</v>
+        <v>3087.2</v>
       </c>
       <c r="N36" t="n">
-        <v>3081.9</v>
+        <v>3104.95</v>
       </c>
       <c r="O36" t="n">
-        <v>3100.1</v>
+        <v>3100.9</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3539,18 +3539,18 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3572,63 +3572,67 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3073.5</v>
+        <v>3063.7</v>
       </c>
       <c r="C37" t="n">
-        <v>3079.9</v>
+        <v>3066.6</v>
       </c>
       <c r="D37" t="n">
-        <v>3055.9</v>
+        <v>3024.1</v>
       </c>
       <c r="E37" t="n">
-        <v>3064.9</v>
+        <v>3026.4</v>
       </c>
       <c r="F37" t="n">
-        <v>-10</v>
+        <v>-38.5</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0126</v>
       </c>
       <c r="H37" t="n">
-        <v>24</v>
+        <v>42.5</v>
       </c>
       <c r="I37" t="n">
-        <v>3027.1</v>
+        <v>3031.9</v>
       </c>
       <c r="J37" t="n">
-        <v>3055.75</v>
+        <v>3039.4</v>
       </c>
       <c r="K37" t="n">
-        <v>3062.6</v>
+        <v>3052.9</v>
       </c>
       <c r="L37" t="n">
-        <v>3069.45</v>
+        <v>3066.4</v>
       </c>
       <c r="M37" t="n">
-        <v>3087.2</v>
+        <v>3076.9</v>
       </c>
       <c r="N37" t="n">
-        <v>3104.95</v>
+        <v>3087.4</v>
       </c>
       <c r="O37" t="n">
-        <v>3100.9</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
+        <v>3103.9</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3642,88 +3646,80 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W37" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3063.7</v>
+        <v>3025.9</v>
       </c>
       <c r="C38" t="n">
-        <v>3066.6</v>
+        <v>3059.1</v>
       </c>
       <c r="D38" t="n">
-        <v>3024.1</v>
+        <v>3019.8</v>
       </c>
       <c r="E38" t="n">
-        <v>3026.4</v>
+        <v>3039.9</v>
       </c>
       <c r="F38" t="n">
-        <v>-38.5</v>
+        <v>13.5</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0045</v>
       </c>
       <c r="H38" t="n">
-        <v>42.5</v>
+        <v>39.3</v>
       </c>
       <c r="I38" t="n">
-        <v>3031.9</v>
+        <v>2981.6</v>
       </c>
       <c r="J38" t="n">
-        <v>3039.4</v>
+        <v>2974.42</v>
       </c>
       <c r="K38" t="n">
-        <v>3052.9</v>
+        <v>3005.15</v>
       </c>
       <c r="L38" t="n">
-        <v>3066.4</v>
+        <v>3035.88</v>
       </c>
       <c r="M38" t="n">
-        <v>3076.9</v>
+        <v>3047.65</v>
       </c>
       <c r="N38" t="n">
-        <v>3087.4</v>
+        <v>3059.42</v>
       </c>
       <c r="O38" t="n">
-        <v>3103.9</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q38" s="6" t="inlineStr">
+        <v>3109.1</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3735,74 +3731,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3025.9</v>
+        <v>3041.4</v>
       </c>
       <c r="C39" t="n">
-        <v>3059.1</v>
+        <v>3048.5</v>
       </c>
       <c r="D39" t="n">
-        <v>3019.8</v>
+        <v>2993.2</v>
       </c>
       <c r="E39" t="n">
-        <v>3039.9</v>
+        <v>2999.2</v>
       </c>
       <c r="F39" t="n">
-        <v>13.5</v>
+        <v>-40.7</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0134</v>
       </c>
       <c r="H39" t="n">
-        <v>39.3</v>
+        <v>55.3</v>
       </c>
       <c r="I39" t="n">
-        <v>2981.6</v>
+        <v>2980.5</v>
       </c>
       <c r="J39" t="n">
-        <v>2974.42</v>
+        <v>3000.82</v>
       </c>
       <c r="K39" t="n">
-        <v>3005.15</v>
+        <v>3020.25</v>
       </c>
       <c r="L39" t="n">
-        <v>3035.88</v>
+        <v>3039.67</v>
       </c>
       <c r="M39" t="n">
-        <v>3047.65</v>
+        <v>3059.55</v>
       </c>
       <c r="N39" t="n">
-        <v>3059.42</v>
+        <v>3079.42</v>
       </c>
       <c r="O39" t="n">
-        <v>3109.1</v>
+        <v>3098.4</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3815,81 +3817,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3041.4</v>
+        <v>2999.6</v>
       </c>
       <c r="C40" t="n">
-        <v>3048.5</v>
+        <v>3026.7</v>
       </c>
       <c r="D40" t="n">
-        <v>2993.2</v>
+        <v>2997.9</v>
       </c>
       <c r="E40" t="n">
-        <v>2999.2</v>
+        <v>3022.1</v>
       </c>
       <c r="F40" t="n">
-        <v>-40.7</v>
+        <v>22.9</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0134</v>
+        <v>0.0076</v>
       </c>
       <c r="H40" t="n">
-        <v>55.3</v>
+        <v>28.8</v>
       </c>
       <c r="I40" t="n">
-        <v>2980.5</v>
+        <v>2937.9</v>
       </c>
       <c r="J40" t="n">
-        <v>3000.82</v>
+        <v>2933.07</v>
       </c>
       <c r="K40" t="n">
-        <v>3020.25</v>
+        <v>2971.55</v>
       </c>
       <c r="L40" t="n">
-        <v>3039.67</v>
+        <v>3010.02</v>
       </c>
       <c r="M40" t="n">
-        <v>3059.55</v>
+        <v>3026.85</v>
       </c>
       <c r="N40" t="n">
-        <v>3079.42</v>
+        <v>3043.67</v>
       </c>
       <c r="O40" t="n">
-        <v>3098.4</v>
+        <v>3103.8</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3901,74 +3897,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2999.6</v>
+        <v>3023</v>
       </c>
       <c r="C41" t="n">
-        <v>3026.7</v>
+        <v>3028.9</v>
       </c>
       <c r="D41" t="n">
-        <v>2997.9</v>
+        <v>2996</v>
       </c>
       <c r="E41" t="n">
-        <v>3022.1</v>
+        <v>3001.6</v>
       </c>
       <c r="F41" t="n">
-        <v>22.9</v>
+        <v>-20.5</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0076</v>
+        <v>-0.0068</v>
       </c>
       <c r="H41" t="n">
-        <v>28.8</v>
+        <v>32.9</v>
       </c>
       <c r="I41" t="n">
-        <v>2937.9</v>
+        <v>2969.1</v>
       </c>
       <c r="J41" t="n">
-        <v>2933.07</v>
+        <v>2998.2</v>
       </c>
       <c r="K41" t="n">
-        <v>2971.55</v>
+        <v>3007.7</v>
       </c>
       <c r="L41" t="n">
-        <v>3010.02</v>
+        <v>3017.2</v>
       </c>
       <c r="M41" t="n">
-        <v>3026.85</v>
+        <v>3036.5</v>
       </c>
       <c r="N41" t="n">
-        <v>3043.67</v>
+        <v>3055.8</v>
       </c>
       <c r="O41" t="n">
-        <v>3103.8</v>
+        <v>3055.5</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3983,79 +3985,77 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3023</v>
+        <v>3004.6</v>
       </c>
       <c r="C42" t="n">
-        <v>3028.9</v>
+        <v>3025.4</v>
       </c>
       <c r="D42" t="n">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="E42" t="n">
-        <v>3001.6</v>
+        <v>3014.4</v>
       </c>
       <c r="F42" t="n">
-        <v>-20.5</v>
+        <v>12.8</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0043</v>
       </c>
       <c r="H42" t="n">
-        <v>32.9</v>
+        <v>28.4</v>
       </c>
       <c r="I42" t="n">
-        <v>2969.1</v>
+        <v>2963.1</v>
       </c>
       <c r="J42" t="n">
-        <v>2998.2</v>
+        <v>2963.28</v>
       </c>
       <c r="K42" t="n">
-        <v>3007.7</v>
+        <v>2985.15</v>
       </c>
       <c r="L42" t="n">
-        <v>3017.2</v>
+        <v>3007.03</v>
       </c>
       <c r="M42" t="n">
-        <v>3036.5</v>
+        <v>3018.05</v>
       </c>
       <c r="N42" t="n">
-        <v>3055.8</v>
+        <v>3029.08</v>
       </c>
       <c r="O42" t="n">
-        <v>3055.5</v>
+        <v>3061.8</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4069,57 +4069,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3004.6</v>
+        <v>3014.6</v>
       </c>
       <c r="C43" t="n">
-        <v>3025.4</v>
+        <v>3020.5</v>
       </c>
       <c r="D43" t="n">
-        <v>2997</v>
+        <v>3002.6</v>
       </c>
       <c r="E43" t="n">
-        <v>3014.4</v>
+        <v>3010.1</v>
       </c>
       <c r="F43" t="n">
-        <v>12.8</v>
+        <v>-4.3</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0014</v>
       </c>
       <c r="H43" t="n">
-        <v>28.4</v>
+        <v>17.9</v>
       </c>
       <c r="I43" t="n">
-        <v>2963.1</v>
+        <v>2968.6</v>
       </c>
       <c r="J43" t="n">
-        <v>2963.28</v>
+        <v>2987.6</v>
       </c>
       <c r="K43" t="n">
-        <v>2985.15</v>
+        <v>3000.2</v>
       </c>
       <c r="L43" t="n">
-        <v>3007.03</v>
+        <v>3012.8</v>
       </c>
       <c r="M43" t="n">
-        <v>3018.05</v>
+        <v>3028.6</v>
       </c>
       <c r="N43" t="n">
-        <v>3029.08</v>
+        <v>3044.4</v>
       </c>
       <c r="O43" t="n">
-        <v>3061.8</v>
+        <v>3053.8</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4132,13 +4132,11 @@
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4153,57 +4151,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3014.6</v>
+        <v>3016.9</v>
       </c>
       <c r="C44" t="n">
-        <v>3020.5</v>
+        <v>3024.2</v>
       </c>
       <c r="D44" t="n">
-        <v>3002.6</v>
+        <v>3002.1</v>
       </c>
       <c r="E44" t="n">
-        <v>3010.1</v>
+        <v>3019</v>
       </c>
       <c r="F44" t="n">
-        <v>-4.3</v>
+        <v>8.9</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0014</v>
+        <v>0.003</v>
       </c>
       <c r="H44" t="n">
-        <v>17.9</v>
+        <v>22.1</v>
       </c>
       <c r="I44" t="n">
-        <v>2968.6</v>
+        <v>2984.7</v>
       </c>
       <c r="J44" t="n">
-        <v>2987.6</v>
+        <v>2991.48</v>
       </c>
       <c r="K44" t="n">
-        <v>3000.2</v>
+        <v>3001.15</v>
       </c>
       <c r="L44" t="n">
-        <v>3012.8</v>
+        <v>3010.83</v>
       </c>
       <c r="M44" t="n">
-        <v>3028.6</v>
+        <v>3019.05</v>
       </c>
       <c r="N44" t="n">
-        <v>3044.4</v>
+        <v>3027.28</v>
       </c>
       <c r="O44" t="n">
-        <v>3053.8</v>
+        <v>3038.4</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4216,11 +4214,13 @@
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4235,76 +4235,80 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3016.9</v>
+        <v>3019.6</v>
       </c>
       <c r="C45" t="n">
-        <v>3024.2</v>
+        <v>3025.5</v>
       </c>
       <c r="D45" t="n">
-        <v>3002.1</v>
+        <v>2976.6</v>
       </c>
       <c r="E45" t="n">
-        <v>3019</v>
+        <v>2977.5</v>
       </c>
       <c r="F45" t="n">
-        <v>8.9</v>
+        <v>-41.5</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0137</v>
       </c>
       <c r="H45" t="n">
-        <v>22.1</v>
+        <v>48.9</v>
       </c>
       <c r="I45" t="n">
-        <v>2984.7</v>
+        <v>2980</v>
       </c>
       <c r="J45" t="n">
-        <v>2991.48</v>
+        <v>2999.83</v>
       </c>
       <c r="K45" t="n">
-        <v>3001.15</v>
+        <v>3007.95</v>
       </c>
       <c r="L45" t="n">
-        <v>3010.83</v>
+        <v>3016.08</v>
       </c>
       <c r="M45" t="n">
-        <v>3019.05</v>
+        <v>3030.05</v>
       </c>
       <c r="N45" t="n">
-        <v>3027.28</v>
+        <v>3044.02</v>
       </c>
       <c r="O45" t="n">
-        <v>3038.4</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+        <v>3046.3</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4319,74 +4323,70 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3019.6</v>
+        <v>2971</v>
       </c>
       <c r="C46" t="n">
-        <v>3025.5</v>
+        <v>2982.5</v>
       </c>
       <c r="D46" t="n">
-        <v>2976.6</v>
+        <v>2946.1</v>
       </c>
       <c r="E46" t="n">
-        <v>2977.5</v>
+        <v>2958.7</v>
       </c>
       <c r="F46" t="n">
-        <v>-41.5</v>
+        <v>-18.8</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0063</v>
       </c>
       <c r="H46" t="n">
-        <v>48.9</v>
+        <v>36.4</v>
       </c>
       <c r="I46" t="n">
-        <v>2980</v>
+        <v>2927.7</v>
       </c>
       <c r="J46" t="n">
-        <v>2999.83</v>
+        <v>2916.83</v>
       </c>
       <c r="K46" t="n">
-        <v>3007.95</v>
+        <v>2953.05</v>
       </c>
       <c r="L46" t="n">
-        <v>3016.08</v>
+        <v>2989.28</v>
       </c>
       <c r="M46" t="n">
-        <v>3030.05</v>
+        <v>3001.95</v>
       </c>
       <c r="N46" t="n">
-        <v>3044.02</v>
+        <v>3014.62</v>
       </c>
       <c r="O46" t="n">
-        <v>3046.3</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
+        <v>3074.4</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4405,72 +4405,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2971</v>
+        <v>2958</v>
       </c>
       <c r="C47" t="n">
-        <v>2982.5</v>
+        <v>2964.6</v>
       </c>
       <c r="D47" t="n">
-        <v>2946.1</v>
+        <v>2918.9</v>
       </c>
       <c r="E47" t="n">
-        <v>2958.7</v>
+        <v>2924.7</v>
       </c>
       <c r="F47" t="n">
-        <v>-18.8</v>
+        <v>-34</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0115</v>
       </c>
       <c r="H47" t="n">
-        <v>36.4</v>
+        <v>45.7</v>
       </c>
       <c r="I47" t="n">
-        <v>2927.7</v>
+        <v>2909.7</v>
       </c>
       <c r="J47" t="n">
-        <v>2916.83</v>
+        <v>2919.5</v>
       </c>
       <c r="K47" t="n">
-        <v>2953.05</v>
+        <v>2940.5</v>
       </c>
       <c r="L47" t="n">
-        <v>2989.28</v>
+        <v>2961.5</v>
       </c>
       <c r="M47" t="n">
-        <v>3001.95</v>
+        <v>2976.9</v>
       </c>
       <c r="N47" t="n">
-        <v>3014.62</v>
+        <v>2992.3</v>
       </c>
       <c r="O47" t="n">
-        <v>3074.4</v>
+        <v>3018.9</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4494,75 +4492,75 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2958</v>
+        <v>2926.4</v>
       </c>
       <c r="C48" t="n">
-        <v>2964.6</v>
+        <v>2962.5</v>
       </c>
       <c r="D48" t="n">
-        <v>2918.9</v>
+        <v>2914.5</v>
       </c>
       <c r="E48" t="n">
-        <v>2924.7</v>
+        <v>2958.8</v>
       </c>
       <c r="F48" t="n">
-        <v>-34</v>
+        <v>34.1</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0.0117</v>
       </c>
       <c r="H48" t="n">
-        <v>45.7</v>
+        <v>48</v>
       </c>
       <c r="I48" t="n">
-        <v>2909.7</v>
+        <v>2873.2</v>
       </c>
       <c r="J48" t="n">
-        <v>2919.5</v>
+        <v>2870.47</v>
       </c>
       <c r="K48" t="n">
-        <v>2940.5</v>
+        <v>2901.85</v>
       </c>
       <c r="L48" t="n">
-        <v>2961.5</v>
+        <v>2933.22</v>
       </c>
       <c r="M48" t="n">
-        <v>2976.9</v>
+        <v>2947.55</v>
       </c>
       <c r="N48" t="n">
-        <v>2992.3</v>
+        <v>2961.88</v>
       </c>
       <c r="O48" t="n">
-        <v>3018.9</v>
+        <v>3010.3</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
@@ -4571,55 +4569,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2926.4</v>
+        <v>2957.6</v>
       </c>
       <c r="C49" t="n">
-        <v>2962.5</v>
+        <v>2983.3</v>
       </c>
       <c r="D49" t="n">
-        <v>2914.5</v>
+        <v>2949.9</v>
       </c>
       <c r="E49" t="n">
-        <v>2958.8</v>
+        <v>2969.7</v>
       </c>
       <c r="F49" t="n">
-        <v>34.1</v>
+        <v>10.9</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0117</v>
+        <v>0.0037</v>
       </c>
       <c r="H49" t="n">
-        <v>48</v>
+        <v>33.4</v>
       </c>
       <c r="I49" t="n">
-        <v>2873.2</v>
+        <v>2866.5</v>
       </c>
       <c r="J49" t="n">
-        <v>2870.47</v>
+        <v>2920.95</v>
       </c>
       <c r="K49" t="n">
-        <v>2901.85</v>
+        <v>2934.8</v>
       </c>
       <c r="L49" t="n">
-        <v>2933.22</v>
+        <v>2948.65</v>
       </c>
       <c r="M49" t="n">
-        <v>2947.55</v>
+        <v>2982.8</v>
       </c>
       <c r="N49" t="n">
-        <v>2961.88</v>
+        <v>3016.95</v>
       </c>
       <c r="O49" t="n">
-        <v>3010.3</v>
+        <v>3010.5</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4630,21 +4632,19 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
@@ -4655,57 +4655,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2957.6</v>
+        <v>2967.9</v>
       </c>
       <c r="C50" t="n">
-        <v>2983.3</v>
+        <v>2979.3</v>
       </c>
       <c r="D50" t="n">
-        <v>2949.9</v>
+        <v>2949.5</v>
       </c>
       <c r="E50" t="n">
-        <v>2969.7</v>
+        <v>2976.6</v>
       </c>
       <c r="F50" t="n">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0023</v>
       </c>
       <c r="H50" t="n">
-        <v>33.4</v>
+        <v>29.8</v>
       </c>
       <c r="I50" t="n">
-        <v>2866.5</v>
+        <v>2916.5</v>
       </c>
       <c r="J50" t="n">
-        <v>2920.95</v>
+        <v>2937.85</v>
       </c>
       <c r="K50" t="n">
-        <v>2934.8</v>
+        <v>2953</v>
       </c>
       <c r="L50" t="n">
-        <v>2948.65</v>
+        <v>2968.15</v>
       </c>
       <c r="M50" t="n">
-        <v>2982.8</v>
+        <v>2986.4</v>
       </c>
       <c r="N50" t="n">
-        <v>3016.95</v>
+        <v>3004.65</v>
       </c>
       <c r="O50" t="n">
-        <v>3010.5</v>
+        <v>3016.7</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4713,18 +4713,18 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4739,57 +4739,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2967.9</v>
+        <v>2974.7</v>
       </c>
       <c r="C51" t="n">
-        <v>2979.3</v>
+        <v>2977.9</v>
       </c>
       <c r="D51" t="n">
-        <v>2949.5</v>
+        <v>2954.7</v>
       </c>
       <c r="E51" t="n">
-        <v>2976.6</v>
+        <v>2963.6</v>
       </c>
       <c r="F51" t="n">
-        <v>6.9</v>
+        <v>-13</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0044</v>
       </c>
       <c r="H51" t="n">
-        <v>29.8</v>
+        <v>23.2</v>
       </c>
       <c r="I51" t="n">
-        <v>2916.5</v>
+        <v>2919.7</v>
       </c>
       <c r="J51" t="n">
-        <v>2937.85</v>
+        <v>2952.9</v>
       </c>
       <c r="K51" t="n">
-        <v>2953</v>
+        <v>2961.7</v>
       </c>
       <c r="L51" t="n">
-        <v>2968.15</v>
+        <v>2970.5</v>
       </c>
       <c r="M51" t="n">
-        <v>2986.4</v>
+        <v>2991.5</v>
       </c>
       <c r="N51" t="n">
-        <v>3004.65</v>
+        <v>3012.5</v>
       </c>
       <c r="O51" t="n">
-        <v>3016.7</v>
+        <v>3009.1</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4799,12 +4799,12 @@
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4830,63 +4830,67 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2974.7</v>
+        <v>2963.1</v>
       </c>
       <c r="C52" t="n">
-        <v>2977.9</v>
+        <v>2966.2</v>
       </c>
       <c r="D52" t="n">
-        <v>2954.7</v>
+        <v>2919.4</v>
       </c>
       <c r="E52" t="n">
-        <v>2963.6</v>
+        <v>2923</v>
       </c>
       <c r="F52" t="n">
-        <v>-13</v>
+        <v>-40.6</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0137</v>
       </c>
       <c r="H52" t="n">
-        <v>23.2</v>
+        <v>46.8</v>
       </c>
       <c r="I52" t="n">
-        <v>2919.7</v>
+        <v>2931.5</v>
       </c>
       <c r="J52" t="n">
-        <v>2952.9</v>
+        <v>2939.05</v>
       </c>
       <c r="K52" t="n">
-        <v>2961.7</v>
+        <v>2952</v>
       </c>
       <c r="L52" t="n">
-        <v>2970.5</v>
+        <v>2964.95</v>
       </c>
       <c r="M52" t="n">
-        <v>2991.5</v>
+        <v>2975.2</v>
       </c>
       <c r="N52" t="n">
-        <v>3012.5</v>
+        <v>2985.45</v>
       </c>
       <c r="O52" t="n">
-        <v>3009.1</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
+        <v>3001.1</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4905,76 +4909,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2963.1</v>
+        <v>2923.1</v>
       </c>
       <c r="C53" t="n">
-        <v>2966.2</v>
+        <v>2933.8</v>
       </c>
       <c r="D53" t="n">
-        <v>2919.4</v>
+        <v>2887.8</v>
       </c>
       <c r="E53" t="n">
-        <v>2923</v>
+        <v>2893.4</v>
       </c>
       <c r="F53" t="n">
-        <v>-40.6</v>
+        <v>-29.6</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0101</v>
       </c>
       <c r="H53" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="I53" t="n">
-        <v>2931.5</v>
+        <v>2872.6</v>
       </c>
       <c r="J53" t="n">
-        <v>2939.05</v>
+        <v>2866.3</v>
       </c>
       <c r="K53" t="n">
-        <v>2952</v>
+        <v>2899.6</v>
       </c>
       <c r="L53" t="n">
-        <v>2964.95</v>
+        <v>2932.9</v>
       </c>
       <c r="M53" t="n">
-        <v>2975.2</v>
+        <v>2946.4</v>
       </c>
       <c r="N53" t="n">
-        <v>2985.45</v>
+        <v>2959.9</v>
       </c>
       <c r="O53" t="n">
-        <v>3001.1</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
+        <v>3013</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4998,50 +4994,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2923.1</v>
+        <v>2890.9</v>
       </c>
       <c r="C54" t="n">
-        <v>2933.8</v>
+        <v>2929.8</v>
       </c>
       <c r="D54" t="n">
-        <v>2887.8</v>
+        <v>2887.6</v>
       </c>
       <c r="E54" t="n">
-        <v>2893.4</v>
+        <v>2904.5</v>
       </c>
       <c r="F54" t="n">
-        <v>-29.6</v>
+        <v>11.1</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0101</v>
+        <v>0.0038</v>
       </c>
       <c r="H54" t="n">
-        <v>46</v>
+        <v>42.2</v>
       </c>
       <c r="I54" t="n">
-        <v>2872.6</v>
+        <v>2841.8</v>
       </c>
       <c r="J54" t="n">
-        <v>2866.3</v>
+        <v>2838.7</v>
       </c>
       <c r="K54" t="n">
-        <v>2899.6</v>
+        <v>2870.4</v>
       </c>
       <c r="L54" t="n">
-        <v>2932.9</v>
+        <v>2902.1</v>
       </c>
       <c r="M54" t="n">
-        <v>2946.4</v>
+        <v>2916.4</v>
       </c>
       <c r="N54" t="n">
-        <v>2959.9</v>
+        <v>2930.7</v>
       </c>
       <c r="O54" t="n">
-        <v>3013</v>
+        <v>2979.8</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5049,18 +5045,18 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R54" s="6" t="n">
+        <v/>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5073,55 +5069,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2890.9</v>
+        <v>2892.7</v>
       </c>
       <c r="C55" t="n">
-        <v>2929.8</v>
+        <v>2913.5</v>
       </c>
       <c r="D55" t="n">
-        <v>2887.6</v>
+        <v>2884.3</v>
       </c>
       <c r="E55" t="n">
-        <v>2904.5</v>
+        <v>2894.1</v>
       </c>
       <c r="F55" t="n">
-        <v>11.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0036</v>
       </c>
       <c r="H55" t="n">
-        <v>42.2</v>
+        <v>29.2</v>
       </c>
       <c r="I55" t="n">
-        <v>2841.8</v>
+        <v>2845.4</v>
       </c>
       <c r="J55" t="n">
-        <v>2838.7</v>
+        <v>2860.2</v>
       </c>
       <c r="K55" t="n">
-        <v>2870.4</v>
+        <v>2883.4</v>
       </c>
       <c r="L55" t="n">
-        <v>2902.1</v>
+        <v>2906.6</v>
       </c>
       <c r="M55" t="n">
-        <v>2916.4</v>
+        <v>2925.6</v>
       </c>
       <c r="N55" t="n">
-        <v>2930.7</v>
+        <v>2944.6</v>
       </c>
       <c r="O55" t="n">
-        <v>2979.8</v>
+        <v>2972</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5129,18 +5129,18 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5153,59 +5153,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2892.7</v>
+        <v>2896.4</v>
       </c>
       <c r="C56" t="n">
-        <v>2913.5</v>
+        <v>2896.5</v>
       </c>
       <c r="D56" t="n">
-        <v>2884.3</v>
+        <v>2862.7</v>
       </c>
       <c r="E56" t="n">
-        <v>2894.1</v>
+        <v>2873.1</v>
       </c>
       <c r="F56" t="n">
-        <v>-10.4</v>
+        <v>-21</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0073</v>
       </c>
       <c r="H56" t="n">
-        <v>29.2</v>
+        <v>33.8</v>
       </c>
       <c r="I56" t="n">
-        <v>2845.4</v>
+        <v>2855.1</v>
       </c>
       <c r="J56" t="n">
-        <v>2860.2</v>
+        <v>2862.5</v>
       </c>
       <c r="K56" t="n">
-        <v>2883.4</v>
+        <v>2879.5</v>
       </c>
       <c r="L56" t="n">
-        <v>2906.6</v>
+        <v>2896.5</v>
       </c>
       <c r="M56" t="n">
-        <v>2925.6</v>
+        <v>2908.7</v>
       </c>
       <c r="N56" t="n">
-        <v>2944.6</v>
+        <v>2920.9</v>
       </c>
       <c r="O56" t="n">
-        <v>2972</v>
+        <v>2942.7</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5218,7 +5214,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5242,69 +5238,73 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2896.4</v>
+        <v>2875.1</v>
       </c>
       <c r="C57" t="n">
-        <v>2896.5</v>
+        <v>2892.5</v>
       </c>
       <c r="D57" t="n">
-        <v>2862.7</v>
+        <v>2831.9</v>
       </c>
       <c r="E57" t="n">
-        <v>2873.1</v>
+        <v>2861.7</v>
       </c>
       <c r="F57" t="n">
-        <v>-21</v>
+        <v>-11.4</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.004</v>
       </c>
       <c r="H57" t="n">
-        <v>33.8</v>
+        <v>60.6</v>
       </c>
       <c r="I57" t="n">
-        <v>2855.1</v>
+        <v>2828.9</v>
       </c>
       <c r="J57" t="n">
-        <v>2862.5</v>
+        <v>2836.05</v>
       </c>
       <c r="K57" t="n">
-        <v>2879.5</v>
+        <v>2856.2</v>
       </c>
       <c r="L57" t="n">
-        <v>2896.5</v>
+        <v>2876.35</v>
       </c>
       <c r="M57" t="n">
-        <v>2908.7</v>
+        <v>2890</v>
       </c>
       <c r="N57" t="n">
-        <v>2920.9</v>
+        <v>2903.65</v>
       </c>
       <c r="O57" t="n">
-        <v>2942.7</v>
+        <v>2930.3</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5322,74 +5322,70 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2875.1</v>
+        <v>2861.2</v>
       </c>
       <c r="C58" t="n">
-        <v>2892.5</v>
+        <v>2904.6</v>
       </c>
       <c r="D58" t="n">
-        <v>2831.9</v>
+        <v>2859.3</v>
       </c>
       <c r="E58" t="n">
-        <v>2861.7</v>
+        <v>2875.9</v>
       </c>
       <c r="F58" t="n">
-        <v>-11.4</v>
+        <v>14.2</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.005</v>
       </c>
       <c r="H58" t="n">
-        <v>60.6</v>
+        <v>45.3</v>
       </c>
       <c r="I58" t="n">
-        <v>2828.9</v>
+        <v>2771.3</v>
       </c>
       <c r="J58" t="n">
-        <v>2836.05</v>
+        <v>2800.85</v>
       </c>
       <c r="K58" t="n">
-        <v>2856.2</v>
+        <v>2831.4</v>
       </c>
       <c r="L58" t="n">
-        <v>2876.35</v>
+        <v>2861.95</v>
       </c>
       <c r="M58" t="n">
-        <v>2890</v>
+        <v>2892</v>
       </c>
       <c r="N58" t="n">
-        <v>2903.65</v>
+        <v>2922.05</v>
       </c>
       <c r="O58" t="n">
-        <v>2930.3</v>
+        <v>2953.1</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U58" s="8" t="n">
         <v/>
       </c>
@@ -5401,55 +5397,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2861.2</v>
+        <v>2870.5</v>
       </c>
       <c r="C59" t="n">
-        <v>2904.6</v>
+        <v>2883</v>
       </c>
       <c r="D59" t="n">
-        <v>2859.3</v>
+        <v>2856.9</v>
       </c>
       <c r="E59" t="n">
-        <v>2875.9</v>
+        <v>2873.23</v>
       </c>
       <c r="F59" t="n">
-        <v>14.2</v>
+        <v>-2.67</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0009</v>
       </c>
       <c r="H59" t="n">
-        <v>45.3</v>
+        <v>26.1</v>
       </c>
       <c r="I59" t="n">
-        <v>2771.3</v>
+        <v>2814</v>
       </c>
       <c r="J59" t="n">
-        <v>2800.85</v>
+        <v>2827.57</v>
       </c>
       <c r="K59" t="n">
-        <v>2831.4</v>
+        <v>2853.25</v>
       </c>
       <c r="L59" t="n">
-        <v>2861.95</v>
+        <v>2878.92</v>
       </c>
       <c r="M59" t="n">
-        <v>2892</v>
+        <v>2898.55</v>
       </c>
       <c r="N59" t="n">
-        <v>2922.05</v>
+        <v>2918.17</v>
       </c>
       <c r="O59" t="n">
-        <v>2953.1</v>
+        <v>2949.9</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5462,13 +5462,11 @@
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5481,59 +5479,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2870.5</v>
+        <v>2879.5</v>
       </c>
       <c r="C60" t="n">
-        <v>2883</v>
+        <v>2907.3</v>
       </c>
       <c r="D60" t="n">
-        <v>2856.9</v>
+        <v>2876.6</v>
       </c>
       <c r="E60" t="n">
-        <v>2873.23</v>
+        <v>2897.4</v>
       </c>
       <c r="F60" t="n">
-        <v>-2.67</v>
+        <v>24.17</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H60" t="n">
-        <v>26.1</v>
+        <v>30.7</v>
       </c>
       <c r="I60" t="n">
-        <v>2814</v>
+        <v>2830.8</v>
       </c>
       <c r="J60" t="n">
-        <v>2827.57</v>
+        <v>2848.77</v>
       </c>
       <c r="K60" t="n">
-        <v>2853.25</v>
+        <v>2860.18</v>
       </c>
       <c r="L60" t="n">
-        <v>2878.92</v>
+        <v>2871.59</v>
       </c>
       <c r="M60" t="n">
-        <v>2898.55</v>
+        <v>2886.28</v>
       </c>
       <c r="N60" t="n">
-        <v>2918.17</v>
+        <v>2900.97</v>
       </c>
       <c r="O60" t="n">
-        <v>2949.9</v>
+        <v>2909.1</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5546,14 +5540,18 @@
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
@@ -5563,55 +5561,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2879.5</v>
+        <v>2897.8</v>
       </c>
       <c r="C61" t="n">
-        <v>2907.3</v>
+        <v>2931.2</v>
       </c>
       <c r="D61" t="n">
-        <v>2876.6</v>
+        <v>2884.2</v>
       </c>
       <c r="E61" t="n">
-        <v>2897.4</v>
+        <v>2914.1</v>
       </c>
       <c r="F61" t="n">
-        <v>24.17</v>
+        <v>16.7</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0058</v>
       </c>
       <c r="H61" t="n">
-        <v>30.7</v>
+        <v>47</v>
       </c>
       <c r="I61" t="n">
-        <v>2830.8</v>
+        <v>2845.9</v>
       </c>
       <c r="J61" t="n">
-        <v>2848.77</v>
+        <v>2869.42</v>
       </c>
       <c r="K61" t="n">
-        <v>2860.18</v>
+        <v>2882.05</v>
       </c>
       <c r="L61" t="n">
-        <v>2871.59</v>
+        <v>2894.67</v>
       </c>
       <c r="M61" t="n">
-        <v>2886.28</v>
+        <v>2912.75</v>
       </c>
       <c r="N61" t="n">
-        <v>2900.97</v>
+        <v>2930.82</v>
       </c>
       <c r="O61" t="n">
-        <v>2909.1</v>
+        <v>2938</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5622,19 +5624,19 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="10" t="inlineStr">
+      <c r="S61" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="V61" s="8" t="n">
@@ -5654,74 +5656,74 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2897.8</v>
+        <v>2860.7</v>
       </c>
       <c r="C62" t="n">
-        <v>2931.2</v>
+        <v>2862</v>
       </c>
       <c r="D62" t="n">
-        <v>2884.2</v>
+        <v>2859.8</v>
       </c>
       <c r="E62" t="n">
-        <v>2914.1</v>
+        <v>2861</v>
       </c>
       <c r="F62" t="n">
-        <v>16.7</v>
+        <v>-53.1</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0182</v>
       </c>
       <c r="H62" t="n">
-        <v>47</v>
+        <v>2.2</v>
       </c>
       <c r="I62" t="n">
-        <v>2845.9</v>
+        <v>2837.2</v>
       </c>
       <c r="J62" t="n">
-        <v>2869.42</v>
+        <v>2870.3</v>
       </c>
       <c r="K62" t="n">
-        <v>2882.05</v>
+        <v>2890.6</v>
       </c>
       <c r="L62" t="n">
-        <v>2894.67</v>
+        <v>2910.9</v>
       </c>
       <c r="M62" t="n">
-        <v>2912.75</v>
+        <v>2937.6</v>
       </c>
       <c r="N62" t="n">
-        <v>2930.82</v>
+        <v>2964.3</v>
       </c>
       <c r="O62" t="n">
-        <v>2938</v>
+        <v>2978.2</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
       </c>
       <c r="V62" s="8" t="n">
         <v/>
@@ -5731,95 +5733,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>2912</v>
-      </c>
-      <c r="C63" t="n">
-        <v>2915.3</v>
-      </c>
-      <c r="D63" t="n">
-        <v>2895.5</v>
-      </c>
-      <c r="E63" t="n">
-        <v>2897.2</v>
-      </c>
-      <c r="F63" t="n">
-        <v>-16.9</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>-0.0058</v>
-      </c>
-      <c r="H63" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="I63" t="n">
-        <v>2837.2</v>
-      </c>
-      <c r="J63" t="n">
-        <v>2870.3</v>
-      </c>
-      <c r="K63" t="n">
-        <v>2890.6</v>
-      </c>
-      <c r="L63" t="n">
-        <v>2910.9</v>
-      </c>
-      <c r="M63" t="n">
-        <v>2937.6</v>
-      </c>
-      <c r="N63" t="n">
-        <v>2964.3</v>
-      </c>
-      <c r="O63" t="n">
-        <v>2978.2</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3020.9</v>
+        <v>3026.1</v>
       </c>
       <c r="C2" t="n">
-        <v>3044.9</v>
+        <v>3050.6</v>
       </c>
       <c r="D2" t="n">
-        <v>2987.8</v>
+        <v>3015.1</v>
       </c>
       <c r="E2" t="n">
-        <v>3030.6</v>
+        <v>3045.6</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0049</v>
       </c>
       <c r="H2" t="n">
-        <v>57.1</v>
+        <v>35.5</v>
       </c>
       <c r="I2" t="n">
-        <v>2953.5</v>
+        <v>2930.7</v>
       </c>
       <c r="J2" t="n">
-        <v>2976.48</v>
+        <v>2980.63</v>
       </c>
       <c r="K2" t="n">
-        <v>2999.55</v>
+        <v>3002.05</v>
       </c>
       <c r="L2" t="n">
-        <v>3022.63</v>
+        <v>3023.48</v>
       </c>
       <c r="M2" t="n">
-        <v>3045.65</v>
+        <v>3059.15</v>
       </c>
       <c r="N2" t="n">
-        <v>3068.67</v>
+        <v>3094.83</v>
       </c>
       <c r="O2" t="n">
-        <v>3091.8</v>
+        <v>3102</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,18 +685,18 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -709,59 +709,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3026.1</v>
+        <v>3040</v>
       </c>
       <c r="C3" t="n">
-        <v>3050.6</v>
+        <v>3068.4</v>
       </c>
       <c r="D3" t="n">
-        <v>3015.1</v>
+        <v>3023.7</v>
       </c>
       <c r="E3" t="n">
-        <v>3045.6</v>
+        <v>3035.1</v>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>-10.5</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.0034</v>
       </c>
       <c r="H3" t="n">
-        <v>35.5</v>
+        <v>44.7</v>
       </c>
       <c r="I3" t="n">
-        <v>2930.7</v>
+        <v>2979.6</v>
       </c>
       <c r="J3" t="n">
-        <v>2980.63</v>
+        <v>3016.48</v>
       </c>
       <c r="K3" t="n">
-        <v>3002.05</v>
+        <v>3027.85</v>
       </c>
       <c r="L3" t="n">
-        <v>3023.48</v>
+        <v>3039.23</v>
       </c>
       <c r="M3" t="n">
-        <v>3059.15</v>
+        <v>3063.35</v>
       </c>
       <c r="N3" t="n">
-        <v>3094.83</v>
+        <v>3087.48</v>
       </c>
       <c r="O3" t="n">
-        <v>3102</v>
+        <v>3086.1</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -769,17 +765,19 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U3" s="8" t="n">
@@ -793,55 +791,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3040</v>
+        <v>3030.9</v>
       </c>
       <c r="C4" t="n">
-        <v>3068.4</v>
+        <v>3062.4</v>
       </c>
       <c r="D4" t="n">
-        <v>3023.7</v>
+        <v>2988.5</v>
       </c>
       <c r="E4" t="n">
-        <v>3035.1</v>
+        <v>3014.2</v>
       </c>
       <c r="F4" t="n">
-        <v>-10.5</v>
+        <v>-20.9</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0069</v>
       </c>
       <c r="H4" t="n">
-        <v>44.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>2979.6</v>
+        <v>2979</v>
       </c>
       <c r="J4" t="n">
-        <v>3016.48</v>
+        <v>2984.93</v>
       </c>
       <c r="K4" t="n">
-        <v>3027.85</v>
+        <v>3012.75</v>
       </c>
       <c r="L4" t="n">
-        <v>3039.23</v>
+        <v>3040.58</v>
       </c>
       <c r="M4" t="n">
-        <v>3063.35</v>
+        <v>3057.45</v>
       </c>
       <c r="N4" t="n">
-        <v>3087.48</v>
+        <v>3074.33</v>
       </c>
       <c r="O4" t="n">
-        <v>3086.1</v>
+        <v>3113.1</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -851,19 +853,19 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -877,57 +879,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3030.9</v>
+        <v>3019.7</v>
       </c>
       <c r="C5" t="n">
-        <v>3062.4</v>
+        <v>3042.1</v>
       </c>
       <c r="D5" t="n">
-        <v>2988.5</v>
+        <v>3006.7</v>
       </c>
       <c r="E5" t="n">
-        <v>3014.2</v>
+        <v>3027</v>
       </c>
       <c r="F5" t="n">
-        <v>-20.9</v>
+        <v>12.8</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0042</v>
       </c>
       <c r="H5" t="n">
-        <v>73.90000000000001</v>
+        <v>35.4</v>
       </c>
       <c r="I5" t="n">
-        <v>2979</v>
+        <v>2914.6</v>
       </c>
       <c r="J5" t="n">
-        <v>2984.93</v>
+        <v>2934.68</v>
       </c>
       <c r="K5" t="n">
-        <v>3012.75</v>
+        <v>2977.25</v>
       </c>
       <c r="L5" t="n">
-        <v>3040.58</v>
+        <v>3019.82</v>
       </c>
       <c r="M5" t="n">
-        <v>3057.45</v>
+        <v>3051.15</v>
       </c>
       <c r="N5" t="n">
-        <v>3074.33</v>
+        <v>3082.47</v>
       </c>
       <c r="O5" t="n">
-        <v>3113.1</v>
+        <v>3136.3</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -935,20 +937,16 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -963,70 +961,74 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3019.7</v>
+        <v>3033.4</v>
       </c>
       <c r="C6" t="n">
-        <v>3042.1</v>
+        <v>3042.6</v>
       </c>
       <c r="D6" t="n">
-        <v>3006.7</v>
+        <v>2988.8</v>
       </c>
       <c r="E6" t="n">
-        <v>3027</v>
+        <v>2998.8</v>
       </c>
       <c r="F6" t="n">
-        <v>12.8</v>
+        <v>-28.2</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>35.4</v>
+        <v>53.8</v>
       </c>
       <c r="I6" t="n">
-        <v>2914.6</v>
+        <v>2971.3</v>
       </c>
       <c r="J6" t="n">
-        <v>2934.68</v>
+        <v>2992.9</v>
       </c>
       <c r="K6" t="n">
-        <v>2977.25</v>
+        <v>3009.3</v>
       </c>
       <c r="L6" t="n">
-        <v>3019.82</v>
+        <v>3025.7</v>
       </c>
       <c r="M6" t="n">
-        <v>3051.15</v>
+        <v>3044.7</v>
       </c>
       <c r="N6" t="n">
-        <v>3082.47</v>
+        <v>3063.7</v>
       </c>
       <c r="O6" t="n">
-        <v>3136.3</v>
+        <v>3077.5</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1045,71 +1047,69 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3033.4</v>
+        <v>2994.3</v>
       </c>
       <c r="C7" t="n">
-        <v>3042.6</v>
+        <v>3004.3</v>
       </c>
       <c r="D7" t="n">
-        <v>2988.8</v>
+        <v>2943.4</v>
       </c>
       <c r="E7" t="n">
-        <v>2998.8</v>
+        <v>2971.5</v>
       </c>
       <c r="F7" t="n">
-        <v>-28.2</v>
+        <v>-27.3</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0091</v>
       </c>
       <c r="H7" t="n">
-        <v>53.8</v>
+        <v>60.9</v>
       </c>
       <c r="I7" t="n">
-        <v>2971.3</v>
+        <v>2935</v>
       </c>
       <c r="J7" t="n">
-        <v>2992.9</v>
+        <v>2936.55</v>
       </c>
       <c r="K7" t="n">
-        <v>3009.3</v>
+        <v>2971.9</v>
       </c>
       <c r="L7" t="n">
+        <v>3007.25</v>
+      </c>
+      <c r="M7" t="n">
         <v>3025.7</v>
       </c>
-      <c r="M7" t="n">
-        <v>3044.7</v>
-      </c>
       <c r="N7" t="n">
-        <v>3063.7</v>
+        <v>3044.15</v>
       </c>
       <c r="O7" t="n">
-        <v>3077.5</v>
+        <v>3096.4</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -1131,57 +1131,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2994.3</v>
+        <v>2965.8</v>
       </c>
       <c r="C8" t="n">
-        <v>3004.3</v>
+        <v>3014.9</v>
       </c>
       <c r="D8" t="n">
-        <v>2943.4</v>
+        <v>2964.3</v>
       </c>
       <c r="E8" t="n">
-        <v>2971.5</v>
+        <v>3008.4</v>
       </c>
       <c r="F8" t="n">
-        <v>-27.3</v>
+        <v>36.9</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0091</v>
+        <v>0.0124</v>
       </c>
       <c r="H8" t="n">
-        <v>60.9</v>
+        <v>50.6</v>
       </c>
       <c r="I8" t="n">
-        <v>2935</v>
+        <v>2882.5</v>
       </c>
       <c r="J8" t="n">
-        <v>2936.55</v>
+        <v>2909.42</v>
       </c>
       <c r="K8" t="n">
-        <v>2971.9</v>
+        <v>2941.05</v>
       </c>
       <c r="L8" t="n">
-        <v>3007.25</v>
+        <v>2972.67</v>
       </c>
       <c r="M8" t="n">
-        <v>3025.7</v>
+        <v>3001.95</v>
       </c>
       <c r="N8" t="n">
-        <v>3044.15</v>
+        <v>3031.23</v>
       </c>
       <c r="O8" t="n">
-        <v>3096.4</v>
+        <v>3065.2</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1189,19 +1189,19 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1213,59 +1213,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2965.8</v>
+        <v>3008.1</v>
       </c>
       <c r="C9" t="n">
-        <v>3014.9</v>
+        <v>3019.5</v>
       </c>
       <c r="D9" t="n">
-        <v>2964.3</v>
+        <v>2970.8</v>
       </c>
       <c r="E9" t="n">
-        <v>3008.4</v>
+        <v>2994</v>
       </c>
       <c r="F9" t="n">
-        <v>36.9</v>
+        <v>-14.4</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0048</v>
       </c>
       <c r="H9" t="n">
-        <v>50.6</v>
+        <v>48.7</v>
       </c>
       <c r="I9" t="n">
-        <v>2882.5</v>
+        <v>2913.7</v>
       </c>
       <c r="J9" t="n">
-        <v>2909.42</v>
+        <v>2967.2</v>
       </c>
       <c r="K9" t="n">
-        <v>2941.05</v>
+        <v>2983.1</v>
       </c>
       <c r="L9" t="n">
-        <v>2972.67</v>
+        <v>2999</v>
       </c>
       <c r="M9" t="n">
-        <v>3001.95</v>
+        <v>3033.7</v>
       </c>
       <c r="N9" t="n">
-        <v>3031.23</v>
+        <v>3068.4</v>
       </c>
       <c r="O9" t="n">
-        <v>3065.2</v>
+        <v>3065.5</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1273,18 +1269,18 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1297,55 +1293,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3008.1</v>
+        <v>2984.7</v>
       </c>
       <c r="C10" t="n">
-        <v>3019.5</v>
+        <v>2995.8</v>
       </c>
       <c r="D10" t="n">
-        <v>2970.8</v>
+        <v>2961.8</v>
       </c>
       <c r="E10" t="n">
-        <v>2994</v>
+        <v>2970.4</v>
       </c>
       <c r="F10" t="n">
-        <v>-14.4</v>
+        <v>-23.6</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>48.7</v>
+        <v>34</v>
       </c>
       <c r="I10" t="n">
-        <v>2913.7</v>
+        <v>2922.1</v>
       </c>
       <c r="J10" t="n">
-        <v>2967.2</v>
+        <v>2944.73</v>
       </c>
       <c r="K10" t="n">
-        <v>2983.1</v>
+        <v>2969.65</v>
       </c>
       <c r="L10" t="n">
-        <v>2999</v>
+        <v>2994.58</v>
       </c>
       <c r="M10" t="n">
-        <v>3033.7</v>
+        <v>3018.35</v>
       </c>
       <c r="N10" t="n">
-        <v>3068.4</v>
+        <v>3042.12</v>
       </c>
       <c r="O10" t="n">
-        <v>3065.5</v>
+        <v>3068.2</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1379,57 +1379,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2984.7</v>
+        <v>2967.2</v>
       </c>
       <c r="C11" t="n">
-        <v>2995.8</v>
+        <v>3029.8</v>
       </c>
       <c r="D11" t="n">
-        <v>2961.8</v>
+        <v>2956.2</v>
       </c>
       <c r="E11" t="n">
-        <v>2970.4</v>
+        <v>2979.9</v>
       </c>
       <c r="F11" t="n">
-        <v>-23.6</v>
+        <v>9.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H11" t="n">
-        <v>34</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>2922.1</v>
+        <v>2927.8</v>
       </c>
       <c r="J11" t="n">
-        <v>2944.73</v>
+        <v>2932.2</v>
       </c>
       <c r="K11" t="n">
-        <v>2969.65</v>
+        <v>2953.4</v>
       </c>
       <c r="L11" t="n">
-        <v>2994.58</v>
+        <v>2974.6</v>
       </c>
       <c r="M11" t="n">
-        <v>3018.35</v>
+        <v>2987.4</v>
       </c>
       <c r="N11" t="n">
-        <v>3042.12</v>
+        <v>3000.2</v>
       </c>
       <c r="O11" t="n">
-        <v>3068.2</v>
+        <v>3029.8</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1437,24 +1437,28 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v/>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
@@ -1463,57 +1467,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2967.2</v>
+        <v>2981.2</v>
       </c>
       <c r="C12" t="n">
-        <v>3029.8</v>
+        <v>3006.1</v>
       </c>
       <c r="D12" t="n">
-        <v>2956.2</v>
+        <v>2974.4</v>
       </c>
       <c r="E12" t="n">
-        <v>2979.9</v>
+        <v>2991.8</v>
       </c>
       <c r="F12" t="n">
-        <v>9.5</v>
+        <v>11.9</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.004</v>
       </c>
       <c r="H12" t="n">
-        <v>73.59999999999999</v>
+        <v>31.7</v>
       </c>
       <c r="I12" t="n">
-        <v>2927.8</v>
+        <v>2882.6</v>
       </c>
       <c r="J12" t="n">
-        <v>2932.2</v>
+        <v>2899.75</v>
       </c>
       <c r="K12" t="n">
-        <v>2953.4</v>
+        <v>2943.1</v>
       </c>
       <c r="L12" t="n">
-        <v>2974.6</v>
+        <v>2986.45</v>
       </c>
       <c r="M12" t="n">
-        <v>2987.4</v>
+        <v>3016.7</v>
       </c>
       <c r="N12" t="n">
-        <v>3000.2</v>
+        <v>3046.95</v>
       </c>
       <c r="O12" t="n">
-        <v>3029.8</v>
+        <v>3103.4</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1529,20 +1533,14 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v/>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
@@ -1558,50 +1556,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2981.2</v>
+        <v>2995.3</v>
       </c>
       <c r="C13" t="n">
-        <v>3006.1</v>
+        <v>3012.8</v>
       </c>
       <c r="D13" t="n">
-        <v>2974.4</v>
+        <v>2972.7</v>
       </c>
       <c r="E13" t="n">
-        <v>2991.8</v>
+        <v>2990.7</v>
       </c>
       <c r="F13" t="n">
-        <v>11.9</v>
+        <v>-1.1</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0004</v>
       </c>
       <c r="H13" t="n">
-        <v>31.7</v>
+        <v>40.1</v>
       </c>
       <c r="I13" t="n">
-        <v>2882.6</v>
+        <v>2942.7</v>
       </c>
       <c r="J13" t="n">
-        <v>2899.75</v>
+        <v>2960.87</v>
       </c>
       <c r="K13" t="n">
-        <v>2943.1</v>
+        <v>2975.95</v>
       </c>
       <c r="L13" t="n">
-        <v>2986.45</v>
+        <v>2991.03</v>
       </c>
       <c r="M13" t="n">
-        <v>3016.7</v>
+        <v>3007.65</v>
       </c>
       <c r="N13" t="n">
-        <v>3046.95</v>
+        <v>3024.28</v>
       </c>
       <c r="O13" t="n">
-        <v>3103.4</v>
+        <v>3037.8</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1609,16 +1607,20 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1633,78 +1635,78 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2995.3</v>
+        <v>2991.7</v>
       </c>
       <c r="C14" t="n">
-        <v>3012.8</v>
+        <v>2994.8</v>
       </c>
       <c r="D14" t="n">
-        <v>2972.7</v>
+        <v>2949.3</v>
       </c>
       <c r="E14" t="n">
-        <v>2990.7</v>
+        <v>2973.5</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1</v>
+        <v>-17.2</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0058</v>
       </c>
       <c r="H14" t="n">
-        <v>40.1</v>
+        <v>45.5</v>
       </c>
       <c r="I14" t="n">
-        <v>2942.7</v>
+        <v>2932.6</v>
       </c>
       <c r="J14" t="n">
-        <v>2960.87</v>
+        <v>2949.57</v>
       </c>
       <c r="K14" t="n">
-        <v>2975.95</v>
+        <v>2970.65</v>
       </c>
       <c r="L14" t="n">
-        <v>2991.03</v>
+        <v>2991.72</v>
       </c>
       <c r="M14" t="n">
-        <v>3007.65</v>
+        <v>3010.75</v>
       </c>
       <c r="N14" t="n">
-        <v>3024.28</v>
+        <v>3029.78</v>
       </c>
       <c r="O14" t="n">
-        <v>3037.8</v>
+        <v>3052.9</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1719,79 +1721,79 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2991.7</v>
+        <v>2964.5</v>
       </c>
       <c r="C15" t="n">
-        <v>2994.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D15" t="n">
-        <v>2949.3</v>
+        <v>2952.7</v>
       </c>
       <c r="E15" t="n">
-        <v>2973.5</v>
+        <v>2955.2</v>
       </c>
       <c r="F15" t="n">
-        <v>-17.2</v>
+        <v>-18.3</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0062</v>
       </c>
       <c r="H15" t="n">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="I15" t="n">
-        <v>2932.6</v>
+        <v>2903.8</v>
       </c>
       <c r="J15" t="n">
-        <v>2949.57</v>
+        <v>2928.72</v>
       </c>
       <c r="K15" t="n">
-        <v>2970.65</v>
+        <v>2950.75</v>
       </c>
       <c r="L15" t="n">
-        <v>2991.72</v>
+        <v>2972.78</v>
       </c>
       <c r="M15" t="n">
-        <v>3010.75</v>
+        <v>2996.25</v>
       </c>
       <c r="N15" t="n">
-        <v>3029.78</v>
+        <v>3019.72</v>
       </c>
       <c r="O15" t="n">
-        <v>3052.9</v>
+        <v>3040.3</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
@@ -1805,57 +1807,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2964.5</v>
+        <v>2955.8</v>
       </c>
       <c r="C16" t="n">
-        <v>2998.7</v>
+        <v>2999.8</v>
       </c>
       <c r="D16" t="n">
-        <v>2952.7</v>
+        <v>2951.1</v>
       </c>
       <c r="E16" t="n">
-        <v>2955.2</v>
+        <v>2997</v>
       </c>
       <c r="F16" t="n">
-        <v>-18.3</v>
+        <v>41.8</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0141</v>
       </c>
       <c r="H16" t="n">
-        <v>46</v>
+        <v>48.7</v>
       </c>
       <c r="I16" t="n">
-        <v>2903.8</v>
+        <v>2906.7</v>
       </c>
       <c r="J16" t="n">
-        <v>2928.72</v>
+        <v>2898.95</v>
       </c>
       <c r="K16" t="n">
-        <v>2950.75</v>
+        <v>2932.2</v>
       </c>
       <c r="L16" t="n">
-        <v>2972.78</v>
+        <v>2965.45</v>
       </c>
       <c r="M16" t="n">
-        <v>2996.25</v>
+        <v>2978.2</v>
       </c>
       <c r="N16" t="n">
-        <v>3019.72</v>
+        <v>2990.95</v>
       </c>
       <c r="O16" t="n">
-        <v>3040.3</v>
+        <v>3044.7</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1863,23 +1865,23 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1898,50 +1900,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2955.8</v>
+        <v>2997</v>
       </c>
       <c r="C17" t="n">
-        <v>2999.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D17" t="n">
-        <v>2951.1</v>
+        <v>2965.5</v>
       </c>
       <c r="E17" t="n">
-        <v>2997</v>
+        <v>2969.8</v>
       </c>
       <c r="F17" t="n">
-        <v>41.8</v>
+        <v>-27.2</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0141</v>
+        <v>-0.0091</v>
       </c>
       <c r="H17" t="n">
-        <v>48.7</v>
+        <v>33.2</v>
       </c>
       <c r="I17" t="n">
-        <v>2906.7</v>
+        <v>2902.4</v>
       </c>
       <c r="J17" t="n">
-        <v>2898.95</v>
+        <v>2959.08</v>
       </c>
       <c r="K17" t="n">
-        <v>2932.2</v>
+        <v>2972.65</v>
       </c>
       <c r="L17" t="n">
-        <v>2965.45</v>
+        <v>2986.23</v>
       </c>
       <c r="M17" t="n">
-        <v>2978.2</v>
+        <v>3021.35</v>
       </c>
       <c r="N17" t="n">
-        <v>2990.95</v>
+        <v>3056.47</v>
       </c>
       <c r="O17" t="n">
-        <v>3044.7</v>
+        <v>3048.5</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1949,24 +1951,22 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
@@ -1977,60 +1977,62 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2997</v>
+        <v>2974.6</v>
       </c>
       <c r="C18" t="n">
-        <v>2998.7</v>
+        <v>2979</v>
       </c>
       <c r="D18" t="n">
-        <v>2965.5</v>
+        <v>2932.1</v>
       </c>
       <c r="E18" t="n">
-        <v>2969.8</v>
+        <v>2951.7</v>
       </c>
       <c r="F18" t="n">
-        <v>-27.2</v>
+        <v>-18.1</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0091</v>
+        <v>-0.0061</v>
       </c>
       <c r="H18" t="n">
-        <v>33.2</v>
+        <v>46.9</v>
       </c>
       <c r="I18" t="n">
-        <v>2902.4</v>
+        <v>2932.3</v>
       </c>
       <c r="J18" t="n">
-        <v>2959.08</v>
+        <v>2930.45</v>
       </c>
       <c r="K18" t="n">
-        <v>2972.65</v>
+        <v>2953.2</v>
       </c>
       <c r="L18" t="n">
-        <v>2986.23</v>
+        <v>2975.95</v>
       </c>
       <c r="M18" t="n">
-        <v>3021.35</v>
+        <v>2986.4</v>
       </c>
       <c r="N18" t="n">
-        <v>3056.47</v>
+        <v>2996.85</v>
       </c>
       <c r="O18" t="n">
-        <v>3048.5</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
+        <v>3031.9</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q18" s="6" t="n">
         <v/>
@@ -2061,74 +2063,70 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2974.6</v>
+        <v>2948.5</v>
       </c>
       <c r="C19" t="n">
-        <v>2979</v>
+        <v>2969.7</v>
       </c>
       <c r="D19" t="n">
-        <v>2932.1</v>
+        <v>2934.5</v>
       </c>
       <c r="E19" t="n">
-        <v>2951.7</v>
+        <v>2941.3</v>
       </c>
       <c r="F19" t="n">
-        <v>-18.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0035</v>
       </c>
       <c r="H19" t="n">
-        <v>46.9</v>
+        <v>35.2</v>
       </c>
       <c r="I19" t="n">
-        <v>2932.3</v>
+        <v>2885.2</v>
       </c>
       <c r="J19" t="n">
-        <v>2930.45</v>
+        <v>2902.88</v>
       </c>
       <c r="K19" t="n">
-        <v>2953.2</v>
+        <v>2928.25</v>
       </c>
       <c r="L19" t="n">
-        <v>2975.95</v>
+        <v>2953.62</v>
       </c>
       <c r="M19" t="n">
-        <v>2986.4</v>
+        <v>2975.15</v>
       </c>
       <c r="N19" t="n">
-        <v>2996.85</v>
+        <v>2996.67</v>
       </c>
       <c r="O19" t="n">
-        <v>3031.9</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3025.9</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
       </c>
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R19" s="6" t="n">
+        <v/>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2147,57 +2145,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2948.5</v>
+        <v>2955.5</v>
       </c>
       <c r="C20" t="n">
-        <v>2969.7</v>
+        <v>2985.9</v>
       </c>
       <c r="D20" t="n">
-        <v>2934.5</v>
+        <v>2941.2</v>
       </c>
       <c r="E20" t="n">
-        <v>2941.3</v>
+        <v>2960</v>
       </c>
       <c r="F20" t="n">
-        <v>-10.4</v>
+        <v>18.7</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0064</v>
       </c>
       <c r="H20" t="n">
-        <v>35.2</v>
+        <v>44.7</v>
       </c>
       <c r="I20" t="n">
-        <v>2885.2</v>
+        <v>2899.3</v>
       </c>
       <c r="J20" t="n">
-        <v>2902.88</v>
+        <v>2900.7</v>
       </c>
       <c r="K20" t="n">
-        <v>2928.25</v>
+        <v>2923.7</v>
       </c>
       <c r="L20" t="n">
-        <v>2953.62</v>
+        <v>2946.7</v>
       </c>
       <c r="M20" t="n">
-        <v>2975.15</v>
+        <v>2958.9</v>
       </c>
       <c r="N20" t="n">
-        <v>2996.67</v>
+        <v>2971.1</v>
       </c>
       <c r="O20" t="n">
-        <v>3025.9</v>
+        <v>3004.9</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2208,16 +2206,20 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2227,59 +2229,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2955.5</v>
+        <v>2961.5</v>
       </c>
       <c r="C21" t="n">
-        <v>2985.9</v>
+        <v>2968.3</v>
       </c>
       <c r="D21" t="n">
-        <v>2941.2</v>
+        <v>2933.4</v>
       </c>
       <c r="E21" t="n">
-        <v>2960</v>
+        <v>2964.5</v>
       </c>
       <c r="F21" t="n">
-        <v>18.7</v>
+        <v>4.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0015</v>
       </c>
       <c r="H21" t="n">
-        <v>44.7</v>
+        <v>34.9</v>
       </c>
       <c r="I21" t="n">
-        <v>2899.3</v>
+        <v>2896.5</v>
       </c>
       <c r="J21" t="n">
-        <v>2900.7</v>
+        <v>2913.53</v>
       </c>
       <c r="K21" t="n">
-        <v>2923.7</v>
+        <v>2937.65</v>
       </c>
       <c r="L21" t="n">
-        <v>2946.7</v>
+        <v>2961.77</v>
       </c>
       <c r="M21" t="n">
-        <v>2958.9</v>
+        <v>2982.35</v>
       </c>
       <c r="N21" t="n">
-        <v>2971.1</v>
+        <v>3002.92</v>
       </c>
       <c r="O21" t="n">
-        <v>3004.9</v>
+        <v>3030.6</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2287,23 +2285,21 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2313,70 +2309,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2961.5</v>
+        <v>2966.9</v>
       </c>
       <c r="C22" t="n">
-        <v>2968.3</v>
+        <v>2978.3</v>
       </c>
       <c r="D22" t="n">
-        <v>2933.4</v>
+        <v>2902.3</v>
       </c>
       <c r="E22" t="n">
-        <v>2964.5</v>
+        <v>2915.4</v>
       </c>
       <c r="F22" t="n">
-        <v>4.5</v>
+        <v>-49.1</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0166</v>
       </c>
       <c r="H22" t="n">
-        <v>34.9</v>
+        <v>76</v>
       </c>
       <c r="I22" t="n">
-        <v>2896.5</v>
+        <v>2898.5</v>
       </c>
       <c r="J22" t="n">
-        <v>2913.53</v>
+        <v>2936.42</v>
       </c>
       <c r="K22" t="n">
-        <v>2937.65</v>
+        <v>2947.05</v>
       </c>
       <c r="L22" t="n">
-        <v>2961.77</v>
+        <v>2957.67</v>
       </c>
       <c r="M22" t="n">
-        <v>2982.35</v>
+        <v>2981.95</v>
       </c>
       <c r="N22" t="n">
-        <v>3002.92</v>
+        <v>3006.23</v>
       </c>
       <c r="O22" t="n">
-        <v>3030.6</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
+        <v>3003.2</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2388,88 +2392,84 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W22" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2966.9</v>
+        <v>2906.6</v>
       </c>
       <c r="C23" t="n">
-        <v>2978.3</v>
+        <v>2957.9</v>
       </c>
       <c r="D23" t="n">
-        <v>2902.3</v>
+        <v>2905.6</v>
       </c>
       <c r="E23" t="n">
-        <v>2915.4</v>
+        <v>2954.3</v>
       </c>
       <c r="F23" t="n">
-        <v>-49.1</v>
+        <v>38.9</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0166</v>
+        <v>0.0133</v>
       </c>
       <c r="H23" t="n">
-        <v>76</v>
+        <v>52.3</v>
       </c>
       <c r="I23" t="n">
-        <v>2898.5</v>
+        <v>2826.3</v>
       </c>
       <c r="J23" t="n">
-        <v>2936.42</v>
+        <v>2826.95</v>
       </c>
       <c r="K23" t="n">
-        <v>2947.05</v>
+        <v>2877.4</v>
       </c>
       <c r="L23" t="n">
-        <v>2957.67</v>
+        <v>2927.85</v>
       </c>
       <c r="M23" t="n">
-        <v>2981.95</v>
+        <v>2953.4</v>
       </c>
       <c r="N23" t="n">
-        <v>3006.23</v>
+        <v>2978.95</v>
       </c>
       <c r="O23" t="n">
-        <v>3003.2</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
+        <v>3054.3</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
@@ -2483,76 +2483,78 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2906.6</v>
+        <v>2954</v>
       </c>
       <c r="C24" t="n">
-        <v>2957.9</v>
+        <v>2976.3</v>
       </c>
       <c r="D24" t="n">
-        <v>2905.6</v>
+        <v>2905.3</v>
       </c>
       <c r="E24" t="n">
-        <v>2954.3</v>
+        <v>2938</v>
       </c>
       <c r="F24" t="n">
-        <v>38.9</v>
+        <v>-16.3</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0055</v>
       </c>
       <c r="H24" t="n">
-        <v>52.3</v>
+        <v>71</v>
       </c>
       <c r="I24" t="n">
-        <v>2826.3</v>
+        <v>2853.3</v>
       </c>
       <c r="J24" t="n">
-        <v>2826.95</v>
+        <v>2913.28</v>
       </c>
       <c r="K24" t="n">
-        <v>2877.4</v>
+        <v>2928.15</v>
       </c>
       <c r="L24" t="n">
-        <v>2927.85</v>
+        <v>2943.03</v>
       </c>
       <c r="M24" t="n">
-        <v>2953.4</v>
+        <v>2980.45</v>
       </c>
       <c r="N24" t="n">
-        <v>2978.95</v>
+        <v>3017.87</v>
       </c>
       <c r="O24" t="n">
-        <v>3054.3</v>
+        <v>3010.2</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2567,78 +2569,76 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2954</v>
+        <v>2950</v>
       </c>
       <c r="C25" t="n">
-        <v>2976.3</v>
+        <v>2994.6</v>
       </c>
       <c r="D25" t="n">
-        <v>2905.3</v>
+        <v>2948.4</v>
       </c>
       <c r="E25" t="n">
-        <v>2938</v>
+        <v>2989.3</v>
       </c>
       <c r="F25" t="n">
-        <v>-16.3</v>
+        <v>51.3</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0175</v>
       </c>
       <c r="H25" t="n">
-        <v>71</v>
+        <v>46.2</v>
       </c>
       <c r="I25" t="n">
-        <v>2853.3</v>
+        <v>2834.3</v>
       </c>
       <c r="J25" t="n">
-        <v>2913.28</v>
+        <v>2865.6</v>
       </c>
       <c r="K25" t="n">
-        <v>2928.15</v>
+        <v>2902.5</v>
       </c>
       <c r="L25" t="n">
-        <v>2943.03</v>
+        <v>2939.4</v>
       </c>
       <c r="M25" t="n">
-        <v>2980.45</v>
+        <v>2973.5</v>
       </c>
       <c r="N25" t="n">
-        <v>3017.87</v>
+        <v>3007.6</v>
       </c>
       <c r="O25" t="n">
-        <v>3010.2</v>
+        <v>3047.3</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2653,57 +2653,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2950</v>
+        <v>2992.4</v>
       </c>
       <c r="C26" t="n">
-        <v>2994.6</v>
+        <v>3051.8</v>
       </c>
       <c r="D26" t="n">
-        <v>2948.4</v>
+        <v>2986.1</v>
       </c>
       <c r="E26" t="n">
-        <v>2989.3</v>
+        <v>3044.7</v>
       </c>
       <c r="F26" t="n">
-        <v>51.3</v>
+        <v>55.4</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0185</v>
       </c>
       <c r="H26" t="n">
-        <v>46.2</v>
+        <v>65.7</v>
       </c>
       <c r="I26" t="n">
-        <v>2834.3</v>
+        <v>2902.2</v>
       </c>
       <c r="J26" t="n">
-        <v>2865.6</v>
+        <v>2952</v>
       </c>
       <c r="K26" t="n">
-        <v>2902.5</v>
+        <v>2966.2</v>
       </c>
       <c r="L26" t="n">
-        <v>2939.4</v>
+        <v>2980.4</v>
       </c>
       <c r="M26" t="n">
-        <v>2973.5</v>
+        <v>3012.4</v>
       </c>
       <c r="N26" t="n">
-        <v>3007.6</v>
+        <v>3044.4</v>
       </c>
       <c r="O26" t="n">
-        <v>3047.3</v>
+        <v>3040.8</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2721,73 +2721,73 @@
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W26" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2992.4</v>
+        <v>3049.1</v>
       </c>
       <c r="C27" t="n">
-        <v>3051.8</v>
+        <v>3058.3</v>
       </c>
       <c r="D27" t="n">
-        <v>2986.1</v>
+        <v>3023.3</v>
       </c>
       <c r="E27" t="n">
-        <v>3044.7</v>
+        <v>3025.4</v>
       </c>
       <c r="F27" t="n">
-        <v>55.4</v>
+        <v>-19.3</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0063</v>
       </c>
       <c r="H27" t="n">
-        <v>65.7</v>
+        <v>35</v>
       </c>
       <c r="I27" t="n">
-        <v>2902.2</v>
+        <v>2920.4</v>
       </c>
       <c r="J27" t="n">
-        <v>2952</v>
+        <v>2991.87</v>
       </c>
       <c r="K27" t="n">
-        <v>2966.2</v>
+        <v>3011.85</v>
       </c>
       <c r="L27" t="n">
-        <v>2980.4</v>
+        <v>3031.83</v>
       </c>
       <c r="M27" t="n">
-        <v>3012.4</v>
+        <v>3077.55</v>
       </c>
       <c r="N27" t="n">
-        <v>3044.4</v>
+        <v>3123.27</v>
       </c>
       <c r="O27" t="n">
-        <v>3040.8</v>
+        <v>3117.5</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2798,80 +2798,78 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3049.1</v>
+        <v>3028.5</v>
       </c>
       <c r="C28" t="n">
-        <v>3058.3</v>
+        <v>3041</v>
       </c>
       <c r="D28" t="n">
-        <v>3023.3</v>
+        <v>3004.9</v>
       </c>
       <c r="E28" t="n">
-        <v>3025.4</v>
+        <v>3009.1</v>
       </c>
       <c r="F28" t="n">
-        <v>-19.3</v>
+        <v>-16.3</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0054</v>
       </c>
       <c r="H28" t="n">
-        <v>35</v>
+        <v>36.1</v>
       </c>
       <c r="I28" t="n">
-        <v>2920.4</v>
+        <v>2988.3</v>
       </c>
       <c r="J28" t="n">
-        <v>2991.87</v>
+        <v>2982.7</v>
       </c>
       <c r="K28" t="n">
-        <v>3011.85</v>
+        <v>3007.9</v>
       </c>
       <c r="L28" t="n">
-        <v>3031.83</v>
+        <v>3033.1</v>
       </c>
       <c r="M28" t="n">
-        <v>3077.55</v>
+        <v>3042.9</v>
       </c>
       <c r="N28" t="n">
-        <v>3123.27</v>
+        <v>3052.7</v>
       </c>
       <c r="O28" t="n">
-        <v>3117.5</v>
+        <v>3093.3</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2879,12 +2877,14 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2903,57 +2903,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3028.5</v>
+        <v>3008.5</v>
       </c>
       <c r="C29" t="n">
-        <v>3041</v>
+        <v>3046.8</v>
       </c>
       <c r="D29" t="n">
-        <v>3004.9</v>
+        <v>3002</v>
       </c>
       <c r="E29" t="n">
-        <v>3009.1</v>
+        <v>3041.6</v>
       </c>
       <c r="F29" t="n">
-        <v>-16.3</v>
+        <v>32.5</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0054</v>
+        <v>0.0108</v>
       </c>
       <c r="H29" t="n">
-        <v>36.1</v>
+        <v>44.8</v>
       </c>
       <c r="I29" t="n">
-        <v>2988.3</v>
+        <v>2968.8</v>
       </c>
       <c r="J29" t="n">
-        <v>2982.7</v>
+        <v>2966.08</v>
       </c>
       <c r="K29" t="n">
-        <v>3007.9</v>
+        <v>2991.05</v>
       </c>
       <c r="L29" t="n">
-        <v>3033.1</v>
+        <v>3016.03</v>
       </c>
       <c r="M29" t="n">
-        <v>3042.9</v>
+        <v>3027.15</v>
       </c>
       <c r="N29" t="n">
-        <v>3052.7</v>
+        <v>3038.28</v>
       </c>
       <c r="O29" t="n">
-        <v>3093.3</v>
+        <v>3077.1</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2961,22 +2961,24 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
@@ -2987,57 +2989,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3008.5</v>
+        <v>3038.9</v>
       </c>
       <c r="C30" t="n">
-        <v>3046.8</v>
+        <v>3044.6</v>
       </c>
       <c r="D30" t="n">
-        <v>3002</v>
+        <v>3016</v>
       </c>
       <c r="E30" t="n">
-        <v>3041.6</v>
+        <v>3025</v>
       </c>
       <c r="F30" t="n">
-        <v>32.5</v>
+        <v>-16.6</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0108</v>
+        <v>-0.0055</v>
       </c>
       <c r="H30" t="n">
-        <v>44.8</v>
+        <v>28.6</v>
       </c>
       <c r="I30" t="n">
-        <v>2968.8</v>
+        <v>2957.2</v>
       </c>
       <c r="J30" t="n">
-        <v>2966.08</v>
+        <v>3005.4</v>
       </c>
       <c r="K30" t="n">
-        <v>2991.05</v>
+        <v>3019.2</v>
       </c>
       <c r="L30" t="n">
-        <v>3016.03</v>
+        <v>3033</v>
       </c>
       <c r="M30" t="n">
-        <v>3027.15</v>
+        <v>3064</v>
       </c>
       <c r="N30" t="n">
-        <v>3038.28</v>
+        <v>3095</v>
       </c>
       <c r="O30" t="n">
-        <v>3077.1</v>
+        <v>3091.6</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3045,24 +3047,22 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
@@ -3073,57 +3073,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3038.9</v>
+        <v>3024.7</v>
       </c>
       <c r="C31" t="n">
-        <v>3044.6</v>
+        <v>3045.8</v>
       </c>
       <c r="D31" t="n">
-        <v>3016</v>
+        <v>3019.9</v>
       </c>
       <c r="E31" t="n">
-        <v>3025</v>
+        <v>3035.5</v>
       </c>
       <c r="F31" t="n">
-        <v>-16.6</v>
+        <v>10.5</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0035</v>
       </c>
       <c r="H31" t="n">
-        <v>28.6</v>
+        <v>25.9</v>
       </c>
       <c r="I31" t="n">
-        <v>2957.2</v>
+        <v>2987.4</v>
       </c>
       <c r="J31" t="n">
-        <v>3005.4</v>
+        <v>2993.75</v>
       </c>
       <c r="K31" t="n">
-        <v>3019.2</v>
+        <v>3010.7</v>
       </c>
       <c r="L31" t="n">
-        <v>3033</v>
+        <v>3027.65</v>
       </c>
       <c r="M31" t="n">
-        <v>3064</v>
+        <v>3039.3</v>
       </c>
       <c r="N31" t="n">
-        <v>3095</v>
+        <v>3050.95</v>
       </c>
       <c r="O31" t="n">
-        <v>3091.6</v>
+        <v>3073.2</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3131,19 +3131,19 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
@@ -3155,59 +3155,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3024.7</v>
+        <v>3036.1</v>
       </c>
       <c r="C32" t="n">
-        <v>3045.8</v>
+        <v>3060</v>
       </c>
       <c r="D32" t="n">
-        <v>3019.9</v>
+        <v>3033.1</v>
       </c>
       <c r="E32" t="n">
-        <v>3035.5</v>
+        <v>3052.8</v>
       </c>
       <c r="F32" t="n">
-        <v>10.5</v>
+        <v>17.3</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0057</v>
       </c>
       <c r="H32" t="n">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
       <c r="I32" t="n">
-        <v>2987.4</v>
+        <v>2994</v>
       </c>
       <c r="J32" t="n">
-        <v>2993.75</v>
+        <v>3010.92</v>
       </c>
       <c r="K32" t="n">
-        <v>3010.7</v>
+        <v>3022.55</v>
       </c>
       <c r="L32" t="n">
-        <v>3027.65</v>
+        <v>3034.17</v>
       </c>
       <c r="M32" t="n">
-        <v>3039.3</v>
+        <v>3048.45</v>
       </c>
       <c r="N32" t="n">
-        <v>3050.95</v>
+        <v>3062.73</v>
       </c>
       <c r="O32" t="n">
-        <v>3073.2</v>
+        <v>3071.7</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3244,50 +3240,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3036.1</v>
+        <v>3056.2</v>
       </c>
       <c r="C33" t="n">
-        <v>3060</v>
+        <v>3076.3</v>
       </c>
       <c r="D33" t="n">
-        <v>3033.1</v>
+        <v>3052.5</v>
       </c>
       <c r="E33" t="n">
-        <v>3052.8</v>
+        <v>3060.2</v>
       </c>
       <c r="F33" t="n">
-        <v>17.3</v>
+        <v>7.4</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0024</v>
       </c>
       <c r="H33" t="n">
-        <v>26.9</v>
+        <v>23.8</v>
       </c>
       <c r="I33" t="n">
-        <v>2994</v>
+        <v>3006.2</v>
       </c>
       <c r="J33" t="n">
-        <v>3010.92</v>
+        <v>3029.03</v>
       </c>
       <c r="K33" t="n">
-        <v>3022.55</v>
+        <v>3039.35</v>
       </c>
       <c r="L33" t="n">
-        <v>3034.17</v>
+        <v>3049.68</v>
       </c>
       <c r="M33" t="n">
-        <v>3048.45</v>
+        <v>3066.25</v>
       </c>
       <c r="N33" t="n">
-        <v>3062.73</v>
+        <v>3082.82</v>
       </c>
       <c r="O33" t="n">
-        <v>3071.7</v>
+        <v>3086.9</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3324,50 +3320,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3056.2</v>
+        <v>3062.2</v>
       </c>
       <c r="C34" t="n">
         <v>3076.3</v>
       </c>
       <c r="D34" t="n">
-        <v>3052.5</v>
+        <v>3051.7</v>
       </c>
       <c r="E34" t="n">
-        <v>3060.2</v>
+        <v>3074.9</v>
       </c>
       <c r="F34" t="n">
-        <v>7.4</v>
+        <v>14.7</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0048</v>
       </c>
       <c r="H34" t="n">
-        <v>23.8</v>
+        <v>24.6</v>
       </c>
       <c r="I34" t="n">
-        <v>3006.2</v>
+        <v>3028.7</v>
       </c>
       <c r="J34" t="n">
-        <v>3029.03</v>
+        <v>3034.3</v>
       </c>
       <c r="K34" t="n">
-        <v>3039.35</v>
+        <v>3048.3</v>
       </c>
       <c r="L34" t="n">
-        <v>3049.68</v>
+        <v>3062.3</v>
       </c>
       <c r="M34" t="n">
-        <v>3066.25</v>
+        <v>3072.1</v>
       </c>
       <c r="N34" t="n">
-        <v>3082.82</v>
+        <v>3081.9</v>
       </c>
       <c r="O34" t="n">
-        <v>3086.9</v>
+        <v>3100.1</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3399,55 +3395,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3062.2</v>
+        <v>3073.5</v>
       </c>
       <c r="C35" t="n">
-        <v>3076.3</v>
+        <v>3079.9</v>
       </c>
       <c r="D35" t="n">
-        <v>3051.7</v>
+        <v>3055.9</v>
       </c>
       <c r="E35" t="n">
-        <v>3074.9</v>
+        <v>3064.9</v>
       </c>
       <c r="F35" t="n">
-        <v>14.7</v>
+        <v>-10</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.0033</v>
       </c>
       <c r="H35" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="I35" t="n">
-        <v>3028.7</v>
+        <v>3027.1</v>
       </c>
       <c r="J35" t="n">
-        <v>3034.3</v>
+        <v>3055.75</v>
       </c>
       <c r="K35" t="n">
-        <v>3048.3</v>
+        <v>3062.6</v>
       </c>
       <c r="L35" t="n">
-        <v>3062.3</v>
+        <v>3069.45</v>
       </c>
       <c r="M35" t="n">
-        <v>3072.1</v>
+        <v>3087.2</v>
       </c>
       <c r="N35" t="n">
-        <v>3081.9</v>
+        <v>3104.95</v>
       </c>
       <c r="O35" t="n">
-        <v>3100.1</v>
+        <v>3100.9</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3455,18 +3455,18 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3488,60 +3488,64 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3073.5</v>
+        <v>3063.7</v>
       </c>
       <c r="C36" t="n">
-        <v>3079.9</v>
+        <v>3066.6</v>
       </c>
       <c r="D36" t="n">
-        <v>3055.9</v>
+        <v>3024.1</v>
       </c>
       <c r="E36" t="n">
-        <v>3064.9</v>
+        <v>3026.4</v>
       </c>
       <c r="F36" t="n">
-        <v>-10</v>
+        <v>-38.5</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0126</v>
       </c>
       <c r="H36" t="n">
-        <v>24</v>
+        <v>42.5</v>
       </c>
       <c r="I36" t="n">
-        <v>3027.1</v>
+        <v>3031.9</v>
       </c>
       <c r="J36" t="n">
-        <v>3055.75</v>
+        <v>3039.4</v>
       </c>
       <c r="K36" t="n">
-        <v>3062.6</v>
+        <v>3052.9</v>
       </c>
       <c r="L36" t="n">
-        <v>3069.45</v>
+        <v>3066.4</v>
       </c>
       <c r="M36" t="n">
-        <v>3087.2</v>
+        <v>3076.9</v>
       </c>
       <c r="N36" t="n">
-        <v>3104.95</v>
+        <v>3087.4</v>
       </c>
       <c r="O36" t="n">
-        <v>3100.9</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
+        <v>3103.9</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
@@ -3558,88 +3562,80 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W36" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3063.7</v>
+        <v>3025.9</v>
       </c>
       <c r="C37" t="n">
-        <v>3066.6</v>
+        <v>3059.1</v>
       </c>
       <c r="D37" t="n">
-        <v>3024.1</v>
+        <v>3019.8</v>
       </c>
       <c r="E37" t="n">
-        <v>3026.4</v>
+        <v>3039.9</v>
       </c>
       <c r="F37" t="n">
-        <v>-38.5</v>
+        <v>13.5</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0045</v>
       </c>
       <c r="H37" t="n">
-        <v>42.5</v>
+        <v>39.3</v>
       </c>
       <c r="I37" t="n">
-        <v>3031.9</v>
+        <v>2981.6</v>
       </c>
       <c r="J37" t="n">
-        <v>3039.4</v>
+        <v>2974.42</v>
       </c>
       <c r="K37" t="n">
-        <v>3052.9</v>
+        <v>3005.15</v>
       </c>
       <c r="L37" t="n">
-        <v>3066.4</v>
+        <v>3035.88</v>
       </c>
       <c r="M37" t="n">
-        <v>3076.9</v>
+        <v>3047.65</v>
       </c>
       <c r="N37" t="n">
-        <v>3087.4</v>
+        <v>3059.42</v>
       </c>
       <c r="O37" t="n">
-        <v>3103.9</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q37" s="6" t="inlineStr">
+        <v>3109.1</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
@@ -3651,75 +3647,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3025.9</v>
+        <v>3041.4</v>
       </c>
       <c r="C38" t="n">
-        <v>3059.1</v>
+        <v>3048.5</v>
       </c>
       <c r="D38" t="n">
-        <v>3019.8</v>
+        <v>2993.2</v>
       </c>
       <c r="E38" t="n">
-        <v>3039.9</v>
+        <v>2999.2</v>
       </c>
       <c r="F38" t="n">
-        <v>13.5</v>
+        <v>-40.7</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0134</v>
       </c>
       <c r="H38" t="n">
-        <v>39.3</v>
+        <v>55.3</v>
       </c>
       <c r="I38" t="n">
-        <v>2981.6</v>
+        <v>2980.5</v>
       </c>
       <c r="J38" t="n">
-        <v>2974.42</v>
+        <v>3000.82</v>
       </c>
       <c r="K38" t="n">
-        <v>3005.15</v>
+        <v>3020.25</v>
       </c>
       <c r="L38" t="n">
-        <v>3035.88</v>
+        <v>3039.67</v>
       </c>
       <c r="M38" t="n">
-        <v>3047.65</v>
+        <v>3059.55</v>
       </c>
       <c r="N38" t="n">
-        <v>3059.42</v>
+        <v>3079.42</v>
       </c>
       <c r="O38" t="n">
-        <v>3109.1</v>
+        <v>3098.4</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3731,81 +3733,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3041.4</v>
+        <v>2999.6</v>
       </c>
       <c r="C39" t="n">
-        <v>3048.5</v>
+        <v>3026.7</v>
       </c>
       <c r="D39" t="n">
-        <v>2993.2</v>
+        <v>2997.9</v>
       </c>
       <c r="E39" t="n">
-        <v>2999.2</v>
+        <v>3022.1</v>
       </c>
       <c r="F39" t="n">
-        <v>-40.7</v>
+        <v>22.9</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0134</v>
+        <v>0.0076</v>
       </c>
       <c r="H39" t="n">
-        <v>55.3</v>
+        <v>28.8</v>
       </c>
       <c r="I39" t="n">
-        <v>2980.5</v>
+        <v>2937.9</v>
       </c>
       <c r="J39" t="n">
-        <v>3000.82</v>
+        <v>2933.07</v>
       </c>
       <c r="K39" t="n">
-        <v>3020.25</v>
+        <v>2971.55</v>
       </c>
       <c r="L39" t="n">
-        <v>3039.67</v>
+        <v>3010.02</v>
       </c>
       <c r="M39" t="n">
-        <v>3059.55</v>
+        <v>3026.85</v>
       </c>
       <c r="N39" t="n">
-        <v>3079.42</v>
+        <v>3043.67</v>
       </c>
       <c r="O39" t="n">
-        <v>3098.4</v>
+        <v>3103.8</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3817,75 +3813,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2999.6</v>
+        <v>3023</v>
       </c>
       <c r="C40" t="n">
-        <v>3026.7</v>
+        <v>3028.9</v>
       </c>
       <c r="D40" t="n">
-        <v>2997.9</v>
+        <v>2996</v>
       </c>
       <c r="E40" t="n">
-        <v>3022.1</v>
+        <v>3001.6</v>
       </c>
       <c r="F40" t="n">
-        <v>22.9</v>
+        <v>-20.5</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0076</v>
+        <v>-0.0068</v>
       </c>
       <c r="H40" t="n">
-        <v>28.8</v>
+        <v>32.9</v>
       </c>
       <c r="I40" t="n">
-        <v>2937.9</v>
+        <v>2969.1</v>
       </c>
       <c r="J40" t="n">
-        <v>2933.07</v>
+        <v>2998.2</v>
       </c>
       <c r="K40" t="n">
-        <v>2971.55</v>
+        <v>3007.7</v>
       </c>
       <c r="L40" t="n">
-        <v>3010.02</v>
+        <v>3017.2</v>
       </c>
       <c r="M40" t="n">
-        <v>3026.85</v>
+        <v>3036.5</v>
       </c>
       <c r="N40" t="n">
-        <v>3043.67</v>
+        <v>3055.8</v>
       </c>
       <c r="O40" t="n">
-        <v>3103.8</v>
+        <v>3055.5</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
+      <c r="Q40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3899,79 +3901,77 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3023</v>
+        <v>3004.6</v>
       </c>
       <c r="C41" t="n">
-        <v>3028.9</v>
+        <v>3025.4</v>
       </c>
       <c r="D41" t="n">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="E41" t="n">
-        <v>3001.6</v>
+        <v>3014.4</v>
       </c>
       <c r="F41" t="n">
-        <v>-20.5</v>
+        <v>12.8</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0043</v>
       </c>
       <c r="H41" t="n">
-        <v>32.9</v>
+        <v>28.4</v>
       </c>
       <c r="I41" t="n">
-        <v>2969.1</v>
+        <v>2963.1</v>
       </c>
       <c r="J41" t="n">
-        <v>2998.2</v>
+        <v>2963.28</v>
       </c>
       <c r="K41" t="n">
-        <v>3007.7</v>
+        <v>2985.15</v>
       </c>
       <c r="L41" t="n">
-        <v>3017.2</v>
+        <v>3007.03</v>
       </c>
       <c r="M41" t="n">
-        <v>3036.5</v>
+        <v>3018.05</v>
       </c>
       <c r="N41" t="n">
-        <v>3055.8</v>
+        <v>3029.08</v>
       </c>
       <c r="O41" t="n">
-        <v>3055.5</v>
+        <v>3061.8</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3985,57 +3985,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3004.6</v>
+        <v>3014.6</v>
       </c>
       <c r="C42" t="n">
-        <v>3025.4</v>
+        <v>3020.5</v>
       </c>
       <c r="D42" t="n">
-        <v>2997</v>
+        <v>3002.6</v>
       </c>
       <c r="E42" t="n">
-        <v>3014.4</v>
+        <v>3010.1</v>
       </c>
       <c r="F42" t="n">
-        <v>12.8</v>
+        <v>-4.3</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0014</v>
       </c>
       <c r="H42" t="n">
-        <v>28.4</v>
+        <v>17.9</v>
       </c>
       <c r="I42" t="n">
-        <v>2963.1</v>
+        <v>2968.6</v>
       </c>
       <c r="J42" t="n">
-        <v>2963.28</v>
+        <v>2987.6</v>
       </c>
       <c r="K42" t="n">
-        <v>2985.15</v>
+        <v>3000.2</v>
       </c>
       <c r="L42" t="n">
-        <v>3007.03</v>
+        <v>3012.8</v>
       </c>
       <c r="M42" t="n">
-        <v>3018.05</v>
+        <v>3028.6</v>
       </c>
       <c r="N42" t="n">
-        <v>3029.08</v>
+        <v>3044.4</v>
       </c>
       <c r="O42" t="n">
-        <v>3061.8</v>
+        <v>3053.8</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4046,15 +4046,13 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4069,57 +4067,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3014.6</v>
+        <v>3016.9</v>
       </c>
       <c r="C43" t="n">
-        <v>3020.5</v>
+        <v>3024.2</v>
       </c>
       <c r="D43" t="n">
-        <v>3002.6</v>
+        <v>3002.1</v>
       </c>
       <c r="E43" t="n">
-        <v>3010.1</v>
+        <v>3019</v>
       </c>
       <c r="F43" t="n">
-        <v>-4.3</v>
+        <v>8.9</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0014</v>
+        <v>0.003</v>
       </c>
       <c r="H43" t="n">
-        <v>17.9</v>
+        <v>22.1</v>
       </c>
       <c r="I43" t="n">
-        <v>2968.6</v>
+        <v>2984.7</v>
       </c>
       <c r="J43" t="n">
-        <v>2987.6</v>
+        <v>2991.48</v>
       </c>
       <c r="K43" t="n">
-        <v>3000.2</v>
+        <v>3001.15</v>
       </c>
       <c r="L43" t="n">
-        <v>3012.8</v>
+        <v>3010.83</v>
       </c>
       <c r="M43" t="n">
-        <v>3028.6</v>
+        <v>3019.05</v>
       </c>
       <c r="N43" t="n">
-        <v>3044.4</v>
+        <v>3027.28</v>
       </c>
       <c r="O43" t="n">
-        <v>3053.8</v>
+        <v>3038.4</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4130,13 +4128,15 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4151,77 +4151,81 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3016.9</v>
+        <v>3019.6</v>
       </c>
       <c r="C44" t="n">
-        <v>3024.2</v>
+        <v>3025.5</v>
       </c>
       <c r="D44" t="n">
-        <v>3002.1</v>
+        <v>2976.6</v>
       </c>
       <c r="E44" t="n">
-        <v>3019</v>
+        <v>2977.5</v>
       </c>
       <c r="F44" t="n">
-        <v>8.9</v>
+        <v>-41.5</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0137</v>
       </c>
       <c r="H44" t="n">
-        <v>22.1</v>
+        <v>48.9</v>
       </c>
       <c r="I44" t="n">
-        <v>2984.7</v>
+        <v>2980</v>
       </c>
       <c r="J44" t="n">
-        <v>2991.48</v>
+        <v>2999.83</v>
       </c>
       <c r="K44" t="n">
-        <v>3001.15</v>
+        <v>3007.95</v>
       </c>
       <c r="L44" t="n">
-        <v>3010.83</v>
+        <v>3016.08</v>
       </c>
       <c r="M44" t="n">
-        <v>3019.05</v>
+        <v>3030.05</v>
       </c>
       <c r="N44" t="n">
-        <v>3027.28</v>
+        <v>3044.02</v>
       </c>
       <c r="O44" t="n">
-        <v>3038.4</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
+        <v>3046.3</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
@@ -4235,73 +4239,69 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3019.6</v>
+        <v>2971</v>
       </c>
       <c r="C45" t="n">
-        <v>3025.5</v>
+        <v>2982.5</v>
       </c>
       <c r="D45" t="n">
-        <v>2976.6</v>
+        <v>2946.1</v>
       </c>
       <c r="E45" t="n">
-        <v>2977.5</v>
+        <v>2958.7</v>
       </c>
       <c r="F45" t="n">
-        <v>-41.5</v>
+        <v>-18.8</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0063</v>
       </c>
       <c r="H45" t="n">
-        <v>48.9</v>
+        <v>36.4</v>
       </c>
       <c r="I45" t="n">
-        <v>2980</v>
+        <v>2927.7</v>
       </c>
       <c r="J45" t="n">
-        <v>2999.83</v>
+        <v>2916.83</v>
       </c>
       <c r="K45" t="n">
-        <v>3007.95</v>
+        <v>2953.05</v>
       </c>
       <c r="L45" t="n">
-        <v>3016.08</v>
+        <v>2989.28</v>
       </c>
       <c r="M45" t="n">
-        <v>3030.05</v>
+        <v>3001.95</v>
       </c>
       <c r="N45" t="n">
-        <v>3044.02</v>
+        <v>3014.62</v>
       </c>
       <c r="O45" t="n">
-        <v>3046.3</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
+        <v>3074.4</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4321,69 +4321,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2971</v>
+        <v>2958</v>
       </c>
       <c r="C46" t="n">
-        <v>2982.5</v>
+        <v>2964.6</v>
       </c>
       <c r="D46" t="n">
-        <v>2946.1</v>
+        <v>2918.9</v>
       </c>
       <c r="E46" t="n">
-        <v>2958.7</v>
+        <v>2924.7</v>
       </c>
       <c r="F46" t="n">
-        <v>-18.8</v>
+        <v>-34</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0115</v>
       </c>
       <c r="H46" t="n">
-        <v>36.4</v>
+        <v>45.7</v>
       </c>
       <c r="I46" t="n">
-        <v>2927.7</v>
+        <v>2909.7</v>
       </c>
       <c r="J46" t="n">
-        <v>2916.83</v>
+        <v>2919.5</v>
       </c>
       <c r="K46" t="n">
-        <v>2953.05</v>
+        <v>2940.5</v>
       </c>
       <c r="L46" t="n">
-        <v>2989.28</v>
+        <v>2961.5</v>
       </c>
       <c r="M46" t="n">
-        <v>3001.95</v>
+        <v>2976.9</v>
       </c>
       <c r="N46" t="n">
-        <v>3014.62</v>
+        <v>2992.3</v>
       </c>
       <c r="O46" t="n">
-        <v>3074.4</v>
+        <v>3018.9</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
@@ -4410,75 +4408,75 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2958</v>
+        <v>2926.4</v>
       </c>
       <c r="C47" t="n">
-        <v>2964.6</v>
+        <v>2962.5</v>
       </c>
       <c r="D47" t="n">
-        <v>2918.9</v>
+        <v>2914.5</v>
       </c>
       <c r="E47" t="n">
-        <v>2924.7</v>
+        <v>2958.8</v>
       </c>
       <c r="F47" t="n">
-        <v>-34</v>
+        <v>34.1</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0.0117</v>
       </c>
       <c r="H47" t="n">
-        <v>45.7</v>
+        <v>48</v>
       </c>
       <c r="I47" t="n">
-        <v>2909.7</v>
+        <v>2873.2</v>
       </c>
       <c r="J47" t="n">
-        <v>2919.5</v>
+        <v>2870.47</v>
       </c>
       <c r="K47" t="n">
-        <v>2940.5</v>
+        <v>2901.85</v>
       </c>
       <c r="L47" t="n">
-        <v>2961.5</v>
+        <v>2933.22</v>
       </c>
       <c r="M47" t="n">
-        <v>2976.9</v>
+        <v>2947.55</v>
       </c>
       <c r="N47" t="n">
-        <v>2992.3</v>
+        <v>2961.88</v>
       </c>
       <c r="O47" t="n">
-        <v>3018.9</v>
+        <v>3010.3</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
@@ -4487,55 +4485,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2926.4</v>
+        <v>2957.6</v>
       </c>
       <c r="C48" t="n">
-        <v>2962.5</v>
+        <v>2983.3</v>
       </c>
       <c r="D48" t="n">
-        <v>2914.5</v>
+        <v>2949.9</v>
       </c>
       <c r="E48" t="n">
-        <v>2958.8</v>
+        <v>2969.7</v>
       </c>
       <c r="F48" t="n">
-        <v>34.1</v>
+        <v>10.9</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0117</v>
+        <v>0.0037</v>
       </c>
       <c r="H48" t="n">
-        <v>48</v>
+        <v>33.4</v>
       </c>
       <c r="I48" t="n">
-        <v>2873.2</v>
+        <v>2866.5</v>
       </c>
       <c r="J48" t="n">
-        <v>2870.47</v>
+        <v>2920.95</v>
       </c>
       <c r="K48" t="n">
-        <v>2901.85</v>
+        <v>2934.8</v>
       </c>
       <c r="L48" t="n">
-        <v>2933.22</v>
+        <v>2948.65</v>
       </c>
       <c r="M48" t="n">
-        <v>2947.55</v>
+        <v>2982.8</v>
       </c>
       <c r="N48" t="n">
-        <v>2961.88</v>
+        <v>3016.95</v>
       </c>
       <c r="O48" t="n">
-        <v>3010.3</v>
+        <v>3010.5</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4553,14 +4555,12 @@
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
@@ -4571,57 +4571,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2957.6</v>
+        <v>2967.9</v>
       </c>
       <c r="C49" t="n">
-        <v>2983.3</v>
+        <v>2979.3</v>
       </c>
       <c r="D49" t="n">
-        <v>2949.9</v>
+        <v>2949.5</v>
       </c>
       <c r="E49" t="n">
-        <v>2969.7</v>
+        <v>2976.6</v>
       </c>
       <c r="F49" t="n">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0023</v>
       </c>
       <c r="H49" t="n">
-        <v>33.4</v>
+        <v>29.8</v>
       </c>
       <c r="I49" t="n">
-        <v>2866.5</v>
+        <v>2916.5</v>
       </c>
       <c r="J49" t="n">
-        <v>2920.95</v>
+        <v>2937.85</v>
       </c>
       <c r="K49" t="n">
-        <v>2934.8</v>
+        <v>2953</v>
       </c>
       <c r="L49" t="n">
-        <v>2948.65</v>
+        <v>2968.15</v>
       </c>
       <c r="M49" t="n">
-        <v>2982.8</v>
+        <v>2986.4</v>
       </c>
       <c r="N49" t="n">
-        <v>3016.95</v>
+        <v>3004.65</v>
       </c>
       <c r="O49" t="n">
-        <v>3010.5</v>
+        <v>3016.7</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4629,18 +4629,18 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4655,57 +4655,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2967.9</v>
+        <v>2974.7</v>
       </c>
       <c r="C50" t="n">
-        <v>2979.3</v>
+        <v>2977.9</v>
       </c>
       <c r="D50" t="n">
-        <v>2949.5</v>
+        <v>2954.7</v>
       </c>
       <c r="E50" t="n">
-        <v>2976.6</v>
+        <v>2963.6</v>
       </c>
       <c r="F50" t="n">
-        <v>6.9</v>
+        <v>-13</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0044</v>
       </c>
       <c r="H50" t="n">
-        <v>29.8</v>
+        <v>23.2</v>
       </c>
       <c r="I50" t="n">
-        <v>2916.5</v>
+        <v>2919.7</v>
       </c>
       <c r="J50" t="n">
-        <v>2937.85</v>
+        <v>2952.9</v>
       </c>
       <c r="K50" t="n">
-        <v>2953</v>
+        <v>2961.7</v>
       </c>
       <c r="L50" t="n">
-        <v>2968.15</v>
+        <v>2970.5</v>
       </c>
       <c r="M50" t="n">
-        <v>2986.4</v>
+        <v>2991.5</v>
       </c>
       <c r="N50" t="n">
-        <v>3004.65</v>
+        <v>3012.5</v>
       </c>
       <c r="O50" t="n">
-        <v>3016.7</v>
+        <v>3009.1</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4715,12 +4715,12 @@
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4746,60 +4746,64 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2974.7</v>
+        <v>2963.1</v>
       </c>
       <c r="C51" t="n">
-        <v>2977.9</v>
+        <v>2966.2</v>
       </c>
       <c r="D51" t="n">
-        <v>2954.7</v>
+        <v>2919.4</v>
       </c>
       <c r="E51" t="n">
-        <v>2963.6</v>
+        <v>2923</v>
       </c>
       <c r="F51" t="n">
-        <v>-13</v>
+        <v>-40.6</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0137</v>
       </c>
       <c r="H51" t="n">
-        <v>23.2</v>
+        <v>46.8</v>
       </c>
       <c r="I51" t="n">
-        <v>2919.7</v>
+        <v>2931.5</v>
       </c>
       <c r="J51" t="n">
-        <v>2952.9</v>
+        <v>2939.05</v>
       </c>
       <c r="K51" t="n">
-        <v>2961.7</v>
+        <v>2952</v>
       </c>
       <c r="L51" t="n">
-        <v>2970.5</v>
+        <v>2964.95</v>
       </c>
       <c r="M51" t="n">
-        <v>2991.5</v>
+        <v>2975.2</v>
       </c>
       <c r="N51" t="n">
-        <v>3012.5</v>
+        <v>2985.45</v>
       </c>
       <c r="O51" t="n">
-        <v>3009.1</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
+        <v>3001.1</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
@@ -4821,73 +4825,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2963.1</v>
+        <v>2923.1</v>
       </c>
       <c r="C52" t="n">
-        <v>2966.2</v>
+        <v>2933.8</v>
       </c>
       <c r="D52" t="n">
-        <v>2919.4</v>
+        <v>2887.8</v>
       </c>
       <c r="E52" t="n">
-        <v>2923</v>
+        <v>2893.4</v>
       </c>
       <c r="F52" t="n">
-        <v>-40.6</v>
+        <v>-29.6</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0101</v>
       </c>
       <c r="H52" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="I52" t="n">
-        <v>2931.5</v>
+        <v>2872.6</v>
       </c>
       <c r="J52" t="n">
-        <v>2939.05</v>
+        <v>2866.3</v>
       </c>
       <c r="K52" t="n">
-        <v>2952</v>
+        <v>2899.6</v>
       </c>
       <c r="L52" t="n">
-        <v>2964.95</v>
+        <v>2932.9</v>
       </c>
       <c r="M52" t="n">
-        <v>2975.2</v>
+        <v>2946.4</v>
       </c>
       <c r="N52" t="n">
-        <v>2985.45</v>
+        <v>2959.9</v>
       </c>
       <c r="O52" t="n">
-        <v>3001.1</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
+        <v>3013</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
@@ -4914,50 +4910,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2923.1</v>
+        <v>2890.9</v>
       </c>
       <c r="C53" t="n">
-        <v>2933.8</v>
+        <v>2929.8</v>
       </c>
       <c r="D53" t="n">
-        <v>2887.8</v>
+        <v>2887.6</v>
       </c>
       <c r="E53" t="n">
-        <v>2893.4</v>
+        <v>2904.5</v>
       </c>
       <c r="F53" t="n">
-        <v>-29.6</v>
+        <v>11.1</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0101</v>
+        <v>0.0038</v>
       </c>
       <c r="H53" t="n">
-        <v>46</v>
+        <v>42.2</v>
       </c>
       <c r="I53" t="n">
-        <v>2872.6</v>
+        <v>2841.8</v>
       </c>
       <c r="J53" t="n">
-        <v>2866.3</v>
+        <v>2838.7</v>
       </c>
       <c r="K53" t="n">
-        <v>2899.6</v>
+        <v>2870.4</v>
       </c>
       <c r="L53" t="n">
-        <v>2932.9</v>
+        <v>2902.1</v>
       </c>
       <c r="M53" t="n">
-        <v>2946.4</v>
+        <v>2916.4</v>
       </c>
       <c r="N53" t="n">
-        <v>2959.9</v>
+        <v>2930.7</v>
       </c>
       <c r="O53" t="n">
-        <v>3013</v>
+        <v>2979.8</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4965,18 +4961,18 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4989,55 +4985,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2890.9</v>
+        <v>2892.7</v>
       </c>
       <c r="C54" t="n">
-        <v>2929.8</v>
+        <v>2913.5</v>
       </c>
       <c r="D54" t="n">
-        <v>2887.6</v>
+        <v>2884.3</v>
       </c>
       <c r="E54" t="n">
-        <v>2904.5</v>
+        <v>2894.1</v>
       </c>
       <c r="F54" t="n">
-        <v>11.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0036</v>
       </c>
       <c r="H54" t="n">
-        <v>42.2</v>
+        <v>29.2</v>
       </c>
       <c r="I54" t="n">
-        <v>2841.8</v>
+        <v>2845.4</v>
       </c>
       <c r="J54" t="n">
-        <v>2838.7</v>
+        <v>2860.2</v>
       </c>
       <c r="K54" t="n">
-        <v>2870.4</v>
+        <v>2883.4</v>
       </c>
       <c r="L54" t="n">
-        <v>2902.1</v>
+        <v>2906.6</v>
       </c>
       <c r="M54" t="n">
-        <v>2916.4</v>
+        <v>2925.6</v>
       </c>
       <c r="N54" t="n">
-        <v>2930.7</v>
+        <v>2944.6</v>
       </c>
       <c r="O54" t="n">
-        <v>2979.8</v>
+        <v>2972</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5045,18 +5045,18 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5069,59 +5069,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2892.7</v>
+        <v>2896.4</v>
       </c>
       <c r="C55" t="n">
-        <v>2913.5</v>
+        <v>2896.5</v>
       </c>
       <c r="D55" t="n">
-        <v>2884.3</v>
+        <v>2862.7</v>
       </c>
       <c r="E55" t="n">
-        <v>2894.1</v>
+        <v>2873.1</v>
       </c>
       <c r="F55" t="n">
-        <v>-10.4</v>
+        <v>-21</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0073</v>
       </c>
       <c r="H55" t="n">
-        <v>29.2</v>
+        <v>33.8</v>
       </c>
       <c r="I55" t="n">
-        <v>2845.4</v>
+        <v>2855.1</v>
       </c>
       <c r="J55" t="n">
-        <v>2860.2</v>
+        <v>2862.5</v>
       </c>
       <c r="K55" t="n">
-        <v>2883.4</v>
+        <v>2879.5</v>
       </c>
       <c r="L55" t="n">
-        <v>2906.6</v>
+        <v>2896.5</v>
       </c>
       <c r="M55" t="n">
-        <v>2925.6</v>
+        <v>2908.7</v>
       </c>
       <c r="N55" t="n">
-        <v>2944.6</v>
+        <v>2920.9</v>
       </c>
       <c r="O55" t="n">
-        <v>2972</v>
+        <v>2942.7</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5158,56 +5154,58 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2896.4</v>
+        <v>2875.1</v>
       </c>
       <c r="C56" t="n">
-        <v>2896.5</v>
+        <v>2892.5</v>
       </c>
       <c r="D56" t="n">
-        <v>2862.7</v>
+        <v>2831.9</v>
       </c>
       <c r="E56" t="n">
-        <v>2873.1</v>
+        <v>2861.7</v>
       </c>
       <c r="F56" t="n">
-        <v>-21</v>
+        <v>-11.4</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.004</v>
       </c>
       <c r="H56" t="n">
-        <v>33.8</v>
+        <v>60.6</v>
       </c>
       <c r="I56" t="n">
-        <v>2855.1</v>
+        <v>2828.9</v>
       </c>
       <c r="J56" t="n">
-        <v>2862.5</v>
+        <v>2836.05</v>
       </c>
       <c r="K56" t="n">
-        <v>2879.5</v>
+        <v>2856.2</v>
       </c>
       <c r="L56" t="n">
-        <v>2896.5</v>
+        <v>2876.35</v>
       </c>
       <c r="M56" t="n">
-        <v>2908.7</v>
+        <v>2890</v>
       </c>
       <c r="N56" t="n">
-        <v>2920.9</v>
+        <v>2903.65</v>
       </c>
       <c r="O56" t="n">
-        <v>2942.7</v>
+        <v>2930.3</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
@@ -5219,8 +5217,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5238,74 +5238,70 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2875.1</v>
+        <v>2861.2</v>
       </c>
       <c r="C57" t="n">
-        <v>2892.5</v>
+        <v>2904.6</v>
       </c>
       <c r="D57" t="n">
-        <v>2831.9</v>
+        <v>2859.3</v>
       </c>
       <c r="E57" t="n">
-        <v>2861.7</v>
+        <v>2875.9</v>
       </c>
       <c r="F57" t="n">
-        <v>-11.4</v>
+        <v>14.2</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.005</v>
       </c>
       <c r="H57" t="n">
-        <v>60.6</v>
+        <v>45.3</v>
       </c>
       <c r="I57" t="n">
-        <v>2828.9</v>
+        <v>2771.3</v>
       </c>
       <c r="J57" t="n">
-        <v>2836.05</v>
+        <v>2800.85</v>
       </c>
       <c r="K57" t="n">
-        <v>2856.2</v>
+        <v>2831.4</v>
       </c>
       <c r="L57" t="n">
-        <v>2876.35</v>
+        <v>2861.95</v>
       </c>
       <c r="M57" t="n">
-        <v>2890</v>
+        <v>2892</v>
       </c>
       <c r="N57" t="n">
-        <v>2903.65</v>
+        <v>2922.05</v>
       </c>
       <c r="O57" t="n">
-        <v>2930.3</v>
+        <v>2953.1</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
@@ -5317,55 +5313,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2861.2</v>
+        <v>2870.5</v>
       </c>
       <c r="C58" t="n">
-        <v>2904.6</v>
+        <v>2883</v>
       </c>
       <c r="D58" t="n">
-        <v>2859.3</v>
+        <v>2856.9</v>
       </c>
       <c r="E58" t="n">
-        <v>2875.9</v>
+        <v>2873.23</v>
       </c>
       <c r="F58" t="n">
-        <v>14.2</v>
+        <v>-2.67</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0009</v>
       </c>
       <c r="H58" t="n">
-        <v>45.3</v>
+        <v>26.1</v>
       </c>
       <c r="I58" t="n">
-        <v>2771.3</v>
+        <v>2814</v>
       </c>
       <c r="J58" t="n">
-        <v>2800.85</v>
+        <v>2827.57</v>
       </c>
       <c r="K58" t="n">
-        <v>2831.4</v>
+        <v>2853.25</v>
       </c>
       <c r="L58" t="n">
-        <v>2861.95</v>
+        <v>2878.92</v>
       </c>
       <c r="M58" t="n">
-        <v>2892</v>
+        <v>2898.55</v>
       </c>
       <c r="N58" t="n">
-        <v>2922.05</v>
+        <v>2918.17</v>
       </c>
       <c r="O58" t="n">
-        <v>2953.1</v>
+        <v>2949.9</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5376,15 +5376,13 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5397,59 +5395,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2870.5</v>
+        <v>2879.5</v>
       </c>
       <c r="C59" t="n">
-        <v>2883</v>
+        <v>2907.3</v>
       </c>
       <c r="D59" t="n">
-        <v>2856.9</v>
+        <v>2876.6</v>
       </c>
       <c r="E59" t="n">
-        <v>2873.23</v>
+        <v>2897.4</v>
       </c>
       <c r="F59" t="n">
-        <v>-2.67</v>
+        <v>24.17</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>26.1</v>
+        <v>30.7</v>
       </c>
       <c r="I59" t="n">
-        <v>2814</v>
+        <v>2830.8</v>
       </c>
       <c r="J59" t="n">
-        <v>2827.57</v>
+        <v>2848.77</v>
       </c>
       <c r="K59" t="n">
-        <v>2853.25</v>
+        <v>2860.18</v>
       </c>
       <c r="L59" t="n">
-        <v>2878.92</v>
+        <v>2871.59</v>
       </c>
       <c r="M59" t="n">
-        <v>2898.55</v>
+        <v>2886.28</v>
       </c>
       <c r="N59" t="n">
-        <v>2918.17</v>
+        <v>2900.97</v>
       </c>
       <c r="O59" t="n">
-        <v>2949.9</v>
+        <v>2909.1</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5460,16 +5454,20 @@
       <c r="R59" s="6" t="n">
         <v/>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
@@ -5479,55 +5477,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2879.5</v>
+        <v>2897.8</v>
       </c>
       <c r="C60" t="n">
-        <v>2907.3</v>
+        <v>2931.2</v>
       </c>
       <c r="D60" t="n">
-        <v>2876.6</v>
+        <v>2884.2</v>
       </c>
       <c r="E60" t="n">
-        <v>2897.4</v>
+        <v>2914.1</v>
       </c>
       <c r="F60" t="n">
-        <v>24.17</v>
+        <v>16.7</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0058</v>
       </c>
       <c r="H60" t="n">
-        <v>30.7</v>
+        <v>47</v>
       </c>
       <c r="I60" t="n">
-        <v>2830.8</v>
+        <v>2845.9</v>
       </c>
       <c r="J60" t="n">
-        <v>2848.77</v>
+        <v>2869.42</v>
       </c>
       <c r="K60" t="n">
-        <v>2860.18</v>
+        <v>2882.05</v>
       </c>
       <c r="L60" t="n">
-        <v>2871.59</v>
+        <v>2894.67</v>
       </c>
       <c r="M60" t="n">
-        <v>2886.28</v>
+        <v>2912.75</v>
       </c>
       <c r="N60" t="n">
-        <v>2900.97</v>
+        <v>2930.82</v>
       </c>
       <c r="O60" t="n">
-        <v>2909.1</v>
+        <v>2938</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5545,12 +5547,12 @@
       </c>
       <c r="T60" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="V60" s="8" t="n">
@@ -5570,75 +5572,75 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2897.8</v>
+        <v>2912</v>
       </c>
       <c r="C61" t="n">
-        <v>2931.2</v>
+        <v>2915.3</v>
       </c>
       <c r="D61" t="n">
-        <v>2884.2</v>
+        <v>2858.8</v>
       </c>
       <c r="E61" t="n">
-        <v>2914.1</v>
+        <v>2860.2</v>
       </c>
       <c r="F61" t="n">
-        <v>16.7</v>
+        <v>-53.9</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0185</v>
       </c>
       <c r="H61" t="n">
-        <v>47</v>
+        <v>56.5</v>
       </c>
       <c r="I61" t="n">
-        <v>2845.9</v>
+        <v>2837.2</v>
       </c>
       <c r="J61" t="n">
-        <v>2869.42</v>
+        <v>2870.3</v>
       </c>
       <c r="K61" t="n">
-        <v>2882.05</v>
+        <v>2890.6</v>
       </c>
       <c r="L61" t="n">
-        <v>2894.67</v>
+        <v>2910.9</v>
       </c>
       <c r="M61" t="n">
-        <v>2912.75</v>
+        <v>2937.6</v>
       </c>
       <c r="N61" t="n">
-        <v>2930.82</v>
+        <v>2964.3</v>
       </c>
       <c r="O61" t="n">
-        <v>2938</v>
+        <v>2978.2</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
+      <c r="Q61" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U61" s="8" t="inlineStr">
+      <c r="R61" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
@@ -5647,76 +5649,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2860.7</v>
+        <v>2854.4</v>
       </c>
       <c r="C62" t="n">
-        <v>2862</v>
+        <v>2855.9</v>
       </c>
       <c r="D62" t="n">
-        <v>2859.8</v>
+        <v>2853.2</v>
       </c>
       <c r="E62" t="n">
-        <v>2861</v>
+        <v>2853.2</v>
       </c>
       <c r="F62" t="n">
-        <v>-53.1</v>
+        <v>-7</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0182</v>
+        <v>-0.0024</v>
       </c>
       <c r="H62" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="I62" t="n">
-        <v>2837.2</v>
+        <v>2802.3</v>
       </c>
       <c r="J62" t="n">
-        <v>2870.3</v>
+        <v>2790.27</v>
       </c>
       <c r="K62" t="n">
-        <v>2890.6</v>
+        <v>2831.95</v>
       </c>
       <c r="L62" t="n">
-        <v>2910.9</v>
+        <v>2873.62</v>
       </c>
       <c r="M62" t="n">
-        <v>2937.6</v>
+        <v>2888.45</v>
       </c>
       <c r="N62" t="n">
-        <v>2964.3</v>
+        <v>2903.27</v>
       </c>
       <c r="O62" t="n">
-        <v>2978.2</v>
+        <v>2971.8</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3026.1</v>
+        <v>3040</v>
       </c>
       <c r="C2" t="n">
-        <v>3050.6</v>
+        <v>3068.4</v>
       </c>
       <c r="D2" t="n">
-        <v>3015.1</v>
+        <v>3023.7</v>
       </c>
       <c r="E2" t="n">
-        <v>3045.6</v>
+        <v>3035.1</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>-10.5</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.0034</v>
       </c>
       <c r="H2" t="n">
-        <v>35.5</v>
+        <v>44.7</v>
       </c>
       <c r="I2" t="n">
-        <v>2930.7</v>
+        <v>2979.6</v>
       </c>
       <c r="J2" t="n">
-        <v>2980.63</v>
+        <v>3016.48</v>
       </c>
       <c r="K2" t="n">
-        <v>3002.05</v>
+        <v>3027.85</v>
       </c>
       <c r="L2" t="n">
-        <v>3023.48</v>
+        <v>3039.23</v>
       </c>
       <c r="M2" t="n">
-        <v>3059.15</v>
+        <v>3063.35</v>
       </c>
       <c r="N2" t="n">
-        <v>3094.83</v>
+        <v>3087.48</v>
       </c>
       <c r="O2" t="n">
-        <v>3102</v>
+        <v>3086.1</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,17 +685,19 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U2" s="8" t="n">
@@ -709,55 +711,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3040</v>
+        <v>3030.9</v>
       </c>
       <c r="C3" t="n">
-        <v>3068.4</v>
+        <v>3062.4</v>
       </c>
       <c r="D3" t="n">
-        <v>3023.7</v>
+        <v>2988.5</v>
       </c>
       <c r="E3" t="n">
-        <v>3035.1</v>
+        <v>3014.2</v>
       </c>
       <c r="F3" t="n">
-        <v>-10.5</v>
+        <v>-20.9</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0069</v>
       </c>
       <c r="H3" t="n">
-        <v>44.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>2979.6</v>
+        <v>2979</v>
       </c>
       <c r="J3" t="n">
-        <v>3016.48</v>
+        <v>2984.93</v>
       </c>
       <c r="K3" t="n">
-        <v>3027.85</v>
+        <v>3012.75</v>
       </c>
       <c r="L3" t="n">
-        <v>3039.23</v>
+        <v>3040.58</v>
       </c>
       <c r="M3" t="n">
-        <v>3063.35</v>
+        <v>3057.45</v>
       </c>
       <c r="N3" t="n">
-        <v>3087.48</v>
+        <v>3074.33</v>
       </c>
       <c r="O3" t="n">
-        <v>3086.1</v>
+        <v>3113.1</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -767,19 +773,19 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
@@ -793,57 +799,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3030.9</v>
+        <v>3019.7</v>
       </c>
       <c r="C4" t="n">
-        <v>3062.4</v>
+        <v>3042.1</v>
       </c>
       <c r="D4" t="n">
-        <v>2988.5</v>
+        <v>3006.7</v>
       </c>
       <c r="E4" t="n">
-        <v>3014.2</v>
+        <v>3027</v>
       </c>
       <c r="F4" t="n">
-        <v>-20.9</v>
+        <v>12.8</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0042</v>
       </c>
       <c r="H4" t="n">
-        <v>73.90000000000001</v>
+        <v>35.4</v>
       </c>
       <c r="I4" t="n">
-        <v>2979</v>
+        <v>2914.6</v>
       </c>
       <c r="J4" t="n">
-        <v>2984.93</v>
+        <v>2934.68</v>
       </c>
       <c r="K4" t="n">
-        <v>3012.75</v>
+        <v>2977.25</v>
       </c>
       <c r="L4" t="n">
-        <v>3040.58</v>
+        <v>3019.82</v>
       </c>
       <c r="M4" t="n">
-        <v>3057.45</v>
+        <v>3051.15</v>
       </c>
       <c r="N4" t="n">
-        <v>3074.33</v>
+        <v>3082.47</v>
       </c>
       <c r="O4" t="n">
-        <v>3113.1</v>
+        <v>3136.3</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -851,20 +857,16 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R4" s="6" t="n">
+        <v/>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -879,70 +881,74 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3019.7</v>
+        <v>3033.4</v>
       </c>
       <c r="C5" t="n">
-        <v>3042.1</v>
+        <v>3042.6</v>
       </c>
       <c r="D5" t="n">
-        <v>3006.7</v>
+        <v>2988.8</v>
       </c>
       <c r="E5" t="n">
-        <v>3027</v>
+        <v>2998.8</v>
       </c>
       <c r="F5" t="n">
-        <v>12.8</v>
+        <v>-28.2</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>35.4</v>
+        <v>53.8</v>
       </c>
       <c r="I5" t="n">
-        <v>2914.6</v>
+        <v>2971.3</v>
       </c>
       <c r="J5" t="n">
-        <v>2934.68</v>
+        <v>2992.9</v>
       </c>
       <c r="K5" t="n">
-        <v>2977.25</v>
+        <v>3009.3</v>
       </c>
       <c r="L5" t="n">
-        <v>3019.82</v>
+        <v>3025.7</v>
       </c>
       <c r="M5" t="n">
-        <v>3051.15</v>
+        <v>3044.7</v>
       </c>
       <c r="N5" t="n">
-        <v>3082.47</v>
+        <v>3063.7</v>
       </c>
       <c r="O5" t="n">
-        <v>3136.3</v>
+        <v>3077.5</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -961,72 +967,70 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3033.4</v>
+        <v>2994.3</v>
       </c>
       <c r="C6" t="n">
-        <v>3042.6</v>
+        <v>3004.3</v>
       </c>
       <c r="D6" t="n">
-        <v>2988.8</v>
+        <v>2943.4</v>
       </c>
       <c r="E6" t="n">
-        <v>2998.8</v>
+        <v>2971.5</v>
       </c>
       <c r="F6" t="n">
-        <v>-28.2</v>
+        <v>-27.3</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0091</v>
       </c>
       <c r="H6" t="n">
-        <v>53.8</v>
+        <v>60.9</v>
       </c>
       <c r="I6" t="n">
-        <v>2971.3</v>
+        <v>2935</v>
       </c>
       <c r="J6" t="n">
-        <v>2992.9</v>
+        <v>2936.55</v>
       </c>
       <c r="K6" t="n">
-        <v>3009.3</v>
+        <v>2971.9</v>
       </c>
       <c r="L6" t="n">
+        <v>3007.25</v>
+      </c>
+      <c r="M6" t="n">
         <v>3025.7</v>
       </c>
-      <c r="M6" t="n">
-        <v>3044.7</v>
-      </c>
       <c r="N6" t="n">
-        <v>3063.7</v>
+        <v>3044.15</v>
       </c>
       <c r="O6" t="n">
-        <v>3077.5</v>
+        <v>3096.4</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1047,57 +1051,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2994.3</v>
+        <v>2965.8</v>
       </c>
       <c r="C7" t="n">
-        <v>3004.3</v>
+        <v>3014.9</v>
       </c>
       <c r="D7" t="n">
-        <v>2943.4</v>
+        <v>2964.3</v>
       </c>
       <c r="E7" t="n">
-        <v>2971.5</v>
+        <v>3008.4</v>
       </c>
       <c r="F7" t="n">
-        <v>-27.3</v>
+        <v>36.9</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0091</v>
+        <v>0.0124</v>
       </c>
       <c r="H7" t="n">
-        <v>60.9</v>
+        <v>50.6</v>
       </c>
       <c r="I7" t="n">
-        <v>2935</v>
+        <v>2882.5</v>
       </c>
       <c r="J7" t="n">
-        <v>2936.55</v>
+        <v>2909.42</v>
       </c>
       <c r="K7" t="n">
-        <v>2971.9</v>
+        <v>2941.05</v>
       </c>
       <c r="L7" t="n">
-        <v>3007.25</v>
+        <v>2972.67</v>
       </c>
       <c r="M7" t="n">
-        <v>3025.7</v>
+        <v>3001.95</v>
       </c>
       <c r="N7" t="n">
-        <v>3044.15</v>
+        <v>3031.23</v>
       </c>
       <c r="O7" t="n">
-        <v>3096.4</v>
+        <v>3065.2</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1105,19 +1109,19 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1129,59 +1133,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2965.8</v>
+        <v>3008.1</v>
       </c>
       <c r="C8" t="n">
-        <v>3014.9</v>
+        <v>3019.5</v>
       </c>
       <c r="D8" t="n">
-        <v>2964.3</v>
+        <v>2970.8</v>
       </c>
       <c r="E8" t="n">
-        <v>3008.4</v>
+        <v>2994</v>
       </c>
       <c r="F8" t="n">
-        <v>36.9</v>
+        <v>-14.4</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0048</v>
       </c>
       <c r="H8" t="n">
-        <v>50.6</v>
+        <v>48.7</v>
       </c>
       <c r="I8" t="n">
-        <v>2882.5</v>
+        <v>2913.7</v>
       </c>
       <c r="J8" t="n">
-        <v>2909.42</v>
+        <v>2967.2</v>
       </c>
       <c r="K8" t="n">
-        <v>2941.05</v>
+        <v>2983.1</v>
       </c>
       <c r="L8" t="n">
-        <v>2972.67</v>
+        <v>2999</v>
       </c>
       <c r="M8" t="n">
-        <v>3001.95</v>
+        <v>3033.7</v>
       </c>
       <c r="N8" t="n">
-        <v>3031.23</v>
+        <v>3068.4</v>
       </c>
       <c r="O8" t="n">
-        <v>3065.2</v>
+        <v>3065.5</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1189,18 +1189,18 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1213,55 +1213,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3008.1</v>
+        <v>2984.7</v>
       </c>
       <c r="C9" t="n">
-        <v>3019.5</v>
+        <v>2995.8</v>
       </c>
       <c r="D9" t="n">
-        <v>2970.8</v>
+        <v>2961.8</v>
       </c>
       <c r="E9" t="n">
-        <v>2994</v>
+        <v>2970.4</v>
       </c>
       <c r="F9" t="n">
-        <v>-14.4</v>
+        <v>-23.6</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>48.7</v>
+        <v>34</v>
       </c>
       <c r="I9" t="n">
-        <v>2913.7</v>
+        <v>2922.1</v>
       </c>
       <c r="J9" t="n">
-        <v>2967.2</v>
+        <v>2944.73</v>
       </c>
       <c r="K9" t="n">
-        <v>2983.1</v>
+        <v>2969.65</v>
       </c>
       <c r="L9" t="n">
-        <v>2999</v>
+        <v>2994.58</v>
       </c>
       <c r="M9" t="n">
-        <v>3033.7</v>
+        <v>3018.35</v>
       </c>
       <c r="N9" t="n">
-        <v>3068.4</v>
+        <v>3042.12</v>
       </c>
       <c r="O9" t="n">
-        <v>3065.5</v>
+        <v>3068.2</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1271,12 +1275,12 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1295,57 +1299,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2984.7</v>
+        <v>2967.2</v>
       </c>
       <c r="C10" t="n">
-        <v>2995.8</v>
+        <v>3029.8</v>
       </c>
       <c r="D10" t="n">
-        <v>2961.8</v>
+        <v>2956.2</v>
       </c>
       <c r="E10" t="n">
-        <v>2970.4</v>
+        <v>2979.9</v>
       </c>
       <c r="F10" t="n">
-        <v>-23.6</v>
+        <v>9.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H10" t="n">
-        <v>34</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>2922.1</v>
+        <v>2927.8</v>
       </c>
       <c r="J10" t="n">
-        <v>2944.73</v>
+        <v>2932.2</v>
       </c>
       <c r="K10" t="n">
-        <v>2969.65</v>
+        <v>2953.4</v>
       </c>
       <c r="L10" t="n">
-        <v>2994.58</v>
+        <v>2974.6</v>
       </c>
       <c r="M10" t="n">
-        <v>3018.35</v>
+        <v>2987.4</v>
       </c>
       <c r="N10" t="n">
-        <v>3042.12</v>
+        <v>3000.2</v>
       </c>
       <c r="O10" t="n">
-        <v>3068.2</v>
+        <v>3029.8</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1353,24 +1357,28 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
@@ -1379,57 +1387,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2967.2</v>
+        <v>2981.2</v>
       </c>
       <c r="C11" t="n">
-        <v>3029.8</v>
+        <v>3006.1</v>
       </c>
       <c r="D11" t="n">
-        <v>2956.2</v>
+        <v>2974.4</v>
       </c>
       <c r="E11" t="n">
-        <v>2979.9</v>
+        <v>2991.8</v>
       </c>
       <c r="F11" t="n">
-        <v>9.5</v>
+        <v>11.9</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.004</v>
       </c>
       <c r="H11" t="n">
-        <v>73.59999999999999</v>
+        <v>31.7</v>
       </c>
       <c r="I11" t="n">
-        <v>2927.8</v>
+        <v>2882.6</v>
       </c>
       <c r="J11" t="n">
-        <v>2932.2</v>
+        <v>2899.75</v>
       </c>
       <c r="K11" t="n">
-        <v>2953.4</v>
+        <v>2943.1</v>
       </c>
       <c r="L11" t="n">
-        <v>2974.6</v>
+        <v>2986.45</v>
       </c>
       <c r="M11" t="n">
-        <v>2987.4</v>
+        <v>3016.7</v>
       </c>
       <c r="N11" t="n">
-        <v>3000.2</v>
+        <v>3046.95</v>
       </c>
       <c r="O11" t="n">
-        <v>3029.8</v>
+        <v>3103.4</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1440,25 +1448,19 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v/>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
@@ -1474,50 +1476,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2981.2</v>
+        <v>2995.3</v>
       </c>
       <c r="C12" t="n">
-        <v>3006.1</v>
+        <v>3012.8</v>
       </c>
       <c r="D12" t="n">
-        <v>2974.4</v>
+        <v>2972.7</v>
       </c>
       <c r="E12" t="n">
-        <v>2991.8</v>
+        <v>2990.7</v>
       </c>
       <c r="F12" t="n">
-        <v>11.9</v>
+        <v>-1.1</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0004</v>
       </c>
       <c r="H12" t="n">
-        <v>31.7</v>
+        <v>40.1</v>
       </c>
       <c r="I12" t="n">
-        <v>2882.6</v>
+        <v>2942.7</v>
       </c>
       <c r="J12" t="n">
-        <v>2899.75</v>
+        <v>2960.87</v>
       </c>
       <c r="K12" t="n">
-        <v>2943.1</v>
+        <v>2975.95</v>
       </c>
       <c r="L12" t="n">
-        <v>2986.45</v>
+        <v>2991.03</v>
       </c>
       <c r="M12" t="n">
-        <v>3016.7</v>
+        <v>3007.65</v>
       </c>
       <c r="N12" t="n">
-        <v>3046.95</v>
+        <v>3024.28</v>
       </c>
       <c r="O12" t="n">
-        <v>3103.4</v>
+        <v>3037.8</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1525,16 +1527,20 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1549,78 +1555,78 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2995.3</v>
+        <v>2991.7</v>
       </c>
       <c r="C13" t="n">
-        <v>3012.8</v>
+        <v>2994.8</v>
       </c>
       <c r="D13" t="n">
-        <v>2972.7</v>
+        <v>2949.3</v>
       </c>
       <c r="E13" t="n">
-        <v>2990.7</v>
+        <v>2973.5</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1</v>
+        <v>-17.2</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0058</v>
       </c>
       <c r="H13" t="n">
-        <v>40.1</v>
+        <v>45.5</v>
       </c>
       <c r="I13" t="n">
-        <v>2942.7</v>
+        <v>2932.6</v>
       </c>
       <c r="J13" t="n">
-        <v>2960.87</v>
+        <v>2949.57</v>
       </c>
       <c r="K13" t="n">
-        <v>2975.95</v>
+        <v>2970.65</v>
       </c>
       <c r="L13" t="n">
-        <v>2991.03</v>
+        <v>2991.72</v>
       </c>
       <c r="M13" t="n">
-        <v>3007.65</v>
+        <v>3010.75</v>
       </c>
       <c r="N13" t="n">
-        <v>3024.28</v>
+        <v>3029.78</v>
       </c>
       <c r="O13" t="n">
-        <v>3037.8</v>
+        <v>3052.9</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1635,79 +1641,79 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2991.7</v>
+        <v>2964.5</v>
       </c>
       <c r="C14" t="n">
-        <v>2994.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D14" t="n">
-        <v>2949.3</v>
+        <v>2952.7</v>
       </c>
       <c r="E14" t="n">
-        <v>2973.5</v>
+        <v>2955.2</v>
       </c>
       <c r="F14" t="n">
-        <v>-17.2</v>
+        <v>-18.3</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0062</v>
       </c>
       <c r="H14" t="n">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="I14" t="n">
-        <v>2932.6</v>
+        <v>2903.8</v>
       </c>
       <c r="J14" t="n">
-        <v>2949.57</v>
+        <v>2928.72</v>
       </c>
       <c r="K14" t="n">
-        <v>2970.65</v>
+        <v>2950.75</v>
       </c>
       <c r="L14" t="n">
-        <v>2991.72</v>
+        <v>2972.78</v>
       </c>
       <c r="M14" t="n">
-        <v>3010.75</v>
+        <v>2996.25</v>
       </c>
       <c r="N14" t="n">
-        <v>3029.78</v>
+        <v>3019.72</v>
       </c>
       <c r="O14" t="n">
-        <v>3052.9</v>
+        <v>3040.3</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
@@ -1721,57 +1727,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2964.5</v>
+        <v>2955.8</v>
       </c>
       <c r="C15" t="n">
-        <v>2998.7</v>
+        <v>2999.8</v>
       </c>
       <c r="D15" t="n">
-        <v>2952.7</v>
+        <v>2951.1</v>
       </c>
       <c r="E15" t="n">
-        <v>2955.2</v>
+        <v>2997</v>
       </c>
       <c r="F15" t="n">
-        <v>-18.3</v>
+        <v>41.8</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0141</v>
       </c>
       <c r="H15" t="n">
-        <v>46</v>
+        <v>48.7</v>
       </c>
       <c r="I15" t="n">
-        <v>2903.8</v>
+        <v>2906.7</v>
       </c>
       <c r="J15" t="n">
-        <v>2928.72</v>
+        <v>2898.95</v>
       </c>
       <c r="K15" t="n">
-        <v>2950.75</v>
+        <v>2932.2</v>
       </c>
       <c r="L15" t="n">
-        <v>2972.78</v>
+        <v>2965.45</v>
       </c>
       <c r="M15" t="n">
-        <v>2996.25</v>
+        <v>2978.2</v>
       </c>
       <c r="N15" t="n">
-        <v>3019.72</v>
+        <v>2990.95</v>
       </c>
       <c r="O15" t="n">
-        <v>3040.3</v>
+        <v>3044.7</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1779,23 +1785,23 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1814,50 +1820,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2955.8</v>
+        <v>2997</v>
       </c>
       <c r="C16" t="n">
-        <v>2999.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D16" t="n">
-        <v>2951.1</v>
+        <v>2965.5</v>
       </c>
       <c r="E16" t="n">
-        <v>2997</v>
+        <v>2969.8</v>
       </c>
       <c r="F16" t="n">
-        <v>41.8</v>
+        <v>-27.2</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0141</v>
+        <v>-0.0091</v>
       </c>
       <c r="H16" t="n">
-        <v>48.7</v>
+        <v>33.2</v>
       </c>
       <c r="I16" t="n">
-        <v>2906.7</v>
+        <v>2902.4</v>
       </c>
       <c r="J16" t="n">
-        <v>2898.95</v>
+        <v>2959.08</v>
       </c>
       <c r="K16" t="n">
-        <v>2932.2</v>
+        <v>2972.65</v>
       </c>
       <c r="L16" t="n">
-        <v>2965.45</v>
+        <v>2986.23</v>
       </c>
       <c r="M16" t="n">
-        <v>2978.2</v>
+        <v>3021.35</v>
       </c>
       <c r="N16" t="n">
-        <v>2990.95</v>
+        <v>3056.47</v>
       </c>
       <c r="O16" t="n">
-        <v>3044.7</v>
+        <v>3048.5</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1865,23 +1871,21 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1893,60 +1897,62 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2997</v>
+        <v>2974.6</v>
       </c>
       <c r="C17" t="n">
-        <v>2998.7</v>
+        <v>2979</v>
       </c>
       <c r="D17" t="n">
-        <v>2965.5</v>
+        <v>2932.1</v>
       </c>
       <c r="E17" t="n">
-        <v>2969.8</v>
+        <v>2951.7</v>
       </c>
       <c r="F17" t="n">
-        <v>-27.2</v>
+        <v>-18.1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0091</v>
+        <v>-0.0061</v>
       </c>
       <c r="H17" t="n">
-        <v>33.2</v>
+        <v>46.9</v>
       </c>
       <c r="I17" t="n">
-        <v>2902.4</v>
+        <v>2932.3</v>
       </c>
       <c r="J17" t="n">
-        <v>2959.08</v>
+        <v>2930.45</v>
       </c>
       <c r="K17" t="n">
-        <v>2972.65</v>
+        <v>2953.2</v>
       </c>
       <c r="L17" t="n">
-        <v>2986.23</v>
+        <v>2975.95</v>
       </c>
       <c r="M17" t="n">
-        <v>3021.35</v>
+        <v>2986.4</v>
       </c>
       <c r="N17" t="n">
-        <v>3056.47</v>
+        <v>2996.85</v>
       </c>
       <c r="O17" t="n">
-        <v>3048.5</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
+        <v>3031.9</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q17" s="6" t="n">
         <v/>
@@ -1956,7 +1962,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1977,74 +1983,70 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2974.6</v>
+        <v>2948.5</v>
       </c>
       <c r="C18" t="n">
-        <v>2979</v>
+        <v>2969.7</v>
       </c>
       <c r="D18" t="n">
-        <v>2932.1</v>
+        <v>2934.5</v>
       </c>
       <c r="E18" t="n">
-        <v>2951.7</v>
+        <v>2941.3</v>
       </c>
       <c r="F18" t="n">
-        <v>-18.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0035</v>
       </c>
       <c r="H18" t="n">
-        <v>46.9</v>
+        <v>35.2</v>
       </c>
       <c r="I18" t="n">
-        <v>2932.3</v>
+        <v>2885.2</v>
       </c>
       <c r="J18" t="n">
-        <v>2930.45</v>
+        <v>2902.88</v>
       </c>
       <c r="K18" t="n">
-        <v>2953.2</v>
+        <v>2928.25</v>
       </c>
       <c r="L18" t="n">
-        <v>2975.95</v>
+        <v>2953.62</v>
       </c>
       <c r="M18" t="n">
-        <v>2986.4</v>
+        <v>2975.15</v>
       </c>
       <c r="N18" t="n">
-        <v>2996.85</v>
+        <v>2996.67</v>
       </c>
       <c r="O18" t="n">
-        <v>3031.9</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3025.9</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
       </c>
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2063,57 +2065,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2948.5</v>
+        <v>2955.5</v>
       </c>
       <c r="C19" t="n">
-        <v>2969.7</v>
+        <v>2985.9</v>
       </c>
       <c r="D19" t="n">
-        <v>2934.5</v>
+        <v>2941.2</v>
       </c>
       <c r="E19" t="n">
-        <v>2941.3</v>
+        <v>2960</v>
       </c>
       <c r="F19" t="n">
-        <v>-10.4</v>
+        <v>18.7</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0064</v>
       </c>
       <c r="H19" t="n">
-        <v>35.2</v>
+        <v>44.7</v>
       </c>
       <c r="I19" t="n">
-        <v>2885.2</v>
+        <v>2899.3</v>
       </c>
       <c r="J19" t="n">
-        <v>2902.88</v>
+        <v>2900.7</v>
       </c>
       <c r="K19" t="n">
-        <v>2928.25</v>
+        <v>2923.7</v>
       </c>
       <c r="L19" t="n">
-        <v>2953.62</v>
+        <v>2946.7</v>
       </c>
       <c r="M19" t="n">
-        <v>2975.15</v>
+        <v>2958.9</v>
       </c>
       <c r="N19" t="n">
-        <v>2996.67</v>
+        <v>2971.1</v>
       </c>
       <c r="O19" t="n">
-        <v>3025.9</v>
+        <v>3004.9</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2126,14 +2128,18 @@
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2143,59 +2149,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2955.5</v>
+        <v>2961.5</v>
       </c>
       <c r="C20" t="n">
-        <v>2985.9</v>
+        <v>2968.3</v>
       </c>
       <c r="D20" t="n">
-        <v>2941.2</v>
+        <v>2933.4</v>
       </c>
       <c r="E20" t="n">
-        <v>2960</v>
+        <v>2964.5</v>
       </c>
       <c r="F20" t="n">
-        <v>18.7</v>
+        <v>4.5</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0015</v>
       </c>
       <c r="H20" t="n">
-        <v>44.7</v>
+        <v>34.9</v>
       </c>
       <c r="I20" t="n">
-        <v>2899.3</v>
+        <v>2896.5</v>
       </c>
       <c r="J20" t="n">
-        <v>2900.7</v>
+        <v>2913.53</v>
       </c>
       <c r="K20" t="n">
-        <v>2923.7</v>
+        <v>2937.65</v>
       </c>
       <c r="L20" t="n">
-        <v>2946.7</v>
+        <v>2961.77</v>
       </c>
       <c r="M20" t="n">
-        <v>2958.9</v>
+        <v>2982.35</v>
       </c>
       <c r="N20" t="n">
-        <v>2971.1</v>
+        <v>3002.92</v>
       </c>
       <c r="O20" t="n">
-        <v>3004.9</v>
+        <v>3030.6</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2203,24 +2205,22 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
@@ -2229,61 +2229,69 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2961.5</v>
+        <v>2966.9</v>
       </c>
       <c r="C21" t="n">
-        <v>2968.3</v>
+        <v>2978.3</v>
       </c>
       <c r="D21" t="n">
-        <v>2933.4</v>
+        <v>2902.3</v>
       </c>
       <c r="E21" t="n">
-        <v>2964.5</v>
+        <v>2915.4</v>
       </c>
       <c r="F21" t="n">
-        <v>4.5</v>
+        <v>-49.1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0166</v>
       </c>
       <c r="H21" t="n">
-        <v>34.9</v>
+        <v>76</v>
       </c>
       <c r="I21" t="n">
-        <v>2896.5</v>
+        <v>2898.5</v>
       </c>
       <c r="J21" t="n">
-        <v>2913.53</v>
+        <v>2936.42</v>
       </c>
       <c r="K21" t="n">
-        <v>2937.65</v>
+        <v>2947.05</v>
       </c>
       <c r="L21" t="n">
-        <v>2961.77</v>
+        <v>2957.67</v>
       </c>
       <c r="M21" t="n">
-        <v>2982.35</v>
+        <v>2981.95</v>
       </c>
       <c r="N21" t="n">
-        <v>3002.92</v>
+        <v>3006.23</v>
       </c>
       <c r="O21" t="n">
-        <v>3030.6</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
+        <v>3003.2</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
@@ -2292,7 +2300,7 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2304,88 +2312,84 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W21" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2966.9</v>
+        <v>2906.6</v>
       </c>
       <c r="C22" t="n">
-        <v>2978.3</v>
+        <v>2957.9</v>
       </c>
       <c r="D22" t="n">
-        <v>2902.3</v>
+        <v>2905.6</v>
       </c>
       <c r="E22" t="n">
-        <v>2915.4</v>
+        <v>2954.3</v>
       </c>
       <c r="F22" t="n">
-        <v>-49.1</v>
+        <v>38.9</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0166</v>
+        <v>0.0133</v>
       </c>
       <c r="H22" t="n">
-        <v>76</v>
+        <v>52.3</v>
       </c>
       <c r="I22" t="n">
-        <v>2898.5</v>
+        <v>2826.3</v>
       </c>
       <c r="J22" t="n">
-        <v>2936.42</v>
+        <v>2826.95</v>
       </c>
       <c r="K22" t="n">
-        <v>2947.05</v>
+        <v>2877.4</v>
       </c>
       <c r="L22" t="n">
-        <v>2957.67</v>
+        <v>2927.85</v>
       </c>
       <c r="M22" t="n">
-        <v>2981.95</v>
+        <v>2953.4</v>
       </c>
       <c r="N22" t="n">
-        <v>3006.23</v>
+        <v>2978.95</v>
       </c>
       <c r="O22" t="n">
-        <v>3003.2</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
+        <v>3054.3</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
@@ -2399,76 +2403,78 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2906.6</v>
+        <v>2954</v>
       </c>
       <c r="C23" t="n">
-        <v>2957.9</v>
+        <v>2976.3</v>
       </c>
       <c r="D23" t="n">
-        <v>2905.6</v>
+        <v>2905.3</v>
       </c>
       <c r="E23" t="n">
-        <v>2954.3</v>
+        <v>2938</v>
       </c>
       <c r="F23" t="n">
-        <v>38.9</v>
+        <v>-16.3</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0055</v>
       </c>
       <c r="H23" t="n">
-        <v>52.3</v>
+        <v>71</v>
       </c>
       <c r="I23" t="n">
-        <v>2826.3</v>
+        <v>2853.3</v>
       </c>
       <c r="J23" t="n">
-        <v>2826.95</v>
+        <v>2913.28</v>
       </c>
       <c r="K23" t="n">
-        <v>2877.4</v>
+        <v>2928.15</v>
       </c>
       <c r="L23" t="n">
-        <v>2927.85</v>
+        <v>2943.03</v>
       </c>
       <c r="M23" t="n">
-        <v>2953.4</v>
+        <v>2980.45</v>
       </c>
       <c r="N23" t="n">
-        <v>2978.95</v>
+        <v>3017.87</v>
       </c>
       <c r="O23" t="n">
-        <v>3054.3</v>
+        <v>3010.2</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2483,78 +2489,76 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2954</v>
+        <v>2950</v>
       </c>
       <c r="C24" t="n">
-        <v>2976.3</v>
+        <v>2994.6</v>
       </c>
       <c r="D24" t="n">
-        <v>2905.3</v>
+        <v>2948.4</v>
       </c>
       <c r="E24" t="n">
-        <v>2938</v>
+        <v>2989.3</v>
       </c>
       <c r="F24" t="n">
-        <v>-16.3</v>
+        <v>51.3</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0175</v>
       </c>
       <c r="H24" t="n">
-        <v>71</v>
+        <v>46.2</v>
       </c>
       <c r="I24" t="n">
-        <v>2853.3</v>
+        <v>2834.3</v>
       </c>
       <c r="J24" t="n">
-        <v>2913.28</v>
+        <v>2865.6</v>
       </c>
       <c r="K24" t="n">
-        <v>2928.15</v>
+        <v>2902.5</v>
       </c>
       <c r="L24" t="n">
-        <v>2943.03</v>
+        <v>2939.4</v>
       </c>
       <c r="M24" t="n">
-        <v>2980.45</v>
+        <v>2973.5</v>
       </c>
       <c r="N24" t="n">
-        <v>3017.87</v>
+        <v>3007.6</v>
       </c>
       <c r="O24" t="n">
-        <v>3010.2</v>
+        <v>3047.3</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2569,57 +2573,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2950</v>
+        <v>2992.4</v>
       </c>
       <c r="C25" t="n">
-        <v>2994.6</v>
+        <v>3051.8</v>
       </c>
       <c r="D25" t="n">
-        <v>2948.4</v>
+        <v>2986.1</v>
       </c>
       <c r="E25" t="n">
-        <v>2989.3</v>
+        <v>3044.7</v>
       </c>
       <c r="F25" t="n">
-        <v>51.3</v>
+        <v>55.4</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0185</v>
       </c>
       <c r="H25" t="n">
-        <v>46.2</v>
+        <v>65.7</v>
       </c>
       <c r="I25" t="n">
-        <v>2834.3</v>
+        <v>2902.2</v>
       </c>
       <c r="J25" t="n">
-        <v>2865.6</v>
+        <v>2952</v>
       </c>
       <c r="K25" t="n">
-        <v>2902.5</v>
+        <v>2966.2</v>
       </c>
       <c r="L25" t="n">
-        <v>2939.4</v>
+        <v>2980.4</v>
       </c>
       <c r="M25" t="n">
-        <v>2973.5</v>
+        <v>3012.4</v>
       </c>
       <c r="N25" t="n">
-        <v>3007.6</v>
+        <v>3044.4</v>
       </c>
       <c r="O25" t="n">
-        <v>3047.3</v>
+        <v>3040.8</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2630,80 +2634,80 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="7" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W25" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W25" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2992.4</v>
+        <v>3049.1</v>
       </c>
       <c r="C26" t="n">
-        <v>3051.8</v>
+        <v>3058.3</v>
       </c>
       <c r="D26" t="n">
-        <v>2986.1</v>
+        <v>3023.3</v>
       </c>
       <c r="E26" t="n">
-        <v>3044.7</v>
+        <v>3025.4</v>
       </c>
       <c r="F26" t="n">
-        <v>55.4</v>
+        <v>-19.3</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0063</v>
       </c>
       <c r="H26" t="n">
-        <v>65.7</v>
+        <v>35</v>
       </c>
       <c r="I26" t="n">
-        <v>2902.2</v>
+        <v>2920.4</v>
       </c>
       <c r="J26" t="n">
-        <v>2952</v>
+        <v>2991.87</v>
       </c>
       <c r="K26" t="n">
-        <v>2966.2</v>
+        <v>3011.85</v>
       </c>
       <c r="L26" t="n">
-        <v>2980.4</v>
+        <v>3031.83</v>
       </c>
       <c r="M26" t="n">
-        <v>3012.4</v>
+        <v>3077.55</v>
       </c>
       <c r="N26" t="n">
-        <v>3044.4</v>
+        <v>3123.27</v>
       </c>
       <c r="O26" t="n">
-        <v>3040.8</v>
+        <v>3117.5</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2716,78 +2720,76 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3049.1</v>
+        <v>3028.5</v>
       </c>
       <c r="C27" t="n">
-        <v>3058.3</v>
+        <v>3041</v>
       </c>
       <c r="D27" t="n">
-        <v>3023.3</v>
+        <v>3004.9</v>
       </c>
       <c r="E27" t="n">
-        <v>3025.4</v>
+        <v>3009.1</v>
       </c>
       <c r="F27" t="n">
-        <v>-19.3</v>
+        <v>-16.3</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0054</v>
       </c>
       <c r="H27" t="n">
-        <v>35</v>
+        <v>36.1</v>
       </c>
       <c r="I27" t="n">
-        <v>2920.4</v>
+        <v>2988.3</v>
       </c>
       <c r="J27" t="n">
-        <v>2991.87</v>
+        <v>2982.7</v>
       </c>
       <c r="K27" t="n">
-        <v>3011.85</v>
+        <v>3007.9</v>
       </c>
       <c r="L27" t="n">
-        <v>3031.83</v>
+        <v>3033.1</v>
       </c>
       <c r="M27" t="n">
-        <v>3077.55</v>
+        <v>3042.9</v>
       </c>
       <c r="N27" t="n">
-        <v>3123.27</v>
+        <v>3052.7</v>
       </c>
       <c r="O27" t="n">
-        <v>3117.5</v>
+        <v>3093.3</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2795,12 +2797,14 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2819,57 +2823,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3028.5</v>
+        <v>3008.5</v>
       </c>
       <c r="C28" t="n">
-        <v>3041</v>
+        <v>3046.8</v>
       </c>
       <c r="D28" t="n">
-        <v>3004.9</v>
+        <v>3002</v>
       </c>
       <c r="E28" t="n">
-        <v>3009.1</v>
+        <v>3041.6</v>
       </c>
       <c r="F28" t="n">
-        <v>-16.3</v>
+        <v>32.5</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0054</v>
+        <v>0.0108</v>
       </c>
       <c r="H28" t="n">
-        <v>36.1</v>
+        <v>44.8</v>
       </c>
       <c r="I28" t="n">
-        <v>2988.3</v>
+        <v>2968.8</v>
       </c>
       <c r="J28" t="n">
-        <v>2982.7</v>
+        <v>2966.08</v>
       </c>
       <c r="K28" t="n">
-        <v>3007.9</v>
+        <v>2991.05</v>
       </c>
       <c r="L28" t="n">
-        <v>3033.1</v>
+        <v>3016.03</v>
       </c>
       <c r="M28" t="n">
-        <v>3042.9</v>
+        <v>3027.15</v>
       </c>
       <c r="N28" t="n">
-        <v>3052.7</v>
+        <v>3038.28</v>
       </c>
       <c r="O28" t="n">
-        <v>3093.3</v>
+        <v>3077.1</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2877,22 +2881,24 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
@@ -2903,57 +2909,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3008.5</v>
+        <v>3038.9</v>
       </c>
       <c r="C29" t="n">
-        <v>3046.8</v>
+        <v>3044.6</v>
       </c>
       <c r="D29" t="n">
-        <v>3002</v>
+        <v>3016</v>
       </c>
       <c r="E29" t="n">
-        <v>3041.6</v>
+        <v>3025</v>
       </c>
       <c r="F29" t="n">
-        <v>32.5</v>
+        <v>-16.6</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0108</v>
+        <v>-0.0055</v>
       </c>
       <c r="H29" t="n">
-        <v>44.8</v>
+        <v>28.6</v>
       </c>
       <c r="I29" t="n">
-        <v>2968.8</v>
+        <v>2957.2</v>
       </c>
       <c r="J29" t="n">
-        <v>2966.08</v>
+        <v>3005.4</v>
       </c>
       <c r="K29" t="n">
-        <v>2991.05</v>
+        <v>3019.2</v>
       </c>
       <c r="L29" t="n">
-        <v>3016.03</v>
+        <v>3033</v>
       </c>
       <c r="M29" t="n">
-        <v>3027.15</v>
+        <v>3064</v>
       </c>
       <c r="N29" t="n">
-        <v>3038.28</v>
+        <v>3095</v>
       </c>
       <c r="O29" t="n">
-        <v>3077.1</v>
+        <v>3091.6</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2961,23 +2967,21 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2989,57 +2993,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3038.9</v>
+        <v>3024.7</v>
       </c>
       <c r="C30" t="n">
-        <v>3044.6</v>
+        <v>3045.8</v>
       </c>
       <c r="D30" t="n">
-        <v>3016</v>
+        <v>3019.9</v>
       </c>
       <c r="E30" t="n">
-        <v>3025</v>
+        <v>3035.5</v>
       </c>
       <c r="F30" t="n">
-        <v>-16.6</v>
+        <v>10.5</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0035</v>
       </c>
       <c r="H30" t="n">
-        <v>28.6</v>
+        <v>25.9</v>
       </c>
       <c r="I30" t="n">
-        <v>2957.2</v>
+        <v>2987.4</v>
       </c>
       <c r="J30" t="n">
-        <v>3005.4</v>
+        <v>2993.75</v>
       </c>
       <c r="K30" t="n">
-        <v>3019.2</v>
+        <v>3010.7</v>
       </c>
       <c r="L30" t="n">
-        <v>3033</v>
+        <v>3027.65</v>
       </c>
       <c r="M30" t="n">
-        <v>3064</v>
+        <v>3039.3</v>
       </c>
       <c r="N30" t="n">
-        <v>3095</v>
+        <v>3050.95</v>
       </c>
       <c r="O30" t="n">
-        <v>3091.6</v>
+        <v>3073.2</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3047,19 +3051,19 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
@@ -3071,59 +3075,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3024.7</v>
+        <v>3036.1</v>
       </c>
       <c r="C31" t="n">
-        <v>3045.8</v>
+        <v>3060</v>
       </c>
       <c r="D31" t="n">
-        <v>3019.9</v>
+        <v>3033.1</v>
       </c>
       <c r="E31" t="n">
-        <v>3035.5</v>
+        <v>3052.8</v>
       </c>
       <c r="F31" t="n">
-        <v>10.5</v>
+        <v>17.3</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0057</v>
       </c>
       <c r="H31" t="n">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
       <c r="I31" t="n">
-        <v>2987.4</v>
+        <v>2994</v>
       </c>
       <c r="J31" t="n">
-        <v>2993.75</v>
+        <v>3010.92</v>
       </c>
       <c r="K31" t="n">
-        <v>3010.7</v>
+        <v>3022.55</v>
       </c>
       <c r="L31" t="n">
-        <v>3027.65</v>
+        <v>3034.17</v>
       </c>
       <c r="M31" t="n">
-        <v>3039.3</v>
+        <v>3048.45</v>
       </c>
       <c r="N31" t="n">
-        <v>3050.95</v>
+        <v>3062.73</v>
       </c>
       <c r="O31" t="n">
-        <v>3073.2</v>
+        <v>3071.7</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3134,7 +3134,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3160,50 +3160,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3036.1</v>
+        <v>3056.2</v>
       </c>
       <c r="C32" t="n">
-        <v>3060</v>
+        <v>3076.3</v>
       </c>
       <c r="D32" t="n">
-        <v>3033.1</v>
+        <v>3052.5</v>
       </c>
       <c r="E32" t="n">
-        <v>3052.8</v>
+        <v>3060.2</v>
       </c>
       <c r="F32" t="n">
-        <v>17.3</v>
+        <v>7.4</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0024</v>
       </c>
       <c r="H32" t="n">
-        <v>26.9</v>
+        <v>23.8</v>
       </c>
       <c r="I32" t="n">
-        <v>2994</v>
+        <v>3006.2</v>
       </c>
       <c r="J32" t="n">
-        <v>3010.92</v>
+        <v>3029.03</v>
       </c>
       <c r="K32" t="n">
-        <v>3022.55</v>
+        <v>3039.35</v>
       </c>
       <c r="L32" t="n">
-        <v>3034.17</v>
+        <v>3049.68</v>
       </c>
       <c r="M32" t="n">
-        <v>3048.45</v>
+        <v>3066.25</v>
       </c>
       <c r="N32" t="n">
-        <v>3062.73</v>
+        <v>3082.82</v>
       </c>
       <c r="O32" t="n">
-        <v>3071.7</v>
+        <v>3086.9</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3214,7 +3214,7 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3240,50 +3240,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3056.2</v>
+        <v>3062.2</v>
       </c>
       <c r="C33" t="n">
         <v>3076.3</v>
       </c>
       <c r="D33" t="n">
-        <v>3052.5</v>
+        <v>3051.7</v>
       </c>
       <c r="E33" t="n">
-        <v>3060.2</v>
+        <v>3074.9</v>
       </c>
       <c r="F33" t="n">
-        <v>7.4</v>
+        <v>14.7</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0048</v>
       </c>
       <c r="H33" t="n">
-        <v>23.8</v>
+        <v>24.6</v>
       </c>
       <c r="I33" t="n">
-        <v>3006.2</v>
+        <v>3028.7</v>
       </c>
       <c r="J33" t="n">
-        <v>3029.03</v>
+        <v>3034.3</v>
       </c>
       <c r="K33" t="n">
-        <v>3039.35</v>
+        <v>3048.3</v>
       </c>
       <c r="L33" t="n">
-        <v>3049.68</v>
+        <v>3062.3</v>
       </c>
       <c r="M33" t="n">
-        <v>3066.25</v>
+        <v>3072.1</v>
       </c>
       <c r="N33" t="n">
-        <v>3082.82</v>
+        <v>3081.9</v>
       </c>
       <c r="O33" t="n">
-        <v>3086.9</v>
+        <v>3100.1</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3294,7 +3294,7 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3315,55 +3315,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3062.2</v>
+        <v>3073.5</v>
       </c>
       <c r="C34" t="n">
-        <v>3076.3</v>
+        <v>3079.9</v>
       </c>
       <c r="D34" t="n">
-        <v>3051.7</v>
+        <v>3055.9</v>
       </c>
       <c r="E34" t="n">
-        <v>3074.9</v>
+        <v>3064.9</v>
       </c>
       <c r="F34" t="n">
-        <v>14.7</v>
+        <v>-10</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.0033</v>
       </c>
       <c r="H34" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="I34" t="n">
-        <v>3028.7</v>
+        <v>3027.1</v>
       </c>
       <c r="J34" t="n">
-        <v>3034.3</v>
+        <v>3055.75</v>
       </c>
       <c r="K34" t="n">
-        <v>3048.3</v>
+        <v>3062.6</v>
       </c>
       <c r="L34" t="n">
-        <v>3062.3</v>
+        <v>3069.45</v>
       </c>
       <c r="M34" t="n">
-        <v>3072.1</v>
+        <v>3087.2</v>
       </c>
       <c r="N34" t="n">
-        <v>3081.9</v>
+        <v>3104.95</v>
       </c>
       <c r="O34" t="n">
-        <v>3100.1</v>
+        <v>3100.9</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3371,18 +3375,18 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3404,63 +3408,67 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3073.5</v>
+        <v>3063.7</v>
       </c>
       <c r="C35" t="n">
-        <v>3079.9</v>
+        <v>3066.6</v>
       </c>
       <c r="D35" t="n">
-        <v>3055.9</v>
+        <v>3024.1</v>
       </c>
       <c r="E35" t="n">
-        <v>3064.9</v>
+        <v>3026.4</v>
       </c>
       <c r="F35" t="n">
-        <v>-10</v>
+        <v>-38.5</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0126</v>
       </c>
       <c r="H35" t="n">
-        <v>24</v>
+        <v>42.5</v>
       </c>
       <c r="I35" t="n">
-        <v>3027.1</v>
+        <v>3031.9</v>
       </c>
       <c r="J35" t="n">
-        <v>3055.75</v>
+        <v>3039.4</v>
       </c>
       <c r="K35" t="n">
-        <v>3062.6</v>
+        <v>3052.9</v>
       </c>
       <c r="L35" t="n">
-        <v>3069.45</v>
+        <v>3066.4</v>
       </c>
       <c r="M35" t="n">
-        <v>3087.2</v>
+        <v>3076.9</v>
       </c>
       <c r="N35" t="n">
-        <v>3104.95</v>
+        <v>3087.4</v>
       </c>
       <c r="O35" t="n">
-        <v>3100.9</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
+        <v>3103.9</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3474,88 +3482,80 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W35" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3063.7</v>
+        <v>3025.9</v>
       </c>
       <c r="C36" t="n">
-        <v>3066.6</v>
+        <v>3059.1</v>
       </c>
       <c r="D36" t="n">
-        <v>3024.1</v>
+        <v>3019.8</v>
       </c>
       <c r="E36" t="n">
-        <v>3026.4</v>
+        <v>3039.9</v>
       </c>
       <c r="F36" t="n">
-        <v>-38.5</v>
+        <v>13.5</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0045</v>
       </c>
       <c r="H36" t="n">
-        <v>42.5</v>
+        <v>39.3</v>
       </c>
       <c r="I36" t="n">
-        <v>3031.9</v>
+        <v>2981.6</v>
       </c>
       <c r="J36" t="n">
-        <v>3039.4</v>
+        <v>2974.42</v>
       </c>
       <c r="K36" t="n">
-        <v>3052.9</v>
+        <v>3005.15</v>
       </c>
       <c r="L36" t="n">
-        <v>3066.4</v>
+        <v>3035.88</v>
       </c>
       <c r="M36" t="n">
-        <v>3076.9</v>
+        <v>3047.65</v>
       </c>
       <c r="N36" t="n">
-        <v>3087.4</v>
+        <v>3059.42</v>
       </c>
       <c r="O36" t="n">
-        <v>3103.9</v>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q36" s="6" t="inlineStr">
+        <v>3109.1</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3567,74 +3567,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3025.9</v>
+        <v>3041.4</v>
       </c>
       <c r="C37" t="n">
-        <v>3059.1</v>
+        <v>3048.5</v>
       </c>
       <c r="D37" t="n">
-        <v>3019.8</v>
+        <v>2993.2</v>
       </c>
       <c r="E37" t="n">
-        <v>3039.9</v>
+        <v>2999.2</v>
       </c>
       <c r="F37" t="n">
-        <v>13.5</v>
+        <v>-40.7</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0134</v>
       </c>
       <c r="H37" t="n">
-        <v>39.3</v>
+        <v>55.3</v>
       </c>
       <c r="I37" t="n">
-        <v>2981.6</v>
+        <v>2980.5</v>
       </c>
       <c r="J37" t="n">
-        <v>2974.42</v>
+        <v>3000.82</v>
       </c>
       <c r="K37" t="n">
-        <v>3005.15</v>
+        <v>3020.25</v>
       </c>
       <c r="L37" t="n">
-        <v>3035.88</v>
+        <v>3039.67</v>
       </c>
       <c r="M37" t="n">
-        <v>3047.65</v>
+        <v>3059.55</v>
       </c>
       <c r="N37" t="n">
-        <v>3059.42</v>
+        <v>3079.42</v>
       </c>
       <c r="O37" t="n">
-        <v>3109.1</v>
+        <v>3098.4</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3647,81 +3653,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3041.4</v>
+        <v>2999.6</v>
       </c>
       <c r="C38" t="n">
-        <v>3048.5</v>
+        <v>3026.7</v>
       </c>
       <c r="D38" t="n">
-        <v>2993.2</v>
+        <v>2997.9</v>
       </c>
       <c r="E38" t="n">
-        <v>2999.2</v>
+        <v>3022.1</v>
       </c>
       <c r="F38" t="n">
-        <v>-40.7</v>
+        <v>22.9</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0134</v>
+        <v>0.0076</v>
       </c>
       <c r="H38" t="n">
-        <v>55.3</v>
+        <v>28.8</v>
       </c>
       <c r="I38" t="n">
-        <v>2980.5</v>
+        <v>2937.9</v>
       </c>
       <c r="J38" t="n">
-        <v>3000.82</v>
+        <v>2933.07</v>
       </c>
       <c r="K38" t="n">
-        <v>3020.25</v>
+        <v>2971.55</v>
       </c>
       <c r="L38" t="n">
-        <v>3039.67</v>
+        <v>3010.02</v>
       </c>
       <c r="M38" t="n">
-        <v>3059.55</v>
+        <v>3026.85</v>
       </c>
       <c r="N38" t="n">
-        <v>3079.42</v>
+        <v>3043.67</v>
       </c>
       <c r="O38" t="n">
-        <v>3098.4</v>
+        <v>3103.8</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3733,74 +3733,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2999.6</v>
+        <v>3023</v>
       </c>
       <c r="C39" t="n">
-        <v>3026.7</v>
+        <v>3028.9</v>
       </c>
       <c r="D39" t="n">
-        <v>2997.9</v>
+        <v>2996</v>
       </c>
       <c r="E39" t="n">
-        <v>3022.1</v>
+        <v>3001.6</v>
       </c>
       <c r="F39" t="n">
-        <v>22.9</v>
+        <v>-20.5</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0076</v>
+        <v>-0.0068</v>
       </c>
       <c r="H39" t="n">
-        <v>28.8</v>
+        <v>32.9</v>
       </c>
       <c r="I39" t="n">
-        <v>2937.9</v>
+        <v>2969.1</v>
       </c>
       <c r="J39" t="n">
-        <v>2933.07</v>
+        <v>2998.2</v>
       </c>
       <c r="K39" t="n">
-        <v>2971.55</v>
+        <v>3007.7</v>
       </c>
       <c r="L39" t="n">
-        <v>3010.02</v>
+        <v>3017.2</v>
       </c>
       <c r="M39" t="n">
-        <v>3026.85</v>
+        <v>3036.5</v>
       </c>
       <c r="N39" t="n">
-        <v>3043.67</v>
+        <v>3055.8</v>
       </c>
       <c r="O39" t="n">
-        <v>3103.8</v>
+        <v>3055.5</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3815,79 +3821,77 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3023</v>
+        <v>3004.6</v>
       </c>
       <c r="C40" t="n">
-        <v>3028.9</v>
+        <v>3025.4</v>
       </c>
       <c r="D40" t="n">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="E40" t="n">
-        <v>3001.6</v>
+        <v>3014.4</v>
       </c>
       <c r="F40" t="n">
-        <v>-20.5</v>
+        <v>12.8</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0043</v>
       </c>
       <c r="H40" t="n">
-        <v>32.9</v>
+        <v>28.4</v>
       </c>
       <c r="I40" t="n">
-        <v>2969.1</v>
+        <v>2963.1</v>
       </c>
       <c r="J40" t="n">
-        <v>2998.2</v>
+        <v>2963.28</v>
       </c>
       <c r="K40" t="n">
-        <v>3007.7</v>
+        <v>2985.15</v>
       </c>
       <c r="L40" t="n">
-        <v>3017.2</v>
+        <v>3007.03</v>
       </c>
       <c r="M40" t="n">
-        <v>3036.5</v>
+        <v>3018.05</v>
       </c>
       <c r="N40" t="n">
-        <v>3055.8</v>
+        <v>3029.08</v>
       </c>
       <c r="O40" t="n">
-        <v>3055.5</v>
+        <v>3061.8</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3901,57 +3905,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3004.6</v>
+        <v>3014.6</v>
       </c>
       <c r="C41" t="n">
-        <v>3025.4</v>
+        <v>3020.5</v>
       </c>
       <c r="D41" t="n">
-        <v>2997</v>
+        <v>3002.6</v>
       </c>
       <c r="E41" t="n">
-        <v>3014.4</v>
+        <v>3010.1</v>
       </c>
       <c r="F41" t="n">
-        <v>12.8</v>
+        <v>-4.3</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0014</v>
       </c>
       <c r="H41" t="n">
-        <v>28.4</v>
+        <v>17.9</v>
       </c>
       <c r="I41" t="n">
-        <v>2963.1</v>
+        <v>2968.6</v>
       </c>
       <c r="J41" t="n">
-        <v>2963.28</v>
+        <v>2987.6</v>
       </c>
       <c r="K41" t="n">
-        <v>2985.15</v>
+        <v>3000.2</v>
       </c>
       <c r="L41" t="n">
-        <v>3007.03</v>
+        <v>3012.8</v>
       </c>
       <c r="M41" t="n">
-        <v>3018.05</v>
+        <v>3028.6</v>
       </c>
       <c r="N41" t="n">
-        <v>3029.08</v>
+        <v>3044.4</v>
       </c>
       <c r="O41" t="n">
-        <v>3061.8</v>
+        <v>3053.8</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3964,13 +3968,11 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3985,57 +3987,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3014.6</v>
+        <v>3016.9</v>
       </c>
       <c r="C42" t="n">
-        <v>3020.5</v>
+        <v>3024.2</v>
       </c>
       <c r="D42" t="n">
-        <v>3002.6</v>
+        <v>3002.1</v>
       </c>
       <c r="E42" t="n">
-        <v>3010.1</v>
+        <v>3019</v>
       </c>
       <c r="F42" t="n">
-        <v>-4.3</v>
+        <v>8.9</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0014</v>
+        <v>0.003</v>
       </c>
       <c r="H42" t="n">
-        <v>17.9</v>
+        <v>22.1</v>
       </c>
       <c r="I42" t="n">
-        <v>2968.6</v>
+        <v>2984.7</v>
       </c>
       <c r="J42" t="n">
-        <v>2987.6</v>
+        <v>2991.48</v>
       </c>
       <c r="K42" t="n">
-        <v>3000.2</v>
+        <v>3001.15</v>
       </c>
       <c r="L42" t="n">
-        <v>3012.8</v>
+        <v>3010.83</v>
       </c>
       <c r="M42" t="n">
-        <v>3028.6</v>
+        <v>3019.05</v>
       </c>
       <c r="N42" t="n">
-        <v>3044.4</v>
+        <v>3027.28</v>
       </c>
       <c r="O42" t="n">
-        <v>3053.8</v>
+        <v>3038.4</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4048,11 +4050,13 @@
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4067,76 +4071,80 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3016.9</v>
+        <v>3019.6</v>
       </c>
       <c r="C43" t="n">
-        <v>3024.2</v>
+        <v>3025.5</v>
       </c>
       <c r="D43" t="n">
-        <v>3002.1</v>
+        <v>2976.6</v>
       </c>
       <c r="E43" t="n">
-        <v>3019</v>
+        <v>2977.5</v>
       </c>
       <c r="F43" t="n">
-        <v>8.9</v>
+        <v>-41.5</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0137</v>
       </c>
       <c r="H43" t="n">
-        <v>22.1</v>
+        <v>48.9</v>
       </c>
       <c r="I43" t="n">
-        <v>2984.7</v>
+        <v>2980</v>
       </c>
       <c r="J43" t="n">
-        <v>2991.48</v>
+        <v>2999.83</v>
       </c>
       <c r="K43" t="n">
-        <v>3001.15</v>
+        <v>3007.95</v>
       </c>
       <c r="L43" t="n">
-        <v>3010.83</v>
+        <v>3016.08</v>
       </c>
       <c r="M43" t="n">
-        <v>3019.05</v>
+        <v>3030.05</v>
       </c>
       <c r="N43" t="n">
-        <v>3027.28</v>
+        <v>3044.02</v>
       </c>
       <c r="O43" t="n">
-        <v>3038.4</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+        <v>3046.3</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4151,74 +4159,70 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3019.6</v>
+        <v>2971</v>
       </c>
       <c r="C44" t="n">
-        <v>3025.5</v>
+        <v>2982.5</v>
       </c>
       <c r="D44" t="n">
-        <v>2976.6</v>
+        <v>2946.1</v>
       </c>
       <c r="E44" t="n">
-        <v>2977.5</v>
+        <v>2958.7</v>
       </c>
       <c r="F44" t="n">
-        <v>-41.5</v>
+        <v>-18.8</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0063</v>
       </c>
       <c r="H44" t="n">
-        <v>48.9</v>
+        <v>36.4</v>
       </c>
       <c r="I44" t="n">
-        <v>2980</v>
+        <v>2927.7</v>
       </c>
       <c r="J44" t="n">
-        <v>2999.83</v>
+        <v>2916.83</v>
       </c>
       <c r="K44" t="n">
-        <v>3007.95</v>
+        <v>2953.05</v>
       </c>
       <c r="L44" t="n">
-        <v>3016.08</v>
+        <v>2989.28</v>
       </c>
       <c r="M44" t="n">
-        <v>3030.05</v>
+        <v>3001.95</v>
       </c>
       <c r="N44" t="n">
-        <v>3044.02</v>
+        <v>3014.62</v>
       </c>
       <c r="O44" t="n">
-        <v>3046.3</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
+        <v>3074.4</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
+      <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4237,72 +4241,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2971</v>
+        <v>2958</v>
       </c>
       <c r="C45" t="n">
-        <v>2982.5</v>
+        <v>2964.6</v>
       </c>
       <c r="D45" t="n">
-        <v>2946.1</v>
+        <v>2918.9</v>
       </c>
       <c r="E45" t="n">
-        <v>2958.7</v>
+        <v>2924.7</v>
       </c>
       <c r="F45" t="n">
-        <v>-18.8</v>
+        <v>-34</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0115</v>
       </c>
       <c r="H45" t="n">
-        <v>36.4</v>
+        <v>45.7</v>
       </c>
       <c r="I45" t="n">
-        <v>2927.7</v>
+        <v>2909.7</v>
       </c>
       <c r="J45" t="n">
-        <v>2916.83</v>
+        <v>2919.5</v>
       </c>
       <c r="K45" t="n">
-        <v>2953.05</v>
+        <v>2940.5</v>
       </c>
       <c r="L45" t="n">
-        <v>2989.28</v>
+        <v>2961.5</v>
       </c>
       <c r="M45" t="n">
-        <v>3001.95</v>
+        <v>2976.9</v>
       </c>
       <c r="N45" t="n">
-        <v>3014.62</v>
+        <v>2992.3</v>
       </c>
       <c r="O45" t="n">
-        <v>3074.4</v>
+        <v>3018.9</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4326,75 +4328,75 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2958</v>
+        <v>2926.4</v>
       </c>
       <c r="C46" t="n">
-        <v>2964.6</v>
+        <v>2962.5</v>
       </c>
       <c r="D46" t="n">
-        <v>2918.9</v>
+        <v>2914.5</v>
       </c>
       <c r="E46" t="n">
-        <v>2924.7</v>
+        <v>2958.8</v>
       </c>
       <c r="F46" t="n">
-        <v>-34</v>
+        <v>34.1</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0.0117</v>
       </c>
       <c r="H46" t="n">
-        <v>45.7</v>
+        <v>48</v>
       </c>
       <c r="I46" t="n">
-        <v>2909.7</v>
+        <v>2873.2</v>
       </c>
       <c r="J46" t="n">
-        <v>2919.5</v>
+        <v>2870.47</v>
       </c>
       <c r="K46" t="n">
-        <v>2940.5</v>
+        <v>2901.85</v>
       </c>
       <c r="L46" t="n">
-        <v>2961.5</v>
+        <v>2933.22</v>
       </c>
       <c r="M46" t="n">
-        <v>2976.9</v>
+        <v>2947.55</v>
       </c>
       <c r="N46" t="n">
-        <v>2992.3</v>
+        <v>2961.88</v>
       </c>
       <c r="O46" t="n">
-        <v>3018.9</v>
+        <v>3010.3</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
@@ -4403,55 +4405,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2926.4</v>
+        <v>2957.6</v>
       </c>
       <c r="C47" t="n">
-        <v>2962.5</v>
+        <v>2983.3</v>
       </c>
       <c r="D47" t="n">
-        <v>2914.5</v>
+        <v>2949.9</v>
       </c>
       <c r="E47" t="n">
-        <v>2958.8</v>
+        <v>2969.7</v>
       </c>
       <c r="F47" t="n">
-        <v>34.1</v>
+        <v>10.9</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0117</v>
+        <v>0.0037</v>
       </c>
       <c r="H47" t="n">
-        <v>48</v>
+        <v>33.4</v>
       </c>
       <c r="I47" t="n">
-        <v>2873.2</v>
+        <v>2866.5</v>
       </c>
       <c r="J47" t="n">
-        <v>2870.47</v>
+        <v>2920.95</v>
       </c>
       <c r="K47" t="n">
-        <v>2901.85</v>
+        <v>2934.8</v>
       </c>
       <c r="L47" t="n">
-        <v>2933.22</v>
+        <v>2948.65</v>
       </c>
       <c r="M47" t="n">
-        <v>2947.55</v>
+        <v>2982.8</v>
       </c>
       <c r="N47" t="n">
-        <v>2961.88</v>
+        <v>3016.95</v>
       </c>
       <c r="O47" t="n">
-        <v>3010.3</v>
+        <v>3010.5</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4462,21 +4468,19 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
+      <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
@@ -4487,57 +4491,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2957.6</v>
+        <v>2967.9</v>
       </c>
       <c r="C48" t="n">
-        <v>2983.3</v>
+        <v>2979.3</v>
       </c>
       <c r="D48" t="n">
-        <v>2949.9</v>
+        <v>2949.5</v>
       </c>
       <c r="E48" t="n">
-        <v>2969.7</v>
+        <v>2976.6</v>
       </c>
       <c r="F48" t="n">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0023</v>
       </c>
       <c r="H48" t="n">
-        <v>33.4</v>
+        <v>29.8</v>
       </c>
       <c r="I48" t="n">
-        <v>2866.5</v>
+        <v>2916.5</v>
       </c>
       <c r="J48" t="n">
-        <v>2920.95</v>
+        <v>2937.85</v>
       </c>
       <c r="K48" t="n">
-        <v>2934.8</v>
+        <v>2953</v>
       </c>
       <c r="L48" t="n">
-        <v>2948.65</v>
+        <v>2968.15</v>
       </c>
       <c r="M48" t="n">
-        <v>2982.8</v>
+        <v>2986.4</v>
       </c>
       <c r="N48" t="n">
-        <v>3016.95</v>
+        <v>3004.65</v>
       </c>
       <c r="O48" t="n">
-        <v>3010.5</v>
+        <v>3016.7</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4545,18 +4549,18 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4571,57 +4575,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2967.9</v>
+        <v>2974.7</v>
       </c>
       <c r="C49" t="n">
-        <v>2979.3</v>
+        <v>2977.9</v>
       </c>
       <c r="D49" t="n">
-        <v>2949.5</v>
+        <v>2954.7</v>
       </c>
       <c r="E49" t="n">
-        <v>2976.6</v>
+        <v>2963.6</v>
       </c>
       <c r="F49" t="n">
-        <v>6.9</v>
+        <v>-13</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0044</v>
       </c>
       <c r="H49" t="n">
-        <v>29.8</v>
+        <v>23.2</v>
       </c>
       <c r="I49" t="n">
-        <v>2916.5</v>
+        <v>2919.7</v>
       </c>
       <c r="J49" t="n">
-        <v>2937.85</v>
+        <v>2952.9</v>
       </c>
       <c r="K49" t="n">
-        <v>2953</v>
+        <v>2961.7</v>
       </c>
       <c r="L49" t="n">
-        <v>2968.15</v>
+        <v>2970.5</v>
       </c>
       <c r="M49" t="n">
-        <v>2986.4</v>
+        <v>2991.5</v>
       </c>
       <c r="N49" t="n">
-        <v>3004.65</v>
+        <v>3012.5</v>
       </c>
       <c r="O49" t="n">
-        <v>3016.7</v>
+        <v>3009.1</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4631,12 +4635,12 @@
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4662,63 +4666,67 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2974.7</v>
+        <v>2963.1</v>
       </c>
       <c r="C50" t="n">
-        <v>2977.9</v>
+        <v>2966.2</v>
       </c>
       <c r="D50" t="n">
-        <v>2954.7</v>
+        <v>2919.4</v>
       </c>
       <c r="E50" t="n">
-        <v>2963.6</v>
+        <v>2923</v>
       </c>
       <c r="F50" t="n">
-        <v>-13</v>
+        <v>-40.6</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0137</v>
       </c>
       <c r="H50" t="n">
-        <v>23.2</v>
+        <v>46.8</v>
       </c>
       <c r="I50" t="n">
-        <v>2919.7</v>
+        <v>2931.5</v>
       </c>
       <c r="J50" t="n">
-        <v>2952.9</v>
+        <v>2939.05</v>
       </c>
       <c r="K50" t="n">
-        <v>2961.7</v>
+        <v>2952</v>
       </c>
       <c r="L50" t="n">
-        <v>2970.5</v>
+        <v>2964.95</v>
       </c>
       <c r="M50" t="n">
-        <v>2991.5</v>
+        <v>2975.2</v>
       </c>
       <c r="N50" t="n">
-        <v>3012.5</v>
+        <v>2985.45</v>
       </c>
       <c r="O50" t="n">
-        <v>3009.1</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
+        <v>3001.1</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4737,76 +4745,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2963.1</v>
+        <v>2923.1</v>
       </c>
       <c r="C51" t="n">
-        <v>2966.2</v>
+        <v>2933.8</v>
       </c>
       <c r="D51" t="n">
-        <v>2919.4</v>
+        <v>2887.8</v>
       </c>
       <c r="E51" t="n">
-        <v>2923</v>
+        <v>2893.4</v>
       </c>
       <c r="F51" t="n">
-        <v>-40.6</v>
+        <v>-29.6</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0101</v>
       </c>
       <c r="H51" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="I51" t="n">
-        <v>2931.5</v>
+        <v>2872.6</v>
       </c>
       <c r="J51" t="n">
-        <v>2939.05</v>
+        <v>2866.3</v>
       </c>
       <c r="K51" t="n">
-        <v>2952</v>
+        <v>2899.6</v>
       </c>
       <c r="L51" t="n">
-        <v>2964.95</v>
+        <v>2932.9</v>
       </c>
       <c r="M51" t="n">
-        <v>2975.2</v>
+        <v>2946.4</v>
       </c>
       <c r="N51" t="n">
-        <v>2985.45</v>
+        <v>2959.9</v>
       </c>
       <c r="O51" t="n">
-        <v>3001.1</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
+        <v>3013</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
+      <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4830,50 +4830,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2923.1</v>
+        <v>2890.9</v>
       </c>
       <c r="C52" t="n">
-        <v>2933.8</v>
+        <v>2929.8</v>
       </c>
       <c r="D52" t="n">
-        <v>2887.8</v>
+        <v>2887.6</v>
       </c>
       <c r="E52" t="n">
-        <v>2893.4</v>
+        <v>2904.5</v>
       </c>
       <c r="F52" t="n">
-        <v>-29.6</v>
+        <v>11.1</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0101</v>
+        <v>0.0038</v>
       </c>
       <c r="H52" t="n">
-        <v>46</v>
+        <v>42.2</v>
       </c>
       <c r="I52" t="n">
-        <v>2872.6</v>
+        <v>2841.8</v>
       </c>
       <c r="J52" t="n">
-        <v>2866.3</v>
+        <v>2838.7</v>
       </c>
       <c r="K52" t="n">
-        <v>2899.6</v>
+        <v>2870.4</v>
       </c>
       <c r="L52" t="n">
-        <v>2932.9</v>
+        <v>2902.1</v>
       </c>
       <c r="M52" t="n">
-        <v>2946.4</v>
+        <v>2916.4</v>
       </c>
       <c r="N52" t="n">
-        <v>2959.9</v>
+        <v>2930.7</v>
       </c>
       <c r="O52" t="n">
-        <v>3013</v>
+        <v>2979.8</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4881,18 +4881,18 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R52" s="6" t="n">
+        <v/>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4905,55 +4905,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2890.9</v>
+        <v>2892.7</v>
       </c>
       <c r="C53" t="n">
-        <v>2929.8</v>
+        <v>2913.5</v>
       </c>
       <c r="D53" t="n">
-        <v>2887.6</v>
+        <v>2884.3</v>
       </c>
       <c r="E53" t="n">
-        <v>2904.5</v>
+        <v>2894.1</v>
       </c>
       <c r="F53" t="n">
-        <v>11.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0036</v>
       </c>
       <c r="H53" t="n">
-        <v>42.2</v>
+        <v>29.2</v>
       </c>
       <c r="I53" t="n">
-        <v>2841.8</v>
+        <v>2845.4</v>
       </c>
       <c r="J53" t="n">
-        <v>2838.7</v>
+        <v>2860.2</v>
       </c>
       <c r="K53" t="n">
-        <v>2870.4</v>
+        <v>2883.4</v>
       </c>
       <c r="L53" t="n">
-        <v>2902.1</v>
+        <v>2906.6</v>
       </c>
       <c r="M53" t="n">
-        <v>2916.4</v>
+        <v>2925.6</v>
       </c>
       <c r="N53" t="n">
-        <v>2930.7</v>
+        <v>2944.6</v>
       </c>
       <c r="O53" t="n">
-        <v>2979.8</v>
+        <v>2972</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4961,18 +4965,18 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4985,59 +4989,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2892.7</v>
+        <v>2896.4</v>
       </c>
       <c r="C54" t="n">
-        <v>2913.5</v>
+        <v>2896.5</v>
       </c>
       <c r="D54" t="n">
-        <v>2884.3</v>
+        <v>2862.7</v>
       </c>
       <c r="E54" t="n">
-        <v>2894.1</v>
+        <v>2873.1</v>
       </c>
       <c r="F54" t="n">
-        <v>-10.4</v>
+        <v>-21</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0073</v>
       </c>
       <c r="H54" t="n">
-        <v>29.2</v>
+        <v>33.8</v>
       </c>
       <c r="I54" t="n">
-        <v>2845.4</v>
+        <v>2855.1</v>
       </c>
       <c r="J54" t="n">
-        <v>2860.2</v>
+        <v>2862.5</v>
       </c>
       <c r="K54" t="n">
-        <v>2883.4</v>
+        <v>2879.5</v>
       </c>
       <c r="L54" t="n">
-        <v>2906.6</v>
+        <v>2896.5</v>
       </c>
       <c r="M54" t="n">
-        <v>2925.6</v>
+        <v>2908.7</v>
       </c>
       <c r="N54" t="n">
-        <v>2944.6</v>
+        <v>2920.9</v>
       </c>
       <c r="O54" t="n">
-        <v>2972</v>
+        <v>2942.7</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5050,7 +5050,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
+      <c r="S54" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5074,69 +5074,73 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2896.4</v>
+        <v>2875.1</v>
       </c>
       <c r="C55" t="n">
-        <v>2896.5</v>
+        <v>2892.5</v>
       </c>
       <c r="D55" t="n">
-        <v>2862.7</v>
+        <v>2831.9</v>
       </c>
       <c r="E55" t="n">
-        <v>2873.1</v>
+        <v>2861.7</v>
       </c>
       <c r="F55" t="n">
-        <v>-21</v>
+        <v>-11.4</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.004</v>
       </c>
       <c r="H55" t="n">
-        <v>33.8</v>
+        <v>60.6</v>
       </c>
       <c r="I55" t="n">
-        <v>2855.1</v>
+        <v>2828.9</v>
       </c>
       <c r="J55" t="n">
-        <v>2862.5</v>
+        <v>2836.05</v>
       </c>
       <c r="K55" t="n">
-        <v>2879.5</v>
+        <v>2856.2</v>
       </c>
       <c r="L55" t="n">
-        <v>2896.5</v>
+        <v>2876.35</v>
       </c>
       <c r="M55" t="n">
-        <v>2908.7</v>
+        <v>2890</v>
       </c>
       <c r="N55" t="n">
-        <v>2920.9</v>
+        <v>2903.65</v>
       </c>
       <c r="O55" t="n">
-        <v>2942.7</v>
+        <v>2930.3</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="10" t="inlineStr">
+      <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5154,74 +5158,70 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2875.1</v>
+        <v>2861.2</v>
       </c>
       <c r="C56" t="n">
-        <v>2892.5</v>
+        <v>2904.6</v>
       </c>
       <c r="D56" t="n">
-        <v>2831.9</v>
+        <v>2859.3</v>
       </c>
       <c r="E56" t="n">
-        <v>2861.7</v>
+        <v>2875.9</v>
       </c>
       <c r="F56" t="n">
-        <v>-11.4</v>
+        <v>14.2</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.005</v>
       </c>
       <c r="H56" t="n">
-        <v>60.6</v>
+        <v>45.3</v>
       </c>
       <c r="I56" t="n">
-        <v>2828.9</v>
+        <v>2771.3</v>
       </c>
       <c r="J56" t="n">
-        <v>2836.05</v>
+        <v>2800.85</v>
       </c>
       <c r="K56" t="n">
-        <v>2856.2</v>
+        <v>2831.4</v>
       </c>
       <c r="L56" t="n">
-        <v>2876.35</v>
+        <v>2861.95</v>
       </c>
       <c r="M56" t="n">
-        <v>2890</v>
+        <v>2892</v>
       </c>
       <c r="N56" t="n">
-        <v>2903.65</v>
+        <v>2922.05</v>
       </c>
       <c r="O56" t="n">
-        <v>2930.3</v>
+        <v>2953.1</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
@@ -5233,55 +5233,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2861.2</v>
+        <v>2870.5</v>
       </c>
       <c r="C57" t="n">
-        <v>2904.6</v>
+        <v>2883</v>
       </c>
       <c r="D57" t="n">
-        <v>2859.3</v>
+        <v>2856.9</v>
       </c>
       <c r="E57" t="n">
-        <v>2875.9</v>
+        <v>2873.23</v>
       </c>
       <c r="F57" t="n">
-        <v>14.2</v>
+        <v>-2.67</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0009</v>
       </c>
       <c r="H57" t="n">
-        <v>45.3</v>
+        <v>26.1</v>
       </c>
       <c r="I57" t="n">
-        <v>2771.3</v>
+        <v>2814</v>
       </c>
       <c r="J57" t="n">
-        <v>2800.85</v>
+        <v>2827.57</v>
       </c>
       <c r="K57" t="n">
-        <v>2831.4</v>
+        <v>2853.25</v>
       </c>
       <c r="L57" t="n">
-        <v>2861.95</v>
+        <v>2878.92</v>
       </c>
       <c r="M57" t="n">
-        <v>2892</v>
+        <v>2898.55</v>
       </c>
       <c r="N57" t="n">
-        <v>2922.05</v>
+        <v>2918.17</v>
       </c>
       <c r="O57" t="n">
-        <v>2953.1</v>
+        <v>2949.9</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5294,13 +5298,11 @@
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5313,59 +5315,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2870.5</v>
+        <v>2879.5</v>
       </c>
       <c r="C58" t="n">
-        <v>2883</v>
+        <v>2907.3</v>
       </c>
       <c r="D58" t="n">
-        <v>2856.9</v>
+        <v>2876.6</v>
       </c>
       <c r="E58" t="n">
-        <v>2873.23</v>
+        <v>2897.4</v>
       </c>
       <c r="F58" t="n">
-        <v>-2.67</v>
+        <v>24.17</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>26.1</v>
+        <v>30.7</v>
       </c>
       <c r="I58" t="n">
-        <v>2814</v>
+        <v>2830.8</v>
       </c>
       <c r="J58" t="n">
-        <v>2827.57</v>
+        <v>2848.77</v>
       </c>
       <c r="K58" t="n">
-        <v>2853.25</v>
+        <v>2860.18</v>
       </c>
       <c r="L58" t="n">
-        <v>2878.92</v>
+        <v>2871.59</v>
       </c>
       <c r="M58" t="n">
-        <v>2898.55</v>
+        <v>2886.28</v>
       </c>
       <c r="N58" t="n">
-        <v>2918.17</v>
+        <v>2900.97</v>
       </c>
       <c r="O58" t="n">
-        <v>2949.9</v>
+        <v>2909.1</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5378,14 +5376,18 @@
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5395,55 +5397,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2879.5</v>
+        <v>2897.8</v>
       </c>
       <c r="C59" t="n">
-        <v>2907.3</v>
+        <v>2931.2</v>
       </c>
       <c r="D59" t="n">
-        <v>2876.6</v>
+        <v>2884.2</v>
       </c>
       <c r="E59" t="n">
-        <v>2897.4</v>
+        <v>2914.1</v>
       </c>
       <c r="F59" t="n">
-        <v>24.17</v>
+        <v>16.7</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0058</v>
       </c>
       <c r="H59" t="n">
-        <v>30.7</v>
+        <v>47</v>
       </c>
       <c r="I59" t="n">
-        <v>2830.8</v>
+        <v>2845.9</v>
       </c>
       <c r="J59" t="n">
-        <v>2848.77</v>
+        <v>2869.42</v>
       </c>
       <c r="K59" t="n">
-        <v>2860.18</v>
+        <v>2882.05</v>
       </c>
       <c r="L59" t="n">
-        <v>2871.59</v>
+        <v>2894.67</v>
       </c>
       <c r="M59" t="n">
-        <v>2886.28</v>
+        <v>2912.75</v>
       </c>
       <c r="N59" t="n">
-        <v>2900.97</v>
+        <v>2930.82</v>
       </c>
       <c r="O59" t="n">
-        <v>2909.1</v>
+        <v>2938</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5454,19 +5460,19 @@
       <c r="R59" s="6" t="n">
         <v/>
       </c>
-      <c r="S59" s="7" t="inlineStr">
+      <c r="S59" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="V59" s="8" t="n">
@@ -5486,74 +5492,74 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2897.8</v>
+        <v>2912</v>
       </c>
       <c r="C60" t="n">
-        <v>2931.2</v>
+        <v>2915.3</v>
       </c>
       <c r="D60" t="n">
-        <v>2884.2</v>
+        <v>2858.8</v>
       </c>
       <c r="E60" t="n">
-        <v>2914.1</v>
+        <v>2860.2</v>
       </c>
       <c r="F60" t="n">
-        <v>16.7</v>
+        <v>-53.9</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0185</v>
       </c>
       <c r="H60" t="n">
-        <v>47</v>
+        <v>56.5</v>
       </c>
       <c r="I60" t="n">
-        <v>2845.9</v>
+        <v>2837.2</v>
       </c>
       <c r="J60" t="n">
-        <v>2869.42</v>
+        <v>2870.3</v>
       </c>
       <c r="K60" t="n">
-        <v>2882.05</v>
+        <v>2890.6</v>
       </c>
       <c r="L60" t="n">
-        <v>2894.67</v>
+        <v>2910.9</v>
       </c>
       <c r="M60" t="n">
-        <v>2912.75</v>
+        <v>2937.6</v>
       </c>
       <c r="N60" t="n">
-        <v>2930.82</v>
+        <v>2964.3</v>
       </c>
       <c r="O60" t="n">
-        <v>2938</v>
+        <v>2978.2</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
@@ -5563,76 +5569,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2912</v>
+        <v>2860.7</v>
       </c>
       <c r="C61" t="n">
-        <v>2915.3</v>
+        <v>2862.4</v>
       </c>
       <c r="D61" t="n">
-        <v>2858.8</v>
+        <v>2829.9</v>
       </c>
       <c r="E61" t="n">
-        <v>2860.2</v>
+        <v>2856.8</v>
       </c>
       <c r="F61" t="n">
-        <v>-53.9</v>
+        <v>-3.4</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0012</v>
       </c>
       <c r="H61" t="n">
-        <v>56.5</v>
+        <v>32.5</v>
       </c>
       <c r="I61" t="n">
-        <v>2837.2</v>
+        <v>2802.3</v>
       </c>
       <c r="J61" t="n">
-        <v>2870.3</v>
+        <v>2790.27</v>
       </c>
       <c r="K61" t="n">
-        <v>2890.6</v>
+        <v>2831.95</v>
       </c>
       <c r="L61" t="n">
-        <v>2910.9</v>
+        <v>2873.62</v>
       </c>
       <c r="M61" t="n">
-        <v>2937.6</v>
+        <v>2888.45</v>
       </c>
       <c r="N61" t="n">
-        <v>2964.3</v>
+        <v>2903.27</v>
       </c>
       <c r="O61" t="n">
-        <v>2978.2</v>
+        <v>2971.8</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q61" s="6" t="n">
+        <v/>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5654,50 +5654,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>2854.4</v>
       </c>
       <c r="C62" t="n">
-        <v>2855.9</v>
+        <v>2874.1</v>
       </c>
       <c r="D62" t="n">
-        <v>2853.2</v>
+        <v>2843</v>
       </c>
       <c r="E62" t="n">
-        <v>2853.2</v>
+        <v>2859.3</v>
       </c>
       <c r="F62" t="n">
-        <v>-7</v>
+        <v>2.5</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0024</v>
+        <v>0.0009</v>
       </c>
       <c r="H62" t="n">
-        <v>2.7</v>
+        <v>31.1</v>
       </c>
       <c r="I62" t="n">
-        <v>2802.3</v>
+        <v>2797.4</v>
       </c>
       <c r="J62" t="n">
-        <v>2790.27</v>
+        <v>2829.63</v>
       </c>
       <c r="K62" t="n">
-        <v>2831.95</v>
+        <v>2840.55</v>
       </c>
       <c r="L62" t="n">
-        <v>2873.62</v>
+        <v>2851.47</v>
       </c>
       <c r="M62" t="n">
-        <v>2888.45</v>
+        <v>2873.05</v>
       </c>
       <c r="N62" t="n">
-        <v>2903.27</v>
+        <v>2894.63</v>
       </c>
       <c r="O62" t="n">
-        <v>2971.8</v>
+        <v>2894.9</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5710,11 +5710,13 @@
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5727,7 +5729,93 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2857.7</v>
+      </c>
+      <c r="C63" t="n">
+        <v>2858.8</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2849.6</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2859.3</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2811.9</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2828.57</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2843.75</v>
+      </c>
+      <c r="L63" t="n">
+        <v>2858.93</v>
+      </c>
+      <c r="M63" t="n">
+        <v>2874.85</v>
+      </c>
+      <c r="N63" t="n">
+        <v>2890.78</v>
+      </c>
+      <c r="O63" t="n">
+        <v>2905.2</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3040</v>
+        <v>3030.9</v>
       </c>
       <c r="C2" t="n">
-        <v>3068.4</v>
+        <v>3062.4</v>
       </c>
       <c r="D2" t="n">
-        <v>3023.7</v>
+        <v>2988.5</v>
       </c>
       <c r="E2" t="n">
-        <v>3035.1</v>
+        <v>3014.2</v>
       </c>
       <c r="F2" t="n">
-        <v>-10.5</v>
+        <v>-20.9</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0069</v>
       </c>
       <c r="H2" t="n">
-        <v>44.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>2979.6</v>
+        <v>2979</v>
       </c>
       <c r="J2" t="n">
-        <v>3016.48</v>
+        <v>2984.93</v>
       </c>
       <c r="K2" t="n">
-        <v>3027.85</v>
+        <v>3012.75</v>
       </c>
       <c r="L2" t="n">
-        <v>3039.23</v>
+        <v>3040.58</v>
       </c>
       <c r="M2" t="n">
-        <v>3063.35</v>
+        <v>3057.45</v>
       </c>
       <c r="N2" t="n">
-        <v>3087.48</v>
+        <v>3074.33</v>
       </c>
       <c r="O2" t="n">
-        <v>3086.1</v>
+        <v>3113.1</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -687,19 +687,19 @@
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -713,57 +713,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3030.9</v>
+        <v>3019.7</v>
       </c>
       <c r="C3" t="n">
-        <v>3062.4</v>
+        <v>3042.1</v>
       </c>
       <c r="D3" t="n">
-        <v>2988.5</v>
+        <v>3006.7</v>
       </c>
       <c r="E3" t="n">
-        <v>3014.2</v>
+        <v>3027</v>
       </c>
       <c r="F3" t="n">
-        <v>-20.9</v>
+        <v>12.8</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0042</v>
       </c>
       <c r="H3" t="n">
-        <v>73.90000000000001</v>
+        <v>35.4</v>
       </c>
       <c r="I3" t="n">
-        <v>2979</v>
+        <v>2914.6</v>
       </c>
       <c r="J3" t="n">
-        <v>2984.93</v>
+        <v>2934.68</v>
       </c>
       <c r="K3" t="n">
-        <v>3012.75</v>
+        <v>2977.25</v>
       </c>
       <c r="L3" t="n">
-        <v>3040.58</v>
+        <v>3019.82</v>
       </c>
       <c r="M3" t="n">
-        <v>3057.45</v>
+        <v>3051.15</v>
       </c>
       <c r="N3" t="n">
-        <v>3074.33</v>
+        <v>3082.47</v>
       </c>
       <c r="O3" t="n">
-        <v>3113.1</v>
+        <v>3136.3</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -771,20 +771,16 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -799,70 +795,74 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3019.7</v>
+        <v>3033.4</v>
       </c>
       <c r="C4" t="n">
-        <v>3042.1</v>
+        <v>3042.6</v>
       </c>
       <c r="D4" t="n">
-        <v>3006.7</v>
+        <v>2988.8</v>
       </c>
       <c r="E4" t="n">
-        <v>3027</v>
+        <v>2998.8</v>
       </c>
       <c r="F4" t="n">
-        <v>12.8</v>
+        <v>-28.2</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>35.4</v>
+        <v>53.8</v>
       </c>
       <c r="I4" t="n">
-        <v>2914.6</v>
+        <v>2971.3</v>
       </c>
       <c r="J4" t="n">
-        <v>2934.68</v>
+        <v>2992.9</v>
       </c>
       <c r="K4" t="n">
-        <v>2977.25</v>
+        <v>3009.3</v>
       </c>
       <c r="L4" t="n">
-        <v>3019.82</v>
+        <v>3025.7</v>
       </c>
       <c r="M4" t="n">
-        <v>3051.15</v>
+        <v>3044.7</v>
       </c>
       <c r="N4" t="n">
-        <v>3082.47</v>
+        <v>3063.7</v>
       </c>
       <c r="O4" t="n">
-        <v>3136.3</v>
+        <v>3077.5</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -881,71 +881,69 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3033.4</v>
+        <v>2994.3</v>
       </c>
       <c r="C5" t="n">
-        <v>3042.6</v>
+        <v>3004.3</v>
       </c>
       <c r="D5" t="n">
-        <v>2988.8</v>
+        <v>2943.4</v>
       </c>
       <c r="E5" t="n">
-        <v>2998.8</v>
+        <v>2971.5</v>
       </c>
       <c r="F5" t="n">
-        <v>-28.2</v>
+        <v>-27.3</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0091</v>
       </c>
       <c r="H5" t="n">
-        <v>53.8</v>
+        <v>60.9</v>
       </c>
       <c r="I5" t="n">
-        <v>2971.3</v>
+        <v>2935</v>
       </c>
       <c r="J5" t="n">
-        <v>2992.9</v>
+        <v>2936.55</v>
       </c>
       <c r="K5" t="n">
-        <v>3009.3</v>
+        <v>2971.9</v>
       </c>
       <c r="L5" t="n">
+        <v>3007.25</v>
+      </c>
+      <c r="M5" t="n">
         <v>3025.7</v>
       </c>
-      <c r="M5" t="n">
-        <v>3044.7</v>
-      </c>
       <c r="N5" t="n">
-        <v>3063.7</v>
+        <v>3044.15</v>
       </c>
       <c r="O5" t="n">
-        <v>3077.5</v>
+        <v>3096.4</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -967,57 +965,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2994.3</v>
+        <v>2965.8</v>
       </c>
       <c r="C6" t="n">
-        <v>3004.3</v>
+        <v>3014.9</v>
       </c>
       <c r="D6" t="n">
-        <v>2943.4</v>
+        <v>2964.3</v>
       </c>
       <c r="E6" t="n">
-        <v>2971.5</v>
+        <v>3008.4</v>
       </c>
       <c r="F6" t="n">
-        <v>-27.3</v>
+        <v>36.9</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0091</v>
+        <v>0.0124</v>
       </c>
       <c r="H6" t="n">
-        <v>60.9</v>
+        <v>50.6</v>
       </c>
       <c r="I6" t="n">
-        <v>2935</v>
+        <v>2882.5</v>
       </c>
       <c r="J6" t="n">
-        <v>2936.55</v>
+        <v>2909.42</v>
       </c>
       <c r="K6" t="n">
-        <v>2971.9</v>
+        <v>2941.05</v>
       </c>
       <c r="L6" t="n">
-        <v>3007.25</v>
+        <v>2972.67</v>
       </c>
       <c r="M6" t="n">
-        <v>3025.7</v>
+        <v>3001.95</v>
       </c>
       <c r="N6" t="n">
-        <v>3044.15</v>
+        <v>3031.23</v>
       </c>
       <c r="O6" t="n">
-        <v>3096.4</v>
+        <v>3065.2</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1025,19 +1023,19 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1049,59 +1047,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2965.8</v>
+        <v>3008.1</v>
       </c>
       <c r="C7" t="n">
-        <v>3014.9</v>
+        <v>3019.5</v>
       </c>
       <c r="D7" t="n">
-        <v>2964.3</v>
+        <v>2970.8</v>
       </c>
       <c r="E7" t="n">
-        <v>3008.4</v>
+        <v>2994</v>
       </c>
       <c r="F7" t="n">
-        <v>36.9</v>
+        <v>-14.4</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0048</v>
       </c>
       <c r="H7" t="n">
-        <v>50.6</v>
+        <v>48.7</v>
       </c>
       <c r="I7" t="n">
-        <v>2882.5</v>
+        <v>2913.7</v>
       </c>
       <c r="J7" t="n">
-        <v>2909.42</v>
+        <v>2967.2</v>
       </c>
       <c r="K7" t="n">
-        <v>2941.05</v>
+        <v>2983.1</v>
       </c>
       <c r="L7" t="n">
-        <v>2972.67</v>
+        <v>2999</v>
       </c>
       <c r="M7" t="n">
-        <v>3001.95</v>
+        <v>3033.7</v>
       </c>
       <c r="N7" t="n">
-        <v>3031.23</v>
+        <v>3068.4</v>
       </c>
       <c r="O7" t="n">
-        <v>3065.2</v>
+        <v>3065.5</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1109,18 +1103,18 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1133,55 +1127,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3008.1</v>
+        <v>2984.7</v>
       </c>
       <c r="C8" t="n">
-        <v>3019.5</v>
+        <v>2995.8</v>
       </c>
       <c r="D8" t="n">
-        <v>2970.8</v>
+        <v>2961.8</v>
       </c>
       <c r="E8" t="n">
-        <v>2994</v>
+        <v>2970.4</v>
       </c>
       <c r="F8" t="n">
-        <v>-14.4</v>
+        <v>-23.6</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>48.7</v>
+        <v>34</v>
       </c>
       <c r="I8" t="n">
-        <v>2913.7</v>
+        <v>2922.1</v>
       </c>
       <c r="J8" t="n">
-        <v>2967.2</v>
+        <v>2944.73</v>
       </c>
       <c r="K8" t="n">
-        <v>2983.1</v>
+        <v>2969.65</v>
       </c>
       <c r="L8" t="n">
-        <v>2999</v>
+        <v>2994.58</v>
       </c>
       <c r="M8" t="n">
-        <v>3033.7</v>
+        <v>3018.35</v>
       </c>
       <c r="N8" t="n">
-        <v>3068.4</v>
+        <v>3042.12</v>
       </c>
       <c r="O8" t="n">
-        <v>3065.5</v>
+        <v>3068.2</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1191,12 +1189,12 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1215,57 +1213,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2984.7</v>
+        <v>2967.2</v>
       </c>
       <c r="C9" t="n">
-        <v>2995.8</v>
+        <v>3029.8</v>
       </c>
       <c r="D9" t="n">
-        <v>2961.8</v>
+        <v>2956.2</v>
       </c>
       <c r="E9" t="n">
-        <v>2970.4</v>
+        <v>2979.9</v>
       </c>
       <c r="F9" t="n">
-        <v>-23.6</v>
+        <v>9.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H9" t="n">
-        <v>34</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>2922.1</v>
+        <v>2927.8</v>
       </c>
       <c r="J9" t="n">
-        <v>2944.73</v>
+        <v>2932.2</v>
       </c>
       <c r="K9" t="n">
-        <v>2969.65</v>
+        <v>2953.4</v>
       </c>
       <c r="L9" t="n">
-        <v>2994.58</v>
+        <v>2974.6</v>
       </c>
       <c r="M9" t="n">
-        <v>3018.35</v>
+        <v>2987.4</v>
       </c>
       <c r="N9" t="n">
-        <v>3042.12</v>
+        <v>3000.2</v>
       </c>
       <c r="O9" t="n">
-        <v>3068.2</v>
+        <v>3029.8</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1273,24 +1271,28 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v/>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
@@ -1299,57 +1301,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2967.2</v>
+        <v>2981.2</v>
       </c>
       <c r="C10" t="n">
-        <v>3029.8</v>
+        <v>3006.1</v>
       </c>
       <c r="D10" t="n">
-        <v>2956.2</v>
+        <v>2974.4</v>
       </c>
       <c r="E10" t="n">
-        <v>2979.9</v>
+        <v>2991.8</v>
       </c>
       <c r="F10" t="n">
-        <v>9.5</v>
+        <v>11.9</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.004</v>
       </c>
       <c r="H10" t="n">
-        <v>73.59999999999999</v>
+        <v>31.7</v>
       </c>
       <c r="I10" t="n">
-        <v>2927.8</v>
+        <v>2882.6</v>
       </c>
       <c r="J10" t="n">
-        <v>2932.2</v>
+        <v>2899.75</v>
       </c>
       <c r="K10" t="n">
-        <v>2953.4</v>
+        <v>2943.1</v>
       </c>
       <c r="L10" t="n">
-        <v>2974.6</v>
+        <v>2986.45</v>
       </c>
       <c r="M10" t="n">
-        <v>2987.4</v>
+        <v>3016.7</v>
       </c>
       <c r="N10" t="n">
-        <v>3000.2</v>
+        <v>3046.95</v>
       </c>
       <c r="O10" t="n">
-        <v>3029.8</v>
+        <v>3103.4</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1365,20 +1367,14 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v/>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
@@ -1394,50 +1390,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2981.2</v>
+        <v>2995.3</v>
       </c>
       <c r="C11" t="n">
-        <v>3006.1</v>
+        <v>3012.8</v>
       </c>
       <c r="D11" t="n">
-        <v>2974.4</v>
+        <v>2972.7</v>
       </c>
       <c r="E11" t="n">
-        <v>2991.8</v>
+        <v>2990.7</v>
       </c>
       <c r="F11" t="n">
-        <v>11.9</v>
+        <v>-1.1</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0004</v>
       </c>
       <c r="H11" t="n">
-        <v>31.7</v>
+        <v>40.1</v>
       </c>
       <c r="I11" t="n">
-        <v>2882.6</v>
+        <v>2942.7</v>
       </c>
       <c r="J11" t="n">
-        <v>2899.75</v>
+        <v>2960.87</v>
       </c>
       <c r="K11" t="n">
-        <v>2943.1</v>
+        <v>2975.95</v>
       </c>
       <c r="L11" t="n">
-        <v>2986.45</v>
+        <v>2991.03</v>
       </c>
       <c r="M11" t="n">
-        <v>3016.7</v>
+        <v>3007.65</v>
       </c>
       <c r="N11" t="n">
-        <v>3046.95</v>
+        <v>3024.28</v>
       </c>
       <c r="O11" t="n">
-        <v>3103.4</v>
+        <v>3037.8</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1445,16 +1441,20 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1469,78 +1469,78 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2995.3</v>
+        <v>2991.7</v>
       </c>
       <c r="C12" t="n">
-        <v>3012.8</v>
+        <v>2994.8</v>
       </c>
       <c r="D12" t="n">
-        <v>2972.7</v>
+        <v>2949.3</v>
       </c>
       <c r="E12" t="n">
-        <v>2990.7</v>
+        <v>2973.5</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1</v>
+        <v>-17.2</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0058</v>
       </c>
       <c r="H12" t="n">
-        <v>40.1</v>
+        <v>45.5</v>
       </c>
       <c r="I12" t="n">
-        <v>2942.7</v>
+        <v>2932.6</v>
       </c>
       <c r="J12" t="n">
-        <v>2960.87</v>
+        <v>2949.57</v>
       </c>
       <c r="K12" t="n">
-        <v>2975.95</v>
+        <v>2970.65</v>
       </c>
       <c r="L12" t="n">
-        <v>2991.03</v>
+        <v>2991.72</v>
       </c>
       <c r="M12" t="n">
-        <v>3007.65</v>
+        <v>3010.75</v>
       </c>
       <c r="N12" t="n">
-        <v>3024.28</v>
+        <v>3029.78</v>
       </c>
       <c r="O12" t="n">
-        <v>3037.8</v>
+        <v>3052.9</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1555,79 +1555,79 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2991.7</v>
+        <v>2964.5</v>
       </c>
       <c r="C13" t="n">
-        <v>2994.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D13" t="n">
-        <v>2949.3</v>
+        <v>2952.7</v>
       </c>
       <c r="E13" t="n">
-        <v>2973.5</v>
+        <v>2955.2</v>
       </c>
       <c r="F13" t="n">
-        <v>-17.2</v>
+        <v>-18.3</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0062</v>
       </c>
       <c r="H13" t="n">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="I13" t="n">
-        <v>2932.6</v>
+        <v>2903.8</v>
       </c>
       <c r="J13" t="n">
-        <v>2949.57</v>
+        <v>2928.72</v>
       </c>
       <c r="K13" t="n">
-        <v>2970.65</v>
+        <v>2950.75</v>
       </c>
       <c r="L13" t="n">
-        <v>2991.72</v>
+        <v>2972.78</v>
       </c>
       <c r="M13" t="n">
-        <v>3010.75</v>
+        <v>2996.25</v>
       </c>
       <c r="N13" t="n">
-        <v>3029.78</v>
+        <v>3019.72</v>
       </c>
       <c r="O13" t="n">
-        <v>3052.9</v>
+        <v>3040.3</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1641,57 +1641,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2964.5</v>
+        <v>2955.8</v>
       </c>
       <c r="C14" t="n">
-        <v>2998.7</v>
+        <v>2999.8</v>
       </c>
       <c r="D14" t="n">
-        <v>2952.7</v>
+        <v>2951.1</v>
       </c>
       <c r="E14" t="n">
-        <v>2955.2</v>
+        <v>2997</v>
       </c>
       <c r="F14" t="n">
-        <v>-18.3</v>
+        <v>41.8</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0141</v>
       </c>
       <c r="H14" t="n">
-        <v>46</v>
+        <v>48.7</v>
       </c>
       <c r="I14" t="n">
-        <v>2903.8</v>
+        <v>2906.7</v>
       </c>
       <c r="J14" t="n">
-        <v>2928.72</v>
+        <v>2898.95</v>
       </c>
       <c r="K14" t="n">
-        <v>2950.75</v>
+        <v>2932.2</v>
       </c>
       <c r="L14" t="n">
-        <v>2972.78</v>
+        <v>2965.45</v>
       </c>
       <c r="M14" t="n">
-        <v>2996.25</v>
+        <v>2978.2</v>
       </c>
       <c r="N14" t="n">
-        <v>3019.72</v>
+        <v>2990.95</v>
       </c>
       <c r="O14" t="n">
-        <v>3040.3</v>
+        <v>3044.7</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1699,23 +1699,23 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1734,50 +1734,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2955.8</v>
+        <v>2997</v>
       </c>
       <c r="C15" t="n">
-        <v>2999.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D15" t="n">
-        <v>2951.1</v>
+        <v>2965.5</v>
       </c>
       <c r="E15" t="n">
-        <v>2997</v>
+        <v>2969.8</v>
       </c>
       <c r="F15" t="n">
-        <v>41.8</v>
+        <v>-27.2</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0141</v>
+        <v>-0.0091</v>
       </c>
       <c r="H15" t="n">
-        <v>48.7</v>
+        <v>33.2</v>
       </c>
       <c r="I15" t="n">
-        <v>2906.7</v>
+        <v>2902.4</v>
       </c>
       <c r="J15" t="n">
-        <v>2898.95</v>
+        <v>2959.08</v>
       </c>
       <c r="K15" t="n">
-        <v>2932.2</v>
+        <v>2972.65</v>
       </c>
       <c r="L15" t="n">
-        <v>2965.45</v>
+        <v>2986.23</v>
       </c>
       <c r="M15" t="n">
-        <v>2978.2</v>
+        <v>3021.35</v>
       </c>
       <c r="N15" t="n">
-        <v>2990.95</v>
+        <v>3056.47</v>
       </c>
       <c r="O15" t="n">
-        <v>3044.7</v>
+        <v>3048.5</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1785,24 +1785,22 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
@@ -1813,60 +1811,62 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2997</v>
+        <v>2974.6</v>
       </c>
       <c r="C16" t="n">
-        <v>2998.7</v>
+        <v>2979</v>
       </c>
       <c r="D16" t="n">
-        <v>2965.5</v>
+        <v>2932.1</v>
       </c>
       <c r="E16" t="n">
-        <v>2969.8</v>
+        <v>2951.7</v>
       </c>
       <c r="F16" t="n">
-        <v>-27.2</v>
+        <v>-18.1</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0091</v>
+        <v>-0.0061</v>
       </c>
       <c r="H16" t="n">
-        <v>33.2</v>
+        <v>46.9</v>
       </c>
       <c r="I16" t="n">
-        <v>2902.4</v>
+        <v>2932.3</v>
       </c>
       <c r="J16" t="n">
-        <v>2959.08</v>
+        <v>2930.45</v>
       </c>
       <c r="K16" t="n">
-        <v>2972.65</v>
+        <v>2953.2</v>
       </c>
       <c r="L16" t="n">
-        <v>2986.23</v>
+        <v>2975.95</v>
       </c>
       <c r="M16" t="n">
-        <v>3021.35</v>
+        <v>2986.4</v>
       </c>
       <c r="N16" t="n">
-        <v>3056.47</v>
+        <v>2996.85</v>
       </c>
       <c r="O16" t="n">
-        <v>3048.5</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
+        <v>3031.9</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q16" s="6" t="n">
         <v/>
@@ -1897,74 +1897,70 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2974.6</v>
+        <v>2948.5</v>
       </c>
       <c r="C17" t="n">
-        <v>2979</v>
+        <v>2969.7</v>
       </c>
       <c r="D17" t="n">
-        <v>2932.1</v>
+        <v>2934.5</v>
       </c>
       <c r="E17" t="n">
-        <v>2951.7</v>
+        <v>2941.3</v>
       </c>
       <c r="F17" t="n">
-        <v>-18.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0035</v>
       </c>
       <c r="H17" t="n">
-        <v>46.9</v>
+        <v>35.2</v>
       </c>
       <c r="I17" t="n">
-        <v>2932.3</v>
+        <v>2885.2</v>
       </c>
       <c r="J17" t="n">
-        <v>2930.45</v>
+        <v>2902.88</v>
       </c>
       <c r="K17" t="n">
-        <v>2953.2</v>
+        <v>2928.25</v>
       </c>
       <c r="L17" t="n">
-        <v>2975.95</v>
+        <v>2953.62</v>
       </c>
       <c r="M17" t="n">
-        <v>2986.4</v>
+        <v>2975.15</v>
       </c>
       <c r="N17" t="n">
-        <v>2996.85</v>
+        <v>2996.67</v>
       </c>
       <c r="O17" t="n">
-        <v>3031.9</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3025.9</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
       </c>
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R17" s="6" t="n">
+        <v/>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1983,57 +1979,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2948.5</v>
+        <v>2955.5</v>
       </c>
       <c r="C18" t="n">
-        <v>2969.7</v>
+        <v>2985.9</v>
       </c>
       <c r="D18" t="n">
-        <v>2934.5</v>
+        <v>2941.2</v>
       </c>
       <c r="E18" t="n">
-        <v>2941.3</v>
+        <v>2960</v>
       </c>
       <c r="F18" t="n">
-        <v>-10.4</v>
+        <v>18.7</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0064</v>
       </c>
       <c r="H18" t="n">
-        <v>35.2</v>
+        <v>44.7</v>
       </c>
       <c r="I18" t="n">
-        <v>2885.2</v>
+        <v>2899.3</v>
       </c>
       <c r="J18" t="n">
-        <v>2902.88</v>
+        <v>2900.7</v>
       </c>
       <c r="K18" t="n">
-        <v>2928.25</v>
+        <v>2923.7</v>
       </c>
       <c r="L18" t="n">
-        <v>2953.62</v>
+        <v>2946.7</v>
       </c>
       <c r="M18" t="n">
-        <v>2975.15</v>
+        <v>2958.9</v>
       </c>
       <c r="N18" t="n">
-        <v>2996.67</v>
+        <v>2971.1</v>
       </c>
       <c r="O18" t="n">
-        <v>3025.9</v>
+        <v>3004.9</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2044,16 +2040,20 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2063,59 +2063,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2955.5</v>
+        <v>2961.5</v>
       </c>
       <c r="C19" t="n">
-        <v>2985.9</v>
+        <v>2968.3</v>
       </c>
       <c r="D19" t="n">
-        <v>2941.2</v>
+        <v>2933.4</v>
       </c>
       <c r="E19" t="n">
-        <v>2960</v>
+        <v>2964.5</v>
       </c>
       <c r="F19" t="n">
-        <v>18.7</v>
+        <v>4.5</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0015</v>
       </c>
       <c r="H19" t="n">
-        <v>44.7</v>
+        <v>34.9</v>
       </c>
       <c r="I19" t="n">
-        <v>2899.3</v>
+        <v>2896.5</v>
       </c>
       <c r="J19" t="n">
-        <v>2900.7</v>
+        <v>2913.53</v>
       </c>
       <c r="K19" t="n">
-        <v>2923.7</v>
+        <v>2937.65</v>
       </c>
       <c r="L19" t="n">
-        <v>2946.7</v>
+        <v>2961.77</v>
       </c>
       <c r="M19" t="n">
-        <v>2958.9</v>
+        <v>2982.35</v>
       </c>
       <c r="N19" t="n">
-        <v>2971.1</v>
+        <v>3002.92</v>
       </c>
       <c r="O19" t="n">
-        <v>3004.9</v>
+        <v>3030.6</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2123,23 +2119,21 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2149,70 +2143,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2961.5</v>
+        <v>2966.9</v>
       </c>
       <c r="C20" t="n">
-        <v>2968.3</v>
+        <v>2978.3</v>
       </c>
       <c r="D20" t="n">
-        <v>2933.4</v>
+        <v>2902.3</v>
       </c>
       <c r="E20" t="n">
-        <v>2964.5</v>
+        <v>2915.4</v>
       </c>
       <c r="F20" t="n">
-        <v>4.5</v>
+        <v>-49.1</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0166</v>
       </c>
       <c r="H20" t="n">
-        <v>34.9</v>
+        <v>76</v>
       </c>
       <c r="I20" t="n">
-        <v>2896.5</v>
+        <v>2898.5</v>
       </c>
       <c r="J20" t="n">
-        <v>2913.53</v>
+        <v>2936.42</v>
       </c>
       <c r="K20" t="n">
-        <v>2937.65</v>
+        <v>2947.05</v>
       </c>
       <c r="L20" t="n">
-        <v>2961.77</v>
+        <v>2957.67</v>
       </c>
       <c r="M20" t="n">
-        <v>2982.35</v>
+        <v>2981.95</v>
       </c>
       <c r="N20" t="n">
-        <v>3002.92</v>
+        <v>3006.23</v>
       </c>
       <c r="O20" t="n">
-        <v>3030.6</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
+        <v>3003.2</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2224,88 +2226,84 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W20" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2966.9</v>
+        <v>2906.6</v>
       </c>
       <c r="C21" t="n">
-        <v>2978.3</v>
+        <v>2957.9</v>
       </c>
       <c r="D21" t="n">
-        <v>2902.3</v>
+        <v>2905.6</v>
       </c>
       <c r="E21" t="n">
-        <v>2915.4</v>
+        <v>2954.3</v>
       </c>
       <c r="F21" t="n">
-        <v>-49.1</v>
+        <v>38.9</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0166</v>
+        <v>0.0133</v>
       </c>
       <c r="H21" t="n">
-        <v>76</v>
+        <v>52.3</v>
       </c>
       <c r="I21" t="n">
-        <v>2898.5</v>
+        <v>2826.3</v>
       </c>
       <c r="J21" t="n">
-        <v>2936.42</v>
+        <v>2826.95</v>
       </c>
       <c r="K21" t="n">
-        <v>2947.05</v>
+        <v>2877.4</v>
       </c>
       <c r="L21" t="n">
-        <v>2957.67</v>
+        <v>2927.85</v>
       </c>
       <c r="M21" t="n">
-        <v>2981.95</v>
+        <v>2953.4</v>
       </c>
       <c r="N21" t="n">
-        <v>3006.23</v>
+        <v>2978.95</v>
       </c>
       <c r="O21" t="n">
-        <v>3003.2</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
+        <v>3054.3</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
@@ -2319,76 +2317,78 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2906.6</v>
+        <v>2954</v>
       </c>
       <c r="C22" t="n">
-        <v>2957.9</v>
+        <v>2976.3</v>
       </c>
       <c r="D22" t="n">
-        <v>2905.6</v>
+        <v>2905.3</v>
       </c>
       <c r="E22" t="n">
-        <v>2954.3</v>
+        <v>2938</v>
       </c>
       <c r="F22" t="n">
-        <v>38.9</v>
+        <v>-16.3</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0055</v>
       </c>
       <c r="H22" t="n">
-        <v>52.3</v>
+        <v>71</v>
       </c>
       <c r="I22" t="n">
-        <v>2826.3</v>
+        <v>2853.3</v>
       </c>
       <c r="J22" t="n">
-        <v>2826.95</v>
+        <v>2913.28</v>
       </c>
       <c r="K22" t="n">
-        <v>2877.4</v>
+        <v>2928.15</v>
       </c>
       <c r="L22" t="n">
-        <v>2927.85</v>
+        <v>2943.03</v>
       </c>
       <c r="M22" t="n">
-        <v>2953.4</v>
+        <v>2980.45</v>
       </c>
       <c r="N22" t="n">
-        <v>2978.95</v>
+        <v>3017.87</v>
       </c>
       <c r="O22" t="n">
-        <v>3054.3</v>
+        <v>3010.2</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2403,78 +2403,76 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2954</v>
+        <v>2950</v>
       </c>
       <c r="C23" t="n">
-        <v>2976.3</v>
+        <v>2994.6</v>
       </c>
       <c r="D23" t="n">
-        <v>2905.3</v>
+        <v>2948.4</v>
       </c>
       <c r="E23" t="n">
-        <v>2938</v>
+        <v>2989.3</v>
       </c>
       <c r="F23" t="n">
-        <v>-16.3</v>
+        <v>51.3</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0175</v>
       </c>
       <c r="H23" t="n">
-        <v>71</v>
+        <v>46.2</v>
       </c>
       <c r="I23" t="n">
-        <v>2853.3</v>
+        <v>2834.3</v>
       </c>
       <c r="J23" t="n">
-        <v>2913.28</v>
+        <v>2865.6</v>
       </c>
       <c r="K23" t="n">
-        <v>2928.15</v>
+        <v>2902.5</v>
       </c>
       <c r="L23" t="n">
-        <v>2943.03</v>
+        <v>2939.4</v>
       </c>
       <c r="M23" t="n">
-        <v>2980.45</v>
+        <v>2973.5</v>
       </c>
       <c r="N23" t="n">
-        <v>3017.87</v>
+        <v>3007.6</v>
       </c>
       <c r="O23" t="n">
-        <v>3010.2</v>
+        <v>3047.3</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2489,57 +2487,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2950</v>
+        <v>2992.4</v>
       </c>
       <c r="C24" t="n">
-        <v>2994.6</v>
+        <v>3051.8</v>
       </c>
       <c r="D24" t="n">
-        <v>2948.4</v>
+        <v>2986.1</v>
       </c>
       <c r="E24" t="n">
-        <v>2989.3</v>
+        <v>3044.7</v>
       </c>
       <c r="F24" t="n">
-        <v>51.3</v>
+        <v>55.4</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0185</v>
       </c>
       <c r="H24" t="n">
-        <v>46.2</v>
+        <v>65.7</v>
       </c>
       <c r="I24" t="n">
-        <v>2834.3</v>
+        <v>2902.2</v>
       </c>
       <c r="J24" t="n">
-        <v>2865.6</v>
+        <v>2952</v>
       </c>
       <c r="K24" t="n">
-        <v>2902.5</v>
+        <v>2966.2</v>
       </c>
       <c r="L24" t="n">
-        <v>2939.4</v>
+        <v>2980.4</v>
       </c>
       <c r="M24" t="n">
-        <v>2973.5</v>
+        <v>3012.4</v>
       </c>
       <c r="N24" t="n">
-        <v>3007.6</v>
+        <v>3044.4</v>
       </c>
       <c r="O24" t="n">
-        <v>3047.3</v>
+        <v>3040.8</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2557,73 +2555,73 @@
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W24" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2992.4</v>
+        <v>3049.1</v>
       </c>
       <c r="C25" t="n">
-        <v>3051.8</v>
+        <v>3058.3</v>
       </c>
       <c r="D25" t="n">
-        <v>2986.1</v>
+        <v>3023.3</v>
       </c>
       <c r="E25" t="n">
-        <v>3044.7</v>
+        <v>3025.4</v>
       </c>
       <c r="F25" t="n">
-        <v>55.4</v>
+        <v>-19.3</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0063</v>
       </c>
       <c r="H25" t="n">
-        <v>65.7</v>
+        <v>35</v>
       </c>
       <c r="I25" t="n">
-        <v>2902.2</v>
+        <v>2920.4</v>
       </c>
       <c r="J25" t="n">
-        <v>2952</v>
+        <v>2991.87</v>
       </c>
       <c r="K25" t="n">
-        <v>2966.2</v>
+        <v>3011.85</v>
       </c>
       <c r="L25" t="n">
-        <v>2980.4</v>
+        <v>3031.83</v>
       </c>
       <c r="M25" t="n">
-        <v>3012.4</v>
+        <v>3077.55</v>
       </c>
       <c r="N25" t="n">
-        <v>3044.4</v>
+        <v>3123.27</v>
       </c>
       <c r="O25" t="n">
-        <v>3040.8</v>
+        <v>3117.5</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2634,80 +2632,78 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3049.1</v>
+        <v>3028.5</v>
       </c>
       <c r="C26" t="n">
-        <v>3058.3</v>
+        <v>3041</v>
       </c>
       <c r="D26" t="n">
-        <v>3023.3</v>
+        <v>3004.9</v>
       </c>
       <c r="E26" t="n">
-        <v>3025.4</v>
+        <v>3009.1</v>
       </c>
       <c r="F26" t="n">
-        <v>-19.3</v>
+        <v>-16.3</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0054</v>
       </c>
       <c r="H26" t="n">
-        <v>35</v>
+        <v>36.1</v>
       </c>
       <c r="I26" t="n">
-        <v>2920.4</v>
+        <v>2988.3</v>
       </c>
       <c r="J26" t="n">
-        <v>2991.87</v>
+        <v>2982.7</v>
       </c>
       <c r="K26" t="n">
-        <v>3011.85</v>
+        <v>3007.9</v>
       </c>
       <c r="L26" t="n">
-        <v>3031.83</v>
+        <v>3033.1</v>
       </c>
       <c r="M26" t="n">
-        <v>3077.55</v>
+        <v>3042.9</v>
       </c>
       <c r="N26" t="n">
-        <v>3123.27</v>
+        <v>3052.7</v>
       </c>
       <c r="O26" t="n">
-        <v>3117.5</v>
+        <v>3093.3</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2715,12 +2711,14 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2739,57 +2737,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3028.5</v>
+        <v>3008.5</v>
       </c>
       <c r="C27" t="n">
-        <v>3041</v>
+        <v>3046.8</v>
       </c>
       <c r="D27" t="n">
-        <v>3004.9</v>
+        <v>3002</v>
       </c>
       <c r="E27" t="n">
-        <v>3009.1</v>
+        <v>3041.6</v>
       </c>
       <c r="F27" t="n">
-        <v>-16.3</v>
+        <v>32.5</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0054</v>
+        <v>0.0108</v>
       </c>
       <c r="H27" t="n">
-        <v>36.1</v>
+        <v>44.8</v>
       </c>
       <c r="I27" t="n">
-        <v>2988.3</v>
+        <v>2968.8</v>
       </c>
       <c r="J27" t="n">
-        <v>2982.7</v>
+        <v>2966.08</v>
       </c>
       <c r="K27" t="n">
-        <v>3007.9</v>
+        <v>2991.05</v>
       </c>
       <c r="L27" t="n">
-        <v>3033.1</v>
+        <v>3016.03</v>
       </c>
       <c r="M27" t="n">
-        <v>3042.9</v>
+        <v>3027.15</v>
       </c>
       <c r="N27" t="n">
-        <v>3052.7</v>
+        <v>3038.28</v>
       </c>
       <c r="O27" t="n">
-        <v>3093.3</v>
+        <v>3077.1</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2797,22 +2795,24 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
@@ -2823,57 +2823,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3008.5</v>
+        <v>3038.9</v>
       </c>
       <c r="C28" t="n">
-        <v>3046.8</v>
+        <v>3044.6</v>
       </c>
       <c r="D28" t="n">
-        <v>3002</v>
+        <v>3016</v>
       </c>
       <c r="E28" t="n">
-        <v>3041.6</v>
+        <v>3025</v>
       </c>
       <c r="F28" t="n">
-        <v>32.5</v>
+        <v>-16.6</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0108</v>
+        <v>-0.0055</v>
       </c>
       <c r="H28" t="n">
-        <v>44.8</v>
+        <v>28.6</v>
       </c>
       <c r="I28" t="n">
-        <v>2968.8</v>
+        <v>2957.2</v>
       </c>
       <c r="J28" t="n">
-        <v>2966.08</v>
+        <v>3005.4</v>
       </c>
       <c r="K28" t="n">
-        <v>2991.05</v>
+        <v>3019.2</v>
       </c>
       <c r="L28" t="n">
-        <v>3016.03</v>
+        <v>3033</v>
       </c>
       <c r="M28" t="n">
-        <v>3027.15</v>
+        <v>3064</v>
       </c>
       <c r="N28" t="n">
-        <v>3038.28</v>
+        <v>3095</v>
       </c>
       <c r="O28" t="n">
-        <v>3077.1</v>
+        <v>3091.6</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2881,24 +2881,22 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
@@ -2909,57 +2907,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3038.9</v>
+        <v>3024.7</v>
       </c>
       <c r="C29" t="n">
-        <v>3044.6</v>
+        <v>3045.8</v>
       </c>
       <c r="D29" t="n">
-        <v>3016</v>
+        <v>3019.9</v>
       </c>
       <c r="E29" t="n">
-        <v>3025</v>
+        <v>3035.5</v>
       </c>
       <c r="F29" t="n">
-        <v>-16.6</v>
+        <v>10.5</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0035</v>
       </c>
       <c r="H29" t="n">
-        <v>28.6</v>
+        <v>25.9</v>
       </c>
       <c r="I29" t="n">
-        <v>2957.2</v>
+        <v>2987.4</v>
       </c>
       <c r="J29" t="n">
-        <v>3005.4</v>
+        <v>2993.75</v>
       </c>
       <c r="K29" t="n">
-        <v>3019.2</v>
+        <v>3010.7</v>
       </c>
       <c r="L29" t="n">
-        <v>3033</v>
+        <v>3027.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3064</v>
+        <v>3039.3</v>
       </c>
       <c r="N29" t="n">
-        <v>3095</v>
+        <v>3050.95</v>
       </c>
       <c r="O29" t="n">
-        <v>3091.6</v>
+        <v>3073.2</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2967,19 +2965,19 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
       <c r="U29" s="8" t="n">
         <v/>
       </c>
@@ -2991,59 +2989,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3024.7</v>
+        <v>3036.1</v>
       </c>
       <c r="C30" t="n">
-        <v>3045.8</v>
+        <v>3060</v>
       </c>
       <c r="D30" t="n">
-        <v>3019.9</v>
+        <v>3033.1</v>
       </c>
       <c r="E30" t="n">
-        <v>3035.5</v>
+        <v>3052.8</v>
       </c>
       <c r="F30" t="n">
-        <v>10.5</v>
+        <v>17.3</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0057</v>
       </c>
       <c r="H30" t="n">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
       <c r="I30" t="n">
-        <v>2987.4</v>
+        <v>2994</v>
       </c>
       <c r="J30" t="n">
-        <v>2993.75</v>
+        <v>3010.92</v>
       </c>
       <c r="K30" t="n">
-        <v>3010.7</v>
+        <v>3022.55</v>
       </c>
       <c r="L30" t="n">
-        <v>3027.65</v>
+        <v>3034.17</v>
       </c>
       <c r="M30" t="n">
-        <v>3039.3</v>
+        <v>3048.45</v>
       </c>
       <c r="N30" t="n">
-        <v>3050.95</v>
+        <v>3062.73</v>
       </c>
       <c r="O30" t="n">
-        <v>3073.2</v>
+        <v>3071.7</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3080,50 +3074,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3036.1</v>
+        <v>3056.2</v>
       </c>
       <c r="C31" t="n">
-        <v>3060</v>
+        <v>3076.3</v>
       </c>
       <c r="D31" t="n">
-        <v>3033.1</v>
+        <v>3052.5</v>
       </c>
       <c r="E31" t="n">
-        <v>3052.8</v>
+        <v>3060.2</v>
       </c>
       <c r="F31" t="n">
-        <v>17.3</v>
+        <v>7.4</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0024</v>
       </c>
       <c r="H31" t="n">
-        <v>26.9</v>
+        <v>23.8</v>
       </c>
       <c r="I31" t="n">
-        <v>2994</v>
+        <v>3006.2</v>
       </c>
       <c r="J31" t="n">
-        <v>3010.92</v>
+        <v>3029.03</v>
       </c>
       <c r="K31" t="n">
-        <v>3022.55</v>
+        <v>3039.35</v>
       </c>
       <c r="L31" t="n">
-        <v>3034.17</v>
+        <v>3049.68</v>
       </c>
       <c r="M31" t="n">
-        <v>3048.45</v>
+        <v>3066.25</v>
       </c>
       <c r="N31" t="n">
-        <v>3062.73</v>
+        <v>3082.82</v>
       </c>
       <c r="O31" t="n">
-        <v>3071.7</v>
+        <v>3086.9</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3160,50 +3154,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3056.2</v>
+        <v>3062.2</v>
       </c>
       <c r="C32" t="n">
         <v>3076.3</v>
       </c>
       <c r="D32" t="n">
-        <v>3052.5</v>
+        <v>3051.7</v>
       </c>
       <c r="E32" t="n">
-        <v>3060.2</v>
+        <v>3074.9</v>
       </c>
       <c r="F32" t="n">
-        <v>7.4</v>
+        <v>14.7</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0048</v>
       </c>
       <c r="H32" t="n">
-        <v>23.8</v>
+        <v>24.6</v>
       </c>
       <c r="I32" t="n">
-        <v>3006.2</v>
+        <v>3028.7</v>
       </c>
       <c r="J32" t="n">
-        <v>3029.03</v>
+        <v>3034.3</v>
       </c>
       <c r="K32" t="n">
-        <v>3039.35</v>
+        <v>3048.3</v>
       </c>
       <c r="L32" t="n">
-        <v>3049.68</v>
+        <v>3062.3</v>
       </c>
       <c r="M32" t="n">
-        <v>3066.25</v>
+        <v>3072.1</v>
       </c>
       <c r="N32" t="n">
-        <v>3082.82</v>
+        <v>3081.9</v>
       </c>
       <c r="O32" t="n">
-        <v>3086.9</v>
+        <v>3100.1</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3235,55 +3229,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3062.2</v>
+        <v>3073.5</v>
       </c>
       <c r="C33" t="n">
-        <v>3076.3</v>
+        <v>3079.9</v>
       </c>
       <c r="D33" t="n">
-        <v>3051.7</v>
+        <v>3055.9</v>
       </c>
       <c r="E33" t="n">
-        <v>3074.9</v>
+        <v>3064.9</v>
       </c>
       <c r="F33" t="n">
-        <v>14.7</v>
+        <v>-10</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.0033</v>
       </c>
       <c r="H33" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="I33" t="n">
-        <v>3028.7</v>
+        <v>3027.1</v>
       </c>
       <c r="J33" t="n">
-        <v>3034.3</v>
+        <v>3055.75</v>
       </c>
       <c r="K33" t="n">
-        <v>3048.3</v>
+        <v>3062.6</v>
       </c>
       <c r="L33" t="n">
-        <v>3062.3</v>
+        <v>3069.45</v>
       </c>
       <c r="M33" t="n">
-        <v>3072.1</v>
+        <v>3087.2</v>
       </c>
       <c r="N33" t="n">
-        <v>3081.9</v>
+        <v>3104.95</v>
       </c>
       <c r="O33" t="n">
-        <v>3100.1</v>
+        <v>3100.9</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3291,18 +3289,18 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
+      <c r="R33" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3324,60 +3322,64 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3073.5</v>
+        <v>3063.7</v>
       </c>
       <c r="C34" t="n">
-        <v>3079.9</v>
+        <v>3066.6</v>
       </c>
       <c r="D34" t="n">
-        <v>3055.9</v>
+        <v>3024.1</v>
       </c>
       <c r="E34" t="n">
-        <v>3064.9</v>
+        <v>3026.4</v>
       </c>
       <c r="F34" t="n">
-        <v>-10</v>
+        <v>-38.5</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0126</v>
       </c>
       <c r="H34" t="n">
-        <v>24</v>
+        <v>42.5</v>
       </c>
       <c r="I34" t="n">
-        <v>3027.1</v>
+        <v>3031.9</v>
       </c>
       <c r="J34" t="n">
-        <v>3055.75</v>
+        <v>3039.4</v>
       </c>
       <c r="K34" t="n">
-        <v>3062.6</v>
+        <v>3052.9</v>
       </c>
       <c r="L34" t="n">
-        <v>3069.45</v>
+        <v>3066.4</v>
       </c>
       <c r="M34" t="n">
-        <v>3087.2</v>
+        <v>3076.9</v>
       </c>
       <c r="N34" t="n">
-        <v>3104.95</v>
+        <v>3087.4</v>
       </c>
       <c r="O34" t="n">
-        <v>3100.9</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
+        <v>3103.9</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S34" s="7" t="inlineStr">
@@ -3394,88 +3396,80 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W34" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3063.7</v>
+        <v>3025.9</v>
       </c>
       <c r="C35" t="n">
-        <v>3066.6</v>
+        <v>3059.1</v>
       </c>
       <c r="D35" t="n">
-        <v>3024.1</v>
+        <v>3019.8</v>
       </c>
       <c r="E35" t="n">
-        <v>3026.4</v>
+        <v>3039.9</v>
       </c>
       <c r="F35" t="n">
-        <v>-38.5</v>
+        <v>13.5</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0045</v>
       </c>
       <c r="H35" t="n">
-        <v>42.5</v>
+        <v>39.3</v>
       </c>
       <c r="I35" t="n">
-        <v>3031.9</v>
+        <v>2981.6</v>
       </c>
       <c r="J35" t="n">
-        <v>3039.4</v>
+        <v>2974.42</v>
       </c>
       <c r="K35" t="n">
-        <v>3052.9</v>
+        <v>3005.15</v>
       </c>
       <c r="L35" t="n">
-        <v>3066.4</v>
+        <v>3035.88</v>
       </c>
       <c r="M35" t="n">
-        <v>3076.9</v>
+        <v>3047.65</v>
       </c>
       <c r="N35" t="n">
-        <v>3087.4</v>
+        <v>3059.42</v>
       </c>
       <c r="O35" t="n">
-        <v>3103.9</v>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
+        <v>3109.1</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
@@ -3487,75 +3481,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3025.9</v>
+        <v>3041.4</v>
       </c>
       <c r="C36" t="n">
-        <v>3059.1</v>
+        <v>3048.5</v>
       </c>
       <c r="D36" t="n">
-        <v>3019.8</v>
+        <v>2993.2</v>
       </c>
       <c r="E36" t="n">
-        <v>3039.9</v>
+        <v>2999.2</v>
       </c>
       <c r="F36" t="n">
-        <v>13.5</v>
+        <v>-40.7</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0134</v>
       </c>
       <c r="H36" t="n">
-        <v>39.3</v>
+        <v>55.3</v>
       </c>
       <c r="I36" t="n">
-        <v>2981.6</v>
+        <v>2980.5</v>
       </c>
       <c r="J36" t="n">
-        <v>2974.42</v>
+        <v>3000.82</v>
       </c>
       <c r="K36" t="n">
-        <v>3005.15</v>
+        <v>3020.25</v>
       </c>
       <c r="L36" t="n">
-        <v>3035.88</v>
+        <v>3039.67</v>
       </c>
       <c r="M36" t="n">
-        <v>3047.65</v>
+        <v>3059.55</v>
       </c>
       <c r="N36" t="n">
-        <v>3059.42</v>
+        <v>3079.42</v>
       </c>
       <c r="O36" t="n">
-        <v>3109.1</v>
+        <v>3098.4</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3567,81 +3567,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3041.4</v>
+        <v>2999.6</v>
       </c>
       <c r="C37" t="n">
-        <v>3048.5</v>
+        <v>3026.7</v>
       </c>
       <c r="D37" t="n">
-        <v>2993.2</v>
+        <v>2997.9</v>
       </c>
       <c r="E37" t="n">
-        <v>2999.2</v>
+        <v>3022.1</v>
       </c>
       <c r="F37" t="n">
-        <v>-40.7</v>
+        <v>22.9</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0134</v>
+        <v>0.0076</v>
       </c>
       <c r="H37" t="n">
-        <v>55.3</v>
+        <v>28.8</v>
       </c>
       <c r="I37" t="n">
-        <v>2980.5</v>
+        <v>2937.9</v>
       </c>
       <c r="J37" t="n">
-        <v>3000.82</v>
+        <v>2933.07</v>
       </c>
       <c r="K37" t="n">
-        <v>3020.25</v>
+        <v>2971.55</v>
       </c>
       <c r="L37" t="n">
-        <v>3039.67</v>
+        <v>3010.02</v>
       </c>
       <c r="M37" t="n">
-        <v>3059.55</v>
+        <v>3026.85</v>
       </c>
       <c r="N37" t="n">
-        <v>3079.42</v>
+        <v>3043.67</v>
       </c>
       <c r="O37" t="n">
-        <v>3098.4</v>
+        <v>3103.8</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
@@ -3653,75 +3647,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2999.6</v>
+        <v>3023</v>
       </c>
       <c r="C38" t="n">
-        <v>3026.7</v>
+        <v>3028.9</v>
       </c>
       <c r="D38" t="n">
-        <v>2997.9</v>
+        <v>2996</v>
       </c>
       <c r="E38" t="n">
-        <v>3022.1</v>
+        <v>3001.6</v>
       </c>
       <c r="F38" t="n">
-        <v>22.9</v>
+        <v>-20.5</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0076</v>
+        <v>-0.0068</v>
       </c>
       <c r="H38" t="n">
-        <v>28.8</v>
+        <v>32.9</v>
       </c>
       <c r="I38" t="n">
-        <v>2937.9</v>
+        <v>2969.1</v>
       </c>
       <c r="J38" t="n">
-        <v>2933.07</v>
+        <v>2998.2</v>
       </c>
       <c r="K38" t="n">
-        <v>2971.55</v>
+        <v>3007.7</v>
       </c>
       <c r="L38" t="n">
-        <v>3010.02</v>
+        <v>3017.2</v>
       </c>
       <c r="M38" t="n">
-        <v>3026.85</v>
+        <v>3036.5</v>
       </c>
       <c r="N38" t="n">
-        <v>3043.67</v>
+        <v>3055.8</v>
       </c>
       <c r="O38" t="n">
-        <v>3103.8</v>
+        <v>3055.5</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
+      <c r="Q38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3735,79 +3735,77 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3023</v>
+        <v>3004.6</v>
       </c>
       <c r="C39" t="n">
-        <v>3028.9</v>
+        <v>3025.4</v>
       </c>
       <c r="D39" t="n">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="E39" t="n">
-        <v>3001.6</v>
+        <v>3014.4</v>
       </c>
       <c r="F39" t="n">
-        <v>-20.5</v>
+        <v>12.8</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0043</v>
       </c>
       <c r="H39" t="n">
-        <v>32.9</v>
+        <v>28.4</v>
       </c>
       <c r="I39" t="n">
-        <v>2969.1</v>
+        <v>2963.1</v>
       </c>
       <c r="J39" t="n">
-        <v>2998.2</v>
+        <v>2963.28</v>
       </c>
       <c r="K39" t="n">
-        <v>3007.7</v>
+        <v>2985.15</v>
       </c>
       <c r="L39" t="n">
-        <v>3017.2</v>
+        <v>3007.03</v>
       </c>
       <c r="M39" t="n">
-        <v>3036.5</v>
+        <v>3018.05</v>
       </c>
       <c r="N39" t="n">
-        <v>3055.8</v>
+        <v>3029.08</v>
       </c>
       <c r="O39" t="n">
-        <v>3055.5</v>
+        <v>3061.8</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3821,57 +3819,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3004.6</v>
+        <v>3014.6</v>
       </c>
       <c r="C40" t="n">
-        <v>3025.4</v>
+        <v>3020.5</v>
       </c>
       <c r="D40" t="n">
-        <v>2997</v>
+        <v>3002.6</v>
       </c>
       <c r="E40" t="n">
-        <v>3014.4</v>
+        <v>3010.1</v>
       </c>
       <c r="F40" t="n">
-        <v>12.8</v>
+        <v>-4.3</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0014</v>
       </c>
       <c r="H40" t="n">
-        <v>28.4</v>
+        <v>17.9</v>
       </c>
       <c r="I40" t="n">
-        <v>2963.1</v>
+        <v>2968.6</v>
       </c>
       <c r="J40" t="n">
-        <v>2963.28</v>
+        <v>2987.6</v>
       </c>
       <c r="K40" t="n">
-        <v>2985.15</v>
+        <v>3000.2</v>
       </c>
       <c r="L40" t="n">
-        <v>3007.03</v>
+        <v>3012.8</v>
       </c>
       <c r="M40" t="n">
-        <v>3018.05</v>
+        <v>3028.6</v>
       </c>
       <c r="N40" t="n">
-        <v>3029.08</v>
+        <v>3044.4</v>
       </c>
       <c r="O40" t="n">
-        <v>3061.8</v>
+        <v>3053.8</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3882,15 +3880,13 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3905,57 +3901,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3014.6</v>
+        <v>3016.9</v>
       </c>
       <c r="C41" t="n">
-        <v>3020.5</v>
+        <v>3024.2</v>
       </c>
       <c r="D41" t="n">
-        <v>3002.6</v>
+        <v>3002.1</v>
       </c>
       <c r="E41" t="n">
-        <v>3010.1</v>
+        <v>3019</v>
       </c>
       <c r="F41" t="n">
-        <v>-4.3</v>
+        <v>8.9</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0014</v>
+        <v>0.003</v>
       </c>
       <c r="H41" t="n">
-        <v>17.9</v>
+        <v>22.1</v>
       </c>
       <c r="I41" t="n">
-        <v>2968.6</v>
+        <v>2984.7</v>
       </c>
       <c r="J41" t="n">
-        <v>2987.6</v>
+        <v>2991.48</v>
       </c>
       <c r="K41" t="n">
-        <v>3000.2</v>
+        <v>3001.15</v>
       </c>
       <c r="L41" t="n">
-        <v>3012.8</v>
+        <v>3010.83</v>
       </c>
       <c r="M41" t="n">
-        <v>3028.6</v>
+        <v>3019.05</v>
       </c>
       <c r="N41" t="n">
-        <v>3044.4</v>
+        <v>3027.28</v>
       </c>
       <c r="O41" t="n">
-        <v>3053.8</v>
+        <v>3038.4</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3966,13 +3962,15 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3987,77 +3985,81 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3016.9</v>
+        <v>3019.6</v>
       </c>
       <c r="C42" t="n">
-        <v>3024.2</v>
+        <v>3025.5</v>
       </c>
       <c r="D42" t="n">
-        <v>3002.1</v>
+        <v>2976.6</v>
       </c>
       <c r="E42" t="n">
-        <v>3019</v>
+        <v>2977.5</v>
       </c>
       <c r="F42" t="n">
-        <v>8.9</v>
+        <v>-41.5</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0137</v>
       </c>
       <c r="H42" t="n">
-        <v>22.1</v>
+        <v>48.9</v>
       </c>
       <c r="I42" t="n">
-        <v>2984.7</v>
+        <v>2980</v>
       </c>
       <c r="J42" t="n">
-        <v>2991.48</v>
+        <v>2999.83</v>
       </c>
       <c r="K42" t="n">
-        <v>3001.15</v>
+        <v>3007.95</v>
       </c>
       <c r="L42" t="n">
-        <v>3010.83</v>
+        <v>3016.08</v>
       </c>
       <c r="M42" t="n">
-        <v>3019.05</v>
+        <v>3030.05</v>
       </c>
       <c r="N42" t="n">
-        <v>3027.28</v>
+        <v>3044.02</v>
       </c>
       <c r="O42" t="n">
-        <v>3038.4</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
+        <v>3046.3</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4071,73 +4073,69 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3019.6</v>
+        <v>2971</v>
       </c>
       <c r="C43" t="n">
-        <v>3025.5</v>
+        <v>2982.5</v>
       </c>
       <c r="D43" t="n">
-        <v>2976.6</v>
+        <v>2946.1</v>
       </c>
       <c r="E43" t="n">
-        <v>2977.5</v>
+        <v>2958.7</v>
       </c>
       <c r="F43" t="n">
-        <v>-41.5</v>
+        <v>-18.8</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0063</v>
       </c>
       <c r="H43" t="n">
-        <v>48.9</v>
+        <v>36.4</v>
       </c>
       <c r="I43" t="n">
-        <v>2980</v>
+        <v>2927.7</v>
       </c>
       <c r="J43" t="n">
-        <v>2999.83</v>
+        <v>2916.83</v>
       </c>
       <c r="K43" t="n">
-        <v>3007.95</v>
+        <v>2953.05</v>
       </c>
       <c r="L43" t="n">
-        <v>3016.08</v>
+        <v>2989.28</v>
       </c>
       <c r="M43" t="n">
-        <v>3030.05</v>
+        <v>3001.95</v>
       </c>
       <c r="N43" t="n">
-        <v>3044.02</v>
+        <v>3014.62</v>
       </c>
       <c r="O43" t="n">
-        <v>3046.3</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
+        <v>3074.4</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4157,69 +4155,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2971</v>
+        <v>2958</v>
       </c>
       <c r="C44" t="n">
-        <v>2982.5</v>
+        <v>2964.6</v>
       </c>
       <c r="D44" t="n">
-        <v>2946.1</v>
+        <v>2918.9</v>
       </c>
       <c r="E44" t="n">
-        <v>2958.7</v>
+        <v>2924.7</v>
       </c>
       <c r="F44" t="n">
-        <v>-18.8</v>
+        <v>-34</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0115</v>
       </c>
       <c r="H44" t="n">
-        <v>36.4</v>
+        <v>45.7</v>
       </c>
       <c r="I44" t="n">
-        <v>2927.7</v>
+        <v>2909.7</v>
       </c>
       <c r="J44" t="n">
-        <v>2916.83</v>
+        <v>2919.5</v>
       </c>
       <c r="K44" t="n">
-        <v>2953.05</v>
+        <v>2940.5</v>
       </c>
       <c r="L44" t="n">
-        <v>2989.28</v>
+        <v>2961.5</v>
       </c>
       <c r="M44" t="n">
-        <v>3001.95</v>
+        <v>2976.9</v>
       </c>
       <c r="N44" t="n">
-        <v>3014.62</v>
+        <v>2992.3</v>
       </c>
       <c r="O44" t="n">
-        <v>3074.4</v>
+        <v>3018.9</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S44" s="7" t="inlineStr">
@@ -4246,75 +4242,75 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2958</v>
+        <v>2926.4</v>
       </c>
       <c r="C45" t="n">
-        <v>2964.6</v>
+        <v>2962.5</v>
       </c>
       <c r="D45" t="n">
-        <v>2918.9</v>
+        <v>2914.5</v>
       </c>
       <c r="E45" t="n">
-        <v>2924.7</v>
+        <v>2958.8</v>
       </c>
       <c r="F45" t="n">
-        <v>-34</v>
+        <v>34.1</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0.0117</v>
       </c>
       <c r="H45" t="n">
-        <v>45.7</v>
+        <v>48</v>
       </c>
       <c r="I45" t="n">
-        <v>2909.7</v>
+        <v>2873.2</v>
       </c>
       <c r="J45" t="n">
-        <v>2919.5</v>
+        <v>2870.47</v>
       </c>
       <c r="K45" t="n">
-        <v>2940.5</v>
+        <v>2901.85</v>
       </c>
       <c r="L45" t="n">
-        <v>2961.5</v>
+        <v>2933.22</v>
       </c>
       <c r="M45" t="n">
-        <v>2976.9</v>
+        <v>2947.55</v>
       </c>
       <c r="N45" t="n">
-        <v>2992.3</v>
+        <v>2961.88</v>
       </c>
       <c r="O45" t="n">
-        <v>3018.9</v>
+        <v>3010.3</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
@@ -4323,55 +4319,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2926.4</v>
+        <v>2957.6</v>
       </c>
       <c r="C46" t="n">
-        <v>2962.5</v>
+        <v>2983.3</v>
       </c>
       <c r="D46" t="n">
-        <v>2914.5</v>
+        <v>2949.9</v>
       </c>
       <c r="E46" t="n">
-        <v>2958.8</v>
+        <v>2969.7</v>
       </c>
       <c r="F46" t="n">
-        <v>34.1</v>
+        <v>10.9</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0117</v>
+        <v>0.0037</v>
       </c>
       <c r="H46" t="n">
-        <v>48</v>
+        <v>33.4</v>
       </c>
       <c r="I46" t="n">
-        <v>2873.2</v>
+        <v>2866.5</v>
       </c>
       <c r="J46" t="n">
-        <v>2870.47</v>
+        <v>2920.95</v>
       </c>
       <c r="K46" t="n">
-        <v>2901.85</v>
+        <v>2934.8</v>
       </c>
       <c r="L46" t="n">
-        <v>2933.22</v>
+        <v>2948.65</v>
       </c>
       <c r="M46" t="n">
-        <v>2947.55</v>
+        <v>2982.8</v>
       </c>
       <c r="N46" t="n">
-        <v>2961.88</v>
+        <v>3016.95</v>
       </c>
       <c r="O46" t="n">
-        <v>3010.3</v>
+        <v>3010.5</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4389,14 +4389,12 @@
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
@@ -4407,57 +4405,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2957.6</v>
+        <v>2967.9</v>
       </c>
       <c r="C47" t="n">
-        <v>2983.3</v>
+        <v>2979.3</v>
       </c>
       <c r="D47" t="n">
-        <v>2949.9</v>
+        <v>2949.5</v>
       </c>
       <c r="E47" t="n">
-        <v>2969.7</v>
+        <v>2976.6</v>
       </c>
       <c r="F47" t="n">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0023</v>
       </c>
       <c r="H47" t="n">
-        <v>33.4</v>
+        <v>29.8</v>
       </c>
       <c r="I47" t="n">
-        <v>2866.5</v>
+        <v>2916.5</v>
       </c>
       <c r="J47" t="n">
-        <v>2920.95</v>
+        <v>2937.85</v>
       </c>
       <c r="K47" t="n">
-        <v>2934.8</v>
+        <v>2953</v>
       </c>
       <c r="L47" t="n">
-        <v>2948.65</v>
+        <v>2968.15</v>
       </c>
       <c r="M47" t="n">
-        <v>2982.8</v>
+        <v>2986.4</v>
       </c>
       <c r="N47" t="n">
-        <v>3016.95</v>
+        <v>3004.65</v>
       </c>
       <c r="O47" t="n">
-        <v>3010.5</v>
+        <v>3016.7</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4465,18 +4463,18 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4491,57 +4489,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2967.9</v>
+        <v>2974.7</v>
       </c>
       <c r="C48" t="n">
-        <v>2979.3</v>
+        <v>2977.9</v>
       </c>
       <c r="D48" t="n">
-        <v>2949.5</v>
+        <v>2954.7</v>
       </c>
       <c r="E48" t="n">
-        <v>2976.6</v>
+        <v>2963.6</v>
       </c>
       <c r="F48" t="n">
-        <v>6.9</v>
+        <v>-13</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0044</v>
       </c>
       <c r="H48" t="n">
-        <v>29.8</v>
+        <v>23.2</v>
       </c>
       <c r="I48" t="n">
-        <v>2916.5</v>
+        <v>2919.7</v>
       </c>
       <c r="J48" t="n">
-        <v>2937.85</v>
+        <v>2952.9</v>
       </c>
       <c r="K48" t="n">
-        <v>2953</v>
+        <v>2961.7</v>
       </c>
       <c r="L48" t="n">
-        <v>2968.15</v>
+        <v>2970.5</v>
       </c>
       <c r="M48" t="n">
-        <v>2986.4</v>
+        <v>2991.5</v>
       </c>
       <c r="N48" t="n">
-        <v>3004.65</v>
+        <v>3012.5</v>
       </c>
       <c r="O48" t="n">
-        <v>3016.7</v>
+        <v>3009.1</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4551,12 +4549,12 @@
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4582,60 +4580,64 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2974.7</v>
+        <v>2963.1</v>
       </c>
       <c r="C49" t="n">
-        <v>2977.9</v>
+        <v>2966.2</v>
       </c>
       <c r="D49" t="n">
-        <v>2954.7</v>
+        <v>2919.4</v>
       </c>
       <c r="E49" t="n">
-        <v>2963.6</v>
+        <v>2923</v>
       </c>
       <c r="F49" t="n">
-        <v>-13</v>
+        <v>-40.6</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0137</v>
       </c>
       <c r="H49" t="n">
-        <v>23.2</v>
+        <v>46.8</v>
       </c>
       <c r="I49" t="n">
-        <v>2919.7</v>
+        <v>2931.5</v>
       </c>
       <c r="J49" t="n">
-        <v>2952.9</v>
+        <v>2939.05</v>
       </c>
       <c r="K49" t="n">
-        <v>2961.7</v>
+        <v>2952</v>
       </c>
       <c r="L49" t="n">
-        <v>2970.5</v>
+        <v>2964.95</v>
       </c>
       <c r="M49" t="n">
-        <v>2991.5</v>
+        <v>2975.2</v>
       </c>
       <c r="N49" t="n">
-        <v>3012.5</v>
+        <v>2985.45</v>
       </c>
       <c r="O49" t="n">
-        <v>3009.1</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
+        <v>3001.1</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
@@ -4657,73 +4659,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2963.1</v>
+        <v>2923.1</v>
       </c>
       <c r="C50" t="n">
-        <v>2966.2</v>
+        <v>2933.8</v>
       </c>
       <c r="D50" t="n">
-        <v>2919.4</v>
+        <v>2887.8</v>
       </c>
       <c r="E50" t="n">
-        <v>2923</v>
+        <v>2893.4</v>
       </c>
       <c r="F50" t="n">
-        <v>-40.6</v>
+        <v>-29.6</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0101</v>
       </c>
       <c r="H50" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="I50" t="n">
-        <v>2931.5</v>
+        <v>2872.6</v>
       </c>
       <c r="J50" t="n">
-        <v>2939.05</v>
+        <v>2866.3</v>
       </c>
       <c r="K50" t="n">
-        <v>2952</v>
+        <v>2899.6</v>
       </c>
       <c r="L50" t="n">
-        <v>2964.95</v>
+        <v>2932.9</v>
       </c>
       <c r="M50" t="n">
-        <v>2975.2</v>
+        <v>2946.4</v>
       </c>
       <c r="N50" t="n">
-        <v>2985.45</v>
+        <v>2959.9</v>
       </c>
       <c r="O50" t="n">
-        <v>3001.1</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
+        <v>3013</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
@@ -4750,50 +4744,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2923.1</v>
+        <v>2890.9</v>
       </c>
       <c r="C51" t="n">
-        <v>2933.8</v>
+        <v>2929.8</v>
       </c>
       <c r="D51" t="n">
-        <v>2887.8</v>
+        <v>2887.6</v>
       </c>
       <c r="E51" t="n">
-        <v>2893.4</v>
+        <v>2904.5</v>
       </c>
       <c r="F51" t="n">
-        <v>-29.6</v>
+        <v>11.1</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0101</v>
+        <v>0.0038</v>
       </c>
       <c r="H51" t="n">
-        <v>46</v>
+        <v>42.2</v>
       </c>
       <c r="I51" t="n">
-        <v>2872.6</v>
+        <v>2841.8</v>
       </c>
       <c r="J51" t="n">
-        <v>2866.3</v>
+        <v>2838.7</v>
       </c>
       <c r="K51" t="n">
-        <v>2899.6</v>
+        <v>2870.4</v>
       </c>
       <c r="L51" t="n">
-        <v>2932.9</v>
+        <v>2902.1</v>
       </c>
       <c r="M51" t="n">
-        <v>2946.4</v>
+        <v>2916.4</v>
       </c>
       <c r="N51" t="n">
-        <v>2959.9</v>
+        <v>2930.7</v>
       </c>
       <c r="O51" t="n">
-        <v>3013</v>
+        <v>2979.8</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4801,18 +4795,18 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4825,55 +4819,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2890.9</v>
+        <v>2892.7</v>
       </c>
       <c r="C52" t="n">
-        <v>2929.8</v>
+        <v>2913.5</v>
       </c>
       <c r="D52" t="n">
-        <v>2887.6</v>
+        <v>2884.3</v>
       </c>
       <c r="E52" t="n">
-        <v>2904.5</v>
+        <v>2894.1</v>
       </c>
       <c r="F52" t="n">
-        <v>11.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0036</v>
       </c>
       <c r="H52" t="n">
-        <v>42.2</v>
+        <v>29.2</v>
       </c>
       <c r="I52" t="n">
-        <v>2841.8</v>
+        <v>2845.4</v>
       </c>
       <c r="J52" t="n">
-        <v>2838.7</v>
+        <v>2860.2</v>
       </c>
       <c r="K52" t="n">
-        <v>2870.4</v>
+        <v>2883.4</v>
       </c>
       <c r="L52" t="n">
-        <v>2902.1</v>
+        <v>2906.6</v>
       </c>
       <c r="M52" t="n">
-        <v>2916.4</v>
+        <v>2925.6</v>
       </c>
       <c r="N52" t="n">
-        <v>2930.7</v>
+        <v>2944.6</v>
       </c>
       <c r="O52" t="n">
-        <v>2979.8</v>
+        <v>2972</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4881,18 +4879,18 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4905,59 +4903,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2892.7</v>
+        <v>2896.4</v>
       </c>
       <c r="C53" t="n">
-        <v>2913.5</v>
+        <v>2896.5</v>
       </c>
       <c r="D53" t="n">
-        <v>2884.3</v>
+        <v>2862.7</v>
       </c>
       <c r="E53" t="n">
-        <v>2894.1</v>
+        <v>2873.1</v>
       </c>
       <c r="F53" t="n">
-        <v>-10.4</v>
+        <v>-21</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0073</v>
       </c>
       <c r="H53" t="n">
-        <v>29.2</v>
+        <v>33.8</v>
       </c>
       <c r="I53" t="n">
-        <v>2845.4</v>
+        <v>2855.1</v>
       </c>
       <c r="J53" t="n">
-        <v>2860.2</v>
+        <v>2862.5</v>
       </c>
       <c r="K53" t="n">
-        <v>2883.4</v>
+        <v>2879.5</v>
       </c>
       <c r="L53" t="n">
-        <v>2906.6</v>
+        <v>2896.5</v>
       </c>
       <c r="M53" t="n">
-        <v>2925.6</v>
+        <v>2908.7</v>
       </c>
       <c r="N53" t="n">
-        <v>2944.6</v>
+        <v>2920.9</v>
       </c>
       <c r="O53" t="n">
-        <v>2972</v>
+        <v>2942.7</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4994,56 +4988,58 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2896.4</v>
+        <v>2875.1</v>
       </c>
       <c r="C54" t="n">
-        <v>2896.5</v>
+        <v>2892.5</v>
       </c>
       <c r="D54" t="n">
-        <v>2862.7</v>
+        <v>2831.9</v>
       </c>
       <c r="E54" t="n">
-        <v>2873.1</v>
+        <v>2861.7</v>
       </c>
       <c r="F54" t="n">
-        <v>-21</v>
+        <v>-11.4</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.004</v>
       </c>
       <c r="H54" t="n">
-        <v>33.8</v>
+        <v>60.6</v>
       </c>
       <c r="I54" t="n">
-        <v>2855.1</v>
+        <v>2828.9</v>
       </c>
       <c r="J54" t="n">
-        <v>2862.5</v>
+        <v>2836.05</v>
       </c>
       <c r="K54" t="n">
-        <v>2879.5</v>
+        <v>2856.2</v>
       </c>
       <c r="L54" t="n">
-        <v>2896.5</v>
+        <v>2876.35</v>
       </c>
       <c r="M54" t="n">
-        <v>2908.7</v>
+        <v>2890</v>
       </c>
       <c r="N54" t="n">
-        <v>2920.9</v>
+        <v>2903.65</v>
       </c>
       <c r="O54" t="n">
-        <v>2942.7</v>
+        <v>2930.3</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
@@ -5055,8 +5051,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5074,74 +5072,70 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2875.1</v>
+        <v>2861.2</v>
       </c>
       <c r="C55" t="n">
-        <v>2892.5</v>
+        <v>2904.6</v>
       </c>
       <c r="D55" t="n">
-        <v>2831.9</v>
+        <v>2859.3</v>
       </c>
       <c r="E55" t="n">
-        <v>2861.7</v>
+        <v>2875.9</v>
       </c>
       <c r="F55" t="n">
-        <v>-11.4</v>
+        <v>14.2</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.005</v>
       </c>
       <c r="H55" t="n">
-        <v>60.6</v>
+        <v>45.3</v>
       </c>
       <c r="I55" t="n">
-        <v>2828.9</v>
+        <v>2771.3</v>
       </c>
       <c r="J55" t="n">
-        <v>2836.05</v>
+        <v>2800.85</v>
       </c>
       <c r="K55" t="n">
-        <v>2856.2</v>
+        <v>2831.4</v>
       </c>
       <c r="L55" t="n">
-        <v>2876.35</v>
+        <v>2861.95</v>
       </c>
       <c r="M55" t="n">
-        <v>2890</v>
+        <v>2892</v>
       </c>
       <c r="N55" t="n">
-        <v>2903.65</v>
+        <v>2922.05</v>
       </c>
       <c r="O55" t="n">
-        <v>2930.3</v>
+        <v>2953.1</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U55" s="8" t="n">
         <v/>
       </c>
@@ -5153,55 +5147,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2861.2</v>
+        <v>2870.5</v>
       </c>
       <c r="C56" t="n">
-        <v>2904.6</v>
+        <v>2883</v>
       </c>
       <c r="D56" t="n">
-        <v>2859.3</v>
+        <v>2856.9</v>
       </c>
       <c r="E56" t="n">
-        <v>2875.9</v>
+        <v>2873.23</v>
       </c>
       <c r="F56" t="n">
-        <v>14.2</v>
+        <v>-2.67</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0009</v>
       </c>
       <c r="H56" t="n">
-        <v>45.3</v>
+        <v>26.1</v>
       </c>
       <c r="I56" t="n">
-        <v>2771.3</v>
+        <v>2814</v>
       </c>
       <c r="J56" t="n">
-        <v>2800.85</v>
+        <v>2827.57</v>
       </c>
       <c r="K56" t="n">
-        <v>2831.4</v>
+        <v>2853.25</v>
       </c>
       <c r="L56" t="n">
-        <v>2861.95</v>
+        <v>2878.92</v>
       </c>
       <c r="M56" t="n">
-        <v>2892</v>
+        <v>2898.55</v>
       </c>
       <c r="N56" t="n">
-        <v>2922.05</v>
+        <v>2918.17</v>
       </c>
       <c r="O56" t="n">
-        <v>2953.1</v>
+        <v>2949.9</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5212,15 +5210,13 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5233,59 +5229,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2870.5</v>
+        <v>2879.5</v>
       </c>
       <c r="C57" t="n">
-        <v>2883</v>
+        <v>2907.3</v>
       </c>
       <c r="D57" t="n">
-        <v>2856.9</v>
+        <v>2876.6</v>
       </c>
       <c r="E57" t="n">
-        <v>2873.23</v>
+        <v>2897.4</v>
       </c>
       <c r="F57" t="n">
-        <v>-2.67</v>
+        <v>24.17</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>26.1</v>
+        <v>30.7</v>
       </c>
       <c r="I57" t="n">
-        <v>2814</v>
+        <v>2830.8</v>
       </c>
       <c r="J57" t="n">
-        <v>2827.57</v>
+        <v>2848.77</v>
       </c>
       <c r="K57" t="n">
-        <v>2853.25</v>
+        <v>2860.18</v>
       </c>
       <c r="L57" t="n">
-        <v>2878.92</v>
+        <v>2871.59</v>
       </c>
       <c r="M57" t="n">
-        <v>2898.55</v>
+        <v>2886.28</v>
       </c>
       <c r="N57" t="n">
-        <v>2918.17</v>
+        <v>2900.97</v>
       </c>
       <c r="O57" t="n">
-        <v>2949.9</v>
+        <v>2909.1</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5296,16 +5288,20 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5315,55 +5311,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2879.5</v>
+        <v>2897.8</v>
       </c>
       <c r="C58" t="n">
-        <v>2907.3</v>
+        <v>2931.2</v>
       </c>
       <c r="D58" t="n">
-        <v>2876.6</v>
+        <v>2884.2</v>
       </c>
       <c r="E58" t="n">
-        <v>2897.4</v>
+        <v>2914.1</v>
       </c>
       <c r="F58" t="n">
-        <v>24.17</v>
+        <v>16.7</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0058</v>
       </c>
       <c r="H58" t="n">
-        <v>30.7</v>
+        <v>47</v>
       </c>
       <c r="I58" t="n">
-        <v>2830.8</v>
+        <v>2845.9</v>
       </c>
       <c r="J58" t="n">
-        <v>2848.77</v>
+        <v>2869.42</v>
       </c>
       <c r="K58" t="n">
-        <v>2860.18</v>
+        <v>2882.05</v>
       </c>
       <c r="L58" t="n">
-        <v>2871.59</v>
+        <v>2894.67</v>
       </c>
       <c r="M58" t="n">
-        <v>2886.28</v>
+        <v>2912.75</v>
       </c>
       <c r="N58" t="n">
-        <v>2900.97</v>
+        <v>2930.82</v>
       </c>
       <c r="O58" t="n">
-        <v>2909.1</v>
+        <v>2938</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5381,12 +5381,12 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="V58" s="8" t="n">
@@ -5406,75 +5406,75 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2897.8</v>
+        <v>2912</v>
       </c>
       <c r="C59" t="n">
-        <v>2931.2</v>
+        <v>2915.3</v>
       </c>
       <c r="D59" t="n">
-        <v>2884.2</v>
+        <v>2858.8</v>
       </c>
       <c r="E59" t="n">
-        <v>2914.1</v>
+        <v>2860.2</v>
       </c>
       <c r="F59" t="n">
-        <v>16.7</v>
+        <v>-53.9</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0185</v>
       </c>
       <c r="H59" t="n">
-        <v>47</v>
+        <v>56.5</v>
       </c>
       <c r="I59" t="n">
-        <v>2845.9</v>
+        <v>2837.2</v>
       </c>
       <c r="J59" t="n">
-        <v>2869.42</v>
+        <v>2870.3</v>
       </c>
       <c r="K59" t="n">
-        <v>2882.05</v>
+        <v>2890.6</v>
       </c>
       <c r="L59" t="n">
-        <v>2894.67</v>
+        <v>2910.9</v>
       </c>
       <c r="M59" t="n">
-        <v>2912.75</v>
+        <v>2937.6</v>
       </c>
       <c r="N59" t="n">
-        <v>2930.82</v>
+        <v>2964.3</v>
       </c>
       <c r="O59" t="n">
-        <v>2938</v>
+        <v>2978.2</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
+      <c r="Q59" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U59" s="8" t="inlineStr">
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
+      </c>
       <c r="V59" s="8" t="n">
         <v/>
       </c>
@@ -5483,67 +5483,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2912</v>
+        <v>2860.7</v>
       </c>
       <c r="C60" t="n">
-        <v>2915.3</v>
+        <v>2862.4</v>
       </c>
       <c r="D60" t="n">
-        <v>2858.8</v>
+        <v>2829.9</v>
       </c>
       <c r="E60" t="n">
-        <v>2860.2</v>
+        <v>2856.8</v>
       </c>
       <c r="F60" t="n">
-        <v>-53.9</v>
+        <v>-3.4</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0012</v>
       </c>
       <c r="H60" t="n">
-        <v>56.5</v>
+        <v>32.5</v>
       </c>
       <c r="I60" t="n">
-        <v>2837.2</v>
+        <v>2802.3</v>
       </c>
       <c r="J60" t="n">
-        <v>2870.3</v>
+        <v>2790.27</v>
       </c>
       <c r="K60" t="n">
-        <v>2890.6</v>
+        <v>2831.95</v>
       </c>
       <c r="L60" t="n">
-        <v>2910.9</v>
+        <v>2873.62</v>
       </c>
       <c r="M60" t="n">
-        <v>2937.6</v>
+        <v>2888.45</v>
       </c>
       <c r="N60" t="n">
-        <v>2964.3</v>
+        <v>2903.27</v>
       </c>
       <c r="O60" t="n">
-        <v>2978.2</v>
+        <v>2971.8</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q60" s="6" t="n">
+        <v/>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
@@ -5552,7 +5546,7 @@
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5574,50 +5568,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2860.7</v>
+        <v>2854.4</v>
       </c>
       <c r="C61" t="n">
-        <v>2862.4</v>
+        <v>2874.1</v>
       </c>
       <c r="D61" t="n">
-        <v>2829.9</v>
+        <v>2843</v>
       </c>
       <c r="E61" t="n">
-        <v>2856.8</v>
+        <v>2859.3</v>
       </c>
       <c r="F61" t="n">
-        <v>-3.4</v>
+        <v>2.5</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="H61" t="n">
-        <v>32.5</v>
+        <v>31.1</v>
       </c>
       <c r="I61" t="n">
-        <v>2802.3</v>
+        <v>2797.4</v>
       </c>
       <c r="J61" t="n">
-        <v>2790.27</v>
+        <v>2829.63</v>
       </c>
       <c r="K61" t="n">
-        <v>2831.95</v>
+        <v>2840.55</v>
       </c>
       <c r="L61" t="n">
-        <v>2873.62</v>
+        <v>2851.47</v>
       </c>
       <c r="M61" t="n">
-        <v>2888.45</v>
+        <v>2873.05</v>
       </c>
       <c r="N61" t="n">
-        <v>2903.27</v>
+        <v>2894.63</v>
       </c>
       <c r="O61" t="n">
-        <v>2971.8</v>
+        <v>2894.9</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5625,19 +5619,19 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
       <c r="U61" s="8" t="n">
         <v/>
       </c>
@@ -5649,55 +5643,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2854.4</v>
+        <v>2839.6</v>
       </c>
       <c r="C62" t="n">
-        <v>2874.1</v>
+        <v>2841.2</v>
       </c>
       <c r="D62" t="n">
-        <v>2843</v>
+        <v>2837.5</v>
       </c>
       <c r="E62" t="n">
-        <v>2859.3</v>
+        <v>2837.8</v>
       </c>
       <c r="F62" t="n">
-        <v>2.5</v>
+        <v>-21.5</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0075</v>
       </c>
       <c r="H62" t="n">
-        <v>31.1</v>
+        <v>3.7</v>
       </c>
       <c r="I62" t="n">
-        <v>2797.4</v>
+        <v>2811.9</v>
       </c>
       <c r="J62" t="n">
-        <v>2829.63</v>
+        <v>2828.57</v>
       </c>
       <c r="K62" t="n">
-        <v>2840.55</v>
+        <v>2843.75</v>
       </c>
       <c r="L62" t="n">
-        <v>2851.47</v>
+        <v>2858.93</v>
       </c>
       <c r="M62" t="n">
-        <v>2873.05</v>
+        <v>2874.85</v>
       </c>
       <c r="N62" t="n">
-        <v>2894.63</v>
+        <v>2890.78</v>
       </c>
       <c r="O62" t="n">
-        <v>2894.9</v>
+        <v>2905.2</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5705,18 +5703,18 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5729,93 +5727,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>2857.7</v>
-      </c>
-      <c r="C63" t="n">
-        <v>2858.8</v>
-      </c>
-      <c r="D63" t="n">
-        <v>2849.6</v>
-      </c>
-      <c r="E63" t="n">
-        <v>2859.3</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="I63" t="n">
-        <v>2811.9</v>
-      </c>
-      <c r="J63" t="n">
-        <v>2828.57</v>
-      </c>
-      <c r="K63" t="n">
-        <v>2843.75</v>
-      </c>
-      <c r="L63" t="n">
-        <v>2858.93</v>
-      </c>
-      <c r="M63" t="n">
-        <v>2874.85</v>
-      </c>
-      <c r="N63" t="n">
-        <v>2890.78</v>
-      </c>
-      <c r="O63" t="n">
-        <v>2905.2</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3030.9</v>
+        <v>3019.7</v>
       </c>
       <c r="C2" t="n">
-        <v>3062.4</v>
+        <v>3042.1</v>
       </c>
       <c r="D2" t="n">
-        <v>2988.5</v>
+        <v>3006.7</v>
       </c>
       <c r="E2" t="n">
-        <v>3014.2</v>
+        <v>3027</v>
       </c>
       <c r="F2" t="n">
-        <v>-20.9</v>
+        <v>12.8</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0042</v>
       </c>
       <c r="H2" t="n">
-        <v>73.90000000000001</v>
+        <v>35.4</v>
       </c>
       <c r="I2" t="n">
-        <v>2979</v>
+        <v>2914.6</v>
       </c>
       <c r="J2" t="n">
-        <v>2984.93</v>
+        <v>2934.68</v>
       </c>
       <c r="K2" t="n">
-        <v>3012.75</v>
+        <v>2977.25</v>
       </c>
       <c r="L2" t="n">
-        <v>3040.58</v>
+        <v>3019.82</v>
       </c>
       <c r="M2" t="n">
-        <v>3057.45</v>
+        <v>3051.15</v>
       </c>
       <c r="N2" t="n">
-        <v>3074.33</v>
+        <v>3082.47</v>
       </c>
       <c r="O2" t="n">
-        <v>3113.1</v>
+        <v>3136.3</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,20 +685,16 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -713,70 +709,74 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3019.7</v>
+        <v>3033.4</v>
       </c>
       <c r="C3" t="n">
-        <v>3042.1</v>
+        <v>3042.6</v>
       </c>
       <c r="D3" t="n">
-        <v>3006.7</v>
+        <v>2988.8</v>
       </c>
       <c r="E3" t="n">
-        <v>3027</v>
+        <v>2998.8</v>
       </c>
       <c r="F3" t="n">
-        <v>12.8</v>
+        <v>-28.2</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>35.4</v>
+        <v>53.8</v>
       </c>
       <c r="I3" t="n">
-        <v>2914.6</v>
+        <v>2971.3</v>
       </c>
       <c r="J3" t="n">
-        <v>2934.68</v>
+        <v>2992.9</v>
       </c>
       <c r="K3" t="n">
-        <v>2977.25</v>
+        <v>3009.3</v>
       </c>
       <c r="L3" t="n">
-        <v>3019.82</v>
+        <v>3025.7</v>
       </c>
       <c r="M3" t="n">
-        <v>3051.15</v>
+        <v>3044.7</v>
       </c>
       <c r="N3" t="n">
-        <v>3082.47</v>
+        <v>3063.7</v>
       </c>
       <c r="O3" t="n">
-        <v>3136.3</v>
+        <v>3077.5</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -795,72 +795,70 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3033.4</v>
+        <v>2994.3</v>
       </c>
       <c r="C4" t="n">
-        <v>3042.6</v>
+        <v>3004.3</v>
       </c>
       <c r="D4" t="n">
-        <v>2988.8</v>
+        <v>2943.4</v>
       </c>
       <c r="E4" t="n">
-        <v>2998.8</v>
+        <v>2971.5</v>
       </c>
       <c r="F4" t="n">
-        <v>-28.2</v>
+        <v>-27.3</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0091</v>
       </c>
       <c r="H4" t="n">
-        <v>53.8</v>
+        <v>60.9</v>
       </c>
       <c r="I4" t="n">
-        <v>2971.3</v>
+        <v>2935</v>
       </c>
       <c r="J4" t="n">
-        <v>2992.9</v>
+        <v>2936.55</v>
       </c>
       <c r="K4" t="n">
-        <v>3009.3</v>
+        <v>2971.9</v>
       </c>
       <c r="L4" t="n">
+        <v>3007.25</v>
+      </c>
+      <c r="M4" t="n">
         <v>3025.7</v>
       </c>
-      <c r="M4" t="n">
-        <v>3044.7</v>
-      </c>
       <c r="N4" t="n">
-        <v>3063.7</v>
+        <v>3044.15</v>
       </c>
       <c r="O4" t="n">
-        <v>3077.5</v>
+        <v>3096.4</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -881,57 +879,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2994.3</v>
+        <v>2965.8</v>
       </c>
       <c r="C5" t="n">
-        <v>3004.3</v>
+        <v>3014.9</v>
       </c>
       <c r="D5" t="n">
-        <v>2943.4</v>
+        <v>2964.3</v>
       </c>
       <c r="E5" t="n">
-        <v>2971.5</v>
+        <v>3008.4</v>
       </c>
       <c r="F5" t="n">
-        <v>-27.3</v>
+        <v>36.9</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0091</v>
+        <v>0.0124</v>
       </c>
       <c r="H5" t="n">
-        <v>60.9</v>
+        <v>50.6</v>
       </c>
       <c r="I5" t="n">
-        <v>2935</v>
+        <v>2882.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2936.55</v>
+        <v>2909.42</v>
       </c>
       <c r="K5" t="n">
-        <v>2971.9</v>
+        <v>2941.05</v>
       </c>
       <c r="L5" t="n">
-        <v>3007.25</v>
+        <v>2972.67</v>
       </c>
       <c r="M5" t="n">
-        <v>3025.7</v>
+        <v>3001.95</v>
       </c>
       <c r="N5" t="n">
-        <v>3044.15</v>
+        <v>3031.23</v>
       </c>
       <c r="O5" t="n">
-        <v>3096.4</v>
+        <v>3065.2</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -939,19 +937,19 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -963,59 +961,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2965.8</v>
+        <v>3008.1</v>
       </c>
       <c r="C6" t="n">
-        <v>3014.9</v>
+        <v>3019.5</v>
       </c>
       <c r="D6" t="n">
-        <v>2964.3</v>
+        <v>2970.8</v>
       </c>
       <c r="E6" t="n">
-        <v>3008.4</v>
+        <v>2994</v>
       </c>
       <c r="F6" t="n">
-        <v>36.9</v>
+        <v>-14.4</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0048</v>
       </c>
       <c r="H6" t="n">
-        <v>50.6</v>
+        <v>48.7</v>
       </c>
       <c r="I6" t="n">
-        <v>2882.5</v>
+        <v>2913.7</v>
       </c>
       <c r="J6" t="n">
-        <v>2909.42</v>
+        <v>2967.2</v>
       </c>
       <c r="K6" t="n">
-        <v>2941.05</v>
+        <v>2983.1</v>
       </c>
       <c r="L6" t="n">
-        <v>2972.67</v>
+        <v>2999</v>
       </c>
       <c r="M6" t="n">
-        <v>3001.95</v>
+        <v>3033.7</v>
       </c>
       <c r="N6" t="n">
-        <v>3031.23</v>
+        <v>3068.4</v>
       </c>
       <c r="O6" t="n">
-        <v>3065.2</v>
+        <v>3065.5</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1023,18 +1017,18 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1047,55 +1041,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3008.1</v>
+        <v>2984.7</v>
       </c>
       <c r="C7" t="n">
-        <v>3019.5</v>
+        <v>2995.8</v>
       </c>
       <c r="D7" t="n">
-        <v>2970.8</v>
+        <v>2961.8</v>
       </c>
       <c r="E7" t="n">
-        <v>2994</v>
+        <v>2970.4</v>
       </c>
       <c r="F7" t="n">
-        <v>-14.4</v>
+        <v>-23.6</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>48.7</v>
+        <v>34</v>
       </c>
       <c r="I7" t="n">
-        <v>2913.7</v>
+        <v>2922.1</v>
       </c>
       <c r="J7" t="n">
-        <v>2967.2</v>
+        <v>2944.73</v>
       </c>
       <c r="K7" t="n">
-        <v>2983.1</v>
+        <v>2969.65</v>
       </c>
       <c r="L7" t="n">
-        <v>2999</v>
+        <v>2994.58</v>
       </c>
       <c r="M7" t="n">
-        <v>3033.7</v>
+        <v>3018.35</v>
       </c>
       <c r="N7" t="n">
-        <v>3068.4</v>
+        <v>3042.12</v>
       </c>
       <c r="O7" t="n">
-        <v>3065.5</v>
+        <v>3068.2</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1105,12 +1103,12 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1129,57 +1127,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2984.7</v>
+        <v>2967.2</v>
       </c>
       <c r="C8" t="n">
-        <v>2995.8</v>
+        <v>3029.8</v>
       </c>
       <c r="D8" t="n">
-        <v>2961.8</v>
+        <v>2956.2</v>
       </c>
       <c r="E8" t="n">
-        <v>2970.4</v>
+        <v>2979.9</v>
       </c>
       <c r="F8" t="n">
-        <v>-23.6</v>
+        <v>9.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H8" t="n">
-        <v>34</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>2922.1</v>
+        <v>2927.8</v>
       </c>
       <c r="J8" t="n">
-        <v>2944.73</v>
+        <v>2932.2</v>
       </c>
       <c r="K8" t="n">
-        <v>2969.65</v>
+        <v>2953.4</v>
       </c>
       <c r="L8" t="n">
-        <v>2994.58</v>
+        <v>2974.6</v>
       </c>
       <c r="M8" t="n">
-        <v>3018.35</v>
+        <v>2987.4</v>
       </c>
       <c r="N8" t="n">
-        <v>3042.12</v>
+        <v>3000.2</v>
       </c>
       <c r="O8" t="n">
-        <v>3068.2</v>
+        <v>3029.8</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1187,24 +1185,28 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R8" s="6" t="n">
+        <v/>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
@@ -1213,57 +1215,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2967.2</v>
+        <v>2981.2</v>
       </c>
       <c r="C9" t="n">
-        <v>3029.8</v>
+        <v>3006.1</v>
       </c>
       <c r="D9" t="n">
-        <v>2956.2</v>
+        <v>2974.4</v>
       </c>
       <c r="E9" t="n">
-        <v>2979.9</v>
+        <v>2991.8</v>
       </c>
       <c r="F9" t="n">
-        <v>9.5</v>
+        <v>11.9</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.004</v>
       </c>
       <c r="H9" t="n">
-        <v>73.59999999999999</v>
+        <v>31.7</v>
       </c>
       <c r="I9" t="n">
-        <v>2927.8</v>
+        <v>2882.6</v>
       </c>
       <c r="J9" t="n">
-        <v>2932.2</v>
+        <v>2899.75</v>
       </c>
       <c r="K9" t="n">
-        <v>2953.4</v>
+        <v>2943.1</v>
       </c>
       <c r="L9" t="n">
-        <v>2974.6</v>
+        <v>2986.45</v>
       </c>
       <c r="M9" t="n">
-        <v>2987.4</v>
+        <v>3016.7</v>
       </c>
       <c r="N9" t="n">
-        <v>3000.2</v>
+        <v>3046.95</v>
       </c>
       <c r="O9" t="n">
-        <v>3029.8</v>
+        <v>3103.4</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1274,25 +1276,19 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
@@ -1308,50 +1304,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2981.2</v>
+        <v>2995.3</v>
       </c>
       <c r="C10" t="n">
-        <v>3006.1</v>
+        <v>3012.8</v>
       </c>
       <c r="D10" t="n">
-        <v>2974.4</v>
+        <v>2972.7</v>
       </c>
       <c r="E10" t="n">
-        <v>2991.8</v>
+        <v>2990.7</v>
       </c>
       <c r="F10" t="n">
-        <v>11.9</v>
+        <v>-1.1</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0004</v>
       </c>
       <c r="H10" t="n">
-        <v>31.7</v>
+        <v>40.1</v>
       </c>
       <c r="I10" t="n">
-        <v>2882.6</v>
+        <v>2942.7</v>
       </c>
       <c r="J10" t="n">
-        <v>2899.75</v>
+        <v>2960.87</v>
       </c>
       <c r="K10" t="n">
-        <v>2943.1</v>
+        <v>2975.95</v>
       </c>
       <c r="L10" t="n">
-        <v>2986.45</v>
+        <v>2991.03</v>
       </c>
       <c r="M10" t="n">
-        <v>3016.7</v>
+        <v>3007.65</v>
       </c>
       <c r="N10" t="n">
-        <v>3046.95</v>
+        <v>3024.28</v>
       </c>
       <c r="O10" t="n">
-        <v>3103.4</v>
+        <v>3037.8</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1359,16 +1355,20 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1383,78 +1383,78 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2995.3</v>
+        <v>2991.7</v>
       </c>
       <c r="C11" t="n">
-        <v>3012.8</v>
+        <v>2994.8</v>
       </c>
       <c r="D11" t="n">
-        <v>2972.7</v>
+        <v>2949.3</v>
       </c>
       <c r="E11" t="n">
-        <v>2990.7</v>
+        <v>2973.5</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1</v>
+        <v>-17.2</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0058</v>
       </c>
       <c r="H11" t="n">
-        <v>40.1</v>
+        <v>45.5</v>
       </c>
       <c r="I11" t="n">
-        <v>2942.7</v>
+        <v>2932.6</v>
       </c>
       <c r="J11" t="n">
-        <v>2960.87</v>
+        <v>2949.57</v>
       </c>
       <c r="K11" t="n">
-        <v>2975.95</v>
+        <v>2970.65</v>
       </c>
       <c r="L11" t="n">
-        <v>2991.03</v>
+        <v>2991.72</v>
       </c>
       <c r="M11" t="n">
-        <v>3007.65</v>
+        <v>3010.75</v>
       </c>
       <c r="N11" t="n">
-        <v>3024.28</v>
+        <v>3029.78</v>
       </c>
       <c r="O11" t="n">
-        <v>3037.8</v>
+        <v>3052.9</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1469,79 +1469,79 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2991.7</v>
+        <v>2964.5</v>
       </c>
       <c r="C12" t="n">
-        <v>2994.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D12" t="n">
-        <v>2949.3</v>
+        <v>2952.7</v>
       </c>
       <c r="E12" t="n">
-        <v>2973.5</v>
+        <v>2955.2</v>
       </c>
       <c r="F12" t="n">
-        <v>-17.2</v>
+        <v>-18.3</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0062</v>
       </c>
       <c r="H12" t="n">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="I12" t="n">
-        <v>2932.6</v>
+        <v>2903.8</v>
       </c>
       <c r="J12" t="n">
-        <v>2949.57</v>
+        <v>2928.72</v>
       </c>
       <c r="K12" t="n">
-        <v>2970.65</v>
+        <v>2950.75</v>
       </c>
       <c r="L12" t="n">
-        <v>2991.72</v>
+        <v>2972.78</v>
       </c>
       <c r="M12" t="n">
-        <v>3010.75</v>
+        <v>2996.25</v>
       </c>
       <c r="N12" t="n">
-        <v>3029.78</v>
+        <v>3019.72</v>
       </c>
       <c r="O12" t="n">
-        <v>3052.9</v>
+        <v>3040.3</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1555,57 +1555,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2964.5</v>
+        <v>2955.8</v>
       </c>
       <c r="C13" t="n">
-        <v>2998.7</v>
+        <v>2999.8</v>
       </c>
       <c r="D13" t="n">
-        <v>2952.7</v>
+        <v>2951.1</v>
       </c>
       <c r="E13" t="n">
-        <v>2955.2</v>
+        <v>2997</v>
       </c>
       <c r="F13" t="n">
-        <v>-18.3</v>
+        <v>41.8</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0141</v>
       </c>
       <c r="H13" t="n">
-        <v>46</v>
+        <v>48.7</v>
       </c>
       <c r="I13" t="n">
-        <v>2903.8</v>
+        <v>2906.7</v>
       </c>
       <c r="J13" t="n">
-        <v>2928.72</v>
+        <v>2898.95</v>
       </c>
       <c r="K13" t="n">
-        <v>2950.75</v>
+        <v>2932.2</v>
       </c>
       <c r="L13" t="n">
-        <v>2972.78</v>
+        <v>2965.45</v>
       </c>
       <c r="M13" t="n">
-        <v>2996.25</v>
+        <v>2978.2</v>
       </c>
       <c r="N13" t="n">
-        <v>3019.72</v>
+        <v>2990.95</v>
       </c>
       <c r="O13" t="n">
-        <v>3040.3</v>
+        <v>3044.7</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1613,23 +1613,23 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1648,50 +1648,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2955.8</v>
+        <v>2997</v>
       </c>
       <c r="C14" t="n">
-        <v>2999.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D14" t="n">
-        <v>2951.1</v>
+        <v>2965.5</v>
       </c>
       <c r="E14" t="n">
-        <v>2997</v>
+        <v>2969.8</v>
       </c>
       <c r="F14" t="n">
-        <v>41.8</v>
+        <v>-27.2</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0141</v>
+        <v>-0.0091</v>
       </c>
       <c r="H14" t="n">
-        <v>48.7</v>
+        <v>33.2</v>
       </c>
       <c r="I14" t="n">
-        <v>2906.7</v>
+        <v>2902.4</v>
       </c>
       <c r="J14" t="n">
-        <v>2898.95</v>
+        <v>2959.08</v>
       </c>
       <c r="K14" t="n">
-        <v>2932.2</v>
+        <v>2972.65</v>
       </c>
       <c r="L14" t="n">
-        <v>2965.45</v>
+        <v>2986.23</v>
       </c>
       <c r="M14" t="n">
-        <v>2978.2</v>
+        <v>3021.35</v>
       </c>
       <c r="N14" t="n">
-        <v>2990.95</v>
+        <v>3056.47</v>
       </c>
       <c r="O14" t="n">
-        <v>3044.7</v>
+        <v>3048.5</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1699,23 +1699,21 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1727,60 +1725,62 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2997</v>
+        <v>2974.6</v>
       </c>
       <c r="C15" t="n">
-        <v>2998.7</v>
+        <v>2979</v>
       </c>
       <c r="D15" t="n">
-        <v>2965.5</v>
+        <v>2932.1</v>
       </c>
       <c r="E15" t="n">
-        <v>2969.8</v>
+        <v>2951.7</v>
       </c>
       <c r="F15" t="n">
-        <v>-27.2</v>
+        <v>-18.1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0091</v>
+        <v>-0.0061</v>
       </c>
       <c r="H15" t="n">
-        <v>33.2</v>
+        <v>46.9</v>
       </c>
       <c r="I15" t="n">
-        <v>2902.4</v>
+        <v>2932.3</v>
       </c>
       <c r="J15" t="n">
-        <v>2959.08</v>
+        <v>2930.45</v>
       </c>
       <c r="K15" t="n">
-        <v>2972.65</v>
+        <v>2953.2</v>
       </c>
       <c r="L15" t="n">
-        <v>2986.23</v>
+        <v>2975.95</v>
       </c>
       <c r="M15" t="n">
-        <v>3021.35</v>
+        <v>2986.4</v>
       </c>
       <c r="N15" t="n">
-        <v>3056.47</v>
+        <v>2996.85</v>
       </c>
       <c r="O15" t="n">
-        <v>3048.5</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
+        <v>3031.9</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q15" s="6" t="n">
         <v/>
@@ -1790,7 +1790,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="7" t="inlineStr">
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1811,74 +1811,70 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2974.6</v>
+        <v>2948.5</v>
       </c>
       <c r="C16" t="n">
-        <v>2979</v>
+        <v>2969.7</v>
       </c>
       <c r="D16" t="n">
-        <v>2932.1</v>
+        <v>2934.5</v>
       </c>
       <c r="E16" t="n">
-        <v>2951.7</v>
+        <v>2941.3</v>
       </c>
       <c r="F16" t="n">
-        <v>-18.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0035</v>
       </c>
       <c r="H16" t="n">
-        <v>46.9</v>
+        <v>35.2</v>
       </c>
       <c r="I16" t="n">
-        <v>2932.3</v>
+        <v>2885.2</v>
       </c>
       <c r="J16" t="n">
-        <v>2930.45</v>
+        <v>2902.88</v>
       </c>
       <c r="K16" t="n">
-        <v>2953.2</v>
+        <v>2928.25</v>
       </c>
       <c r="L16" t="n">
-        <v>2975.95</v>
+        <v>2953.62</v>
       </c>
       <c r="M16" t="n">
-        <v>2986.4</v>
+        <v>2975.15</v>
       </c>
       <c r="N16" t="n">
-        <v>2996.85</v>
+        <v>2996.67</v>
       </c>
       <c r="O16" t="n">
-        <v>3031.9</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3025.9</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
       </c>
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1897,57 +1893,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2948.5</v>
+        <v>2955.5</v>
       </c>
       <c r="C17" t="n">
-        <v>2969.7</v>
+        <v>2985.9</v>
       </c>
       <c r="D17" t="n">
-        <v>2934.5</v>
+        <v>2941.2</v>
       </c>
       <c r="E17" t="n">
-        <v>2941.3</v>
+        <v>2960</v>
       </c>
       <c r="F17" t="n">
-        <v>-10.4</v>
+        <v>18.7</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0064</v>
       </c>
       <c r="H17" t="n">
-        <v>35.2</v>
+        <v>44.7</v>
       </c>
       <c r="I17" t="n">
-        <v>2885.2</v>
+        <v>2899.3</v>
       </c>
       <c r="J17" t="n">
-        <v>2902.88</v>
+        <v>2900.7</v>
       </c>
       <c r="K17" t="n">
-        <v>2928.25</v>
+        <v>2923.7</v>
       </c>
       <c r="L17" t="n">
-        <v>2953.62</v>
+        <v>2946.7</v>
       </c>
       <c r="M17" t="n">
-        <v>2975.15</v>
+        <v>2958.9</v>
       </c>
       <c r="N17" t="n">
-        <v>2996.67</v>
+        <v>2971.1</v>
       </c>
       <c r="O17" t="n">
-        <v>3025.9</v>
+        <v>3004.9</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1960,14 +1956,18 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1977,59 +1977,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2955.5</v>
+        <v>2961.5</v>
       </c>
       <c r="C18" t="n">
-        <v>2985.9</v>
+        <v>2968.3</v>
       </c>
       <c r="D18" t="n">
-        <v>2941.2</v>
+        <v>2933.4</v>
       </c>
       <c r="E18" t="n">
-        <v>2960</v>
+        <v>2964.5</v>
       </c>
       <c r="F18" t="n">
-        <v>18.7</v>
+        <v>4.5</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0015</v>
       </c>
       <c r="H18" t="n">
-        <v>44.7</v>
+        <v>34.9</v>
       </c>
       <c r="I18" t="n">
-        <v>2899.3</v>
+        <v>2896.5</v>
       </c>
       <c r="J18" t="n">
-        <v>2900.7</v>
+        <v>2913.53</v>
       </c>
       <c r="K18" t="n">
-        <v>2923.7</v>
+        <v>2937.65</v>
       </c>
       <c r="L18" t="n">
-        <v>2946.7</v>
+        <v>2961.77</v>
       </c>
       <c r="M18" t="n">
-        <v>2958.9</v>
+        <v>2982.35</v>
       </c>
       <c r="N18" t="n">
-        <v>2971.1</v>
+        <v>3002.92</v>
       </c>
       <c r="O18" t="n">
-        <v>3004.9</v>
+        <v>3030.6</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2037,24 +2033,22 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
@@ -2063,61 +2057,69 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2961.5</v>
+        <v>2966.9</v>
       </c>
       <c r="C19" t="n">
-        <v>2968.3</v>
+        <v>2978.3</v>
       </c>
       <c r="D19" t="n">
-        <v>2933.4</v>
+        <v>2902.3</v>
       </c>
       <c r="E19" t="n">
-        <v>2964.5</v>
+        <v>2915.4</v>
       </c>
       <c r="F19" t="n">
-        <v>4.5</v>
+        <v>-49.1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0166</v>
       </c>
       <c r="H19" t="n">
-        <v>34.9</v>
+        <v>76</v>
       </c>
       <c r="I19" t="n">
-        <v>2896.5</v>
+        <v>2898.5</v>
       </c>
       <c r="J19" t="n">
-        <v>2913.53</v>
+        <v>2936.42</v>
       </c>
       <c r="K19" t="n">
-        <v>2937.65</v>
+        <v>2947.05</v>
       </c>
       <c r="L19" t="n">
-        <v>2961.77</v>
+        <v>2957.67</v>
       </c>
       <c r="M19" t="n">
-        <v>2982.35</v>
+        <v>2981.95</v>
       </c>
       <c r="N19" t="n">
-        <v>3002.92</v>
+        <v>3006.23</v>
       </c>
       <c r="O19" t="n">
-        <v>3030.6</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
+        <v>3003.2</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
@@ -2126,7 +2128,7 @@
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2138,88 +2140,84 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W19" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2966.9</v>
+        <v>2906.6</v>
       </c>
       <c r="C20" t="n">
-        <v>2978.3</v>
+        <v>2957.9</v>
       </c>
       <c r="D20" t="n">
-        <v>2902.3</v>
+        <v>2905.6</v>
       </c>
       <c r="E20" t="n">
-        <v>2915.4</v>
+        <v>2954.3</v>
       </c>
       <c r="F20" t="n">
-        <v>-49.1</v>
+        <v>38.9</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0166</v>
+        <v>0.0133</v>
       </c>
       <c r="H20" t="n">
-        <v>76</v>
+        <v>52.3</v>
       </c>
       <c r="I20" t="n">
-        <v>2898.5</v>
+        <v>2826.3</v>
       </c>
       <c r="J20" t="n">
-        <v>2936.42</v>
+        <v>2826.95</v>
       </c>
       <c r="K20" t="n">
-        <v>2947.05</v>
+        <v>2877.4</v>
       </c>
       <c r="L20" t="n">
-        <v>2957.67</v>
+        <v>2927.85</v>
       </c>
       <c r="M20" t="n">
-        <v>2981.95</v>
+        <v>2953.4</v>
       </c>
       <c r="N20" t="n">
-        <v>3006.23</v>
+        <v>2978.95</v>
       </c>
       <c r="O20" t="n">
-        <v>3003.2</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
+        <v>3054.3</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
@@ -2233,76 +2231,78 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2906.6</v>
+        <v>2954</v>
       </c>
       <c r="C21" t="n">
-        <v>2957.9</v>
+        <v>2976.3</v>
       </c>
       <c r="D21" t="n">
-        <v>2905.6</v>
+        <v>2905.3</v>
       </c>
       <c r="E21" t="n">
-        <v>2954.3</v>
+        <v>2938</v>
       </c>
       <c r="F21" t="n">
-        <v>38.9</v>
+        <v>-16.3</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0055</v>
       </c>
       <c r="H21" t="n">
-        <v>52.3</v>
+        <v>71</v>
       </c>
       <c r="I21" t="n">
-        <v>2826.3</v>
+        <v>2853.3</v>
       </c>
       <c r="J21" t="n">
-        <v>2826.95</v>
+        <v>2913.28</v>
       </c>
       <c r="K21" t="n">
-        <v>2877.4</v>
+        <v>2928.15</v>
       </c>
       <c r="L21" t="n">
-        <v>2927.85</v>
+        <v>2943.03</v>
       </c>
       <c r="M21" t="n">
-        <v>2953.4</v>
+        <v>2980.45</v>
       </c>
       <c r="N21" t="n">
-        <v>2978.95</v>
+        <v>3017.87</v>
       </c>
       <c r="O21" t="n">
-        <v>3054.3</v>
+        <v>3010.2</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2317,78 +2317,76 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2954</v>
+        <v>2950</v>
       </c>
       <c r="C22" t="n">
-        <v>2976.3</v>
+        <v>2994.6</v>
       </c>
       <c r="D22" t="n">
-        <v>2905.3</v>
+        <v>2948.4</v>
       </c>
       <c r="E22" t="n">
-        <v>2938</v>
+        <v>2989.3</v>
       </c>
       <c r="F22" t="n">
-        <v>-16.3</v>
+        <v>51.3</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0175</v>
       </c>
       <c r="H22" t="n">
-        <v>71</v>
+        <v>46.2</v>
       </c>
       <c r="I22" t="n">
-        <v>2853.3</v>
+        <v>2834.3</v>
       </c>
       <c r="J22" t="n">
-        <v>2913.28</v>
+        <v>2865.6</v>
       </c>
       <c r="K22" t="n">
-        <v>2928.15</v>
+        <v>2902.5</v>
       </c>
       <c r="L22" t="n">
-        <v>2943.03</v>
+        <v>2939.4</v>
       </c>
       <c r="M22" t="n">
-        <v>2980.45</v>
+        <v>2973.5</v>
       </c>
       <c r="N22" t="n">
-        <v>3017.87</v>
+        <v>3007.6</v>
       </c>
       <c r="O22" t="n">
-        <v>3010.2</v>
+        <v>3047.3</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2403,57 +2401,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2950</v>
+        <v>2992.4</v>
       </c>
       <c r="C23" t="n">
-        <v>2994.6</v>
+        <v>3051.8</v>
       </c>
       <c r="D23" t="n">
-        <v>2948.4</v>
+        <v>2986.1</v>
       </c>
       <c r="E23" t="n">
-        <v>2989.3</v>
+        <v>3044.7</v>
       </c>
       <c r="F23" t="n">
-        <v>51.3</v>
+        <v>55.4</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0185</v>
       </c>
       <c r="H23" t="n">
-        <v>46.2</v>
+        <v>65.7</v>
       </c>
       <c r="I23" t="n">
-        <v>2834.3</v>
+        <v>2902.2</v>
       </c>
       <c r="J23" t="n">
-        <v>2865.6</v>
+        <v>2952</v>
       </c>
       <c r="K23" t="n">
-        <v>2902.5</v>
+        <v>2966.2</v>
       </c>
       <c r="L23" t="n">
-        <v>2939.4</v>
+        <v>2980.4</v>
       </c>
       <c r="M23" t="n">
-        <v>2973.5</v>
+        <v>3012.4</v>
       </c>
       <c r="N23" t="n">
-        <v>3007.6</v>
+        <v>3044.4</v>
       </c>
       <c r="O23" t="n">
-        <v>3047.3</v>
+        <v>3040.8</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2464,80 +2462,80 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W23" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2992.4</v>
+        <v>3049.1</v>
       </c>
       <c r="C24" t="n">
-        <v>3051.8</v>
+        <v>3058.3</v>
       </c>
       <c r="D24" t="n">
-        <v>2986.1</v>
+        <v>3023.3</v>
       </c>
       <c r="E24" t="n">
-        <v>3044.7</v>
+        <v>3025.4</v>
       </c>
       <c r="F24" t="n">
-        <v>55.4</v>
+        <v>-19.3</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0063</v>
       </c>
       <c r="H24" t="n">
-        <v>65.7</v>
+        <v>35</v>
       </c>
       <c r="I24" t="n">
-        <v>2902.2</v>
+        <v>2920.4</v>
       </c>
       <c r="J24" t="n">
-        <v>2952</v>
+        <v>2991.87</v>
       </c>
       <c r="K24" t="n">
-        <v>2966.2</v>
+        <v>3011.85</v>
       </c>
       <c r="L24" t="n">
-        <v>2980.4</v>
+        <v>3031.83</v>
       </c>
       <c r="M24" t="n">
-        <v>3012.4</v>
+        <v>3077.55</v>
       </c>
       <c r="N24" t="n">
-        <v>3044.4</v>
+        <v>3123.27</v>
       </c>
       <c r="O24" t="n">
-        <v>3040.8</v>
+        <v>3117.5</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2550,78 +2548,76 @@
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3049.1</v>
+        <v>3028.5</v>
       </c>
       <c r="C25" t="n">
-        <v>3058.3</v>
+        <v>3041</v>
       </c>
       <c r="D25" t="n">
-        <v>3023.3</v>
+        <v>3004.9</v>
       </c>
       <c r="E25" t="n">
-        <v>3025.4</v>
+        <v>3009.1</v>
       </c>
       <c r="F25" t="n">
-        <v>-19.3</v>
+        <v>-16.3</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0054</v>
       </c>
       <c r="H25" t="n">
-        <v>35</v>
+        <v>36.1</v>
       </c>
       <c r="I25" t="n">
-        <v>2920.4</v>
+        <v>2988.3</v>
       </c>
       <c r="J25" t="n">
-        <v>2991.87</v>
+        <v>2982.7</v>
       </c>
       <c r="K25" t="n">
-        <v>3011.85</v>
+        <v>3007.9</v>
       </c>
       <c r="L25" t="n">
-        <v>3031.83</v>
+        <v>3033.1</v>
       </c>
       <c r="M25" t="n">
-        <v>3077.55</v>
+        <v>3042.9</v>
       </c>
       <c r="N25" t="n">
-        <v>3123.27</v>
+        <v>3052.7</v>
       </c>
       <c r="O25" t="n">
-        <v>3117.5</v>
+        <v>3093.3</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2629,12 +2625,14 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2653,57 +2651,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3028.5</v>
+        <v>3008.5</v>
       </c>
       <c r="C26" t="n">
-        <v>3041</v>
+        <v>3046.8</v>
       </c>
       <c r="D26" t="n">
-        <v>3004.9</v>
+        <v>3002</v>
       </c>
       <c r="E26" t="n">
-        <v>3009.1</v>
+        <v>3041.6</v>
       </c>
       <c r="F26" t="n">
-        <v>-16.3</v>
+        <v>32.5</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0054</v>
+        <v>0.0108</v>
       </c>
       <c r="H26" t="n">
-        <v>36.1</v>
+        <v>44.8</v>
       </c>
       <c r="I26" t="n">
-        <v>2988.3</v>
+        <v>2968.8</v>
       </c>
       <c r="J26" t="n">
-        <v>2982.7</v>
+        <v>2966.08</v>
       </c>
       <c r="K26" t="n">
-        <v>3007.9</v>
+        <v>2991.05</v>
       </c>
       <c r="L26" t="n">
-        <v>3033.1</v>
+        <v>3016.03</v>
       </c>
       <c r="M26" t="n">
-        <v>3042.9</v>
+        <v>3027.15</v>
       </c>
       <c r="N26" t="n">
-        <v>3052.7</v>
+        <v>3038.28</v>
       </c>
       <c r="O26" t="n">
-        <v>3093.3</v>
+        <v>3077.1</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2711,22 +2709,24 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
@@ -2737,57 +2737,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3008.5</v>
+        <v>3038.9</v>
       </c>
       <c r="C27" t="n">
-        <v>3046.8</v>
+        <v>3044.6</v>
       </c>
       <c r="D27" t="n">
-        <v>3002</v>
+        <v>3016</v>
       </c>
       <c r="E27" t="n">
-        <v>3041.6</v>
+        <v>3025</v>
       </c>
       <c r="F27" t="n">
-        <v>32.5</v>
+        <v>-16.6</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0108</v>
+        <v>-0.0055</v>
       </c>
       <c r="H27" t="n">
-        <v>44.8</v>
+        <v>28.6</v>
       </c>
       <c r="I27" t="n">
-        <v>2968.8</v>
+        <v>2957.2</v>
       </c>
       <c r="J27" t="n">
-        <v>2966.08</v>
+        <v>3005.4</v>
       </c>
       <c r="K27" t="n">
-        <v>2991.05</v>
+        <v>3019.2</v>
       </c>
       <c r="L27" t="n">
-        <v>3016.03</v>
+        <v>3033</v>
       </c>
       <c r="M27" t="n">
-        <v>3027.15</v>
+        <v>3064</v>
       </c>
       <c r="N27" t="n">
-        <v>3038.28</v>
+        <v>3095</v>
       </c>
       <c r="O27" t="n">
-        <v>3077.1</v>
+        <v>3091.6</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2795,23 +2795,21 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2823,57 +2821,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3038.9</v>
+        <v>3024.7</v>
       </c>
       <c r="C28" t="n">
-        <v>3044.6</v>
+        <v>3045.8</v>
       </c>
       <c r="D28" t="n">
-        <v>3016</v>
+        <v>3019.9</v>
       </c>
       <c r="E28" t="n">
-        <v>3025</v>
+        <v>3035.5</v>
       </c>
       <c r="F28" t="n">
-        <v>-16.6</v>
+        <v>10.5</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0035</v>
       </c>
       <c r="H28" t="n">
-        <v>28.6</v>
+        <v>25.9</v>
       </c>
       <c r="I28" t="n">
-        <v>2957.2</v>
+        <v>2987.4</v>
       </c>
       <c r="J28" t="n">
-        <v>3005.4</v>
+        <v>2993.75</v>
       </c>
       <c r="K28" t="n">
-        <v>3019.2</v>
+        <v>3010.7</v>
       </c>
       <c r="L28" t="n">
-        <v>3033</v>
+        <v>3027.65</v>
       </c>
       <c r="M28" t="n">
-        <v>3064</v>
+        <v>3039.3</v>
       </c>
       <c r="N28" t="n">
-        <v>3095</v>
+        <v>3050.95</v>
       </c>
       <c r="O28" t="n">
-        <v>3091.6</v>
+        <v>3073.2</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2881,19 +2879,19 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
       <c r="U28" s="8" t="n">
         <v/>
       </c>
@@ -2905,59 +2903,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3024.7</v>
+        <v>3036.1</v>
       </c>
       <c r="C29" t="n">
-        <v>3045.8</v>
+        <v>3060</v>
       </c>
       <c r="D29" t="n">
-        <v>3019.9</v>
+        <v>3033.1</v>
       </c>
       <c r="E29" t="n">
-        <v>3035.5</v>
+        <v>3052.8</v>
       </c>
       <c r="F29" t="n">
-        <v>10.5</v>
+        <v>17.3</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0057</v>
       </c>
       <c r="H29" t="n">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
       <c r="I29" t="n">
-        <v>2987.4</v>
+        <v>2994</v>
       </c>
       <c r="J29" t="n">
-        <v>2993.75</v>
+        <v>3010.92</v>
       </c>
       <c r="K29" t="n">
-        <v>3010.7</v>
+        <v>3022.55</v>
       </c>
       <c r="L29" t="n">
-        <v>3027.65</v>
+        <v>3034.17</v>
       </c>
       <c r="M29" t="n">
-        <v>3039.3</v>
+        <v>3048.45</v>
       </c>
       <c r="N29" t="n">
-        <v>3050.95</v>
+        <v>3062.73</v>
       </c>
       <c r="O29" t="n">
-        <v>3073.2</v>
+        <v>3071.7</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2968,7 +2962,7 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="10" t="inlineStr">
+      <c r="S29" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2994,50 +2988,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3036.1</v>
+        <v>3056.2</v>
       </c>
       <c r="C30" t="n">
-        <v>3060</v>
+        <v>3076.3</v>
       </c>
       <c r="D30" t="n">
-        <v>3033.1</v>
+        <v>3052.5</v>
       </c>
       <c r="E30" t="n">
-        <v>3052.8</v>
+        <v>3060.2</v>
       </c>
       <c r="F30" t="n">
-        <v>17.3</v>
+        <v>7.4</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0024</v>
       </c>
       <c r="H30" t="n">
-        <v>26.9</v>
+        <v>23.8</v>
       </c>
       <c r="I30" t="n">
-        <v>2994</v>
+        <v>3006.2</v>
       </c>
       <c r="J30" t="n">
-        <v>3010.92</v>
+        <v>3029.03</v>
       </c>
       <c r="K30" t="n">
-        <v>3022.55</v>
+        <v>3039.35</v>
       </c>
       <c r="L30" t="n">
-        <v>3034.17</v>
+        <v>3049.68</v>
       </c>
       <c r="M30" t="n">
-        <v>3048.45</v>
+        <v>3066.25</v>
       </c>
       <c r="N30" t="n">
-        <v>3062.73</v>
+        <v>3082.82</v>
       </c>
       <c r="O30" t="n">
-        <v>3071.7</v>
+        <v>3086.9</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3048,7 +3042,7 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3074,50 +3068,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3056.2</v>
+        <v>3062.2</v>
       </c>
       <c r="C31" t="n">
         <v>3076.3</v>
       </c>
       <c r="D31" t="n">
-        <v>3052.5</v>
+        <v>3051.7</v>
       </c>
       <c r="E31" t="n">
-        <v>3060.2</v>
+        <v>3074.9</v>
       </c>
       <c r="F31" t="n">
-        <v>7.4</v>
+        <v>14.7</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0048</v>
       </c>
       <c r="H31" t="n">
-        <v>23.8</v>
+        <v>24.6</v>
       </c>
       <c r="I31" t="n">
-        <v>3006.2</v>
+        <v>3028.7</v>
       </c>
       <c r="J31" t="n">
-        <v>3029.03</v>
+        <v>3034.3</v>
       </c>
       <c r="K31" t="n">
-        <v>3039.35</v>
+        <v>3048.3</v>
       </c>
       <c r="L31" t="n">
-        <v>3049.68</v>
+        <v>3062.3</v>
       </c>
       <c r="M31" t="n">
-        <v>3066.25</v>
+        <v>3072.1</v>
       </c>
       <c r="N31" t="n">
-        <v>3082.82</v>
+        <v>3081.9</v>
       </c>
       <c r="O31" t="n">
-        <v>3086.9</v>
+        <v>3100.1</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3128,7 +3122,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3149,55 +3143,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3062.2</v>
+        <v>3073.5</v>
       </c>
       <c r="C32" t="n">
-        <v>3076.3</v>
+        <v>3079.9</v>
       </c>
       <c r="D32" t="n">
-        <v>3051.7</v>
+        <v>3055.9</v>
       </c>
       <c r="E32" t="n">
-        <v>3074.9</v>
+        <v>3064.9</v>
       </c>
       <c r="F32" t="n">
-        <v>14.7</v>
+        <v>-10</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.0033</v>
       </c>
       <c r="H32" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="I32" t="n">
-        <v>3028.7</v>
+        <v>3027.1</v>
       </c>
       <c r="J32" t="n">
-        <v>3034.3</v>
+        <v>3055.75</v>
       </c>
       <c r="K32" t="n">
-        <v>3048.3</v>
+        <v>3062.6</v>
       </c>
       <c r="L32" t="n">
-        <v>3062.3</v>
+        <v>3069.45</v>
       </c>
       <c r="M32" t="n">
-        <v>3072.1</v>
+        <v>3087.2</v>
       </c>
       <c r="N32" t="n">
-        <v>3081.9</v>
+        <v>3104.95</v>
       </c>
       <c r="O32" t="n">
-        <v>3100.1</v>
+        <v>3100.9</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3205,18 +3203,18 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3238,63 +3236,67 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3073.5</v>
+        <v>3063.7</v>
       </c>
       <c r="C33" t="n">
-        <v>3079.9</v>
+        <v>3066.6</v>
       </c>
       <c r="D33" t="n">
-        <v>3055.9</v>
+        <v>3024.1</v>
       </c>
       <c r="E33" t="n">
-        <v>3064.9</v>
+        <v>3026.4</v>
       </c>
       <c r="F33" t="n">
-        <v>-10</v>
+        <v>-38.5</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0126</v>
       </c>
       <c r="H33" t="n">
-        <v>24</v>
+        <v>42.5</v>
       </c>
       <c r="I33" t="n">
-        <v>3027.1</v>
+        <v>3031.9</v>
       </c>
       <c r="J33" t="n">
-        <v>3055.75</v>
+        <v>3039.4</v>
       </c>
       <c r="K33" t="n">
-        <v>3062.6</v>
+        <v>3052.9</v>
       </c>
       <c r="L33" t="n">
-        <v>3069.45</v>
+        <v>3066.4</v>
       </c>
       <c r="M33" t="n">
-        <v>3087.2</v>
+        <v>3076.9</v>
       </c>
       <c r="N33" t="n">
-        <v>3104.95</v>
+        <v>3087.4</v>
       </c>
       <c r="O33" t="n">
-        <v>3100.9</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
+        <v>3103.9</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3308,88 +3310,80 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W33" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3063.7</v>
+        <v>3025.9</v>
       </c>
       <c r="C34" t="n">
-        <v>3066.6</v>
+        <v>3059.1</v>
       </c>
       <c r="D34" t="n">
-        <v>3024.1</v>
+        <v>3019.8</v>
       </c>
       <c r="E34" t="n">
-        <v>3026.4</v>
+        <v>3039.9</v>
       </c>
       <c r="F34" t="n">
-        <v>-38.5</v>
+        <v>13.5</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0045</v>
       </c>
       <c r="H34" t="n">
-        <v>42.5</v>
+        <v>39.3</v>
       </c>
       <c r="I34" t="n">
-        <v>3031.9</v>
+        <v>2981.6</v>
       </c>
       <c r="J34" t="n">
-        <v>3039.4</v>
+        <v>2974.42</v>
       </c>
       <c r="K34" t="n">
-        <v>3052.9</v>
+        <v>3005.15</v>
       </c>
       <c r="L34" t="n">
-        <v>3066.4</v>
+        <v>3035.88</v>
       </c>
       <c r="M34" t="n">
-        <v>3076.9</v>
+        <v>3047.65</v>
       </c>
       <c r="N34" t="n">
-        <v>3087.4</v>
+        <v>3059.42</v>
       </c>
       <c r="O34" t="n">
-        <v>3103.9</v>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q34" s="6" t="inlineStr">
+        <v>3109.1</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
@@ -3401,74 +3395,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3025.9</v>
+        <v>3041.4</v>
       </c>
       <c r="C35" t="n">
-        <v>3059.1</v>
+        <v>3048.5</v>
       </c>
       <c r="D35" t="n">
-        <v>3019.8</v>
+        <v>2993.2</v>
       </c>
       <c r="E35" t="n">
-        <v>3039.9</v>
+        <v>2999.2</v>
       </c>
       <c r="F35" t="n">
-        <v>13.5</v>
+        <v>-40.7</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0134</v>
       </c>
       <c r="H35" t="n">
-        <v>39.3</v>
+        <v>55.3</v>
       </c>
       <c r="I35" t="n">
-        <v>2981.6</v>
+        <v>2980.5</v>
       </c>
       <c r="J35" t="n">
-        <v>2974.42</v>
+        <v>3000.82</v>
       </c>
       <c r="K35" t="n">
-        <v>3005.15</v>
+        <v>3020.25</v>
       </c>
       <c r="L35" t="n">
-        <v>3035.88</v>
+        <v>3039.67</v>
       </c>
       <c r="M35" t="n">
-        <v>3047.65</v>
+        <v>3059.55</v>
       </c>
       <c r="N35" t="n">
-        <v>3059.42</v>
+        <v>3079.42</v>
       </c>
       <c r="O35" t="n">
-        <v>3109.1</v>
+        <v>3098.4</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3481,81 +3481,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3041.4</v>
+        <v>2999.6</v>
       </c>
       <c r="C36" t="n">
-        <v>3048.5</v>
+        <v>3026.7</v>
       </c>
       <c r="D36" t="n">
-        <v>2993.2</v>
+        <v>2997.9</v>
       </c>
       <c r="E36" t="n">
-        <v>2999.2</v>
+        <v>3022.1</v>
       </c>
       <c r="F36" t="n">
-        <v>-40.7</v>
+        <v>22.9</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0134</v>
+        <v>0.0076</v>
       </c>
       <c r="H36" t="n">
-        <v>55.3</v>
+        <v>28.8</v>
       </c>
       <c r="I36" t="n">
-        <v>2980.5</v>
+        <v>2937.9</v>
       </c>
       <c r="J36" t="n">
-        <v>3000.82</v>
+        <v>2933.07</v>
       </c>
       <c r="K36" t="n">
-        <v>3020.25</v>
+        <v>2971.55</v>
       </c>
       <c r="L36" t="n">
-        <v>3039.67</v>
+        <v>3010.02</v>
       </c>
       <c r="M36" t="n">
-        <v>3059.55</v>
+        <v>3026.85</v>
       </c>
       <c r="N36" t="n">
-        <v>3079.42</v>
+        <v>3043.67</v>
       </c>
       <c r="O36" t="n">
-        <v>3098.4</v>
+        <v>3103.8</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3567,74 +3561,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2999.6</v>
+        <v>3023</v>
       </c>
       <c r="C37" t="n">
-        <v>3026.7</v>
+        <v>3028.9</v>
       </c>
       <c r="D37" t="n">
-        <v>2997.9</v>
+        <v>2996</v>
       </c>
       <c r="E37" t="n">
-        <v>3022.1</v>
+        <v>3001.6</v>
       </c>
       <c r="F37" t="n">
-        <v>22.9</v>
+        <v>-20.5</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0076</v>
+        <v>-0.0068</v>
       </c>
       <c r="H37" t="n">
-        <v>28.8</v>
+        <v>32.9</v>
       </c>
       <c r="I37" t="n">
-        <v>2937.9</v>
+        <v>2969.1</v>
       </c>
       <c r="J37" t="n">
-        <v>2933.07</v>
+        <v>2998.2</v>
       </c>
       <c r="K37" t="n">
-        <v>2971.55</v>
+        <v>3007.7</v>
       </c>
       <c r="L37" t="n">
-        <v>3010.02</v>
+        <v>3017.2</v>
       </c>
       <c r="M37" t="n">
-        <v>3026.85</v>
+        <v>3036.5</v>
       </c>
       <c r="N37" t="n">
-        <v>3043.67</v>
+        <v>3055.8</v>
       </c>
       <c r="O37" t="n">
-        <v>3103.8</v>
+        <v>3055.5</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3649,79 +3649,77 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3023</v>
+        <v>3004.6</v>
       </c>
       <c r="C38" t="n">
-        <v>3028.9</v>
+        <v>3025.4</v>
       </c>
       <c r="D38" t="n">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="E38" t="n">
-        <v>3001.6</v>
+        <v>3014.4</v>
       </c>
       <c r="F38" t="n">
-        <v>-20.5</v>
+        <v>12.8</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0043</v>
       </c>
       <c r="H38" t="n">
-        <v>32.9</v>
+        <v>28.4</v>
       </c>
       <c r="I38" t="n">
-        <v>2969.1</v>
+        <v>2963.1</v>
       </c>
       <c r="J38" t="n">
-        <v>2998.2</v>
+        <v>2963.28</v>
       </c>
       <c r="K38" t="n">
-        <v>3007.7</v>
+        <v>2985.15</v>
       </c>
       <c r="L38" t="n">
-        <v>3017.2</v>
+        <v>3007.03</v>
       </c>
       <c r="M38" t="n">
-        <v>3036.5</v>
+        <v>3018.05</v>
       </c>
       <c r="N38" t="n">
-        <v>3055.8</v>
+        <v>3029.08</v>
       </c>
       <c r="O38" t="n">
-        <v>3055.5</v>
+        <v>3061.8</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3735,57 +3733,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3004.6</v>
+        <v>3014.6</v>
       </c>
       <c r="C39" t="n">
-        <v>3025.4</v>
+        <v>3020.5</v>
       </c>
       <c r="D39" t="n">
-        <v>2997</v>
+        <v>3002.6</v>
       </c>
       <c r="E39" t="n">
-        <v>3014.4</v>
+        <v>3010.1</v>
       </c>
       <c r="F39" t="n">
-        <v>12.8</v>
+        <v>-4.3</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0014</v>
       </c>
       <c r="H39" t="n">
-        <v>28.4</v>
+        <v>17.9</v>
       </c>
       <c r="I39" t="n">
-        <v>2963.1</v>
+        <v>2968.6</v>
       </c>
       <c r="J39" t="n">
-        <v>2963.28</v>
+        <v>2987.6</v>
       </c>
       <c r="K39" t="n">
-        <v>2985.15</v>
+        <v>3000.2</v>
       </c>
       <c r="L39" t="n">
-        <v>3007.03</v>
+        <v>3012.8</v>
       </c>
       <c r="M39" t="n">
-        <v>3018.05</v>
+        <v>3028.6</v>
       </c>
       <c r="N39" t="n">
-        <v>3029.08</v>
+        <v>3044.4</v>
       </c>
       <c r="O39" t="n">
-        <v>3061.8</v>
+        <v>3053.8</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3798,13 +3796,11 @@
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3819,57 +3815,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3014.6</v>
+        <v>3016.9</v>
       </c>
       <c r="C40" t="n">
-        <v>3020.5</v>
+        <v>3024.2</v>
       </c>
       <c r="D40" t="n">
-        <v>3002.6</v>
+        <v>3002.1</v>
       </c>
       <c r="E40" t="n">
-        <v>3010.1</v>
+        <v>3019</v>
       </c>
       <c r="F40" t="n">
-        <v>-4.3</v>
+        <v>8.9</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0014</v>
+        <v>0.003</v>
       </c>
       <c r="H40" t="n">
-        <v>17.9</v>
+        <v>22.1</v>
       </c>
       <c r="I40" t="n">
-        <v>2968.6</v>
+        <v>2984.7</v>
       </c>
       <c r="J40" t="n">
-        <v>2987.6</v>
+        <v>2991.48</v>
       </c>
       <c r="K40" t="n">
-        <v>3000.2</v>
+        <v>3001.15</v>
       </c>
       <c r="L40" t="n">
-        <v>3012.8</v>
+        <v>3010.83</v>
       </c>
       <c r="M40" t="n">
-        <v>3028.6</v>
+        <v>3019.05</v>
       </c>
       <c r="N40" t="n">
-        <v>3044.4</v>
+        <v>3027.28</v>
       </c>
       <c r="O40" t="n">
-        <v>3053.8</v>
+        <v>3038.4</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3882,11 +3878,13 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3901,76 +3899,80 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3016.9</v>
+        <v>3019.6</v>
       </c>
       <c r="C41" t="n">
-        <v>3024.2</v>
+        <v>3025.5</v>
       </c>
       <c r="D41" t="n">
-        <v>3002.1</v>
+        <v>2976.6</v>
       </c>
       <c r="E41" t="n">
-        <v>3019</v>
+        <v>2977.5</v>
       </c>
       <c r="F41" t="n">
-        <v>8.9</v>
+        <v>-41.5</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0137</v>
       </c>
       <c r="H41" t="n">
-        <v>22.1</v>
+        <v>48.9</v>
       </c>
       <c r="I41" t="n">
-        <v>2984.7</v>
+        <v>2980</v>
       </c>
       <c r="J41" t="n">
-        <v>2991.48</v>
+        <v>2999.83</v>
       </c>
       <c r="K41" t="n">
-        <v>3001.15</v>
+        <v>3007.95</v>
       </c>
       <c r="L41" t="n">
-        <v>3010.83</v>
+        <v>3016.08</v>
       </c>
       <c r="M41" t="n">
-        <v>3019.05</v>
+        <v>3030.05</v>
       </c>
       <c r="N41" t="n">
-        <v>3027.28</v>
+        <v>3044.02</v>
       </c>
       <c r="O41" t="n">
-        <v>3038.4</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+        <v>3046.3</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3985,74 +3987,70 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3019.6</v>
+        <v>2971</v>
       </c>
       <c r="C42" t="n">
-        <v>3025.5</v>
+        <v>2982.5</v>
       </c>
       <c r="D42" t="n">
-        <v>2976.6</v>
+        <v>2946.1</v>
       </c>
       <c r="E42" t="n">
-        <v>2977.5</v>
+        <v>2958.7</v>
       </c>
       <c r="F42" t="n">
-        <v>-41.5</v>
+        <v>-18.8</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0063</v>
       </c>
       <c r="H42" t="n">
-        <v>48.9</v>
+        <v>36.4</v>
       </c>
       <c r="I42" t="n">
-        <v>2980</v>
+        <v>2927.7</v>
       </c>
       <c r="J42" t="n">
-        <v>2999.83</v>
+        <v>2916.83</v>
       </c>
       <c r="K42" t="n">
-        <v>3007.95</v>
+        <v>2953.05</v>
       </c>
       <c r="L42" t="n">
-        <v>3016.08</v>
+        <v>2989.28</v>
       </c>
       <c r="M42" t="n">
-        <v>3030.05</v>
+        <v>3001.95</v>
       </c>
       <c r="N42" t="n">
-        <v>3044.02</v>
+        <v>3014.62</v>
       </c>
       <c r="O42" t="n">
-        <v>3046.3</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
+        <v>3074.4</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4071,72 +4069,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2971</v>
+        <v>2958</v>
       </c>
       <c r="C43" t="n">
-        <v>2982.5</v>
+        <v>2964.6</v>
       </c>
       <c r="D43" t="n">
-        <v>2946.1</v>
+        <v>2918.9</v>
       </c>
       <c r="E43" t="n">
-        <v>2958.7</v>
+        <v>2924.7</v>
       </c>
       <c r="F43" t="n">
-        <v>-18.8</v>
+        <v>-34</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0115</v>
       </c>
       <c r="H43" t="n">
-        <v>36.4</v>
+        <v>45.7</v>
       </c>
       <c r="I43" t="n">
-        <v>2927.7</v>
+        <v>2909.7</v>
       </c>
       <c r="J43" t="n">
-        <v>2916.83</v>
+        <v>2919.5</v>
       </c>
       <c r="K43" t="n">
-        <v>2953.05</v>
+        <v>2940.5</v>
       </c>
       <c r="L43" t="n">
-        <v>2989.28</v>
+        <v>2961.5</v>
       </c>
       <c r="M43" t="n">
-        <v>3001.95</v>
+        <v>2976.9</v>
       </c>
       <c r="N43" t="n">
-        <v>3014.62</v>
+        <v>2992.3</v>
       </c>
       <c r="O43" t="n">
-        <v>3074.4</v>
+        <v>3018.9</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4160,75 +4156,75 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2958</v>
+        <v>2926.4</v>
       </c>
       <c r="C44" t="n">
-        <v>2964.6</v>
+        <v>2962.5</v>
       </c>
       <c r="D44" t="n">
-        <v>2918.9</v>
+        <v>2914.5</v>
       </c>
       <c r="E44" t="n">
-        <v>2924.7</v>
+        <v>2958.8</v>
       </c>
       <c r="F44" t="n">
-        <v>-34</v>
+        <v>34.1</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0.0117</v>
       </c>
       <c r="H44" t="n">
-        <v>45.7</v>
+        <v>48</v>
       </c>
       <c r="I44" t="n">
-        <v>2909.7</v>
+        <v>2873.2</v>
       </c>
       <c r="J44" t="n">
-        <v>2919.5</v>
+        <v>2870.47</v>
       </c>
       <c r="K44" t="n">
-        <v>2940.5</v>
+        <v>2901.85</v>
       </c>
       <c r="L44" t="n">
-        <v>2961.5</v>
+        <v>2933.22</v>
       </c>
       <c r="M44" t="n">
-        <v>2976.9</v>
+        <v>2947.55</v>
       </c>
       <c r="N44" t="n">
-        <v>2992.3</v>
+        <v>2961.88</v>
       </c>
       <c r="O44" t="n">
-        <v>3018.9</v>
+        <v>3010.3</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
@@ -4237,55 +4233,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2926.4</v>
+        <v>2957.6</v>
       </c>
       <c r="C45" t="n">
-        <v>2962.5</v>
+        <v>2983.3</v>
       </c>
       <c r="D45" t="n">
-        <v>2914.5</v>
+        <v>2949.9</v>
       </c>
       <c r="E45" t="n">
-        <v>2958.8</v>
+        <v>2969.7</v>
       </c>
       <c r="F45" t="n">
-        <v>34.1</v>
+        <v>10.9</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0117</v>
+        <v>0.0037</v>
       </c>
       <c r="H45" t="n">
-        <v>48</v>
+        <v>33.4</v>
       </c>
       <c r="I45" t="n">
-        <v>2873.2</v>
+        <v>2866.5</v>
       </c>
       <c r="J45" t="n">
-        <v>2870.47</v>
+        <v>2920.95</v>
       </c>
       <c r="K45" t="n">
-        <v>2901.85</v>
+        <v>2934.8</v>
       </c>
       <c r="L45" t="n">
-        <v>2933.22</v>
+        <v>2948.65</v>
       </c>
       <c r="M45" t="n">
-        <v>2947.55</v>
+        <v>2982.8</v>
       </c>
       <c r="N45" t="n">
-        <v>2961.88</v>
+        <v>3016.95</v>
       </c>
       <c r="O45" t="n">
-        <v>3010.3</v>
+        <v>3010.5</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4296,21 +4296,19 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="S45" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
@@ -4321,57 +4319,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2957.6</v>
+        <v>2967.9</v>
       </c>
       <c r="C46" t="n">
-        <v>2983.3</v>
+        <v>2979.3</v>
       </c>
       <c r="D46" t="n">
-        <v>2949.9</v>
+        <v>2949.5</v>
       </c>
       <c r="E46" t="n">
-        <v>2969.7</v>
+        <v>2976.6</v>
       </c>
       <c r="F46" t="n">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0023</v>
       </c>
       <c r="H46" t="n">
-        <v>33.4</v>
+        <v>29.8</v>
       </c>
       <c r="I46" t="n">
-        <v>2866.5</v>
+        <v>2916.5</v>
       </c>
       <c r="J46" t="n">
-        <v>2920.95</v>
+        <v>2937.85</v>
       </c>
       <c r="K46" t="n">
-        <v>2934.8</v>
+        <v>2953</v>
       </c>
       <c r="L46" t="n">
-        <v>2948.65</v>
+        <v>2968.15</v>
       </c>
       <c r="M46" t="n">
-        <v>2982.8</v>
+        <v>2986.4</v>
       </c>
       <c r="N46" t="n">
-        <v>3016.95</v>
+        <v>3004.65</v>
       </c>
       <c r="O46" t="n">
-        <v>3010.5</v>
+        <v>3016.7</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4379,18 +4377,18 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4405,57 +4403,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2967.9</v>
+        <v>2974.7</v>
       </c>
       <c r="C47" t="n">
-        <v>2979.3</v>
+        <v>2977.9</v>
       </c>
       <c r="D47" t="n">
-        <v>2949.5</v>
+        <v>2954.7</v>
       </c>
       <c r="E47" t="n">
-        <v>2976.6</v>
+        <v>2963.6</v>
       </c>
       <c r="F47" t="n">
-        <v>6.9</v>
+        <v>-13</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0044</v>
       </c>
       <c r="H47" t="n">
-        <v>29.8</v>
+        <v>23.2</v>
       </c>
       <c r="I47" t="n">
-        <v>2916.5</v>
+        <v>2919.7</v>
       </c>
       <c r="J47" t="n">
-        <v>2937.85</v>
+        <v>2952.9</v>
       </c>
       <c r="K47" t="n">
-        <v>2953</v>
+        <v>2961.7</v>
       </c>
       <c r="L47" t="n">
-        <v>2968.15</v>
+        <v>2970.5</v>
       </c>
       <c r="M47" t="n">
-        <v>2986.4</v>
+        <v>2991.5</v>
       </c>
       <c r="N47" t="n">
-        <v>3004.65</v>
+        <v>3012.5</v>
       </c>
       <c r="O47" t="n">
-        <v>3016.7</v>
+        <v>3009.1</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4465,12 +4463,12 @@
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4496,63 +4494,67 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2974.7</v>
+        <v>2963.1</v>
       </c>
       <c r="C48" t="n">
-        <v>2977.9</v>
+        <v>2966.2</v>
       </c>
       <c r="D48" t="n">
-        <v>2954.7</v>
+        <v>2919.4</v>
       </c>
       <c r="E48" t="n">
-        <v>2963.6</v>
+        <v>2923</v>
       </c>
       <c r="F48" t="n">
-        <v>-13</v>
+        <v>-40.6</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0137</v>
       </c>
       <c r="H48" t="n">
-        <v>23.2</v>
+        <v>46.8</v>
       </c>
       <c r="I48" t="n">
-        <v>2919.7</v>
+        <v>2931.5</v>
       </c>
       <c r="J48" t="n">
-        <v>2952.9</v>
+        <v>2939.05</v>
       </c>
       <c r="K48" t="n">
-        <v>2961.7</v>
+        <v>2952</v>
       </c>
       <c r="L48" t="n">
-        <v>2970.5</v>
+        <v>2964.95</v>
       </c>
       <c r="M48" t="n">
-        <v>2991.5</v>
+        <v>2975.2</v>
       </c>
       <c r="N48" t="n">
-        <v>3012.5</v>
+        <v>2985.45</v>
       </c>
       <c r="O48" t="n">
-        <v>3009.1</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
+        <v>3001.1</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4571,76 +4573,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2963.1</v>
+        <v>2923.1</v>
       </c>
       <c r="C49" t="n">
-        <v>2966.2</v>
+        <v>2933.8</v>
       </c>
       <c r="D49" t="n">
-        <v>2919.4</v>
+        <v>2887.8</v>
       </c>
       <c r="E49" t="n">
-        <v>2923</v>
+        <v>2893.4</v>
       </c>
       <c r="F49" t="n">
-        <v>-40.6</v>
+        <v>-29.6</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0101</v>
       </c>
       <c r="H49" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="I49" t="n">
-        <v>2931.5</v>
+        <v>2872.6</v>
       </c>
       <c r="J49" t="n">
-        <v>2939.05</v>
+        <v>2866.3</v>
       </c>
       <c r="K49" t="n">
-        <v>2952</v>
+        <v>2899.6</v>
       </c>
       <c r="L49" t="n">
-        <v>2964.95</v>
+        <v>2932.9</v>
       </c>
       <c r="M49" t="n">
-        <v>2975.2</v>
+        <v>2946.4</v>
       </c>
       <c r="N49" t="n">
-        <v>2985.45</v>
+        <v>2959.9</v>
       </c>
       <c r="O49" t="n">
-        <v>3001.1</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
+        <v>3013</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4664,50 +4658,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2923.1</v>
+        <v>2890.9</v>
       </c>
       <c r="C50" t="n">
-        <v>2933.8</v>
+        <v>2929.8</v>
       </c>
       <c r="D50" t="n">
-        <v>2887.8</v>
+        <v>2887.6</v>
       </c>
       <c r="E50" t="n">
-        <v>2893.4</v>
+        <v>2904.5</v>
       </c>
       <c r="F50" t="n">
-        <v>-29.6</v>
+        <v>11.1</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0101</v>
+        <v>0.0038</v>
       </c>
       <c r="H50" t="n">
-        <v>46</v>
+        <v>42.2</v>
       </c>
       <c r="I50" t="n">
-        <v>2872.6</v>
+        <v>2841.8</v>
       </c>
       <c r="J50" t="n">
-        <v>2866.3</v>
+        <v>2838.7</v>
       </c>
       <c r="K50" t="n">
-        <v>2899.6</v>
+        <v>2870.4</v>
       </c>
       <c r="L50" t="n">
-        <v>2932.9</v>
+        <v>2902.1</v>
       </c>
       <c r="M50" t="n">
-        <v>2946.4</v>
+        <v>2916.4</v>
       </c>
       <c r="N50" t="n">
-        <v>2959.9</v>
+        <v>2930.7</v>
       </c>
       <c r="O50" t="n">
-        <v>3013</v>
+        <v>2979.8</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4715,18 +4709,18 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R50" s="6" t="n">
+        <v/>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4739,55 +4733,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2890.9</v>
+        <v>2892.7</v>
       </c>
       <c r="C51" t="n">
-        <v>2929.8</v>
+        <v>2913.5</v>
       </c>
       <c r="D51" t="n">
-        <v>2887.6</v>
+        <v>2884.3</v>
       </c>
       <c r="E51" t="n">
-        <v>2904.5</v>
+        <v>2894.1</v>
       </c>
       <c r="F51" t="n">
-        <v>11.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0036</v>
       </c>
       <c r="H51" t="n">
-        <v>42.2</v>
+        <v>29.2</v>
       </c>
       <c r="I51" t="n">
-        <v>2841.8</v>
+        <v>2845.4</v>
       </c>
       <c r="J51" t="n">
-        <v>2838.7</v>
+        <v>2860.2</v>
       </c>
       <c r="K51" t="n">
-        <v>2870.4</v>
+        <v>2883.4</v>
       </c>
       <c r="L51" t="n">
-        <v>2902.1</v>
+        <v>2906.6</v>
       </c>
       <c r="M51" t="n">
-        <v>2916.4</v>
+        <v>2925.6</v>
       </c>
       <c r="N51" t="n">
-        <v>2930.7</v>
+        <v>2944.6</v>
       </c>
       <c r="O51" t="n">
-        <v>2979.8</v>
+        <v>2972</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4795,18 +4793,18 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4819,59 +4817,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2892.7</v>
+        <v>2896.4</v>
       </c>
       <c r="C52" t="n">
-        <v>2913.5</v>
+        <v>2896.5</v>
       </c>
       <c r="D52" t="n">
-        <v>2884.3</v>
+        <v>2862.7</v>
       </c>
       <c r="E52" t="n">
-        <v>2894.1</v>
+        <v>2873.1</v>
       </c>
       <c r="F52" t="n">
-        <v>-10.4</v>
+        <v>-21</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0073</v>
       </c>
       <c r="H52" t="n">
-        <v>29.2</v>
+        <v>33.8</v>
       </c>
       <c r="I52" t="n">
-        <v>2845.4</v>
+        <v>2855.1</v>
       </c>
       <c r="J52" t="n">
-        <v>2860.2</v>
+        <v>2862.5</v>
       </c>
       <c r="K52" t="n">
-        <v>2883.4</v>
+        <v>2879.5</v>
       </c>
       <c r="L52" t="n">
-        <v>2906.6</v>
+        <v>2896.5</v>
       </c>
       <c r="M52" t="n">
-        <v>2925.6</v>
+        <v>2908.7</v>
       </c>
       <c r="N52" t="n">
-        <v>2944.6</v>
+        <v>2920.9</v>
       </c>
       <c r="O52" t="n">
-        <v>2972</v>
+        <v>2942.7</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4884,7 +4878,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4908,69 +4902,73 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2896.4</v>
+        <v>2875.1</v>
       </c>
       <c r="C53" t="n">
-        <v>2896.5</v>
+        <v>2892.5</v>
       </c>
       <c r="D53" t="n">
-        <v>2862.7</v>
+        <v>2831.9</v>
       </c>
       <c r="E53" t="n">
-        <v>2873.1</v>
+        <v>2861.7</v>
       </c>
       <c r="F53" t="n">
-        <v>-21</v>
+        <v>-11.4</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.004</v>
       </c>
       <c r="H53" t="n">
-        <v>33.8</v>
+        <v>60.6</v>
       </c>
       <c r="I53" t="n">
-        <v>2855.1</v>
+        <v>2828.9</v>
       </c>
       <c r="J53" t="n">
-        <v>2862.5</v>
+        <v>2836.05</v>
       </c>
       <c r="K53" t="n">
-        <v>2879.5</v>
+        <v>2856.2</v>
       </c>
       <c r="L53" t="n">
-        <v>2896.5</v>
+        <v>2876.35</v>
       </c>
       <c r="M53" t="n">
-        <v>2908.7</v>
+        <v>2890</v>
       </c>
       <c r="N53" t="n">
-        <v>2920.9</v>
+        <v>2903.65</v>
       </c>
       <c r="O53" t="n">
-        <v>2942.7</v>
+        <v>2930.3</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4988,74 +4986,70 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2875.1</v>
+        <v>2861.2</v>
       </c>
       <c r="C54" t="n">
-        <v>2892.5</v>
+        <v>2904.6</v>
       </c>
       <c r="D54" t="n">
-        <v>2831.9</v>
+        <v>2859.3</v>
       </c>
       <c r="E54" t="n">
-        <v>2861.7</v>
+        <v>2875.9</v>
       </c>
       <c r="F54" t="n">
-        <v>-11.4</v>
+        <v>14.2</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.005</v>
       </c>
       <c r="H54" t="n">
-        <v>60.6</v>
+        <v>45.3</v>
       </c>
       <c r="I54" t="n">
-        <v>2828.9</v>
+        <v>2771.3</v>
       </c>
       <c r="J54" t="n">
-        <v>2836.05</v>
+        <v>2800.85</v>
       </c>
       <c r="K54" t="n">
-        <v>2856.2</v>
+        <v>2831.4</v>
       </c>
       <c r="L54" t="n">
-        <v>2876.35</v>
+        <v>2861.95</v>
       </c>
       <c r="M54" t="n">
-        <v>2890</v>
+        <v>2892</v>
       </c>
       <c r="N54" t="n">
-        <v>2903.65</v>
+        <v>2922.05</v>
       </c>
       <c r="O54" t="n">
-        <v>2930.3</v>
+        <v>2953.1</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U54" s="8" t="n">
         <v/>
       </c>
@@ -5067,55 +5061,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2861.2</v>
+        <v>2870.5</v>
       </c>
       <c r="C55" t="n">
-        <v>2904.6</v>
+        <v>2883</v>
       </c>
       <c r="D55" t="n">
-        <v>2859.3</v>
+        <v>2856.9</v>
       </c>
       <c r="E55" t="n">
-        <v>2875.9</v>
+        <v>2873.23</v>
       </c>
       <c r="F55" t="n">
-        <v>14.2</v>
+        <v>-2.67</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0009</v>
       </c>
       <c r="H55" t="n">
-        <v>45.3</v>
+        <v>26.1</v>
       </c>
       <c r="I55" t="n">
-        <v>2771.3</v>
+        <v>2814</v>
       </c>
       <c r="J55" t="n">
-        <v>2800.85</v>
+        <v>2827.57</v>
       </c>
       <c r="K55" t="n">
-        <v>2831.4</v>
+        <v>2853.25</v>
       </c>
       <c r="L55" t="n">
-        <v>2861.95</v>
+        <v>2878.92</v>
       </c>
       <c r="M55" t="n">
-        <v>2892</v>
+        <v>2898.55</v>
       </c>
       <c r="N55" t="n">
-        <v>2922.05</v>
+        <v>2918.17</v>
       </c>
       <c r="O55" t="n">
-        <v>2953.1</v>
+        <v>2949.9</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5128,13 +5126,11 @@
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5147,59 +5143,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2870.5</v>
+        <v>2879.5</v>
       </c>
       <c r="C56" t="n">
-        <v>2883</v>
+        <v>2907.3</v>
       </c>
       <c r="D56" t="n">
-        <v>2856.9</v>
+        <v>2876.6</v>
       </c>
       <c r="E56" t="n">
-        <v>2873.23</v>
+        <v>2897.4</v>
       </c>
       <c r="F56" t="n">
-        <v>-2.67</v>
+        <v>24.17</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>26.1</v>
+        <v>30.7</v>
       </c>
       <c r="I56" t="n">
-        <v>2814</v>
+        <v>2830.8</v>
       </c>
       <c r="J56" t="n">
-        <v>2827.57</v>
+        <v>2848.77</v>
       </c>
       <c r="K56" t="n">
-        <v>2853.25</v>
+        <v>2860.18</v>
       </c>
       <c r="L56" t="n">
-        <v>2878.92</v>
+        <v>2871.59</v>
       </c>
       <c r="M56" t="n">
-        <v>2898.55</v>
+        <v>2886.28</v>
       </c>
       <c r="N56" t="n">
-        <v>2918.17</v>
+        <v>2900.97</v>
       </c>
       <c r="O56" t="n">
-        <v>2949.9</v>
+        <v>2909.1</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5212,14 +5204,18 @@
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5229,55 +5225,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2879.5</v>
+        <v>2897.8</v>
       </c>
       <c r="C57" t="n">
-        <v>2907.3</v>
+        <v>2931.2</v>
       </c>
       <c r="D57" t="n">
-        <v>2876.6</v>
+        <v>2884.2</v>
       </c>
       <c r="E57" t="n">
-        <v>2897.4</v>
+        <v>2914.1</v>
       </c>
       <c r="F57" t="n">
-        <v>24.17</v>
+        <v>16.7</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0058</v>
       </c>
       <c r="H57" t="n">
-        <v>30.7</v>
+        <v>47</v>
       </c>
       <c r="I57" t="n">
-        <v>2830.8</v>
+        <v>2845.9</v>
       </c>
       <c r="J57" t="n">
-        <v>2848.77</v>
+        <v>2869.42</v>
       </c>
       <c r="K57" t="n">
-        <v>2860.18</v>
+        <v>2882.05</v>
       </c>
       <c r="L57" t="n">
-        <v>2871.59</v>
+        <v>2894.67</v>
       </c>
       <c r="M57" t="n">
-        <v>2886.28</v>
+        <v>2912.75</v>
       </c>
       <c r="N57" t="n">
-        <v>2900.97</v>
+        <v>2930.82</v>
       </c>
       <c r="O57" t="n">
-        <v>2909.1</v>
+        <v>2938</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5288,19 +5288,19 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="10" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="V57" s="8" t="n">
@@ -5320,74 +5320,74 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2897.8</v>
+        <v>2912</v>
       </c>
       <c r="C58" t="n">
-        <v>2931.2</v>
+        <v>2915.3</v>
       </c>
       <c r="D58" t="n">
-        <v>2884.2</v>
+        <v>2858.8</v>
       </c>
       <c r="E58" t="n">
-        <v>2914.1</v>
+        <v>2860.2</v>
       </c>
       <c r="F58" t="n">
-        <v>16.7</v>
+        <v>-53.9</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0185</v>
       </c>
       <c r="H58" t="n">
-        <v>47</v>
+        <v>56.5</v>
       </c>
       <c r="I58" t="n">
-        <v>2845.9</v>
+        <v>2837.2</v>
       </c>
       <c r="J58" t="n">
-        <v>2869.42</v>
+        <v>2870.3</v>
       </c>
       <c r="K58" t="n">
-        <v>2882.05</v>
+        <v>2890.6</v>
       </c>
       <c r="L58" t="n">
-        <v>2894.67</v>
+        <v>2910.9</v>
       </c>
       <c r="M58" t="n">
-        <v>2912.75</v>
+        <v>2937.6</v>
       </c>
       <c r="N58" t="n">
-        <v>2930.82</v>
+        <v>2964.3</v>
       </c>
       <c r="O58" t="n">
-        <v>2938</v>
+        <v>2978.2</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5397,76 +5397,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2912</v>
+        <v>2860.7</v>
       </c>
       <c r="C59" t="n">
-        <v>2915.3</v>
+        <v>2862.4</v>
       </c>
       <c r="D59" t="n">
-        <v>2858.8</v>
+        <v>2829.9</v>
       </c>
       <c r="E59" t="n">
-        <v>2860.2</v>
+        <v>2856.8</v>
       </c>
       <c r="F59" t="n">
-        <v>-53.9</v>
+        <v>-3.4</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0012</v>
       </c>
       <c r="H59" t="n">
-        <v>56.5</v>
+        <v>32.5</v>
       </c>
       <c r="I59" t="n">
-        <v>2837.2</v>
+        <v>2802.3</v>
       </c>
       <c r="J59" t="n">
-        <v>2870.3</v>
+        <v>2790.27</v>
       </c>
       <c r="K59" t="n">
-        <v>2890.6</v>
+        <v>2831.95</v>
       </c>
       <c r="L59" t="n">
-        <v>2910.9</v>
+        <v>2873.62</v>
       </c>
       <c r="M59" t="n">
-        <v>2937.6</v>
+        <v>2888.45</v>
       </c>
       <c r="N59" t="n">
-        <v>2964.3</v>
+        <v>2903.27</v>
       </c>
       <c r="O59" t="n">
-        <v>2978.2</v>
+        <v>2971.8</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q59" s="6" t="n">
+        <v/>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5488,50 +5482,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2860.7</v>
+        <v>2854.4</v>
       </c>
       <c r="C60" t="n">
-        <v>2862.4</v>
+        <v>2874.1</v>
       </c>
       <c r="D60" t="n">
-        <v>2829.9</v>
+        <v>2843</v>
       </c>
       <c r="E60" t="n">
-        <v>2856.8</v>
+        <v>2859.3</v>
       </c>
       <c r="F60" t="n">
-        <v>-3.4</v>
+        <v>2.5</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="H60" t="n">
-        <v>32.5</v>
+        <v>31.1</v>
       </c>
       <c r="I60" t="n">
-        <v>2802.3</v>
+        <v>2797.4</v>
       </c>
       <c r="J60" t="n">
-        <v>2790.27</v>
+        <v>2829.63</v>
       </c>
       <c r="K60" t="n">
-        <v>2831.95</v>
+        <v>2840.55</v>
       </c>
       <c r="L60" t="n">
-        <v>2873.62</v>
+        <v>2851.47</v>
       </c>
       <c r="M60" t="n">
-        <v>2888.45</v>
+        <v>2873.05</v>
       </c>
       <c r="N60" t="n">
-        <v>2903.27</v>
+        <v>2894.63</v>
       </c>
       <c r="O60" t="n">
-        <v>2971.8</v>
+        <v>2894.9</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5539,19 +5533,19 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
       <c r="U60" s="8" t="n">
         <v/>
       </c>
@@ -5563,74 +5557,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2854.4</v>
+        <v>2857.7</v>
       </c>
       <c r="C61" t="n">
-        <v>2874.1</v>
+        <v>2858.8</v>
       </c>
       <c r="D61" t="n">
-        <v>2843</v>
+        <v>2826.8</v>
       </c>
       <c r="E61" t="n">
-        <v>2859.3</v>
+        <v>2840.1</v>
       </c>
       <c r="F61" t="n">
-        <v>2.5</v>
+        <v>-19.2</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0067</v>
       </c>
       <c r="H61" t="n">
-        <v>31.1</v>
+        <v>32</v>
       </c>
       <c r="I61" t="n">
-        <v>2797.4</v>
+        <v>2811.9</v>
       </c>
       <c r="J61" t="n">
-        <v>2829.63</v>
+        <v>2828.57</v>
       </c>
       <c r="K61" t="n">
-        <v>2840.55</v>
+        <v>2843.75</v>
       </c>
       <c r="L61" t="n">
-        <v>2851.47</v>
+        <v>2858.93</v>
       </c>
       <c r="M61" t="n">
-        <v>2873.05</v>
+        <v>2874.85</v>
       </c>
       <c r="N61" t="n">
-        <v>2894.63</v>
+        <v>2890.78</v>
       </c>
       <c r="O61" t="n">
-        <v>2894.9</v>
+        <v>2905.2</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5643,59 +5643,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2839.6</v>
+        <v>2831.6</v>
       </c>
       <c r="C62" t="n">
-        <v>2841.2</v>
+        <v>2834.9</v>
       </c>
       <c r="D62" t="n">
-        <v>2837.5</v>
+        <v>2831.4</v>
       </c>
       <c r="E62" t="n">
-        <v>2837.8</v>
+        <v>2834.1</v>
       </c>
       <c r="F62" t="n">
-        <v>-21.5</v>
+        <v>-6</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0075</v>
+        <v>-0.0021</v>
       </c>
       <c r="H62" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I62" t="n">
-        <v>2811.9</v>
+        <v>2794.8</v>
       </c>
       <c r="J62" t="n">
-        <v>2828.57</v>
+        <v>2806.75</v>
       </c>
       <c r="K62" t="n">
-        <v>2843.75</v>
+        <v>2824.1</v>
       </c>
       <c r="L62" t="n">
-        <v>2858.93</v>
+        <v>2841.45</v>
       </c>
       <c r="M62" t="n">
-        <v>2874.85</v>
+        <v>2856.1</v>
       </c>
       <c r="N62" t="n">
-        <v>2890.78</v>
+        <v>2870.75</v>
       </c>
       <c r="O62" t="n">
-        <v>2905.2</v>
+        <v>2890.8</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5703,14 +5699,12 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5727,7 +5721,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,63 +634,67 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3019.7</v>
+        <v>3033.4</v>
       </c>
       <c r="C2" t="n">
-        <v>3042.1</v>
+        <v>3042.6</v>
       </c>
       <c r="D2" t="n">
-        <v>3006.7</v>
+        <v>2988.8</v>
       </c>
       <c r="E2" t="n">
-        <v>3027</v>
+        <v>2998.8</v>
       </c>
       <c r="F2" t="n">
-        <v>12.8</v>
+        <v>-28.2</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>35.4</v>
+        <v>53.8</v>
       </c>
       <c r="I2" t="n">
-        <v>2914.6</v>
+        <v>2971.3</v>
       </c>
       <c r="J2" t="n">
-        <v>2934.68</v>
+        <v>2992.9</v>
       </c>
       <c r="K2" t="n">
-        <v>2977.25</v>
+        <v>3009.3</v>
       </c>
       <c r="L2" t="n">
-        <v>3019.82</v>
+        <v>3025.7</v>
       </c>
       <c r="M2" t="n">
-        <v>3051.15</v>
+        <v>3044.7</v>
       </c>
       <c r="N2" t="n">
-        <v>3082.47</v>
+        <v>3063.7</v>
       </c>
       <c r="O2" t="n">
-        <v>3136.3</v>
+        <v>3077.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -709,72 +713,70 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3033.4</v>
+        <v>2994.3</v>
       </c>
       <c r="C3" t="n">
-        <v>3042.6</v>
+        <v>3004.3</v>
       </c>
       <c r="D3" t="n">
-        <v>2988.8</v>
+        <v>2943.4</v>
       </c>
       <c r="E3" t="n">
-        <v>2998.8</v>
+        <v>2971.5</v>
       </c>
       <c r="F3" t="n">
-        <v>-28.2</v>
+        <v>-27.3</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0091</v>
       </c>
       <c r="H3" t="n">
-        <v>53.8</v>
+        <v>60.9</v>
       </c>
       <c r="I3" t="n">
-        <v>2971.3</v>
+        <v>2935</v>
       </c>
       <c r="J3" t="n">
-        <v>2992.9</v>
+        <v>2936.55</v>
       </c>
       <c r="K3" t="n">
-        <v>3009.3</v>
+        <v>2971.9</v>
       </c>
       <c r="L3" t="n">
+        <v>3007.25</v>
+      </c>
+      <c r="M3" t="n">
         <v>3025.7</v>
       </c>
-      <c r="M3" t="n">
-        <v>3044.7</v>
-      </c>
       <c r="N3" t="n">
-        <v>3063.7</v>
+        <v>3044.15</v>
       </c>
       <c r="O3" t="n">
-        <v>3077.5</v>
+        <v>3096.4</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -795,57 +797,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2994.3</v>
+        <v>2965.8</v>
       </c>
       <c r="C4" t="n">
-        <v>3004.3</v>
+        <v>3014.9</v>
       </c>
       <c r="D4" t="n">
-        <v>2943.4</v>
+        <v>2964.3</v>
       </c>
       <c r="E4" t="n">
-        <v>2971.5</v>
+        <v>3008.4</v>
       </c>
       <c r="F4" t="n">
-        <v>-27.3</v>
+        <v>36.9</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0091</v>
+        <v>0.0124</v>
       </c>
       <c r="H4" t="n">
-        <v>60.9</v>
+        <v>50.6</v>
       </c>
       <c r="I4" t="n">
-        <v>2935</v>
+        <v>2882.5</v>
       </c>
       <c r="J4" t="n">
-        <v>2936.55</v>
+        <v>2909.42</v>
       </c>
       <c r="K4" t="n">
-        <v>2971.9</v>
+        <v>2941.05</v>
       </c>
       <c r="L4" t="n">
-        <v>3007.25</v>
+        <v>2972.67</v>
       </c>
       <c r="M4" t="n">
-        <v>3025.7</v>
+        <v>3001.95</v>
       </c>
       <c r="N4" t="n">
-        <v>3044.15</v>
+        <v>3031.23</v>
       </c>
       <c r="O4" t="n">
-        <v>3096.4</v>
+        <v>3065.2</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -853,19 +855,19 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -877,59 +879,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2965.8</v>
+        <v>3008.1</v>
       </c>
       <c r="C5" t="n">
-        <v>3014.9</v>
+        <v>3019.5</v>
       </c>
       <c r="D5" t="n">
-        <v>2964.3</v>
+        <v>2970.8</v>
       </c>
       <c r="E5" t="n">
-        <v>3008.4</v>
+        <v>2994</v>
       </c>
       <c r="F5" t="n">
-        <v>36.9</v>
+        <v>-14.4</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0048</v>
       </c>
       <c r="H5" t="n">
-        <v>50.6</v>
+        <v>48.7</v>
       </c>
       <c r="I5" t="n">
-        <v>2882.5</v>
+        <v>2913.7</v>
       </c>
       <c r="J5" t="n">
-        <v>2909.42</v>
+        <v>2967.2</v>
       </c>
       <c r="K5" t="n">
-        <v>2941.05</v>
+        <v>2983.1</v>
       </c>
       <c r="L5" t="n">
-        <v>2972.67</v>
+        <v>2999</v>
       </c>
       <c r="M5" t="n">
-        <v>3001.95</v>
+        <v>3033.7</v>
       </c>
       <c r="N5" t="n">
-        <v>3031.23</v>
+        <v>3068.4</v>
       </c>
       <c r="O5" t="n">
-        <v>3065.2</v>
+        <v>3065.5</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -937,18 +935,18 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -961,55 +959,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3008.1</v>
+        <v>2984.7</v>
       </c>
       <c r="C6" t="n">
-        <v>3019.5</v>
+        <v>2995.8</v>
       </c>
       <c r="D6" t="n">
-        <v>2970.8</v>
+        <v>2961.8</v>
       </c>
       <c r="E6" t="n">
-        <v>2994</v>
+        <v>2970.4</v>
       </c>
       <c r="F6" t="n">
-        <v>-14.4</v>
+        <v>-23.6</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>48.7</v>
+        <v>34</v>
       </c>
       <c r="I6" t="n">
-        <v>2913.7</v>
+        <v>2922.1</v>
       </c>
       <c r="J6" t="n">
-        <v>2967.2</v>
+        <v>2944.73</v>
       </c>
       <c r="K6" t="n">
-        <v>2983.1</v>
+        <v>2969.65</v>
       </c>
       <c r="L6" t="n">
-        <v>2999</v>
+        <v>2994.58</v>
       </c>
       <c r="M6" t="n">
-        <v>3033.7</v>
+        <v>3018.35</v>
       </c>
       <c r="N6" t="n">
-        <v>3068.4</v>
+        <v>3042.12</v>
       </c>
       <c r="O6" t="n">
-        <v>3065.5</v>
+        <v>3068.2</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1019,12 +1021,12 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1043,57 +1045,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2984.7</v>
+        <v>2967.2</v>
       </c>
       <c r="C7" t="n">
-        <v>2995.8</v>
+        <v>3029.8</v>
       </c>
       <c r="D7" t="n">
-        <v>2961.8</v>
+        <v>2956.2</v>
       </c>
       <c r="E7" t="n">
-        <v>2970.4</v>
+        <v>2979.9</v>
       </c>
       <c r="F7" t="n">
-        <v>-23.6</v>
+        <v>9.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H7" t="n">
-        <v>34</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>2922.1</v>
+        <v>2927.8</v>
       </c>
       <c r="J7" t="n">
-        <v>2944.73</v>
+        <v>2932.2</v>
       </c>
       <c r="K7" t="n">
-        <v>2969.65</v>
+        <v>2953.4</v>
       </c>
       <c r="L7" t="n">
-        <v>2994.58</v>
+        <v>2974.6</v>
       </c>
       <c r="M7" t="n">
-        <v>3018.35</v>
+        <v>2987.4</v>
       </c>
       <c r="N7" t="n">
-        <v>3042.12</v>
+        <v>3000.2</v>
       </c>
       <c r="O7" t="n">
-        <v>3068.2</v>
+        <v>3029.8</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1101,24 +1103,28 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R7" s="6" t="n">
+        <v/>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
@@ -1127,57 +1133,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2967.2</v>
+        <v>2981.2</v>
       </c>
       <c r="C8" t="n">
-        <v>3029.8</v>
+        <v>3006.1</v>
       </c>
       <c r="D8" t="n">
-        <v>2956.2</v>
+        <v>2974.4</v>
       </c>
       <c r="E8" t="n">
-        <v>2979.9</v>
+        <v>2991.8</v>
       </c>
       <c r="F8" t="n">
-        <v>9.5</v>
+        <v>11.9</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.004</v>
       </c>
       <c r="H8" t="n">
-        <v>73.59999999999999</v>
+        <v>31.7</v>
       </c>
       <c r="I8" t="n">
-        <v>2927.8</v>
+        <v>2882.6</v>
       </c>
       <c r="J8" t="n">
-        <v>2932.2</v>
+        <v>2899.75</v>
       </c>
       <c r="K8" t="n">
-        <v>2953.4</v>
+        <v>2943.1</v>
       </c>
       <c r="L8" t="n">
-        <v>2974.6</v>
+        <v>2986.45</v>
       </c>
       <c r="M8" t="n">
-        <v>2987.4</v>
+        <v>3016.7</v>
       </c>
       <c r="N8" t="n">
-        <v>3000.2</v>
+        <v>3046.95</v>
       </c>
       <c r="O8" t="n">
-        <v>3029.8</v>
+        <v>3103.4</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1188,25 +1194,19 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
@@ -1222,50 +1222,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2981.2</v>
+        <v>2995.3</v>
       </c>
       <c r="C9" t="n">
-        <v>3006.1</v>
+        <v>3012.8</v>
       </c>
       <c r="D9" t="n">
-        <v>2974.4</v>
+        <v>2972.7</v>
       </c>
       <c r="E9" t="n">
-        <v>2991.8</v>
+        <v>2990.7</v>
       </c>
       <c r="F9" t="n">
-        <v>11.9</v>
+        <v>-1.1</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0004</v>
       </c>
       <c r="H9" t="n">
-        <v>31.7</v>
+        <v>40.1</v>
       </c>
       <c r="I9" t="n">
-        <v>2882.6</v>
+        <v>2942.7</v>
       </c>
       <c r="J9" t="n">
-        <v>2899.75</v>
+        <v>2960.87</v>
       </c>
       <c r="K9" t="n">
-        <v>2943.1</v>
+        <v>2975.95</v>
       </c>
       <c r="L9" t="n">
-        <v>2986.45</v>
+        <v>2991.03</v>
       </c>
       <c r="M9" t="n">
-        <v>3016.7</v>
+        <v>3007.65</v>
       </c>
       <c r="N9" t="n">
-        <v>3046.95</v>
+        <v>3024.28</v>
       </c>
       <c r="O9" t="n">
-        <v>3103.4</v>
+        <v>3037.8</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1273,16 +1273,20 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1297,78 +1301,78 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2995.3</v>
+        <v>2991.7</v>
       </c>
       <c r="C10" t="n">
-        <v>3012.8</v>
+        <v>2994.8</v>
       </c>
       <c r="D10" t="n">
-        <v>2972.7</v>
+        <v>2949.3</v>
       </c>
       <c r="E10" t="n">
-        <v>2990.7</v>
+        <v>2973.5</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1</v>
+        <v>-17.2</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0058</v>
       </c>
       <c r="H10" t="n">
-        <v>40.1</v>
+        <v>45.5</v>
       </c>
       <c r="I10" t="n">
-        <v>2942.7</v>
+        <v>2932.6</v>
       </c>
       <c r="J10" t="n">
-        <v>2960.87</v>
+        <v>2949.57</v>
       </c>
       <c r="K10" t="n">
-        <v>2975.95</v>
+        <v>2970.65</v>
       </c>
       <c r="L10" t="n">
-        <v>2991.03</v>
+        <v>2991.72</v>
       </c>
       <c r="M10" t="n">
-        <v>3007.65</v>
+        <v>3010.75</v>
       </c>
       <c r="N10" t="n">
-        <v>3024.28</v>
+        <v>3029.78</v>
       </c>
       <c r="O10" t="n">
-        <v>3037.8</v>
+        <v>3052.9</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1383,79 +1387,79 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2991.7</v>
+        <v>2964.5</v>
       </c>
       <c r="C11" t="n">
-        <v>2994.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D11" t="n">
-        <v>2949.3</v>
+        <v>2952.7</v>
       </c>
       <c r="E11" t="n">
-        <v>2973.5</v>
+        <v>2955.2</v>
       </c>
       <c r="F11" t="n">
-        <v>-17.2</v>
+        <v>-18.3</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0062</v>
       </c>
       <c r="H11" t="n">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="I11" t="n">
-        <v>2932.6</v>
+        <v>2903.8</v>
       </c>
       <c r="J11" t="n">
-        <v>2949.57</v>
+        <v>2928.72</v>
       </c>
       <c r="K11" t="n">
-        <v>2970.65</v>
+        <v>2950.75</v>
       </c>
       <c r="L11" t="n">
-        <v>2991.72</v>
+        <v>2972.78</v>
       </c>
       <c r="M11" t="n">
-        <v>3010.75</v>
+        <v>2996.25</v>
       </c>
       <c r="N11" t="n">
-        <v>3029.78</v>
+        <v>3019.72</v>
       </c>
       <c r="O11" t="n">
-        <v>3052.9</v>
+        <v>3040.3</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
@@ -1469,57 +1473,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2964.5</v>
+        <v>2955.8</v>
       </c>
       <c r="C12" t="n">
-        <v>2998.7</v>
+        <v>2999.8</v>
       </c>
       <c r="D12" t="n">
-        <v>2952.7</v>
+        <v>2951.1</v>
       </c>
       <c r="E12" t="n">
-        <v>2955.2</v>
+        <v>2997</v>
       </c>
       <c r="F12" t="n">
-        <v>-18.3</v>
+        <v>41.8</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0141</v>
       </c>
       <c r="H12" t="n">
-        <v>46</v>
+        <v>48.7</v>
       </c>
       <c r="I12" t="n">
-        <v>2903.8</v>
+        <v>2906.7</v>
       </c>
       <c r="J12" t="n">
-        <v>2928.72</v>
+        <v>2898.95</v>
       </c>
       <c r="K12" t="n">
-        <v>2950.75</v>
+        <v>2932.2</v>
       </c>
       <c r="L12" t="n">
-        <v>2972.78</v>
+        <v>2965.45</v>
       </c>
       <c r="M12" t="n">
-        <v>2996.25</v>
+        <v>2978.2</v>
       </c>
       <c r="N12" t="n">
-        <v>3019.72</v>
+        <v>2990.95</v>
       </c>
       <c r="O12" t="n">
-        <v>3040.3</v>
+        <v>3044.7</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1527,23 +1531,23 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1562,50 +1566,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2955.8</v>
+        <v>2997</v>
       </c>
       <c r="C13" t="n">
-        <v>2999.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D13" t="n">
-        <v>2951.1</v>
+        <v>2965.5</v>
       </c>
       <c r="E13" t="n">
-        <v>2997</v>
+        <v>2969.8</v>
       </c>
       <c r="F13" t="n">
-        <v>41.8</v>
+        <v>-27.2</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0141</v>
+        <v>-0.0091</v>
       </c>
       <c r="H13" t="n">
-        <v>48.7</v>
+        <v>33.2</v>
       </c>
       <c r="I13" t="n">
-        <v>2906.7</v>
+        <v>2902.4</v>
       </c>
       <c r="J13" t="n">
-        <v>2898.95</v>
+        <v>2959.08</v>
       </c>
       <c r="K13" t="n">
-        <v>2932.2</v>
+        <v>2972.65</v>
       </c>
       <c r="L13" t="n">
-        <v>2965.45</v>
+        <v>2986.23</v>
       </c>
       <c r="M13" t="n">
-        <v>2978.2</v>
+        <v>3021.35</v>
       </c>
       <c r="N13" t="n">
-        <v>2990.95</v>
+        <v>3056.47</v>
       </c>
       <c r="O13" t="n">
-        <v>3044.7</v>
+        <v>3048.5</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1613,23 +1617,21 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1641,60 +1643,62 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2997</v>
+        <v>2974.6</v>
       </c>
       <c r="C14" t="n">
-        <v>2998.7</v>
+        <v>2979</v>
       </c>
       <c r="D14" t="n">
-        <v>2965.5</v>
+        <v>2932.1</v>
       </c>
       <c r="E14" t="n">
-        <v>2969.8</v>
+        <v>2951.7</v>
       </c>
       <c r="F14" t="n">
-        <v>-27.2</v>
+        <v>-18.1</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0091</v>
+        <v>-0.0061</v>
       </c>
       <c r="H14" t="n">
-        <v>33.2</v>
+        <v>46.9</v>
       </c>
       <c r="I14" t="n">
-        <v>2902.4</v>
+        <v>2932.3</v>
       </c>
       <c r="J14" t="n">
-        <v>2959.08</v>
+        <v>2930.45</v>
       </c>
       <c r="K14" t="n">
-        <v>2972.65</v>
+        <v>2953.2</v>
       </c>
       <c r="L14" t="n">
-        <v>2986.23</v>
+        <v>2975.95</v>
       </c>
       <c r="M14" t="n">
-        <v>3021.35</v>
+        <v>2986.4</v>
       </c>
       <c r="N14" t="n">
-        <v>3056.47</v>
+        <v>2996.85</v>
       </c>
       <c r="O14" t="n">
-        <v>3048.5</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
+        <v>3031.9</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q14" s="6" t="n">
         <v/>
@@ -1704,7 +1708,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1725,74 +1729,70 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2974.6</v>
+        <v>2948.5</v>
       </c>
       <c r="C15" t="n">
-        <v>2979</v>
+        <v>2969.7</v>
       </c>
       <c r="D15" t="n">
-        <v>2932.1</v>
+        <v>2934.5</v>
       </c>
       <c r="E15" t="n">
-        <v>2951.7</v>
+        <v>2941.3</v>
       </c>
       <c r="F15" t="n">
-        <v>-18.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0035</v>
       </c>
       <c r="H15" t="n">
-        <v>46.9</v>
+        <v>35.2</v>
       </c>
       <c r="I15" t="n">
-        <v>2932.3</v>
+        <v>2885.2</v>
       </c>
       <c r="J15" t="n">
-        <v>2930.45</v>
+        <v>2902.88</v>
       </c>
       <c r="K15" t="n">
-        <v>2953.2</v>
+        <v>2928.25</v>
       </c>
       <c r="L15" t="n">
-        <v>2975.95</v>
+        <v>2953.62</v>
       </c>
       <c r="M15" t="n">
-        <v>2986.4</v>
+        <v>2975.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2996.85</v>
+        <v>2996.67</v>
       </c>
       <c r="O15" t="n">
-        <v>3031.9</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3025.9</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
       </c>
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1811,57 +1811,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2948.5</v>
+        <v>2955.5</v>
       </c>
       <c r="C16" t="n">
-        <v>2969.7</v>
+        <v>2985.9</v>
       </c>
       <c r="D16" t="n">
-        <v>2934.5</v>
+        <v>2941.2</v>
       </c>
       <c r="E16" t="n">
-        <v>2941.3</v>
+        <v>2960</v>
       </c>
       <c r="F16" t="n">
-        <v>-10.4</v>
+        <v>18.7</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0064</v>
       </c>
       <c r="H16" t="n">
-        <v>35.2</v>
+        <v>44.7</v>
       </c>
       <c r="I16" t="n">
-        <v>2885.2</v>
+        <v>2899.3</v>
       </c>
       <c r="J16" t="n">
-        <v>2902.88</v>
+        <v>2900.7</v>
       </c>
       <c r="K16" t="n">
-        <v>2928.25</v>
+        <v>2923.7</v>
       </c>
       <c r="L16" t="n">
-        <v>2953.62</v>
+        <v>2946.7</v>
       </c>
       <c r="M16" t="n">
-        <v>2975.15</v>
+        <v>2958.9</v>
       </c>
       <c r="N16" t="n">
-        <v>2996.67</v>
+        <v>2971.1</v>
       </c>
       <c r="O16" t="n">
-        <v>3025.9</v>
+        <v>3004.9</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1874,14 +1874,18 @@
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1891,59 +1895,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2955.5</v>
+        <v>2961.5</v>
       </c>
       <c r="C17" t="n">
-        <v>2985.9</v>
+        <v>2968.3</v>
       </c>
       <c r="D17" t="n">
-        <v>2941.2</v>
+        <v>2933.4</v>
       </c>
       <c r="E17" t="n">
-        <v>2960</v>
+        <v>2964.5</v>
       </c>
       <c r="F17" t="n">
-        <v>18.7</v>
+        <v>4.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0015</v>
       </c>
       <c r="H17" t="n">
-        <v>44.7</v>
+        <v>34.9</v>
       </c>
       <c r="I17" t="n">
-        <v>2899.3</v>
+        <v>2896.5</v>
       </c>
       <c r="J17" t="n">
-        <v>2900.7</v>
+        <v>2913.53</v>
       </c>
       <c r="K17" t="n">
-        <v>2923.7</v>
+        <v>2937.65</v>
       </c>
       <c r="L17" t="n">
-        <v>2946.7</v>
+        <v>2961.77</v>
       </c>
       <c r="M17" t="n">
-        <v>2958.9</v>
+        <v>2982.35</v>
       </c>
       <c r="N17" t="n">
-        <v>2971.1</v>
+        <v>3002.92</v>
       </c>
       <c r="O17" t="n">
-        <v>3004.9</v>
+        <v>3030.6</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1951,24 +1951,22 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
@@ -1977,61 +1975,69 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2961.5</v>
+        <v>2966.9</v>
       </c>
       <c r="C18" t="n">
-        <v>2968.3</v>
+        <v>2978.3</v>
       </c>
       <c r="D18" t="n">
-        <v>2933.4</v>
+        <v>2902.3</v>
       </c>
       <c r="E18" t="n">
-        <v>2964.5</v>
+        <v>2915.4</v>
       </c>
       <c r="F18" t="n">
-        <v>4.5</v>
+        <v>-49.1</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0166</v>
       </c>
       <c r="H18" t="n">
-        <v>34.9</v>
+        <v>76</v>
       </c>
       <c r="I18" t="n">
-        <v>2896.5</v>
+        <v>2898.5</v>
       </c>
       <c r="J18" t="n">
-        <v>2913.53</v>
+        <v>2936.42</v>
       </c>
       <c r="K18" t="n">
-        <v>2937.65</v>
+        <v>2947.05</v>
       </c>
       <c r="L18" t="n">
-        <v>2961.77</v>
+        <v>2957.67</v>
       </c>
       <c r="M18" t="n">
-        <v>2982.35</v>
+        <v>2981.95</v>
       </c>
       <c r="N18" t="n">
-        <v>3002.92</v>
+        <v>3006.23</v>
       </c>
       <c r="O18" t="n">
-        <v>3030.6</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
+        <v>3003.2</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
@@ -2040,7 +2046,7 @@
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2052,88 +2058,84 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W18" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2966.9</v>
+        <v>2906.6</v>
       </c>
       <c r="C19" t="n">
-        <v>2978.3</v>
+        <v>2957.9</v>
       </c>
       <c r="D19" t="n">
-        <v>2902.3</v>
+        <v>2905.6</v>
       </c>
       <c r="E19" t="n">
-        <v>2915.4</v>
+        <v>2954.3</v>
       </c>
       <c r="F19" t="n">
-        <v>-49.1</v>
+        <v>38.9</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0166</v>
+        <v>0.0133</v>
       </c>
       <c r="H19" t="n">
-        <v>76</v>
+        <v>52.3</v>
       </c>
       <c r="I19" t="n">
-        <v>2898.5</v>
+        <v>2826.3</v>
       </c>
       <c r="J19" t="n">
-        <v>2936.42</v>
+        <v>2826.95</v>
       </c>
       <c r="K19" t="n">
-        <v>2947.05</v>
+        <v>2877.4</v>
       </c>
       <c r="L19" t="n">
-        <v>2957.67</v>
+        <v>2927.85</v>
       </c>
       <c r="M19" t="n">
-        <v>2981.95</v>
+        <v>2953.4</v>
       </c>
       <c r="N19" t="n">
-        <v>3006.23</v>
+        <v>2978.95</v>
       </c>
       <c r="O19" t="n">
-        <v>3003.2</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
+        <v>3054.3</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
@@ -2147,76 +2149,78 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2906.6</v>
+        <v>2954</v>
       </c>
       <c r="C20" t="n">
-        <v>2957.9</v>
+        <v>2976.3</v>
       </c>
       <c r="D20" t="n">
-        <v>2905.6</v>
+        <v>2905.3</v>
       </c>
       <c r="E20" t="n">
-        <v>2954.3</v>
+        <v>2938</v>
       </c>
       <c r="F20" t="n">
-        <v>38.9</v>
+        <v>-16.3</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0055</v>
       </c>
       <c r="H20" t="n">
-        <v>52.3</v>
+        <v>71</v>
       </c>
       <c r="I20" t="n">
-        <v>2826.3</v>
+        <v>2853.3</v>
       </c>
       <c r="J20" t="n">
-        <v>2826.95</v>
+        <v>2913.28</v>
       </c>
       <c r="K20" t="n">
-        <v>2877.4</v>
+        <v>2928.15</v>
       </c>
       <c r="L20" t="n">
-        <v>2927.85</v>
+        <v>2943.03</v>
       </c>
       <c r="M20" t="n">
-        <v>2953.4</v>
+        <v>2980.45</v>
       </c>
       <c r="N20" t="n">
-        <v>2978.95</v>
+        <v>3017.87</v>
       </c>
       <c r="O20" t="n">
-        <v>3054.3</v>
+        <v>3010.2</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2231,78 +2235,76 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2954</v>
+        <v>2950</v>
       </c>
       <c r="C21" t="n">
-        <v>2976.3</v>
+        <v>2994.6</v>
       </c>
       <c r="D21" t="n">
-        <v>2905.3</v>
+        <v>2948.4</v>
       </c>
       <c r="E21" t="n">
-        <v>2938</v>
+        <v>2989.3</v>
       </c>
       <c r="F21" t="n">
-        <v>-16.3</v>
+        <v>51.3</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0175</v>
       </c>
       <c r="H21" t="n">
-        <v>71</v>
+        <v>46.2</v>
       </c>
       <c r="I21" t="n">
-        <v>2853.3</v>
+        <v>2834.3</v>
       </c>
       <c r="J21" t="n">
-        <v>2913.28</v>
+        <v>2865.6</v>
       </c>
       <c r="K21" t="n">
-        <v>2928.15</v>
+        <v>2902.5</v>
       </c>
       <c r="L21" t="n">
-        <v>2943.03</v>
+        <v>2939.4</v>
       </c>
       <c r="M21" t="n">
-        <v>2980.45</v>
+        <v>2973.5</v>
       </c>
       <c r="N21" t="n">
-        <v>3017.87</v>
+        <v>3007.6</v>
       </c>
       <c r="O21" t="n">
-        <v>3010.2</v>
+        <v>3047.3</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2317,57 +2319,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2950</v>
+        <v>2992.4</v>
       </c>
       <c r="C22" t="n">
-        <v>2994.6</v>
+        <v>3051.8</v>
       </c>
       <c r="D22" t="n">
-        <v>2948.4</v>
+        <v>2986.1</v>
       </c>
       <c r="E22" t="n">
-        <v>2989.3</v>
+        <v>3044.7</v>
       </c>
       <c r="F22" t="n">
-        <v>51.3</v>
+        <v>55.4</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0185</v>
       </c>
       <c r="H22" t="n">
-        <v>46.2</v>
+        <v>65.7</v>
       </c>
       <c r="I22" t="n">
-        <v>2834.3</v>
+        <v>2902.2</v>
       </c>
       <c r="J22" t="n">
-        <v>2865.6</v>
+        <v>2952</v>
       </c>
       <c r="K22" t="n">
-        <v>2902.5</v>
+        <v>2966.2</v>
       </c>
       <c r="L22" t="n">
-        <v>2939.4</v>
+        <v>2980.4</v>
       </c>
       <c r="M22" t="n">
-        <v>2973.5</v>
+        <v>3012.4</v>
       </c>
       <c r="N22" t="n">
-        <v>3007.6</v>
+        <v>3044.4</v>
       </c>
       <c r="O22" t="n">
-        <v>3047.3</v>
+        <v>3040.8</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2378,80 +2380,80 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W22" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2992.4</v>
+        <v>3049.1</v>
       </c>
       <c r="C23" t="n">
-        <v>3051.8</v>
+        <v>3058.3</v>
       </c>
       <c r="D23" t="n">
-        <v>2986.1</v>
+        <v>3023.3</v>
       </c>
       <c r="E23" t="n">
-        <v>3044.7</v>
+        <v>3025.4</v>
       </c>
       <c r="F23" t="n">
-        <v>55.4</v>
+        <v>-19.3</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0063</v>
       </c>
       <c r="H23" t="n">
-        <v>65.7</v>
+        <v>35</v>
       </c>
       <c r="I23" t="n">
-        <v>2902.2</v>
+        <v>2920.4</v>
       </c>
       <c r="J23" t="n">
-        <v>2952</v>
+        <v>2991.87</v>
       </c>
       <c r="K23" t="n">
-        <v>2966.2</v>
+        <v>3011.85</v>
       </c>
       <c r="L23" t="n">
-        <v>2980.4</v>
+        <v>3031.83</v>
       </c>
       <c r="M23" t="n">
-        <v>3012.4</v>
+        <v>3077.55</v>
       </c>
       <c r="N23" t="n">
-        <v>3044.4</v>
+        <v>3123.27</v>
       </c>
       <c r="O23" t="n">
-        <v>3040.8</v>
+        <v>3117.5</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2464,78 +2466,76 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3049.1</v>
+        <v>3028.5</v>
       </c>
       <c r="C24" t="n">
-        <v>3058.3</v>
+        <v>3041</v>
       </c>
       <c r="D24" t="n">
-        <v>3023.3</v>
+        <v>3004.9</v>
       </c>
       <c r="E24" t="n">
-        <v>3025.4</v>
+        <v>3009.1</v>
       </c>
       <c r="F24" t="n">
-        <v>-19.3</v>
+        <v>-16.3</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0054</v>
       </c>
       <c r="H24" t="n">
-        <v>35</v>
+        <v>36.1</v>
       </c>
       <c r="I24" t="n">
-        <v>2920.4</v>
+        <v>2988.3</v>
       </c>
       <c r="J24" t="n">
-        <v>2991.87</v>
+        <v>2982.7</v>
       </c>
       <c r="K24" t="n">
-        <v>3011.85</v>
+        <v>3007.9</v>
       </c>
       <c r="L24" t="n">
-        <v>3031.83</v>
+        <v>3033.1</v>
       </c>
       <c r="M24" t="n">
-        <v>3077.55</v>
+        <v>3042.9</v>
       </c>
       <c r="N24" t="n">
-        <v>3123.27</v>
+        <v>3052.7</v>
       </c>
       <c r="O24" t="n">
-        <v>3117.5</v>
+        <v>3093.3</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2543,12 +2543,14 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2567,57 +2569,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3028.5</v>
+        <v>3008.5</v>
       </c>
       <c r="C25" t="n">
-        <v>3041</v>
+        <v>3046.8</v>
       </c>
       <c r="D25" t="n">
-        <v>3004.9</v>
+        <v>3002</v>
       </c>
       <c r="E25" t="n">
-        <v>3009.1</v>
+        <v>3041.6</v>
       </c>
       <c r="F25" t="n">
-        <v>-16.3</v>
+        <v>32.5</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0054</v>
+        <v>0.0108</v>
       </c>
       <c r="H25" t="n">
-        <v>36.1</v>
+        <v>44.8</v>
       </c>
       <c r="I25" t="n">
-        <v>2988.3</v>
+        <v>2968.8</v>
       </c>
       <c r="J25" t="n">
-        <v>2982.7</v>
+        <v>2966.08</v>
       </c>
       <c r="K25" t="n">
-        <v>3007.9</v>
+        <v>2991.05</v>
       </c>
       <c r="L25" t="n">
-        <v>3033.1</v>
+        <v>3016.03</v>
       </c>
       <c r="M25" t="n">
-        <v>3042.9</v>
+        <v>3027.15</v>
       </c>
       <c r="N25" t="n">
-        <v>3052.7</v>
+        <v>3038.28</v>
       </c>
       <c r="O25" t="n">
-        <v>3093.3</v>
+        <v>3077.1</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2625,22 +2627,24 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
@@ -2651,57 +2655,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3008.5</v>
+        <v>3038.9</v>
       </c>
       <c r="C26" t="n">
-        <v>3046.8</v>
+        <v>3044.6</v>
       </c>
       <c r="D26" t="n">
-        <v>3002</v>
+        <v>3016</v>
       </c>
       <c r="E26" t="n">
-        <v>3041.6</v>
+        <v>3025</v>
       </c>
       <c r="F26" t="n">
-        <v>32.5</v>
+        <v>-16.6</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0108</v>
+        <v>-0.0055</v>
       </c>
       <c r="H26" t="n">
-        <v>44.8</v>
+        <v>28.6</v>
       </c>
       <c r="I26" t="n">
-        <v>2968.8</v>
+        <v>2957.2</v>
       </c>
       <c r="J26" t="n">
-        <v>2966.08</v>
+        <v>3005.4</v>
       </c>
       <c r="K26" t="n">
-        <v>2991.05</v>
+        <v>3019.2</v>
       </c>
       <c r="L26" t="n">
-        <v>3016.03</v>
+        <v>3033</v>
       </c>
       <c r="M26" t="n">
-        <v>3027.15</v>
+        <v>3064</v>
       </c>
       <c r="N26" t="n">
-        <v>3038.28</v>
+        <v>3095</v>
       </c>
       <c r="O26" t="n">
-        <v>3077.1</v>
+        <v>3091.6</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2709,23 +2713,21 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2737,57 +2739,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3038.9</v>
+        <v>3024.7</v>
       </c>
       <c r="C27" t="n">
-        <v>3044.6</v>
+        <v>3045.8</v>
       </c>
       <c r="D27" t="n">
-        <v>3016</v>
+        <v>3019.9</v>
       </c>
       <c r="E27" t="n">
-        <v>3025</v>
+        <v>3035.5</v>
       </c>
       <c r="F27" t="n">
-        <v>-16.6</v>
+        <v>10.5</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0035</v>
       </c>
       <c r="H27" t="n">
-        <v>28.6</v>
+        <v>25.9</v>
       </c>
       <c r="I27" t="n">
-        <v>2957.2</v>
+        <v>2987.4</v>
       </c>
       <c r="J27" t="n">
-        <v>3005.4</v>
+        <v>2993.75</v>
       </c>
       <c r="K27" t="n">
-        <v>3019.2</v>
+        <v>3010.7</v>
       </c>
       <c r="L27" t="n">
-        <v>3033</v>
+        <v>3027.65</v>
       </c>
       <c r="M27" t="n">
-        <v>3064</v>
+        <v>3039.3</v>
       </c>
       <c r="N27" t="n">
-        <v>3095</v>
+        <v>3050.95</v>
       </c>
       <c r="O27" t="n">
-        <v>3091.6</v>
+        <v>3073.2</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2795,19 +2797,19 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
       <c r="U27" s="8" t="n">
         <v/>
       </c>
@@ -2819,59 +2821,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3024.7</v>
+        <v>3036.1</v>
       </c>
       <c r="C28" t="n">
-        <v>3045.8</v>
+        <v>3060</v>
       </c>
       <c r="D28" t="n">
-        <v>3019.9</v>
+        <v>3033.1</v>
       </c>
       <c r="E28" t="n">
-        <v>3035.5</v>
+        <v>3052.8</v>
       </c>
       <c r="F28" t="n">
-        <v>10.5</v>
+        <v>17.3</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0057</v>
       </c>
       <c r="H28" t="n">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
       <c r="I28" t="n">
-        <v>2987.4</v>
+        <v>2994</v>
       </c>
       <c r="J28" t="n">
-        <v>2993.75</v>
+        <v>3010.92</v>
       </c>
       <c r="K28" t="n">
-        <v>3010.7</v>
+        <v>3022.55</v>
       </c>
       <c r="L28" t="n">
-        <v>3027.65</v>
+        <v>3034.17</v>
       </c>
       <c r="M28" t="n">
-        <v>3039.3</v>
+        <v>3048.45</v>
       </c>
       <c r="N28" t="n">
-        <v>3050.95</v>
+        <v>3062.73</v>
       </c>
       <c r="O28" t="n">
-        <v>3073.2</v>
+        <v>3071.7</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2882,7 +2880,7 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2908,50 +2906,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3036.1</v>
+        <v>3056.2</v>
       </c>
       <c r="C29" t="n">
-        <v>3060</v>
+        <v>3076.3</v>
       </c>
       <c r="D29" t="n">
-        <v>3033.1</v>
+        <v>3052.5</v>
       </c>
       <c r="E29" t="n">
-        <v>3052.8</v>
+        <v>3060.2</v>
       </c>
       <c r="F29" t="n">
-        <v>17.3</v>
+        <v>7.4</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0024</v>
       </c>
       <c r="H29" t="n">
-        <v>26.9</v>
+        <v>23.8</v>
       </c>
       <c r="I29" t="n">
-        <v>2994</v>
+        <v>3006.2</v>
       </c>
       <c r="J29" t="n">
-        <v>3010.92</v>
+        <v>3029.03</v>
       </c>
       <c r="K29" t="n">
-        <v>3022.55</v>
+        <v>3039.35</v>
       </c>
       <c r="L29" t="n">
-        <v>3034.17</v>
+        <v>3049.68</v>
       </c>
       <c r="M29" t="n">
-        <v>3048.45</v>
+        <v>3066.25</v>
       </c>
       <c r="N29" t="n">
-        <v>3062.73</v>
+        <v>3082.82</v>
       </c>
       <c r="O29" t="n">
-        <v>3071.7</v>
+        <v>3086.9</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2962,7 +2960,7 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2988,50 +2986,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3056.2</v>
+        <v>3062.2</v>
       </c>
       <c r="C30" t="n">
         <v>3076.3</v>
       </c>
       <c r="D30" t="n">
-        <v>3052.5</v>
+        <v>3051.7</v>
       </c>
       <c r="E30" t="n">
-        <v>3060.2</v>
+        <v>3074.9</v>
       </c>
       <c r="F30" t="n">
-        <v>7.4</v>
+        <v>14.7</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0048</v>
       </c>
       <c r="H30" t="n">
-        <v>23.8</v>
+        <v>24.6</v>
       </c>
       <c r="I30" t="n">
-        <v>3006.2</v>
+        <v>3028.7</v>
       </c>
       <c r="J30" t="n">
-        <v>3029.03</v>
+        <v>3034.3</v>
       </c>
       <c r="K30" t="n">
-        <v>3039.35</v>
+        <v>3048.3</v>
       </c>
       <c r="L30" t="n">
-        <v>3049.68</v>
+        <v>3062.3</v>
       </c>
       <c r="M30" t="n">
-        <v>3066.25</v>
+        <v>3072.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3082.82</v>
+        <v>3081.9</v>
       </c>
       <c r="O30" t="n">
-        <v>3086.9</v>
+        <v>3100.1</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3042,7 +3040,7 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3063,55 +3061,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3062.2</v>
+        <v>3073.5</v>
       </c>
       <c r="C31" t="n">
-        <v>3076.3</v>
+        <v>3079.9</v>
       </c>
       <c r="D31" t="n">
-        <v>3051.7</v>
+        <v>3055.9</v>
       </c>
       <c r="E31" t="n">
-        <v>3074.9</v>
+        <v>3064.9</v>
       </c>
       <c r="F31" t="n">
-        <v>14.7</v>
+        <v>-10</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.0033</v>
       </c>
       <c r="H31" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="I31" t="n">
-        <v>3028.7</v>
+        <v>3027.1</v>
       </c>
       <c r="J31" t="n">
-        <v>3034.3</v>
+        <v>3055.75</v>
       </c>
       <c r="K31" t="n">
-        <v>3048.3</v>
+        <v>3062.6</v>
       </c>
       <c r="L31" t="n">
-        <v>3062.3</v>
+        <v>3069.45</v>
       </c>
       <c r="M31" t="n">
-        <v>3072.1</v>
+        <v>3087.2</v>
       </c>
       <c r="N31" t="n">
-        <v>3081.9</v>
+        <v>3104.95</v>
       </c>
       <c r="O31" t="n">
-        <v>3100.1</v>
+        <v>3100.9</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3119,18 +3121,18 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3152,63 +3154,67 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3073.5</v>
+        <v>3063.7</v>
       </c>
       <c r="C32" t="n">
-        <v>3079.9</v>
+        <v>3066.6</v>
       </c>
       <c r="D32" t="n">
-        <v>3055.9</v>
+        <v>3024.1</v>
       </c>
       <c r="E32" t="n">
-        <v>3064.9</v>
+        <v>3026.4</v>
       </c>
       <c r="F32" t="n">
-        <v>-10</v>
+        <v>-38.5</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0126</v>
       </c>
       <c r="H32" t="n">
-        <v>24</v>
+        <v>42.5</v>
       </c>
       <c r="I32" t="n">
-        <v>3027.1</v>
+        <v>3031.9</v>
       </c>
       <c r="J32" t="n">
-        <v>3055.75</v>
+        <v>3039.4</v>
       </c>
       <c r="K32" t="n">
-        <v>3062.6</v>
+        <v>3052.9</v>
       </c>
       <c r="L32" t="n">
-        <v>3069.45</v>
+        <v>3066.4</v>
       </c>
       <c r="M32" t="n">
-        <v>3087.2</v>
+        <v>3076.9</v>
       </c>
       <c r="N32" t="n">
-        <v>3104.95</v>
+        <v>3087.4</v>
       </c>
       <c r="O32" t="n">
-        <v>3100.9</v>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
+        <v>3103.9</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3222,88 +3228,80 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W32" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3063.7</v>
+        <v>3025.9</v>
       </c>
       <c r="C33" t="n">
-        <v>3066.6</v>
+        <v>3059.1</v>
       </c>
       <c r="D33" t="n">
-        <v>3024.1</v>
+        <v>3019.8</v>
       </c>
       <c r="E33" t="n">
-        <v>3026.4</v>
+        <v>3039.9</v>
       </c>
       <c r="F33" t="n">
-        <v>-38.5</v>
+        <v>13.5</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0045</v>
       </c>
       <c r="H33" t="n">
-        <v>42.5</v>
+        <v>39.3</v>
       </c>
       <c r="I33" t="n">
-        <v>3031.9</v>
+        <v>2981.6</v>
       </c>
       <c r="J33" t="n">
-        <v>3039.4</v>
+        <v>2974.42</v>
       </c>
       <c r="K33" t="n">
-        <v>3052.9</v>
+        <v>3005.15</v>
       </c>
       <c r="L33" t="n">
-        <v>3066.4</v>
+        <v>3035.88</v>
       </c>
       <c r="M33" t="n">
-        <v>3076.9</v>
+        <v>3047.65</v>
       </c>
       <c r="N33" t="n">
-        <v>3087.4</v>
+        <v>3059.42</v>
       </c>
       <c r="O33" t="n">
-        <v>3103.9</v>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q33" s="6" t="inlineStr">
+        <v>3109.1</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3315,74 +3313,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3025.9</v>
+        <v>3041.4</v>
       </c>
       <c r="C34" t="n">
-        <v>3059.1</v>
+        <v>3048.5</v>
       </c>
       <c r="D34" t="n">
-        <v>3019.8</v>
+        <v>2993.2</v>
       </c>
       <c r="E34" t="n">
-        <v>3039.9</v>
+        <v>2999.2</v>
       </c>
       <c r="F34" t="n">
-        <v>13.5</v>
+        <v>-40.7</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0134</v>
       </c>
       <c r="H34" t="n">
-        <v>39.3</v>
+        <v>55.3</v>
       </c>
       <c r="I34" t="n">
-        <v>2981.6</v>
+        <v>2980.5</v>
       </c>
       <c r="J34" t="n">
-        <v>2974.42</v>
+        <v>3000.82</v>
       </c>
       <c r="K34" t="n">
-        <v>3005.15</v>
+        <v>3020.25</v>
       </c>
       <c r="L34" t="n">
-        <v>3035.88</v>
+        <v>3039.67</v>
       </c>
       <c r="M34" t="n">
-        <v>3047.65</v>
+        <v>3059.55</v>
       </c>
       <c r="N34" t="n">
-        <v>3059.42</v>
+        <v>3079.42</v>
       </c>
       <c r="O34" t="n">
-        <v>3109.1</v>
+        <v>3098.4</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3395,81 +3399,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3041.4</v>
+        <v>2999.6</v>
       </c>
       <c r="C35" t="n">
-        <v>3048.5</v>
+        <v>3026.7</v>
       </c>
       <c r="D35" t="n">
-        <v>2993.2</v>
+        <v>2997.9</v>
       </c>
       <c r="E35" t="n">
-        <v>2999.2</v>
+        <v>3022.1</v>
       </c>
       <c r="F35" t="n">
-        <v>-40.7</v>
+        <v>22.9</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0134</v>
+        <v>0.0076</v>
       </c>
       <c r="H35" t="n">
-        <v>55.3</v>
+        <v>28.8</v>
       </c>
       <c r="I35" t="n">
-        <v>2980.5</v>
+        <v>2937.9</v>
       </c>
       <c r="J35" t="n">
-        <v>3000.82</v>
+        <v>2933.07</v>
       </c>
       <c r="K35" t="n">
-        <v>3020.25</v>
+        <v>2971.55</v>
       </c>
       <c r="L35" t="n">
-        <v>3039.67</v>
+        <v>3010.02</v>
       </c>
       <c r="M35" t="n">
-        <v>3059.55</v>
+        <v>3026.85</v>
       </c>
       <c r="N35" t="n">
-        <v>3079.42</v>
+        <v>3043.67</v>
       </c>
       <c r="O35" t="n">
-        <v>3098.4</v>
+        <v>3103.8</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
@@ -3481,74 +3479,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2999.6</v>
+        <v>3023</v>
       </c>
       <c r="C36" t="n">
-        <v>3026.7</v>
+        <v>3028.9</v>
       </c>
       <c r="D36" t="n">
-        <v>2997.9</v>
+        <v>2996</v>
       </c>
       <c r="E36" t="n">
-        <v>3022.1</v>
+        <v>3001.6</v>
       </c>
       <c r="F36" t="n">
-        <v>22.9</v>
+        <v>-20.5</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0076</v>
+        <v>-0.0068</v>
       </c>
       <c r="H36" t="n">
-        <v>28.8</v>
+        <v>32.9</v>
       </c>
       <c r="I36" t="n">
-        <v>2937.9</v>
+        <v>2969.1</v>
       </c>
       <c r="J36" t="n">
-        <v>2933.07</v>
+        <v>2998.2</v>
       </c>
       <c r="K36" t="n">
-        <v>2971.55</v>
+        <v>3007.7</v>
       </c>
       <c r="L36" t="n">
-        <v>3010.02</v>
+        <v>3017.2</v>
       </c>
       <c r="M36" t="n">
-        <v>3026.85</v>
+        <v>3036.5</v>
       </c>
       <c r="N36" t="n">
-        <v>3043.67</v>
+        <v>3055.8</v>
       </c>
       <c r="O36" t="n">
-        <v>3103.8</v>
+        <v>3055.5</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3563,79 +3567,77 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3023</v>
+        <v>3004.6</v>
       </c>
       <c r="C37" t="n">
-        <v>3028.9</v>
+        <v>3025.4</v>
       </c>
       <c r="D37" t="n">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="E37" t="n">
-        <v>3001.6</v>
+        <v>3014.4</v>
       </c>
       <c r="F37" t="n">
-        <v>-20.5</v>
+        <v>12.8</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0043</v>
       </c>
       <c r="H37" t="n">
-        <v>32.9</v>
+        <v>28.4</v>
       </c>
       <c r="I37" t="n">
-        <v>2969.1</v>
+        <v>2963.1</v>
       </c>
       <c r="J37" t="n">
-        <v>2998.2</v>
+        <v>2963.28</v>
       </c>
       <c r="K37" t="n">
-        <v>3007.7</v>
+        <v>2985.15</v>
       </c>
       <c r="L37" t="n">
-        <v>3017.2</v>
+        <v>3007.03</v>
       </c>
       <c r="M37" t="n">
-        <v>3036.5</v>
+        <v>3018.05</v>
       </c>
       <c r="N37" t="n">
-        <v>3055.8</v>
+        <v>3029.08</v>
       </c>
       <c r="O37" t="n">
-        <v>3055.5</v>
+        <v>3061.8</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
@@ -3649,57 +3651,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3004.6</v>
+        <v>3014.6</v>
       </c>
       <c r="C38" t="n">
-        <v>3025.4</v>
+        <v>3020.5</v>
       </c>
       <c r="D38" t="n">
-        <v>2997</v>
+        <v>3002.6</v>
       </c>
       <c r="E38" t="n">
-        <v>3014.4</v>
+        <v>3010.1</v>
       </c>
       <c r="F38" t="n">
-        <v>12.8</v>
+        <v>-4.3</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0014</v>
       </c>
       <c r="H38" t="n">
-        <v>28.4</v>
+        <v>17.9</v>
       </c>
       <c r="I38" t="n">
-        <v>2963.1</v>
+        <v>2968.6</v>
       </c>
       <c r="J38" t="n">
-        <v>2963.28</v>
+        <v>2987.6</v>
       </c>
       <c r="K38" t="n">
-        <v>2985.15</v>
+        <v>3000.2</v>
       </c>
       <c r="L38" t="n">
-        <v>3007.03</v>
+        <v>3012.8</v>
       </c>
       <c r="M38" t="n">
-        <v>3018.05</v>
+        <v>3028.6</v>
       </c>
       <c r="N38" t="n">
-        <v>3029.08</v>
+        <v>3044.4</v>
       </c>
       <c r="O38" t="n">
-        <v>3061.8</v>
+        <v>3053.8</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3712,13 +3714,11 @@
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3733,57 +3733,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3014.6</v>
+        <v>3016.9</v>
       </c>
       <c r="C39" t="n">
-        <v>3020.5</v>
+        <v>3024.2</v>
       </c>
       <c r="D39" t="n">
-        <v>3002.6</v>
+        <v>3002.1</v>
       </c>
       <c r="E39" t="n">
-        <v>3010.1</v>
+        <v>3019</v>
       </c>
       <c r="F39" t="n">
-        <v>-4.3</v>
+        <v>8.9</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0014</v>
+        <v>0.003</v>
       </c>
       <c r="H39" t="n">
-        <v>17.9</v>
+        <v>22.1</v>
       </c>
       <c r="I39" t="n">
-        <v>2968.6</v>
+        <v>2984.7</v>
       </c>
       <c r="J39" t="n">
-        <v>2987.6</v>
+        <v>2991.48</v>
       </c>
       <c r="K39" t="n">
-        <v>3000.2</v>
+        <v>3001.15</v>
       </c>
       <c r="L39" t="n">
-        <v>3012.8</v>
+        <v>3010.83</v>
       </c>
       <c r="M39" t="n">
-        <v>3028.6</v>
+        <v>3019.05</v>
       </c>
       <c r="N39" t="n">
-        <v>3044.4</v>
+        <v>3027.28</v>
       </c>
       <c r="O39" t="n">
-        <v>3053.8</v>
+        <v>3038.4</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3796,11 +3796,13 @@
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3815,76 +3817,80 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3016.9</v>
+        <v>3019.6</v>
       </c>
       <c r="C40" t="n">
-        <v>3024.2</v>
+        <v>3025.5</v>
       </c>
       <c r="D40" t="n">
-        <v>3002.1</v>
+        <v>2976.6</v>
       </c>
       <c r="E40" t="n">
-        <v>3019</v>
+        <v>2977.5</v>
       </c>
       <c r="F40" t="n">
-        <v>8.9</v>
+        <v>-41.5</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0137</v>
       </c>
       <c r="H40" t="n">
-        <v>22.1</v>
+        <v>48.9</v>
       </c>
       <c r="I40" t="n">
-        <v>2984.7</v>
+        <v>2980</v>
       </c>
       <c r="J40" t="n">
-        <v>2991.48</v>
+        <v>2999.83</v>
       </c>
       <c r="K40" t="n">
-        <v>3001.15</v>
+        <v>3007.95</v>
       </c>
       <c r="L40" t="n">
-        <v>3010.83</v>
+        <v>3016.08</v>
       </c>
       <c r="M40" t="n">
-        <v>3019.05</v>
+        <v>3030.05</v>
       </c>
       <c r="N40" t="n">
-        <v>3027.28</v>
+        <v>3044.02</v>
       </c>
       <c r="O40" t="n">
-        <v>3038.4</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+        <v>3046.3</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3899,74 +3905,70 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3019.6</v>
+        <v>2971</v>
       </c>
       <c r="C41" t="n">
-        <v>3025.5</v>
+        <v>2982.5</v>
       </c>
       <c r="D41" t="n">
-        <v>2976.6</v>
+        <v>2946.1</v>
       </c>
       <c r="E41" t="n">
-        <v>2977.5</v>
+        <v>2958.7</v>
       </c>
       <c r="F41" t="n">
-        <v>-41.5</v>
+        <v>-18.8</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0063</v>
       </c>
       <c r="H41" t="n">
-        <v>48.9</v>
+        <v>36.4</v>
       </c>
       <c r="I41" t="n">
-        <v>2980</v>
+        <v>2927.7</v>
       </c>
       <c r="J41" t="n">
-        <v>2999.83</v>
+        <v>2916.83</v>
       </c>
       <c r="K41" t="n">
-        <v>3007.95</v>
+        <v>2953.05</v>
       </c>
       <c r="L41" t="n">
-        <v>3016.08</v>
+        <v>2989.28</v>
       </c>
       <c r="M41" t="n">
-        <v>3030.05</v>
+        <v>3001.95</v>
       </c>
       <c r="N41" t="n">
-        <v>3044.02</v>
+        <v>3014.62</v>
       </c>
       <c r="O41" t="n">
-        <v>3046.3</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
+        <v>3074.4</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3985,72 +3987,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2971</v>
+        <v>2958</v>
       </c>
       <c r="C42" t="n">
-        <v>2982.5</v>
+        <v>2964.6</v>
       </c>
       <c r="D42" t="n">
-        <v>2946.1</v>
+        <v>2918.9</v>
       </c>
       <c r="E42" t="n">
-        <v>2958.7</v>
+        <v>2924.7</v>
       </c>
       <c r="F42" t="n">
-        <v>-18.8</v>
+        <v>-34</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0115</v>
       </c>
       <c r="H42" t="n">
-        <v>36.4</v>
+        <v>45.7</v>
       </c>
       <c r="I42" t="n">
-        <v>2927.7</v>
+        <v>2909.7</v>
       </c>
       <c r="J42" t="n">
-        <v>2916.83</v>
+        <v>2919.5</v>
       </c>
       <c r="K42" t="n">
-        <v>2953.05</v>
+        <v>2940.5</v>
       </c>
       <c r="L42" t="n">
-        <v>2989.28</v>
+        <v>2961.5</v>
       </c>
       <c r="M42" t="n">
-        <v>3001.95</v>
+        <v>2976.9</v>
       </c>
       <c r="N42" t="n">
-        <v>3014.62</v>
+        <v>2992.3</v>
       </c>
       <c r="O42" t="n">
-        <v>3074.4</v>
+        <v>3018.9</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4074,75 +4074,75 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2958</v>
+        <v>2926.4</v>
       </c>
       <c r="C43" t="n">
-        <v>2964.6</v>
+        <v>2962.5</v>
       </c>
       <c r="D43" t="n">
-        <v>2918.9</v>
+        <v>2914.5</v>
       </c>
       <c r="E43" t="n">
-        <v>2924.7</v>
+        <v>2958.8</v>
       </c>
       <c r="F43" t="n">
-        <v>-34</v>
+        <v>34.1</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0.0117</v>
       </c>
       <c r="H43" t="n">
-        <v>45.7</v>
+        <v>48</v>
       </c>
       <c r="I43" t="n">
-        <v>2909.7</v>
+        <v>2873.2</v>
       </c>
       <c r="J43" t="n">
-        <v>2919.5</v>
+        <v>2870.47</v>
       </c>
       <c r="K43" t="n">
-        <v>2940.5</v>
+        <v>2901.85</v>
       </c>
       <c r="L43" t="n">
-        <v>2961.5</v>
+        <v>2933.22</v>
       </c>
       <c r="M43" t="n">
-        <v>2976.9</v>
+        <v>2947.55</v>
       </c>
       <c r="N43" t="n">
-        <v>2992.3</v>
+        <v>2961.88</v>
       </c>
       <c r="O43" t="n">
-        <v>3018.9</v>
+        <v>3010.3</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
@@ -4151,55 +4151,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2926.4</v>
+        <v>2957.6</v>
       </c>
       <c r="C44" t="n">
-        <v>2962.5</v>
+        <v>2983.3</v>
       </c>
       <c r="D44" t="n">
-        <v>2914.5</v>
+        <v>2949.9</v>
       </c>
       <c r="E44" t="n">
-        <v>2958.8</v>
+        <v>2969.7</v>
       </c>
       <c r="F44" t="n">
-        <v>34.1</v>
+        <v>10.9</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0117</v>
+        <v>0.0037</v>
       </c>
       <c r="H44" t="n">
-        <v>48</v>
+        <v>33.4</v>
       </c>
       <c r="I44" t="n">
-        <v>2873.2</v>
+        <v>2866.5</v>
       </c>
       <c r="J44" t="n">
-        <v>2870.47</v>
+        <v>2920.95</v>
       </c>
       <c r="K44" t="n">
-        <v>2901.85</v>
+        <v>2934.8</v>
       </c>
       <c r="L44" t="n">
-        <v>2933.22</v>
+        <v>2948.65</v>
       </c>
       <c r="M44" t="n">
-        <v>2947.55</v>
+        <v>2982.8</v>
       </c>
       <c r="N44" t="n">
-        <v>2961.88</v>
+        <v>3016.95</v>
       </c>
       <c r="O44" t="n">
-        <v>3010.3</v>
+        <v>3010.5</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4210,21 +4214,19 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
@@ -4235,57 +4237,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2957.6</v>
+        <v>2967.9</v>
       </c>
       <c r="C45" t="n">
-        <v>2983.3</v>
+        <v>2979.3</v>
       </c>
       <c r="D45" t="n">
-        <v>2949.9</v>
+        <v>2949.5</v>
       </c>
       <c r="E45" t="n">
-        <v>2969.7</v>
+        <v>2976.6</v>
       </c>
       <c r="F45" t="n">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0023</v>
       </c>
       <c r="H45" t="n">
-        <v>33.4</v>
+        <v>29.8</v>
       </c>
       <c r="I45" t="n">
-        <v>2866.5</v>
+        <v>2916.5</v>
       </c>
       <c r="J45" t="n">
-        <v>2920.95</v>
+        <v>2937.85</v>
       </c>
       <c r="K45" t="n">
-        <v>2934.8</v>
+        <v>2953</v>
       </c>
       <c r="L45" t="n">
-        <v>2948.65</v>
+        <v>2968.15</v>
       </c>
       <c r="M45" t="n">
-        <v>2982.8</v>
+        <v>2986.4</v>
       </c>
       <c r="N45" t="n">
-        <v>3016.95</v>
+        <v>3004.65</v>
       </c>
       <c r="O45" t="n">
-        <v>3010.5</v>
+        <v>3016.7</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4293,18 +4295,18 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4319,57 +4321,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2967.9</v>
+        <v>2974.7</v>
       </c>
       <c r="C46" t="n">
-        <v>2979.3</v>
+        <v>2977.9</v>
       </c>
       <c r="D46" t="n">
-        <v>2949.5</v>
+        <v>2954.7</v>
       </c>
       <c r="E46" t="n">
-        <v>2976.6</v>
+        <v>2963.6</v>
       </c>
       <c r="F46" t="n">
-        <v>6.9</v>
+        <v>-13</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0044</v>
       </c>
       <c r="H46" t="n">
-        <v>29.8</v>
+        <v>23.2</v>
       </c>
       <c r="I46" t="n">
-        <v>2916.5</v>
+        <v>2919.7</v>
       </c>
       <c r="J46" t="n">
-        <v>2937.85</v>
+        <v>2952.9</v>
       </c>
       <c r="K46" t="n">
-        <v>2953</v>
+        <v>2961.7</v>
       </c>
       <c r="L46" t="n">
-        <v>2968.15</v>
+        <v>2970.5</v>
       </c>
       <c r="M46" t="n">
-        <v>2986.4</v>
+        <v>2991.5</v>
       </c>
       <c r="N46" t="n">
-        <v>3004.65</v>
+        <v>3012.5</v>
       </c>
       <c r="O46" t="n">
-        <v>3016.7</v>
+        <v>3009.1</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4379,12 +4381,12 @@
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4410,63 +4412,67 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2974.7</v>
+        <v>2963.1</v>
       </c>
       <c r="C47" t="n">
-        <v>2977.9</v>
+        <v>2966.2</v>
       </c>
       <c r="D47" t="n">
-        <v>2954.7</v>
+        <v>2919.4</v>
       </c>
       <c r="E47" t="n">
-        <v>2963.6</v>
+        <v>2923</v>
       </c>
       <c r="F47" t="n">
-        <v>-13</v>
+        <v>-40.6</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0137</v>
       </c>
       <c r="H47" t="n">
-        <v>23.2</v>
+        <v>46.8</v>
       </c>
       <c r="I47" t="n">
-        <v>2919.7</v>
+        <v>2931.5</v>
       </c>
       <c r="J47" t="n">
-        <v>2952.9</v>
+        <v>2939.05</v>
       </c>
       <c r="K47" t="n">
-        <v>2961.7</v>
+        <v>2952</v>
       </c>
       <c r="L47" t="n">
-        <v>2970.5</v>
+        <v>2964.95</v>
       </c>
       <c r="M47" t="n">
-        <v>2991.5</v>
+        <v>2975.2</v>
       </c>
       <c r="N47" t="n">
-        <v>3012.5</v>
+        <v>2985.45</v>
       </c>
       <c r="O47" t="n">
-        <v>3009.1</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
+        <v>3001.1</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4485,76 +4491,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2963.1</v>
+        <v>2923.1</v>
       </c>
       <c r="C48" t="n">
-        <v>2966.2</v>
+        <v>2933.8</v>
       </c>
       <c r="D48" t="n">
-        <v>2919.4</v>
+        <v>2887.8</v>
       </c>
       <c r="E48" t="n">
-        <v>2923</v>
+        <v>2893.4</v>
       </c>
       <c r="F48" t="n">
-        <v>-40.6</v>
+        <v>-29.6</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0101</v>
       </c>
       <c r="H48" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="I48" t="n">
-        <v>2931.5</v>
+        <v>2872.6</v>
       </c>
       <c r="J48" t="n">
-        <v>2939.05</v>
+        <v>2866.3</v>
       </c>
       <c r="K48" t="n">
-        <v>2952</v>
+        <v>2899.6</v>
       </c>
       <c r="L48" t="n">
-        <v>2964.95</v>
+        <v>2932.9</v>
       </c>
       <c r="M48" t="n">
-        <v>2975.2</v>
+        <v>2946.4</v>
       </c>
       <c r="N48" t="n">
-        <v>2985.45</v>
+        <v>2959.9</v>
       </c>
       <c r="O48" t="n">
-        <v>3001.1</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
+        <v>3013</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
+      <c r="S48" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4578,50 +4576,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2923.1</v>
+        <v>2890.9</v>
       </c>
       <c r="C49" t="n">
-        <v>2933.8</v>
+        <v>2929.8</v>
       </c>
       <c r="D49" t="n">
-        <v>2887.8</v>
+        <v>2887.6</v>
       </c>
       <c r="E49" t="n">
-        <v>2893.4</v>
+        <v>2904.5</v>
       </c>
       <c r="F49" t="n">
-        <v>-29.6</v>
+        <v>11.1</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0101</v>
+        <v>0.0038</v>
       </c>
       <c r="H49" t="n">
-        <v>46</v>
+        <v>42.2</v>
       </c>
       <c r="I49" t="n">
-        <v>2872.6</v>
+        <v>2841.8</v>
       </c>
       <c r="J49" t="n">
-        <v>2866.3</v>
+        <v>2838.7</v>
       </c>
       <c r="K49" t="n">
-        <v>2899.6</v>
+        <v>2870.4</v>
       </c>
       <c r="L49" t="n">
-        <v>2932.9</v>
+        <v>2902.1</v>
       </c>
       <c r="M49" t="n">
-        <v>2946.4</v>
+        <v>2916.4</v>
       </c>
       <c r="N49" t="n">
-        <v>2959.9</v>
+        <v>2930.7</v>
       </c>
       <c r="O49" t="n">
-        <v>3013</v>
+        <v>2979.8</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4629,18 +4627,18 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R49" s="6" t="n">
+        <v/>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4653,55 +4651,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2890.9</v>
+        <v>2892.7</v>
       </c>
       <c r="C50" t="n">
-        <v>2929.8</v>
+        <v>2913.5</v>
       </c>
       <c r="D50" t="n">
-        <v>2887.6</v>
+        <v>2884.3</v>
       </c>
       <c r="E50" t="n">
-        <v>2904.5</v>
+        <v>2894.1</v>
       </c>
       <c r="F50" t="n">
-        <v>11.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0036</v>
       </c>
       <c r="H50" t="n">
-        <v>42.2</v>
+        <v>29.2</v>
       </c>
       <c r="I50" t="n">
-        <v>2841.8</v>
+        <v>2845.4</v>
       </c>
       <c r="J50" t="n">
-        <v>2838.7</v>
+        <v>2860.2</v>
       </c>
       <c r="K50" t="n">
-        <v>2870.4</v>
+        <v>2883.4</v>
       </c>
       <c r="L50" t="n">
-        <v>2902.1</v>
+        <v>2906.6</v>
       </c>
       <c r="M50" t="n">
-        <v>2916.4</v>
+        <v>2925.6</v>
       </c>
       <c r="N50" t="n">
-        <v>2930.7</v>
+        <v>2944.6</v>
       </c>
       <c r="O50" t="n">
-        <v>2979.8</v>
+        <v>2972</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4709,18 +4711,18 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4733,59 +4735,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2892.7</v>
+        <v>2896.4</v>
       </c>
       <c r="C51" t="n">
-        <v>2913.5</v>
+        <v>2896.5</v>
       </c>
       <c r="D51" t="n">
-        <v>2884.3</v>
+        <v>2862.7</v>
       </c>
       <c r="E51" t="n">
-        <v>2894.1</v>
+        <v>2873.1</v>
       </c>
       <c r="F51" t="n">
-        <v>-10.4</v>
+        <v>-21</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0073</v>
       </c>
       <c r="H51" t="n">
-        <v>29.2</v>
+        <v>33.8</v>
       </c>
       <c r="I51" t="n">
-        <v>2845.4</v>
+        <v>2855.1</v>
       </c>
       <c r="J51" t="n">
-        <v>2860.2</v>
+        <v>2862.5</v>
       </c>
       <c r="K51" t="n">
-        <v>2883.4</v>
+        <v>2879.5</v>
       </c>
       <c r="L51" t="n">
-        <v>2906.6</v>
+        <v>2896.5</v>
       </c>
       <c r="M51" t="n">
-        <v>2925.6</v>
+        <v>2908.7</v>
       </c>
       <c r="N51" t="n">
-        <v>2944.6</v>
+        <v>2920.9</v>
       </c>
       <c r="O51" t="n">
-        <v>2972</v>
+        <v>2942.7</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4798,7 +4796,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
+      <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4822,69 +4820,73 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2896.4</v>
+        <v>2875.1</v>
       </c>
       <c r="C52" t="n">
-        <v>2896.5</v>
+        <v>2892.5</v>
       </c>
       <c r="D52" t="n">
-        <v>2862.7</v>
+        <v>2831.9</v>
       </c>
       <c r="E52" t="n">
-        <v>2873.1</v>
+        <v>2861.7</v>
       </c>
       <c r="F52" t="n">
-        <v>-21</v>
+        <v>-11.4</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.004</v>
       </c>
       <c r="H52" t="n">
-        <v>33.8</v>
+        <v>60.6</v>
       </c>
       <c r="I52" t="n">
-        <v>2855.1</v>
+        <v>2828.9</v>
       </c>
       <c r="J52" t="n">
-        <v>2862.5</v>
+        <v>2836.05</v>
       </c>
       <c r="K52" t="n">
-        <v>2879.5</v>
+        <v>2856.2</v>
       </c>
       <c r="L52" t="n">
-        <v>2896.5</v>
+        <v>2876.35</v>
       </c>
       <c r="M52" t="n">
-        <v>2908.7</v>
+        <v>2890</v>
       </c>
       <c r="N52" t="n">
-        <v>2920.9</v>
+        <v>2903.65</v>
       </c>
       <c r="O52" t="n">
-        <v>2942.7</v>
+        <v>2930.3</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="10" t="inlineStr">
+      <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4902,74 +4904,70 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2875.1</v>
+        <v>2861.2</v>
       </c>
       <c r="C53" t="n">
-        <v>2892.5</v>
+        <v>2904.6</v>
       </c>
       <c r="D53" t="n">
-        <v>2831.9</v>
+        <v>2859.3</v>
       </c>
       <c r="E53" t="n">
-        <v>2861.7</v>
+        <v>2875.9</v>
       </c>
       <c r="F53" t="n">
-        <v>-11.4</v>
+        <v>14.2</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.005</v>
       </c>
       <c r="H53" t="n">
-        <v>60.6</v>
+        <v>45.3</v>
       </c>
       <c r="I53" t="n">
-        <v>2828.9</v>
+        <v>2771.3</v>
       </c>
       <c r="J53" t="n">
-        <v>2836.05</v>
+        <v>2800.85</v>
       </c>
       <c r="K53" t="n">
-        <v>2856.2</v>
+        <v>2831.4</v>
       </c>
       <c r="L53" t="n">
-        <v>2876.35</v>
+        <v>2861.95</v>
       </c>
       <c r="M53" t="n">
-        <v>2890</v>
+        <v>2892</v>
       </c>
       <c r="N53" t="n">
-        <v>2903.65</v>
+        <v>2922.05</v>
       </c>
       <c r="O53" t="n">
-        <v>2930.3</v>
+        <v>2953.1</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U53" s="8" t="n">
         <v/>
       </c>
@@ -4981,55 +4979,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2861.2</v>
+        <v>2870.5</v>
       </c>
       <c r="C54" t="n">
-        <v>2904.6</v>
+        <v>2883</v>
       </c>
       <c r="D54" t="n">
-        <v>2859.3</v>
+        <v>2856.9</v>
       </c>
       <c r="E54" t="n">
-        <v>2875.9</v>
+        <v>2873.23</v>
       </c>
       <c r="F54" t="n">
-        <v>14.2</v>
+        <v>-2.67</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0009</v>
       </c>
       <c r="H54" t="n">
-        <v>45.3</v>
+        <v>26.1</v>
       </c>
       <c r="I54" t="n">
-        <v>2771.3</v>
+        <v>2814</v>
       </c>
       <c r="J54" t="n">
-        <v>2800.85</v>
+        <v>2827.57</v>
       </c>
       <c r="K54" t="n">
-        <v>2831.4</v>
+        <v>2853.25</v>
       </c>
       <c r="L54" t="n">
-        <v>2861.95</v>
+        <v>2878.92</v>
       </c>
       <c r="M54" t="n">
-        <v>2892</v>
+        <v>2898.55</v>
       </c>
       <c r="N54" t="n">
-        <v>2922.05</v>
+        <v>2918.17</v>
       </c>
       <c r="O54" t="n">
-        <v>2953.1</v>
+        <v>2949.9</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5042,13 +5044,11 @@
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5061,59 +5061,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2870.5</v>
+        <v>2879.5</v>
       </c>
       <c r="C55" t="n">
-        <v>2883</v>
+        <v>2907.3</v>
       </c>
       <c r="D55" t="n">
-        <v>2856.9</v>
+        <v>2876.6</v>
       </c>
       <c r="E55" t="n">
-        <v>2873.23</v>
+        <v>2897.4</v>
       </c>
       <c r="F55" t="n">
-        <v>-2.67</v>
+        <v>24.17</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>26.1</v>
+        <v>30.7</v>
       </c>
       <c r="I55" t="n">
-        <v>2814</v>
+        <v>2830.8</v>
       </c>
       <c r="J55" t="n">
-        <v>2827.57</v>
+        <v>2848.77</v>
       </c>
       <c r="K55" t="n">
-        <v>2853.25</v>
+        <v>2860.18</v>
       </c>
       <c r="L55" t="n">
-        <v>2878.92</v>
+        <v>2871.59</v>
       </c>
       <c r="M55" t="n">
-        <v>2898.55</v>
+        <v>2886.28</v>
       </c>
       <c r="N55" t="n">
-        <v>2918.17</v>
+        <v>2900.97</v>
       </c>
       <c r="O55" t="n">
-        <v>2949.9</v>
+        <v>2909.1</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5126,14 +5122,18 @@
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5143,55 +5143,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2879.5</v>
+        <v>2897.8</v>
       </c>
       <c r="C56" t="n">
-        <v>2907.3</v>
+        <v>2931.2</v>
       </c>
       <c r="D56" t="n">
-        <v>2876.6</v>
+        <v>2884.2</v>
       </c>
       <c r="E56" t="n">
-        <v>2897.4</v>
+        <v>2914.1</v>
       </c>
       <c r="F56" t="n">
-        <v>24.17</v>
+        <v>16.7</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0058</v>
       </c>
       <c r="H56" t="n">
-        <v>30.7</v>
+        <v>47</v>
       </c>
       <c r="I56" t="n">
-        <v>2830.8</v>
+        <v>2845.9</v>
       </c>
       <c r="J56" t="n">
-        <v>2848.77</v>
+        <v>2869.42</v>
       </c>
       <c r="K56" t="n">
-        <v>2860.18</v>
+        <v>2882.05</v>
       </c>
       <c r="L56" t="n">
-        <v>2871.59</v>
+        <v>2894.67</v>
       </c>
       <c r="M56" t="n">
-        <v>2886.28</v>
+        <v>2912.75</v>
       </c>
       <c r="N56" t="n">
-        <v>2900.97</v>
+        <v>2930.82</v>
       </c>
       <c r="O56" t="n">
-        <v>2909.1</v>
+        <v>2938</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5202,19 +5206,19 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="V56" s="8" t="n">
@@ -5234,74 +5238,74 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2897.8</v>
+        <v>2912</v>
       </c>
       <c r="C57" t="n">
-        <v>2931.2</v>
+        <v>2915.3</v>
       </c>
       <c r="D57" t="n">
-        <v>2884.2</v>
+        <v>2858.8</v>
       </c>
       <c r="E57" t="n">
-        <v>2914.1</v>
+        <v>2860.2</v>
       </c>
       <c r="F57" t="n">
-        <v>16.7</v>
+        <v>-53.9</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0185</v>
       </c>
       <c r="H57" t="n">
-        <v>47</v>
+        <v>56.5</v>
       </c>
       <c r="I57" t="n">
-        <v>2845.9</v>
+        <v>2837.2</v>
       </c>
       <c r="J57" t="n">
-        <v>2869.42</v>
+        <v>2870.3</v>
       </c>
       <c r="K57" t="n">
-        <v>2882.05</v>
+        <v>2890.6</v>
       </c>
       <c r="L57" t="n">
-        <v>2894.67</v>
+        <v>2910.9</v>
       </c>
       <c r="M57" t="n">
-        <v>2912.75</v>
+        <v>2937.6</v>
       </c>
       <c r="N57" t="n">
-        <v>2930.82</v>
+        <v>2964.3</v>
       </c>
       <c r="O57" t="n">
-        <v>2938</v>
+        <v>2978.2</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5311,76 +5315,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2912</v>
+        <v>2860.7</v>
       </c>
       <c r="C58" t="n">
-        <v>2915.3</v>
+        <v>2862.4</v>
       </c>
       <c r="D58" t="n">
-        <v>2858.8</v>
+        <v>2829.9</v>
       </c>
       <c r="E58" t="n">
-        <v>2860.2</v>
+        <v>2856.8</v>
       </c>
       <c r="F58" t="n">
-        <v>-53.9</v>
+        <v>-3.4</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0012</v>
       </c>
       <c r="H58" t="n">
-        <v>56.5</v>
+        <v>32.5</v>
       </c>
       <c r="I58" t="n">
-        <v>2837.2</v>
+        <v>2802.3</v>
       </c>
       <c r="J58" t="n">
-        <v>2870.3</v>
+        <v>2790.27</v>
       </c>
       <c r="K58" t="n">
-        <v>2890.6</v>
+        <v>2831.95</v>
       </c>
       <c r="L58" t="n">
-        <v>2910.9</v>
+        <v>2873.62</v>
       </c>
       <c r="M58" t="n">
-        <v>2937.6</v>
+        <v>2888.45</v>
       </c>
       <c r="N58" t="n">
-        <v>2964.3</v>
+        <v>2903.27</v>
       </c>
       <c r="O58" t="n">
-        <v>2978.2</v>
+        <v>2971.8</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q58" s="6" t="n">
+        <v/>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5402,50 +5400,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2860.7</v>
+        <v>2854.4</v>
       </c>
       <c r="C59" t="n">
-        <v>2862.4</v>
+        <v>2874.1</v>
       </c>
       <c r="D59" t="n">
-        <v>2829.9</v>
+        <v>2843</v>
       </c>
       <c r="E59" t="n">
-        <v>2856.8</v>
+        <v>2859.3</v>
       </c>
       <c r="F59" t="n">
-        <v>-3.4</v>
+        <v>2.5</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="H59" t="n">
-        <v>32.5</v>
+        <v>31.1</v>
       </c>
       <c r="I59" t="n">
-        <v>2802.3</v>
+        <v>2797.4</v>
       </c>
       <c r="J59" t="n">
-        <v>2790.27</v>
+        <v>2829.63</v>
       </c>
       <c r="K59" t="n">
-        <v>2831.95</v>
+        <v>2840.55</v>
       </c>
       <c r="L59" t="n">
-        <v>2873.62</v>
+        <v>2851.47</v>
       </c>
       <c r="M59" t="n">
-        <v>2888.45</v>
+        <v>2873.05</v>
       </c>
       <c r="N59" t="n">
-        <v>2903.27</v>
+        <v>2894.63</v>
       </c>
       <c r="O59" t="n">
-        <v>2971.8</v>
+        <v>2894.9</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5453,19 +5451,19 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
       <c r="U59" s="8" t="n">
         <v/>
       </c>
@@ -5477,74 +5475,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2854.4</v>
+        <v>2857.7</v>
       </c>
       <c r="C60" t="n">
-        <v>2874.1</v>
+        <v>2858.8</v>
       </c>
       <c r="D60" t="n">
-        <v>2843</v>
+        <v>2826.8</v>
       </c>
       <c r="E60" t="n">
-        <v>2859.3</v>
+        <v>2840.1</v>
       </c>
       <c r="F60" t="n">
-        <v>2.5</v>
+        <v>-19.2</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0067</v>
       </c>
       <c r="H60" t="n">
-        <v>31.1</v>
+        <v>32</v>
       </c>
       <c r="I60" t="n">
-        <v>2797.4</v>
+        <v>2811.9</v>
       </c>
       <c r="J60" t="n">
-        <v>2829.63</v>
+        <v>2828.57</v>
       </c>
       <c r="K60" t="n">
-        <v>2840.55</v>
+        <v>2843.75</v>
       </c>
       <c r="L60" t="n">
-        <v>2851.47</v>
+        <v>2858.93</v>
       </c>
       <c r="M60" t="n">
-        <v>2873.05</v>
+        <v>2874.85</v>
       </c>
       <c r="N60" t="n">
-        <v>2894.63</v>
+        <v>2890.78</v>
       </c>
       <c r="O60" t="n">
-        <v>2894.9</v>
+        <v>2905.2</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5557,74 +5561,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2857.7</v>
+        <v>2839.6</v>
       </c>
       <c r="C61" t="n">
-        <v>2858.8</v>
+        <v>2851.8</v>
       </c>
       <c r="D61" t="n">
-        <v>2826.8</v>
+        <v>2811.9</v>
       </c>
       <c r="E61" t="n">
-        <v>2840.1</v>
+        <v>2829.2</v>
       </c>
       <c r="F61" t="n">
-        <v>-19.2</v>
+        <v>-10.9</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0067</v>
+        <v>-0.0038</v>
       </c>
       <c r="H61" t="n">
-        <v>32</v>
+        <v>39.9</v>
       </c>
       <c r="I61" t="n">
-        <v>2811.9</v>
+        <v>2794.8</v>
       </c>
       <c r="J61" t="n">
-        <v>2828.57</v>
+        <v>2806.75</v>
       </c>
       <c r="K61" t="n">
-        <v>2843.75</v>
+        <v>2824.1</v>
       </c>
       <c r="L61" t="n">
-        <v>2858.93</v>
+        <v>2841.45</v>
       </c>
       <c r="M61" t="n">
-        <v>2874.85</v>
+        <v>2856.1</v>
       </c>
       <c r="N61" t="n">
-        <v>2890.78</v>
+        <v>2870.75</v>
       </c>
       <c r="O61" t="n">
-        <v>2905.2</v>
+        <v>2890.8</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q61" s="6" t="n">
+        <v/>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S61" s="10" t="inlineStr">
+      <c r="S61" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5648,50 +5646,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2831.6</v>
+        <v>2819.6</v>
       </c>
       <c r="C62" t="n">
-        <v>2834.9</v>
+        <v>2821.3</v>
       </c>
       <c r="D62" t="n">
-        <v>2831.4</v>
+        <v>2819.1</v>
       </c>
       <c r="E62" t="n">
-        <v>2834.1</v>
+        <v>2821.2</v>
       </c>
       <c r="F62" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0028</v>
       </c>
       <c r="H62" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="I62" t="n">
-        <v>2794.8</v>
+        <v>2772</v>
       </c>
       <c r="J62" t="n">
-        <v>2806.75</v>
+        <v>2787.97</v>
       </c>
       <c r="K62" t="n">
-        <v>2824.1</v>
+        <v>2809.25</v>
       </c>
       <c r="L62" t="n">
-        <v>2841.45</v>
+        <v>2830.52</v>
       </c>
       <c r="M62" t="n">
-        <v>2856.1</v>
+        <v>2849.15</v>
       </c>
       <c r="N62" t="n">
-        <v>2870.75</v>
+        <v>2867.78</v>
       </c>
       <c r="O62" t="n">
-        <v>2890.8</v>
+        <v>2891.7</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5702,7 +5700,7 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="10" t="inlineStr">
+      <c r="S62" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5650,25 +5650,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2819.6</v>
+        <v>2831.6</v>
       </c>
       <c r="C62" t="n">
-        <v>2821.3</v>
+        <v>2853.8</v>
       </c>
       <c r="D62" t="n">
-        <v>2819.1</v>
+        <v>2812.8</v>
       </c>
       <c r="E62" t="n">
-        <v>2821.2</v>
+        <v>2817.5</v>
       </c>
       <c r="F62" t="n">
-        <v>-8</v>
+        <v>-11.7</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0028</v>
+        <v>-0.0041</v>
       </c>
       <c r="H62" t="n">
-        <v>2.2</v>
+        <v>41</v>
       </c>
       <c r="I62" t="n">
         <v>2772</v>
@@ -5697,16 +5697,20 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5721,7 +5725,89 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2829</v>
+      </c>
+      <c r="C63" t="n">
+        <v>2830.6</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2828.5</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2830.4</v>
+      </c>
+      <c r="F63" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2771.8</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2768.6</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2797</v>
+      </c>
+      <c r="L63" t="n">
+        <v>2825.4</v>
+      </c>
+      <c r="M63" t="n">
+        <v>2838</v>
+      </c>
+      <c r="N63" t="n">
+        <v>2850.6</v>
+      </c>
+      <c r="O63" t="n">
+        <v>2894.8</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,64 +634,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3033.4</v>
+        <v>2994.3</v>
       </c>
       <c r="C2" t="n">
-        <v>3042.6</v>
+        <v>3004.3</v>
       </c>
       <c r="D2" t="n">
-        <v>2988.8</v>
+        <v>2943.4</v>
       </c>
       <c r="E2" t="n">
-        <v>2998.8</v>
+        <v>2971.5</v>
       </c>
       <c r="F2" t="n">
-        <v>-28.2</v>
+        <v>-27.3</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0091</v>
       </c>
       <c r="H2" t="n">
-        <v>53.8</v>
+        <v>60.9</v>
       </c>
       <c r="I2" t="n">
-        <v>2971.3</v>
+        <v>2935</v>
       </c>
       <c r="J2" t="n">
-        <v>2992.9</v>
+        <v>2936.55</v>
       </c>
       <c r="K2" t="n">
-        <v>3009.3</v>
+        <v>2971.9</v>
       </c>
       <c r="L2" t="n">
+        <v>3007.25</v>
+      </c>
+      <c r="M2" t="n">
         <v>3025.7</v>
       </c>
-      <c r="M2" t="n">
-        <v>3044.7</v>
-      </c>
       <c r="N2" t="n">
-        <v>3063.7</v>
+        <v>3044.15</v>
       </c>
       <c r="O2" t="n">
-        <v>3077.5</v>
+        <v>3096.4</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -713,57 +711,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2994.3</v>
+        <v>2965.8</v>
       </c>
       <c r="C3" t="n">
-        <v>3004.3</v>
+        <v>3014.9</v>
       </c>
       <c r="D3" t="n">
-        <v>2943.4</v>
+        <v>2964.3</v>
       </c>
       <c r="E3" t="n">
-        <v>2971.5</v>
+        <v>3008.4</v>
       </c>
       <c r="F3" t="n">
-        <v>-27.3</v>
+        <v>36.9</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0091</v>
+        <v>0.0124</v>
       </c>
       <c r="H3" t="n">
-        <v>60.9</v>
+        <v>50.6</v>
       </c>
       <c r="I3" t="n">
-        <v>2935</v>
+        <v>2882.5</v>
       </c>
       <c r="J3" t="n">
-        <v>2936.55</v>
+        <v>2909.42</v>
       </c>
       <c r="K3" t="n">
-        <v>2971.9</v>
+        <v>2941.05</v>
       </c>
       <c r="L3" t="n">
-        <v>3007.25</v>
+        <v>2972.67</v>
       </c>
       <c r="M3" t="n">
-        <v>3025.7</v>
+        <v>3001.95</v>
       </c>
       <c r="N3" t="n">
-        <v>3044.15</v>
+        <v>3031.23</v>
       </c>
       <c r="O3" t="n">
-        <v>3096.4</v>
+        <v>3065.2</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -771,19 +769,19 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
@@ -795,59 +793,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2965.8</v>
+        <v>3008.1</v>
       </c>
       <c r="C4" t="n">
-        <v>3014.9</v>
+        <v>3019.5</v>
       </c>
       <c r="D4" t="n">
-        <v>2964.3</v>
+        <v>2970.8</v>
       </c>
       <c r="E4" t="n">
-        <v>3008.4</v>
+        <v>2994</v>
       </c>
       <c r="F4" t="n">
-        <v>36.9</v>
+        <v>-14.4</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0048</v>
       </c>
       <c r="H4" t="n">
-        <v>50.6</v>
+        <v>48.7</v>
       </c>
       <c r="I4" t="n">
-        <v>2882.5</v>
+        <v>2913.7</v>
       </c>
       <c r="J4" t="n">
-        <v>2909.42</v>
+        <v>2967.2</v>
       </c>
       <c r="K4" t="n">
-        <v>2941.05</v>
+        <v>2983.1</v>
       </c>
       <c r="L4" t="n">
-        <v>2972.67</v>
+        <v>2999</v>
       </c>
       <c r="M4" t="n">
-        <v>3001.95</v>
+        <v>3033.7</v>
       </c>
       <c r="N4" t="n">
-        <v>3031.23</v>
+        <v>3068.4</v>
       </c>
       <c r="O4" t="n">
-        <v>3065.2</v>
+        <v>3065.5</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -855,18 +849,18 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -879,55 +873,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3008.1</v>
+        <v>2984.7</v>
       </c>
       <c r="C5" t="n">
-        <v>3019.5</v>
+        <v>2995.8</v>
       </c>
       <c r="D5" t="n">
-        <v>2970.8</v>
+        <v>2961.8</v>
       </c>
       <c r="E5" t="n">
-        <v>2994</v>
+        <v>2970.4</v>
       </c>
       <c r="F5" t="n">
-        <v>-14.4</v>
+        <v>-23.6</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>48.7</v>
+        <v>34</v>
       </c>
       <c r="I5" t="n">
-        <v>2913.7</v>
+        <v>2922.1</v>
       </c>
       <c r="J5" t="n">
-        <v>2967.2</v>
+        <v>2944.73</v>
       </c>
       <c r="K5" t="n">
-        <v>2983.1</v>
+        <v>2969.65</v>
       </c>
       <c r="L5" t="n">
-        <v>2999</v>
+        <v>2994.58</v>
       </c>
       <c r="M5" t="n">
-        <v>3033.7</v>
+        <v>3018.35</v>
       </c>
       <c r="N5" t="n">
-        <v>3068.4</v>
+        <v>3042.12</v>
       </c>
       <c r="O5" t="n">
-        <v>3065.5</v>
+        <v>3068.2</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -937,12 +935,12 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -961,57 +959,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2984.7</v>
+        <v>2967.2</v>
       </c>
       <c r="C6" t="n">
-        <v>2995.8</v>
+        <v>3029.8</v>
       </c>
       <c r="D6" t="n">
-        <v>2961.8</v>
+        <v>2956.2</v>
       </c>
       <c r="E6" t="n">
-        <v>2970.4</v>
+        <v>2979.9</v>
       </c>
       <c r="F6" t="n">
-        <v>-23.6</v>
+        <v>9.5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H6" t="n">
-        <v>34</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>2922.1</v>
+        <v>2927.8</v>
       </c>
       <c r="J6" t="n">
-        <v>2944.73</v>
+        <v>2932.2</v>
       </c>
       <c r="K6" t="n">
-        <v>2969.65</v>
+        <v>2953.4</v>
       </c>
       <c r="L6" t="n">
-        <v>2994.58</v>
+        <v>2974.6</v>
       </c>
       <c r="M6" t="n">
-        <v>3018.35</v>
+        <v>2987.4</v>
       </c>
       <c r="N6" t="n">
-        <v>3042.12</v>
+        <v>3000.2</v>
       </c>
       <c r="O6" t="n">
-        <v>3068.2</v>
+        <v>3029.8</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1019,24 +1017,28 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
@@ -1045,57 +1047,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2967.2</v>
+        <v>2981.2</v>
       </c>
       <c r="C7" t="n">
-        <v>3029.8</v>
+        <v>3006.1</v>
       </c>
       <c r="D7" t="n">
-        <v>2956.2</v>
+        <v>2974.4</v>
       </c>
       <c r="E7" t="n">
-        <v>2979.9</v>
+        <v>2991.8</v>
       </c>
       <c r="F7" t="n">
-        <v>9.5</v>
+        <v>11.9</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.004</v>
       </c>
       <c r="H7" t="n">
-        <v>73.59999999999999</v>
+        <v>31.7</v>
       </c>
       <c r="I7" t="n">
-        <v>2927.8</v>
+        <v>2882.6</v>
       </c>
       <c r="J7" t="n">
-        <v>2932.2</v>
+        <v>2899.75</v>
       </c>
       <c r="K7" t="n">
-        <v>2953.4</v>
+        <v>2943.1</v>
       </c>
       <c r="L7" t="n">
-        <v>2974.6</v>
+        <v>2986.45</v>
       </c>
       <c r="M7" t="n">
-        <v>2987.4</v>
+        <v>3016.7</v>
       </c>
       <c r="N7" t="n">
-        <v>3000.2</v>
+        <v>3046.95</v>
       </c>
       <c r="O7" t="n">
-        <v>3029.8</v>
+        <v>3103.4</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1111,20 +1113,14 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
@@ -1140,50 +1136,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2981.2</v>
+        <v>2995.3</v>
       </c>
       <c r="C8" t="n">
-        <v>3006.1</v>
+        <v>3012.8</v>
       </c>
       <c r="D8" t="n">
-        <v>2974.4</v>
+        <v>2972.7</v>
       </c>
       <c r="E8" t="n">
-        <v>2991.8</v>
+        <v>2990.7</v>
       </c>
       <c r="F8" t="n">
-        <v>11.9</v>
+        <v>-1.1</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0004</v>
       </c>
       <c r="H8" t="n">
-        <v>31.7</v>
+        <v>40.1</v>
       </c>
       <c r="I8" t="n">
-        <v>2882.6</v>
+        <v>2942.7</v>
       </c>
       <c r="J8" t="n">
-        <v>2899.75</v>
+        <v>2960.87</v>
       </c>
       <c r="K8" t="n">
-        <v>2943.1</v>
+        <v>2975.95</v>
       </c>
       <c r="L8" t="n">
-        <v>2986.45</v>
+        <v>2991.03</v>
       </c>
       <c r="M8" t="n">
-        <v>3016.7</v>
+        <v>3007.65</v>
       </c>
       <c r="N8" t="n">
-        <v>3046.95</v>
+        <v>3024.28</v>
       </c>
       <c r="O8" t="n">
-        <v>3103.4</v>
+        <v>3037.8</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1191,16 +1187,20 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1215,78 +1215,78 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2995.3</v>
+        <v>2991.7</v>
       </c>
       <c r="C9" t="n">
-        <v>3012.8</v>
+        <v>2994.8</v>
       </c>
       <c r="D9" t="n">
-        <v>2972.7</v>
+        <v>2949.3</v>
       </c>
       <c r="E9" t="n">
-        <v>2990.7</v>
+        <v>2973.5</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1</v>
+        <v>-17.2</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0058</v>
       </c>
       <c r="H9" t="n">
-        <v>40.1</v>
+        <v>45.5</v>
       </c>
       <c r="I9" t="n">
-        <v>2942.7</v>
+        <v>2932.6</v>
       </c>
       <c r="J9" t="n">
-        <v>2960.87</v>
+        <v>2949.57</v>
       </c>
       <c r="K9" t="n">
-        <v>2975.95</v>
+        <v>2970.65</v>
       </c>
       <c r="L9" t="n">
-        <v>2991.03</v>
+        <v>2991.72</v>
       </c>
       <c r="M9" t="n">
-        <v>3007.65</v>
+        <v>3010.75</v>
       </c>
       <c r="N9" t="n">
-        <v>3024.28</v>
+        <v>3029.78</v>
       </c>
       <c r="O9" t="n">
-        <v>3037.8</v>
+        <v>3052.9</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1301,79 +1301,79 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2991.7</v>
+        <v>2964.5</v>
       </c>
       <c r="C10" t="n">
-        <v>2994.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D10" t="n">
-        <v>2949.3</v>
+        <v>2952.7</v>
       </c>
       <c r="E10" t="n">
-        <v>2973.5</v>
+        <v>2955.2</v>
       </c>
       <c r="F10" t="n">
-        <v>-17.2</v>
+        <v>-18.3</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0062</v>
       </c>
       <c r="H10" t="n">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="I10" t="n">
-        <v>2932.6</v>
+        <v>2903.8</v>
       </c>
       <c r="J10" t="n">
-        <v>2949.57</v>
+        <v>2928.72</v>
       </c>
       <c r="K10" t="n">
-        <v>2970.65</v>
+        <v>2950.75</v>
       </c>
       <c r="L10" t="n">
-        <v>2991.72</v>
+        <v>2972.78</v>
       </c>
       <c r="M10" t="n">
-        <v>3010.75</v>
+        <v>2996.25</v>
       </c>
       <c r="N10" t="n">
-        <v>3029.78</v>
+        <v>3019.72</v>
       </c>
       <c r="O10" t="n">
-        <v>3052.9</v>
+        <v>3040.3</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
@@ -1387,57 +1387,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2964.5</v>
+        <v>2955.8</v>
       </c>
       <c r="C11" t="n">
-        <v>2998.7</v>
+        <v>2999.8</v>
       </c>
       <c r="D11" t="n">
-        <v>2952.7</v>
+        <v>2951.1</v>
       </c>
       <c r="E11" t="n">
-        <v>2955.2</v>
+        <v>2997</v>
       </c>
       <c r="F11" t="n">
-        <v>-18.3</v>
+        <v>41.8</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0141</v>
       </c>
       <c r="H11" t="n">
-        <v>46</v>
+        <v>48.7</v>
       </c>
       <c r="I11" t="n">
-        <v>2903.8</v>
+        <v>2906.7</v>
       </c>
       <c r="J11" t="n">
-        <v>2928.72</v>
+        <v>2898.95</v>
       </c>
       <c r="K11" t="n">
-        <v>2950.75</v>
+        <v>2932.2</v>
       </c>
       <c r="L11" t="n">
-        <v>2972.78</v>
+        <v>2965.45</v>
       </c>
       <c r="M11" t="n">
-        <v>2996.25</v>
+        <v>2978.2</v>
       </c>
       <c r="N11" t="n">
-        <v>3019.72</v>
+        <v>2990.95</v>
       </c>
       <c r="O11" t="n">
-        <v>3040.3</v>
+        <v>3044.7</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1445,23 +1445,23 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1480,50 +1480,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2955.8</v>
+        <v>2997</v>
       </c>
       <c r="C12" t="n">
-        <v>2999.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D12" t="n">
-        <v>2951.1</v>
+        <v>2965.5</v>
       </c>
       <c r="E12" t="n">
-        <v>2997</v>
+        <v>2969.8</v>
       </c>
       <c r="F12" t="n">
-        <v>41.8</v>
+        <v>-27.2</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0141</v>
+        <v>-0.0091</v>
       </c>
       <c r="H12" t="n">
-        <v>48.7</v>
+        <v>33.2</v>
       </c>
       <c r="I12" t="n">
-        <v>2906.7</v>
+        <v>2902.4</v>
       </c>
       <c r="J12" t="n">
-        <v>2898.95</v>
+        <v>2959.08</v>
       </c>
       <c r="K12" t="n">
-        <v>2932.2</v>
+        <v>2972.65</v>
       </c>
       <c r="L12" t="n">
-        <v>2965.45</v>
+        <v>2986.23</v>
       </c>
       <c r="M12" t="n">
-        <v>2978.2</v>
+        <v>3021.35</v>
       </c>
       <c r="N12" t="n">
-        <v>2990.95</v>
+        <v>3056.47</v>
       </c>
       <c r="O12" t="n">
-        <v>3044.7</v>
+        <v>3048.5</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1531,24 +1531,22 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
+      <c r="R12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
@@ -1559,60 +1557,62 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2997</v>
+        <v>2974.6</v>
       </c>
       <c r="C13" t="n">
-        <v>2998.7</v>
+        <v>2979</v>
       </c>
       <c r="D13" t="n">
-        <v>2965.5</v>
+        <v>2932.1</v>
       </c>
       <c r="E13" t="n">
-        <v>2969.8</v>
+        <v>2951.7</v>
       </c>
       <c r="F13" t="n">
-        <v>-27.2</v>
+        <v>-18.1</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0091</v>
+        <v>-0.0061</v>
       </c>
       <c r="H13" t="n">
-        <v>33.2</v>
+        <v>46.9</v>
       </c>
       <c r="I13" t="n">
-        <v>2902.4</v>
+        <v>2932.3</v>
       </c>
       <c r="J13" t="n">
-        <v>2959.08</v>
+        <v>2930.45</v>
       </c>
       <c r="K13" t="n">
-        <v>2972.65</v>
+        <v>2953.2</v>
       </c>
       <c r="L13" t="n">
-        <v>2986.23</v>
+        <v>2975.95</v>
       </c>
       <c r="M13" t="n">
-        <v>3021.35</v>
+        <v>2986.4</v>
       </c>
       <c r="N13" t="n">
-        <v>3056.47</v>
+        <v>2996.85</v>
       </c>
       <c r="O13" t="n">
-        <v>3048.5</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
+        <v>3031.9</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q13" s="6" t="n">
         <v/>
@@ -1643,74 +1643,70 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2974.6</v>
+        <v>2948.5</v>
       </c>
       <c r="C14" t="n">
-        <v>2979</v>
+        <v>2969.7</v>
       </c>
       <c r="D14" t="n">
-        <v>2932.1</v>
+        <v>2934.5</v>
       </c>
       <c r="E14" t="n">
-        <v>2951.7</v>
+        <v>2941.3</v>
       </c>
       <c r="F14" t="n">
-        <v>-18.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0035</v>
       </c>
       <c r="H14" t="n">
-        <v>46.9</v>
+        <v>35.2</v>
       </c>
       <c r="I14" t="n">
-        <v>2932.3</v>
+        <v>2885.2</v>
       </c>
       <c r="J14" t="n">
-        <v>2930.45</v>
+        <v>2902.88</v>
       </c>
       <c r="K14" t="n">
-        <v>2953.2</v>
+        <v>2928.25</v>
       </c>
       <c r="L14" t="n">
-        <v>2975.95</v>
+        <v>2953.62</v>
       </c>
       <c r="M14" t="n">
-        <v>2986.4</v>
+        <v>2975.15</v>
       </c>
       <c r="N14" t="n">
-        <v>2996.85</v>
+        <v>2996.67</v>
       </c>
       <c r="O14" t="n">
-        <v>3031.9</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3025.9</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
       </c>
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R14" s="6" t="n">
+        <v/>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1729,57 +1725,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2948.5</v>
+        <v>2955.5</v>
       </c>
       <c r="C15" t="n">
-        <v>2969.7</v>
+        <v>2985.9</v>
       </c>
       <c r="D15" t="n">
-        <v>2934.5</v>
+        <v>2941.2</v>
       </c>
       <c r="E15" t="n">
-        <v>2941.3</v>
+        <v>2960</v>
       </c>
       <c r="F15" t="n">
-        <v>-10.4</v>
+        <v>18.7</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0064</v>
       </c>
       <c r="H15" t="n">
-        <v>35.2</v>
+        <v>44.7</v>
       </c>
       <c r="I15" t="n">
-        <v>2885.2</v>
+        <v>2899.3</v>
       </c>
       <c r="J15" t="n">
-        <v>2902.88</v>
+        <v>2900.7</v>
       </c>
       <c r="K15" t="n">
-        <v>2928.25</v>
+        <v>2923.7</v>
       </c>
       <c r="L15" t="n">
-        <v>2953.62</v>
+        <v>2946.7</v>
       </c>
       <c r="M15" t="n">
-        <v>2975.15</v>
+        <v>2958.9</v>
       </c>
       <c r="N15" t="n">
-        <v>2996.67</v>
+        <v>2971.1</v>
       </c>
       <c r="O15" t="n">
-        <v>3025.9</v>
+        <v>3004.9</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1790,16 +1786,20 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1809,59 +1809,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2955.5</v>
+        <v>2961.5</v>
       </c>
       <c r="C16" t="n">
-        <v>2985.9</v>
+        <v>2968.3</v>
       </c>
       <c r="D16" t="n">
-        <v>2941.2</v>
+        <v>2933.4</v>
       </c>
       <c r="E16" t="n">
-        <v>2960</v>
+        <v>2964.5</v>
       </c>
       <c r="F16" t="n">
-        <v>18.7</v>
+        <v>4.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0015</v>
       </c>
       <c r="H16" t="n">
-        <v>44.7</v>
+        <v>34.9</v>
       </c>
       <c r="I16" t="n">
-        <v>2899.3</v>
+        <v>2896.5</v>
       </c>
       <c r="J16" t="n">
-        <v>2900.7</v>
+        <v>2913.53</v>
       </c>
       <c r="K16" t="n">
-        <v>2923.7</v>
+        <v>2937.65</v>
       </c>
       <c r="L16" t="n">
-        <v>2946.7</v>
+        <v>2961.77</v>
       </c>
       <c r="M16" t="n">
-        <v>2958.9</v>
+        <v>2982.35</v>
       </c>
       <c r="N16" t="n">
-        <v>2971.1</v>
+        <v>3002.92</v>
       </c>
       <c r="O16" t="n">
-        <v>3004.9</v>
+        <v>3030.6</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1869,23 +1865,21 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1895,70 +1889,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2961.5</v>
+        <v>2966.9</v>
       </c>
       <c r="C17" t="n">
-        <v>2968.3</v>
+        <v>2978.3</v>
       </c>
       <c r="D17" t="n">
-        <v>2933.4</v>
+        <v>2902.3</v>
       </c>
       <c r="E17" t="n">
-        <v>2964.5</v>
+        <v>2915.4</v>
       </c>
       <c r="F17" t="n">
-        <v>4.5</v>
+        <v>-49.1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0166</v>
       </c>
       <c r="H17" t="n">
-        <v>34.9</v>
+        <v>76</v>
       </c>
       <c r="I17" t="n">
-        <v>2896.5</v>
+        <v>2898.5</v>
       </c>
       <c r="J17" t="n">
-        <v>2913.53</v>
+        <v>2936.42</v>
       </c>
       <c r="K17" t="n">
-        <v>2937.65</v>
+        <v>2947.05</v>
       </c>
       <c r="L17" t="n">
-        <v>2961.77</v>
+        <v>2957.67</v>
       </c>
       <c r="M17" t="n">
-        <v>2982.35</v>
+        <v>2981.95</v>
       </c>
       <c r="N17" t="n">
-        <v>3002.92</v>
+        <v>3006.23</v>
       </c>
       <c r="O17" t="n">
-        <v>3030.6</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
+        <v>3003.2</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1970,88 +1972,84 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W17" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2966.9</v>
+        <v>2906.6</v>
       </c>
       <c r="C18" t="n">
-        <v>2978.3</v>
+        <v>2957.9</v>
       </c>
       <c r="D18" t="n">
-        <v>2902.3</v>
+        <v>2905.6</v>
       </c>
       <c r="E18" t="n">
-        <v>2915.4</v>
+        <v>2954.3</v>
       </c>
       <c r="F18" t="n">
-        <v>-49.1</v>
+        <v>38.9</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0166</v>
+        <v>0.0133</v>
       </c>
       <c r="H18" t="n">
-        <v>76</v>
+        <v>52.3</v>
       </c>
       <c r="I18" t="n">
-        <v>2898.5</v>
+        <v>2826.3</v>
       </c>
       <c r="J18" t="n">
-        <v>2936.42</v>
+        <v>2826.95</v>
       </c>
       <c r="K18" t="n">
-        <v>2947.05</v>
+        <v>2877.4</v>
       </c>
       <c r="L18" t="n">
-        <v>2957.67</v>
+        <v>2927.85</v>
       </c>
       <c r="M18" t="n">
-        <v>2981.95</v>
+        <v>2953.4</v>
       </c>
       <c r="N18" t="n">
-        <v>3006.23</v>
+        <v>2978.95</v>
       </c>
       <c r="O18" t="n">
-        <v>3003.2</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
+        <v>3054.3</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
@@ -2065,76 +2063,78 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2906.6</v>
+        <v>2954</v>
       </c>
       <c r="C19" t="n">
-        <v>2957.9</v>
+        <v>2976.3</v>
       </c>
       <c r="D19" t="n">
-        <v>2905.6</v>
+        <v>2905.3</v>
       </c>
       <c r="E19" t="n">
-        <v>2954.3</v>
+        <v>2938</v>
       </c>
       <c r="F19" t="n">
-        <v>38.9</v>
+        <v>-16.3</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0055</v>
       </c>
       <c r="H19" t="n">
-        <v>52.3</v>
+        <v>71</v>
       </c>
       <c r="I19" t="n">
-        <v>2826.3</v>
+        <v>2853.3</v>
       </c>
       <c r="J19" t="n">
-        <v>2826.95</v>
+        <v>2913.28</v>
       </c>
       <c r="K19" t="n">
-        <v>2877.4</v>
+        <v>2928.15</v>
       </c>
       <c r="L19" t="n">
-        <v>2927.85</v>
+        <v>2943.03</v>
       </c>
       <c r="M19" t="n">
-        <v>2953.4</v>
+        <v>2980.45</v>
       </c>
       <c r="N19" t="n">
-        <v>2978.95</v>
+        <v>3017.87</v>
       </c>
       <c r="O19" t="n">
-        <v>3054.3</v>
+        <v>3010.2</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2149,78 +2149,76 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2954</v>
+        <v>2950</v>
       </c>
       <c r="C20" t="n">
-        <v>2976.3</v>
+        <v>2994.6</v>
       </c>
       <c r="D20" t="n">
-        <v>2905.3</v>
+        <v>2948.4</v>
       </c>
       <c r="E20" t="n">
-        <v>2938</v>
+        <v>2989.3</v>
       </c>
       <c r="F20" t="n">
-        <v>-16.3</v>
+        <v>51.3</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0175</v>
       </c>
       <c r="H20" t="n">
-        <v>71</v>
+        <v>46.2</v>
       </c>
       <c r="I20" t="n">
-        <v>2853.3</v>
+        <v>2834.3</v>
       </c>
       <c r="J20" t="n">
-        <v>2913.28</v>
+        <v>2865.6</v>
       </c>
       <c r="K20" t="n">
-        <v>2928.15</v>
+        <v>2902.5</v>
       </c>
       <c r="L20" t="n">
-        <v>2943.03</v>
+        <v>2939.4</v>
       </c>
       <c r="M20" t="n">
-        <v>2980.45</v>
+        <v>2973.5</v>
       </c>
       <c r="N20" t="n">
-        <v>3017.87</v>
+        <v>3007.6</v>
       </c>
       <c r="O20" t="n">
-        <v>3010.2</v>
+        <v>3047.3</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2235,57 +2233,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2950</v>
+        <v>2992.4</v>
       </c>
       <c r="C21" t="n">
-        <v>2994.6</v>
+        <v>3051.8</v>
       </c>
       <c r="D21" t="n">
-        <v>2948.4</v>
+        <v>2986.1</v>
       </c>
       <c r="E21" t="n">
-        <v>2989.3</v>
+        <v>3044.7</v>
       </c>
       <c r="F21" t="n">
-        <v>51.3</v>
+        <v>55.4</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0185</v>
       </c>
       <c r="H21" t="n">
-        <v>46.2</v>
+        <v>65.7</v>
       </c>
       <c r="I21" t="n">
-        <v>2834.3</v>
+        <v>2902.2</v>
       </c>
       <c r="J21" t="n">
-        <v>2865.6</v>
+        <v>2952</v>
       </c>
       <c r="K21" t="n">
-        <v>2902.5</v>
+        <v>2966.2</v>
       </c>
       <c r="L21" t="n">
-        <v>2939.4</v>
+        <v>2980.4</v>
       </c>
       <c r="M21" t="n">
-        <v>2973.5</v>
+        <v>3012.4</v>
       </c>
       <c r="N21" t="n">
-        <v>3007.6</v>
+        <v>3044.4</v>
       </c>
       <c r="O21" t="n">
-        <v>3047.3</v>
+        <v>3040.8</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2303,73 +2301,73 @@
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W21" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2992.4</v>
+        <v>3049.1</v>
       </c>
       <c r="C22" t="n">
-        <v>3051.8</v>
+        <v>3058.3</v>
       </c>
       <c r="D22" t="n">
-        <v>2986.1</v>
+        <v>3023.3</v>
       </c>
       <c r="E22" t="n">
-        <v>3044.7</v>
+        <v>3025.4</v>
       </c>
       <c r="F22" t="n">
-        <v>55.4</v>
+        <v>-19.3</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0063</v>
       </c>
       <c r="H22" t="n">
-        <v>65.7</v>
+        <v>35</v>
       </c>
       <c r="I22" t="n">
-        <v>2902.2</v>
+        <v>2920.4</v>
       </c>
       <c r="J22" t="n">
-        <v>2952</v>
+        <v>2991.87</v>
       </c>
       <c r="K22" t="n">
-        <v>2966.2</v>
+        <v>3011.85</v>
       </c>
       <c r="L22" t="n">
-        <v>2980.4</v>
+        <v>3031.83</v>
       </c>
       <c r="M22" t="n">
-        <v>3012.4</v>
+        <v>3077.55</v>
       </c>
       <c r="N22" t="n">
-        <v>3044.4</v>
+        <v>3123.27</v>
       </c>
       <c r="O22" t="n">
-        <v>3040.8</v>
+        <v>3117.5</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2380,80 +2378,78 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3049.1</v>
+        <v>3028.5</v>
       </c>
       <c r="C23" t="n">
-        <v>3058.3</v>
+        <v>3041</v>
       </c>
       <c r="D23" t="n">
-        <v>3023.3</v>
+        <v>3004.9</v>
       </c>
       <c r="E23" t="n">
-        <v>3025.4</v>
+        <v>3009.1</v>
       </c>
       <c r="F23" t="n">
-        <v>-19.3</v>
+        <v>-16.3</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0054</v>
       </c>
       <c r="H23" t="n">
-        <v>35</v>
+        <v>36.1</v>
       </c>
       <c r="I23" t="n">
-        <v>2920.4</v>
+        <v>2988.3</v>
       </c>
       <c r="J23" t="n">
-        <v>2991.87</v>
+        <v>2982.7</v>
       </c>
       <c r="K23" t="n">
-        <v>3011.85</v>
+        <v>3007.9</v>
       </c>
       <c r="L23" t="n">
-        <v>3031.83</v>
+        <v>3033.1</v>
       </c>
       <c r="M23" t="n">
-        <v>3077.55</v>
+        <v>3042.9</v>
       </c>
       <c r="N23" t="n">
-        <v>3123.27</v>
+        <v>3052.7</v>
       </c>
       <c r="O23" t="n">
-        <v>3117.5</v>
+        <v>3093.3</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2461,12 +2457,14 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2485,57 +2483,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3028.5</v>
+        <v>3008.5</v>
       </c>
       <c r="C24" t="n">
-        <v>3041</v>
+        <v>3046.8</v>
       </c>
       <c r="D24" t="n">
-        <v>3004.9</v>
+        <v>3002</v>
       </c>
       <c r="E24" t="n">
-        <v>3009.1</v>
+        <v>3041.6</v>
       </c>
       <c r="F24" t="n">
-        <v>-16.3</v>
+        <v>32.5</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0054</v>
+        <v>0.0108</v>
       </c>
       <c r="H24" t="n">
-        <v>36.1</v>
+        <v>44.8</v>
       </c>
       <c r="I24" t="n">
-        <v>2988.3</v>
+        <v>2968.8</v>
       </c>
       <c r="J24" t="n">
-        <v>2982.7</v>
+        <v>2966.08</v>
       </c>
       <c r="K24" t="n">
-        <v>3007.9</v>
+        <v>2991.05</v>
       </c>
       <c r="L24" t="n">
-        <v>3033.1</v>
+        <v>3016.03</v>
       </c>
       <c r="M24" t="n">
-        <v>3042.9</v>
+        <v>3027.15</v>
       </c>
       <c r="N24" t="n">
-        <v>3052.7</v>
+        <v>3038.28</v>
       </c>
       <c r="O24" t="n">
-        <v>3093.3</v>
+        <v>3077.1</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2543,22 +2541,24 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
@@ -2569,57 +2569,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3008.5</v>
+        <v>3038.9</v>
       </c>
       <c r="C25" t="n">
-        <v>3046.8</v>
+        <v>3044.6</v>
       </c>
       <c r="D25" t="n">
-        <v>3002</v>
+        <v>3016</v>
       </c>
       <c r="E25" t="n">
-        <v>3041.6</v>
+        <v>3025</v>
       </c>
       <c r="F25" t="n">
-        <v>32.5</v>
+        <v>-16.6</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0108</v>
+        <v>-0.0055</v>
       </c>
       <c r="H25" t="n">
-        <v>44.8</v>
+        <v>28.6</v>
       </c>
       <c r="I25" t="n">
-        <v>2968.8</v>
+        <v>2957.2</v>
       </c>
       <c r="J25" t="n">
-        <v>2966.08</v>
+        <v>3005.4</v>
       </c>
       <c r="K25" t="n">
-        <v>2991.05</v>
+        <v>3019.2</v>
       </c>
       <c r="L25" t="n">
-        <v>3016.03</v>
+        <v>3033</v>
       </c>
       <c r="M25" t="n">
-        <v>3027.15</v>
+        <v>3064</v>
       </c>
       <c r="N25" t="n">
-        <v>3038.28</v>
+        <v>3095</v>
       </c>
       <c r="O25" t="n">
-        <v>3077.1</v>
+        <v>3091.6</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2627,24 +2627,22 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
@@ -2655,57 +2653,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3038.9</v>
+        <v>3024.7</v>
       </c>
       <c r="C26" t="n">
-        <v>3044.6</v>
+        <v>3045.8</v>
       </c>
       <c r="D26" t="n">
-        <v>3016</v>
+        <v>3019.9</v>
       </c>
       <c r="E26" t="n">
-        <v>3025</v>
+        <v>3035.5</v>
       </c>
       <c r="F26" t="n">
-        <v>-16.6</v>
+        <v>10.5</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0035</v>
       </c>
       <c r="H26" t="n">
-        <v>28.6</v>
+        <v>25.9</v>
       </c>
       <c r="I26" t="n">
-        <v>2957.2</v>
+        <v>2987.4</v>
       </c>
       <c r="J26" t="n">
-        <v>3005.4</v>
+        <v>2993.75</v>
       </c>
       <c r="K26" t="n">
-        <v>3019.2</v>
+        <v>3010.7</v>
       </c>
       <c r="L26" t="n">
-        <v>3033</v>
+        <v>3027.65</v>
       </c>
       <c r="M26" t="n">
-        <v>3064</v>
+        <v>3039.3</v>
       </c>
       <c r="N26" t="n">
-        <v>3095</v>
+        <v>3050.95</v>
       </c>
       <c r="O26" t="n">
-        <v>3091.6</v>
+        <v>3073.2</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2713,19 +2711,19 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
       <c r="U26" s="8" t="n">
         <v/>
       </c>
@@ -2737,59 +2735,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3024.7</v>
+        <v>3036.1</v>
       </c>
       <c r="C27" t="n">
-        <v>3045.8</v>
+        <v>3060</v>
       </c>
       <c r="D27" t="n">
-        <v>3019.9</v>
+        <v>3033.1</v>
       </c>
       <c r="E27" t="n">
-        <v>3035.5</v>
+        <v>3052.8</v>
       </c>
       <c r="F27" t="n">
-        <v>10.5</v>
+        <v>17.3</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0057</v>
       </c>
       <c r="H27" t="n">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
       <c r="I27" t="n">
-        <v>2987.4</v>
+        <v>2994</v>
       </c>
       <c r="J27" t="n">
-        <v>2993.75</v>
+        <v>3010.92</v>
       </c>
       <c r="K27" t="n">
-        <v>3010.7</v>
+        <v>3022.55</v>
       </c>
       <c r="L27" t="n">
-        <v>3027.65</v>
+        <v>3034.17</v>
       </c>
       <c r="M27" t="n">
-        <v>3039.3</v>
+        <v>3048.45</v>
       </c>
       <c r="N27" t="n">
-        <v>3050.95</v>
+        <v>3062.73</v>
       </c>
       <c r="O27" t="n">
-        <v>3073.2</v>
+        <v>3071.7</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2826,50 +2820,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3036.1</v>
+        <v>3056.2</v>
       </c>
       <c r="C28" t="n">
-        <v>3060</v>
+        <v>3076.3</v>
       </c>
       <c r="D28" t="n">
-        <v>3033.1</v>
+        <v>3052.5</v>
       </c>
       <c r="E28" t="n">
-        <v>3052.8</v>
+        <v>3060.2</v>
       </c>
       <c r="F28" t="n">
-        <v>17.3</v>
+        <v>7.4</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0024</v>
       </c>
       <c r="H28" t="n">
-        <v>26.9</v>
+        <v>23.8</v>
       </c>
       <c r="I28" t="n">
-        <v>2994</v>
+        <v>3006.2</v>
       </c>
       <c r="J28" t="n">
-        <v>3010.92</v>
+        <v>3029.03</v>
       </c>
       <c r="K28" t="n">
-        <v>3022.55</v>
+        <v>3039.35</v>
       </c>
       <c r="L28" t="n">
-        <v>3034.17</v>
+        <v>3049.68</v>
       </c>
       <c r="M28" t="n">
-        <v>3048.45</v>
+        <v>3066.25</v>
       </c>
       <c r="N28" t="n">
-        <v>3062.73</v>
+        <v>3082.82</v>
       </c>
       <c r="O28" t="n">
-        <v>3071.7</v>
+        <v>3086.9</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2906,50 +2900,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3056.2</v>
+        <v>3062.2</v>
       </c>
       <c r="C29" t="n">
         <v>3076.3</v>
       </c>
       <c r="D29" t="n">
-        <v>3052.5</v>
+        <v>3051.7</v>
       </c>
       <c r="E29" t="n">
-        <v>3060.2</v>
+        <v>3074.9</v>
       </c>
       <c r="F29" t="n">
-        <v>7.4</v>
+        <v>14.7</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0048</v>
       </c>
       <c r="H29" t="n">
-        <v>23.8</v>
+        <v>24.6</v>
       </c>
       <c r="I29" t="n">
-        <v>3006.2</v>
+        <v>3028.7</v>
       </c>
       <c r="J29" t="n">
-        <v>3029.03</v>
+        <v>3034.3</v>
       </c>
       <c r="K29" t="n">
-        <v>3039.35</v>
+        <v>3048.3</v>
       </c>
       <c r="L29" t="n">
-        <v>3049.68</v>
+        <v>3062.3</v>
       </c>
       <c r="M29" t="n">
-        <v>3066.25</v>
+        <v>3072.1</v>
       </c>
       <c r="N29" t="n">
-        <v>3082.82</v>
+        <v>3081.9</v>
       </c>
       <c r="O29" t="n">
-        <v>3086.9</v>
+        <v>3100.1</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2981,55 +2975,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3062.2</v>
+        <v>3073.5</v>
       </c>
       <c r="C30" t="n">
-        <v>3076.3</v>
+        <v>3079.9</v>
       </c>
       <c r="D30" t="n">
-        <v>3051.7</v>
+        <v>3055.9</v>
       </c>
       <c r="E30" t="n">
-        <v>3074.9</v>
+        <v>3064.9</v>
       </c>
       <c r="F30" t="n">
-        <v>14.7</v>
+        <v>-10</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.0033</v>
       </c>
       <c r="H30" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="I30" t="n">
-        <v>3028.7</v>
+        <v>3027.1</v>
       </c>
       <c r="J30" t="n">
-        <v>3034.3</v>
+        <v>3055.75</v>
       </c>
       <c r="K30" t="n">
-        <v>3048.3</v>
+        <v>3062.6</v>
       </c>
       <c r="L30" t="n">
-        <v>3062.3</v>
+        <v>3069.45</v>
       </c>
       <c r="M30" t="n">
-        <v>3072.1</v>
+        <v>3087.2</v>
       </c>
       <c r="N30" t="n">
-        <v>3081.9</v>
+        <v>3104.95</v>
       </c>
       <c r="O30" t="n">
-        <v>3100.1</v>
+        <v>3100.9</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3037,18 +3035,18 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3070,60 +3068,64 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3073.5</v>
+        <v>3063.7</v>
       </c>
       <c r="C31" t="n">
-        <v>3079.9</v>
+        <v>3066.6</v>
       </c>
       <c r="D31" t="n">
-        <v>3055.9</v>
+        <v>3024.1</v>
       </c>
       <c r="E31" t="n">
-        <v>3064.9</v>
+        <v>3026.4</v>
       </c>
       <c r="F31" t="n">
-        <v>-10</v>
+        <v>-38.5</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0126</v>
       </c>
       <c r="H31" t="n">
-        <v>24</v>
+        <v>42.5</v>
       </c>
       <c r="I31" t="n">
-        <v>3027.1</v>
+        <v>3031.9</v>
       </c>
       <c r="J31" t="n">
-        <v>3055.75</v>
+        <v>3039.4</v>
       </c>
       <c r="K31" t="n">
-        <v>3062.6</v>
+        <v>3052.9</v>
       </c>
       <c r="L31" t="n">
-        <v>3069.45</v>
+        <v>3066.4</v>
       </c>
       <c r="M31" t="n">
-        <v>3087.2</v>
+        <v>3076.9</v>
       </c>
       <c r="N31" t="n">
-        <v>3104.95</v>
+        <v>3087.4</v>
       </c>
       <c r="O31" t="n">
-        <v>3100.9</v>
-      </c>
-      <c r="P31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
+        <v>3103.9</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S31" s="7" t="inlineStr">
@@ -3140,88 +3142,80 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W31" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3063.7</v>
+        <v>3025.9</v>
       </c>
       <c r="C32" t="n">
-        <v>3066.6</v>
+        <v>3059.1</v>
       </c>
       <c r="D32" t="n">
-        <v>3024.1</v>
+        <v>3019.8</v>
       </c>
       <c r="E32" t="n">
-        <v>3026.4</v>
+        <v>3039.9</v>
       </c>
       <c r="F32" t="n">
-        <v>-38.5</v>
+        <v>13.5</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0045</v>
       </c>
       <c r="H32" t="n">
-        <v>42.5</v>
+        <v>39.3</v>
       </c>
       <c r="I32" t="n">
-        <v>3031.9</v>
+        <v>2981.6</v>
       </c>
       <c r="J32" t="n">
-        <v>3039.4</v>
+        <v>2974.42</v>
       </c>
       <c r="K32" t="n">
-        <v>3052.9</v>
+        <v>3005.15</v>
       </c>
       <c r="L32" t="n">
-        <v>3066.4</v>
+        <v>3035.88</v>
       </c>
       <c r="M32" t="n">
-        <v>3076.9</v>
+        <v>3047.65</v>
       </c>
       <c r="N32" t="n">
-        <v>3087.4</v>
+        <v>3059.42</v>
       </c>
       <c r="O32" t="n">
-        <v>3103.9</v>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q32" s="6" t="inlineStr">
+        <v>3109.1</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
@@ -3233,75 +3227,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3025.9</v>
+        <v>3041.4</v>
       </c>
       <c r="C33" t="n">
-        <v>3059.1</v>
+        <v>3048.5</v>
       </c>
       <c r="D33" t="n">
-        <v>3019.8</v>
+        <v>2993.2</v>
       </c>
       <c r="E33" t="n">
-        <v>3039.9</v>
+        <v>2999.2</v>
       </c>
       <c r="F33" t="n">
-        <v>13.5</v>
+        <v>-40.7</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0134</v>
       </c>
       <c r="H33" t="n">
-        <v>39.3</v>
+        <v>55.3</v>
       </c>
       <c r="I33" t="n">
-        <v>2981.6</v>
+        <v>2980.5</v>
       </c>
       <c r="J33" t="n">
-        <v>2974.42</v>
+        <v>3000.82</v>
       </c>
       <c r="K33" t="n">
-        <v>3005.15</v>
+        <v>3020.25</v>
       </c>
       <c r="L33" t="n">
-        <v>3035.88</v>
+        <v>3039.67</v>
       </c>
       <c r="M33" t="n">
-        <v>3047.65</v>
+        <v>3059.55</v>
       </c>
       <c r="N33" t="n">
-        <v>3059.42</v>
+        <v>3079.42</v>
       </c>
       <c r="O33" t="n">
-        <v>3109.1</v>
+        <v>3098.4</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3313,81 +3313,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3041.4</v>
+        <v>2999.6</v>
       </c>
       <c r="C34" t="n">
-        <v>3048.5</v>
+        <v>3026.7</v>
       </c>
       <c r="D34" t="n">
-        <v>2993.2</v>
+        <v>2997.9</v>
       </c>
       <c r="E34" t="n">
-        <v>2999.2</v>
+        <v>3022.1</v>
       </c>
       <c r="F34" t="n">
-        <v>-40.7</v>
+        <v>22.9</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0134</v>
+        <v>0.0076</v>
       </c>
       <c r="H34" t="n">
-        <v>55.3</v>
+        <v>28.8</v>
       </c>
       <c r="I34" t="n">
-        <v>2980.5</v>
+        <v>2937.9</v>
       </c>
       <c r="J34" t="n">
-        <v>3000.82</v>
+        <v>2933.07</v>
       </c>
       <c r="K34" t="n">
-        <v>3020.25</v>
+        <v>2971.55</v>
       </c>
       <c r="L34" t="n">
-        <v>3039.67</v>
+        <v>3010.02</v>
       </c>
       <c r="M34" t="n">
-        <v>3059.55</v>
+        <v>3026.85</v>
       </c>
       <c r="N34" t="n">
-        <v>3079.42</v>
+        <v>3043.67</v>
       </c>
       <c r="O34" t="n">
-        <v>3098.4</v>
+        <v>3103.8</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
@@ -3399,75 +3393,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2999.6</v>
+        <v>3023</v>
       </c>
       <c r="C35" t="n">
-        <v>3026.7</v>
+        <v>3028.9</v>
       </c>
       <c r="D35" t="n">
-        <v>2997.9</v>
+        <v>2996</v>
       </c>
       <c r="E35" t="n">
-        <v>3022.1</v>
+        <v>3001.6</v>
       </c>
       <c r="F35" t="n">
-        <v>22.9</v>
+        <v>-20.5</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0076</v>
+        <v>-0.0068</v>
       </c>
       <c r="H35" t="n">
-        <v>28.8</v>
+        <v>32.9</v>
       </c>
       <c r="I35" t="n">
-        <v>2937.9</v>
+        <v>2969.1</v>
       </c>
       <c r="J35" t="n">
-        <v>2933.07</v>
+        <v>2998.2</v>
       </c>
       <c r="K35" t="n">
-        <v>2971.55</v>
+        <v>3007.7</v>
       </c>
       <c r="L35" t="n">
-        <v>3010.02</v>
+        <v>3017.2</v>
       </c>
       <c r="M35" t="n">
-        <v>3026.85</v>
+        <v>3036.5</v>
       </c>
       <c r="N35" t="n">
-        <v>3043.67</v>
+        <v>3055.8</v>
       </c>
       <c r="O35" t="n">
-        <v>3103.8</v>
+        <v>3055.5</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
+      <c r="Q35" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
@@ -3481,79 +3481,77 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3023</v>
+        <v>3004.6</v>
       </c>
       <c r="C36" t="n">
-        <v>3028.9</v>
+        <v>3025.4</v>
       </c>
       <c r="D36" t="n">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="E36" t="n">
-        <v>3001.6</v>
+        <v>3014.4</v>
       </c>
       <c r="F36" t="n">
-        <v>-20.5</v>
+        <v>12.8</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0043</v>
       </c>
       <c r="H36" t="n">
-        <v>32.9</v>
+        <v>28.4</v>
       </c>
       <c r="I36" t="n">
-        <v>2969.1</v>
+        <v>2963.1</v>
       </c>
       <c r="J36" t="n">
-        <v>2998.2</v>
+        <v>2963.28</v>
       </c>
       <c r="K36" t="n">
-        <v>3007.7</v>
+        <v>2985.15</v>
       </c>
       <c r="L36" t="n">
-        <v>3017.2</v>
+        <v>3007.03</v>
       </c>
       <c r="M36" t="n">
-        <v>3036.5</v>
+        <v>3018.05</v>
       </c>
       <c r="N36" t="n">
-        <v>3055.8</v>
+        <v>3029.08</v>
       </c>
       <c r="O36" t="n">
-        <v>3055.5</v>
+        <v>3061.8</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3567,57 +3565,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3004.6</v>
+        <v>3014.6</v>
       </c>
       <c r="C37" t="n">
-        <v>3025.4</v>
+        <v>3020.5</v>
       </c>
       <c r="D37" t="n">
-        <v>2997</v>
+        <v>3002.6</v>
       </c>
       <c r="E37" t="n">
-        <v>3014.4</v>
+        <v>3010.1</v>
       </c>
       <c r="F37" t="n">
-        <v>12.8</v>
+        <v>-4.3</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0014</v>
       </c>
       <c r="H37" t="n">
-        <v>28.4</v>
+        <v>17.9</v>
       </c>
       <c r="I37" t="n">
-        <v>2963.1</v>
+        <v>2968.6</v>
       </c>
       <c r="J37" t="n">
-        <v>2963.28</v>
+        <v>2987.6</v>
       </c>
       <c r="K37" t="n">
-        <v>2985.15</v>
+        <v>3000.2</v>
       </c>
       <c r="L37" t="n">
-        <v>3007.03</v>
+        <v>3012.8</v>
       </c>
       <c r="M37" t="n">
-        <v>3018.05</v>
+        <v>3028.6</v>
       </c>
       <c r="N37" t="n">
-        <v>3029.08</v>
+        <v>3044.4</v>
       </c>
       <c r="O37" t="n">
-        <v>3061.8</v>
+        <v>3053.8</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3628,15 +3626,13 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3651,57 +3647,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3014.6</v>
+        <v>3016.9</v>
       </c>
       <c r="C38" t="n">
-        <v>3020.5</v>
+        <v>3024.2</v>
       </c>
       <c r="D38" t="n">
-        <v>3002.6</v>
+        <v>3002.1</v>
       </c>
       <c r="E38" t="n">
-        <v>3010.1</v>
+        <v>3019</v>
       </c>
       <c r="F38" t="n">
-        <v>-4.3</v>
+        <v>8.9</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0014</v>
+        <v>0.003</v>
       </c>
       <c r="H38" t="n">
-        <v>17.9</v>
+        <v>22.1</v>
       </c>
       <c r="I38" t="n">
-        <v>2968.6</v>
+        <v>2984.7</v>
       </c>
       <c r="J38" t="n">
-        <v>2987.6</v>
+        <v>2991.48</v>
       </c>
       <c r="K38" t="n">
-        <v>3000.2</v>
+        <v>3001.15</v>
       </c>
       <c r="L38" t="n">
-        <v>3012.8</v>
+        <v>3010.83</v>
       </c>
       <c r="M38" t="n">
-        <v>3028.6</v>
+        <v>3019.05</v>
       </c>
       <c r="N38" t="n">
-        <v>3044.4</v>
+        <v>3027.28</v>
       </c>
       <c r="O38" t="n">
-        <v>3053.8</v>
+        <v>3038.4</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3712,13 +3708,15 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3733,77 +3731,81 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3016.9</v>
+        <v>3019.6</v>
       </c>
       <c r="C39" t="n">
-        <v>3024.2</v>
+        <v>3025.5</v>
       </c>
       <c r="D39" t="n">
-        <v>3002.1</v>
+        <v>2976.6</v>
       </c>
       <c r="E39" t="n">
-        <v>3019</v>
+        <v>2977.5</v>
       </c>
       <c r="F39" t="n">
-        <v>8.9</v>
+        <v>-41.5</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0137</v>
       </c>
       <c r="H39" t="n">
-        <v>22.1</v>
+        <v>48.9</v>
       </c>
       <c r="I39" t="n">
-        <v>2984.7</v>
+        <v>2980</v>
       </c>
       <c r="J39" t="n">
-        <v>2991.48</v>
+        <v>2999.83</v>
       </c>
       <c r="K39" t="n">
-        <v>3001.15</v>
+        <v>3007.95</v>
       </c>
       <c r="L39" t="n">
-        <v>3010.83</v>
+        <v>3016.08</v>
       </c>
       <c r="M39" t="n">
-        <v>3019.05</v>
+        <v>3030.05</v>
       </c>
       <c r="N39" t="n">
-        <v>3027.28</v>
+        <v>3044.02</v>
       </c>
       <c r="O39" t="n">
-        <v>3038.4</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
+        <v>3046.3</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3817,73 +3819,69 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3019.6</v>
+        <v>2971</v>
       </c>
       <c r="C40" t="n">
-        <v>3025.5</v>
+        <v>2982.5</v>
       </c>
       <c r="D40" t="n">
-        <v>2976.6</v>
+        <v>2946.1</v>
       </c>
       <c r="E40" t="n">
-        <v>2977.5</v>
+        <v>2958.7</v>
       </c>
       <c r="F40" t="n">
-        <v>-41.5</v>
+        <v>-18.8</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0063</v>
       </c>
       <c r="H40" t="n">
-        <v>48.9</v>
+        <v>36.4</v>
       </c>
       <c r="I40" t="n">
-        <v>2980</v>
+        <v>2927.7</v>
       </c>
       <c r="J40" t="n">
-        <v>2999.83</v>
+        <v>2916.83</v>
       </c>
       <c r="K40" t="n">
-        <v>3007.95</v>
+        <v>2953.05</v>
       </c>
       <c r="L40" t="n">
-        <v>3016.08</v>
+        <v>2989.28</v>
       </c>
       <c r="M40" t="n">
-        <v>3030.05</v>
+        <v>3001.95</v>
       </c>
       <c r="N40" t="n">
-        <v>3044.02</v>
+        <v>3014.62</v>
       </c>
       <c r="O40" t="n">
-        <v>3046.3</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
+        <v>3074.4</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -3903,69 +3901,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2971</v>
+        <v>2958</v>
       </c>
       <c r="C41" t="n">
-        <v>2982.5</v>
+        <v>2964.6</v>
       </c>
       <c r="D41" t="n">
-        <v>2946.1</v>
+        <v>2918.9</v>
       </c>
       <c r="E41" t="n">
-        <v>2958.7</v>
+        <v>2924.7</v>
       </c>
       <c r="F41" t="n">
-        <v>-18.8</v>
+        <v>-34</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0115</v>
       </c>
       <c r="H41" t="n">
-        <v>36.4</v>
+        <v>45.7</v>
       </c>
       <c r="I41" t="n">
-        <v>2927.7</v>
+        <v>2909.7</v>
       </c>
       <c r="J41" t="n">
-        <v>2916.83</v>
+        <v>2919.5</v>
       </c>
       <c r="K41" t="n">
-        <v>2953.05</v>
+        <v>2940.5</v>
       </c>
       <c r="L41" t="n">
-        <v>2989.28</v>
+        <v>2961.5</v>
       </c>
       <c r="M41" t="n">
-        <v>3001.95</v>
+        <v>2976.9</v>
       </c>
       <c r="N41" t="n">
-        <v>3014.62</v>
+        <v>2992.3</v>
       </c>
       <c r="O41" t="n">
-        <v>3074.4</v>
+        <v>3018.9</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S41" s="7" t="inlineStr">
@@ -3992,75 +3988,75 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2958</v>
+        <v>2926.4</v>
       </c>
       <c r="C42" t="n">
-        <v>2964.6</v>
+        <v>2962.5</v>
       </c>
       <c r="D42" t="n">
-        <v>2918.9</v>
+        <v>2914.5</v>
       </c>
       <c r="E42" t="n">
-        <v>2924.7</v>
+        <v>2958.8</v>
       </c>
       <c r="F42" t="n">
-        <v>-34</v>
+        <v>34.1</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0.0117</v>
       </c>
       <c r="H42" t="n">
-        <v>45.7</v>
+        <v>48</v>
       </c>
       <c r="I42" t="n">
-        <v>2909.7</v>
+        <v>2873.2</v>
       </c>
       <c r="J42" t="n">
-        <v>2919.5</v>
+        <v>2870.47</v>
       </c>
       <c r="K42" t="n">
-        <v>2940.5</v>
+        <v>2901.85</v>
       </c>
       <c r="L42" t="n">
-        <v>2961.5</v>
+        <v>2933.22</v>
       </c>
       <c r="M42" t="n">
-        <v>2976.9</v>
+        <v>2947.55</v>
       </c>
       <c r="N42" t="n">
-        <v>2992.3</v>
+        <v>2961.88</v>
       </c>
       <c r="O42" t="n">
-        <v>3018.9</v>
+        <v>3010.3</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
@@ -4069,55 +4065,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2926.4</v>
+        <v>2957.6</v>
       </c>
       <c r="C43" t="n">
-        <v>2962.5</v>
+        <v>2983.3</v>
       </c>
       <c r="D43" t="n">
-        <v>2914.5</v>
+        <v>2949.9</v>
       </c>
       <c r="E43" t="n">
-        <v>2958.8</v>
+        <v>2969.7</v>
       </c>
       <c r="F43" t="n">
-        <v>34.1</v>
+        <v>10.9</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0117</v>
+        <v>0.0037</v>
       </c>
       <c r="H43" t="n">
-        <v>48</v>
+        <v>33.4</v>
       </c>
       <c r="I43" t="n">
-        <v>2873.2</v>
+        <v>2866.5</v>
       </c>
       <c r="J43" t="n">
-        <v>2870.47</v>
+        <v>2920.95</v>
       </c>
       <c r="K43" t="n">
-        <v>2901.85</v>
+        <v>2934.8</v>
       </c>
       <c r="L43" t="n">
-        <v>2933.22</v>
+        <v>2948.65</v>
       </c>
       <c r="M43" t="n">
-        <v>2947.55</v>
+        <v>2982.8</v>
       </c>
       <c r="N43" t="n">
-        <v>2961.88</v>
+        <v>3016.95</v>
       </c>
       <c r="O43" t="n">
-        <v>3010.3</v>
+        <v>3010.5</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4135,14 +4135,12 @@
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
@@ -4153,57 +4151,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2957.6</v>
+        <v>2967.9</v>
       </c>
       <c r="C44" t="n">
-        <v>2983.3</v>
+        <v>2979.3</v>
       </c>
       <c r="D44" t="n">
-        <v>2949.9</v>
+        <v>2949.5</v>
       </c>
       <c r="E44" t="n">
-        <v>2969.7</v>
+        <v>2976.6</v>
       </c>
       <c r="F44" t="n">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0023</v>
       </c>
       <c r="H44" t="n">
-        <v>33.4</v>
+        <v>29.8</v>
       </c>
       <c r="I44" t="n">
-        <v>2866.5</v>
+        <v>2916.5</v>
       </c>
       <c r="J44" t="n">
-        <v>2920.95</v>
+        <v>2937.85</v>
       </c>
       <c r="K44" t="n">
-        <v>2934.8</v>
+        <v>2953</v>
       </c>
       <c r="L44" t="n">
-        <v>2948.65</v>
+        <v>2968.15</v>
       </c>
       <c r="M44" t="n">
-        <v>2982.8</v>
+        <v>2986.4</v>
       </c>
       <c r="N44" t="n">
-        <v>3016.95</v>
+        <v>3004.65</v>
       </c>
       <c r="O44" t="n">
-        <v>3010.5</v>
+        <v>3016.7</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4211,18 +4209,18 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4237,57 +4235,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2967.9</v>
+        <v>2974.7</v>
       </c>
       <c r="C45" t="n">
-        <v>2979.3</v>
+        <v>2977.9</v>
       </c>
       <c r="D45" t="n">
-        <v>2949.5</v>
+        <v>2954.7</v>
       </c>
       <c r="E45" t="n">
-        <v>2976.6</v>
+        <v>2963.6</v>
       </c>
       <c r="F45" t="n">
-        <v>6.9</v>
+        <v>-13</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0044</v>
       </c>
       <c r="H45" t="n">
-        <v>29.8</v>
+        <v>23.2</v>
       </c>
       <c r="I45" t="n">
-        <v>2916.5</v>
+        <v>2919.7</v>
       </c>
       <c r="J45" t="n">
-        <v>2937.85</v>
+        <v>2952.9</v>
       </c>
       <c r="K45" t="n">
-        <v>2953</v>
+        <v>2961.7</v>
       </c>
       <c r="L45" t="n">
-        <v>2968.15</v>
+        <v>2970.5</v>
       </c>
       <c r="M45" t="n">
-        <v>2986.4</v>
+        <v>2991.5</v>
       </c>
       <c r="N45" t="n">
-        <v>3004.65</v>
+        <v>3012.5</v>
       </c>
       <c r="O45" t="n">
-        <v>3016.7</v>
+        <v>3009.1</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4297,12 +4295,12 @@
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4328,60 +4326,64 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2974.7</v>
+        <v>2963.1</v>
       </c>
       <c r="C46" t="n">
-        <v>2977.9</v>
+        <v>2966.2</v>
       </c>
       <c r="D46" t="n">
-        <v>2954.7</v>
+        <v>2919.4</v>
       </c>
       <c r="E46" t="n">
-        <v>2963.6</v>
+        <v>2923</v>
       </c>
       <c r="F46" t="n">
-        <v>-13</v>
+        <v>-40.6</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0137</v>
       </c>
       <c r="H46" t="n">
-        <v>23.2</v>
+        <v>46.8</v>
       </c>
       <c r="I46" t="n">
-        <v>2919.7</v>
+        <v>2931.5</v>
       </c>
       <c r="J46" t="n">
-        <v>2952.9</v>
+        <v>2939.05</v>
       </c>
       <c r="K46" t="n">
-        <v>2961.7</v>
+        <v>2952</v>
       </c>
       <c r="L46" t="n">
-        <v>2970.5</v>
+        <v>2964.95</v>
       </c>
       <c r="M46" t="n">
-        <v>2991.5</v>
+        <v>2975.2</v>
       </c>
       <c r="N46" t="n">
-        <v>3012.5</v>
+        <v>2985.45</v>
       </c>
       <c r="O46" t="n">
-        <v>3009.1</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
+        <v>3001.1</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
@@ -4403,73 +4405,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2963.1</v>
+        <v>2923.1</v>
       </c>
       <c r="C47" t="n">
-        <v>2966.2</v>
+        <v>2933.8</v>
       </c>
       <c r="D47" t="n">
-        <v>2919.4</v>
+        <v>2887.8</v>
       </c>
       <c r="E47" t="n">
-        <v>2923</v>
+        <v>2893.4</v>
       </c>
       <c r="F47" t="n">
-        <v>-40.6</v>
+        <v>-29.6</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0101</v>
       </c>
       <c r="H47" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="I47" t="n">
-        <v>2931.5</v>
+        <v>2872.6</v>
       </c>
       <c r="J47" t="n">
-        <v>2939.05</v>
+        <v>2866.3</v>
       </c>
       <c r="K47" t="n">
-        <v>2952</v>
+        <v>2899.6</v>
       </c>
       <c r="L47" t="n">
-        <v>2964.95</v>
+        <v>2932.9</v>
       </c>
       <c r="M47" t="n">
-        <v>2975.2</v>
+        <v>2946.4</v>
       </c>
       <c r="N47" t="n">
-        <v>2985.45</v>
+        <v>2959.9</v>
       </c>
       <c r="O47" t="n">
-        <v>3001.1</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
+        <v>3013</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S47" s="7" t="inlineStr">
@@ -4496,50 +4490,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2923.1</v>
+        <v>2890.9</v>
       </c>
       <c r="C48" t="n">
-        <v>2933.8</v>
+        <v>2929.8</v>
       </c>
       <c r="D48" t="n">
-        <v>2887.8</v>
+        <v>2887.6</v>
       </c>
       <c r="E48" t="n">
-        <v>2893.4</v>
+        <v>2904.5</v>
       </c>
       <c r="F48" t="n">
-        <v>-29.6</v>
+        <v>11.1</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0101</v>
+        <v>0.0038</v>
       </c>
       <c r="H48" t="n">
-        <v>46</v>
+        <v>42.2</v>
       </c>
       <c r="I48" t="n">
-        <v>2872.6</v>
+        <v>2841.8</v>
       </c>
       <c r="J48" t="n">
-        <v>2866.3</v>
+        <v>2838.7</v>
       </c>
       <c r="K48" t="n">
-        <v>2899.6</v>
+        <v>2870.4</v>
       </c>
       <c r="L48" t="n">
-        <v>2932.9</v>
+        <v>2902.1</v>
       </c>
       <c r="M48" t="n">
-        <v>2946.4</v>
+        <v>2916.4</v>
       </c>
       <c r="N48" t="n">
-        <v>2959.9</v>
+        <v>2930.7</v>
       </c>
       <c r="O48" t="n">
-        <v>3013</v>
+        <v>2979.8</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4547,18 +4541,18 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4571,55 +4565,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2890.9</v>
+        <v>2892.7</v>
       </c>
       <c r="C49" t="n">
-        <v>2929.8</v>
+        <v>2913.5</v>
       </c>
       <c r="D49" t="n">
-        <v>2887.6</v>
+        <v>2884.3</v>
       </c>
       <c r="E49" t="n">
-        <v>2904.5</v>
+        <v>2894.1</v>
       </c>
       <c r="F49" t="n">
-        <v>11.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0036</v>
       </c>
       <c r="H49" t="n">
-        <v>42.2</v>
+        <v>29.2</v>
       </c>
       <c r="I49" t="n">
-        <v>2841.8</v>
+        <v>2845.4</v>
       </c>
       <c r="J49" t="n">
-        <v>2838.7</v>
+        <v>2860.2</v>
       </c>
       <c r="K49" t="n">
-        <v>2870.4</v>
+        <v>2883.4</v>
       </c>
       <c r="L49" t="n">
-        <v>2902.1</v>
+        <v>2906.6</v>
       </c>
       <c r="M49" t="n">
-        <v>2916.4</v>
+        <v>2925.6</v>
       </c>
       <c r="N49" t="n">
-        <v>2930.7</v>
+        <v>2944.6</v>
       </c>
       <c r="O49" t="n">
-        <v>2979.8</v>
+        <v>2972</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4627,18 +4625,18 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4651,59 +4649,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2892.7</v>
+        <v>2896.4</v>
       </c>
       <c r="C50" t="n">
-        <v>2913.5</v>
+        <v>2896.5</v>
       </c>
       <c r="D50" t="n">
-        <v>2884.3</v>
+        <v>2862.7</v>
       </c>
       <c r="E50" t="n">
-        <v>2894.1</v>
+        <v>2873.1</v>
       </c>
       <c r="F50" t="n">
-        <v>-10.4</v>
+        <v>-21</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0073</v>
       </c>
       <c r="H50" t="n">
-        <v>29.2</v>
+        <v>33.8</v>
       </c>
       <c r="I50" t="n">
-        <v>2845.4</v>
+        <v>2855.1</v>
       </c>
       <c r="J50" t="n">
-        <v>2860.2</v>
+        <v>2862.5</v>
       </c>
       <c r="K50" t="n">
-        <v>2883.4</v>
+        <v>2879.5</v>
       </c>
       <c r="L50" t="n">
-        <v>2906.6</v>
+        <v>2896.5</v>
       </c>
       <c r="M50" t="n">
-        <v>2925.6</v>
+        <v>2908.7</v>
       </c>
       <c r="N50" t="n">
-        <v>2944.6</v>
+        <v>2920.9</v>
       </c>
       <c r="O50" t="n">
-        <v>2972</v>
+        <v>2942.7</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4740,56 +4734,58 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2896.4</v>
+        <v>2875.1</v>
       </c>
       <c r="C51" t="n">
-        <v>2896.5</v>
+        <v>2892.5</v>
       </c>
       <c r="D51" t="n">
-        <v>2862.7</v>
+        <v>2831.9</v>
       </c>
       <c r="E51" t="n">
-        <v>2873.1</v>
+        <v>2861.7</v>
       </c>
       <c r="F51" t="n">
-        <v>-21</v>
+        <v>-11.4</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.004</v>
       </c>
       <c r="H51" t="n">
-        <v>33.8</v>
+        <v>60.6</v>
       </c>
       <c r="I51" t="n">
-        <v>2855.1</v>
+        <v>2828.9</v>
       </c>
       <c r="J51" t="n">
-        <v>2862.5</v>
+        <v>2836.05</v>
       </c>
       <c r="K51" t="n">
-        <v>2879.5</v>
+        <v>2856.2</v>
       </c>
       <c r="L51" t="n">
-        <v>2896.5</v>
+        <v>2876.35</v>
       </c>
       <c r="M51" t="n">
-        <v>2908.7</v>
+        <v>2890</v>
       </c>
       <c r="N51" t="n">
-        <v>2920.9</v>
+        <v>2903.65</v>
       </c>
       <c r="O51" t="n">
-        <v>2942.7</v>
+        <v>2930.3</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
@@ -4801,8 +4797,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4820,74 +4818,70 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2875.1</v>
+        <v>2861.2</v>
       </c>
       <c r="C52" t="n">
-        <v>2892.5</v>
+        <v>2904.6</v>
       </c>
       <c r="D52" t="n">
-        <v>2831.9</v>
+        <v>2859.3</v>
       </c>
       <c r="E52" t="n">
-        <v>2861.7</v>
+        <v>2875.9</v>
       </c>
       <c r="F52" t="n">
-        <v>-11.4</v>
+        <v>14.2</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.005</v>
       </c>
       <c r="H52" t="n">
-        <v>60.6</v>
+        <v>45.3</v>
       </c>
       <c r="I52" t="n">
-        <v>2828.9</v>
+        <v>2771.3</v>
       </c>
       <c r="J52" t="n">
-        <v>2836.05</v>
+        <v>2800.85</v>
       </c>
       <c r="K52" t="n">
-        <v>2856.2</v>
+        <v>2831.4</v>
       </c>
       <c r="L52" t="n">
-        <v>2876.35</v>
+        <v>2861.95</v>
       </c>
       <c r="M52" t="n">
-        <v>2890</v>
+        <v>2892</v>
       </c>
       <c r="N52" t="n">
-        <v>2903.65</v>
+        <v>2922.05</v>
       </c>
       <c r="O52" t="n">
-        <v>2930.3</v>
+        <v>2953.1</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
@@ -4899,55 +4893,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2861.2</v>
+        <v>2870.5</v>
       </c>
       <c r="C53" t="n">
-        <v>2904.6</v>
+        <v>2883</v>
       </c>
       <c r="D53" t="n">
-        <v>2859.3</v>
+        <v>2856.9</v>
       </c>
       <c r="E53" t="n">
-        <v>2875.9</v>
+        <v>2873.23</v>
       </c>
       <c r="F53" t="n">
-        <v>14.2</v>
+        <v>-2.67</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0009</v>
       </c>
       <c r="H53" t="n">
-        <v>45.3</v>
+        <v>26.1</v>
       </c>
       <c r="I53" t="n">
-        <v>2771.3</v>
+        <v>2814</v>
       </c>
       <c r="J53" t="n">
-        <v>2800.85</v>
+        <v>2827.57</v>
       </c>
       <c r="K53" t="n">
-        <v>2831.4</v>
+        <v>2853.25</v>
       </c>
       <c r="L53" t="n">
-        <v>2861.95</v>
+        <v>2878.92</v>
       </c>
       <c r="M53" t="n">
-        <v>2892</v>
+        <v>2898.55</v>
       </c>
       <c r="N53" t="n">
-        <v>2922.05</v>
+        <v>2918.17</v>
       </c>
       <c r="O53" t="n">
-        <v>2953.1</v>
+        <v>2949.9</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4958,15 +4956,13 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4979,59 +4975,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2870.5</v>
+        <v>2879.5</v>
       </c>
       <c r="C54" t="n">
-        <v>2883</v>
+        <v>2907.3</v>
       </c>
       <c r="D54" t="n">
-        <v>2856.9</v>
+        <v>2876.6</v>
       </c>
       <c r="E54" t="n">
-        <v>2873.23</v>
+        <v>2897.4</v>
       </c>
       <c r="F54" t="n">
-        <v>-2.67</v>
+        <v>24.17</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>26.1</v>
+        <v>30.7</v>
       </c>
       <c r="I54" t="n">
-        <v>2814</v>
+        <v>2830.8</v>
       </c>
       <c r="J54" t="n">
-        <v>2827.57</v>
+        <v>2848.77</v>
       </c>
       <c r="K54" t="n">
-        <v>2853.25</v>
+        <v>2860.18</v>
       </c>
       <c r="L54" t="n">
-        <v>2878.92</v>
+        <v>2871.59</v>
       </c>
       <c r="M54" t="n">
-        <v>2898.55</v>
+        <v>2886.28</v>
       </c>
       <c r="N54" t="n">
-        <v>2918.17</v>
+        <v>2900.97</v>
       </c>
       <c r="O54" t="n">
-        <v>2949.9</v>
+        <v>2909.1</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5042,16 +5034,20 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
@@ -5061,55 +5057,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2879.5</v>
+        <v>2897.8</v>
       </c>
       <c r="C55" t="n">
-        <v>2907.3</v>
+        <v>2931.2</v>
       </c>
       <c r="D55" t="n">
-        <v>2876.6</v>
+        <v>2884.2</v>
       </c>
       <c r="E55" t="n">
-        <v>2897.4</v>
+        <v>2914.1</v>
       </c>
       <c r="F55" t="n">
-        <v>24.17</v>
+        <v>16.7</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0058</v>
       </c>
       <c r="H55" t="n">
-        <v>30.7</v>
+        <v>47</v>
       </c>
       <c r="I55" t="n">
-        <v>2830.8</v>
+        <v>2845.9</v>
       </c>
       <c r="J55" t="n">
-        <v>2848.77</v>
+        <v>2869.42</v>
       </c>
       <c r="K55" t="n">
-        <v>2860.18</v>
+        <v>2882.05</v>
       </c>
       <c r="L55" t="n">
-        <v>2871.59</v>
+        <v>2894.67</v>
       </c>
       <c r="M55" t="n">
-        <v>2886.28</v>
+        <v>2912.75</v>
       </c>
       <c r="N55" t="n">
-        <v>2900.97</v>
+        <v>2930.82</v>
       </c>
       <c r="O55" t="n">
-        <v>2909.1</v>
+        <v>2938</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5127,12 +5127,12 @@
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="V55" s="8" t="n">
@@ -5152,75 +5152,75 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2897.8</v>
+        <v>2912</v>
       </c>
       <c r="C56" t="n">
-        <v>2931.2</v>
+        <v>2915.3</v>
       </c>
       <c r="D56" t="n">
-        <v>2884.2</v>
+        <v>2858.8</v>
       </c>
       <c r="E56" t="n">
-        <v>2914.1</v>
+        <v>2860.2</v>
       </c>
       <c r="F56" t="n">
-        <v>16.7</v>
+        <v>-53.9</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0185</v>
       </c>
       <c r="H56" t="n">
-        <v>47</v>
+        <v>56.5</v>
       </c>
       <c r="I56" t="n">
-        <v>2845.9</v>
+        <v>2837.2</v>
       </c>
       <c r="J56" t="n">
-        <v>2869.42</v>
+        <v>2870.3</v>
       </c>
       <c r="K56" t="n">
-        <v>2882.05</v>
+        <v>2890.6</v>
       </c>
       <c r="L56" t="n">
-        <v>2894.67</v>
+        <v>2910.9</v>
       </c>
       <c r="M56" t="n">
-        <v>2912.75</v>
+        <v>2937.6</v>
       </c>
       <c r="N56" t="n">
-        <v>2930.82</v>
+        <v>2964.3</v>
       </c>
       <c r="O56" t="n">
-        <v>2938</v>
+        <v>2978.2</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
+      <c r="Q56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U56" s="8" t="inlineStr">
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
@@ -5229,67 +5229,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2912</v>
+        <v>2860.7</v>
       </c>
       <c r="C57" t="n">
-        <v>2915.3</v>
+        <v>2862.4</v>
       </c>
       <c r="D57" t="n">
-        <v>2858.8</v>
+        <v>2829.9</v>
       </c>
       <c r="E57" t="n">
-        <v>2860.2</v>
+        <v>2856.8</v>
       </c>
       <c r="F57" t="n">
-        <v>-53.9</v>
+        <v>-3.4</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0012</v>
       </c>
       <c r="H57" t="n">
-        <v>56.5</v>
+        <v>32.5</v>
       </c>
       <c r="I57" t="n">
-        <v>2837.2</v>
+        <v>2802.3</v>
       </c>
       <c r="J57" t="n">
-        <v>2870.3</v>
+        <v>2790.27</v>
       </c>
       <c r="K57" t="n">
-        <v>2890.6</v>
+        <v>2831.95</v>
       </c>
       <c r="L57" t="n">
-        <v>2910.9</v>
+        <v>2873.62</v>
       </c>
       <c r="M57" t="n">
-        <v>2937.6</v>
+        <v>2888.45</v>
       </c>
       <c r="N57" t="n">
-        <v>2964.3</v>
+        <v>2903.27</v>
       </c>
       <c r="O57" t="n">
-        <v>2978.2</v>
+        <v>2971.8</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q57" s="6" t="n">
+        <v/>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
@@ -5298,7 +5292,7 @@
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5320,50 +5314,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2860.7</v>
+        <v>2854.4</v>
       </c>
       <c r="C58" t="n">
-        <v>2862.4</v>
+        <v>2874.1</v>
       </c>
       <c r="D58" t="n">
-        <v>2829.9</v>
+        <v>2843</v>
       </c>
       <c r="E58" t="n">
-        <v>2856.8</v>
+        <v>2859.3</v>
       </c>
       <c r="F58" t="n">
-        <v>-3.4</v>
+        <v>2.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="H58" t="n">
-        <v>32.5</v>
+        <v>31.1</v>
       </c>
       <c r="I58" t="n">
-        <v>2802.3</v>
+        <v>2797.4</v>
       </c>
       <c r="J58" t="n">
-        <v>2790.27</v>
+        <v>2829.63</v>
       </c>
       <c r="K58" t="n">
-        <v>2831.95</v>
+        <v>2840.55</v>
       </c>
       <c r="L58" t="n">
-        <v>2873.62</v>
+        <v>2851.47</v>
       </c>
       <c r="M58" t="n">
-        <v>2888.45</v>
+        <v>2873.05</v>
       </c>
       <c r="N58" t="n">
-        <v>2903.27</v>
+        <v>2894.63</v>
       </c>
       <c r="O58" t="n">
-        <v>2971.8</v>
+        <v>2894.9</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5371,19 +5365,19 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
       <c r="U58" s="8" t="n">
         <v/>
       </c>
@@ -5395,75 +5389,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2854.4</v>
+        <v>2857.7</v>
       </c>
       <c r="C59" t="n">
-        <v>2874.1</v>
+        <v>2858.8</v>
       </c>
       <c r="D59" t="n">
-        <v>2843</v>
+        <v>2826.8</v>
       </c>
       <c r="E59" t="n">
-        <v>2859.3</v>
+        <v>2840.1</v>
       </c>
       <c r="F59" t="n">
-        <v>2.5</v>
+        <v>-19.2</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0067</v>
       </c>
       <c r="H59" t="n">
-        <v>31.1</v>
+        <v>32</v>
       </c>
       <c r="I59" t="n">
-        <v>2797.4</v>
+        <v>2811.9</v>
       </c>
       <c r="J59" t="n">
-        <v>2829.63</v>
+        <v>2828.57</v>
       </c>
       <c r="K59" t="n">
-        <v>2840.55</v>
+        <v>2843.75</v>
       </c>
       <c r="L59" t="n">
-        <v>2851.47</v>
+        <v>2858.93</v>
       </c>
       <c r="M59" t="n">
-        <v>2873.05</v>
+        <v>2874.85</v>
       </c>
       <c r="N59" t="n">
-        <v>2894.63</v>
+        <v>2890.78</v>
       </c>
       <c r="O59" t="n">
-        <v>2894.9</v>
+        <v>2905.2</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
+      <c r="Q59" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
       <c r="U59" s="8" t="n">
         <v/>
       </c>
@@ -5475,67 +5475,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2857.7</v>
+        <v>2839.6</v>
       </c>
       <c r="C60" t="n">
-        <v>2858.8</v>
+        <v>2851.8</v>
       </c>
       <c r="D60" t="n">
-        <v>2826.8</v>
+        <v>2811.9</v>
       </c>
       <c r="E60" t="n">
-        <v>2840.1</v>
+        <v>2829.2</v>
       </c>
       <c r="F60" t="n">
-        <v>-19.2</v>
+        <v>-10.9</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0067</v>
+        <v>-0.0038</v>
       </c>
       <c r="H60" t="n">
-        <v>32</v>
+        <v>39.9</v>
       </c>
       <c r="I60" t="n">
-        <v>2811.9</v>
+        <v>2794.8</v>
       </c>
       <c r="J60" t="n">
-        <v>2828.57</v>
+        <v>2806.75</v>
       </c>
       <c r="K60" t="n">
-        <v>2843.75</v>
+        <v>2824.1</v>
       </c>
       <c r="L60" t="n">
-        <v>2858.93</v>
+        <v>2841.45</v>
       </c>
       <c r="M60" t="n">
-        <v>2874.85</v>
+        <v>2856.1</v>
       </c>
       <c r="N60" t="n">
-        <v>2890.78</v>
+        <v>2870.75</v>
       </c>
       <c r="O60" t="n">
-        <v>2905.2</v>
+        <v>2890.8</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q60" s="6" t="n">
+        <v/>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
@@ -5566,50 +5560,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2839.6</v>
+        <v>2831.6</v>
       </c>
       <c r="C61" t="n">
-        <v>2851.8</v>
+        <v>2853.8</v>
       </c>
       <c r="D61" t="n">
-        <v>2811.9</v>
+        <v>2812.8</v>
       </c>
       <c r="E61" t="n">
-        <v>2829.2</v>
+        <v>2817.5</v>
       </c>
       <c r="F61" t="n">
-        <v>-10.9</v>
+        <v>-11.7</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0041</v>
       </c>
       <c r="H61" t="n">
-        <v>39.9</v>
+        <v>41</v>
       </c>
       <c r="I61" t="n">
-        <v>2794.8</v>
+        <v>2772</v>
       </c>
       <c r="J61" t="n">
-        <v>2806.75</v>
+        <v>2787.97</v>
       </c>
       <c r="K61" t="n">
-        <v>2824.1</v>
+        <v>2809.25</v>
       </c>
       <c r="L61" t="n">
-        <v>2841.45</v>
+        <v>2830.52</v>
       </c>
       <c r="M61" t="n">
-        <v>2856.1</v>
+        <v>2849.15</v>
       </c>
       <c r="N61" t="n">
-        <v>2870.75</v>
+        <v>2867.78</v>
       </c>
       <c r="O61" t="n">
-        <v>2890.8</v>
+        <v>2891.7</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5627,8 +5621,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T61" s="8" t="n">
-        <v/>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5641,55 +5637,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2831.6</v>
+        <v>2819.6</v>
       </c>
       <c r="C62" t="n">
-        <v>2853.8</v>
+        <v>2843.3</v>
       </c>
       <c r="D62" t="n">
-        <v>2812.8</v>
+        <v>2791.5</v>
       </c>
       <c r="E62" t="n">
-        <v>2817.5</v>
+        <v>2826.9</v>
       </c>
       <c r="F62" t="n">
-        <v>-11.7</v>
+        <v>9.4</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0041</v>
+        <v>0.0033</v>
       </c>
       <c r="H62" t="n">
-        <v>41</v>
+        <v>51.8</v>
       </c>
       <c r="I62" t="n">
-        <v>2772</v>
+        <v>2771.8</v>
       </c>
       <c r="J62" t="n">
-        <v>2787.97</v>
+        <v>2768.6</v>
       </c>
       <c r="K62" t="n">
-        <v>2809.25</v>
+        <v>2797</v>
       </c>
       <c r="L62" t="n">
-        <v>2830.52</v>
+        <v>2825.4</v>
       </c>
       <c r="M62" t="n">
-        <v>2849.15</v>
+        <v>2838</v>
       </c>
       <c r="N62" t="n">
-        <v>2867.78</v>
+        <v>2850.6</v>
       </c>
       <c r="O62" t="n">
-        <v>2891.7</v>
+        <v>2894.8</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5699,12 +5699,12 @@
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T62" s="8" t="inlineStr">
@@ -5725,89 +5725,173 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>2829</v>
       </c>
       <c r="C63" t="n">
-        <v>2830.6</v>
+        <v>2875.3</v>
       </c>
       <c r="D63" t="n">
-        <v>2828.5</v>
+        <v>2827.7</v>
       </c>
       <c r="E63" t="n">
-        <v>2830.4</v>
+        <v>2850.9</v>
       </c>
       <c r="F63" t="n">
-        <v>12.9</v>
+        <v>24</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0046</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H63" t="n">
-        <v>2.1</v>
+        <v>47.6</v>
       </c>
       <c r="I63" t="n">
-        <v>2771.8</v>
+        <v>2739.7</v>
       </c>
       <c r="J63" t="n">
-        <v>2768.6</v>
+        <v>2779.85</v>
       </c>
       <c r="K63" t="n">
-        <v>2797</v>
+        <v>2801</v>
       </c>
       <c r="L63" t="n">
-        <v>2825.4</v>
+        <v>2822.15</v>
       </c>
       <c r="M63" t="n">
-        <v>2838</v>
+        <v>2852.8</v>
       </c>
       <c r="N63" t="n">
+        <v>2883.45</v>
+      </c>
+      <c r="O63" t="n">
+        <v>2895.1</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
         <v>2850.6</v>
       </c>
-      <c r="O63" t="n">
-        <v>2894.8</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
+      <c r="C64" t="n">
+        <v>2857</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2850.6</v>
+      </c>
+      <c r="E64" t="n">
+        <v>2850.9</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I64" t="n">
+        <v>2780.1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2803</v>
+      </c>
+      <c r="K64" t="n">
+        <v>2827.1</v>
+      </c>
+      <c r="L64" t="n">
+        <v>2851.2</v>
+      </c>
+      <c r="M64" t="n">
+        <v>2874.7</v>
+      </c>
+      <c r="N64" t="n">
+        <v>2898.2</v>
+      </c>
+      <c r="O64" t="n">
+        <v>2922.9</v>
+      </c>
+      <c r="P64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W64" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>中警訊</t>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2994.3</v>
+        <v>2965.8</v>
       </c>
       <c r="C2" t="n">
-        <v>3004.3</v>
+        <v>3014.9</v>
       </c>
       <c r="D2" t="n">
-        <v>2943.4</v>
+        <v>2964.3</v>
       </c>
       <c r="E2" t="n">
-        <v>2971.5</v>
+        <v>3008.4</v>
       </c>
       <c r="F2" t="n">
-        <v>-27.3</v>
+        <v>36.9</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0091</v>
+        <v>0.0124</v>
       </c>
       <c r="H2" t="n">
-        <v>60.9</v>
+        <v>50.6</v>
       </c>
       <c r="I2" t="n">
-        <v>2935</v>
+        <v>2882.5</v>
       </c>
       <c r="J2" t="n">
-        <v>2936.55</v>
+        <v>2909.42</v>
       </c>
       <c r="K2" t="n">
-        <v>2971.9</v>
+        <v>2941.05</v>
       </c>
       <c r="L2" t="n">
-        <v>3007.25</v>
+        <v>2972.67</v>
       </c>
       <c r="M2" t="n">
-        <v>3025.7</v>
+        <v>3001.95</v>
       </c>
       <c r="N2" t="n">
-        <v>3044.15</v>
+        <v>3031.23</v>
       </c>
       <c r="O2" t="n">
-        <v>3096.4</v>
+        <v>3065.2</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,19 +685,19 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -709,59 +709,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2965.8</v>
+        <v>3008.1</v>
       </c>
       <c r="C3" t="n">
-        <v>3014.9</v>
+        <v>3019.5</v>
       </c>
       <c r="D3" t="n">
-        <v>2964.3</v>
+        <v>2970.8</v>
       </c>
       <c r="E3" t="n">
-        <v>3008.4</v>
+        <v>2994</v>
       </c>
       <c r="F3" t="n">
-        <v>36.9</v>
+        <v>-14.4</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0048</v>
       </c>
       <c r="H3" t="n">
-        <v>50.6</v>
+        <v>48.7</v>
       </c>
       <c r="I3" t="n">
-        <v>2882.5</v>
+        <v>2913.7</v>
       </c>
       <c r="J3" t="n">
-        <v>2909.42</v>
+        <v>2967.2</v>
       </c>
       <c r="K3" t="n">
-        <v>2941.05</v>
+        <v>2983.1</v>
       </c>
       <c r="L3" t="n">
-        <v>2972.67</v>
+        <v>2999</v>
       </c>
       <c r="M3" t="n">
-        <v>3001.95</v>
+        <v>3033.7</v>
       </c>
       <c r="N3" t="n">
-        <v>3031.23</v>
+        <v>3068.4</v>
       </c>
       <c r="O3" t="n">
-        <v>3065.2</v>
+        <v>3065.5</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -769,18 +765,18 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -793,55 +789,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3008.1</v>
+        <v>2984.7</v>
       </c>
       <c r="C4" t="n">
-        <v>3019.5</v>
+        <v>2995.8</v>
       </c>
       <c r="D4" t="n">
-        <v>2970.8</v>
+        <v>2961.8</v>
       </c>
       <c r="E4" t="n">
-        <v>2994</v>
+        <v>2970.4</v>
       </c>
       <c r="F4" t="n">
-        <v>-14.4</v>
+        <v>-23.6</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>48.7</v>
+        <v>34</v>
       </c>
       <c r="I4" t="n">
-        <v>2913.7</v>
+        <v>2922.1</v>
       </c>
       <c r="J4" t="n">
-        <v>2967.2</v>
+        <v>2944.73</v>
       </c>
       <c r="K4" t="n">
-        <v>2983.1</v>
+        <v>2969.65</v>
       </c>
       <c r="L4" t="n">
-        <v>2999</v>
+        <v>2994.58</v>
       </c>
       <c r="M4" t="n">
-        <v>3033.7</v>
+        <v>3018.35</v>
       </c>
       <c r="N4" t="n">
-        <v>3068.4</v>
+        <v>3042.12</v>
       </c>
       <c r="O4" t="n">
-        <v>3065.5</v>
+        <v>3068.2</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -851,12 +851,12 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -875,57 +875,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2984.7</v>
+        <v>2967.2</v>
       </c>
       <c r="C5" t="n">
-        <v>2995.8</v>
+        <v>3029.8</v>
       </c>
       <c r="D5" t="n">
-        <v>2961.8</v>
+        <v>2956.2</v>
       </c>
       <c r="E5" t="n">
-        <v>2970.4</v>
+        <v>2979.9</v>
       </c>
       <c r="F5" t="n">
-        <v>-23.6</v>
+        <v>9.5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H5" t="n">
-        <v>34</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>2922.1</v>
+        <v>2927.8</v>
       </c>
       <c r="J5" t="n">
-        <v>2944.73</v>
+        <v>2932.2</v>
       </c>
       <c r="K5" t="n">
-        <v>2969.65</v>
+        <v>2953.4</v>
       </c>
       <c r="L5" t="n">
-        <v>2994.58</v>
+        <v>2974.6</v>
       </c>
       <c r="M5" t="n">
-        <v>3018.35</v>
+        <v>2987.4</v>
       </c>
       <c r="N5" t="n">
-        <v>3042.12</v>
+        <v>3000.2</v>
       </c>
       <c r="O5" t="n">
-        <v>3068.2</v>
+        <v>3029.8</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -933,24 +933,28 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R5" s="6" t="n">
+        <v/>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
@@ -959,57 +963,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2967.2</v>
+        <v>2981.2</v>
       </c>
       <c r="C6" t="n">
-        <v>3029.8</v>
+        <v>3006.1</v>
       </c>
       <c r="D6" t="n">
-        <v>2956.2</v>
+        <v>2974.4</v>
       </c>
       <c r="E6" t="n">
-        <v>2979.9</v>
+        <v>2991.8</v>
       </c>
       <c r="F6" t="n">
-        <v>9.5</v>
+        <v>11.9</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.004</v>
       </c>
       <c r="H6" t="n">
-        <v>73.59999999999999</v>
+        <v>31.7</v>
       </c>
       <c r="I6" t="n">
-        <v>2927.8</v>
+        <v>2882.6</v>
       </c>
       <c r="J6" t="n">
-        <v>2932.2</v>
+        <v>2899.75</v>
       </c>
       <c r="K6" t="n">
-        <v>2953.4</v>
+        <v>2943.1</v>
       </c>
       <c r="L6" t="n">
-        <v>2974.6</v>
+        <v>2986.45</v>
       </c>
       <c r="M6" t="n">
-        <v>2987.4</v>
+        <v>3016.7</v>
       </c>
       <c r="N6" t="n">
-        <v>3000.2</v>
+        <v>3046.95</v>
       </c>
       <c r="O6" t="n">
-        <v>3029.8</v>
+        <v>3103.4</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1020,25 +1024,19 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
@@ -1054,50 +1052,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2981.2</v>
+        <v>2995.3</v>
       </c>
       <c r="C7" t="n">
-        <v>3006.1</v>
+        <v>3012.8</v>
       </c>
       <c r="D7" t="n">
-        <v>2974.4</v>
+        <v>2972.7</v>
       </c>
       <c r="E7" t="n">
-        <v>2991.8</v>
+        <v>2990.7</v>
       </c>
       <c r="F7" t="n">
-        <v>11.9</v>
+        <v>-1.1</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0004</v>
       </c>
       <c r="H7" t="n">
-        <v>31.7</v>
+        <v>40.1</v>
       </c>
       <c r="I7" t="n">
-        <v>2882.6</v>
+        <v>2942.7</v>
       </c>
       <c r="J7" t="n">
-        <v>2899.75</v>
+        <v>2960.87</v>
       </c>
       <c r="K7" t="n">
-        <v>2943.1</v>
+        <v>2975.95</v>
       </c>
       <c r="L7" t="n">
-        <v>2986.45</v>
+        <v>2991.03</v>
       </c>
       <c r="M7" t="n">
-        <v>3016.7</v>
+        <v>3007.65</v>
       </c>
       <c r="N7" t="n">
-        <v>3046.95</v>
+        <v>3024.28</v>
       </c>
       <c r="O7" t="n">
-        <v>3103.4</v>
+        <v>3037.8</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1105,16 +1103,20 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1129,78 +1131,78 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2995.3</v>
+        <v>2991.7</v>
       </c>
       <c r="C8" t="n">
-        <v>3012.8</v>
+        <v>2994.8</v>
       </c>
       <c r="D8" t="n">
-        <v>2972.7</v>
+        <v>2949.3</v>
       </c>
       <c r="E8" t="n">
-        <v>2990.7</v>
+        <v>2973.5</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1</v>
+        <v>-17.2</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0058</v>
       </c>
       <c r="H8" t="n">
-        <v>40.1</v>
+        <v>45.5</v>
       </c>
       <c r="I8" t="n">
-        <v>2942.7</v>
+        <v>2932.6</v>
       </c>
       <c r="J8" t="n">
-        <v>2960.87</v>
+        <v>2949.57</v>
       </c>
       <c r="K8" t="n">
-        <v>2975.95</v>
+        <v>2970.65</v>
       </c>
       <c r="L8" t="n">
-        <v>2991.03</v>
+        <v>2991.72</v>
       </c>
       <c r="M8" t="n">
-        <v>3007.65</v>
+        <v>3010.75</v>
       </c>
       <c r="N8" t="n">
-        <v>3024.28</v>
+        <v>3029.78</v>
       </c>
       <c r="O8" t="n">
-        <v>3037.8</v>
+        <v>3052.9</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1215,79 +1217,79 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2991.7</v>
+        <v>2964.5</v>
       </c>
       <c r="C9" t="n">
-        <v>2994.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D9" t="n">
-        <v>2949.3</v>
+        <v>2952.7</v>
       </c>
       <c r="E9" t="n">
-        <v>2973.5</v>
+        <v>2955.2</v>
       </c>
       <c r="F9" t="n">
-        <v>-17.2</v>
+        <v>-18.3</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0062</v>
       </c>
       <c r="H9" t="n">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="I9" t="n">
-        <v>2932.6</v>
+        <v>2903.8</v>
       </c>
       <c r="J9" t="n">
-        <v>2949.57</v>
+        <v>2928.72</v>
       </c>
       <c r="K9" t="n">
-        <v>2970.65</v>
+        <v>2950.75</v>
       </c>
       <c r="L9" t="n">
-        <v>2991.72</v>
+        <v>2972.78</v>
       </c>
       <c r="M9" t="n">
-        <v>3010.75</v>
+        <v>2996.25</v>
       </c>
       <c r="N9" t="n">
-        <v>3029.78</v>
+        <v>3019.72</v>
       </c>
       <c r="O9" t="n">
-        <v>3052.9</v>
+        <v>3040.3</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1301,57 +1303,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2964.5</v>
+        <v>2955.8</v>
       </c>
       <c r="C10" t="n">
-        <v>2998.7</v>
+        <v>2999.8</v>
       </c>
       <c r="D10" t="n">
-        <v>2952.7</v>
+        <v>2951.1</v>
       </c>
       <c r="E10" t="n">
-        <v>2955.2</v>
+        <v>2997</v>
       </c>
       <c r="F10" t="n">
-        <v>-18.3</v>
+        <v>41.8</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0141</v>
       </c>
       <c r="H10" t="n">
-        <v>46</v>
+        <v>48.7</v>
       </c>
       <c r="I10" t="n">
-        <v>2903.8</v>
+        <v>2906.7</v>
       </c>
       <c r="J10" t="n">
-        <v>2928.72</v>
+        <v>2898.95</v>
       </c>
       <c r="K10" t="n">
-        <v>2950.75</v>
+        <v>2932.2</v>
       </c>
       <c r="L10" t="n">
-        <v>2972.78</v>
+        <v>2965.45</v>
       </c>
       <c r="M10" t="n">
-        <v>2996.25</v>
+        <v>2978.2</v>
       </c>
       <c r="N10" t="n">
-        <v>3019.72</v>
+        <v>2990.95</v>
       </c>
       <c r="O10" t="n">
-        <v>3040.3</v>
+        <v>3044.7</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1359,23 +1361,23 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1394,50 +1396,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2955.8</v>
+        <v>2997</v>
       </c>
       <c r="C11" t="n">
-        <v>2999.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D11" t="n">
-        <v>2951.1</v>
+        <v>2965.5</v>
       </c>
       <c r="E11" t="n">
-        <v>2997</v>
+        <v>2969.8</v>
       </c>
       <c r="F11" t="n">
-        <v>41.8</v>
+        <v>-27.2</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0141</v>
+        <v>-0.0091</v>
       </c>
       <c r="H11" t="n">
-        <v>48.7</v>
+        <v>33.2</v>
       </c>
       <c r="I11" t="n">
-        <v>2906.7</v>
+        <v>2902.4</v>
       </c>
       <c r="J11" t="n">
-        <v>2898.95</v>
+        <v>2959.08</v>
       </c>
       <c r="K11" t="n">
-        <v>2932.2</v>
+        <v>2972.65</v>
       </c>
       <c r="L11" t="n">
-        <v>2965.45</v>
+        <v>2986.23</v>
       </c>
       <c r="M11" t="n">
-        <v>2978.2</v>
+        <v>3021.35</v>
       </c>
       <c r="N11" t="n">
-        <v>2990.95</v>
+        <v>3056.47</v>
       </c>
       <c r="O11" t="n">
-        <v>3044.7</v>
+        <v>3048.5</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1445,23 +1447,21 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1473,60 +1473,62 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2997</v>
+        <v>2974.6</v>
       </c>
       <c r="C12" t="n">
-        <v>2998.7</v>
+        <v>2979</v>
       </c>
       <c r="D12" t="n">
-        <v>2965.5</v>
+        <v>2932.1</v>
       </c>
       <c r="E12" t="n">
-        <v>2969.8</v>
+        <v>2951.7</v>
       </c>
       <c r="F12" t="n">
-        <v>-27.2</v>
+        <v>-18.1</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0091</v>
+        <v>-0.0061</v>
       </c>
       <c r="H12" t="n">
-        <v>33.2</v>
+        <v>46.9</v>
       </c>
       <c r="I12" t="n">
-        <v>2902.4</v>
+        <v>2932.3</v>
       </c>
       <c r="J12" t="n">
-        <v>2959.08</v>
+        <v>2930.45</v>
       </c>
       <c r="K12" t="n">
-        <v>2972.65</v>
+        <v>2953.2</v>
       </c>
       <c r="L12" t="n">
-        <v>2986.23</v>
+        <v>2975.95</v>
       </c>
       <c r="M12" t="n">
-        <v>3021.35</v>
+        <v>2986.4</v>
       </c>
       <c r="N12" t="n">
-        <v>3056.47</v>
+        <v>2996.85</v>
       </c>
       <c r="O12" t="n">
-        <v>3048.5</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
+        <v>3031.9</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q12" s="6" t="n">
         <v/>
@@ -1536,7 +1538,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1557,74 +1559,70 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2974.6</v>
+        <v>2948.5</v>
       </c>
       <c r="C13" t="n">
-        <v>2979</v>
+        <v>2969.7</v>
       </c>
       <c r="D13" t="n">
-        <v>2932.1</v>
+        <v>2934.5</v>
       </c>
       <c r="E13" t="n">
-        <v>2951.7</v>
+        <v>2941.3</v>
       </c>
       <c r="F13" t="n">
-        <v>-18.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0035</v>
       </c>
       <c r="H13" t="n">
-        <v>46.9</v>
+        <v>35.2</v>
       </c>
       <c r="I13" t="n">
-        <v>2932.3</v>
+        <v>2885.2</v>
       </c>
       <c r="J13" t="n">
-        <v>2930.45</v>
+        <v>2902.88</v>
       </c>
       <c r="K13" t="n">
-        <v>2953.2</v>
+        <v>2928.25</v>
       </c>
       <c r="L13" t="n">
-        <v>2975.95</v>
+        <v>2953.62</v>
       </c>
       <c r="M13" t="n">
-        <v>2986.4</v>
+        <v>2975.15</v>
       </c>
       <c r="N13" t="n">
-        <v>2996.85</v>
+        <v>2996.67</v>
       </c>
       <c r="O13" t="n">
-        <v>3031.9</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3025.9</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
       </c>
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1643,57 +1641,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2948.5</v>
+        <v>2955.5</v>
       </c>
       <c r="C14" t="n">
-        <v>2969.7</v>
+        <v>2985.9</v>
       </c>
       <c r="D14" t="n">
-        <v>2934.5</v>
+        <v>2941.2</v>
       </c>
       <c r="E14" t="n">
-        <v>2941.3</v>
+        <v>2960</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.4</v>
+        <v>18.7</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0064</v>
       </c>
       <c r="H14" t="n">
-        <v>35.2</v>
+        <v>44.7</v>
       </c>
       <c r="I14" t="n">
-        <v>2885.2</v>
+        <v>2899.3</v>
       </c>
       <c r="J14" t="n">
-        <v>2902.88</v>
+        <v>2900.7</v>
       </c>
       <c r="K14" t="n">
-        <v>2928.25</v>
+        <v>2923.7</v>
       </c>
       <c r="L14" t="n">
-        <v>2953.62</v>
+        <v>2946.7</v>
       </c>
       <c r="M14" t="n">
-        <v>2975.15</v>
+        <v>2958.9</v>
       </c>
       <c r="N14" t="n">
-        <v>2996.67</v>
+        <v>2971.1</v>
       </c>
       <c r="O14" t="n">
-        <v>3025.9</v>
+        <v>3004.9</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1706,14 +1704,18 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1723,59 +1725,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2955.5</v>
+        <v>2961.5</v>
       </c>
       <c r="C15" t="n">
-        <v>2985.9</v>
+        <v>2968.3</v>
       </c>
       <c r="D15" t="n">
-        <v>2941.2</v>
+        <v>2933.4</v>
       </c>
       <c r="E15" t="n">
-        <v>2960</v>
+        <v>2964.5</v>
       </c>
       <c r="F15" t="n">
-        <v>18.7</v>
+        <v>4.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0015</v>
       </c>
       <c r="H15" t="n">
-        <v>44.7</v>
+        <v>34.9</v>
       </c>
       <c r="I15" t="n">
-        <v>2899.3</v>
+        <v>2896.5</v>
       </c>
       <c r="J15" t="n">
-        <v>2900.7</v>
+        <v>2913.53</v>
       </c>
       <c r="K15" t="n">
-        <v>2923.7</v>
+        <v>2937.65</v>
       </c>
       <c r="L15" t="n">
-        <v>2946.7</v>
+        <v>2961.77</v>
       </c>
       <c r="M15" t="n">
-        <v>2958.9</v>
+        <v>2982.35</v>
       </c>
       <c r="N15" t="n">
-        <v>2971.1</v>
+        <v>3002.92</v>
       </c>
       <c r="O15" t="n">
-        <v>3004.9</v>
+        <v>3030.6</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1783,24 +1781,22 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
@@ -1809,61 +1805,69 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2961.5</v>
+        <v>2966.9</v>
       </c>
       <c r="C16" t="n">
-        <v>2968.3</v>
+        <v>2978.3</v>
       </c>
       <c r="D16" t="n">
-        <v>2933.4</v>
+        <v>2902.3</v>
       </c>
       <c r="E16" t="n">
-        <v>2964.5</v>
+        <v>2915.4</v>
       </c>
       <c r="F16" t="n">
-        <v>4.5</v>
+        <v>-49.1</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0166</v>
       </c>
       <c r="H16" t="n">
-        <v>34.9</v>
+        <v>76</v>
       </c>
       <c r="I16" t="n">
-        <v>2896.5</v>
+        <v>2898.5</v>
       </c>
       <c r="J16" t="n">
-        <v>2913.53</v>
+        <v>2936.42</v>
       </c>
       <c r="K16" t="n">
-        <v>2937.65</v>
+        <v>2947.05</v>
       </c>
       <c r="L16" t="n">
-        <v>2961.77</v>
+        <v>2957.67</v>
       </c>
       <c r="M16" t="n">
-        <v>2982.35</v>
+        <v>2981.95</v>
       </c>
       <c r="N16" t="n">
-        <v>3002.92</v>
+        <v>3006.23</v>
       </c>
       <c r="O16" t="n">
-        <v>3030.6</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
+        <v>3003.2</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
@@ -1872,7 +1876,7 @@
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1884,88 +1888,84 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W16" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2966.9</v>
+        <v>2906.6</v>
       </c>
       <c r="C17" t="n">
-        <v>2978.3</v>
+        <v>2957.9</v>
       </c>
       <c r="D17" t="n">
-        <v>2902.3</v>
+        <v>2905.6</v>
       </c>
       <c r="E17" t="n">
-        <v>2915.4</v>
+        <v>2954.3</v>
       </c>
       <c r="F17" t="n">
-        <v>-49.1</v>
+        <v>38.9</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0166</v>
+        <v>0.0133</v>
       </c>
       <c r="H17" t="n">
-        <v>76</v>
+        <v>52.3</v>
       </c>
       <c r="I17" t="n">
-        <v>2898.5</v>
+        <v>2826.3</v>
       </c>
       <c r="J17" t="n">
-        <v>2936.42</v>
+        <v>2826.95</v>
       </c>
       <c r="K17" t="n">
-        <v>2947.05</v>
+        <v>2877.4</v>
       </c>
       <c r="L17" t="n">
-        <v>2957.67</v>
+        <v>2927.85</v>
       </c>
       <c r="M17" t="n">
-        <v>2981.95</v>
+        <v>2953.4</v>
       </c>
       <c r="N17" t="n">
-        <v>3006.23</v>
+        <v>2978.95</v>
       </c>
       <c r="O17" t="n">
-        <v>3003.2</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
+        <v>3054.3</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
@@ -1979,76 +1979,78 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2906.6</v>
+        <v>2954</v>
       </c>
       <c r="C18" t="n">
-        <v>2957.9</v>
+        <v>2976.3</v>
       </c>
       <c r="D18" t="n">
-        <v>2905.6</v>
+        <v>2905.3</v>
       </c>
       <c r="E18" t="n">
-        <v>2954.3</v>
+        <v>2938</v>
       </c>
       <c r="F18" t="n">
-        <v>38.9</v>
+        <v>-16.3</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0055</v>
       </c>
       <c r="H18" t="n">
-        <v>52.3</v>
+        <v>71</v>
       </c>
       <c r="I18" t="n">
-        <v>2826.3</v>
+        <v>2853.3</v>
       </c>
       <c r="J18" t="n">
-        <v>2826.95</v>
+        <v>2913.28</v>
       </c>
       <c r="K18" t="n">
-        <v>2877.4</v>
+        <v>2928.15</v>
       </c>
       <c r="L18" t="n">
-        <v>2927.85</v>
+        <v>2943.03</v>
       </c>
       <c r="M18" t="n">
-        <v>2953.4</v>
+        <v>2980.45</v>
       </c>
       <c r="N18" t="n">
-        <v>2978.95</v>
+        <v>3017.87</v>
       </c>
       <c r="O18" t="n">
-        <v>3054.3</v>
+        <v>3010.2</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2063,78 +2065,76 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2954</v>
+        <v>2950</v>
       </c>
       <c r="C19" t="n">
-        <v>2976.3</v>
+        <v>2994.6</v>
       </c>
       <c r="D19" t="n">
-        <v>2905.3</v>
+        <v>2948.4</v>
       </c>
       <c r="E19" t="n">
-        <v>2938</v>
+        <v>2989.3</v>
       </c>
       <c r="F19" t="n">
-        <v>-16.3</v>
+        <v>51.3</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0175</v>
       </c>
       <c r="H19" t="n">
-        <v>71</v>
+        <v>46.2</v>
       </c>
       <c r="I19" t="n">
-        <v>2853.3</v>
+        <v>2834.3</v>
       </c>
       <c r="J19" t="n">
-        <v>2913.28</v>
+        <v>2865.6</v>
       </c>
       <c r="K19" t="n">
-        <v>2928.15</v>
+        <v>2902.5</v>
       </c>
       <c r="L19" t="n">
-        <v>2943.03</v>
+        <v>2939.4</v>
       </c>
       <c r="M19" t="n">
-        <v>2980.45</v>
+        <v>2973.5</v>
       </c>
       <c r="N19" t="n">
-        <v>3017.87</v>
+        <v>3007.6</v>
       </c>
       <c r="O19" t="n">
-        <v>3010.2</v>
+        <v>3047.3</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2149,57 +2149,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2950</v>
+        <v>2992.4</v>
       </c>
       <c r="C20" t="n">
-        <v>2994.6</v>
+        <v>3051.8</v>
       </c>
       <c r="D20" t="n">
-        <v>2948.4</v>
+        <v>2986.1</v>
       </c>
       <c r="E20" t="n">
-        <v>2989.3</v>
+        <v>3044.7</v>
       </c>
       <c r="F20" t="n">
-        <v>51.3</v>
+        <v>55.4</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0185</v>
       </c>
       <c r="H20" t="n">
-        <v>46.2</v>
+        <v>65.7</v>
       </c>
       <c r="I20" t="n">
-        <v>2834.3</v>
+        <v>2902.2</v>
       </c>
       <c r="J20" t="n">
-        <v>2865.6</v>
+        <v>2952</v>
       </c>
       <c r="K20" t="n">
-        <v>2902.5</v>
+        <v>2966.2</v>
       </c>
       <c r="L20" t="n">
-        <v>2939.4</v>
+        <v>2980.4</v>
       </c>
       <c r="M20" t="n">
-        <v>2973.5</v>
+        <v>3012.4</v>
       </c>
       <c r="N20" t="n">
-        <v>3007.6</v>
+        <v>3044.4</v>
       </c>
       <c r="O20" t="n">
-        <v>3047.3</v>
+        <v>3040.8</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2210,80 +2210,80 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W20" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2992.4</v>
+        <v>3049.1</v>
       </c>
       <c r="C21" t="n">
-        <v>3051.8</v>
+        <v>3058.3</v>
       </c>
       <c r="D21" t="n">
-        <v>2986.1</v>
+        <v>3023.3</v>
       </c>
       <c r="E21" t="n">
-        <v>3044.7</v>
+        <v>3025.4</v>
       </c>
       <c r="F21" t="n">
-        <v>55.4</v>
+        <v>-19.3</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0063</v>
       </c>
       <c r="H21" t="n">
-        <v>65.7</v>
+        <v>35</v>
       </c>
       <c r="I21" t="n">
-        <v>2902.2</v>
+        <v>2920.4</v>
       </c>
       <c r="J21" t="n">
-        <v>2952</v>
+        <v>2991.87</v>
       </c>
       <c r="K21" t="n">
-        <v>2966.2</v>
+        <v>3011.85</v>
       </c>
       <c r="L21" t="n">
-        <v>2980.4</v>
+        <v>3031.83</v>
       </c>
       <c r="M21" t="n">
-        <v>3012.4</v>
+        <v>3077.55</v>
       </c>
       <c r="N21" t="n">
-        <v>3044.4</v>
+        <v>3123.27</v>
       </c>
       <c r="O21" t="n">
-        <v>3040.8</v>
+        <v>3117.5</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2296,78 +2296,76 @@
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3049.1</v>
+        <v>3028.5</v>
       </c>
       <c r="C22" t="n">
-        <v>3058.3</v>
+        <v>3041</v>
       </c>
       <c r="D22" t="n">
-        <v>3023.3</v>
+        <v>3004.9</v>
       </c>
       <c r="E22" t="n">
-        <v>3025.4</v>
+        <v>3009.1</v>
       </c>
       <c r="F22" t="n">
-        <v>-19.3</v>
+        <v>-16.3</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0054</v>
       </c>
       <c r="H22" t="n">
-        <v>35</v>
+        <v>36.1</v>
       </c>
       <c r="I22" t="n">
-        <v>2920.4</v>
+        <v>2988.3</v>
       </c>
       <c r="J22" t="n">
-        <v>2991.87</v>
+        <v>2982.7</v>
       </c>
       <c r="K22" t="n">
-        <v>3011.85</v>
+        <v>3007.9</v>
       </c>
       <c r="L22" t="n">
-        <v>3031.83</v>
+        <v>3033.1</v>
       </c>
       <c r="M22" t="n">
-        <v>3077.55</v>
+        <v>3042.9</v>
       </c>
       <c r="N22" t="n">
-        <v>3123.27</v>
+        <v>3052.7</v>
       </c>
       <c r="O22" t="n">
-        <v>3117.5</v>
+        <v>3093.3</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2375,12 +2373,14 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2399,57 +2399,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3028.5</v>
+        <v>3008.5</v>
       </c>
       <c r="C23" t="n">
-        <v>3041</v>
+        <v>3046.8</v>
       </c>
       <c r="D23" t="n">
-        <v>3004.9</v>
+        <v>3002</v>
       </c>
       <c r="E23" t="n">
-        <v>3009.1</v>
+        <v>3041.6</v>
       </c>
       <c r="F23" t="n">
-        <v>-16.3</v>
+        <v>32.5</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0054</v>
+        <v>0.0108</v>
       </c>
       <c r="H23" t="n">
-        <v>36.1</v>
+        <v>44.8</v>
       </c>
       <c r="I23" t="n">
-        <v>2988.3</v>
+        <v>2968.8</v>
       </c>
       <c r="J23" t="n">
-        <v>2982.7</v>
+        <v>2966.08</v>
       </c>
       <c r="K23" t="n">
-        <v>3007.9</v>
+        <v>2991.05</v>
       </c>
       <c r="L23" t="n">
-        <v>3033.1</v>
+        <v>3016.03</v>
       </c>
       <c r="M23" t="n">
-        <v>3042.9</v>
+        <v>3027.15</v>
       </c>
       <c r="N23" t="n">
-        <v>3052.7</v>
+        <v>3038.28</v>
       </c>
       <c r="O23" t="n">
-        <v>3093.3</v>
+        <v>3077.1</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2457,22 +2457,24 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
@@ -2483,57 +2485,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3008.5</v>
+        <v>3038.9</v>
       </c>
       <c r="C24" t="n">
-        <v>3046.8</v>
+        <v>3044.6</v>
       </c>
       <c r="D24" t="n">
-        <v>3002</v>
+        <v>3016</v>
       </c>
       <c r="E24" t="n">
-        <v>3041.6</v>
+        <v>3025</v>
       </c>
       <c r="F24" t="n">
-        <v>32.5</v>
+        <v>-16.6</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0108</v>
+        <v>-0.0055</v>
       </c>
       <c r="H24" t="n">
-        <v>44.8</v>
+        <v>28.6</v>
       </c>
       <c r="I24" t="n">
-        <v>2968.8</v>
+        <v>2957.2</v>
       </c>
       <c r="J24" t="n">
-        <v>2966.08</v>
+        <v>3005.4</v>
       </c>
       <c r="K24" t="n">
-        <v>2991.05</v>
+        <v>3019.2</v>
       </c>
       <c r="L24" t="n">
-        <v>3016.03</v>
+        <v>3033</v>
       </c>
       <c r="M24" t="n">
-        <v>3027.15</v>
+        <v>3064</v>
       </c>
       <c r="N24" t="n">
-        <v>3038.28</v>
+        <v>3095</v>
       </c>
       <c r="O24" t="n">
-        <v>3077.1</v>
+        <v>3091.6</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2541,23 +2543,21 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2569,57 +2569,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3038.9</v>
+        <v>3024.7</v>
       </c>
       <c r="C25" t="n">
-        <v>3044.6</v>
+        <v>3045.8</v>
       </c>
       <c r="D25" t="n">
-        <v>3016</v>
+        <v>3019.9</v>
       </c>
       <c r="E25" t="n">
-        <v>3025</v>
+        <v>3035.5</v>
       </c>
       <c r="F25" t="n">
-        <v>-16.6</v>
+        <v>10.5</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0055</v>
+        <v>0.0035</v>
       </c>
       <c r="H25" t="n">
-        <v>28.6</v>
+        <v>25.9</v>
       </c>
       <c r="I25" t="n">
-        <v>2957.2</v>
+        <v>2987.4</v>
       </c>
       <c r="J25" t="n">
-        <v>3005.4</v>
+        <v>2993.75</v>
       </c>
       <c r="K25" t="n">
-        <v>3019.2</v>
+        <v>3010.7</v>
       </c>
       <c r="L25" t="n">
-        <v>3033</v>
+        <v>3027.65</v>
       </c>
       <c r="M25" t="n">
-        <v>3064</v>
+        <v>3039.3</v>
       </c>
       <c r="N25" t="n">
-        <v>3095</v>
+        <v>3050.95</v>
       </c>
       <c r="O25" t="n">
-        <v>3091.6</v>
+        <v>3073.2</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2627,19 +2627,19 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
       <c r="U25" s="8" t="n">
         <v/>
       </c>
@@ -2651,59 +2651,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3024.7</v>
+        <v>3036.1</v>
       </c>
       <c r="C26" t="n">
-        <v>3045.8</v>
+        <v>3060</v>
       </c>
       <c r="D26" t="n">
-        <v>3019.9</v>
+        <v>3033.1</v>
       </c>
       <c r="E26" t="n">
-        <v>3035.5</v>
+        <v>3052.8</v>
       </c>
       <c r="F26" t="n">
-        <v>10.5</v>
+        <v>17.3</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0057</v>
       </c>
       <c r="H26" t="n">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
       <c r="I26" t="n">
-        <v>2987.4</v>
+        <v>2994</v>
       </c>
       <c r="J26" t="n">
-        <v>2993.75</v>
+        <v>3010.92</v>
       </c>
       <c r="K26" t="n">
-        <v>3010.7</v>
+        <v>3022.55</v>
       </c>
       <c r="L26" t="n">
-        <v>3027.65</v>
+        <v>3034.17</v>
       </c>
       <c r="M26" t="n">
-        <v>3039.3</v>
+        <v>3048.45</v>
       </c>
       <c r="N26" t="n">
-        <v>3050.95</v>
+        <v>3062.73</v>
       </c>
       <c r="O26" t="n">
-        <v>3073.2</v>
+        <v>3071.7</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2714,7 +2710,7 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2740,50 +2736,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3036.1</v>
+        <v>3056.2</v>
       </c>
       <c r="C27" t="n">
-        <v>3060</v>
+        <v>3076.3</v>
       </c>
       <c r="D27" t="n">
-        <v>3033.1</v>
+        <v>3052.5</v>
       </c>
       <c r="E27" t="n">
-        <v>3052.8</v>
+        <v>3060.2</v>
       </c>
       <c r="F27" t="n">
-        <v>17.3</v>
+        <v>7.4</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0024</v>
       </c>
       <c r="H27" t="n">
-        <v>26.9</v>
+        <v>23.8</v>
       </c>
       <c r="I27" t="n">
-        <v>2994</v>
+        <v>3006.2</v>
       </c>
       <c r="J27" t="n">
-        <v>3010.92</v>
+        <v>3029.03</v>
       </c>
       <c r="K27" t="n">
-        <v>3022.55</v>
+        <v>3039.35</v>
       </c>
       <c r="L27" t="n">
-        <v>3034.17</v>
+        <v>3049.68</v>
       </c>
       <c r="M27" t="n">
-        <v>3048.45</v>
+        <v>3066.25</v>
       </c>
       <c r="N27" t="n">
-        <v>3062.73</v>
+        <v>3082.82</v>
       </c>
       <c r="O27" t="n">
-        <v>3071.7</v>
+        <v>3086.9</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2794,7 +2790,7 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2820,50 +2816,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3056.2</v>
+        <v>3062.2</v>
       </c>
       <c r="C28" t="n">
         <v>3076.3</v>
       </c>
       <c r="D28" t="n">
-        <v>3052.5</v>
+        <v>3051.7</v>
       </c>
       <c r="E28" t="n">
-        <v>3060.2</v>
+        <v>3074.9</v>
       </c>
       <c r="F28" t="n">
-        <v>7.4</v>
+        <v>14.7</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0048</v>
       </c>
       <c r="H28" t="n">
-        <v>23.8</v>
+        <v>24.6</v>
       </c>
       <c r="I28" t="n">
-        <v>3006.2</v>
+        <v>3028.7</v>
       </c>
       <c r="J28" t="n">
-        <v>3029.03</v>
+        <v>3034.3</v>
       </c>
       <c r="K28" t="n">
-        <v>3039.35</v>
+        <v>3048.3</v>
       </c>
       <c r="L28" t="n">
-        <v>3049.68</v>
+        <v>3062.3</v>
       </c>
       <c r="M28" t="n">
-        <v>3066.25</v>
+        <v>3072.1</v>
       </c>
       <c r="N28" t="n">
-        <v>3082.82</v>
+        <v>3081.9</v>
       </c>
       <c r="O28" t="n">
-        <v>3086.9</v>
+        <v>3100.1</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2874,7 +2870,7 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2895,55 +2891,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3062.2</v>
+        <v>3073.5</v>
       </c>
       <c r="C29" t="n">
-        <v>3076.3</v>
+        <v>3079.9</v>
       </c>
       <c r="D29" t="n">
-        <v>3051.7</v>
+        <v>3055.9</v>
       </c>
       <c r="E29" t="n">
-        <v>3074.9</v>
+        <v>3064.9</v>
       </c>
       <c r="F29" t="n">
-        <v>14.7</v>
+        <v>-10</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.0033</v>
       </c>
       <c r="H29" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="I29" t="n">
-        <v>3028.7</v>
+        <v>3027.1</v>
       </c>
       <c r="J29" t="n">
-        <v>3034.3</v>
+        <v>3055.75</v>
       </c>
       <c r="K29" t="n">
-        <v>3048.3</v>
+        <v>3062.6</v>
       </c>
       <c r="L29" t="n">
-        <v>3062.3</v>
+        <v>3069.45</v>
       </c>
       <c r="M29" t="n">
-        <v>3072.1</v>
+        <v>3087.2</v>
       </c>
       <c r="N29" t="n">
-        <v>3081.9</v>
+        <v>3104.95</v>
       </c>
       <c r="O29" t="n">
-        <v>3100.1</v>
+        <v>3100.9</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2951,18 +2951,18 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2984,63 +2984,67 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3073.5</v>
+        <v>3063.7</v>
       </c>
       <c r="C30" t="n">
-        <v>3079.9</v>
+        <v>3066.6</v>
       </c>
       <c r="D30" t="n">
-        <v>3055.9</v>
+        <v>3024.1</v>
       </c>
       <c r="E30" t="n">
-        <v>3064.9</v>
+        <v>3026.4</v>
       </c>
       <c r="F30" t="n">
-        <v>-10</v>
+        <v>-38.5</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0126</v>
       </c>
       <c r="H30" t="n">
-        <v>24</v>
+        <v>42.5</v>
       </c>
       <c r="I30" t="n">
-        <v>3027.1</v>
+        <v>3031.9</v>
       </c>
       <c r="J30" t="n">
-        <v>3055.75</v>
+        <v>3039.4</v>
       </c>
       <c r="K30" t="n">
-        <v>3062.6</v>
+        <v>3052.9</v>
       </c>
       <c r="L30" t="n">
-        <v>3069.45</v>
+        <v>3066.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3087.2</v>
+        <v>3076.9</v>
       </c>
       <c r="N30" t="n">
-        <v>3104.95</v>
+        <v>3087.4</v>
       </c>
       <c r="O30" t="n">
-        <v>3100.9</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
+        <v>3103.9</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3054,88 +3058,80 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W30" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3063.7</v>
+        <v>3025.9</v>
       </c>
       <c r="C31" t="n">
-        <v>3066.6</v>
+        <v>3059.1</v>
       </c>
       <c r="D31" t="n">
-        <v>3024.1</v>
+        <v>3019.8</v>
       </c>
       <c r="E31" t="n">
-        <v>3026.4</v>
+        <v>3039.9</v>
       </c>
       <c r="F31" t="n">
-        <v>-38.5</v>
+        <v>13.5</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0045</v>
       </c>
       <c r="H31" t="n">
-        <v>42.5</v>
+        <v>39.3</v>
       </c>
       <c r="I31" t="n">
-        <v>3031.9</v>
+        <v>2981.6</v>
       </c>
       <c r="J31" t="n">
-        <v>3039.4</v>
+        <v>2974.42</v>
       </c>
       <c r="K31" t="n">
-        <v>3052.9</v>
+        <v>3005.15</v>
       </c>
       <c r="L31" t="n">
-        <v>3066.4</v>
+        <v>3035.88</v>
       </c>
       <c r="M31" t="n">
-        <v>3076.9</v>
+        <v>3047.65</v>
       </c>
       <c r="N31" t="n">
-        <v>3087.4</v>
+        <v>3059.42</v>
       </c>
       <c r="O31" t="n">
-        <v>3103.9</v>
-      </c>
-      <c r="P31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q31" s="6" t="inlineStr">
+        <v>3109.1</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
@@ -3147,74 +3143,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3025.9</v>
+        <v>3041.4</v>
       </c>
       <c r="C32" t="n">
-        <v>3059.1</v>
+        <v>3048.5</v>
       </c>
       <c r="D32" t="n">
-        <v>3019.8</v>
+        <v>2993.2</v>
       </c>
       <c r="E32" t="n">
-        <v>3039.9</v>
+        <v>2999.2</v>
       </c>
       <c r="F32" t="n">
-        <v>13.5</v>
+        <v>-40.7</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0134</v>
       </c>
       <c r="H32" t="n">
-        <v>39.3</v>
+        <v>55.3</v>
       </c>
       <c r="I32" t="n">
-        <v>2981.6</v>
+        <v>2980.5</v>
       </c>
       <c r="J32" t="n">
-        <v>2974.42</v>
+        <v>3000.82</v>
       </c>
       <c r="K32" t="n">
-        <v>3005.15</v>
+        <v>3020.25</v>
       </c>
       <c r="L32" t="n">
-        <v>3035.88</v>
+        <v>3039.67</v>
       </c>
       <c r="M32" t="n">
-        <v>3047.65</v>
+        <v>3059.55</v>
       </c>
       <c r="N32" t="n">
-        <v>3059.42</v>
+        <v>3079.42</v>
       </c>
       <c r="O32" t="n">
-        <v>3109.1</v>
+        <v>3098.4</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3227,81 +3229,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3041.4</v>
+        <v>2999.6</v>
       </c>
       <c r="C33" t="n">
-        <v>3048.5</v>
+        <v>3026.7</v>
       </c>
       <c r="D33" t="n">
-        <v>2993.2</v>
+        <v>2997.9</v>
       </c>
       <c r="E33" t="n">
-        <v>2999.2</v>
+        <v>3022.1</v>
       </c>
       <c r="F33" t="n">
-        <v>-40.7</v>
+        <v>22.9</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0134</v>
+        <v>0.0076</v>
       </c>
       <c r="H33" t="n">
-        <v>55.3</v>
+        <v>28.8</v>
       </c>
       <c r="I33" t="n">
-        <v>2980.5</v>
+        <v>2937.9</v>
       </c>
       <c r="J33" t="n">
-        <v>3000.82</v>
+        <v>2933.07</v>
       </c>
       <c r="K33" t="n">
-        <v>3020.25</v>
+        <v>2971.55</v>
       </c>
       <c r="L33" t="n">
-        <v>3039.67</v>
+        <v>3010.02</v>
       </c>
       <c r="M33" t="n">
-        <v>3059.55</v>
+        <v>3026.85</v>
       </c>
       <c r="N33" t="n">
-        <v>3079.42</v>
+        <v>3043.67</v>
       </c>
       <c r="O33" t="n">
-        <v>3098.4</v>
+        <v>3103.8</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3313,74 +3309,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2999.6</v>
+        <v>3023</v>
       </c>
       <c r="C34" t="n">
-        <v>3026.7</v>
+        <v>3028.9</v>
       </c>
       <c r="D34" t="n">
-        <v>2997.9</v>
+        <v>2996</v>
       </c>
       <c r="E34" t="n">
-        <v>3022.1</v>
+        <v>3001.6</v>
       </c>
       <c r="F34" t="n">
-        <v>22.9</v>
+        <v>-20.5</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0076</v>
+        <v>-0.0068</v>
       </c>
       <c r="H34" t="n">
-        <v>28.8</v>
+        <v>32.9</v>
       </c>
       <c r="I34" t="n">
-        <v>2937.9</v>
+        <v>2969.1</v>
       </c>
       <c r="J34" t="n">
-        <v>2933.07</v>
+        <v>2998.2</v>
       </c>
       <c r="K34" t="n">
-        <v>2971.55</v>
+        <v>3007.7</v>
       </c>
       <c r="L34" t="n">
-        <v>3010.02</v>
+        <v>3017.2</v>
       </c>
       <c r="M34" t="n">
-        <v>3026.85</v>
+        <v>3036.5</v>
       </c>
       <c r="N34" t="n">
-        <v>3043.67</v>
+        <v>3055.8</v>
       </c>
       <c r="O34" t="n">
-        <v>3103.8</v>
+        <v>3055.5</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3395,79 +3397,77 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3023</v>
+        <v>3004.6</v>
       </c>
       <c r="C35" t="n">
-        <v>3028.9</v>
+        <v>3025.4</v>
       </c>
       <c r="D35" t="n">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="E35" t="n">
-        <v>3001.6</v>
+        <v>3014.4</v>
       </c>
       <c r="F35" t="n">
-        <v>-20.5</v>
+        <v>12.8</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0043</v>
       </c>
       <c r="H35" t="n">
-        <v>32.9</v>
+        <v>28.4</v>
       </c>
       <c r="I35" t="n">
-        <v>2969.1</v>
+        <v>2963.1</v>
       </c>
       <c r="J35" t="n">
-        <v>2998.2</v>
+        <v>2963.28</v>
       </c>
       <c r="K35" t="n">
-        <v>3007.7</v>
+        <v>2985.15</v>
       </c>
       <c r="L35" t="n">
-        <v>3017.2</v>
+        <v>3007.03</v>
       </c>
       <c r="M35" t="n">
-        <v>3036.5</v>
+        <v>3018.05</v>
       </c>
       <c r="N35" t="n">
-        <v>3055.8</v>
+        <v>3029.08</v>
       </c>
       <c r="O35" t="n">
-        <v>3055.5</v>
+        <v>3061.8</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
@@ -3481,57 +3481,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3004.6</v>
+        <v>3014.6</v>
       </c>
       <c r="C36" t="n">
-        <v>3025.4</v>
+        <v>3020.5</v>
       </c>
       <c r="D36" t="n">
-        <v>2997</v>
+        <v>3002.6</v>
       </c>
       <c r="E36" t="n">
-        <v>3014.4</v>
+        <v>3010.1</v>
       </c>
       <c r="F36" t="n">
-        <v>12.8</v>
+        <v>-4.3</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0014</v>
       </c>
       <c r="H36" t="n">
-        <v>28.4</v>
+        <v>17.9</v>
       </c>
       <c r="I36" t="n">
-        <v>2963.1</v>
+        <v>2968.6</v>
       </c>
       <c r="J36" t="n">
-        <v>2963.28</v>
+        <v>2987.6</v>
       </c>
       <c r="K36" t="n">
-        <v>2985.15</v>
+        <v>3000.2</v>
       </c>
       <c r="L36" t="n">
-        <v>3007.03</v>
+        <v>3012.8</v>
       </c>
       <c r="M36" t="n">
-        <v>3018.05</v>
+        <v>3028.6</v>
       </c>
       <c r="N36" t="n">
-        <v>3029.08</v>
+        <v>3044.4</v>
       </c>
       <c r="O36" t="n">
-        <v>3061.8</v>
+        <v>3053.8</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3544,13 +3544,11 @@
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3565,57 +3563,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3014.6</v>
+        <v>3016.9</v>
       </c>
       <c r="C37" t="n">
-        <v>3020.5</v>
+        <v>3024.2</v>
       </c>
       <c r="D37" t="n">
-        <v>3002.6</v>
+        <v>3002.1</v>
       </c>
       <c r="E37" t="n">
-        <v>3010.1</v>
+        <v>3019</v>
       </c>
       <c r="F37" t="n">
-        <v>-4.3</v>
+        <v>8.9</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0014</v>
+        <v>0.003</v>
       </c>
       <c r="H37" t="n">
-        <v>17.9</v>
+        <v>22.1</v>
       </c>
       <c r="I37" t="n">
-        <v>2968.6</v>
+        <v>2984.7</v>
       </c>
       <c r="J37" t="n">
-        <v>2987.6</v>
+        <v>2991.48</v>
       </c>
       <c r="K37" t="n">
-        <v>3000.2</v>
+        <v>3001.15</v>
       </c>
       <c r="L37" t="n">
-        <v>3012.8</v>
+        <v>3010.83</v>
       </c>
       <c r="M37" t="n">
-        <v>3028.6</v>
+        <v>3019.05</v>
       </c>
       <c r="N37" t="n">
-        <v>3044.4</v>
+        <v>3027.28</v>
       </c>
       <c r="O37" t="n">
-        <v>3053.8</v>
+        <v>3038.4</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3628,11 +3626,13 @@
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3647,76 +3647,80 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3016.9</v>
+        <v>3019.6</v>
       </c>
       <c r="C38" t="n">
-        <v>3024.2</v>
+        <v>3025.5</v>
       </c>
       <c r="D38" t="n">
-        <v>3002.1</v>
+        <v>2976.6</v>
       </c>
       <c r="E38" t="n">
-        <v>3019</v>
+        <v>2977.5</v>
       </c>
       <c r="F38" t="n">
-        <v>8.9</v>
+        <v>-41.5</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0137</v>
       </c>
       <c r="H38" t="n">
-        <v>22.1</v>
+        <v>48.9</v>
       </c>
       <c r="I38" t="n">
-        <v>2984.7</v>
+        <v>2980</v>
       </c>
       <c r="J38" t="n">
-        <v>2991.48</v>
+        <v>2999.83</v>
       </c>
       <c r="K38" t="n">
-        <v>3001.15</v>
+        <v>3007.95</v>
       </c>
       <c r="L38" t="n">
-        <v>3010.83</v>
+        <v>3016.08</v>
       </c>
       <c r="M38" t="n">
-        <v>3019.05</v>
+        <v>3030.05</v>
       </c>
       <c r="N38" t="n">
-        <v>3027.28</v>
+        <v>3044.02</v>
       </c>
       <c r="O38" t="n">
-        <v>3038.4</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+        <v>3046.3</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3731,74 +3735,70 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3019.6</v>
+        <v>2971</v>
       </c>
       <c r="C39" t="n">
-        <v>3025.5</v>
+        <v>2982.5</v>
       </c>
       <c r="D39" t="n">
-        <v>2976.6</v>
+        <v>2946.1</v>
       </c>
       <c r="E39" t="n">
-        <v>2977.5</v>
+        <v>2958.7</v>
       </c>
       <c r="F39" t="n">
-        <v>-41.5</v>
+        <v>-18.8</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0063</v>
       </c>
       <c r="H39" t="n">
-        <v>48.9</v>
+        <v>36.4</v>
       </c>
       <c r="I39" t="n">
-        <v>2980</v>
+        <v>2927.7</v>
       </c>
       <c r="J39" t="n">
-        <v>2999.83</v>
+        <v>2916.83</v>
       </c>
       <c r="K39" t="n">
-        <v>3007.95</v>
+        <v>2953.05</v>
       </c>
       <c r="L39" t="n">
-        <v>3016.08</v>
+        <v>2989.28</v>
       </c>
       <c r="M39" t="n">
-        <v>3030.05</v>
+        <v>3001.95</v>
       </c>
       <c r="N39" t="n">
-        <v>3044.02</v>
+        <v>3014.62</v>
       </c>
       <c r="O39" t="n">
-        <v>3046.3</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
+        <v>3074.4</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3817,72 +3817,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2971</v>
+        <v>2958</v>
       </c>
       <c r="C40" t="n">
-        <v>2982.5</v>
+        <v>2964.6</v>
       </c>
       <c r="D40" t="n">
-        <v>2946.1</v>
+        <v>2918.9</v>
       </c>
       <c r="E40" t="n">
-        <v>2958.7</v>
+        <v>2924.7</v>
       </c>
       <c r="F40" t="n">
-        <v>-18.8</v>
+        <v>-34</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0115</v>
       </c>
       <c r="H40" t="n">
-        <v>36.4</v>
+        <v>45.7</v>
       </c>
       <c r="I40" t="n">
-        <v>2927.7</v>
+        <v>2909.7</v>
       </c>
       <c r="J40" t="n">
-        <v>2916.83</v>
+        <v>2919.5</v>
       </c>
       <c r="K40" t="n">
-        <v>2953.05</v>
+        <v>2940.5</v>
       </c>
       <c r="L40" t="n">
-        <v>2989.28</v>
+        <v>2961.5</v>
       </c>
       <c r="M40" t="n">
-        <v>3001.95</v>
+        <v>2976.9</v>
       </c>
       <c r="N40" t="n">
-        <v>3014.62</v>
+        <v>2992.3</v>
       </c>
       <c r="O40" t="n">
-        <v>3074.4</v>
+        <v>3018.9</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3906,75 +3904,75 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2958</v>
+        <v>2926.4</v>
       </c>
       <c r="C41" t="n">
-        <v>2964.6</v>
+        <v>2962.5</v>
       </c>
       <c r="D41" t="n">
-        <v>2918.9</v>
+        <v>2914.5</v>
       </c>
       <c r="E41" t="n">
-        <v>2924.7</v>
+        <v>2958.8</v>
       </c>
       <c r="F41" t="n">
-        <v>-34</v>
+        <v>34.1</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0.0117</v>
       </c>
       <c r="H41" t="n">
-        <v>45.7</v>
+        <v>48</v>
       </c>
       <c r="I41" t="n">
-        <v>2909.7</v>
+        <v>2873.2</v>
       </c>
       <c r="J41" t="n">
-        <v>2919.5</v>
+        <v>2870.47</v>
       </c>
       <c r="K41" t="n">
-        <v>2940.5</v>
+        <v>2901.85</v>
       </c>
       <c r="L41" t="n">
-        <v>2961.5</v>
+        <v>2933.22</v>
       </c>
       <c r="M41" t="n">
-        <v>2976.9</v>
+        <v>2947.55</v>
       </c>
       <c r="N41" t="n">
-        <v>2992.3</v>
+        <v>2961.88</v>
       </c>
       <c r="O41" t="n">
-        <v>3018.9</v>
+        <v>3010.3</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
@@ -3983,55 +3981,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2926.4</v>
+        <v>2957.6</v>
       </c>
       <c r="C42" t="n">
-        <v>2962.5</v>
+        <v>2983.3</v>
       </c>
       <c r="D42" t="n">
-        <v>2914.5</v>
+        <v>2949.9</v>
       </c>
       <c r="E42" t="n">
-        <v>2958.8</v>
+        <v>2969.7</v>
       </c>
       <c r="F42" t="n">
-        <v>34.1</v>
+        <v>10.9</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0117</v>
+        <v>0.0037</v>
       </c>
       <c r="H42" t="n">
-        <v>48</v>
+        <v>33.4</v>
       </c>
       <c r="I42" t="n">
-        <v>2873.2</v>
+        <v>2866.5</v>
       </c>
       <c r="J42" t="n">
-        <v>2870.47</v>
+        <v>2920.95</v>
       </c>
       <c r="K42" t="n">
-        <v>2901.85</v>
+        <v>2934.8</v>
       </c>
       <c r="L42" t="n">
-        <v>2933.22</v>
+        <v>2948.65</v>
       </c>
       <c r="M42" t="n">
-        <v>2947.55</v>
+        <v>2982.8</v>
       </c>
       <c r="N42" t="n">
-        <v>2961.88</v>
+        <v>3016.95</v>
       </c>
       <c r="O42" t="n">
-        <v>3010.3</v>
+        <v>3010.5</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4042,21 +4044,19 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="10" t="inlineStr">
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
@@ -4067,57 +4067,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2957.6</v>
+        <v>2967.9</v>
       </c>
       <c r="C43" t="n">
-        <v>2983.3</v>
+        <v>2979.3</v>
       </c>
       <c r="D43" t="n">
-        <v>2949.9</v>
+        <v>2949.5</v>
       </c>
       <c r="E43" t="n">
-        <v>2969.7</v>
+        <v>2976.6</v>
       </c>
       <c r="F43" t="n">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0023</v>
       </c>
       <c r="H43" t="n">
-        <v>33.4</v>
+        <v>29.8</v>
       </c>
       <c r="I43" t="n">
-        <v>2866.5</v>
+        <v>2916.5</v>
       </c>
       <c r="J43" t="n">
-        <v>2920.95</v>
+        <v>2937.85</v>
       </c>
       <c r="K43" t="n">
-        <v>2934.8</v>
+        <v>2953</v>
       </c>
       <c r="L43" t="n">
-        <v>2948.65</v>
+        <v>2968.15</v>
       </c>
       <c r="M43" t="n">
-        <v>2982.8</v>
+        <v>2986.4</v>
       </c>
       <c r="N43" t="n">
-        <v>3016.95</v>
+        <v>3004.65</v>
       </c>
       <c r="O43" t="n">
-        <v>3010.5</v>
+        <v>3016.7</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4125,18 +4125,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4151,57 +4151,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2967.9</v>
+        <v>2974.7</v>
       </c>
       <c r="C44" t="n">
-        <v>2979.3</v>
+        <v>2977.9</v>
       </c>
       <c r="D44" t="n">
-        <v>2949.5</v>
+        <v>2954.7</v>
       </c>
       <c r="E44" t="n">
-        <v>2976.6</v>
+        <v>2963.6</v>
       </c>
       <c r="F44" t="n">
-        <v>6.9</v>
+        <v>-13</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0044</v>
       </c>
       <c r="H44" t="n">
-        <v>29.8</v>
+        <v>23.2</v>
       </c>
       <c r="I44" t="n">
-        <v>2916.5</v>
+        <v>2919.7</v>
       </c>
       <c r="J44" t="n">
-        <v>2937.85</v>
+        <v>2952.9</v>
       </c>
       <c r="K44" t="n">
-        <v>2953</v>
+        <v>2961.7</v>
       </c>
       <c r="L44" t="n">
-        <v>2968.15</v>
+        <v>2970.5</v>
       </c>
       <c r="M44" t="n">
-        <v>2986.4</v>
+        <v>2991.5</v>
       </c>
       <c r="N44" t="n">
-        <v>3004.65</v>
+        <v>3012.5</v>
       </c>
       <c r="O44" t="n">
-        <v>3016.7</v>
+        <v>3009.1</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4211,12 +4211,12 @@
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4242,63 +4242,67 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2974.7</v>
+        <v>2963.1</v>
       </c>
       <c r="C45" t="n">
-        <v>2977.9</v>
+        <v>2966.2</v>
       </c>
       <c r="D45" t="n">
-        <v>2954.7</v>
+        <v>2919.4</v>
       </c>
       <c r="E45" t="n">
-        <v>2963.6</v>
+        <v>2923</v>
       </c>
       <c r="F45" t="n">
-        <v>-13</v>
+        <v>-40.6</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0137</v>
       </c>
       <c r="H45" t="n">
-        <v>23.2</v>
+        <v>46.8</v>
       </c>
       <c r="I45" t="n">
-        <v>2919.7</v>
+        <v>2931.5</v>
       </c>
       <c r="J45" t="n">
-        <v>2952.9</v>
+        <v>2939.05</v>
       </c>
       <c r="K45" t="n">
-        <v>2961.7</v>
+        <v>2952</v>
       </c>
       <c r="L45" t="n">
-        <v>2970.5</v>
+        <v>2964.95</v>
       </c>
       <c r="M45" t="n">
-        <v>2991.5</v>
+        <v>2975.2</v>
       </c>
       <c r="N45" t="n">
-        <v>3012.5</v>
+        <v>2985.45</v>
       </c>
       <c r="O45" t="n">
-        <v>3009.1</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
+        <v>3001.1</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4317,76 +4321,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2963.1</v>
+        <v>2923.1</v>
       </c>
       <c r="C46" t="n">
-        <v>2966.2</v>
+        <v>2933.8</v>
       </c>
       <c r="D46" t="n">
-        <v>2919.4</v>
+        <v>2887.8</v>
       </c>
       <c r="E46" t="n">
-        <v>2923</v>
+        <v>2893.4</v>
       </c>
       <c r="F46" t="n">
-        <v>-40.6</v>
+        <v>-29.6</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0137</v>
+        <v>-0.0101</v>
       </c>
       <c r="H46" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="I46" t="n">
-        <v>2931.5</v>
+        <v>2872.6</v>
       </c>
       <c r="J46" t="n">
-        <v>2939.05</v>
+        <v>2866.3</v>
       </c>
       <c r="K46" t="n">
-        <v>2952</v>
+        <v>2899.6</v>
       </c>
       <c r="L46" t="n">
-        <v>2964.95</v>
+        <v>2932.9</v>
       </c>
       <c r="M46" t="n">
-        <v>2975.2</v>
+        <v>2946.4</v>
       </c>
       <c r="N46" t="n">
-        <v>2985.45</v>
+        <v>2959.9</v>
       </c>
       <c r="O46" t="n">
-        <v>3001.1</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
+        <v>3013</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4410,50 +4406,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2923.1</v>
+        <v>2890.9</v>
       </c>
       <c r="C47" t="n">
-        <v>2933.8</v>
+        <v>2929.8</v>
       </c>
       <c r="D47" t="n">
-        <v>2887.8</v>
+        <v>2887.6</v>
       </c>
       <c r="E47" t="n">
-        <v>2893.4</v>
+        <v>2904.5</v>
       </c>
       <c r="F47" t="n">
-        <v>-29.6</v>
+        <v>11.1</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0101</v>
+        <v>0.0038</v>
       </c>
       <c r="H47" t="n">
-        <v>46</v>
+        <v>42.2</v>
       </c>
       <c r="I47" t="n">
-        <v>2872.6</v>
+        <v>2841.8</v>
       </c>
       <c r="J47" t="n">
-        <v>2866.3</v>
+        <v>2838.7</v>
       </c>
       <c r="K47" t="n">
-        <v>2899.6</v>
+        <v>2870.4</v>
       </c>
       <c r="L47" t="n">
-        <v>2932.9</v>
+        <v>2902.1</v>
       </c>
       <c r="M47" t="n">
-        <v>2946.4</v>
+        <v>2916.4</v>
       </c>
       <c r="N47" t="n">
-        <v>2959.9</v>
+        <v>2930.7</v>
       </c>
       <c r="O47" t="n">
-        <v>3013</v>
+        <v>2979.8</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4461,18 +4457,18 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R47" s="6" t="n">
+        <v/>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4485,55 +4481,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2890.9</v>
+        <v>2892.7</v>
       </c>
       <c r="C48" t="n">
-        <v>2929.8</v>
+        <v>2913.5</v>
       </c>
       <c r="D48" t="n">
-        <v>2887.6</v>
+        <v>2884.3</v>
       </c>
       <c r="E48" t="n">
-        <v>2904.5</v>
+        <v>2894.1</v>
       </c>
       <c r="F48" t="n">
-        <v>11.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0036</v>
       </c>
       <c r="H48" t="n">
-        <v>42.2</v>
+        <v>29.2</v>
       </c>
       <c r="I48" t="n">
-        <v>2841.8</v>
+        <v>2845.4</v>
       </c>
       <c r="J48" t="n">
-        <v>2838.7</v>
+        <v>2860.2</v>
       </c>
       <c r="K48" t="n">
-        <v>2870.4</v>
+        <v>2883.4</v>
       </c>
       <c r="L48" t="n">
-        <v>2902.1</v>
+        <v>2906.6</v>
       </c>
       <c r="M48" t="n">
-        <v>2916.4</v>
+        <v>2925.6</v>
       </c>
       <c r="N48" t="n">
-        <v>2930.7</v>
+        <v>2944.6</v>
       </c>
       <c r="O48" t="n">
-        <v>2979.8</v>
+        <v>2972</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4541,18 +4541,18 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4565,59 +4565,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2892.7</v>
+        <v>2896.4</v>
       </c>
       <c r="C49" t="n">
-        <v>2913.5</v>
+        <v>2896.5</v>
       </c>
       <c r="D49" t="n">
-        <v>2884.3</v>
+        <v>2862.7</v>
       </c>
       <c r="E49" t="n">
-        <v>2894.1</v>
+        <v>2873.1</v>
       </c>
       <c r="F49" t="n">
-        <v>-10.4</v>
+        <v>-21</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0073</v>
       </c>
       <c r="H49" t="n">
-        <v>29.2</v>
+        <v>33.8</v>
       </c>
       <c r="I49" t="n">
-        <v>2845.4</v>
+        <v>2855.1</v>
       </c>
       <c r="J49" t="n">
-        <v>2860.2</v>
+        <v>2862.5</v>
       </c>
       <c r="K49" t="n">
-        <v>2883.4</v>
+        <v>2879.5</v>
       </c>
       <c r="L49" t="n">
-        <v>2906.6</v>
+        <v>2896.5</v>
       </c>
       <c r="M49" t="n">
-        <v>2925.6</v>
+        <v>2908.7</v>
       </c>
       <c r="N49" t="n">
-        <v>2944.6</v>
+        <v>2920.9</v>
       </c>
       <c r="O49" t="n">
-        <v>2972</v>
+        <v>2942.7</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4630,7 +4626,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4654,69 +4650,73 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2896.4</v>
+        <v>2875.1</v>
       </c>
       <c r="C50" t="n">
-        <v>2896.5</v>
+        <v>2892.5</v>
       </c>
       <c r="D50" t="n">
-        <v>2862.7</v>
+        <v>2831.9</v>
       </c>
       <c r="E50" t="n">
-        <v>2873.1</v>
+        <v>2861.7</v>
       </c>
       <c r="F50" t="n">
-        <v>-21</v>
+        <v>-11.4</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.004</v>
       </c>
       <c r="H50" t="n">
-        <v>33.8</v>
+        <v>60.6</v>
       </c>
       <c r="I50" t="n">
-        <v>2855.1</v>
+        <v>2828.9</v>
       </c>
       <c r="J50" t="n">
-        <v>2862.5</v>
+        <v>2836.05</v>
       </c>
       <c r="K50" t="n">
-        <v>2879.5</v>
+        <v>2856.2</v>
       </c>
       <c r="L50" t="n">
-        <v>2896.5</v>
+        <v>2876.35</v>
       </c>
       <c r="M50" t="n">
-        <v>2908.7</v>
+        <v>2890</v>
       </c>
       <c r="N50" t="n">
-        <v>2920.9</v>
+        <v>2903.65</v>
       </c>
       <c r="O50" t="n">
-        <v>2942.7</v>
+        <v>2930.3</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S50" s="7" t="inlineStr">
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4734,74 +4734,70 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2875.1</v>
+        <v>2861.2</v>
       </c>
       <c r="C51" t="n">
-        <v>2892.5</v>
+        <v>2904.6</v>
       </c>
       <c r="D51" t="n">
-        <v>2831.9</v>
+        <v>2859.3</v>
       </c>
       <c r="E51" t="n">
-        <v>2861.7</v>
+        <v>2875.9</v>
       </c>
       <c r="F51" t="n">
-        <v>-11.4</v>
+        <v>14.2</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.005</v>
       </c>
       <c r="H51" t="n">
-        <v>60.6</v>
+        <v>45.3</v>
       </c>
       <c r="I51" t="n">
-        <v>2828.9</v>
+        <v>2771.3</v>
       </c>
       <c r="J51" t="n">
-        <v>2836.05</v>
+        <v>2800.85</v>
       </c>
       <c r="K51" t="n">
-        <v>2856.2</v>
+        <v>2831.4</v>
       </c>
       <c r="L51" t="n">
-        <v>2876.35</v>
+        <v>2861.95</v>
       </c>
       <c r="M51" t="n">
-        <v>2890</v>
+        <v>2892</v>
       </c>
       <c r="N51" t="n">
-        <v>2903.65</v>
+        <v>2922.05</v>
       </c>
       <c r="O51" t="n">
-        <v>2930.3</v>
+        <v>2953.1</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U51" s="8" t="n">
         <v/>
       </c>
@@ -4813,55 +4809,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2861.2</v>
+        <v>2870.5</v>
       </c>
       <c r="C52" t="n">
-        <v>2904.6</v>
+        <v>2883</v>
       </c>
       <c r="D52" t="n">
-        <v>2859.3</v>
+        <v>2856.9</v>
       </c>
       <c r="E52" t="n">
-        <v>2875.9</v>
+        <v>2873.23</v>
       </c>
       <c r="F52" t="n">
-        <v>14.2</v>
+        <v>-2.67</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0009</v>
       </c>
       <c r="H52" t="n">
-        <v>45.3</v>
+        <v>26.1</v>
       </c>
       <c r="I52" t="n">
-        <v>2771.3</v>
+        <v>2814</v>
       </c>
       <c r="J52" t="n">
-        <v>2800.85</v>
+        <v>2827.57</v>
       </c>
       <c r="K52" t="n">
-        <v>2831.4</v>
+        <v>2853.25</v>
       </c>
       <c r="L52" t="n">
-        <v>2861.95</v>
+        <v>2878.92</v>
       </c>
       <c r="M52" t="n">
-        <v>2892</v>
+        <v>2898.55</v>
       </c>
       <c r="N52" t="n">
-        <v>2922.05</v>
+        <v>2918.17</v>
       </c>
       <c r="O52" t="n">
-        <v>2953.1</v>
+        <v>2949.9</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4874,13 +4874,11 @@
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4893,59 +4891,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2870.5</v>
+        <v>2879.5</v>
       </c>
       <c r="C53" t="n">
-        <v>2883</v>
+        <v>2907.3</v>
       </c>
       <c r="D53" t="n">
-        <v>2856.9</v>
+        <v>2876.6</v>
       </c>
       <c r="E53" t="n">
-        <v>2873.23</v>
+        <v>2897.4</v>
       </c>
       <c r="F53" t="n">
-        <v>-2.67</v>
+        <v>24.17</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>26.1</v>
+        <v>30.7</v>
       </c>
       <c r="I53" t="n">
-        <v>2814</v>
+        <v>2830.8</v>
       </c>
       <c r="J53" t="n">
-        <v>2827.57</v>
+        <v>2848.77</v>
       </c>
       <c r="K53" t="n">
-        <v>2853.25</v>
+        <v>2860.18</v>
       </c>
       <c r="L53" t="n">
-        <v>2878.92</v>
+        <v>2871.59</v>
       </c>
       <c r="M53" t="n">
-        <v>2898.55</v>
+        <v>2886.28</v>
       </c>
       <c r="N53" t="n">
-        <v>2918.17</v>
+        <v>2900.97</v>
       </c>
       <c r="O53" t="n">
-        <v>2949.9</v>
+        <v>2909.1</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4958,14 +4952,18 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4975,55 +4973,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2879.5</v>
+        <v>2897.8</v>
       </c>
       <c r="C54" t="n">
-        <v>2907.3</v>
+        <v>2931.2</v>
       </c>
       <c r="D54" t="n">
-        <v>2876.6</v>
+        <v>2884.2</v>
       </c>
       <c r="E54" t="n">
-        <v>2897.4</v>
+        <v>2914.1</v>
       </c>
       <c r="F54" t="n">
-        <v>24.17</v>
+        <v>16.7</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0058</v>
       </c>
       <c r="H54" t="n">
-        <v>30.7</v>
+        <v>47</v>
       </c>
       <c r="I54" t="n">
-        <v>2830.8</v>
+        <v>2845.9</v>
       </c>
       <c r="J54" t="n">
-        <v>2848.77</v>
+        <v>2869.42</v>
       </c>
       <c r="K54" t="n">
-        <v>2860.18</v>
+        <v>2882.05</v>
       </c>
       <c r="L54" t="n">
-        <v>2871.59</v>
+        <v>2894.67</v>
       </c>
       <c r="M54" t="n">
-        <v>2886.28</v>
+        <v>2912.75</v>
       </c>
       <c r="N54" t="n">
-        <v>2900.97</v>
+        <v>2930.82</v>
       </c>
       <c r="O54" t="n">
-        <v>2909.1</v>
+        <v>2938</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5034,19 +5036,19 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="10" t="inlineStr">
+      <c r="S54" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="V54" s="8" t="n">
@@ -5066,74 +5068,74 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2897.8</v>
+        <v>2912</v>
       </c>
       <c r="C55" t="n">
-        <v>2931.2</v>
+        <v>2915.3</v>
       </c>
       <c r="D55" t="n">
-        <v>2884.2</v>
+        <v>2858.8</v>
       </c>
       <c r="E55" t="n">
-        <v>2914.1</v>
+        <v>2860.2</v>
       </c>
       <c r="F55" t="n">
-        <v>16.7</v>
+        <v>-53.9</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0185</v>
       </c>
       <c r="H55" t="n">
-        <v>47</v>
+        <v>56.5</v>
       </c>
       <c r="I55" t="n">
-        <v>2845.9</v>
+        <v>2837.2</v>
       </c>
       <c r="J55" t="n">
-        <v>2869.42</v>
+        <v>2870.3</v>
       </c>
       <c r="K55" t="n">
-        <v>2882.05</v>
+        <v>2890.6</v>
       </c>
       <c r="L55" t="n">
-        <v>2894.67</v>
+        <v>2910.9</v>
       </c>
       <c r="M55" t="n">
-        <v>2912.75</v>
+        <v>2937.6</v>
       </c>
       <c r="N55" t="n">
-        <v>2930.82</v>
+        <v>2964.3</v>
       </c>
       <c r="O55" t="n">
-        <v>2938</v>
+        <v>2978.2</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5143,76 +5145,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2912</v>
+        <v>2860.7</v>
       </c>
       <c r="C56" t="n">
-        <v>2915.3</v>
+        <v>2862.4</v>
       </c>
       <c r="D56" t="n">
-        <v>2858.8</v>
+        <v>2829.9</v>
       </c>
       <c r="E56" t="n">
-        <v>2860.2</v>
+        <v>2856.8</v>
       </c>
       <c r="F56" t="n">
-        <v>-53.9</v>
+        <v>-3.4</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0012</v>
       </c>
       <c r="H56" t="n">
-        <v>56.5</v>
+        <v>32.5</v>
       </c>
       <c r="I56" t="n">
-        <v>2837.2</v>
+        <v>2802.3</v>
       </c>
       <c r="J56" t="n">
-        <v>2870.3</v>
+        <v>2790.27</v>
       </c>
       <c r="K56" t="n">
-        <v>2890.6</v>
+        <v>2831.95</v>
       </c>
       <c r="L56" t="n">
-        <v>2910.9</v>
+        <v>2873.62</v>
       </c>
       <c r="M56" t="n">
-        <v>2937.6</v>
+        <v>2888.45</v>
       </c>
       <c r="N56" t="n">
-        <v>2964.3</v>
+        <v>2903.27</v>
       </c>
       <c r="O56" t="n">
-        <v>2978.2</v>
+        <v>2971.8</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q56" s="6" t="n">
+        <v/>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5234,50 +5230,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2860.7</v>
+        <v>2854.4</v>
       </c>
       <c r="C57" t="n">
-        <v>2862.4</v>
+        <v>2874.1</v>
       </c>
       <c r="D57" t="n">
-        <v>2829.9</v>
+        <v>2843</v>
       </c>
       <c r="E57" t="n">
-        <v>2856.8</v>
+        <v>2859.3</v>
       </c>
       <c r="F57" t="n">
-        <v>-3.4</v>
+        <v>2.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="H57" t="n">
-        <v>32.5</v>
+        <v>31.1</v>
       </c>
       <c r="I57" t="n">
-        <v>2802.3</v>
+        <v>2797.4</v>
       </c>
       <c r="J57" t="n">
-        <v>2790.27</v>
+        <v>2829.63</v>
       </c>
       <c r="K57" t="n">
-        <v>2831.95</v>
+        <v>2840.55</v>
       </c>
       <c r="L57" t="n">
-        <v>2873.62</v>
+        <v>2851.47</v>
       </c>
       <c r="M57" t="n">
-        <v>2888.45</v>
+        <v>2873.05</v>
       </c>
       <c r="N57" t="n">
-        <v>2903.27</v>
+        <v>2894.63</v>
       </c>
       <c r="O57" t="n">
-        <v>2971.8</v>
+        <v>2894.9</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5285,19 +5281,19 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
@@ -5309,74 +5305,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2854.4</v>
+        <v>2857.7</v>
       </c>
       <c r="C58" t="n">
-        <v>2874.1</v>
+        <v>2858.8</v>
       </c>
       <c r="D58" t="n">
-        <v>2843</v>
+        <v>2826.8</v>
       </c>
       <c r="E58" t="n">
-        <v>2859.3</v>
+        <v>2840.1</v>
       </c>
       <c r="F58" t="n">
-        <v>2.5</v>
+        <v>-19.2</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0067</v>
       </c>
       <c r="H58" t="n">
-        <v>31.1</v>
+        <v>32</v>
       </c>
       <c r="I58" t="n">
-        <v>2797.4</v>
+        <v>2811.9</v>
       </c>
       <c r="J58" t="n">
-        <v>2829.63</v>
+        <v>2828.57</v>
       </c>
       <c r="K58" t="n">
-        <v>2840.55</v>
+        <v>2843.75</v>
       </c>
       <c r="L58" t="n">
-        <v>2851.47</v>
+        <v>2858.93</v>
       </c>
       <c r="M58" t="n">
-        <v>2873.05</v>
+        <v>2874.85</v>
       </c>
       <c r="N58" t="n">
-        <v>2894.63</v>
+        <v>2890.78</v>
       </c>
       <c r="O58" t="n">
-        <v>2894.9</v>
+        <v>2905.2</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5389,74 +5391,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2857.7</v>
+        <v>2839.6</v>
       </c>
       <c r="C59" t="n">
-        <v>2858.8</v>
+        <v>2851.8</v>
       </c>
       <c r="D59" t="n">
-        <v>2826.8</v>
+        <v>2811.9</v>
       </c>
       <c r="E59" t="n">
-        <v>2840.1</v>
+        <v>2829.2</v>
       </c>
       <c r="F59" t="n">
-        <v>-19.2</v>
+        <v>-10.9</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0067</v>
+        <v>-0.0038</v>
       </c>
       <c r="H59" t="n">
-        <v>32</v>
+        <v>39.9</v>
       </c>
       <c r="I59" t="n">
-        <v>2811.9</v>
+        <v>2794.8</v>
       </c>
       <c r="J59" t="n">
-        <v>2828.57</v>
+        <v>2806.75</v>
       </c>
       <c r="K59" t="n">
-        <v>2843.75</v>
+        <v>2824.1</v>
       </c>
       <c r="L59" t="n">
-        <v>2858.93</v>
+        <v>2841.45</v>
       </c>
       <c r="M59" t="n">
-        <v>2874.85</v>
+        <v>2856.1</v>
       </c>
       <c r="N59" t="n">
-        <v>2890.78</v>
+        <v>2870.75</v>
       </c>
       <c r="O59" t="n">
-        <v>2905.2</v>
+        <v>2890.8</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q59" s="6" t="n">
+        <v/>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S59" s="7" t="inlineStr">
+      <c r="S59" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5480,50 +5476,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2839.6</v>
+        <v>2831.6</v>
       </c>
       <c r="C60" t="n">
-        <v>2851.8</v>
+        <v>2853.8</v>
       </c>
       <c r="D60" t="n">
-        <v>2811.9</v>
+        <v>2812.8</v>
       </c>
       <c r="E60" t="n">
-        <v>2829.2</v>
+        <v>2817.5</v>
       </c>
       <c r="F60" t="n">
-        <v>-10.9</v>
+        <v>-11.7</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0041</v>
       </c>
       <c r="H60" t="n">
-        <v>39.9</v>
+        <v>41</v>
       </c>
       <c r="I60" t="n">
-        <v>2794.8</v>
+        <v>2772</v>
       </c>
       <c r="J60" t="n">
-        <v>2806.75</v>
+        <v>2787.97</v>
       </c>
       <c r="K60" t="n">
-        <v>2824.1</v>
+        <v>2809.25</v>
       </c>
       <c r="L60" t="n">
-        <v>2841.45</v>
+        <v>2830.52</v>
       </c>
       <c r="M60" t="n">
-        <v>2856.1</v>
+        <v>2849.15</v>
       </c>
       <c r="N60" t="n">
-        <v>2870.75</v>
+        <v>2867.78</v>
       </c>
       <c r="O60" t="n">
-        <v>2890.8</v>
+        <v>2891.7</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5536,13 +5532,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S60" s="7" t="inlineStr">
+      <c r="S60" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T60" s="8" t="n">
-        <v/>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5555,55 +5553,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2831.6</v>
+        <v>2819.6</v>
       </c>
       <c r="C61" t="n">
-        <v>2853.8</v>
+        <v>2843.3</v>
       </c>
       <c r="D61" t="n">
-        <v>2812.8</v>
+        <v>2791.5</v>
       </c>
       <c r="E61" t="n">
-        <v>2817.5</v>
+        <v>2826.9</v>
       </c>
       <c r="F61" t="n">
-        <v>-11.7</v>
+        <v>9.4</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0041</v>
+        <v>0.0033</v>
       </c>
       <c r="H61" t="n">
-        <v>41</v>
+        <v>51.8</v>
       </c>
       <c r="I61" t="n">
-        <v>2772</v>
+        <v>2771.8</v>
       </c>
       <c r="J61" t="n">
-        <v>2787.97</v>
+        <v>2768.6</v>
       </c>
       <c r="K61" t="n">
-        <v>2809.25</v>
+        <v>2797</v>
       </c>
       <c r="L61" t="n">
-        <v>2830.52</v>
+        <v>2825.4</v>
       </c>
       <c r="M61" t="n">
-        <v>2849.15</v>
+        <v>2838</v>
       </c>
       <c r="N61" t="n">
-        <v>2867.78</v>
+        <v>2850.6</v>
       </c>
       <c r="O61" t="n">
-        <v>2891.7</v>
+        <v>2894.8</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5613,12 +5615,12 @@
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T61" s="8" t="inlineStr">
@@ -5639,57 +5641,57 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2819.6</v>
+        <v>2829</v>
       </c>
       <c r="C62" t="n">
-        <v>2843.3</v>
+        <v>2875.3</v>
       </c>
       <c r="D62" t="n">
-        <v>2791.5</v>
+        <v>2827.7</v>
       </c>
       <c r="E62" t="n">
-        <v>2826.9</v>
+        <v>2850.9</v>
       </c>
       <c r="F62" t="n">
-        <v>9.4</v>
+        <v>24</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>51.8</v>
+        <v>47.6</v>
       </c>
       <c r="I62" t="n">
-        <v>2771.8</v>
+        <v>2739.7</v>
       </c>
       <c r="J62" t="n">
-        <v>2768.6</v>
+        <v>2779.85</v>
       </c>
       <c r="K62" t="n">
-        <v>2797</v>
+        <v>2801</v>
       </c>
       <c r="L62" t="n">
-        <v>2825.4</v>
+        <v>2822.15</v>
       </c>
       <c r="M62" t="n">
-        <v>2838</v>
+        <v>2852.8</v>
       </c>
       <c r="N62" t="n">
-        <v>2850.6</v>
+        <v>2883.45</v>
       </c>
       <c r="O62" t="n">
-        <v>2894.8</v>
+        <v>2895.1</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5697,19 +5699,17 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T62" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U62" s="8" t="n">
@@ -5725,57 +5725,57 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2829</v>
+        <v>2869.4</v>
       </c>
       <c r="C63" t="n">
-        <v>2875.3</v>
+        <v>2871.8</v>
       </c>
       <c r="D63" t="n">
-        <v>2827.7</v>
+        <v>2869.2</v>
       </c>
       <c r="E63" t="n">
-        <v>2850.9</v>
+        <v>2869.8</v>
       </c>
       <c r="F63" t="n">
-        <v>24</v>
+        <v>18.9</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0066</v>
       </c>
       <c r="H63" t="n">
-        <v>47.6</v>
+        <v>2.6</v>
       </c>
       <c r="I63" t="n">
-        <v>2739.7</v>
+        <v>2780.1</v>
       </c>
       <c r="J63" t="n">
-        <v>2779.85</v>
+        <v>2803</v>
       </c>
       <c r="K63" t="n">
-        <v>2801</v>
+        <v>2827.1</v>
       </c>
       <c r="L63" t="n">
-        <v>2822.15</v>
+        <v>2851.2</v>
       </c>
       <c r="M63" t="n">
-        <v>2852.8</v>
+        <v>2874.7</v>
       </c>
       <c r="N63" t="n">
-        <v>2883.45</v>
+        <v>2898.2</v>
       </c>
       <c r="O63" t="n">
-        <v>2895.1</v>
+        <v>2922.9</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5786,7 +5786,7 @@
       <c r="R63" s="6" t="n">
         <v/>
       </c>
-      <c r="S63" s="10" t="inlineStr">
+      <c r="S63" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5809,89 +5809,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>2850.6</v>
-      </c>
-      <c r="C64" t="n">
-        <v>2857</v>
-      </c>
-      <c r="D64" t="n">
-        <v>2850.6</v>
-      </c>
-      <c r="E64" t="n">
-        <v>2850.9</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="I64" t="n">
-        <v>2780.1</v>
-      </c>
-      <c r="J64" t="n">
-        <v>2803</v>
-      </c>
-      <c r="K64" t="n">
-        <v>2827.1</v>
-      </c>
-      <c r="L64" t="n">
-        <v>2851.2</v>
-      </c>
-      <c r="M64" t="n">
-        <v>2874.7</v>
-      </c>
-      <c r="N64" t="n">
-        <v>2898.2</v>
-      </c>
-      <c r="O64" t="n">
-        <v>2922.9</v>
-      </c>
-      <c r="P64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W64" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/RTY_daily.xlsx
+++ b/three_gate/analysis/RTY_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2965.8</v>
+        <v>3008.1</v>
       </c>
       <c r="C2" t="n">
-        <v>3014.9</v>
+        <v>3019.5</v>
       </c>
       <c r="D2" t="n">
-        <v>2964.3</v>
+        <v>2970.8</v>
       </c>
       <c r="E2" t="n">
-        <v>3008.4</v>
+        <v>2994</v>
       </c>
       <c r="F2" t="n">
-        <v>36.9</v>
+        <v>-14.4</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0048</v>
       </c>
       <c r="H2" t="n">
-        <v>50.6</v>
+        <v>48.7</v>
       </c>
       <c r="I2" t="n">
-        <v>2882.5</v>
+        <v>2913.7</v>
       </c>
       <c r="J2" t="n">
-        <v>2909.42</v>
+        <v>2967.2</v>
       </c>
       <c r="K2" t="n">
-        <v>2941.05</v>
+        <v>2983.1</v>
       </c>
       <c r="L2" t="n">
-        <v>2972.67</v>
+        <v>2999</v>
       </c>
       <c r="M2" t="n">
-        <v>3001.95</v>
+        <v>3033.7</v>
       </c>
       <c r="N2" t="n">
-        <v>3031.23</v>
+        <v>3068.4</v>
       </c>
       <c r="O2" t="n">
-        <v>3065.2</v>
+        <v>3065.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,18 +685,18 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -709,55 +709,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3008.1</v>
+        <v>2984.7</v>
       </c>
       <c r="C3" t="n">
-        <v>3019.5</v>
+        <v>2995.8</v>
       </c>
       <c r="D3" t="n">
-        <v>2970.8</v>
+        <v>2961.8</v>
       </c>
       <c r="E3" t="n">
-        <v>2994</v>
+        <v>2970.4</v>
       </c>
       <c r="F3" t="n">
-        <v>-14.4</v>
+        <v>-23.6</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>48.7</v>
+        <v>34</v>
       </c>
       <c r="I3" t="n">
-        <v>2913.7</v>
+        <v>2922.1</v>
       </c>
       <c r="J3" t="n">
-        <v>2967.2</v>
+        <v>2944.73</v>
       </c>
       <c r="K3" t="n">
-        <v>2983.1</v>
+        <v>2969.65</v>
       </c>
       <c r="L3" t="n">
-        <v>2999</v>
+        <v>2994.58</v>
       </c>
       <c r="M3" t="n">
-        <v>3033.7</v>
+        <v>3018.35</v>
       </c>
       <c r="N3" t="n">
-        <v>3068.4</v>
+        <v>3042.12</v>
       </c>
       <c r="O3" t="n">
-        <v>3065.5</v>
+        <v>3068.2</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -767,12 +771,12 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -791,57 +795,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2984.7</v>
+        <v>2967.2</v>
       </c>
       <c r="C4" t="n">
-        <v>2995.8</v>
+        <v>3029.8</v>
       </c>
       <c r="D4" t="n">
-        <v>2961.8</v>
+        <v>2956.2</v>
       </c>
       <c r="E4" t="n">
-        <v>2970.4</v>
+        <v>2979.9</v>
       </c>
       <c r="F4" t="n">
-        <v>-23.6</v>
+        <v>9.5</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H4" t="n">
-        <v>34</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>2922.1</v>
+        <v>2927.8</v>
       </c>
       <c r="J4" t="n">
-        <v>2944.73</v>
+        <v>2932.2</v>
       </c>
       <c r="K4" t="n">
-        <v>2969.65</v>
+        <v>2953.4</v>
       </c>
       <c r="L4" t="n">
-        <v>2994.58</v>
+        <v>2974.6</v>
       </c>
       <c r="M4" t="n">
-        <v>3018.35</v>
+        <v>2987.4</v>
       </c>
       <c r="N4" t="n">
-        <v>3042.12</v>
+        <v>3000.2</v>
       </c>
       <c r="O4" t="n">
-        <v>3068.2</v>
+        <v>3029.8</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -849,24 +853,28 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R4" s="6" t="n">
+        <v/>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
@@ -875,57 +883,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2967.2</v>
+        <v>2981.2</v>
       </c>
       <c r="C5" t="n">
-        <v>3029.8</v>
+        <v>3006.1</v>
       </c>
       <c r="D5" t="n">
-        <v>2956.2</v>
+        <v>2974.4</v>
       </c>
       <c r="E5" t="n">
-        <v>2979.9</v>
+        <v>2991.8</v>
       </c>
       <c r="F5" t="n">
-        <v>9.5</v>
+        <v>11.9</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.004</v>
       </c>
       <c r="H5" t="n">
-        <v>73.59999999999999</v>
+        <v>31.7</v>
       </c>
       <c r="I5" t="n">
-        <v>2927.8</v>
+        <v>2882.6</v>
       </c>
       <c r="J5" t="n">
-        <v>2932.2</v>
+        <v>2899.75</v>
       </c>
       <c r="K5" t="n">
-        <v>2953.4</v>
+        <v>2943.1</v>
       </c>
       <c r="L5" t="n">
-        <v>2974.6</v>
+        <v>2986.45</v>
       </c>
       <c r="M5" t="n">
-        <v>2987.4</v>
+        <v>3016.7</v>
       </c>
       <c r="N5" t="n">
-        <v>3000.2</v>
+        <v>3046.95</v>
       </c>
       <c r="O5" t="n">
-        <v>3029.8</v>
+        <v>3103.4</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -936,25 +944,19 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
@@ -970,50 +972,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2981.2</v>
+        <v>2995.3</v>
       </c>
       <c r="C6" t="n">
-        <v>3006.1</v>
+        <v>3012.8</v>
       </c>
       <c r="D6" t="n">
-        <v>2974.4</v>
+        <v>2972.7</v>
       </c>
       <c r="E6" t="n">
-        <v>2991.8</v>
+        <v>2990.7</v>
       </c>
       <c r="F6" t="n">
-        <v>11.9</v>
+        <v>-1.1</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0004</v>
       </c>
       <c r="H6" t="n">
-        <v>31.7</v>
+        <v>40.1</v>
       </c>
       <c r="I6" t="n">
-        <v>2882.6</v>
+        <v>2942.7</v>
       </c>
       <c r="J6" t="n">
-        <v>2899.75</v>
+        <v>2960.87</v>
       </c>
       <c r="K6" t="n">
-        <v>2943.1</v>
+        <v>2975.95</v>
       </c>
       <c r="L6" t="n">
-        <v>2986.45</v>
+        <v>2991.03</v>
       </c>
       <c r="M6" t="n">
-        <v>3016.7</v>
+        <v>3007.65</v>
       </c>
       <c r="N6" t="n">
-        <v>3046.95</v>
+        <v>3024.28</v>
       </c>
       <c r="O6" t="n">
-        <v>3103.4</v>
+        <v>3037.8</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1021,16 +1023,20 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1045,78 +1051,78 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2995.3</v>
+        <v>2991.7</v>
       </c>
       <c r="C7" t="n">
-        <v>3012.8</v>
+        <v>2994.8</v>
       </c>
       <c r="D7" t="n">
-        <v>2972.7</v>
+        <v>2949.3</v>
       </c>
       <c r="E7" t="n">
-        <v>2990.7</v>
+        <v>2973.5</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1</v>
+        <v>-17.2</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0058</v>
       </c>
       <c r="H7" t="n">
-        <v>40.1</v>
+        <v>45.5</v>
       </c>
       <c r="I7" t="n">
-        <v>2942.7</v>
+        <v>2932.6</v>
       </c>
       <c r="J7" t="n">
-        <v>2960.87</v>
+        <v>2949.57</v>
       </c>
       <c r="K7" t="n">
-        <v>2975.95</v>
+        <v>2970.65</v>
       </c>
       <c r="L7" t="n">
-        <v>2991.03</v>
+        <v>2991.72</v>
       </c>
       <c r="M7" t="n">
-        <v>3007.65</v>
+        <v>3010.75</v>
       </c>
       <c r="N7" t="n">
-        <v>3024.28</v>
+        <v>3029.78</v>
       </c>
       <c r="O7" t="n">
-        <v>3037.8</v>
+        <v>3052.9</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1131,79 +1137,79 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2991.7</v>
+        <v>2964.5</v>
       </c>
       <c r="C8" t="n">
-        <v>2994.8</v>
+        <v>2998.7</v>
       </c>
       <c r="D8" t="n">
-        <v>2949.3</v>
+        <v>2952.7</v>
       </c>
       <c r="E8" t="n">
-        <v>2973.5</v>
+        <v>2955.2</v>
       </c>
       <c r="F8" t="n">
-        <v>-17.2</v>
+        <v>-18.3</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0062</v>
       </c>
       <c r="H8" t="n">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="I8" t="n">
-        <v>2932.6</v>
+        <v>2903.8</v>
       </c>
       <c r="J8" t="n">
-        <v>2949.57</v>
+        <v>2928.72</v>
       </c>
       <c r="K8" t="n">
-        <v>2970.65</v>
+        <v>2950.75</v>
       </c>
       <c r="L8" t="n">
-        <v>2991.72</v>
+        <v>2972.78</v>
       </c>
       <c r="M8" t="n">
-        <v>3010.75</v>
+        <v>2996.25</v>
       </c>
       <c r="N8" t="n">
-        <v>3029.78</v>
+        <v>3019.72</v>
       </c>
       <c r="O8" t="n">
-        <v>3052.9</v>
+        <v>3040.3</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1217,57 +1223,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2964.5</v>
+        <v>2955.8</v>
       </c>
       <c r="C9" t="n">
-        <v>2998.7</v>
+        <v>2999.8</v>
       </c>
       <c r="D9" t="n">
-        <v>2952.7</v>
+        <v>2951.1</v>
       </c>
       <c r="E9" t="n">
-        <v>2955.2</v>
+        <v>2997</v>
       </c>
       <c r="F9" t="n">
-        <v>-18.3</v>
+        <v>41.8</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0141</v>
       </c>
       <c r="H9" t="n">
-        <v>46</v>
+        <v>48.7</v>
       </c>
       <c r="I9" t="n">
-        <v>2903.8</v>
+        <v>2906.7</v>
       </c>
       <c r="J9" t="n">
-        <v>2928.72</v>
+        <v>2898.95</v>
       </c>
       <c r="K9" t="n">
-        <v>2950.75</v>
+        <v>2932.2</v>
       </c>
       <c r="L9" t="n">
-        <v>2972.78</v>
+        <v>2965.45</v>
       </c>
       <c r="M9" t="n">
-        <v>2996.25</v>
+        <v>2978.2</v>
       </c>
       <c r="N9" t="n">
-        <v>3019.72</v>
+        <v>2990.95</v>
       </c>
       <c r="O9" t="n">
-        <v>3040.3</v>
+        <v>3044.7</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1275,23 +1281,23 @@
       <c r="Q9" s="6"